--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E54EDBD3-0CCD-40C4-B9AB-CB5C26D275CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463A888C-41F9-42A2-9F5C-02CB4B74A449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="1138">
   <si>
     <t>trigger</t>
   </si>
@@ -102,10 +102,3343 @@
     <t>There is a lesion measuring 1.5x1.2 cm which shows peripheral nodular enhancement in arterial phase with progressive centripetal filling and enhancement corresponding to adjacent blood pool in subsequent phase.</t>
   </si>
   <si>
-    <t xml:space="preserve">Soft tissue density is noted in right middle ear cavity involving epitympanum, mesotympanum and hypotympanum which is extending to mastoid cavity through aditus ad antrum. Tegmen tympani, ear ossicles, sinus plate, scutum and facial canal appear normal </t>
-  </si>
-  <si>
     <t>emh</t>
+  </si>
+  <si>
+    <t>Soft tissue density is noted in right middle ear cavity involving epitympanum, mesotympanum and hypotympanum which is extending to mastoid cavity through aditus ad antrum. Tegmen tympani, ear ossicles, sinus plate, scutum and facial canal appear normal.</t>
+  </si>
+  <si>
+    <t>ln</t>
+  </si>
+  <si>
+    <t>lns</t>
+  </si>
+  <si>
+    <t>tc</t>
+  </si>
+  <si>
+    <t>tcs</t>
+  </si>
+  <si>
+    <t>prox</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>masi</t>
+  </si>
+  <si>
+    <t>eth</t>
+  </si>
+  <si>
+    <t>sph</t>
+  </si>
+  <si>
+    <t>fros</t>
+  </si>
+  <si>
+    <t>eths</t>
+  </si>
+  <si>
+    <t>sphs</t>
+  </si>
+  <si>
+    <t>maxi</t>
+  </si>
+  <si>
+    <t>pess</t>
+  </si>
+  <si>
+    <t>pes</t>
+  </si>
+  <si>
+    <t>svds</t>
+  </si>
+  <si>
+    <t>ceat</t>
+  </si>
+  <si>
+    <t>cea</t>
+  </si>
+  <si>
+    <t>svd</t>
+  </si>
+  <si>
+    <t>sins</t>
+  </si>
+  <si>
+    <t>polip</t>
+  </si>
+  <si>
+    <t>ant</t>
+  </si>
+  <si>
+    <t>pos</t>
+  </si>
+  <si>
+    <t>med</t>
+  </si>
+  <si>
+    <t>lat</t>
+  </si>
+  <si>
+    <t>anty</t>
+  </si>
+  <si>
+    <t>posy</t>
+  </si>
+  <si>
+    <t>medy</t>
+  </si>
+  <si>
+    <t>laty</t>
+  </si>
+  <si>
+    <t>sup</t>
+  </si>
+  <si>
+    <t>inf</t>
+  </si>
+  <si>
+    <t>supy</t>
+  </si>
+  <si>
+    <t>infy</t>
+  </si>
+  <si>
+    <t>bll</t>
+  </si>
+  <si>
+    <t>blk</t>
+  </si>
+  <si>
+    <t>bul</t>
+  </si>
+  <si>
+    <t>blf</t>
+  </si>
+  <si>
+    <t>rll</t>
+  </si>
+  <si>
+    <t>lll</t>
+  </si>
+  <si>
+    <t>rul</t>
+  </si>
+  <si>
+    <t>lul</t>
+  </si>
+  <si>
+    <t>rml</t>
+  </si>
+  <si>
+    <t>seg</t>
+  </si>
+  <si>
+    <t>segs</t>
+  </si>
+  <si>
+    <t>apos</t>
+  </si>
+  <si>
+    <t>abs</t>
+  </si>
+  <si>
+    <t>mbs</t>
+  </si>
+  <si>
+    <t>lbs</t>
+  </si>
+  <si>
+    <t>pbs</t>
+  </si>
+  <si>
+    <t>ambs</t>
+  </si>
+  <si>
+    <t>pul</t>
+  </si>
+  <si>
+    <t>pula</t>
+  </si>
+  <si>
+    <t>htn</t>
+  </si>
+  <si>
+    <t>pulv</t>
+  </si>
+  <si>
+    <t>rt</t>
+  </si>
+  <si>
+    <t>lt</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>chd</t>
+  </si>
+  <si>
+    <t>cl</t>
+  </si>
+  <si>
+    <t>nl</t>
+  </si>
+  <si>
+    <t>ihbd</t>
+  </si>
+  <si>
+    <t>ihbr</t>
+  </si>
+  <si>
+    <t>hdn</t>
+  </si>
+  <si>
+    <t>hdun</t>
+  </si>
+  <si>
+    <t>hcp</t>
+  </si>
+  <si>
+    <t>dila</t>
+  </si>
+  <si>
+    <t>ud</t>
+  </si>
+  <si>
+    <t>ri</t>
+  </si>
+  <si>
+    <t>mod</t>
+  </si>
+  <si>
+    <t>sev</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>ff</t>
+  </si>
+  <si>
+    <t>plc</t>
+  </si>
+  <si>
+    <t>ple</t>
+  </si>
+  <si>
+    <t>eff</t>
+  </si>
+  <si>
+    <t>col</t>
+  </si>
+  <si>
+    <t>coll</t>
+  </si>
+  <si>
+    <t>cn</t>
+  </si>
+  <si>
+    <t>cnt</t>
+  </si>
+  <si>
+    <t>tib</t>
+  </si>
+  <si>
+    <t>fc</t>
+  </si>
+  <si>
+    <t>pfc</t>
+  </si>
+  <si>
+    <t>lfc</t>
+  </si>
+  <si>
+    <t>fcc</t>
+  </si>
+  <si>
+    <t>fibron</t>
+  </si>
+  <si>
+    <t>fatel</t>
+  </si>
+  <si>
+    <t>cha</t>
+  </si>
+  <si>
+    <t>poc</t>
+  </si>
+  <si>
+    <t>ppc</t>
+  </si>
+  <si>
+    <t>chea</t>
+  </si>
+  <si>
+    <t>gda</t>
+  </si>
+  <si>
+    <t>pj</t>
+  </si>
+  <si>
+    <t>gj</t>
+  </si>
+  <si>
+    <t>hj</t>
+  </si>
+  <si>
+    <t>rif</t>
+  </si>
+  <si>
+    <t>lif</t>
+  </si>
+  <si>
+    <t>ruq</t>
+  </si>
+  <si>
+    <t>luq</t>
+  </si>
+  <si>
+    <t>cir</t>
+  </si>
+  <si>
+    <t>circ</t>
+  </si>
+  <si>
+    <t>het</t>
+  </si>
+  <si>
+    <t>homo</t>
+  </si>
+  <si>
+    <t>hetly</t>
+  </si>
+  <si>
+    <t>homly</t>
+  </si>
+  <si>
+    <t>enhg</t>
+  </si>
+  <si>
+    <t>hge</t>
+  </si>
+  <si>
+    <t>hgic</t>
+  </si>
+  <si>
+    <t>rk</t>
+  </si>
+  <si>
+    <t>lk</t>
+  </si>
+  <si>
+    <t>rb</t>
+  </si>
+  <si>
+    <t>lb</t>
+  </si>
+  <si>
+    <t>af</t>
+  </si>
+  <si>
+    <t>ag</t>
+  </si>
+  <si>
+    <t>thy</t>
+  </si>
+  <si>
+    <t>parat</t>
+  </si>
+  <si>
+    <t>apw</t>
+  </si>
+  <si>
+    <t>subc</t>
+  </si>
+  <si>
+    <t>paraa</t>
+  </si>
+  <si>
+    <t>prev</t>
+  </si>
+  <si>
+    <t>lpy</t>
+  </si>
+  <si>
+    <t>medly</t>
+  </si>
+  <si>
+    <t>aa</t>
+  </si>
+  <si>
+    <t>asc</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>aoa</t>
+  </si>
+  <si>
+    <t>dta</t>
+  </si>
+  <si>
+    <t>cia</t>
+  </si>
+  <si>
+    <t>iia</t>
+  </si>
+  <si>
+    <t>eia</t>
+  </si>
+  <si>
+    <t>civ</t>
+  </si>
+  <si>
+    <t>iiv</t>
+  </si>
+  <si>
+    <t>eiv</t>
+  </si>
+  <si>
+    <t>ijv</t>
+  </si>
+  <si>
+    <t>svc</t>
+  </si>
+  <si>
+    <t>ivc</t>
+  </si>
+  <si>
+    <t>aib</t>
+  </si>
+  <si>
+    <t>conso</t>
+  </si>
+  <si>
+    <t>cocon</t>
+  </si>
+  <si>
+    <t>inv</t>
+  </si>
+  <si>
+    <t>sym</t>
+  </si>
+  <si>
+    <t>asym</t>
+  </si>
+  <si>
+    <t>hypod</t>
+  </si>
+  <si>
+    <t>hyperd</t>
+  </si>
+  <si>
+    <t>extd</t>
+  </si>
+  <si>
+    <t>extg</t>
+  </si>
+  <si>
+    <t>lrc</t>
+  </si>
+  <si>
+    <t>usgc</t>
+  </si>
+  <si>
+    <t>hpec</t>
+  </si>
+  <si>
+    <t>adv</t>
+  </si>
+  <si>
+    <t>dd</t>
+  </si>
+  <si>
+    <t>prob</t>
+  </si>
+  <si>
+    <t>flo</t>
+  </si>
+  <si>
+    <t>falo</t>
+  </si>
+  <si>
+    <t>fcw</t>
+  </si>
+  <si>
+    <t>fso</t>
+  </si>
+  <si>
+    <t>s/o</t>
+  </si>
+  <si>
+    <t>fo</t>
+  </si>
+  <si>
+    <t>eo</t>
+  </si>
+  <si>
+    <t>kco</t>
+  </si>
+  <si>
+    <t>susp</t>
+  </si>
+  <si>
+    <t>nv</t>
+  </si>
+  <si>
+    <t>nonvis</t>
+  </si>
+  <si>
+    <t>opa</t>
+  </si>
+  <si>
+    <t>vis</t>
+  </si>
+  <si>
+    <t>opd</t>
+  </si>
+  <si>
+    <t>lun</t>
+  </si>
+  <si>
+    <t>lus</t>
+  </si>
+  <si>
+    <t>sig</t>
+  </si>
+  <si>
+    <t>cald</t>
+  </si>
+  <si>
+    <t>ath</t>
+  </si>
+  <si>
+    <t>cap</t>
+  </si>
+  <si>
+    <t>nap</t>
+  </si>
+  <si>
+    <t>cnap</t>
+  </si>
+  <si>
+    <t>cg</t>
+  </si>
+  <si>
+    <t>upc</t>
+  </si>
+  <si>
+    <t>ipc</t>
+  </si>
+  <si>
+    <t>lpc</t>
+  </si>
+  <si>
+    <t>upco</t>
+  </si>
+  <si>
+    <t>ipco</t>
+  </si>
+  <si>
+    <t>lpco</t>
+  </si>
+  <si>
+    <t>loll</t>
+  </si>
+  <si>
+    <t>locl</t>
+  </si>
+  <si>
+    <t>gdb</t>
+  </si>
+  <si>
+    <t>paf</t>
+  </si>
+  <si>
+    <t>pat</t>
+  </si>
+  <si>
+    <t>ddc</t>
+  </si>
+  <si>
+    <t>mos</t>
+  </si>
+  <si>
+    <t>ddmos</t>
+  </si>
+  <si>
+    <t>relr</t>
+  </si>
+  <si>
+    <t>rebr</t>
+  </si>
+  <si>
+    <t>redr</t>
+  </si>
+  <si>
+    <t>cf</t>
+  </si>
+  <si>
+    <t>cfi</t>
+  </si>
+  <si>
+    <t>acl</t>
+  </si>
+  <si>
+    <t>pcl</t>
+  </si>
+  <si>
+    <t>lcl</t>
+  </si>
+  <si>
+    <t>mcl</t>
+  </si>
+  <si>
+    <t>mem</t>
+  </si>
+  <si>
+    <t>lm</t>
+  </si>
+  <si>
+    <t>res</t>
+  </si>
+  <si>
+    <t>fl</t>
+  </si>
+  <si>
+    <t>pdfs</t>
+  </si>
+  <si>
+    <t>st</t>
+  </si>
+  <si>
+    <t>ind</t>
+  </si>
+  <si>
+    <t>ben</t>
+  </si>
+  <si>
+    <t>malig</t>
+  </si>
+  <si>
+    <t>benp</t>
+  </si>
+  <si>
+    <t>maligp</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>infl</t>
+  </si>
+  <si>
+    <t>inp</t>
+  </si>
+  <si>
+    <t>broc</t>
+  </si>
+  <si>
+    <t>fbro</t>
+  </si>
+  <si>
+    <t>atel</t>
+  </si>
+  <si>
+    <t>atl</t>
+  </si>
+  <si>
+    <t>lfh</t>
+  </si>
+  <si>
+    <t>fja</t>
+  </si>
+  <si>
+    <t>kjs</t>
+  </si>
+  <si>
+    <t>kje</t>
+  </si>
+  <si>
+    <t>dgcv</t>
+  </si>
+  <si>
+    <t>atha</t>
+  </si>
+  <si>
+    <t>dgc</t>
+  </si>
+  <si>
+    <t>mn</t>
+  </si>
+  <si>
+    <t>mns</t>
+  </si>
+  <si>
+    <t>tb</t>
+  </si>
+  <si>
+    <t>ild</t>
+  </si>
+  <si>
+    <t>ven</t>
+  </si>
+  <si>
+    <t>frol</t>
+  </si>
+  <si>
+    <t>parl</t>
+  </si>
+  <si>
+    <t>teml</t>
+  </si>
+  <si>
+    <t>occl</t>
+  </si>
+  <si>
+    <t>sss</t>
+  </si>
+  <si>
+    <t>iss</t>
+  </si>
+  <si>
+    <t>tras</t>
+  </si>
+  <si>
+    <t>om</t>
+  </si>
+  <si>
+    <t>omc</t>
+  </si>
+  <si>
+    <t>hsi</t>
+  </si>
+  <si>
+    <t>lsi</t>
+  </si>
+  <si>
+    <t>si</t>
+  </si>
+  <si>
+    <t>supp</t>
+  </si>
+  <si>
+    <t>dires</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>ub</t>
+  </si>
+  <si>
+    <t>ubp</t>
+  </si>
+  <si>
+    <t>ubm</t>
+  </si>
+  <si>
+    <t>ube</t>
+  </si>
+  <si>
+    <t>ubpf</t>
+  </si>
+  <si>
+    <t>ubmf</t>
+  </si>
+  <si>
+    <t>ubef</t>
+  </si>
+  <si>
+    <t>gb</t>
+  </si>
+  <si>
+    <t>cdl</t>
+  </si>
+  <si>
+    <t>hl</t>
+  </si>
+  <si>
+    <t>mea</t>
+  </si>
+  <si>
+    <t>meaa</t>
+  </si>
+  <si>
+    <t>larm</t>
+  </si>
+  <si>
+    <t>larma</t>
+  </si>
+  <si>
+    <t>approx</t>
+  </si>
+  <si>
+    <t>scd</t>
+  </si>
+  <si>
+    <t>sc</t>
+  </si>
+  <si>
+    <t>im</t>
+  </si>
+  <si>
+    <t>carmeg</t>
+  </si>
+  <si>
+    <t>carme</t>
+  </si>
+  <si>
+    <t>cfa</t>
+  </si>
+  <si>
+    <t>sfa</t>
+  </si>
+  <si>
+    <t>popa</t>
+  </si>
+  <si>
+    <t>ata</t>
+  </si>
+  <si>
+    <t>tpt</t>
+  </si>
+  <si>
+    <t>pta</t>
+  </si>
+  <si>
+    <t>pera</t>
+  </si>
+  <si>
+    <t>dpa</t>
+  </si>
+  <si>
+    <t>cfv</t>
+  </si>
+  <si>
+    <t>sfv</t>
+  </si>
+  <si>
+    <t>gsv</t>
+  </si>
+  <si>
+    <t>popv</t>
+  </si>
+  <si>
+    <t>atv</t>
+  </si>
+  <si>
+    <t>ptv</t>
+  </si>
+  <si>
+    <t>ssv</t>
+  </si>
+  <si>
+    <t>bct</t>
+  </si>
+  <si>
+    <t>ica</t>
+  </si>
+  <si>
+    <t>cca</t>
+  </si>
+  <si>
+    <t>mca</t>
+  </si>
+  <si>
+    <t>aca</t>
+  </si>
+  <si>
+    <t>pca</t>
+  </si>
+  <si>
+    <t>ss</t>
+  </si>
+  <si>
+    <t>atc</t>
+  </si>
+  <si>
+    <t>vol</t>
+  </si>
+  <si>
+    <t>voll</t>
+  </si>
+  <si>
+    <t>ips</t>
+  </si>
+  <si>
+    <t>cnl</t>
+  </si>
+  <si>
+    <t>me</t>
+  </si>
+  <si>
+    <t>prom</t>
+  </si>
+  <si>
+    <t>ref</t>
+  </si>
+  <si>
+    <t>bif</t>
+  </si>
+  <si>
+    <t>trif</t>
+  </si>
+  <si>
+    <t>oa</t>
+  </si>
+  <si>
+    <t>calc</t>
+  </si>
+  <si>
+    <t>enl</t>
+  </si>
+  <si>
+    <t>ccca</t>
+  </si>
+  <si>
+    <t>sma</t>
+  </si>
+  <si>
+    <t>smv</t>
+  </si>
+  <si>
+    <t>ima</t>
+  </si>
+  <si>
+    <t>imv</t>
+  </si>
+  <si>
+    <t>lga</t>
+  </si>
+  <si>
+    <t>pv</t>
+  </si>
+  <si>
+    <t>mpv</t>
+  </si>
+  <si>
+    <t>pars</t>
+  </si>
+  <si>
+    <t>trans</t>
+  </si>
+  <si>
+    <t>cdp</t>
+  </si>
+  <si>
+    <t>pdp</t>
+  </si>
+  <si>
+    <t>tra</t>
+  </si>
+  <si>
+    <t>dia</t>
+  </si>
+  <si>
+    <t>cau</t>
+  </si>
+  <si>
+    <t>ac</t>
+  </si>
+  <si>
+    <t>perig</t>
+  </si>
+  <si>
+    <t>perip</t>
+  </si>
+  <si>
+    <t>peripa</t>
+  </si>
+  <si>
+    <t>pc</t>
+  </si>
+  <si>
+    <t>pf</t>
+  </si>
+  <si>
+    <t>abdominal aorta</t>
+  </si>
+  <si>
+    <t>anterobasal segment</t>
+  </si>
+  <si>
+    <t>aortocaval</t>
+  </si>
+  <si>
+    <t>anterior cruciate ligament</t>
+  </si>
+  <si>
+    <t>Advice:</t>
+  </si>
+  <si>
+    <t>arising from</t>
+  </si>
+  <si>
+    <t>adrenal gland</t>
+  </si>
+  <si>
+    <t>air bronchograms</t>
+  </si>
+  <si>
+    <t>antero medial basal segment</t>
+  </si>
+  <si>
+    <t>anterior</t>
+  </si>
+  <si>
+    <t>anteriorly</t>
+  </si>
+  <si>
+    <t>arch of aorta</t>
+  </si>
+  <si>
+    <t>apicoposterior segment</t>
+  </si>
+  <si>
+    <t>approximately</t>
+  </si>
+  <si>
+    <t>aortopulmonary window</t>
+  </si>
+  <si>
+    <t>ascending</t>
+  </si>
+  <si>
+    <t>asymmetric</t>
+  </si>
+  <si>
+    <t>anterior tibial artery</t>
+  </si>
+  <si>
+    <t>(AP x Tra x CC)</t>
+  </si>
+  <si>
+    <t>atelectasis</t>
+  </si>
+  <si>
+    <t>atherosclerotic</t>
+  </si>
+  <si>
+    <t>anterior tibial vein</t>
+  </si>
+  <si>
+    <t>brachiocephalic trunk</t>
+  </si>
+  <si>
+    <t>benign</t>
+  </si>
+  <si>
+    <t>benign pathology</t>
+  </si>
+  <si>
+    <t>bifurcation</t>
+  </si>
+  <si>
+    <t>bilateral lung fields</t>
+  </si>
+  <si>
+    <t>bilateral kidneys</t>
+  </si>
+  <si>
+    <t>bilateral lower lobes</t>
+  </si>
+  <si>
+    <t>bronchiectatic changes</t>
+  </si>
+  <si>
+    <t>bilateral upper lobes</t>
+  </si>
+  <si>
+    <t>calcification</t>
+  </si>
+  <si>
+    <t>calcified</t>
+  </si>
+  <si>
+    <t>calcified atherosclerotic plaques</t>
+  </si>
+  <si>
+    <t>cardiomegaly</t>
+  </si>
+  <si>
+    <t>Cardiac size is enlarged with cardiothoracic ratio of</t>
+  </si>
+  <si>
+    <t>causing</t>
+  </si>
+  <si>
+    <t>common carotid artery</t>
+  </si>
+  <si>
+    <t>craniocaudal axis</t>
+  </si>
+  <si>
+    <t>choledocholithiasis</t>
+  </si>
+  <si>
+    <t>central disc protrusion</t>
+  </si>
+  <si>
+    <t>cerebral atrophy</t>
+  </si>
+  <si>
+    <t>There is volume loss of bilateral cerebral hemispheres with prominent sulci, extraaxial CSF spaces &amp; proportionate dilatation of ventricles.</t>
+  </si>
+  <si>
+    <t>calcific focus</t>
+  </si>
+  <si>
+    <t>common femoral artery</t>
+  </si>
+  <si>
+    <t>calcific foci</t>
+  </si>
+  <si>
+    <t>common femoral vein</t>
+  </si>
+  <si>
+    <t>calcified granuloma</t>
+  </si>
+  <si>
+    <t>changes</t>
+  </si>
+  <si>
+    <t>common hepatic duct</t>
+  </si>
+  <si>
+    <t>common hepatic artery</t>
+  </si>
+  <si>
+    <t>common iliac artery</t>
+  </si>
+  <si>
+    <t>circumferential</t>
+  </si>
+  <si>
+    <t>circumscribed</t>
+  </si>
+  <si>
+    <t>common iliac vein</t>
+  </si>
+  <si>
+    <t>cholelithiasis</t>
+  </si>
+  <si>
+    <t>centrilobular nodules</t>
+  </si>
+  <si>
+    <t>calcified and non-calcified atherosclerotic plaques</t>
+  </si>
+  <si>
+    <t>contralateral</t>
+  </si>
+  <si>
+    <t>centrilobular nodules with tree in bud pattern</t>
+  </si>
+  <si>
+    <t>collapse consolidation</t>
+  </si>
+  <si>
+    <t>collection</t>
+  </si>
+  <si>
+    <t>collaterals</t>
+  </si>
+  <si>
+    <t>consolidation</t>
+  </si>
+  <si>
+    <t>D/D:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">disc dessication changes </t>
+  </si>
+  <si>
+    <t>disc dessication changes  with marginal osteophytes</t>
+  </si>
+  <si>
+    <t>descending</t>
+  </si>
+  <si>
+    <t>degenerative changes</t>
+  </si>
+  <si>
+    <t>diameter</t>
+  </si>
+  <si>
+    <t>dilatation</t>
+  </si>
+  <si>
+    <t>diffusion restriction</t>
+  </si>
+  <si>
+    <t>dorsalis pedis artery</t>
+  </si>
+  <si>
+    <t>descending thoracic aorta</t>
+  </si>
+  <si>
+    <t>effacement</t>
+  </si>
+  <si>
+    <t>external iliac artery</t>
+  </si>
+  <si>
+    <t>external iliac vein</t>
+  </si>
+  <si>
+    <t>enhancing</t>
+  </si>
+  <si>
+    <t>enlarged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evidence of </t>
+  </si>
+  <si>
+    <t>ethmoidal</t>
+  </si>
+  <si>
+    <t>ethmoid sinus</t>
+  </si>
+  <si>
+    <t>extending</t>
+  </si>
+  <si>
+    <t>features are likely of</t>
+  </si>
+  <si>
+    <t>fibroatelectatic</t>
+  </si>
+  <si>
+    <t>fibro bronchiectatic</t>
+  </si>
+  <si>
+    <t>fibrotic changes</t>
+  </si>
+  <si>
+    <t>fibrocalcific changes</t>
+  </si>
+  <si>
+    <t>features are consistent with</t>
+  </si>
+  <si>
+    <t>free fluid</t>
+  </si>
+  <si>
+    <t>fibronodular</t>
+  </si>
+  <si>
+    <t>facet joint arthropathy</t>
+  </si>
+  <si>
+    <t>FLAIR</t>
+  </si>
+  <si>
+    <t>features likely of</t>
+  </si>
+  <si>
+    <t>features of</t>
+  </si>
+  <si>
+    <t>frontal lobe</t>
+  </si>
+  <si>
+    <t>frontal sinus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">features suggestive of </t>
+  </si>
+  <si>
+    <t>gall bladder</t>
+  </si>
+  <si>
+    <t>gastroduodenal artery</t>
+  </si>
+  <si>
+    <t>global disc bulge</t>
+  </si>
+  <si>
+    <t>gastrojejunostomy</t>
+  </si>
+  <si>
+    <t>great saphenous vein</t>
+  </si>
+  <si>
+    <t>hydrocephalus</t>
+  </si>
+  <si>
+    <t>hydronephrosis</t>
+  </si>
+  <si>
+    <t>hydroureteronephrosis</t>
+  </si>
+  <si>
+    <t>heterogeneous</t>
+  </si>
+  <si>
+    <t>heterogeneously</t>
+  </si>
+  <si>
+    <t>hemorrhage</t>
+  </si>
+  <si>
+    <t>hemorrhagic</t>
+  </si>
+  <si>
+    <t>hepaticojejunostomy</t>
+  </si>
+  <si>
+    <t>hepaticolithiasis</t>
+  </si>
+  <si>
+    <t>homogeneously</t>
+  </si>
+  <si>
+    <t>homogeneous</t>
+  </si>
+  <si>
+    <t>HPE correlation</t>
+  </si>
+  <si>
+    <t>high signal intensity</t>
+  </si>
+  <si>
+    <t>hypertension</t>
+  </si>
+  <si>
+    <t>hyperdense</t>
+  </si>
+  <si>
+    <t>hypodense</t>
+  </si>
+  <si>
+    <t>internal carotid artery</t>
+  </si>
+  <si>
+    <t>intrahepatic bile ducts</t>
+  </si>
+  <si>
+    <t>intrahepatic biliary radicals</t>
+  </si>
+  <si>
+    <t>internal iliac artery</t>
+  </si>
+  <si>
+    <t>internal iliac vein</t>
+  </si>
+  <si>
+    <t>internal jugular vein</t>
+  </si>
+  <si>
+    <t>interstitial lung disease</t>
+  </si>
+  <si>
+    <t>intramuscular</t>
+  </si>
+  <si>
+    <t>inferior mesenteric artery</t>
+  </si>
+  <si>
+    <t>inferior mesenteric vein</t>
+  </si>
+  <si>
+    <t>indeterminate</t>
+  </si>
+  <si>
+    <t>inferior</t>
+  </si>
+  <si>
+    <t>inflammatory</t>
+  </si>
+  <si>
+    <t>inferiorly</t>
+  </si>
+  <si>
+    <t>infective pathology</t>
+  </si>
+  <si>
+    <t>involving</t>
+  </si>
+  <si>
+    <t>interpolar calyx</t>
+  </si>
+  <si>
+    <t>interpolar cortex</t>
+  </si>
+  <si>
+    <t>ipsilateral</t>
+  </si>
+  <si>
+    <t>inferior sagittal sinus</t>
+  </si>
+  <si>
+    <t>inferior vena cava</t>
+  </si>
+  <si>
+    <t xml:space="preserve">known case of </t>
+  </si>
+  <si>
+    <t>knee joint effusion</t>
+  </si>
+  <si>
+    <t>knee joint space</t>
+  </si>
+  <si>
+    <t>largest measuring</t>
+  </si>
+  <si>
+    <t>largest measuring approximately</t>
+  </si>
+  <si>
+    <t>lateral</t>
+  </si>
+  <si>
+    <t>laterally</t>
+  </si>
+  <si>
+    <t>lateral basal segment</t>
+  </si>
+  <si>
+    <t>left breast</t>
+  </si>
+  <si>
+    <t>lateral collateral ligament</t>
+  </si>
+  <si>
+    <t>linear fibrotic changes</t>
+  </si>
+  <si>
+    <t>ligamentum flavum hypertrophy</t>
+  </si>
+  <si>
+    <t>left gastric artery</t>
+  </si>
+  <si>
+    <t>left iliac fossa</t>
+  </si>
+  <si>
+    <t>left kidney</t>
+  </si>
+  <si>
+    <t>left lower lobe</t>
+  </si>
+  <si>
+    <t>lateral meniscus</t>
+  </si>
+  <si>
+    <t>lymph node</t>
+  </si>
+  <si>
+    <t>lymph nodes</t>
+  </si>
+  <si>
+    <t>Loss of cervical lordosis is seen.</t>
+  </si>
+  <si>
+    <t>Loss of lumbar lordosis is seen.</t>
+  </si>
+  <si>
+    <t>lower pole calyx</t>
+  </si>
+  <si>
+    <t>lower pole cortex</t>
+  </si>
+  <si>
+    <t>lymphadenopathy</t>
+  </si>
+  <si>
+    <t>likely reactive</t>
+  </si>
+  <si>
+    <t>low signal intensity</t>
+  </si>
+  <si>
+    <t>left</t>
+  </si>
+  <si>
+    <t>left upper lobe</t>
+  </si>
+  <si>
+    <t>luminal narrowing</t>
+  </si>
+  <si>
+    <t>left upper quadrant</t>
+  </si>
+  <si>
+    <t>luminal stenosis</t>
+  </si>
+  <si>
+    <t>malignant</t>
+  </si>
+  <si>
+    <t>malignant pathology</t>
+  </si>
+  <si>
+    <t>maxillary sinus</t>
+  </si>
+  <si>
+    <t>maximum</t>
+  </si>
+  <si>
+    <t>maxillary</t>
+  </si>
+  <si>
+    <t>medial basal segment</t>
+  </si>
+  <si>
+    <t>middle cerebral artery</t>
+  </si>
+  <si>
+    <t>medial collateral ligament</t>
+  </si>
+  <si>
+    <t>mass effect</t>
+  </si>
+  <si>
+    <t>measuring</t>
+  </si>
+  <si>
+    <t>measuring approximately</t>
+  </si>
+  <si>
+    <t>medial</t>
+  </si>
+  <si>
+    <t>mediastinal lymphadenopathy</t>
+  </si>
+  <si>
+    <t>medially</t>
+  </si>
+  <si>
+    <t>medial meniscus</t>
+  </si>
+  <si>
+    <t>minimal</t>
+  </si>
+  <si>
+    <t>micronodule</t>
+  </si>
+  <si>
+    <t>micronodules</t>
+  </si>
+  <si>
+    <t>moderate</t>
+  </si>
+  <si>
+    <t>marginal osteophytes</t>
+  </si>
+  <si>
+    <t>main portal vein</t>
+  </si>
+  <si>
+    <t>and</t>
+  </si>
+  <si>
+    <t>non-calcified atherosclerotic plaques</t>
+  </si>
+  <si>
+    <t>nephrolithiasis</t>
+  </si>
+  <si>
+    <t>non-visualization</t>
+  </si>
+  <si>
+    <t>not visualized</t>
+  </si>
+  <si>
+    <t>osteoarthritic</t>
+  </si>
+  <si>
+    <t>occipital lobe</t>
+  </si>
+  <si>
+    <t>oto-mastoiditis</t>
+  </si>
+  <si>
+    <t>ostiomeatal complex</t>
+  </si>
+  <si>
+    <t>opacification</t>
+  </si>
+  <si>
+    <t>opacified</t>
+  </si>
+  <si>
+    <t>posterior annular fissure</t>
+  </si>
+  <si>
+    <t>paraaortic</t>
+  </si>
+  <si>
+    <t>paratracheal</t>
+  </si>
+  <si>
+    <t>parietal lobe</t>
+  </si>
+  <si>
+    <t>pars interarticularis</t>
+  </si>
+  <si>
+    <t>patchy</t>
+  </si>
+  <si>
+    <t>pathology</t>
+  </si>
+  <si>
+    <t>posterobasal segment</t>
+  </si>
+  <si>
+    <t>portocaval</t>
+  </si>
+  <si>
+    <t>posterior cerebral artery</t>
+  </si>
+  <si>
+    <t>posterior collateral ligament</t>
+  </si>
+  <si>
+    <t>PD FS</t>
+  </si>
+  <si>
+    <t>paramedian disc protrusion</t>
+  </si>
+  <si>
+    <t>peroneal artery</t>
+  </si>
+  <si>
+    <t>perigastric</t>
+  </si>
+  <si>
+    <t>periportal</t>
+  </si>
+  <si>
+    <t>peripancreatic</t>
+  </si>
+  <si>
+    <t>There is fluid signal intensity noted in the pituitary fossa suggestive of partial empty sella.</t>
+  </si>
+  <si>
+    <t>partially empty sella</t>
+  </si>
+  <si>
+    <t>patchy fibrosis</t>
+  </si>
+  <si>
+    <t>patchy fibrotic changes</t>
+  </si>
+  <si>
+    <t>pancreaticojejunostomy</t>
+  </si>
+  <si>
+    <t>pleural cavity</t>
+  </si>
+  <si>
+    <t>pleural effusion</t>
+  </si>
+  <si>
+    <t>post-operative changes</t>
+  </si>
+  <si>
+    <t>Soft tissue density with convex outward margin is noted in right maxillary sinus – polyp/ retention cyst.</t>
+  </si>
+  <si>
+    <t>popliteal artery</t>
+  </si>
+  <si>
+    <t>popliteal vein</t>
+  </si>
+  <si>
+    <t>posterior</t>
+  </si>
+  <si>
+    <t>posteriorly</t>
+  </si>
+  <si>
+    <t>post-procedural changes</t>
+  </si>
+  <si>
+    <t>prevascular</t>
+  </si>
+  <si>
+    <t>probably</t>
+  </si>
+  <si>
+    <t>prominent</t>
+  </si>
+  <si>
+    <t>proximal</t>
+  </si>
+  <si>
+    <t>posterior tibial artery</t>
+  </si>
+  <si>
+    <t>posterior tibial vein</t>
+  </si>
+  <si>
+    <t>pulmonary</t>
+  </si>
+  <si>
+    <t>pulmonary artery</t>
+  </si>
+  <si>
+    <t>pulmonary vein</t>
+  </si>
+  <si>
+    <t>portal vein</t>
+  </si>
+  <si>
+    <t>right breast</t>
+  </si>
+  <si>
+    <t>Rest of the brain is normal in morphology and signal intensity</t>
+  </si>
+  <si>
+    <t>Rest of the intervertebral discs are normal in height and signal intensity.</t>
+  </si>
+  <si>
+    <t>reformation</t>
+  </si>
+  <si>
+    <t>Rest of the lung fields shows normal attenuation and normal in aeration.</t>
+  </si>
+  <si>
+    <t>restriction of diffusion on DWI</t>
+  </si>
+  <si>
+    <t>resulting in</t>
+  </si>
+  <si>
+    <t>right iliac fossa</t>
+  </si>
+  <si>
+    <t>right kidney</t>
+  </si>
+  <si>
+    <t>right lower lobe</t>
+  </si>
+  <si>
+    <t>right middle lobe</t>
+  </si>
+  <si>
+    <t>right</t>
+  </si>
+  <si>
+    <t>right upper lobe</t>
+  </si>
+  <si>
+    <t>right upper quadrant</t>
+  </si>
+  <si>
+    <t>suggestive of</t>
+  </si>
+  <si>
+    <t>subcutaneous</t>
+  </si>
+  <si>
+    <t>skin to calculus distance of</t>
+  </si>
+  <si>
+    <t>segment</t>
+  </si>
+  <si>
+    <t>segments</t>
+  </si>
+  <si>
+    <t>severe</t>
+  </si>
+  <si>
+    <t>superficial femoral artery</t>
+  </si>
+  <si>
+    <t>superficial femoral vein</t>
+  </si>
+  <si>
+    <t>signal intensity</t>
+  </si>
+  <si>
+    <t>significant</t>
+  </si>
+  <si>
+    <t>Mucosal thickening noted in bilateral maxillary sinus - suggestive of sinusitis.</t>
+  </si>
+  <si>
+    <t>superior mesenteric artery</t>
+  </si>
+  <si>
+    <t>superior mesenteric vein</t>
+  </si>
+  <si>
+    <t>sphenoid</t>
+  </si>
+  <si>
+    <t>sphenoid sinus</t>
+  </si>
+  <si>
+    <t>sigmoid sinus</t>
+  </si>
+  <si>
+    <t>superior sagital sinus</t>
+  </si>
+  <si>
+    <t>short saphenous vein</t>
+  </si>
+  <si>
+    <t>STIR</t>
+  </si>
+  <si>
+    <t>subcarinal</t>
+  </si>
+  <si>
+    <t>superior</t>
+  </si>
+  <si>
+    <t>suppressed</t>
+  </si>
+  <si>
+    <t>superiorly</t>
+  </si>
+  <si>
+    <t>suspicious</t>
+  </si>
+  <si>
+    <t>superior vena cava</t>
+  </si>
+  <si>
+    <t>small vessel disease</t>
+  </si>
+  <si>
+    <t>Discrete and confluent T2/FLAIR high signal intensities are noted in bilateral periventricular white matter and centrum semi-ovale.</t>
+  </si>
+  <si>
+    <t>symmetrical</t>
+  </si>
+  <si>
+    <t>tuberculosis</t>
+  </si>
+  <si>
+    <t>tiny calculi (&lt;3mm)</t>
+  </si>
+  <si>
+    <t>tiny calculus (&lt;3mm)</t>
+  </si>
+  <si>
+    <t>temporal lobe</t>
+  </si>
+  <si>
+    <t>thrombosis</t>
+  </si>
+  <si>
+    <t>thyroid</t>
+  </si>
+  <si>
+    <t>tree in bud pattern</t>
+  </si>
+  <si>
+    <t>tibioperoneal trunk</t>
+  </si>
+  <si>
+    <t>transverse</t>
+  </si>
+  <si>
+    <t>translation</t>
+  </si>
+  <si>
+    <t>transverse sinus</t>
+  </si>
+  <si>
+    <t>trifurcation</t>
+  </si>
+  <si>
+    <t>urinary bladder</t>
+  </si>
+  <si>
+    <t>Urinary bladder is empty.</t>
+  </si>
+  <si>
+    <t>Urinary bladder is empty with Foley's in situ.</t>
+  </si>
+  <si>
+    <t>Urinary bladder is minimally filled.</t>
+  </si>
+  <si>
+    <t>Urinary bladder is minimally filled with Foley's in situ.</t>
+  </si>
+  <si>
+    <t>Urinary bladder is partially filled.</t>
+  </si>
+  <si>
+    <t>Urinary bladder is partially filled with Foley's in situ.</t>
+  </si>
+  <si>
+    <t>upstream dilatation</t>
+  </si>
+  <si>
+    <t>upper pole calyx</t>
+  </si>
+  <si>
+    <t>upper polar cortex</t>
+  </si>
+  <si>
+    <t>USG correlation</t>
+  </si>
+  <si>
+    <t>ventricle</t>
+  </si>
+  <si>
+    <t>visualised</t>
+  </si>
+  <si>
+    <t>volume</t>
+  </si>
+  <si>
+    <t>volume loss</t>
+  </si>
+  <si>
+    <t>with</t>
+  </si>
+  <si>
+    <t>gm</t>
+  </si>
+  <si>
+    <t>wm</t>
+  </si>
+  <si>
+    <t>gwm</t>
+  </si>
+  <si>
+    <t>gwmd</t>
+  </si>
+  <si>
+    <t>periv</t>
+  </si>
+  <si>
+    <t>cso</t>
+  </si>
+  <si>
+    <t>athp</t>
+  </si>
+  <si>
+    <t>ch</t>
+  </si>
+  <si>
+    <t>ceh</t>
+  </si>
+  <si>
+    <t>diff</t>
+  </si>
+  <si>
+    <t>wd</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>occ</t>
+  </si>
+  <si>
+    <t>nar</t>
+  </si>
+  <si>
+    <t>stn</t>
+  </si>
+  <si>
+    <t>obl</t>
+  </si>
+  <si>
+    <t>infil</t>
+  </si>
+  <si>
+    <t>obv</t>
+  </si>
+  <si>
+    <t>br</t>
+  </si>
+  <si>
+    <t>asp</t>
+  </si>
+  <si>
+    <t>thru</t>
+  </si>
+  <si>
+    <t>thrut</t>
+  </si>
+  <si>
+    <t>lr</t>
+  </si>
+  <si>
+    <t>nf</t>
+  </si>
+  <si>
+    <t>csc</t>
+  </si>
+  <si>
+    <t>pll</t>
+  </si>
+  <si>
+    <t>fd</t>
+  </si>
+  <si>
+    <t>c12</t>
+  </si>
+  <si>
+    <t>c23</t>
+  </si>
+  <si>
+    <t>c34</t>
+  </si>
+  <si>
+    <t>c45</t>
+  </si>
+  <si>
+    <t>c56</t>
+  </si>
+  <si>
+    <t>c67</t>
+  </si>
+  <si>
+    <t>c71</t>
+  </si>
+  <si>
+    <t>d23</t>
+  </si>
+  <si>
+    <t>d34</t>
+  </si>
+  <si>
+    <t>d45</t>
+  </si>
+  <si>
+    <t>d56</t>
+  </si>
+  <si>
+    <t>d67</t>
+  </si>
+  <si>
+    <t>d78</t>
+  </si>
+  <si>
+    <t>d89</t>
+  </si>
+  <si>
+    <t>d910</t>
+  </si>
+  <si>
+    <t>d1011</t>
+  </si>
+  <si>
+    <t>d1112</t>
+  </si>
+  <si>
+    <t>d121</t>
+  </si>
+  <si>
+    <t>l12</t>
+  </si>
+  <si>
+    <t>l23</t>
+  </si>
+  <si>
+    <t>l34</t>
+  </si>
+  <si>
+    <t>l45</t>
+  </si>
+  <si>
+    <t>l51</t>
+  </si>
+  <si>
+    <t>s12</t>
+  </si>
+  <si>
+    <t>ivd</t>
+  </si>
+  <si>
+    <t>vb</t>
+  </si>
+  <si>
+    <t>ver</t>
+  </si>
+  <si>
+    <t>anterior longitudinal ligament</t>
+  </si>
+  <si>
+    <t>aspect</t>
+  </si>
+  <si>
+    <t>atherosclerotic plaque</t>
+  </si>
+  <si>
+    <t>branch</t>
+  </si>
+  <si>
+    <t>C1-C2</t>
+  </si>
+  <si>
+    <t>C2-C3</t>
+  </si>
+  <si>
+    <t>C3-C4</t>
+  </si>
+  <si>
+    <t>C4-C5</t>
+  </si>
+  <si>
+    <t>C5-C6</t>
+  </si>
+  <si>
+    <t>C6-C7</t>
+  </si>
+  <si>
+    <t>C7-D1</t>
+  </si>
+  <si>
+    <t>cerebellar hemisphere</t>
+  </si>
+  <si>
+    <t>cerebral hemisphere</t>
+  </si>
+  <si>
+    <t>central spinal canal</t>
+  </si>
+  <si>
+    <t>centrum semi-ovale</t>
+  </si>
+  <si>
+    <t>D10-D11</t>
+  </si>
+  <si>
+    <t>D11-D12</t>
+  </si>
+  <si>
+    <t>D12-L1</t>
+  </si>
+  <si>
+    <t>D2-D3</t>
+  </si>
+  <si>
+    <t>D3-D4</t>
+  </si>
+  <si>
+    <t>D4-D5</t>
+  </si>
+  <si>
+    <t>D5-D6</t>
+  </si>
+  <si>
+    <t>D6-D7</t>
+  </si>
+  <si>
+    <t>D7-D8</t>
+  </si>
+  <si>
+    <t>D8-D9</t>
+  </si>
+  <si>
+    <t>D9-D10</t>
+  </si>
+  <si>
+    <t>differentiation</t>
+  </si>
+  <si>
+    <t>filling defect</t>
+  </si>
+  <si>
+    <t>grey matter</t>
+  </si>
+  <si>
+    <t>grey and white matter</t>
+  </si>
+  <si>
+    <t>grey-white matter differentiation</t>
+  </si>
+  <si>
+    <t>ill-defined</t>
+  </si>
+  <si>
+    <t>infiltration</t>
+  </si>
+  <si>
+    <t>intervertebral disc</t>
+  </si>
+  <si>
+    <t>L1-L2</t>
+  </si>
+  <si>
+    <t>L2-L3</t>
+  </si>
+  <si>
+    <t>L3-L4</t>
+  </si>
+  <si>
+    <t>L4-L5</t>
+  </si>
+  <si>
+    <t>L5-S1</t>
+  </si>
+  <si>
+    <t>lateral recess</t>
+  </si>
+  <si>
+    <t>narrowing</t>
+  </si>
+  <si>
+    <t>neural foramina</t>
+  </si>
+  <si>
+    <t>obliteration</t>
+  </si>
+  <si>
+    <t>obvious</t>
+  </si>
+  <si>
+    <t>occlusion</t>
+  </si>
+  <si>
+    <t>periventricular</t>
+  </si>
+  <si>
+    <t>posterior longitudinal ligament</t>
+  </si>
+  <si>
+    <t>S1-S2</t>
+  </si>
+  <si>
+    <t>stenosis</t>
+  </si>
+  <si>
+    <t>through</t>
+  </si>
+  <si>
+    <t>throughout</t>
+  </si>
+  <si>
+    <t>vertebral body</t>
+  </si>
+  <si>
+    <t>vertebra</t>
+  </si>
+  <si>
+    <t>well-defined</t>
+  </si>
+  <si>
+    <t>white matter</t>
+  </si>
+  <si>
+    <t>lig</t>
+  </si>
+  <si>
+    <t>ligament</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>are</t>
+  </si>
+  <si>
+    <t>edh</t>
+  </si>
+  <si>
+    <t>extradural hemorrhage</t>
+  </si>
+  <si>
+    <t>sdh</t>
+  </si>
+  <si>
+    <t>subdural hemorrhage</t>
+  </si>
+  <si>
+    <t>ich</t>
+  </si>
+  <si>
+    <t>intracerebral hemorrhage</t>
+  </si>
+  <si>
+    <t>ivh</t>
+  </si>
+  <si>
+    <t>intraventricular hemorrhage</t>
+  </si>
+  <si>
+    <t>bl</t>
+  </si>
+  <si>
+    <t>bilateral</t>
+  </si>
+  <si>
+    <t>ext</t>
+  </si>
+  <si>
+    <t>extension</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>intermediate</t>
+  </si>
+  <si>
+    <t>adj</t>
+  </si>
+  <si>
+    <t>adjacent</t>
+  </si>
+  <si>
+    <t>ni</t>
+  </si>
+  <si>
+    <t>noted in</t>
+  </si>
+  <si>
+    <t>na</t>
+  </si>
+  <si>
+    <t>noted at</t>
+  </si>
+  <si>
+    <t>att</t>
+  </si>
+  <si>
+    <t>attenuating</t>
+  </si>
+  <si>
+    <t>attn</t>
+  </si>
+  <si>
+    <t>attenuation</t>
+  </si>
+  <si>
+    <t>peed</t>
+  </si>
+  <si>
+    <t>perilesional edema</t>
+  </si>
+  <si>
+    <t>perile</t>
+  </si>
+  <si>
+    <t>lir</t>
+  </si>
+  <si>
+    <t>(Left &gt; Right)</t>
+  </si>
+  <si>
+    <t>ril</t>
+  </si>
+  <si>
+    <t>(Right &gt; Left)</t>
+  </si>
+  <si>
+    <t>sts</t>
+  </si>
+  <si>
+    <t>soft tissue strandings</t>
+  </si>
+  <si>
+    <t>fs</t>
+  </si>
+  <si>
+    <t>fat strandings</t>
+  </si>
+  <si>
+    <t>bg</t>
+  </si>
+  <si>
+    <t>basal ganglia</t>
+  </si>
+  <si>
+    <t>ic</t>
+  </si>
+  <si>
+    <t>internal capsule</t>
+  </si>
+  <si>
+    <t>ec</t>
+  </si>
+  <si>
+    <t>external capsule</t>
+  </si>
+  <si>
+    <t>thic</t>
+  </si>
+  <si>
+    <t>thickening</t>
+  </si>
+  <si>
+    <t>nsr</t>
+  </si>
+  <si>
+    <t>Nasal septum is deviated to right.</t>
+  </si>
+  <si>
+    <t>nsl</t>
+  </si>
+  <si>
+    <t>Nasal septum is deviated to left.</t>
+  </si>
+  <si>
+    <t>dns</t>
+  </si>
+  <si>
+    <t>deviated nasal septum</t>
+  </si>
+  <si>
+    <t>s/p</t>
+  </si>
+  <si>
+    <t>status post</t>
+  </si>
+  <si>
+    <t>ada</t>
+  </si>
+  <si>
+    <t>as described above</t>
+  </si>
+  <si>
+    <t>rada</t>
+  </si>
+  <si>
+    <t>relations and extensions as described above</t>
+  </si>
+  <si>
+    <t>chr</t>
+  </si>
+  <si>
+    <t>chronic</t>
+  </si>
+  <si>
+    <t>nonopa</t>
+  </si>
+  <si>
+    <t>non-opacification</t>
+  </si>
+  <si>
+    <t>nw</t>
+  </si>
+  <si>
+    <t>noted within</t>
+  </si>
+  <si>
+    <t>dwm</t>
+  </si>
+  <si>
+    <t>deep white matter</t>
+  </si>
+  <si>
+    <t>gp</t>
+  </si>
+  <si>
+    <t>globus pallidus</t>
+  </si>
+  <si>
+    <t>nu</t>
+  </si>
+  <si>
+    <t>nucleus</t>
+  </si>
+  <si>
+    <t>enh</t>
+  </si>
+  <si>
+    <t>enhancement</t>
+  </si>
+  <si>
+    <t>nc</t>
+  </si>
+  <si>
+    <t>nasal cavity</t>
+  </si>
+  <si>
+    <t>pns</t>
+  </si>
+  <si>
+    <t>paranasal sinuses</t>
+  </si>
+  <si>
+    <t>rot</t>
+  </si>
+  <si>
+    <t>rest of the</t>
+  </si>
+  <si>
+    <t>nor</t>
+  </si>
+  <si>
+    <t>normal</t>
+  </si>
+  <si>
+    <t>nof</t>
+  </si>
+  <si>
+    <t>normal findings</t>
+  </si>
+  <si>
+    <t>mec</t>
+  </si>
+  <si>
+    <t>middle ear cavity</t>
+  </si>
+  <si>
+    <t>eac</t>
+  </si>
+  <si>
+    <t>external auditory canal</t>
+  </si>
+  <si>
+    <t>iac</t>
+  </si>
+  <si>
+    <t>internal acoustic canal</t>
+  </si>
+  <si>
+    <t>cp</t>
+  </si>
+  <si>
+    <t>cerebello-pontine</t>
+  </si>
+  <si>
+    <t>cpa</t>
+  </si>
+  <si>
+    <t>cerebello-pontine angle</t>
+  </si>
+  <si>
+    <t>scc</t>
+  </si>
+  <si>
+    <t>semicircular canal</t>
+  </si>
+  <si>
+    <t>pce</t>
+  </si>
+  <si>
+    <t>post-contrast enhancement</t>
+  </si>
+  <si>
+    <t>pci</t>
+  </si>
+  <si>
+    <t>post-contrast images</t>
+  </si>
+  <si>
+    <t>postop</t>
+  </si>
+  <si>
+    <t>post-operative</t>
+  </si>
+  <si>
+    <t>snp</t>
+  </si>
+  <si>
+    <t>sinonasal polyposis</t>
+  </si>
+  <si>
+    <t>pans</t>
+  </si>
+  <si>
+    <t>pansinusitis</t>
+  </si>
+  <si>
+    <t>pred</t>
+  </si>
+  <si>
+    <t>predominantly</t>
+  </si>
+  <si>
+    <t>obs</t>
+  </si>
+  <si>
+    <t>obstruction</t>
+  </si>
+  <si>
+    <t>gbl</t>
+  </si>
+  <si>
+    <t>gall bladder lumen</t>
+  </si>
+  <si>
+    <t>ts</t>
+  </si>
+  <si>
+    <t>thecal sac</t>
+  </si>
+  <si>
+    <t>ats</t>
+  </si>
+  <si>
+    <t>anterior thecal sac</t>
+  </si>
+  <si>
+    <t>nr</t>
+  </si>
+  <si>
+    <t>nerve root</t>
+  </si>
+  <si>
+    <t>tnr</t>
+  </si>
+  <si>
+    <t>traversing nerve root</t>
+  </si>
+  <si>
+    <t>enr</t>
+  </si>
+  <si>
+    <t>exiting nerve root</t>
+  </si>
+  <si>
+    <t>spc</t>
+  </si>
+  <si>
+    <t>spinal cord</t>
+  </si>
+  <si>
+    <t>pp</t>
+  </si>
+  <si>
+    <t>peripheral</t>
+  </si>
+  <si>
+    <t>irr</t>
+  </si>
+  <si>
+    <t>irregular</t>
+  </si>
+  <si>
+    <t>ca</t>
+  </si>
+  <si>
+    <t>carcinoma</t>
+  </si>
+  <si>
+    <t>adenoca</t>
+  </si>
+  <si>
+    <t>adenocarcinoma</t>
+  </si>
+  <si>
+    <t>cholangioca</t>
+  </si>
+  <si>
+    <t>cholangiocarcinoma</t>
+  </si>
+  <si>
+    <t>acj</t>
+  </si>
+  <si>
+    <t>acromio-clavicular joint</t>
+  </si>
+  <si>
+    <t>scm</t>
+  </si>
+  <si>
+    <t>sternocleidomastoid</t>
+  </si>
+  <si>
+    <t>bm</t>
+  </si>
+  <si>
+    <t>bone marrow</t>
+  </si>
+  <si>
+    <t>sol</t>
+  </si>
+  <si>
+    <t>space occupying lesion</t>
+  </si>
+  <si>
+    <t>pod</t>
+  </si>
+  <si>
+    <t>pouch of Douglas</t>
+  </si>
+  <si>
+    <t>et</t>
+  </si>
+  <si>
+    <t>endometrial thickness</t>
+  </si>
+  <si>
+    <t>jz</t>
+  </si>
+  <si>
+    <t>junctional zone</t>
+  </si>
+  <si>
+    <t>jxn</t>
+  </si>
+  <si>
+    <t>junction</t>
+  </si>
+  <si>
+    <t>icj</t>
+  </si>
+  <si>
+    <t>ileo-cecal junction</t>
+  </si>
+  <si>
+    <t>cbd</t>
+  </si>
+  <si>
+    <t>common bile duct</t>
+  </si>
+  <si>
+    <t>sij</t>
+  </si>
+  <si>
+    <t>sacro-iliac joint</t>
+  </si>
+  <si>
+    <t>pit</t>
+  </si>
+  <si>
+    <t>pituitary</t>
+  </si>
+  <si>
+    <t>abn</t>
+  </si>
+  <si>
+    <t>abnormal</t>
+  </si>
+  <si>
+    <t>acom</t>
+  </si>
+  <si>
+    <t>anterior communicating artery</t>
+  </si>
+  <si>
+    <t>pcom</t>
+  </si>
+  <si>
+    <t>posterior communicating artery</t>
+  </si>
+  <si>
+    <t>art</t>
+  </si>
+  <si>
+    <t>artery</t>
+  </si>
+  <si>
+    <t>anterior cerebral artery</t>
+  </si>
+  <si>
+    <t>mpd</t>
+  </si>
+  <si>
+    <t>main pancreatic duct</t>
+  </si>
+  <si>
+    <t>mpa</t>
+  </si>
+  <si>
+    <t>main pulmonary artery</t>
+  </si>
+  <si>
+    <t>mpt</t>
+  </si>
+  <si>
+    <t>main pulmonary trunk</t>
+  </si>
+  <si>
+    <t>lev</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>wi</t>
+  </si>
+  <si>
+    <t>which is</t>
+  </si>
+  <si>
+    <t>abu</t>
+  </si>
+  <si>
+    <t>abutting</t>
+  </si>
+  <si>
+    <t>abut</t>
+  </si>
+  <si>
+    <t>abutment</t>
+  </si>
+  <si>
+    <t>comp</t>
+  </si>
+  <si>
+    <t>compression</t>
+  </si>
+  <si>
+    <t>comm</t>
+  </si>
+  <si>
+    <t>communication</t>
+  </si>
+  <si>
+    <t>dz</t>
+  </si>
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>nos</t>
+  </si>
+  <si>
+    <t>No septations, solid component or calcification noted within.</t>
+  </si>
+  <si>
+    <t>recc</t>
+  </si>
+  <si>
+    <t>renal cortical cyst</t>
+  </si>
+  <si>
+    <t>Atherosclerotic changes are noted in the aorta and its branches.</t>
+  </si>
+  <si>
+    <t>Degenerative changes are seen in visualised spine.</t>
+  </si>
+  <si>
+    <t>ow</t>
+  </si>
+  <si>
+    <t>otherwise</t>
+  </si>
+  <si>
+    <t>hwe</t>
+  </si>
+  <si>
+    <t>however</t>
+  </si>
+  <si>
+    <t>csp</t>
+  </si>
+  <si>
+    <t>cavum septum pellucidum</t>
+  </si>
+  <si>
+    <t>abd</t>
+  </si>
+  <si>
+    <t>abdominal</t>
+  </si>
+  <si>
+    <t>aaw</t>
+  </si>
+  <si>
+    <t>anterior abdominal wall</t>
+  </si>
+  <si>
+    <t>abdly</t>
+  </si>
+  <si>
+    <t>abdominal lymphadenopathy</t>
+  </si>
+  <si>
+    <t>retly</t>
+  </si>
+  <si>
+    <t>retroperitoneal lymphadenopathy</t>
+  </si>
+  <si>
+    <t>rp</t>
+  </si>
+  <si>
+    <t>retroperitoneum</t>
+  </si>
+  <si>
+    <t>peric</t>
+  </si>
+  <si>
+    <t>pericardial</t>
+  </si>
+  <si>
+    <t>abdp</t>
+  </si>
+  <si>
+    <t>abdomen and pelvis</t>
+  </si>
+  <si>
+    <t>subseg</t>
+  </si>
+  <si>
+    <t>subsegmental</t>
+  </si>
+  <si>
+    <t>nehng</t>
+  </si>
+  <si>
+    <t>nenhg</t>
+  </si>
+  <si>
+    <t>locll</t>
+  </si>
+  <si>
+    <t>Loss of cervical and lumbar lordosis is seen.</t>
+  </si>
+  <si>
+    <t>duo</t>
+  </si>
+  <si>
+    <t>duodenum</t>
+  </si>
+  <si>
+    <t>pcs</t>
+  </si>
+  <si>
+    <t>pelvicalyceal system</t>
+  </si>
+  <si>
+    <t>cld</t>
+  </si>
+  <si>
+    <t>chronic liver disease</t>
+  </si>
+  <si>
+    <t>ckd</t>
+  </si>
+  <si>
+    <t>chronic kidney disease</t>
+  </si>
+  <si>
+    <t>wo</t>
+  </si>
+  <si>
+    <t>without</t>
+  </si>
+  <si>
+    <t>pe</t>
+  </si>
+  <si>
+    <t>pulmonary embolism</t>
+  </si>
+  <si>
+    <t>sca</t>
+  </si>
+  <si>
+    <t>subclavian artery</t>
+  </si>
+  <si>
+    <t>supraclavicular</t>
+  </si>
+  <si>
+    <t>suprac</t>
+  </si>
+  <si>
+    <t>fpt</t>
+  </si>
+  <si>
+    <t>fronto-parieto-temporal</t>
+  </si>
+  <si>
+    <t>fpto</t>
+  </si>
+  <si>
+    <t>fronto-parieto-temporo-occipital</t>
+  </si>
+  <si>
+    <t>pto</t>
+  </si>
+  <si>
+    <t>parieto-temporo-occipital</t>
+  </si>
+  <si>
+    <t>itfo</t>
+  </si>
+  <si>
+    <t>in the form of</t>
+  </si>
+  <si>
+    <t>adb</t>
+  </si>
+  <si>
+    <t>asymmetric disc bulge</t>
+  </si>
+  <si>
+    <t>atsl</t>
+  </si>
+  <si>
+    <t>at the same level</t>
+  </si>
+  <si>
+    <t>vl</t>
+  </si>
+  <si>
+    <t>vertebral level</t>
+  </si>
+  <si>
+    <t>mvl</t>
+  </si>
+  <si>
+    <t>multiple vertebral levels</t>
+  </si>
+  <si>
+    <t>mvs</t>
+  </si>
+  <si>
+    <t>multiple variable sized</t>
+  </si>
+  <si>
+    <t>mul</t>
+  </si>
+  <si>
+    <t>multiple</t>
+  </si>
+  <si>
+    <t>isi</t>
+  </si>
+  <si>
+    <t>iso signal intensity</t>
+  </si>
+  <si>
+    <t>rena</t>
+  </si>
+  <si>
+    <t>renal artery</t>
+  </si>
+  <si>
+    <t>renv</t>
+  </si>
+  <si>
+    <t>renal vein</t>
+  </si>
+  <si>
+    <t>puj</t>
+  </si>
+  <si>
+    <t>pelviureteric junction</t>
+  </si>
+  <si>
+    <t>vuj</t>
+  </si>
+  <si>
+    <t>vesicoureteric junction</t>
+  </si>
+  <si>
+    <t>pujo</t>
+  </si>
+  <si>
+    <t>pelviureteric junction obstruction</t>
+  </si>
+  <si>
+    <t>internal</t>
+  </si>
+  <si>
+    <t>external</t>
+  </si>
+  <si>
+    <t>extn</t>
+  </si>
+  <si>
+    <t>intm</t>
+  </si>
+  <si>
+    <t>anteromedial</t>
+  </si>
+  <si>
+    <t>bw</t>
+  </si>
+  <si>
+    <t>between</t>
+  </si>
+  <si>
+    <t>asup</t>
+  </si>
+  <si>
+    <t>anterosuperior</t>
+  </si>
+  <si>
+    <t>psup</t>
+  </si>
+  <si>
+    <t>posterosuperior</t>
+  </si>
+  <si>
+    <t>alat</t>
+  </si>
+  <si>
+    <t>anterolateral</t>
+  </si>
+  <si>
+    <t>ap</t>
+  </si>
+  <si>
+    <t>anteroposterior</t>
+  </si>
+  <si>
+    <t>posteromedial</t>
+  </si>
+  <si>
+    <t>plat</t>
+  </si>
+  <si>
+    <t>posterolateral</t>
+  </si>
+  <si>
+    <t>ainf</t>
+  </si>
+  <si>
+    <t>anteroinferior</t>
+  </si>
+  <si>
+    <t>pinf</t>
+  </si>
+  <si>
+    <t>posteroinferior</t>
+  </si>
+  <si>
+    <t>pa</t>
+  </si>
+  <si>
+    <t>posteroanterior</t>
+  </si>
+  <si>
+    <t>vrs</t>
+  </si>
+  <si>
+    <t>Multiple tiny T2 high signal intensity foci noted in  bilateral frontoparietal lobe which are suppressed on FLAIR , likely Virchow Robin spaces.</t>
+  </si>
+  <si>
+    <t>tmas</t>
+  </si>
+  <si>
+    <t>T2 high signal intensity noted in bilateral maxillary sinus - suggestive of sinusitis.</t>
+  </si>
+  <si>
+    <t>T2 high signal intensity with convex free margin is noted in right maxillary sinus - polyp/ retention cyst.</t>
+  </si>
+  <si>
+    <t>tpor</t>
+  </si>
+  <si>
+    <t>hcc</t>
+  </si>
+  <si>
+    <t>hepatocellular carcinoma</t>
+  </si>
+  <si>
+    <t>rcc</t>
+  </si>
+  <si>
+    <t>renal cell carcinoma</t>
+  </si>
+  <si>
+    <t>tcc</t>
+  </si>
+  <si>
+    <t>transitional cell carcinoma</t>
+  </si>
+  <si>
+    <t>ehpvo</t>
+  </si>
+  <si>
+    <t>extrahepatic portal vein obstruction</t>
+  </si>
+  <si>
+    <t>nsf</t>
+  </si>
+  <si>
+    <t>non-specific</t>
+  </si>
+  <si>
+    <t>com</t>
+  </si>
+  <si>
+    <t>complete</t>
+  </si>
+  <si>
+    <t>rhv</t>
+  </si>
+  <si>
+    <t>right hepatic vein</t>
+  </si>
+  <si>
+    <t>mhv</t>
+  </si>
+  <si>
+    <t>middle hepatic vein</t>
+  </si>
+  <si>
+    <t>lhv</t>
+  </si>
+  <si>
+    <t>left hepatic vein</t>
+  </si>
+  <si>
+    <t>adpkd</t>
+  </si>
+  <si>
+    <t>autosomal dominant polycystic kidney disease</t>
+  </si>
+  <si>
+    <t>gist</t>
+  </si>
+  <si>
+    <t>gastrointestinal stromal tumor</t>
+  </si>
+  <si>
+    <t>adem</t>
+  </si>
+  <si>
+    <t>acute disseminated encephalomyelitis</t>
+  </si>
+  <si>
+    <t>letm</t>
+  </si>
+  <si>
+    <t>longitudinally extensive transverse myelitis</t>
+  </si>
+  <si>
+    <t>nmosd</t>
+  </si>
+  <si>
+    <t>neuromyelitis optica spectrum disorder</t>
+  </si>
+  <si>
+    <t>mogad</t>
+  </si>
+  <si>
+    <t>myelin oligodendrocyte glycoprotein antibody-associated disease</t>
+  </si>
+  <si>
+    <t>ms</t>
+  </si>
+  <si>
+    <t>multiple sclerosis</t>
+  </si>
+  <si>
+    <t>ncc</t>
+  </si>
+  <si>
+    <t>neurocysticercosis</t>
+  </si>
+  <si>
+    <t>slo</t>
+  </si>
+  <si>
+    <t>spanning a length of</t>
+  </si>
+  <si>
+    <t>hee</t>
+  </si>
+  <si>
+    <t>heterogeneous enhancement</t>
+  </si>
+  <si>
+    <t>hoe</t>
+  </si>
+  <si>
+    <t>homogeneous enhancement</t>
+  </si>
+  <si>
+    <t>enc</t>
+  </si>
+  <si>
+    <t>encasing</t>
+  </si>
+  <si>
+    <t>sec</t>
+  </si>
+  <si>
+    <t>secondary</t>
+  </si>
+  <si>
+    <t>pri</t>
+  </si>
+  <si>
+    <t>primary</t>
+  </si>
+  <si>
+    <t>reg</t>
+  </si>
+  <si>
+    <t>region</t>
+  </si>
+  <si>
+    <t>cs</t>
+  </si>
+  <si>
+    <t>cervical spine</t>
+  </si>
+  <si>
+    <t>ds</t>
+  </si>
+  <si>
+    <t>dorsal spine</t>
+  </si>
+  <si>
+    <t>ls</t>
+  </si>
+  <si>
+    <t>lumbar spine</t>
+  </si>
+  <si>
+    <t>lss</t>
+  </si>
+  <si>
+    <t>lumbosacral spine</t>
+  </si>
+  <si>
+    <t>dt</t>
+  </si>
+  <si>
+    <t>due to</t>
+  </si>
+  <si>
+    <t>mets</t>
+  </si>
+  <si>
+    <t>metastasis</t>
+  </si>
+  <si>
+    <t>disp</t>
+  </si>
+  <si>
+    <t>displacement</t>
+  </si>
+  <si>
+    <t>rhd</t>
+  </si>
+  <si>
+    <t>right hepatic duct</t>
+  </si>
+  <si>
+    <t>lhd</t>
+  </si>
+  <si>
+    <t>left hepatic duct</t>
+  </si>
+  <si>
+    <t>asd</t>
+  </si>
+  <si>
+    <t>anterior sectoral duct</t>
+  </si>
+  <si>
+    <t>psd</t>
+  </si>
+  <si>
+    <t>posterior sectoral duct</t>
+  </si>
+  <si>
+    <t>allg</t>
+  </si>
+  <si>
+    <t>pmed</t>
+  </si>
+  <si>
+    <t>amed</t>
   </si>
 </sst>
 </file>
@@ -158,6 +3491,20 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B572" totalsRowShown="0">
+  <autoFilter ref="A1:B572" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B572">
+    <sortCondition ref="A1:A572"/>
+  </sortState>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
+    <tableColumn id="2" xr3:uid="{E6F1011B-AD4F-4E60-AC2C-05C4D215D6C1}" name="replacement"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight13" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -423,7 +3770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B572"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -440,109 +3787,4577 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>149</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>969</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>970</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>967</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>968</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>971</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>972</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>979</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>980</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>926</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>927</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>945</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>946</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>947</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>948</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>340</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>348</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>309</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>934</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>902</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>903</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>221</v>
+      </c>
+      <c r="B14" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>928</v>
+      </c>
+      <c r="B15" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>824</v>
+      </c>
+      <c r="B16" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>898</v>
+      </c>
+      <c r="B19" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>787</v>
+      </c>
+      <c r="B20" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>176</v>
+      </c>
+      <c r="B22" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>139</v>
+      </c>
+      <c r="B23" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>140</v>
+      </c>
+      <c r="B24" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>163</v>
+      </c>
+      <c r="B25" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B28" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>152</v>
+      </c>
+      <c r="B33" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>71</v>
+      </c>
+      <c r="B35" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>284</v>
+      </c>
+      <c r="B36" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>143</v>
+      </c>
+      <c r="B37" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>932</v>
+      </c>
+      <c r="B38" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>150</v>
+      </c>
+      <c r="B39" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>679</v>
+      </c>
+      <c r="B41" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>168</v>
+      </c>
+      <c r="B43" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>293</v>
+      </c>
+      <c r="B44" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>312</v>
+      </c>
+      <c r="B45" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>241</v>
+      </c>
+      <c r="B46" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>197</v>
+      </c>
+      <c r="B47" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>248</v>
+      </c>
+      <c r="B48" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>666</v>
+      </c>
+      <c r="B49" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>242</v>
+      </c>
+      <c r="B50" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>882</v>
+      </c>
+      <c r="B51" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>793</v>
+      </c>
+      <c r="B53" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>795</v>
+      </c>
+      <c r="B54" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>302</v>
+      </c>
+      <c r="B55" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>305</v>
+      </c>
+      <c r="B56" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>232</v>
+      </c>
+      <c r="B57" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>234</v>
+      </c>
+      <c r="B58" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>808</v>
+      </c>
+      <c r="B59" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>320</v>
+      </c>
+      <c r="B60" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>781</v>
+      </c>
+      <c r="B61" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>63</v>
+      </c>
+      <c r="B62" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>60</v>
+      </c>
+      <c r="B64" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>906</v>
+      </c>
+      <c r="B65" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>678</v>
+      </c>
+      <c r="B66" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>239</v>
+      </c>
+      <c r="B67" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>62</v>
+      </c>
+      <c r="B68" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>687</v>
+      </c>
+      <c r="B70" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>688</v>
+      </c>
+      <c r="B71" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>689</v>
+      </c>
+      <c r="B72" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>690</v>
+      </c>
+      <c r="B73" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>691</v>
+      </c>
+      <c r="B74" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>692</v>
+      </c>
+      <c r="B75" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>693</v>
+      </c>
+      <c r="B76" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>896</v>
+      </c>
+      <c r="B77" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>323</v>
+      </c>
+      <c r="B78" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>196</v>
+      </c>
+      <c r="B79" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>21</v>
+      </c>
+      <c r="B80" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>19</v>
+      </c>
+      <c r="B81" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>198</v>
+      </c>
+      <c r="B82" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>289</v>
+      </c>
+      <c r="B83" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>288</v>
+      </c>
+      <c r="B84" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>339</v>
+      </c>
+      <c r="B85" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>920</v>
+      </c>
+      <c r="B86" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>307</v>
+      </c>
+      <c r="B87" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>325</v>
+      </c>
+      <c r="B88" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>278</v>
+      </c>
+      <c r="B89" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>335</v>
+      </c>
+      <c r="B90" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>44</v>
+      </c>
+      <c r="B91" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>43</v>
+      </c>
+      <c r="B92" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>668</v>
+      </c>
+      <c r="B93" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>219</v>
+      </c>
+      <c r="B94" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>290</v>
+      </c>
+      <c r="B95" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>220</v>
+      </c>
+      <c r="B96" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>298</v>
+      </c>
+      <c r="B97" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>201</v>
+      </c>
+      <c r="B98" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>667</v>
+      </c>
+      <c r="B99" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>114</v>
+      </c>
+      <c r="B100" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>85</v>
+      </c>
+      <c r="B101" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>117</v>
+      </c>
+      <c r="B102" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>900</v>
+      </c>
+      <c r="B103" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>828</v>
+      </c>
+      <c r="B104" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>154</v>
+      </c>
+      <c r="B105" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>126</v>
+      </c>
+      <c r="B106" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>127</v>
+      </c>
+      <c r="B107" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>157</v>
+      </c>
+      <c r="B108" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>993</v>
+      </c>
+      <c r="B109" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>86</v>
+      </c>
+      <c r="B110" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>991</v>
+      </c>
+      <c r="B111" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>105</v>
+      </c>
+      <c r="B112" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>200</v>
+      </c>
+      <c r="B113" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>316</v>
+      </c>
+      <c r="B114" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>106</v>
+      </c>
+      <c r="B115" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>165</v>
+      </c>
+      <c r="B116" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>103</v>
+      </c>
+      <c r="B117" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>104</v>
+      </c>
+      <c r="B118" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>951</v>
+      </c>
+      <c r="B120" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>949</v>
+      </c>
+      <c r="B121" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>164</v>
+      </c>
+      <c r="B122" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>858</v>
+      </c>
+      <c r="B123" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>860</v>
+      </c>
+      <c r="B124" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B125" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>684</v>
+      </c>
+      <c r="B126" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>665</v>
+      </c>
+      <c r="B127" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>965</v>
+      </c>
+      <c r="B128" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>702</v>
+      </c>
+      <c r="B129" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>703</v>
+      </c>
+      <c r="B130" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>704</v>
+      </c>
+      <c r="B131" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>694</v>
+      </c>
+      <c r="B132" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>695</v>
+      </c>
+      <c r="B133" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>696</v>
+      </c>
+      <c r="B134" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>697</v>
+      </c>
+      <c r="B135" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>698</v>
+      </c>
+      <c r="B136" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>699</v>
+      </c>
+      <c r="B137" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>700</v>
+      </c>
+      <c r="B138" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>701</v>
+      </c>
+      <c r="B139" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>177</v>
+      </c>
+      <c r="B140" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>213</v>
+      </c>
+      <c r="B141" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>215</v>
+      </c>
+      <c r="B142" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>151</v>
+      </c>
+      <c r="B143" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>249</v>
+      </c>
+      <c r="B144" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>247</v>
+      </c>
+      <c r="B145" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>338</v>
+      </c>
+      <c r="B146" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>669</v>
+      </c>
+      <c r="B147" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>93</v>
+      </c>
+      <c r="B148" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>268</v>
+      </c>
+      <c r="B149" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B150" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>820</v>
+      </c>
+      <c r="B151" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>297</v>
+      </c>
+      <c r="B152" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B153" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B154" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>153</v>
+      </c>
+      <c r="B155" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>987</v>
+      </c>
+      <c r="B156" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>834</v>
+      </c>
+      <c r="B157" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>953</v>
+      </c>
+      <c r="B158" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>854</v>
+      </c>
+      <c r="B159" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>812</v>
+      </c>
+      <c r="B160" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>773</v>
+      </c>
+      <c r="B161" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>102</v>
+      </c>
+      <c r="B162" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B163" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>156</v>
+      </c>
+      <c r="B164" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>159</v>
+      </c>
+      <c r="B165" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>25</v>
+      </c>
+      <c r="B166" t="s">
         <v>26</v>
       </c>
-      <c r="B14" t="s">
-        <v>25</v>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B167" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>840</v>
+      </c>
+      <c r="B168" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>132</v>
+      </c>
+      <c r="B169" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>324</v>
+      </c>
+      <c r="B170" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>888</v>
+      </c>
+      <c r="B171" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>185</v>
+      </c>
+      <c r="B172" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>912</v>
+      </c>
+      <c r="B173" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>34</v>
+      </c>
+      <c r="B174" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>37</v>
+      </c>
+      <c r="B175" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>783</v>
+      </c>
+      <c r="B176" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>171</v>
+      </c>
+      <c r="B177" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>172</v>
+      </c>
+      <c r="B178" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B179" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
+        <v>180</v>
+      </c>
+      <c r="B180" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
+        <v>113</v>
+      </c>
+      <c r="B181" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>240</v>
+      </c>
+      <c r="B182" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A183" t="s">
+        <v>108</v>
+      </c>
+      <c r="B183" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>111</v>
+      </c>
+      <c r="B184" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>181</v>
+      </c>
+      <c r="B185" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
+        <v>686</v>
+      </c>
+      <c r="B186" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A187" t="s">
+        <v>99</v>
+      </c>
+      <c r="B187" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A188" t="s">
+        <v>112</v>
+      </c>
+      <c r="B188" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A189" t="s">
+        <v>244</v>
+      </c>
+      <c r="B189" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A190" t="s">
+        <v>228</v>
+      </c>
+      <c r="B190" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>179</v>
+      </c>
+      <c r="B191" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
+        <v>184</v>
+      </c>
+      <c r="B192" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A193" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B193" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B194" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
+        <v>255</v>
+      </c>
+      <c r="B195" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
+        <v>36</v>
+      </c>
+      <c r="B196" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A197" t="s">
+        <v>806</v>
+      </c>
+      <c r="B197" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A198" t="s">
+        <v>182</v>
+      </c>
+      <c r="B198" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A199" t="s">
+        <v>277</v>
+      </c>
+      <c r="B199" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A200" t="s">
+        <v>878</v>
+      </c>
+      <c r="B200" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A201" t="s">
+        <v>118</v>
+      </c>
+      <c r="B201" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A202" t="s">
+        <v>210</v>
+      </c>
+      <c r="B202" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A203" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B203" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A204" t="s">
+        <v>120</v>
+      </c>
+      <c r="B204" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
+        <v>660</v>
+      </c>
+      <c r="B205" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A206" t="s">
+        <v>836</v>
+      </c>
+      <c r="B206" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A207" t="s">
+        <v>300</v>
+      </c>
+      <c r="B207" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
+        <v>662</v>
+      </c>
+      <c r="B208" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
+        <v>663</v>
+      </c>
+      <c r="B209" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B210" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
+        <v>92</v>
+      </c>
+      <c r="B211" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
+        <v>90</v>
+      </c>
+      <c r="B212" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>91</v>
+      </c>
+      <c r="B213" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B214" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
+        <v>23</v>
+      </c>
+      <c r="B215" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
+        <v>5</v>
+      </c>
+      <c r="B216" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A217" t="s">
+        <v>128</v>
+      </c>
+      <c r="B217" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>130</v>
+      </c>
+      <c r="B218" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
+        <v>133</v>
+      </c>
+      <c r="B219" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
+        <v>134</v>
+      </c>
+      <c r="B220" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A221" t="s">
+        <v>121</v>
+      </c>
+      <c r="B221" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>279</v>
+      </c>
+      <c r="B222" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B223" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
+        <v>9</v>
+      </c>
+      <c r="B224" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
+        <v>131</v>
+      </c>
+      <c r="B225" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
+        <v>129</v>
+      </c>
+      <c r="B226" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>175</v>
+      </c>
+      <c r="B227" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>264</v>
+      </c>
+      <c r="B228" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>79</v>
+      </c>
+      <c r="B229" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>963</v>
+      </c>
+      <c r="B230" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>170</v>
+      </c>
+      <c r="B231" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>169</v>
+      </c>
+      <c r="B232" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>856</v>
+      </c>
+      <c r="B233" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>810</v>
+      </c>
+      <c r="B234" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>306</v>
+      </c>
+      <c r="B235" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>777</v>
+      </c>
+      <c r="B236" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>918</v>
+      </c>
+      <c r="B237" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>671</v>
+      </c>
+      <c r="B238" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>88</v>
+      </c>
+      <c r="B239" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>89</v>
+      </c>
+      <c r="B240" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>155</v>
+      </c>
+      <c r="B241" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
+        <v>158</v>
+      </c>
+      <c r="B242" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A243" t="s">
+        <v>160</v>
+      </c>
+      <c r="B243" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A244" t="s">
+        <v>253</v>
+      </c>
+      <c r="B244" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A245" t="s">
+        <v>287</v>
+      </c>
+      <c r="B245" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A246" t="s">
+        <v>328</v>
+      </c>
+      <c r="B246" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A247" t="s">
+        <v>329</v>
+      </c>
+      <c r="B247" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A248" t="s">
+        <v>231</v>
+      </c>
+      <c r="B248" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A249" t="s">
+        <v>57</v>
+      </c>
+      <c r="B249" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A250" t="s">
+        <v>676</v>
+      </c>
+      <c r="B250" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A251" t="s">
+        <v>237</v>
+      </c>
+      <c r="B251" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A252" t="s">
+        <v>59</v>
+      </c>
+      <c r="B252" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A253" t="s">
+        <v>238</v>
+      </c>
+      <c r="B253" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A254" t="s">
+        <v>785</v>
+      </c>
+      <c r="B254" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A255" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B255" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A256" t="s">
+        <v>166</v>
+      </c>
+      <c r="B256" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A257" t="s">
+        <v>203</v>
+      </c>
+      <c r="B257" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A258" t="s">
+        <v>206</v>
+      </c>
+      <c r="B258" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A259" t="s">
+        <v>315</v>
+      </c>
+      <c r="B259" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A260" t="s">
+        <v>894</v>
+      </c>
+      <c r="B260" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A261" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B261" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A262" t="s">
+        <v>260</v>
+      </c>
+      <c r="B262" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A263" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B263" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A264" t="s">
+        <v>162</v>
+      </c>
+      <c r="B264" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A265" t="s">
+        <v>711</v>
+      </c>
+      <c r="B265" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A266" t="s">
+        <v>779</v>
+      </c>
+      <c r="B266" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A267" t="s">
+        <v>916</v>
+      </c>
+      <c r="B267" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A268" t="s">
+        <v>914</v>
+      </c>
+      <c r="B268" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A269" t="s">
+        <v>186</v>
+      </c>
+      <c r="B269" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A270" t="s">
+        <v>246</v>
+      </c>
+      <c r="B270" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A271" t="s">
+        <v>245</v>
+      </c>
+      <c r="B271" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A272" t="s">
+        <v>705</v>
+      </c>
+      <c r="B272" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A273" t="s">
+        <v>706</v>
+      </c>
+      <c r="B273" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A274" t="s">
+        <v>707</v>
+      </c>
+      <c r="B274" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A275" t="s">
+        <v>708</v>
+      </c>
+      <c r="B275" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
+        <v>709</v>
+      </c>
+      <c r="B276" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A277" t="s">
+        <v>282</v>
+      </c>
+      <c r="B277" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A278" t="s">
+        <v>283</v>
+      </c>
+      <c r="B278" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A279" t="s">
+        <v>51</v>
+      </c>
+      <c r="B279" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A280" t="s">
+        <v>55</v>
+      </c>
+      <c r="B280" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A281" t="s">
+        <v>138</v>
+      </c>
+      <c r="B281" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>74</v>
+      </c>
+      <c r="B282" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>223</v>
+      </c>
+      <c r="B283" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>15</v>
+      </c>
+      <c r="B284" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B285" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>941</v>
+      </c>
+      <c r="B286" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>110</v>
+      </c>
+      <c r="B287" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>243</v>
+      </c>
+      <c r="B288" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>330</v>
+      </c>
+      <c r="B289" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B290" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B291" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>123</v>
+      </c>
+      <c r="B292" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A293" t="s">
+        <v>769</v>
+      </c>
+      <c r="B293" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A294" t="s">
+        <v>800</v>
+      </c>
+      <c r="B294" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A295" t="s">
+        <v>136</v>
+      </c>
+      <c r="B295" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A296" t="s">
+        <v>65</v>
+      </c>
+      <c r="B296" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A297" t="s">
+        <v>226</v>
+      </c>
+      <c r="B297" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A298" t="s">
+        <v>27</v>
+      </c>
+      <c r="B298" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A299" t="s">
+        <v>28</v>
+      </c>
+      <c r="B299" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A300" t="s">
+        <v>209</v>
+      </c>
+      <c r="B300" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A301" t="s">
+        <v>985</v>
+      </c>
+      <c r="B301" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A302" t="s">
+        <v>208</v>
+      </c>
+      <c r="B302" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
+        <v>204</v>
+      </c>
+      <c r="B303" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>207</v>
+      </c>
+      <c r="B304" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A305" t="s">
+        <v>147</v>
+      </c>
+      <c r="B305" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A306" t="s">
+        <v>682</v>
+      </c>
+      <c r="B306" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A307" t="s">
+        <v>173</v>
+      </c>
+      <c r="B307" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A308" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B308" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
+        <v>265</v>
+      </c>
+      <c r="B309" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B310" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>82</v>
+      </c>
+      <c r="B311" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
+        <v>67</v>
+      </c>
+      <c r="B312" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A313" t="s">
+        <v>193</v>
+      </c>
+      <c r="B313" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
+        <v>125</v>
+      </c>
+      <c r="B314" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
+        <v>194</v>
+      </c>
+      <c r="B315" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A316" t="s">
+        <v>233</v>
+      </c>
+      <c r="B316" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A317" t="s">
+        <v>235</v>
+      </c>
+      <c r="B317" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A318" t="s">
+        <v>33</v>
+      </c>
+      <c r="B318" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A319" t="s">
+        <v>32</v>
+      </c>
+      <c r="B319" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A320" t="s">
+        <v>39</v>
+      </c>
+      <c r="B320" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
+        <v>73</v>
+      </c>
+      <c r="B321" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A322" t="s">
+        <v>308</v>
+      </c>
+      <c r="B322" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A323" t="s">
+        <v>224</v>
+      </c>
+      <c r="B323" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
+        <v>317</v>
+      </c>
+      <c r="B324" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A325" t="s">
+        <v>280</v>
+      </c>
+      <c r="B325" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A326" t="s">
+        <v>281</v>
+      </c>
+      <c r="B326" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A327" t="s">
+        <v>852</v>
+      </c>
+      <c r="B327" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A328" t="s">
+        <v>50</v>
+      </c>
+      <c r="B328" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A329" t="s">
+        <v>148</v>
+      </c>
+      <c r="B329" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A330" t="s">
+        <v>54</v>
+      </c>
+      <c r="B330" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A331" t="s">
+        <v>225</v>
+      </c>
+      <c r="B331" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A332" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B332" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A333" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B333" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A334" t="s">
+        <v>98</v>
+      </c>
+      <c r="B334" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A335" t="s">
+        <v>250</v>
+      </c>
+      <c r="B335" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A336" t="s">
+        <v>251</v>
+      </c>
+      <c r="B336" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A337" t="s">
+        <v>96</v>
+      </c>
+      <c r="B337" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A338" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B338" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A339" t="s">
+        <v>214</v>
+      </c>
+      <c r="B339" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A340" t="s">
+        <v>937</v>
+      </c>
+      <c r="B340" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A341" t="s">
+        <v>935</v>
+      </c>
+      <c r="B341" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A342" t="s">
+        <v>939</v>
+      </c>
+      <c r="B342" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A343" t="s">
+        <v>332</v>
+      </c>
+      <c r="B343" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A344" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B344" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A345" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B345" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A346" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B346" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A347" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B347" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A348" t="s">
+        <v>84</v>
+      </c>
+      <c r="B348" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A349" t="s">
+        <v>791</v>
+      </c>
+      <c r="B349" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A350" t="s">
+        <v>199</v>
+      </c>
+      <c r="B350" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A351" t="s">
+        <v>673</v>
+      </c>
+      <c r="B351" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A352" t="s">
+        <v>842</v>
+      </c>
+      <c r="B352" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A353" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B353" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A354" t="s">
+        <v>3</v>
+      </c>
+      <c r="B354" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A355" t="s">
+        <v>983</v>
+      </c>
+      <c r="B355" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A356" t="s">
+        <v>984</v>
+      </c>
+      <c r="B356" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A357" t="s">
+        <v>683</v>
+      </c>
+      <c r="B357" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A358" t="s">
+        <v>789</v>
+      </c>
+      <c r="B358" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A359" t="s">
+        <v>87</v>
+      </c>
+      <c r="B359" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A360" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B360" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A361" t="s">
+        <v>850</v>
+      </c>
+      <c r="B361" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A362" t="s">
+        <v>830</v>
+      </c>
+      <c r="B362" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A363" t="s">
+        <v>189</v>
+      </c>
+      <c r="B363" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A364" t="s">
+        <v>848</v>
+      </c>
+      <c r="B364" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A365" t="s">
+        <v>955</v>
+      </c>
+      <c r="B365" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A366" t="s">
+        <v>884</v>
+      </c>
+      <c r="B366" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A367" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B367" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A368" t="s">
+        <v>818</v>
+      </c>
+      <c r="B368" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A369" t="s">
+        <v>816</v>
+      </c>
+      <c r="B369" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A370" t="s">
+        <v>13</v>
+      </c>
+      <c r="B370" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A371" t="s">
+        <v>838</v>
+      </c>
+      <c r="B371" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A372" t="s">
+        <v>188</v>
+      </c>
+      <c r="B372" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A373" t="s">
+        <v>832</v>
+      </c>
+      <c r="B373" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A374" t="s">
+        <v>322</v>
+      </c>
+      <c r="B374" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A375" t="s">
+        <v>675</v>
+      </c>
+      <c r="B375" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A376" t="s">
+        <v>876</v>
+      </c>
+      <c r="B376" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A377" t="s">
+        <v>677</v>
+      </c>
+      <c r="B377" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A378" t="s">
+        <v>672</v>
+      </c>
+      <c r="B378" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A379" t="s">
+        <v>258</v>
+      </c>
+      <c r="B379" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A380" t="s">
+        <v>262</v>
+      </c>
+      <c r="B380" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A381" t="s">
+        <v>263</v>
+      </c>
+      <c r="B381" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A382" t="s">
+        <v>190</v>
+      </c>
+      <c r="B382" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A383" t="s">
+        <v>192</v>
+      </c>
+      <c r="B383" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A384" t="s">
+        <v>961</v>
+      </c>
+      <c r="B384" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A385" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B385" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A386" t="s">
+        <v>211</v>
+      </c>
+      <c r="B386" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A387" t="s">
+        <v>872</v>
+      </c>
+      <c r="B387" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A388" t="s">
+        <v>145</v>
+      </c>
+      <c r="B388" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A389" t="s">
+        <v>142</v>
+      </c>
+      <c r="B389" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A390" t="s">
+        <v>256</v>
+      </c>
+      <c r="B390" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A391" t="s">
+        <v>333</v>
+      </c>
+      <c r="B391" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A392" t="s">
+        <v>212</v>
+      </c>
+      <c r="B392" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A393" t="s">
+        <v>236</v>
+      </c>
+      <c r="B393" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A394" t="s">
+        <v>75</v>
+      </c>
+      <c r="B394" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A395" t="s">
+        <v>344</v>
+      </c>
+      <c r="B395" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A396" t="s">
+        <v>310</v>
+      </c>
+      <c r="B396" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A397" t="s">
+        <v>864</v>
+      </c>
+      <c r="B397" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A398" t="s">
+        <v>866</v>
+      </c>
+      <c r="B398" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A399" t="s">
+        <v>222</v>
+      </c>
+      <c r="B399" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A400" t="s">
+        <v>930</v>
+      </c>
+      <c r="B400" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A401" t="s">
+        <v>989</v>
+      </c>
+      <c r="B401" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A402" t="s">
+        <v>229</v>
+      </c>
+      <c r="B402" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A403" t="s">
+        <v>336</v>
+      </c>
+      <c r="B403" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A404" t="s">
+        <v>997</v>
+      </c>
+      <c r="B404" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A405" t="s">
+        <v>797</v>
+      </c>
+      <c r="B405" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A406" t="s">
+        <v>296</v>
+      </c>
+      <c r="B406" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A407" t="s">
+        <v>977</v>
+      </c>
+      <c r="B407" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A408" t="s">
+        <v>341</v>
+      </c>
+      <c r="B408" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A409" t="s">
+        <v>799</v>
+      </c>
+      <c r="B409" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A410" t="s">
+        <v>342</v>
+      </c>
+      <c r="B410" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A411" t="s">
+        <v>343</v>
+      </c>
+      <c r="B411" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A412" t="s">
+        <v>664</v>
+      </c>
+      <c r="B412" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A413" t="s">
+        <v>41</v>
+      </c>
+      <c r="B413" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A414" t="s">
+        <v>40</v>
+      </c>
+      <c r="B414" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A415" t="s">
+        <v>345</v>
+      </c>
+      <c r="B415" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A416" t="s">
+        <v>109</v>
+      </c>
+      <c r="B416" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A417" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B417" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A418" t="s">
+        <v>924</v>
+      </c>
+      <c r="B418" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A419" t="s">
+        <v>119</v>
+      </c>
+      <c r="B419" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A420" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B420" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A421" t="s">
+        <v>100</v>
+      </c>
+      <c r="B421" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A422" t="s">
+        <v>101</v>
+      </c>
+      <c r="B422" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A423" t="s">
+        <v>685</v>
+      </c>
+      <c r="B423" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A424" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B424" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A425" t="s">
+        <v>844</v>
+      </c>
+      <c r="B425" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A426" t="s">
+        <v>115</v>
+      </c>
+      <c r="B426" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A427" t="s">
+        <v>910</v>
+      </c>
+      <c r="B427" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A428" t="s">
+        <v>47</v>
+      </c>
+      <c r="B428" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A429" t="s">
+        <v>292</v>
+      </c>
+      <c r="B429" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A430" t="s">
+        <v>301</v>
+      </c>
+      <c r="B430" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A431" t="s">
+        <v>49</v>
+      </c>
+      <c r="B431" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A432" t="s">
+        <v>868</v>
+      </c>
+      <c r="B432" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A433" t="s">
+        <v>53</v>
+      </c>
+      <c r="B433" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A434" t="s">
+        <v>892</v>
+      </c>
+      <c r="B434" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A435" t="s">
+        <v>116</v>
+      </c>
+      <c r="B435" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A436" t="s">
+        <v>874</v>
+      </c>
+      <c r="B436" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A437" t="s">
+        <v>146</v>
+      </c>
+      <c r="B437" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A438" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B438" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A439" t="s">
+        <v>178</v>
+      </c>
+      <c r="B439" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A440" t="s">
+        <v>318</v>
+      </c>
+      <c r="B440" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A441" t="s">
+        <v>31</v>
+      </c>
+      <c r="B441" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A442" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B442" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A443" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B443" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A444" t="s">
+        <v>295</v>
+      </c>
+      <c r="B444" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A445" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B445" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A446" t="s">
+        <v>303</v>
+      </c>
+      <c r="B446" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A447" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B447" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A448" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B448" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A449" t="s">
+        <v>77</v>
+      </c>
+      <c r="B449" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A450" t="s">
+        <v>78</v>
+      </c>
+      <c r="B450" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A451" t="s">
+        <v>80</v>
+      </c>
+      <c r="B451" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A452" t="s">
+        <v>331</v>
+      </c>
+      <c r="B452" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A453" t="s">
+        <v>771</v>
+      </c>
+      <c r="B453" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A454" t="s">
+        <v>826</v>
+      </c>
+      <c r="B454" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A455" t="s">
+        <v>137</v>
+      </c>
+      <c r="B455" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A456" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B456" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A457" t="s">
+        <v>217</v>
+      </c>
+      <c r="B457" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A458" t="s">
+        <v>957</v>
+      </c>
+      <c r="B458" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A459" t="s">
+        <v>218</v>
+      </c>
+      <c r="B459" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A460" t="s">
+        <v>319</v>
+      </c>
+      <c r="B460" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A461" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B461" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A462" t="s">
+        <v>216</v>
+      </c>
+      <c r="B462" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A463" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B463" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A464" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B464" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A465" t="s">
+        <v>227</v>
+      </c>
+      <c r="B465" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A466" t="s">
+        <v>973</v>
+      </c>
+      <c r="B466" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A467" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B467" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A468" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B468" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A469" t="s">
+        <v>95</v>
+      </c>
+      <c r="B469" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A470" t="s">
+        <v>122</v>
+      </c>
+      <c r="B470" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A471" t="s">
+        <v>802</v>
+      </c>
+      <c r="B471" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A472" t="s">
+        <v>135</v>
+      </c>
+      <c r="B472" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A473" t="s">
+        <v>64</v>
+      </c>
+      <c r="B473" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A474" t="s">
+        <v>68</v>
+      </c>
+      <c r="B474" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A475" t="s">
+        <v>846</v>
+      </c>
+      <c r="B475" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A476" t="s">
+        <v>975</v>
+      </c>
+      <c r="B476" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A477" t="s">
+        <v>81</v>
+      </c>
+      <c r="B477" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A478" t="s">
+        <v>66</v>
+      </c>
+      <c r="B478" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A479" t="s">
+        <v>124</v>
+      </c>
+      <c r="B479" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A480" t="s">
+        <v>183</v>
+      </c>
+      <c r="B480" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A481" t="s">
+        <v>822</v>
+      </c>
+      <c r="B481" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A482" t="s">
+        <v>710</v>
+      </c>
+      <c r="B482" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A483" t="s">
+        <v>286</v>
+      </c>
+      <c r="B483" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A484" t="s">
+        <v>999</v>
+      </c>
+      <c r="B484" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A485" t="s">
+        <v>862</v>
+      </c>
+      <c r="B485" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A486" t="s">
+        <v>285</v>
+      </c>
+      <c r="B486" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A487" t="s">
+        <v>904</v>
+      </c>
+      <c r="B487" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A488" t="s">
+        <v>775</v>
+      </c>
+      <c r="B488" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A489" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B489" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A490" t="s">
+        <v>69</v>
+      </c>
+      <c r="B490" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A491" t="s">
+        <v>70</v>
+      </c>
+      <c r="B491" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A492" t="s">
+        <v>97</v>
+      </c>
+      <c r="B492" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A493" t="s">
+        <v>291</v>
+      </c>
+      <c r="B493" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A494" t="s">
+        <v>299</v>
+      </c>
+      <c r="B494" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A495" t="s">
+        <v>266</v>
+      </c>
+      <c r="B495" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A496" t="s">
+        <v>195</v>
+      </c>
+      <c r="B496" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A497" t="s">
+        <v>922</v>
+      </c>
+      <c r="B497" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A498" t="s">
+        <v>46</v>
+      </c>
+      <c r="B498" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A499" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B499" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A500" t="s">
+        <v>326</v>
+      </c>
+      <c r="B500" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A501" t="s">
+        <v>327</v>
+      </c>
+      <c r="B501" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A502" t="s">
+        <v>870</v>
+      </c>
+      <c r="B502" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A503" t="s">
+        <v>908</v>
+      </c>
+      <c r="B503" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A504" t="s">
+        <v>890</v>
+      </c>
+      <c r="B504" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A505" t="s">
+        <v>35</v>
+      </c>
+      <c r="B505" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A506" t="s">
+        <v>38</v>
+      </c>
+      <c r="B506" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A507" t="s">
+        <v>311</v>
+      </c>
+      <c r="B507" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A508" t="s">
+        <v>259</v>
+      </c>
+      <c r="B508" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A509" t="s">
+        <v>304</v>
+      </c>
+      <c r="B509" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A510" t="s">
+        <v>230</v>
+      </c>
+      <c r="B510" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A511" t="s">
+        <v>17</v>
+      </c>
+      <c r="B511" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A512" t="s">
+        <v>674</v>
+      </c>
+      <c r="B512" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A513" t="s">
+        <v>804</v>
+      </c>
+      <c r="B513" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A514" t="s">
+        <v>144</v>
+      </c>
+      <c r="B514" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A515" t="s">
+        <v>981</v>
+      </c>
+      <c r="B515" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A516" t="s">
+        <v>56</v>
+      </c>
+      <c r="B516" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A517" t="s">
+        <v>267</v>
+      </c>
+      <c r="B517" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A518" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B518" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A519" t="s">
+        <v>58</v>
+      </c>
+      <c r="B519" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A520" t="s">
+        <v>187</v>
+      </c>
+      <c r="B520" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A521" t="s">
+        <v>161</v>
+      </c>
+      <c r="B521" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A522" t="s">
+        <v>45</v>
+      </c>
+      <c r="B522" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A523" t="s">
+        <v>42</v>
+      </c>
+      <c r="B523" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A524" t="s">
+        <v>167</v>
+      </c>
+      <c r="B524" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A525" t="s">
+        <v>12</v>
+      </c>
+      <c r="B525" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A526" t="s">
+        <v>252</v>
+      </c>
+      <c r="B526" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A527" t="s">
+        <v>29</v>
+      </c>
+      <c r="B527" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A528" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B528" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A529" t="s">
+        <v>30</v>
+      </c>
+      <c r="B529" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A530" t="s">
+        <v>257</v>
+      </c>
+      <c r="B530" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A531" t="s">
+        <v>814</v>
+      </c>
+      <c r="B531" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A532" t="s">
+        <v>269</v>
+      </c>
+      <c r="B532" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A533" t="s">
+        <v>680</v>
+      </c>
+      <c r="B533" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A534" t="s">
+        <v>681</v>
+      </c>
+      <c r="B534" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A535" t="s">
+        <v>141</v>
+      </c>
+      <c r="B535" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A536" t="s">
+        <v>7</v>
+      </c>
+      <c r="B536" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A537" t="s">
+        <v>107</v>
+      </c>
+      <c r="B537" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A538" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B538" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A539" t="s">
+        <v>886</v>
+      </c>
+      <c r="B539" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A540" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B540" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A541" t="s">
+        <v>294</v>
+      </c>
+      <c r="B541" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A542" t="s">
+        <v>8</v>
+      </c>
+      <c r="B542" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A543" t="s">
+        <v>337</v>
+      </c>
+      <c r="B543" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A544" t="s">
+        <v>334</v>
+      </c>
+      <c r="B544" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A545" t="s">
+        <v>261</v>
+      </c>
+      <c r="B545" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A546" t="s">
+        <v>321</v>
+      </c>
+      <c r="B546" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A547" t="s">
+        <v>880</v>
+      </c>
+      <c r="B547" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A548" t="s">
+        <v>270</v>
+      </c>
+      <c r="B548" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A549" t="s">
+        <v>273</v>
+      </c>
+      <c r="B549" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A550" t="s">
+        <v>276</v>
+      </c>
+      <c r="B550" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A551" t="s">
+        <v>272</v>
+      </c>
+      <c r="B551" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A552" t="s">
+        <v>275</v>
+      </c>
+      <c r="B552" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A553" t="s">
+        <v>271</v>
+      </c>
+      <c r="B553" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A554" t="s">
+        <v>274</v>
+      </c>
+      <c r="B554" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A555" t="s">
+        <v>94</v>
+      </c>
+      <c r="B555" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A556" t="s">
+        <v>202</v>
+      </c>
+      <c r="B556" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A557" t="s">
+        <v>205</v>
+      </c>
+      <c r="B557" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A558" t="s">
+        <v>174</v>
+      </c>
+      <c r="B558" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A559" t="s">
+        <v>712</v>
+      </c>
+      <c r="B559" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A560" t="s">
+        <v>254</v>
+      </c>
+      <c r="B560" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A561" t="s">
+        <v>713</v>
+      </c>
+      <c r="B561" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A562" t="s">
+        <v>191</v>
+      </c>
+      <c r="B562" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A563" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B563" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A564" t="s">
+        <v>313</v>
+      </c>
+      <c r="B564" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A565" t="s">
+        <v>314</v>
+      </c>
+      <c r="B565" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A566" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B566" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A567" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B567" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A568" t="s">
+        <v>83</v>
+      </c>
+      <c r="B568" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A569" t="s">
+        <v>670</v>
+      </c>
+      <c r="B569" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A570" t="s">
+        <v>943</v>
+      </c>
+      <c r="B570" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A571" t="s">
+        <v>661</v>
+      </c>
+      <c r="B571" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A572" t="s">
+        <v>995</v>
+      </c>
+      <c r="B572" t="s">
+        <v>996</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463A888C-41F9-42A2-9F5C-02CB4B74A449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05844A1E-B978-4D42-9BF8-11A6CB0AD385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="1138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="1148">
   <si>
     <t>trigger</t>
   </si>
@@ -99,15 +99,9 @@
     <t>hemangiomaex</t>
   </si>
   <si>
-    <t>There is a lesion measuring 1.5x1.2 cm which shows peripheral nodular enhancement in arterial phase with progressive centripetal filling and enhancement corresponding to adjacent blood pool in subsequent phase.</t>
-  </si>
-  <si>
     <t>emh</t>
   </si>
   <si>
-    <t>Soft tissue density is noted in right middle ear cavity involving epitympanum, mesotympanum and hypotympanum which is extending to mastoid cavity through aditus ad antrum. Tegmen tympani, ear ossicles, sinus plate, scutum and facial canal appear normal.</t>
-  </si>
-  <si>
     <t>ln</t>
   </si>
   <si>
@@ -1191,9 +1185,6 @@
     <t>cerebral atrophy</t>
   </si>
   <si>
-    <t>There is volume loss of bilateral cerebral hemispheres with prominent sulci, extraaxial CSF spaces &amp; proportionate dilatation of ventricles.</t>
-  </si>
-  <si>
     <t>calcific focus</t>
   </si>
   <si>
@@ -1542,12 +1533,6 @@
     <t>lymph nodes</t>
   </si>
   <si>
-    <t>Loss of cervical lordosis is seen.</t>
-  </si>
-  <si>
-    <t>Loss of lumbar lordosis is seen.</t>
-  </si>
-  <si>
     <t>lower pole calyx</t>
   </si>
   <si>
@@ -1725,9 +1710,6 @@
     <t>peripancreatic</t>
   </si>
   <si>
-    <t>There is fluid signal intensity noted in the pituitary fossa suggestive of partial empty sella.</t>
-  </si>
-  <si>
     <t>partially empty sella</t>
   </si>
   <si>
@@ -1749,9 +1731,6 @@
     <t>post-operative changes</t>
   </si>
   <si>
-    <t>Soft tissue density with convex outward margin is noted in right maxillary sinus – polyp/ retention cyst.</t>
-  </si>
-  <si>
     <t>popliteal artery</t>
   </si>
   <si>
@@ -1803,15 +1782,9 @@
     <t>Rest of the brain is normal in morphology and signal intensity</t>
   </si>
   <si>
-    <t>Rest of the intervertebral discs are normal in height and signal intensity.</t>
-  </si>
-  <si>
     <t>reformation</t>
   </si>
   <si>
-    <t>Rest of the lung fields shows normal attenuation and normal in aeration.</t>
-  </si>
-  <si>
     <t>restriction of diffusion on DWI</t>
   </si>
   <si>
@@ -1869,9 +1842,6 @@
     <t>significant</t>
   </si>
   <si>
-    <t>Mucosal thickening noted in bilateral maxillary sinus - suggestive of sinusitis.</t>
-  </si>
-  <si>
     <t>superior mesenteric artery</t>
   </si>
   <si>
@@ -1914,12 +1884,6 @@
     <t>superior vena cava</t>
   </si>
   <si>
-    <t>small vessel disease</t>
-  </si>
-  <si>
-    <t>Discrete and confluent T2/FLAIR high signal intensities are noted in bilateral periventricular white matter and centrum semi-ovale.</t>
-  </si>
-  <si>
     <t>symmetrical</t>
   </si>
   <si>
@@ -1962,24 +1926,6 @@
     <t>urinary bladder</t>
   </si>
   <si>
-    <t>Urinary bladder is empty.</t>
-  </si>
-  <si>
-    <t>Urinary bladder is empty with Foley's in situ.</t>
-  </si>
-  <si>
-    <t>Urinary bladder is minimally filled.</t>
-  </si>
-  <si>
-    <t>Urinary bladder is minimally filled with Foley's in situ.</t>
-  </si>
-  <si>
-    <t>Urinary bladder is partially filled.</t>
-  </si>
-  <si>
-    <t>Urinary bladder is partially filled with Foley's in situ.</t>
-  </si>
-  <si>
     <t>upstream dilatation</t>
   </si>
   <si>
@@ -2478,15 +2424,9 @@
     <t>nsr</t>
   </si>
   <si>
-    <t>Nasal septum is deviated to right.</t>
-  </si>
-  <si>
     <t>nsl</t>
   </si>
   <si>
-    <t>Nasal septum is deviated to left.</t>
-  </si>
-  <si>
     <t>dns</t>
   </si>
   <si>
@@ -2895,21 +2835,9 @@
     <t>nos</t>
   </si>
   <si>
-    <t>No septations, solid component or calcification noted within.</t>
-  </si>
-  <si>
     <t>recc</t>
   </si>
   <si>
-    <t>renal cortical cyst</t>
-  </si>
-  <si>
-    <t>Atherosclerotic changes are noted in the aorta and its branches.</t>
-  </si>
-  <si>
-    <t>Degenerative changes are seen in visualised spine.</t>
-  </si>
-  <si>
     <t>ow</t>
   </si>
   <si>
@@ -2985,9 +2913,6 @@
     <t>locll</t>
   </si>
   <si>
-    <t>Loss of cervical and lumbar lordosis is seen.</t>
-  </si>
-  <si>
     <t>duo</t>
   </si>
   <si>
@@ -3207,18 +3132,9 @@
     <t>vrs</t>
   </si>
   <si>
-    <t>Multiple tiny T2 high signal intensity foci noted in  bilateral frontoparietal lobe which are suppressed on FLAIR , likely Virchow Robin spaces.</t>
-  </si>
-  <si>
     <t>tmas</t>
   </si>
   <si>
-    <t>T2 high signal intensity noted in bilateral maxillary sinus - suggestive of sinusitis.</t>
-  </si>
-  <si>
-    <t>T2 high signal intensity with convex free margin is noted in right maxillary sinus - polyp/ retention cyst.</t>
-  </si>
-  <si>
     <t>tpor</t>
   </si>
   <si>
@@ -3439,6 +3355,120 @@
   </si>
   <si>
     <t>amed</t>
+  </si>
+  <si>
+    <t>mfp</t>
+  </si>
+  <si>
+    <t>fp</t>
+  </si>
+  <si>
+    <t>fat plane</t>
+  </si>
+  <si>
+    <t>maintained fat plane</t>
+  </si>
+  <si>
+    <t>lofp</t>
+  </si>
+  <si>
+    <t>loss of fat plane</t>
+  </si>
+  <si>
+    <t>Multiple tiny T2 high signal intensity foci noted in  bilateral frontoparietal lobe which are suppressed on FLAIR , likely Virchow Robin spaces</t>
+  </si>
+  <si>
+    <t>Urinary bladder is partially filled with Foley's in situ</t>
+  </si>
+  <si>
+    <t>Urinary bladder is empty</t>
+  </si>
+  <si>
+    <t>Urinary bladder is empty with Foley's in situ</t>
+  </si>
+  <si>
+    <t>Urinary bladder is minimally filled</t>
+  </si>
+  <si>
+    <t>Urinary bladder is minimally filled with Foley's in situ</t>
+  </si>
+  <si>
+    <t>Urinary bladder is partially filled</t>
+  </si>
+  <si>
+    <t>T2 high signal intensity with convex free margin is noted in right maxillary sinus - polyp/ retention cyst</t>
+  </si>
+  <si>
+    <t>T2 high signal intensity noted in bilateral maxillary sinus - suggestive of sinusitis</t>
+  </si>
+  <si>
+    <t>Discrete and confluent T2/FLAIR high signal intensities are noted in bilateral periventricular white matter and centrum semi-ovale</t>
+  </si>
+  <si>
+    <t>Mucosal thickening noted in bilateral maxillary sinus - suggestive of sinusitis</t>
+  </si>
+  <si>
+    <t>Rest of the intervertebral discs are normal in height and signal intensity</t>
+  </si>
+  <si>
+    <t>Rest of the lung fields shows normal attenuation and normal in aeration</t>
+  </si>
+  <si>
+    <t>Soft tissue density with convex outward margin is noted in right maxillary sinus – polyp/ retention cyst</t>
+  </si>
+  <si>
+    <t>There is fluid signal intensity noted in the pituitary fossa suggestive of partial empty sella</t>
+  </si>
+  <si>
+    <t>No septations, solid component or calcification noted within</t>
+  </si>
+  <si>
+    <t>Nasal septum is deviated to left</t>
+  </si>
+  <si>
+    <t>Nasal septum is deviated to right</t>
+  </si>
+  <si>
+    <t>Loss of cervical lordosis is seen</t>
+  </si>
+  <si>
+    <t>Loss of cervical and lumbar lordosis is seen</t>
+  </si>
+  <si>
+    <t>Loss of lumbar lordosis is seen</t>
+  </si>
+  <si>
+    <t>There is a lesion measuring 1.5x1.2 cm which shows peripheral nodular enhancement in arterial phase with progressive centripetal filling and enhancement corresponding to adjacent blood pool in subsequent phase</t>
+  </si>
+  <si>
+    <t>Soft tissue density is noted in right middle ear cavity involving epitympanum, mesotympanum and hypotympanum which is extending to mastoid cavity through aditus ad antrum. Tegmen tympani, ear ossicles, sinus plate, scutum and facial canal appear normal</t>
+  </si>
+  <si>
+    <t>Degenerative changes are seen in visualised spine</t>
+  </si>
+  <si>
+    <t>There is volume loss of bilateral cerebral hemispheres with prominent sulci, extraaxial CSF spaces &amp; proportionate dilatation of ventricles</t>
+  </si>
+  <si>
+    <t>Atherosclerotic changes are noted in the aorta and its branches</t>
+  </si>
+  <si>
+    <t>hepa</t>
+  </si>
+  <si>
+    <t>hepatic artery</t>
+  </si>
+  <si>
+    <t>spla</t>
+  </si>
+  <si>
+    <t>splenic artery</t>
+  </si>
+  <si>
+    <t>renal cortical cyst (Bosniak cat-I)</t>
+  </si>
+  <si>
+    <t>small vessel disease (Fazekas grade-I)</t>
   </si>
 </sst>
 </file>
@@ -3494,10 +3524,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B572" totalsRowShown="0">
-  <autoFilter ref="A1:B572" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B572">
-    <sortCondition ref="A1:A572"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B577" totalsRowShown="0">
+  <autoFilter ref="A1:B577" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B577">
+    <sortCondition ref="A1:A577"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -3770,7 +3800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B572"/>
+  <dimension ref="A1:B577"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -3787,626 +3817,626 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>969</v>
+        <v>945</v>
       </c>
       <c r="B3" t="s">
-        <v>970</v>
+        <v>946</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>967</v>
+        <v>943</v>
       </c>
       <c r="B4" t="s">
-        <v>968</v>
+        <v>944</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>971</v>
+        <v>947</v>
       </c>
       <c r="B5" t="s">
-        <v>972</v>
+        <v>948</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>979</v>
+        <v>955</v>
       </c>
       <c r="B6" t="s">
-        <v>980</v>
+        <v>956</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>926</v>
+        <v>906</v>
       </c>
       <c r="B7" t="s">
-        <v>927</v>
+        <v>907</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B8" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>945</v>
+        <v>925</v>
       </c>
       <c r="B9" t="s">
-        <v>946</v>
+        <v>926</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>947</v>
+        <v>927</v>
       </c>
       <c r="B10" t="s">
-        <v>948</v>
+        <v>928</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B11" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B12" t="s">
-        <v>934</v>
+        <v>914</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>902</v>
+        <v>882</v>
       </c>
       <c r="B13" t="s">
-        <v>903</v>
+        <v>883</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B14" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>928</v>
+        <v>908</v>
       </c>
       <c r="B15" t="s">
-        <v>929</v>
+        <v>909</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>824</v>
+        <v>804</v>
       </c>
       <c r="B16" t="s">
-        <v>825</v>
+        <v>805</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>1011</v>
+        <v>986</v>
       </c>
       <c r="B17" t="s">
-        <v>1012</v>
+        <v>987</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>1087</v>
+        <v>1059</v>
       </c>
       <c r="B18" t="s">
-        <v>1088</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>898</v>
+        <v>878</v>
       </c>
       <c r="B19" t="s">
-        <v>899</v>
+        <v>879</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>787</v>
+        <v>769</v>
       </c>
       <c r="B20" t="s">
-        <v>788</v>
+        <v>770</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>1083</v>
+        <v>1055</v>
       </c>
       <c r="B21" t="s">
-        <v>1084</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B22" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B23" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B24" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B25" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>1053</v>
+        <v>1028</v>
       </c>
       <c r="B26" t="s">
-        <v>1054</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>1046</v>
+        <v>1021</v>
       </c>
       <c r="B27" t="s">
-        <v>1047</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>1135</v>
+        <v>1107</v>
       </c>
       <c r="B28" t="s">
-        <v>714</v>
+        <v>696</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B29" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>1137</v>
+        <v>1109</v>
       </c>
       <c r="B30" t="s">
-        <v>1039</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B31" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B32" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B33" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>1048</v>
+        <v>1023</v>
       </c>
       <c r="B34" t="s">
-        <v>1049</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B35" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B36" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B37" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>932</v>
+        <v>912</v>
       </c>
       <c r="B38" t="s">
-        <v>933</v>
+        <v>913</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B39" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>1131</v>
+        <v>1103</v>
       </c>
       <c r="B40" t="s">
-        <v>1132</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>679</v>
+        <v>661</v>
       </c>
       <c r="B41" t="s">
-        <v>715</v>
+        <v>697</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>1042</v>
+        <v>1017</v>
       </c>
       <c r="B42" t="s">
-        <v>1043</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B43" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B44" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B45" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B46" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B47" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B48" t="s">
-        <v>959</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>666</v>
+        <v>648</v>
       </c>
       <c r="B49" t="s">
-        <v>716</v>
+        <v>698</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B50" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>882</v>
+        <v>862</v>
       </c>
       <c r="B51" t="s">
-        <v>883</v>
+        <v>863</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>1013</v>
+        <v>988</v>
       </c>
       <c r="B52" t="s">
-        <v>1014</v>
+        <v>989</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>793</v>
+        <v>775</v>
       </c>
       <c r="B53" t="s">
-        <v>794</v>
+        <v>776</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>795</v>
+        <v>777</v>
       </c>
       <c r="B54" t="s">
-        <v>796</v>
+        <v>778</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B55" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B56" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B57" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B58" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>808</v>
+        <v>790</v>
       </c>
       <c r="B59" t="s">
-        <v>809</v>
+        <v>791</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B60" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>781</v>
+        <v>763</v>
       </c>
       <c r="B61" t="s">
-        <v>782</v>
+        <v>764</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B63" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B64" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>906</v>
+        <v>886</v>
       </c>
       <c r="B65" t="s">
-        <v>907</v>
+        <v>887</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>678</v>
+        <v>660</v>
       </c>
       <c r="B66" t="s">
-        <v>717</v>
+        <v>699</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B67" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B68" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>1040</v>
+        <v>1015</v>
       </c>
       <c r="B69" t="s">
-        <v>1041</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>687</v>
+        <v>669</v>
       </c>
       <c r="B70" t="s">
-        <v>718</v>
+        <v>700</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>688</v>
+        <v>670</v>
       </c>
       <c r="B71" t="s">
-        <v>719</v>
+        <v>701</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>689</v>
+        <v>671</v>
       </c>
       <c r="B72" t="s">
-        <v>720</v>
+        <v>702</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>690</v>
+        <v>672</v>
       </c>
       <c r="B73" t="s">
-        <v>721</v>
+        <v>703</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>691</v>
+        <v>673</v>
       </c>
       <c r="B74" t="s">
-        <v>722</v>
+        <v>704</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>692</v>
+        <v>674</v>
       </c>
       <c r="B75" t="s">
-        <v>723</v>
+        <v>705</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>693</v>
+        <v>675</v>
       </c>
       <c r="B76" t="s">
-        <v>724</v>
+        <v>706</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>896</v>
+        <v>876</v>
       </c>
       <c r="B77" t="s">
-        <v>897</v>
+        <v>877</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B78" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B79" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
@@ -4427,1042 +4457,1042 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B82" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B83" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B84" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B85" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>920</v>
+        <v>900</v>
       </c>
       <c r="B86" t="s">
-        <v>921</v>
+        <v>901</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B87" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B88" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B89" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B90" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B91" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B92" t="s">
-        <v>388</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>668</v>
+        <v>650</v>
       </c>
       <c r="B93" t="s">
-        <v>725</v>
+        <v>707</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B94" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B95" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B96" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B97" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B98" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>667</v>
+        <v>649</v>
       </c>
       <c r="B99" t="s">
-        <v>726</v>
+        <v>708</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B100" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B101" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B102" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>900</v>
+        <v>880</v>
       </c>
       <c r="B103" t="s">
-        <v>901</v>
+        <v>881</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>828</v>
+        <v>808</v>
       </c>
       <c r="B104" t="s">
-        <v>829</v>
+        <v>809</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B105" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B106" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B107" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B108" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>993</v>
+        <v>968</v>
       </c>
       <c r="B109" t="s">
-        <v>994</v>
+        <v>969</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B110" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>991</v>
+        <v>966</v>
       </c>
       <c r="B111" t="s">
-        <v>992</v>
+        <v>967</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B112" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B113" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B114" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B115" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B116" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B117" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B118" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>1075</v>
+        <v>1047</v>
       </c>
       <c r="B119" t="s">
-        <v>1076</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>951</v>
+        <v>931</v>
       </c>
       <c r="B120" t="s">
-        <v>952</v>
+        <v>932</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>949</v>
+        <v>929</v>
       </c>
       <c r="B121" t="s">
-        <v>950</v>
+        <v>930</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B122" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>858</v>
+        <v>838</v>
       </c>
       <c r="B123" t="s">
-        <v>859</v>
+        <v>839</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>860</v>
+        <v>840</v>
       </c>
       <c r="B124" t="s">
-        <v>861</v>
+        <v>841</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>1113</v>
+        <v>1085</v>
       </c>
       <c r="B125" t="s">
-        <v>1114</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>684</v>
+        <v>666</v>
       </c>
       <c r="B126" t="s">
-        <v>727</v>
+        <v>709</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>665</v>
+        <v>647</v>
       </c>
       <c r="B127" t="s">
-        <v>728</v>
+        <v>710</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>965</v>
+        <v>941</v>
       </c>
       <c r="B128" t="s">
-        <v>966</v>
+        <v>942</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>702</v>
+        <v>684</v>
       </c>
       <c r="B129" t="s">
-        <v>729</v>
+        <v>711</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>703</v>
+        <v>685</v>
       </c>
       <c r="B130" t="s">
-        <v>730</v>
+        <v>712</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>704</v>
+        <v>686</v>
       </c>
       <c r="B131" t="s">
-        <v>731</v>
+        <v>713</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>694</v>
+        <v>676</v>
       </c>
       <c r="B132" t="s">
-        <v>732</v>
+        <v>714</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>695</v>
+        <v>677</v>
       </c>
       <c r="B133" t="s">
-        <v>733</v>
+        <v>715</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>696</v>
+        <v>678</v>
       </c>
       <c r="B134" t="s">
-        <v>734</v>
+        <v>716</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>697</v>
+        <v>679</v>
       </c>
       <c r="B135" t="s">
-        <v>735</v>
+        <v>717</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>698</v>
+        <v>680</v>
       </c>
       <c r="B136" t="s">
-        <v>736</v>
+        <v>718</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>699</v>
+        <v>681</v>
       </c>
       <c r="B137" t="s">
-        <v>737</v>
+        <v>719</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>700</v>
+        <v>682</v>
       </c>
       <c r="B138" t="s">
-        <v>738</v>
+        <v>720</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>701</v>
+        <v>683</v>
       </c>
       <c r="B139" t="s">
-        <v>739</v>
+        <v>721</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B140" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B141" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B142" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B143" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B144" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B145" t="s">
-        <v>960</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B146" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>669</v>
+        <v>651</v>
       </c>
       <c r="B147" t="s">
-        <v>740</v>
+        <v>722</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B148" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B149" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>1125</v>
+        <v>1097</v>
       </c>
       <c r="B150" t="s">
-        <v>1126</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>820</v>
+        <v>800</v>
       </c>
       <c r="B151" t="s">
-        <v>821</v>
+        <v>801</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B152" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>1115</v>
+        <v>1087</v>
       </c>
       <c r="B153" t="s">
-        <v>1116</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>1121</v>
+        <v>1093</v>
       </c>
       <c r="B154" t="s">
-        <v>1122</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B155" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>987</v>
+        <v>962</v>
       </c>
       <c r="B156" t="s">
-        <v>988</v>
+        <v>963</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>834</v>
+        <v>814</v>
       </c>
       <c r="B157" t="s">
-        <v>835</v>
+        <v>815</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>953</v>
+        <v>933</v>
       </c>
       <c r="B158" t="s">
-        <v>954</v>
+        <v>934</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>854</v>
+        <v>834</v>
       </c>
       <c r="B159" t="s">
-        <v>855</v>
+        <v>835</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>812</v>
+        <v>794</v>
       </c>
       <c r="B160" t="s">
-        <v>813</v>
+        <v>795</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>773</v>
+        <v>755</v>
       </c>
       <c r="B161" t="s">
-        <v>774</v>
+        <v>756</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B162" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>1071</v>
+        <v>1043</v>
       </c>
       <c r="B163" t="s">
-        <v>1072</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B164" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B165" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B166" t="s">
-        <v>26</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>1105</v>
+        <v>1077</v>
       </c>
       <c r="B167" t="s">
-        <v>1106</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>840</v>
+        <v>820</v>
       </c>
       <c r="B168" t="s">
-        <v>841</v>
+        <v>821</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B169" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B170" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>888</v>
+        <v>868</v>
       </c>
       <c r="B171" t="s">
-        <v>889</v>
+        <v>869</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B172" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>912</v>
+        <v>892</v>
       </c>
       <c r="B173" t="s">
-        <v>913</v>
+        <v>893</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B174" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B175" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>783</v>
+        <v>765</v>
       </c>
       <c r="B176" t="s">
-        <v>1036</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B177" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B178" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>1037</v>
+        <v>1012</v>
       </c>
       <c r="B179" t="s">
-        <v>784</v>
+        <v>766</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B181" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B182" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B183" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B184" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B185" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>686</v>
+        <v>668</v>
       </c>
       <c r="B186" t="s">
-        <v>741</v>
+        <v>723</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B187" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B188" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B189" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B190" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B191" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B192" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>1003</v>
+        <v>1111</v>
       </c>
       <c r="B193" t="s">
-        <v>1004</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>1005</v>
+        <v>978</v>
       </c>
       <c r="B194" t="s">
-        <v>1006</v>
+        <v>979</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>255</v>
+        <v>980</v>
       </c>
       <c r="B195" t="s">
-        <v>441</v>
+        <v>981</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>36</v>
+        <v>253</v>
       </c>
       <c r="B196" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>806</v>
+        <v>34</v>
       </c>
       <c r="B197" t="s">
-        <v>807</v>
+        <v>439</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>182</v>
+        <v>788</v>
       </c>
       <c r="B198" t="s">
-        <v>443</v>
+        <v>789</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>277</v>
+        <v>180</v>
       </c>
       <c r="B199" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>878</v>
+        <v>275</v>
       </c>
       <c r="B200" t="s">
-        <v>879</v>
+        <v>441</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>118</v>
+        <v>858</v>
       </c>
       <c r="B201" t="s">
-        <v>445</v>
+        <v>859</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>210</v>
+        <v>116</v>
       </c>
       <c r="B202" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>1085</v>
+        <v>208</v>
       </c>
       <c r="B203" t="s">
-        <v>1086</v>
+        <v>443</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>120</v>
+        <v>1057</v>
       </c>
       <c r="B204" t="s">
-        <v>447</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>660</v>
+        <v>118</v>
       </c>
       <c r="B205" t="s">
-        <v>742</v>
+        <v>444</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>836</v>
+        <v>642</v>
       </c>
       <c r="B206" t="s">
-        <v>837</v>
+        <v>724</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>300</v>
+        <v>816</v>
       </c>
       <c r="B207" t="s">
-        <v>448</v>
+        <v>817</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>662</v>
+        <v>298</v>
       </c>
       <c r="B208" t="s">
-        <v>743</v>
+        <v>445</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>663</v>
+        <v>644</v>
       </c>
       <c r="B209" t="s">
-        <v>744</v>
+        <v>725</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>1065</v>
+        <v>645</v>
       </c>
       <c r="B210" t="s">
-        <v>1066</v>
+        <v>726</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>92</v>
+        <v>1037</v>
       </c>
       <c r="B211" t="s">
-        <v>449</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
@@ -5470,2127 +5500,2127 @@
         <v>90</v>
       </c>
       <c r="B212" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B213" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>1101</v>
+        <v>89</v>
       </c>
       <c r="B214" t="s">
-        <v>1102</v>
+        <v>448</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>23</v>
+        <v>1073</v>
       </c>
       <c r="B215" t="s">
-        <v>24</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B216" t="s">
-        <v>6</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>128</v>
+        <v>5</v>
       </c>
       <c r="B217" t="s">
-        <v>452</v>
+        <v>6</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>130</v>
+        <v>1142</v>
       </c>
       <c r="B218" t="s">
-        <v>453</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B219" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B220" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B221" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>279</v>
+        <v>132</v>
       </c>
       <c r="B222" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>1103</v>
+        <v>119</v>
       </c>
       <c r="B223" t="s">
-        <v>1104</v>
+        <v>453</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>9</v>
+        <v>277</v>
       </c>
       <c r="B224" t="s">
-        <v>10</v>
+        <v>454</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>131</v>
+        <v>1075</v>
       </c>
       <c r="B225" t="s">
-        <v>458</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="B226" t="s">
-        <v>459</v>
+        <v>10</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="B227" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>264</v>
+        <v>127</v>
       </c>
       <c r="B228" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>79</v>
+        <v>173</v>
       </c>
       <c r="B229" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>963</v>
+        <v>262</v>
       </c>
       <c r="B230" t="s">
-        <v>964</v>
+        <v>458</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="B231" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>169</v>
+        <v>939</v>
       </c>
       <c r="B232" t="s">
-        <v>464</v>
+        <v>940</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>856</v>
+        <v>168</v>
       </c>
       <c r="B233" t="s">
-        <v>857</v>
+        <v>460</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>810</v>
+        <v>167</v>
       </c>
       <c r="B234" t="s">
-        <v>811</v>
+        <v>461</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>306</v>
+        <v>836</v>
       </c>
       <c r="B235" t="s">
-        <v>465</v>
+        <v>837</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>777</v>
+        <v>792</v>
       </c>
       <c r="B236" t="s">
-        <v>778</v>
+        <v>793</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>918</v>
+        <v>304</v>
       </c>
       <c r="B237" t="s">
-        <v>919</v>
+        <v>462</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>671</v>
+        <v>759</v>
       </c>
       <c r="B238" t="s">
-        <v>745</v>
+        <v>760</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>88</v>
+        <v>898</v>
       </c>
       <c r="B239" t="s">
-        <v>466</v>
+        <v>899</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>89</v>
+        <v>653</v>
       </c>
       <c r="B240" t="s">
-        <v>467</v>
+        <v>727</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>155</v>
+        <v>86</v>
       </c>
       <c r="B241" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>158</v>
+        <v>87</v>
       </c>
       <c r="B242" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="B243" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>253</v>
+        <v>156</v>
       </c>
       <c r="B244" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>287</v>
+        <v>158</v>
       </c>
       <c r="B245" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>328</v>
+        <v>251</v>
       </c>
       <c r="B246" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>329</v>
+        <v>285</v>
       </c>
       <c r="B247" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>231</v>
+        <v>326</v>
       </c>
       <c r="B248" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>57</v>
+        <v>327</v>
       </c>
       <c r="B249" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>676</v>
+        <v>229</v>
       </c>
       <c r="B250" t="s">
-        <v>746</v>
+        <v>472</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>237</v>
+        <v>55</v>
       </c>
       <c r="B251" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>59</v>
+        <v>658</v>
       </c>
       <c r="B252" t="s">
-        <v>478</v>
+        <v>728</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B253" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>785</v>
+        <v>57</v>
       </c>
       <c r="B254" t="s">
-        <v>1035</v>
+        <v>475</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>1038</v>
+        <v>236</v>
       </c>
       <c r="B255" t="s">
-        <v>786</v>
+        <v>476</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>166</v>
+        <v>767</v>
       </c>
       <c r="B256" t="s">
-        <v>480</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>203</v>
+        <v>1013</v>
       </c>
       <c r="B257" t="s">
-        <v>481</v>
+        <v>768</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>206</v>
+        <v>164</v>
       </c>
       <c r="B258" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>315</v>
+        <v>201</v>
       </c>
       <c r="B259" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>894</v>
+        <v>204</v>
       </c>
       <c r="B260" t="s">
-        <v>895</v>
+        <v>479</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>1023</v>
+        <v>313</v>
       </c>
       <c r="B261" t="s">
-        <v>1024</v>
+        <v>480</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>260</v>
+        <v>874</v>
       </c>
       <c r="B262" t="s">
-        <v>484</v>
+        <v>875</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>1009</v>
+        <v>998</v>
       </c>
       <c r="B263" t="s">
-        <v>1010</v>
+        <v>999</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>162</v>
+        <v>258</v>
       </c>
       <c r="B264" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>711</v>
+        <v>984</v>
       </c>
       <c r="B265" t="s">
-        <v>747</v>
+        <v>985</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>779</v>
+        <v>160</v>
       </c>
       <c r="B266" t="s">
-        <v>780</v>
+        <v>482</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>916</v>
+        <v>693</v>
       </c>
       <c r="B267" t="s">
-        <v>917</v>
+        <v>729</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>914</v>
+        <v>761</v>
       </c>
       <c r="B268" t="s">
-        <v>915</v>
+        <v>762</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>186</v>
+        <v>896</v>
       </c>
       <c r="B269" t="s">
-        <v>486</v>
+        <v>897</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>246</v>
+        <v>894</v>
       </c>
       <c r="B270" t="s">
-        <v>487</v>
+        <v>895</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>245</v>
+        <v>184</v>
       </c>
       <c r="B271" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>705</v>
+        <v>244</v>
       </c>
       <c r="B272" t="s">
-        <v>748</v>
+        <v>484</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>706</v>
+        <v>243</v>
       </c>
       <c r="B273" t="s">
-        <v>749</v>
+        <v>485</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>707</v>
+        <v>687</v>
       </c>
       <c r="B274" t="s">
-        <v>750</v>
+        <v>730</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>708</v>
+        <v>688</v>
       </c>
       <c r="B275" t="s">
-        <v>751</v>
+        <v>731</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>709</v>
+        <v>689</v>
       </c>
       <c r="B276" t="s">
-        <v>752</v>
+        <v>732</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>282</v>
+        <v>690</v>
       </c>
       <c r="B277" t="s">
-        <v>489</v>
+        <v>733</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>283</v>
+        <v>691</v>
       </c>
       <c r="B278" t="s">
-        <v>490</v>
+        <v>734</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>51</v>
+        <v>280</v>
       </c>
       <c r="B279" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>55</v>
+        <v>281</v>
       </c>
       <c r="B280" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>138</v>
+        <v>49</v>
       </c>
       <c r="B281" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="B282" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>223</v>
+        <v>136</v>
       </c>
       <c r="B283" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="B284" t="s">
-        <v>16</v>
+        <v>490</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>1089</v>
+        <v>221</v>
       </c>
       <c r="B285" t="s">
-        <v>1090</v>
+        <v>492</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>941</v>
+        <v>15</v>
       </c>
       <c r="B286" t="s">
-        <v>942</v>
+        <v>16</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>110</v>
+        <v>1061</v>
       </c>
       <c r="B287" t="s">
-        <v>496</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>243</v>
+        <v>921</v>
       </c>
       <c r="B288" t="s">
-        <v>497</v>
+        <v>922</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>330</v>
+        <v>108</v>
       </c>
       <c r="B289" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>1129</v>
+        <v>241</v>
       </c>
       <c r="B290" t="s">
-        <v>1130</v>
+        <v>494</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>1081</v>
+        <v>328</v>
       </c>
       <c r="B291" t="s">
-        <v>1082</v>
+        <v>495</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>123</v>
+        <v>1101</v>
       </c>
       <c r="B292" t="s">
-        <v>499</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>769</v>
+        <v>1053</v>
       </c>
       <c r="B293" t="s">
-        <v>770</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>800</v>
+        <v>121</v>
       </c>
       <c r="B294" t="s">
-        <v>801</v>
+        <v>496</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>136</v>
+        <v>751</v>
       </c>
       <c r="B295" t="s">
-        <v>500</v>
+        <v>752</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>65</v>
+        <v>782</v>
       </c>
       <c r="B296" t="s">
-        <v>501</v>
+        <v>783</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>226</v>
+        <v>134</v>
       </c>
       <c r="B297" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="B298" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>28</v>
+        <v>224</v>
       </c>
       <c r="B299" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>209</v>
+        <v>25</v>
       </c>
       <c r="B300" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>985</v>
+        <v>26</v>
       </c>
       <c r="B301" t="s">
-        <v>986</v>
+        <v>501</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B302" t="s">
-        <v>506</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>204</v>
+        <v>961</v>
       </c>
       <c r="B303" t="s">
-        <v>507</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>207</v>
+        <v>1114</v>
       </c>
       <c r="B304" t="s">
-        <v>508</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>147</v>
+        <v>206</v>
       </c>
       <c r="B305" t="s">
-        <v>509</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>682</v>
+        <v>202</v>
       </c>
       <c r="B306" t="s">
-        <v>753</v>
+        <v>502</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="B307" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>1117</v>
+        <v>145</v>
       </c>
       <c r="B308" t="s">
-        <v>1118</v>
+        <v>504</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>265</v>
+        <v>664</v>
       </c>
       <c r="B309" t="s">
-        <v>511</v>
+        <v>735</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>1119</v>
+        <v>171</v>
       </c>
       <c r="B310" t="s">
-        <v>1120</v>
+        <v>505</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>82</v>
+        <v>1089</v>
       </c>
       <c r="B311" t="s">
-        <v>512</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>67</v>
+        <v>263</v>
       </c>
       <c r="B312" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>193</v>
+        <v>1091</v>
       </c>
       <c r="B313" t="s">
-        <v>514</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="B314" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>194</v>
+        <v>65</v>
       </c>
       <c r="B315" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>233</v>
+        <v>191</v>
       </c>
       <c r="B316" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>235</v>
+        <v>123</v>
       </c>
       <c r="B317" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>33</v>
+        <v>192</v>
       </c>
       <c r="B318" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>32</v>
+        <v>231</v>
       </c>
       <c r="B319" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>39</v>
+        <v>233</v>
       </c>
       <c r="B320" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="B321" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>308</v>
+        <v>30</v>
       </c>
       <c r="B322" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>224</v>
+        <v>37</v>
       </c>
       <c r="B323" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>317</v>
+        <v>71</v>
       </c>
       <c r="B324" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="B325" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>281</v>
+        <v>222</v>
       </c>
       <c r="B326" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>852</v>
+        <v>315</v>
       </c>
       <c r="B327" t="s">
-        <v>853</v>
+        <v>520</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>50</v>
+        <v>278</v>
       </c>
       <c r="B328" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>148</v>
+        <v>279</v>
       </c>
       <c r="B329" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>54</v>
+        <v>832</v>
       </c>
       <c r="B330" t="s">
-        <v>530</v>
+        <v>833</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>225</v>
+        <v>48</v>
       </c>
       <c r="B331" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>1123</v>
+        <v>146</v>
       </c>
       <c r="B332" t="s">
-        <v>1124</v>
+        <v>524</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>1079</v>
+        <v>52</v>
       </c>
       <c r="B333" t="s">
-        <v>1080</v>
+        <v>525</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>98</v>
+        <v>223</v>
       </c>
       <c r="B334" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>250</v>
+        <v>1095</v>
       </c>
       <c r="B335" t="s">
-        <v>533</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>251</v>
+        <v>1110</v>
       </c>
       <c r="B336" t="s">
-        <v>534</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>96</v>
+        <v>1051</v>
       </c>
       <c r="B337" t="s">
-        <v>535</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>1093</v>
+        <v>96</v>
       </c>
       <c r="B338" t="s">
-        <v>1094</v>
+        <v>527</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>214</v>
+        <v>248</v>
       </c>
       <c r="B339" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>937</v>
+        <v>249</v>
       </c>
       <c r="B340" t="s">
-        <v>938</v>
+        <v>529</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>935</v>
+        <v>94</v>
       </c>
       <c r="B341" t="s">
-        <v>936</v>
+        <v>530</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>939</v>
+        <v>1065</v>
       </c>
       <c r="B342" t="s">
-        <v>940</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>332</v>
+        <v>212</v>
       </c>
       <c r="B343" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>1095</v>
+        <v>917</v>
       </c>
       <c r="B344" t="s">
-        <v>1096</v>
+        <v>918</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>1021</v>
+        <v>915</v>
       </c>
       <c r="B345" t="s">
-        <v>1022</v>
+        <v>916</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>1017</v>
+        <v>919</v>
       </c>
       <c r="B346" t="s">
-        <v>1018</v>
+        <v>920</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>1019</v>
+        <v>330</v>
       </c>
       <c r="B347" t="s">
-        <v>1020</v>
+        <v>532</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>84</v>
+        <v>1067</v>
       </c>
       <c r="B348" t="s">
-        <v>538</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>791</v>
+        <v>996</v>
       </c>
       <c r="B349" t="s">
-        <v>792</v>
+        <v>997</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>199</v>
+        <v>992</v>
       </c>
       <c r="B350" t="s">
-        <v>539</v>
+        <v>993</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>673</v>
+        <v>994</v>
       </c>
       <c r="B351" t="s">
-        <v>754</v>
+        <v>995</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>842</v>
+        <v>82</v>
       </c>
       <c r="B352" t="s">
-        <v>843</v>
+        <v>533</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>1097</v>
+        <v>773</v>
       </c>
       <c r="B353" t="s">
-        <v>1098</v>
+        <v>774</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>3</v>
+        <v>197</v>
       </c>
       <c r="B354" t="s">
-        <v>4</v>
+        <v>534</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>983</v>
+        <v>655</v>
       </c>
       <c r="B355" t="s">
-        <v>4</v>
+        <v>736</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>984</v>
+        <v>822</v>
       </c>
       <c r="B356" t="s">
-        <v>4</v>
+        <v>823</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>683</v>
+        <v>1069</v>
       </c>
       <c r="B357" t="s">
-        <v>755</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>789</v>
+        <v>3</v>
       </c>
       <c r="B358" t="s">
-        <v>790</v>
+        <v>4</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>87</v>
+        <v>959</v>
       </c>
       <c r="B359" t="s">
-        <v>540</v>
+        <v>4</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>1091</v>
+        <v>960</v>
       </c>
       <c r="B360" t="s">
-        <v>1092</v>
+        <v>4</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>850</v>
+        <v>665</v>
       </c>
       <c r="B361" t="s">
-        <v>851</v>
+        <v>737</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>830</v>
+        <v>771</v>
       </c>
       <c r="B362" t="s">
-        <v>831</v>
+        <v>772</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="B363" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>848</v>
+        <v>1063</v>
       </c>
       <c r="B364" t="s">
-        <v>849</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>955</v>
+        <v>830</v>
       </c>
       <c r="B365" t="s">
-        <v>956</v>
+        <v>831</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>884</v>
+        <v>810</v>
       </c>
       <c r="B366" t="s">
-        <v>885</v>
+        <v>811</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>1073</v>
+        <v>187</v>
       </c>
       <c r="B367" t="s">
-        <v>1074</v>
+        <v>536</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>818</v>
+        <v>828</v>
       </c>
       <c r="B368" t="s">
-        <v>819</v>
+        <v>829</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>816</v>
+        <v>935</v>
       </c>
       <c r="B369" t="s">
-        <v>817</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>13</v>
+        <v>864</v>
       </c>
       <c r="B370" t="s">
-        <v>14</v>
+        <v>865</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>838</v>
+        <v>1045</v>
       </c>
       <c r="B371" t="s">
-        <v>839</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>188</v>
+        <v>799</v>
       </c>
       <c r="B372" t="s">
-        <v>542</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>832</v>
+        <v>798</v>
       </c>
       <c r="B373" t="s">
-        <v>833</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>322</v>
+        <v>13</v>
       </c>
       <c r="B374" t="s">
-        <v>543</v>
+        <v>14</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>675</v>
+        <v>818</v>
       </c>
       <c r="B375" t="s">
-        <v>756</v>
+        <v>819</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>876</v>
+        <v>186</v>
       </c>
       <c r="B376" t="s">
-        <v>877</v>
+        <v>537</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>677</v>
+        <v>812</v>
       </c>
       <c r="B377" t="s">
-        <v>757</v>
+        <v>813</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>672</v>
+        <v>320</v>
       </c>
       <c r="B378" t="s">
-        <v>758</v>
+        <v>538</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>258</v>
+        <v>657</v>
       </c>
       <c r="B379" t="s">
-        <v>544</v>
+        <v>738</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>262</v>
+        <v>856</v>
       </c>
       <c r="B380" t="s">
-        <v>545</v>
+        <v>857</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>263</v>
+        <v>659</v>
       </c>
       <c r="B381" t="s">
-        <v>546</v>
+        <v>739</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>190</v>
+        <v>654</v>
       </c>
       <c r="B382" t="s">
-        <v>547</v>
+        <v>740</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>192</v>
+        <v>256</v>
       </c>
       <c r="B383" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>961</v>
+        <v>260</v>
       </c>
       <c r="B384" t="s">
-        <v>962</v>
+        <v>540</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>1057</v>
+        <v>261</v>
       </c>
       <c r="B385" t="s">
-        <v>1058</v>
+        <v>541</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>211</v>
+        <v>188</v>
       </c>
       <c r="B386" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>872</v>
+        <v>190</v>
       </c>
       <c r="B387" t="s">
-        <v>873</v>
+        <v>543</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>145</v>
+        <v>937</v>
       </c>
       <c r="B388" t="s">
-        <v>550</v>
+        <v>938</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>142</v>
+        <v>1032</v>
       </c>
       <c r="B389" t="s">
-        <v>551</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>256</v>
+        <v>209</v>
       </c>
       <c r="B390" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>333</v>
+        <v>852</v>
       </c>
       <c r="B391" t="s">
-        <v>553</v>
+        <v>853</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>212</v>
+        <v>143</v>
       </c>
       <c r="B392" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>236</v>
+        <v>140</v>
       </c>
       <c r="B393" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>75</v>
+        <v>254</v>
       </c>
       <c r="B394" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="B395" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>310</v>
+        <v>210</v>
       </c>
       <c r="B396" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>864</v>
+        <v>234</v>
       </c>
       <c r="B397" t="s">
-        <v>865</v>
+        <v>550</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>866</v>
+        <v>73</v>
       </c>
       <c r="B398" t="s">
-        <v>867</v>
+        <v>551</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>222</v>
+        <v>342</v>
       </c>
       <c r="B399" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>930</v>
+        <v>308</v>
       </c>
       <c r="B400" t="s">
-        <v>931</v>
+        <v>553</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>989</v>
+        <v>844</v>
       </c>
       <c r="B401" t="s">
-        <v>990</v>
+        <v>845</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>229</v>
+        <v>846</v>
       </c>
       <c r="B402" t="s">
-        <v>560</v>
+        <v>847</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>336</v>
+        <v>220</v>
       </c>
       <c r="B403" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>997</v>
+        <v>910</v>
       </c>
       <c r="B404" t="s">
-        <v>998</v>
+        <v>911</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>797</v>
+        <v>964</v>
       </c>
       <c r="B405" t="s">
-        <v>798</v>
+        <v>965</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>296</v>
+        <v>227</v>
       </c>
       <c r="B406" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>977</v>
+        <v>334</v>
       </c>
       <c r="B407" t="s">
-        <v>978</v>
+        <v>556</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>341</v>
+        <v>972</v>
       </c>
       <c r="B408" t="s">
-        <v>563</v>
+        <v>973</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>799</v>
+        <v>779</v>
       </c>
       <c r="B409" t="s">
-        <v>798</v>
+        <v>780</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>342</v>
+        <v>294</v>
       </c>
       <c r="B410" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>343</v>
+        <v>953</v>
       </c>
       <c r="B411" t="s">
-        <v>565</v>
+        <v>954</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>664</v>
+        <v>339</v>
       </c>
       <c r="B412" t="s">
-        <v>759</v>
+        <v>558</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>41</v>
+        <v>781</v>
       </c>
       <c r="B413" t="s">
-        <v>567</v>
+        <v>780</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>40</v>
+        <v>340</v>
       </c>
       <c r="B414" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B415" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>109</v>
+        <v>646</v>
       </c>
       <c r="B416" t="s">
-        <v>569</v>
+        <v>741</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>1055</v>
+        <v>39</v>
       </c>
       <c r="B417" t="s">
-        <v>1056</v>
+        <v>561</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>924</v>
+        <v>38</v>
       </c>
       <c r="B418" t="s">
-        <v>925</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>119</v>
+        <v>343</v>
       </c>
       <c r="B419" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>1051</v>
+        <v>107</v>
       </c>
       <c r="B420" t="s">
-        <v>1052</v>
+        <v>563</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>100</v>
+        <v>1030</v>
       </c>
       <c r="B421" t="s">
-        <v>571</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>101</v>
+        <v>904</v>
       </c>
       <c r="B422" t="s">
-        <v>572</v>
+        <v>905</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>685</v>
+        <v>117</v>
       </c>
       <c r="B423" t="s">
-        <v>760</v>
+        <v>564</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>1136</v>
+        <v>1026</v>
       </c>
       <c r="B424" t="s">
-        <v>1050</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>844</v>
+        <v>98</v>
       </c>
       <c r="B425" t="s">
-        <v>845</v>
+        <v>565</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="B426" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>910</v>
+        <v>667</v>
       </c>
       <c r="B427" t="s">
-        <v>911</v>
+        <v>742</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>47</v>
+        <v>1108</v>
       </c>
       <c r="B428" t="s">
-        <v>574</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>292</v>
+        <v>824</v>
       </c>
       <c r="B429" t="s">
-        <v>575</v>
+        <v>825</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>301</v>
+        <v>113</v>
       </c>
       <c r="B430" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>49</v>
+        <v>890</v>
       </c>
       <c r="B431" t="s">
-        <v>577</v>
+        <v>891</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>868</v>
+        <v>45</v>
       </c>
       <c r="B432" t="s">
-        <v>869</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>53</v>
+        <v>290</v>
       </c>
       <c r="B433" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>892</v>
+        <v>299</v>
       </c>
       <c r="B434" t="s">
-        <v>893</v>
+        <v>569</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="B435" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>874</v>
+        <v>848</v>
       </c>
       <c r="B436" t="s">
-        <v>875</v>
+        <v>849</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>146</v>
+        <v>51</v>
       </c>
       <c r="B437" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>1109</v>
+        <v>872</v>
       </c>
       <c r="B438" t="s">
-        <v>1110</v>
+        <v>873</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>178</v>
+        <v>114</v>
       </c>
       <c r="B439" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>318</v>
+        <v>854</v>
       </c>
       <c r="B440" t="s">
-        <v>582</v>
+        <v>855</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>31</v>
+        <v>144</v>
       </c>
       <c r="B441" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>1133</v>
+        <v>1081</v>
       </c>
       <c r="B442" t="s">
-        <v>1134</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>1044</v>
+        <v>176</v>
       </c>
       <c r="B443" t="s">
-        <v>1045</v>
+        <v>574</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="B444" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>1007</v>
+        <v>29</v>
       </c>
       <c r="B445" t="s">
-        <v>1008</v>
+        <v>576</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>303</v>
+        <v>1105</v>
       </c>
       <c r="B446" t="s">
-        <v>585</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>1029</v>
+        <v>1019</v>
       </c>
       <c r="B447" t="s">
-        <v>1030</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>1033</v>
+        <v>293</v>
       </c>
       <c r="B448" t="s">
-        <v>1034</v>
+        <v>577</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>77</v>
+        <v>982</v>
       </c>
       <c r="B449" t="s">
-        <v>586</v>
+        <v>983</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>78</v>
+        <v>301</v>
       </c>
       <c r="B450" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>80</v>
+        <v>1004</v>
       </c>
       <c r="B451" t="s">
-        <v>588</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>331</v>
+        <v>1008</v>
       </c>
       <c r="B452" t="s">
-        <v>589</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>771</v>
+        <v>75</v>
       </c>
       <c r="B453" t="s">
-        <v>772</v>
+        <v>579</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>826</v>
+        <v>76</v>
       </c>
       <c r="B454" t="s">
-        <v>827</v>
+        <v>580</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="B455" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>1067</v>
+        <v>329</v>
       </c>
       <c r="B456" t="s">
-        <v>1068</v>
+        <v>582</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>217</v>
+        <v>753</v>
       </c>
       <c r="B457" t="s">
-        <v>591</v>
+        <v>754</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>957</v>
+        <v>806</v>
       </c>
       <c r="B458" t="s">
-        <v>958</v>
+        <v>807</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>218</v>
+        <v>135</v>
       </c>
       <c r="B459" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>319</v>
+        <v>1039</v>
       </c>
       <c r="B460" t="s">
-        <v>593</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>1111</v>
+        <v>215</v>
       </c>
       <c r="B461" t="s">
-        <v>1112</v>
+        <v>584</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>216</v>
+        <v>936</v>
       </c>
       <c r="B462" t="s">
-        <v>594</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>1025</v>
+        <v>216</v>
       </c>
       <c r="B463" t="s">
-        <v>1026</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>1027</v>
+        <v>317</v>
       </c>
       <c r="B464" t="s">
-        <v>1028</v>
+        <v>585</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>227</v>
+        <v>1083</v>
       </c>
       <c r="B465" t="s">
-        <v>595</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>973</v>
+        <v>214</v>
       </c>
       <c r="B466" t="s">
-        <v>974</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>1127</v>
+        <v>1000</v>
       </c>
       <c r="B467" t="s">
-        <v>1128</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>1077</v>
+        <v>1002</v>
       </c>
       <c r="B468" t="s">
-        <v>1078</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>95</v>
+        <v>225</v>
       </c>
       <c r="B469" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>122</v>
+        <v>949</v>
       </c>
       <c r="B470" t="s">
-        <v>597</v>
+        <v>950</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>802</v>
+        <v>1099</v>
       </c>
       <c r="B471" t="s">
-        <v>803</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>135</v>
+        <v>1049</v>
       </c>
       <c r="B472" t="s">
-        <v>598</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="B473" t="s">
-        <v>599</v>
+        <v>587</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="B474" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>846</v>
+        <v>784</v>
       </c>
       <c r="B475" t="s">
-        <v>847</v>
+        <v>785</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>975</v>
+        <v>133</v>
       </c>
       <c r="B476" t="s">
-        <v>976</v>
+        <v>589</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="B477" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
@@ -7598,759 +7628,799 @@
         <v>66</v>
       </c>
       <c r="B478" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>124</v>
+        <v>826</v>
       </c>
       <c r="B479" t="s">
-        <v>603</v>
+        <v>827</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>183</v>
+        <v>951</v>
       </c>
       <c r="B480" t="s">
-        <v>604</v>
+        <v>952</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>822</v>
+        <v>79</v>
       </c>
       <c r="B481" t="s">
-        <v>823</v>
+        <v>592</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>710</v>
+        <v>64</v>
       </c>
       <c r="B482" t="s">
-        <v>761</v>
+        <v>593</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>286</v>
+        <v>122</v>
       </c>
       <c r="B483" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>999</v>
+        <v>181</v>
       </c>
       <c r="B484" t="s">
-        <v>1000</v>
+        <v>595</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>862</v>
+        <v>802</v>
       </c>
       <c r="B485" t="s">
-        <v>863</v>
+        <v>803</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>285</v>
+        <v>692</v>
       </c>
       <c r="B486" t="s">
-        <v>606</v>
+        <v>743</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>904</v>
+        <v>284</v>
       </c>
       <c r="B487" t="s">
-        <v>905</v>
+        <v>596</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>775</v>
+        <v>974</v>
       </c>
       <c r="B488" t="s">
-        <v>776</v>
+        <v>975</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>1107</v>
+        <v>842</v>
       </c>
       <c r="B489" t="s">
-        <v>1108</v>
+        <v>843</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>69</v>
+        <v>283</v>
       </c>
       <c r="B490" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>70</v>
+        <v>884</v>
       </c>
       <c r="B491" t="s">
-        <v>608</v>
+        <v>885</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>97</v>
+        <v>757</v>
       </c>
       <c r="B492" t="s">
-        <v>609</v>
+        <v>758</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>291</v>
+        <v>1079</v>
       </c>
       <c r="B493" t="s">
-        <v>610</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>299</v>
+        <v>67</v>
       </c>
       <c r="B494" t="s">
-        <v>611</v>
+        <v>598</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>266</v>
+        <v>68</v>
       </c>
       <c r="B495" t="s">
-        <v>612</v>
+        <v>599</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>195</v>
+        <v>95</v>
       </c>
       <c r="B496" t="s">
-        <v>613</v>
+        <v>600</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>922</v>
+        <v>289</v>
       </c>
       <c r="B497" t="s">
-        <v>923</v>
+        <v>601</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>46</v>
+        <v>297</v>
       </c>
       <c r="B498" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>1099</v>
+        <v>264</v>
       </c>
       <c r="B499" t="s">
-        <v>1100</v>
+        <v>603</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>326</v>
+        <v>193</v>
       </c>
       <c r="B500" t="s">
-        <v>615</v>
+        <v>604</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>327</v>
+        <v>902</v>
       </c>
       <c r="B501" t="s">
-        <v>616</v>
+        <v>903</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>870</v>
+        <v>44</v>
       </c>
       <c r="B502" t="s">
-        <v>871</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>908</v>
+        <v>1071</v>
       </c>
       <c r="B503" t="s">
-        <v>909</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>890</v>
+        <v>324</v>
       </c>
       <c r="B504" t="s">
-        <v>891</v>
+        <v>605</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>35</v>
+        <v>325</v>
       </c>
       <c r="B505" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>38</v>
+        <v>850</v>
       </c>
       <c r="B506" t="s">
-        <v>618</v>
+        <v>851</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>311</v>
+        <v>888</v>
       </c>
       <c r="B507" t="s">
-        <v>619</v>
+        <v>889</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>259</v>
+        <v>870</v>
       </c>
       <c r="B508" t="s">
-        <v>620</v>
+        <v>871</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>304</v>
+        <v>33</v>
       </c>
       <c r="B509" t="s">
-        <v>621</v>
+        <v>607</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>230</v>
+        <v>36</v>
       </c>
       <c r="B510" t="s">
-        <v>622</v>
+        <v>608</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>17</v>
+        <v>1144</v>
       </c>
       <c r="B511" t="s">
-        <v>18</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>674</v>
+        <v>309</v>
       </c>
       <c r="B512" t="s">
-        <v>762</v>
+        <v>609</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>804</v>
+        <v>257</v>
       </c>
       <c r="B513" t="s">
-        <v>805</v>
+        <v>610</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>144</v>
+        <v>302</v>
       </c>
       <c r="B514" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>981</v>
+        <v>228</v>
       </c>
       <c r="B515" t="s">
-        <v>982</v>
+        <v>612</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="B516" t="s">
-        <v>624</v>
+        <v>18</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>267</v>
+        <v>656</v>
       </c>
       <c r="B517" t="s">
-        <v>625</v>
+        <v>744</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>1002</v>
+        <v>786</v>
       </c>
       <c r="B518" t="s">
-        <v>1001</v>
+        <v>787</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>58</v>
+        <v>142</v>
       </c>
       <c r="B519" t="s">
-        <v>626</v>
+        <v>613</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>187</v>
+        <v>957</v>
       </c>
       <c r="B520" t="s">
-        <v>627</v>
+        <v>958</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>161</v>
+        <v>54</v>
       </c>
       <c r="B521" t="s">
-        <v>628</v>
+        <v>614</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>45</v>
+        <v>265</v>
       </c>
       <c r="B522" t="s">
-        <v>629</v>
+        <v>615</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>42</v>
+        <v>977</v>
       </c>
       <c r="B523" t="s">
-        <v>630</v>
+        <v>976</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="B524" t="s">
-        <v>631</v>
+        <v>616</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>12</v>
+        <v>185</v>
       </c>
       <c r="B525" t="s">
-        <v>11</v>
+        <v>617</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>252</v>
+        <v>159</v>
       </c>
       <c r="B526" t="s">
-        <v>632</v>
+        <v>618</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B527" t="s">
-        <v>633</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>1069</v>
+        <v>40</v>
       </c>
       <c r="B528" t="s">
-        <v>1070</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>30</v>
+        <v>165</v>
       </c>
       <c r="B529" t="s">
-        <v>634</v>
+        <v>619</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>257</v>
+        <v>12</v>
       </c>
       <c r="B530" t="s">
-        <v>635</v>
+        <v>11</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>814</v>
+        <v>250</v>
       </c>
       <c r="B531" t="s">
-        <v>815</v>
+        <v>620</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>269</v>
+        <v>27</v>
       </c>
       <c r="B532" t="s">
-        <v>636</v>
+        <v>621</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>680</v>
+        <v>1041</v>
       </c>
       <c r="B533" t="s">
-        <v>763</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>681</v>
+        <v>28</v>
       </c>
       <c r="B534" t="s">
-        <v>764</v>
+        <v>622</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>141</v>
+        <v>255</v>
       </c>
       <c r="B535" t="s">
-        <v>637</v>
+        <v>623</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>7</v>
+        <v>796</v>
       </c>
       <c r="B536" t="s">
-        <v>2</v>
+        <v>797</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>107</v>
+        <v>267</v>
       </c>
       <c r="B537" t="s">
-        <v>638</v>
+        <v>624</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>1061</v>
+        <v>662</v>
       </c>
       <c r="B538" t="s">
-        <v>1062</v>
+        <v>745</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>886</v>
+        <v>663</v>
       </c>
       <c r="B539" t="s">
-        <v>887</v>
+        <v>746</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>1064</v>
+        <v>139</v>
       </c>
       <c r="B540" t="s">
-        <v>1063</v>
+        <v>625</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>294</v>
+        <v>7</v>
       </c>
       <c r="B541" t="s">
-        <v>639</v>
+        <v>2</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B542" t="s">
-        <v>11</v>
+        <v>626</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>337</v>
+        <v>1035</v>
       </c>
       <c r="B543" t="s">
-        <v>640</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>334</v>
+        <v>866</v>
       </c>
       <c r="B544" t="s">
-        <v>641</v>
+        <v>867</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>261</v>
+        <v>1036</v>
       </c>
       <c r="B545" t="s">
-        <v>642</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>321</v>
+        <v>292</v>
       </c>
       <c r="B546" t="s">
-        <v>643</v>
+        <v>627</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>880</v>
+        <v>8</v>
       </c>
       <c r="B547" t="s">
-        <v>881</v>
+        <v>11</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>270</v>
+        <v>335</v>
       </c>
       <c r="B548" t="s">
-        <v>644</v>
+        <v>628</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>273</v>
+        <v>332</v>
       </c>
       <c r="B549" t="s">
-        <v>645</v>
+        <v>629</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="B550" t="s">
-        <v>646</v>
+        <v>630</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>272</v>
+        <v>319</v>
       </c>
       <c r="B551" t="s">
-        <v>647</v>
+        <v>631</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>275</v>
+        <v>860</v>
       </c>
       <c r="B552" t="s">
-        <v>648</v>
+        <v>861</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B553" t="s">
-        <v>649</v>
+        <v>632</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B554" t="s">
-        <v>650</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>94</v>
+        <v>274</v>
       </c>
       <c r="B555" t="s">
-        <v>651</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>202</v>
+        <v>270</v>
       </c>
       <c r="B556" t="s">
-        <v>652</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>205</v>
+        <v>273</v>
       </c>
       <c r="B557" t="s">
-        <v>653</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>174</v>
+        <v>269</v>
       </c>
       <c r="B558" t="s">
-        <v>654</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>712</v>
+        <v>272</v>
       </c>
       <c r="B559" t="s">
-        <v>765</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>254</v>
+        <v>92</v>
       </c>
       <c r="B560" t="s">
-        <v>655</v>
+        <v>633</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>713</v>
+        <v>200</v>
       </c>
       <c r="B561" t="s">
-        <v>766</v>
+        <v>634</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="B562" t="s">
-        <v>656</v>
+        <v>635</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>1015</v>
+        <v>172</v>
       </c>
       <c r="B563" t="s">
-        <v>1016</v>
+        <v>636</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>313</v>
+        <v>694</v>
       </c>
       <c r="B564" t="s">
-        <v>657</v>
+        <v>747</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>314</v>
+        <v>252</v>
       </c>
       <c r="B565" t="s">
-        <v>658</v>
+        <v>637</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>1059</v>
+        <v>695</v>
       </c>
       <c r="B566" t="s">
-        <v>1060</v>
+        <v>748</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>1031</v>
+        <v>189</v>
       </c>
       <c r="B567" t="s">
-        <v>1032</v>
+        <v>638</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>83</v>
+        <v>990</v>
       </c>
       <c r="B568" t="s">
-        <v>659</v>
+        <v>991</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>670</v>
+        <v>311</v>
       </c>
       <c r="B569" t="s">
-        <v>767</v>
+        <v>639</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>943</v>
+        <v>312</v>
       </c>
       <c r="B570" t="s">
-        <v>944</v>
+        <v>640</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>661</v>
+        <v>1034</v>
       </c>
       <c r="B571" t="s">
-        <v>768</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>995</v>
+        <v>1006</v>
       </c>
       <c r="B572" t="s">
-        <v>996</v>
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A573" t="s">
+        <v>81</v>
+      </c>
+      <c r="B573" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A574" t="s">
+        <v>652</v>
+      </c>
+      <c r="B574" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A575" t="s">
+        <v>923</v>
+      </c>
+      <c r="B575" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A576" t="s">
+        <v>643</v>
+      </c>
+      <c r="B576" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A577" t="s">
+        <v>970</v>
+      </c>
+      <c r="B577" t="s">
+        <v>971</v>
       </c>
     </row>
   </sheetData>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05844A1E-B978-4D42-9BF8-11A6CB0AD385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15397DE8-B2F9-4228-8B59-E54937A47490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="1148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="1170">
   <si>
     <t>trigger</t>
   </si>
@@ -1695,9 +1695,6 @@
     <t>PD FS</t>
   </si>
   <si>
-    <t>paramedian disc protrusion</t>
-  </si>
-  <si>
     <t>peroneal artery</t>
   </si>
   <si>
@@ -3469,6 +3466,75 @@
   </si>
   <si>
     <t>small vessel disease (Fazekas grade-I)</t>
+  </si>
+  <si>
+    <t>awa</t>
+  </si>
+  <si>
+    <t>as well as</t>
+  </si>
+  <si>
+    <t>sah</t>
+  </si>
+  <si>
+    <t>subarachnoid hemorrhage</t>
+  </si>
+  <si>
+    <t>sag</t>
+  </si>
+  <si>
+    <t>sagittal</t>
+  </si>
+  <si>
+    <t>cor</t>
+  </si>
+  <si>
+    <t>coronal</t>
+  </si>
+  <si>
+    <t>ep</t>
+  </si>
+  <si>
+    <t>endplate</t>
+  </si>
+  <si>
+    <t>eps</t>
+  </si>
+  <si>
+    <t>endplates</t>
+  </si>
+  <si>
+    <t>cde</t>
+  </si>
+  <si>
+    <t>central disc extrusion</t>
+  </si>
+  <si>
+    <t>paracentral disc protrusion</t>
+  </si>
+  <si>
+    <t>wss</t>
+  </si>
+  <si>
+    <t>whole spine screening</t>
+  </si>
+  <si>
+    <t>emos</t>
+  </si>
+  <si>
+    <t>early marginal osteophytes</t>
+  </si>
+  <si>
+    <t>ivds</t>
+  </si>
+  <si>
+    <t>intervertebral discs</t>
+  </si>
+  <si>
+    <t>doc</t>
+  </si>
+  <si>
+    <t>disc-osteophyte complex</t>
   </si>
 </sst>
 </file>
@@ -3524,10 +3590,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B577" totalsRowShown="0">
-  <autoFilter ref="A1:B577" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B577">
-    <sortCondition ref="A1:A577"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B588" totalsRowShown="0">
+  <autoFilter ref="A1:B588" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B588">
+    <sortCondition ref="A1:A588"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -3800,7 +3866,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B577"/>
+  <dimension ref="A1:B588"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -3825,42 +3891,42 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>944</v>
+      </c>
+      <c r="B3" t="s">
         <v>945</v>
-      </c>
-      <c r="B3" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>942</v>
+      </c>
+      <c r="B4" t="s">
         <v>943</v>
-      </c>
-      <c r="B4" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>946</v>
+      </c>
+      <c r="B5" t="s">
         <v>947</v>
-      </c>
-      <c r="B5" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>954</v>
+      </c>
+      <c r="B6" t="s">
         <v>955</v>
-      </c>
-      <c r="B6" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>905</v>
+      </c>
+      <c r="B7" t="s">
         <v>906</v>
-      </c>
-      <c r="B7" t="s">
-        <v>907</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -3873,18 +3939,18 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>924</v>
+      </c>
+      <c r="B9" t="s">
         <v>925</v>
-      </c>
-      <c r="B9" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>926</v>
+      </c>
+      <c r="B10" t="s">
         <v>927</v>
-      </c>
-      <c r="B10" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -3900,15 +3966,15 @@
         <v>307</v>
       </c>
       <c r="B12" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>881</v>
+      </c>
+      <c r="B13" t="s">
         <v>882</v>
-      </c>
-      <c r="B13" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -3921,58 +3987,58 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>907</v>
+      </c>
+      <c r="B15" t="s">
         <v>908</v>
-      </c>
-      <c r="B15" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>803</v>
+      </c>
+      <c r="B16" t="s">
         <v>804</v>
-      </c>
-      <c r="B16" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>985</v>
+      </c>
+      <c r="B17" t="s">
         <v>986</v>
-      </c>
-      <c r="B17" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B18" t="s">
         <v>1059</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1060</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>877</v>
+      </c>
+      <c r="B19" t="s">
         <v>878</v>
-      </c>
-      <c r="B19" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>768</v>
+      </c>
+      <c r="B20" t="s">
         <v>769</v>
-      </c>
-      <c r="B20" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B21" t="s">
         <v>1055</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1056</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
@@ -4009,26 +4075,26 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B26" t="s">
         <v>1028</v>
-      </c>
-      <c r="B26" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B27" t="s">
         <v>1021</v>
-      </c>
-      <c r="B27" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B28" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
@@ -4041,10 +4107,10 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B30" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
@@ -4073,10 +4139,10 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B34" t="s">
         <v>1023</v>
-      </c>
-      <c r="B34" t="s">
-        <v>1024</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
@@ -4105,10 +4171,10 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
+        <v>911</v>
+      </c>
+      <c r="B38" t="s">
         <v>912</v>
-      </c>
-      <c r="B38" t="s">
-        <v>913</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
@@ -4121,26 +4187,26 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B40" t="s">
         <v>1103</v>
-      </c>
-      <c r="B40" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B41" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B42" t="s">
         <v>1017</v>
-      </c>
-      <c r="B42" t="s">
-        <v>1018</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
@@ -4188,15 +4254,15 @@
         <v>246</v>
       </c>
       <c r="B48" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B49" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
@@ -4209,34 +4275,34 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
+        <v>861</v>
+      </c>
+      <c r="B51" t="s">
         <v>862</v>
-      </c>
-      <c r="B51" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
+        <v>987</v>
+      </c>
+      <c r="B52" t="s">
         <v>988</v>
-      </c>
-      <c r="B52" t="s">
-        <v>989</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
+        <v>774</v>
+      </c>
+      <c r="B53" t="s">
         <v>775</v>
-      </c>
-      <c r="B53" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
+        <v>776</v>
+      </c>
+      <c r="B54" t="s">
         <v>777</v>
-      </c>
-      <c r="B54" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
@@ -4249,4178 +4315,4266 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>303</v>
+        <v>1147</v>
       </c>
       <c r="B56" t="s">
-        <v>366</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>230</v>
+        <v>303</v>
       </c>
       <c r="B57" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B58" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>790</v>
+        <v>232</v>
       </c>
       <c r="B59" t="s">
-        <v>791</v>
+        <v>368</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>318</v>
+        <v>789</v>
       </c>
       <c r="B60" t="s">
-        <v>369</v>
+        <v>790</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>763</v>
+        <v>318</v>
       </c>
       <c r="B61" t="s">
-        <v>764</v>
+        <v>369</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>61</v>
+        <v>762</v>
       </c>
       <c r="B62" t="s">
-        <v>370</v>
+        <v>763</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B64" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>886</v>
+        <v>58</v>
       </c>
       <c r="B65" t="s">
-        <v>887</v>
+        <v>372</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>660</v>
+        <v>885</v>
       </c>
       <c r="B66" t="s">
-        <v>699</v>
+        <v>886</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>237</v>
+        <v>659</v>
       </c>
       <c r="B67" t="s">
-        <v>373</v>
+        <v>698</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>60</v>
+        <v>237</v>
       </c>
       <c r="B68" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>1015</v>
+        <v>60</v>
       </c>
       <c r="B69" t="s">
-        <v>1016</v>
+        <v>374</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>669</v>
+        <v>1014</v>
       </c>
       <c r="B70" t="s">
-        <v>700</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B71" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B72" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B73" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B74" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B75" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B76" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>876</v>
+        <v>674</v>
       </c>
       <c r="B77" t="s">
-        <v>877</v>
+        <v>705</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>321</v>
+        <v>875</v>
       </c>
       <c r="B78" t="s">
-        <v>375</v>
+        <v>876</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>194</v>
+        <v>321</v>
       </c>
       <c r="B79" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="B80" t="s">
-        <v>22</v>
+        <v>376</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B81" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>196</v>
+        <v>19</v>
       </c>
       <c r="B82" t="s">
-        <v>377</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>287</v>
+        <v>196</v>
       </c>
       <c r="B83" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B84" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>337</v>
+        <v>286</v>
       </c>
       <c r="B85" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>900</v>
+        <v>337</v>
       </c>
       <c r="B86" t="s">
-        <v>901</v>
+        <v>380</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>305</v>
+        <v>899</v>
       </c>
       <c r="B87" t="s">
-        <v>381</v>
+        <v>900</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="B88" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="B89" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>333</v>
+        <v>1159</v>
       </c>
       <c r="B90" t="s">
-        <v>384</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>42</v>
+        <v>276</v>
       </c>
       <c r="B91" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>41</v>
+        <v>333</v>
       </c>
       <c r="B92" t="s">
-        <v>1140</v>
+        <v>384</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>650</v>
+        <v>42</v>
       </c>
       <c r="B93" t="s">
-        <v>707</v>
+        <v>385</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>217</v>
+        <v>41</v>
       </c>
       <c r="B94" t="s">
-        <v>386</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>288</v>
+        <v>649</v>
       </c>
       <c r="B95" t="s">
-        <v>387</v>
+        <v>706</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B96" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="B97" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="B98" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>649</v>
+        <v>296</v>
       </c>
       <c r="B99" t="s">
-        <v>708</v>
+        <v>389</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>112</v>
+        <v>199</v>
       </c>
       <c r="B100" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>83</v>
+        <v>648</v>
       </c>
       <c r="B101" t="s">
-        <v>392</v>
+        <v>707</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B102" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>880</v>
+        <v>83</v>
       </c>
       <c r="B103" t="s">
-        <v>881</v>
+        <v>392</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>808</v>
+        <v>115</v>
       </c>
       <c r="B104" t="s">
-        <v>809</v>
+        <v>393</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>152</v>
+        <v>879</v>
       </c>
       <c r="B105" t="s">
-        <v>394</v>
+        <v>880</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>124</v>
+        <v>807</v>
       </c>
       <c r="B106" t="s">
-        <v>396</v>
+        <v>808</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="B107" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="B108" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>968</v>
+        <v>125</v>
       </c>
       <c r="B109" t="s">
-        <v>969</v>
+        <v>395</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="B110" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B111" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="B112" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>198</v>
+        <v>965</v>
       </c>
       <c r="B113" t="s">
-        <v>400</v>
+        <v>966</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>314</v>
+        <v>103</v>
       </c>
       <c r="B114" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>104</v>
+        <v>198</v>
       </c>
       <c r="B115" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>163</v>
+        <v>314</v>
       </c>
       <c r="B116" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B117" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="B118" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>1047</v>
+        <v>101</v>
       </c>
       <c r="B119" t="s">
-        <v>1048</v>
+        <v>404</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>931</v>
+        <v>102</v>
       </c>
       <c r="B120" t="s">
-        <v>932</v>
+        <v>405</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>929</v>
+        <v>1046</v>
       </c>
       <c r="B121" t="s">
-        <v>930</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>162</v>
+        <v>930</v>
       </c>
       <c r="B122" t="s">
-        <v>406</v>
+        <v>931</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>838</v>
+        <v>928</v>
       </c>
       <c r="B123" t="s">
-        <v>839</v>
+        <v>929</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>840</v>
+        <v>162</v>
       </c>
       <c r="B124" t="s">
-        <v>841</v>
+        <v>406</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>1085</v>
+        <v>1153</v>
       </c>
       <c r="B125" t="s">
-        <v>1086</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>666</v>
+        <v>837</v>
       </c>
       <c r="B126" t="s">
-        <v>709</v>
+        <v>838</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>647</v>
+        <v>839</v>
       </c>
       <c r="B127" t="s">
-        <v>710</v>
+        <v>840</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>941</v>
+        <v>1084</v>
       </c>
       <c r="B128" t="s">
-        <v>942</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>684</v>
+        <v>665</v>
       </c>
       <c r="B129" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>685</v>
+        <v>646</v>
       </c>
       <c r="B130" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>686</v>
+        <v>940</v>
       </c>
       <c r="B131" t="s">
-        <v>713</v>
+        <v>941</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="B132" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="B133" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="B134" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="B135" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="B136" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="B137" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B138" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="B139" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>175</v>
+        <v>680</v>
       </c>
       <c r="B140" t="s">
-        <v>407</v>
+        <v>718</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>211</v>
+        <v>681</v>
       </c>
       <c r="B141" t="s">
-        <v>408</v>
+        <v>719</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>213</v>
+        <v>682</v>
       </c>
       <c r="B142" t="s">
-        <v>409</v>
+        <v>720</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="B143" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>247</v>
+        <v>211</v>
       </c>
       <c r="B144" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="B145" t="s">
-        <v>1139</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>336</v>
+        <v>149</v>
       </c>
       <c r="B146" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>651</v>
+        <v>247</v>
       </c>
       <c r="B147" t="s">
-        <v>722</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="B148" t="s">
-        <v>413</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>266</v>
+        <v>336</v>
       </c>
       <c r="B149" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>1097</v>
+        <v>650</v>
       </c>
       <c r="B150" t="s">
-        <v>1098</v>
+        <v>721</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>800</v>
+        <v>91</v>
       </c>
       <c r="B151" t="s">
-        <v>801</v>
+        <v>413</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>295</v>
+        <v>266</v>
       </c>
       <c r="B152" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>1087</v>
+        <v>1096</v>
       </c>
       <c r="B153" t="s">
-        <v>1088</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>1093</v>
+        <v>799</v>
       </c>
       <c r="B154" t="s">
-        <v>1094</v>
+        <v>800</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>151</v>
+        <v>1168</v>
       </c>
       <c r="B155" t="s">
-        <v>416</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>962</v>
+        <v>295</v>
       </c>
       <c r="B156" t="s">
-        <v>963</v>
+        <v>415</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>814</v>
+        <v>1086</v>
       </c>
       <c r="B157" t="s">
-        <v>815</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>933</v>
+        <v>1092</v>
       </c>
       <c r="B158" t="s">
-        <v>934</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>834</v>
+        <v>151</v>
       </c>
       <c r="B159" t="s">
-        <v>835</v>
+        <v>416</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>794</v>
+        <v>961</v>
       </c>
       <c r="B160" t="s">
-        <v>795</v>
+        <v>962</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>755</v>
+        <v>813</v>
       </c>
       <c r="B161" t="s">
-        <v>756</v>
+        <v>814</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>100</v>
+        <v>932</v>
       </c>
       <c r="B162" t="s">
-        <v>417</v>
+        <v>933</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>1043</v>
+        <v>833</v>
       </c>
       <c r="B163" t="s">
-        <v>1044</v>
+        <v>834</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>154</v>
+        <v>793</v>
       </c>
       <c r="B164" t="s">
-        <v>418</v>
+        <v>794</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>157</v>
+        <v>754</v>
       </c>
       <c r="B165" t="s">
-        <v>419</v>
+        <v>755</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="B166" t="s">
-        <v>1138</v>
+        <v>417</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>1077</v>
+        <v>1042</v>
       </c>
       <c r="B167" t="s">
-        <v>1078</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>820</v>
+        <v>154</v>
       </c>
       <c r="B168" t="s">
-        <v>821</v>
+        <v>418</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="B169" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>322</v>
+        <v>24</v>
       </c>
       <c r="B170" t="s">
-        <v>421</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>868</v>
+        <v>1164</v>
       </c>
       <c r="B171" t="s">
-        <v>869</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>183</v>
+        <v>1076</v>
       </c>
       <c r="B172" t="s">
-        <v>422</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>892</v>
+        <v>819</v>
       </c>
       <c r="B173" t="s">
-        <v>893</v>
+        <v>820</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>32</v>
+        <v>130</v>
       </c>
       <c r="B174" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>35</v>
+        <v>322</v>
       </c>
       <c r="B175" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>765</v>
+        <v>867</v>
       </c>
       <c r="B176" t="s">
-        <v>1011</v>
+        <v>868</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="B177" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>170</v>
+        <v>1155</v>
       </c>
       <c r="B178" t="s">
-        <v>425</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>1012</v>
+        <v>1157</v>
       </c>
       <c r="B179" t="s">
-        <v>766</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>178</v>
+        <v>891</v>
       </c>
       <c r="B180" t="s">
-        <v>426</v>
+        <v>892</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>111</v>
+        <v>32</v>
       </c>
       <c r="B181" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>238</v>
+        <v>35</v>
       </c>
       <c r="B182" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>106</v>
+        <v>764</v>
       </c>
       <c r="B183" t="s">
-        <v>429</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="B184" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="B185" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>668</v>
+        <v>1011</v>
       </c>
       <c r="B186" t="s">
-        <v>723</v>
+        <v>765</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="B187" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B188" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B189" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>226</v>
+        <v>106</v>
       </c>
       <c r="B190" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>177</v>
+        <v>109</v>
       </c>
       <c r="B191" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B192" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>1111</v>
+        <v>667</v>
       </c>
       <c r="B193" t="s">
-        <v>1112</v>
+        <v>722</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>978</v>
+        <v>97</v>
       </c>
       <c r="B194" t="s">
-        <v>979</v>
+        <v>432</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>980</v>
+        <v>110</v>
       </c>
       <c r="B195" t="s">
-        <v>981</v>
+        <v>433</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="B196" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>34</v>
+        <v>226</v>
       </c>
       <c r="B197" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>788</v>
+        <v>177</v>
       </c>
       <c r="B198" t="s">
-        <v>789</v>
+        <v>436</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B199" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>275</v>
+        <v>1110</v>
       </c>
       <c r="B200" t="s">
-        <v>441</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>858</v>
+        <v>977</v>
       </c>
       <c r="B201" t="s">
-        <v>859</v>
+        <v>978</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>116</v>
+        <v>979</v>
       </c>
       <c r="B202" t="s">
-        <v>442</v>
+        <v>980</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>208</v>
+        <v>253</v>
       </c>
       <c r="B203" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>1057</v>
+        <v>34</v>
       </c>
       <c r="B204" t="s">
-        <v>1058</v>
+        <v>439</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>118</v>
+        <v>787</v>
       </c>
       <c r="B205" t="s">
-        <v>444</v>
+        <v>788</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>642</v>
+        <v>180</v>
       </c>
       <c r="B206" t="s">
-        <v>724</v>
+        <v>440</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>816</v>
+        <v>275</v>
       </c>
       <c r="B207" t="s">
-        <v>817</v>
+        <v>441</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>298</v>
+        <v>857</v>
       </c>
       <c r="B208" t="s">
-        <v>445</v>
+        <v>858</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>644</v>
+        <v>116</v>
       </c>
       <c r="B209" t="s">
-        <v>725</v>
+        <v>442</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>645</v>
+        <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>726</v>
+        <v>443</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>1037</v>
+        <v>1056</v>
       </c>
       <c r="B211" t="s">
-        <v>1038</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="B212" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>88</v>
+        <v>641</v>
       </c>
       <c r="B213" t="s">
-        <v>447</v>
+        <v>723</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>89</v>
+        <v>815</v>
       </c>
       <c r="B214" t="s">
-        <v>448</v>
+        <v>816</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>1073</v>
+        <v>298</v>
       </c>
       <c r="B215" t="s">
-        <v>1074</v>
+        <v>445</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>23</v>
+        <v>643</v>
       </c>
       <c r="B216" t="s">
-        <v>1137</v>
+        <v>724</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>5</v>
+        <v>644</v>
       </c>
       <c r="B217" t="s">
-        <v>6</v>
+        <v>725</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>1142</v>
+        <v>1036</v>
       </c>
       <c r="B218" t="s">
-        <v>1143</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="B219" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="B220" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="B221" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>132</v>
+        <v>1072</v>
       </c>
       <c r="B222" t="s">
-        <v>452</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="B223" t="s">
-        <v>453</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>277</v>
+        <v>5</v>
       </c>
       <c r="B224" t="s">
-        <v>454</v>
+        <v>6</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>1075</v>
+        <v>1141</v>
       </c>
       <c r="B225" t="s">
-        <v>1076</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>9</v>
+        <v>126</v>
       </c>
       <c r="B226" t="s">
-        <v>10</v>
+        <v>449</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B227" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B228" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>173</v>
+        <v>132</v>
       </c>
       <c r="B229" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>262</v>
+        <v>119</v>
       </c>
       <c r="B230" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>77</v>
+        <v>277</v>
       </c>
       <c r="B231" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>939</v>
+        <v>1074</v>
       </c>
       <c r="B232" t="s">
-        <v>940</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>168</v>
+        <v>9</v>
       </c>
       <c r="B233" t="s">
-        <v>460</v>
+        <v>10</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>167</v>
+        <v>129</v>
       </c>
       <c r="B234" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>836</v>
+        <v>127</v>
       </c>
       <c r="B235" t="s">
-        <v>837</v>
+        <v>456</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>792</v>
+        <v>173</v>
       </c>
       <c r="B236" t="s">
-        <v>793</v>
+        <v>457</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>304</v>
+        <v>262</v>
       </c>
       <c r="B237" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>759</v>
+        <v>77</v>
       </c>
       <c r="B238" t="s">
-        <v>760</v>
+        <v>459</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>898</v>
+        <v>938</v>
       </c>
       <c r="B239" t="s">
-        <v>899</v>
+        <v>939</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>653</v>
+        <v>168</v>
       </c>
       <c r="B240" t="s">
-        <v>727</v>
+        <v>460</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>86</v>
+        <v>167</v>
       </c>
       <c r="B241" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>87</v>
+        <v>835</v>
       </c>
       <c r="B242" t="s">
-        <v>464</v>
+        <v>836</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>153</v>
+        <v>791</v>
       </c>
       <c r="B243" t="s">
-        <v>465</v>
+        <v>792</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>156</v>
+        <v>304</v>
       </c>
       <c r="B244" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>158</v>
+        <v>758</v>
       </c>
       <c r="B245" t="s">
-        <v>467</v>
+        <v>759</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>251</v>
+        <v>897</v>
       </c>
       <c r="B246" t="s">
-        <v>468</v>
+        <v>898</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>285</v>
+        <v>652</v>
       </c>
       <c r="B247" t="s">
-        <v>469</v>
+        <v>726</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>326</v>
+        <v>86</v>
       </c>
       <c r="B248" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>327</v>
+        <v>87</v>
       </c>
       <c r="B249" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>229</v>
+        <v>153</v>
       </c>
       <c r="B250" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>55</v>
+        <v>156</v>
       </c>
       <c r="B251" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>658</v>
+        <v>158</v>
       </c>
       <c r="B252" t="s">
-        <v>728</v>
+        <v>467</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>57</v>
+        <v>285</v>
       </c>
       <c r="B254" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>236</v>
+        <v>326</v>
       </c>
       <c r="B255" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>767</v>
+        <v>327</v>
       </c>
       <c r="B256" t="s">
-        <v>1010</v>
+        <v>471</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>1013</v>
+        <v>229</v>
       </c>
       <c r="B257" t="s">
-        <v>768</v>
+        <v>472</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>164</v>
+        <v>55</v>
       </c>
       <c r="B258" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>201</v>
+        <v>657</v>
       </c>
       <c r="B259" t="s">
-        <v>478</v>
+        <v>727</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="B260" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>313</v>
+        <v>57</v>
       </c>
       <c r="B261" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>874</v>
+        <v>236</v>
       </c>
       <c r="B262" t="s">
-        <v>875</v>
+        <v>476</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>998</v>
+        <v>766</v>
       </c>
       <c r="B263" t="s">
-        <v>999</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>258</v>
+        <v>1012</v>
       </c>
       <c r="B264" t="s">
-        <v>481</v>
+        <v>767</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>984</v>
+        <v>164</v>
       </c>
       <c r="B265" t="s">
-        <v>985</v>
+        <v>477</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>160</v>
+        <v>201</v>
       </c>
       <c r="B266" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>693</v>
+        <v>204</v>
       </c>
       <c r="B267" t="s">
-        <v>729</v>
+        <v>479</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>761</v>
+        <v>313</v>
       </c>
       <c r="B268" t="s">
-        <v>762</v>
+        <v>480</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>896</v>
+        <v>873</v>
       </c>
       <c r="B269" t="s">
-        <v>897</v>
+        <v>874</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>894</v>
+        <v>997</v>
       </c>
       <c r="B270" t="s">
-        <v>895</v>
+        <v>998</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>184</v>
+        <v>258</v>
       </c>
       <c r="B271" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>244</v>
+        <v>983</v>
       </c>
       <c r="B272" t="s">
-        <v>484</v>
+        <v>984</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>243</v>
+        <v>160</v>
       </c>
       <c r="B273" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="B274" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>688</v>
+        <v>1166</v>
       </c>
       <c r="B275" t="s">
-        <v>731</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>689</v>
+        <v>760</v>
       </c>
       <c r="B276" t="s">
-        <v>732</v>
+        <v>761</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>690</v>
+        <v>895</v>
       </c>
       <c r="B277" t="s">
-        <v>733</v>
+        <v>896</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>691</v>
+        <v>893</v>
       </c>
       <c r="B278" t="s">
-        <v>734</v>
+        <v>894</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>280</v>
+        <v>184</v>
       </c>
       <c r="B279" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>281</v>
+        <v>244</v>
       </c>
       <c r="B280" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>49</v>
+        <v>243</v>
       </c>
       <c r="B281" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>53</v>
+        <v>686</v>
       </c>
       <c r="B282" t="s">
-        <v>489</v>
+        <v>729</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>136</v>
+        <v>687</v>
       </c>
       <c r="B283" t="s">
-        <v>491</v>
+        <v>730</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>72</v>
+        <v>688</v>
       </c>
       <c r="B284" t="s">
-        <v>490</v>
+        <v>731</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>221</v>
+        <v>689</v>
       </c>
       <c r="B285" t="s">
-        <v>492</v>
+        <v>732</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>15</v>
+        <v>690</v>
       </c>
       <c r="B286" t="s">
-        <v>16</v>
+        <v>733</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>1061</v>
+        <v>280</v>
       </c>
       <c r="B287" t="s">
-        <v>1062</v>
+        <v>486</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>921</v>
+        <v>281</v>
       </c>
       <c r="B288" t="s">
-        <v>922</v>
+        <v>487</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="B289" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>241</v>
+        <v>53</v>
       </c>
       <c r="B290" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>328</v>
+        <v>136</v>
       </c>
       <c r="B291" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>1101</v>
+        <v>72</v>
       </c>
       <c r="B292" t="s">
-        <v>1102</v>
+        <v>490</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>1053</v>
+        <v>221</v>
       </c>
       <c r="B293" t="s">
-        <v>1054</v>
+        <v>492</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>121</v>
+        <v>15</v>
       </c>
       <c r="B294" t="s">
-        <v>496</v>
+        <v>16</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>751</v>
+        <v>1060</v>
       </c>
       <c r="B295" t="s">
-        <v>752</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>782</v>
+        <v>920</v>
       </c>
       <c r="B296" t="s">
-        <v>783</v>
+        <v>921</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="B297" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>63</v>
+        <v>241</v>
       </c>
       <c r="B298" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>224</v>
+        <v>328</v>
       </c>
       <c r="B299" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>25</v>
+        <v>1100</v>
       </c>
       <c r="B300" t="s">
-        <v>500</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>26</v>
+        <v>1052</v>
       </c>
       <c r="B301" t="s">
-        <v>501</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>207</v>
+        <v>121</v>
       </c>
       <c r="B302" t="s">
-        <v>1134</v>
+        <v>496</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>961</v>
+        <v>750</v>
       </c>
       <c r="B303" t="s">
-        <v>1135</v>
+        <v>751</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>1114</v>
+        <v>781</v>
       </c>
       <c r="B304" t="s">
-        <v>1115</v>
+        <v>782</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>206</v>
+        <v>134</v>
       </c>
       <c r="B305" t="s">
-        <v>1136</v>
+        <v>497</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>202</v>
+        <v>63</v>
       </c>
       <c r="B306" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="B307" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="B308" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>664</v>
+        <v>26</v>
       </c>
       <c r="B309" t="s">
-        <v>735</v>
+        <v>501</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="B310" t="s">
-        <v>505</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>1089</v>
+        <v>960</v>
       </c>
       <c r="B311" t="s">
-        <v>1090</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>263</v>
+        <v>1113</v>
       </c>
       <c r="B312" t="s">
-        <v>506</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>1091</v>
+        <v>206</v>
       </c>
       <c r="B313" t="s">
-        <v>1092</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>80</v>
+        <v>202</v>
       </c>
       <c r="B314" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>65</v>
+        <v>205</v>
       </c>
       <c r="B315" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>191</v>
+        <v>145</v>
       </c>
       <c r="B316" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>123</v>
+        <v>663</v>
       </c>
       <c r="B317" t="s">
-        <v>510</v>
+        <v>734</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="B318" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>231</v>
+        <v>1088</v>
       </c>
       <c r="B319" t="s">
-        <v>512</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>233</v>
+        <v>263</v>
       </c>
       <c r="B320" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>31</v>
+        <v>1090</v>
       </c>
       <c r="B321" t="s">
-        <v>514</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="B322" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="B323" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>71</v>
+        <v>191</v>
       </c>
       <c r="B324" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>306</v>
+        <v>123</v>
       </c>
       <c r="B325" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>222</v>
+        <v>192</v>
       </c>
       <c r="B326" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>315</v>
+        <v>231</v>
       </c>
       <c r="B327" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>278</v>
+        <v>233</v>
       </c>
       <c r="B328" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>279</v>
+        <v>31</v>
       </c>
       <c r="B329" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>832</v>
+        <v>30</v>
       </c>
       <c r="B330" t="s">
-        <v>833</v>
+        <v>515</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B331" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>146</v>
+        <v>71</v>
       </c>
       <c r="B332" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>52</v>
+        <v>306</v>
       </c>
       <c r="B333" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B334" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>1095</v>
+        <v>315</v>
       </c>
       <c r="B335" t="s">
-        <v>1096</v>
+        <v>520</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>1110</v>
+        <v>278</v>
       </c>
       <c r="B336" t="s">
-        <v>1113</v>
+        <v>521</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>1051</v>
+        <v>279</v>
       </c>
       <c r="B337" t="s">
-        <v>1052</v>
+        <v>522</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>96</v>
+        <v>831</v>
       </c>
       <c r="B338" t="s">
-        <v>527</v>
+        <v>832</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>248</v>
+        <v>48</v>
       </c>
       <c r="B339" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>249</v>
+        <v>146</v>
       </c>
       <c r="B340" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="B341" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>1065</v>
+        <v>223</v>
       </c>
       <c r="B342" t="s">
-        <v>1066</v>
+        <v>526</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>212</v>
+        <v>1094</v>
       </c>
       <c r="B343" t="s">
-        <v>531</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>917</v>
+        <v>1109</v>
       </c>
       <c r="B344" t="s">
-        <v>918</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>915</v>
+        <v>1050</v>
       </c>
       <c r="B345" t="s">
-        <v>916</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>919</v>
+        <v>96</v>
       </c>
       <c r="B346" t="s">
-        <v>920</v>
+        <v>527</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>330</v>
+        <v>248</v>
       </c>
       <c r="B347" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>1067</v>
+        <v>249</v>
       </c>
       <c r="B348" t="s">
-        <v>1068</v>
+        <v>529</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>996</v>
+        <v>94</v>
       </c>
       <c r="B349" t="s">
-        <v>997</v>
+        <v>530</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>992</v>
+        <v>1064</v>
       </c>
       <c r="B350" t="s">
-        <v>993</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>994</v>
+        <v>212</v>
       </c>
       <c r="B351" t="s">
-        <v>995</v>
+        <v>531</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>82</v>
+        <v>916</v>
       </c>
       <c r="B352" t="s">
-        <v>533</v>
+        <v>917</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>773</v>
+        <v>914</v>
       </c>
       <c r="B353" t="s">
-        <v>774</v>
+        <v>915</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>197</v>
+        <v>918</v>
       </c>
       <c r="B354" t="s">
-        <v>534</v>
+        <v>919</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>655</v>
+        <v>330</v>
       </c>
       <c r="B355" t="s">
-        <v>736</v>
+        <v>532</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>822</v>
+        <v>1066</v>
       </c>
       <c r="B356" t="s">
-        <v>823</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>1069</v>
+        <v>995</v>
       </c>
       <c r="B357" t="s">
-        <v>1070</v>
+        <v>996</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>3</v>
+        <v>991</v>
       </c>
       <c r="B358" t="s">
-        <v>4</v>
+        <v>992</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>959</v>
+        <v>993</v>
       </c>
       <c r="B359" t="s">
-        <v>4</v>
+        <v>994</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>960</v>
+        <v>82</v>
       </c>
       <c r="B360" t="s">
-        <v>4</v>
+        <v>533</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>665</v>
+        <v>772</v>
       </c>
       <c r="B361" t="s">
-        <v>737</v>
+        <v>773</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>771</v>
+        <v>197</v>
       </c>
       <c r="B362" t="s">
-        <v>772</v>
+        <v>534</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>85</v>
+        <v>654</v>
       </c>
       <c r="B363" t="s">
-        <v>535</v>
+        <v>735</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>1063</v>
+        <v>821</v>
       </c>
       <c r="B364" t="s">
-        <v>1064</v>
+        <v>822</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>830</v>
+        <v>1068</v>
       </c>
       <c r="B365" t="s">
-        <v>831</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>810</v>
+        <v>3</v>
       </c>
       <c r="B366" t="s">
-        <v>811</v>
+        <v>4</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>187</v>
+        <v>958</v>
       </c>
       <c r="B367" t="s">
-        <v>536</v>
+        <v>4</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>828</v>
+        <v>959</v>
       </c>
       <c r="B368" t="s">
-        <v>829</v>
+        <v>4</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>935</v>
+        <v>664</v>
       </c>
       <c r="B369" t="s">
-        <v>1131</v>
+        <v>736</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>864</v>
+        <v>770</v>
       </c>
       <c r="B370" t="s">
-        <v>865</v>
+        <v>771</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>1045</v>
+        <v>85</v>
       </c>
       <c r="B371" t="s">
-        <v>1046</v>
+        <v>535</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>799</v>
+        <v>1062</v>
       </c>
       <c r="B372" t="s">
-        <v>1132</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>798</v>
+        <v>829</v>
       </c>
       <c r="B373" t="s">
-        <v>1133</v>
+        <v>830</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>13</v>
+        <v>809</v>
       </c>
       <c r="B374" t="s">
-        <v>14</v>
+        <v>810</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>818</v>
+        <v>187</v>
       </c>
       <c r="B375" t="s">
-        <v>819</v>
+        <v>536</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>186</v>
+        <v>827</v>
       </c>
       <c r="B376" t="s">
-        <v>537</v>
+        <v>828</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>812</v>
+        <v>934</v>
       </c>
       <c r="B377" t="s">
-        <v>813</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>320</v>
+        <v>863</v>
       </c>
       <c r="B378" t="s">
-        <v>538</v>
+        <v>864</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>657</v>
+        <v>1044</v>
       </c>
       <c r="B379" t="s">
-        <v>738</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>856</v>
+        <v>798</v>
       </c>
       <c r="B380" t="s">
-        <v>857</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>659</v>
+        <v>797</v>
       </c>
       <c r="B381" t="s">
-        <v>739</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>654</v>
+        <v>13</v>
       </c>
       <c r="B382" t="s">
-        <v>740</v>
+        <v>14</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>256</v>
+        <v>817</v>
       </c>
       <c r="B383" t="s">
-        <v>539</v>
+        <v>818</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>260</v>
+        <v>186</v>
       </c>
       <c r="B384" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>261</v>
+        <v>811</v>
       </c>
       <c r="B385" t="s">
-        <v>541</v>
+        <v>812</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>188</v>
+        <v>320</v>
       </c>
       <c r="B386" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>190</v>
+        <v>656</v>
       </c>
       <c r="B387" t="s">
-        <v>543</v>
+        <v>737</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>937</v>
+        <v>855</v>
       </c>
       <c r="B388" t="s">
-        <v>938</v>
+        <v>856</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>1032</v>
+        <v>658</v>
       </c>
       <c r="B389" t="s">
-        <v>1033</v>
+        <v>738</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>209</v>
+        <v>653</v>
       </c>
       <c r="B390" t="s">
-        <v>544</v>
+        <v>739</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>852</v>
+        <v>256</v>
       </c>
       <c r="B391" t="s">
-        <v>853</v>
+        <v>539</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>143</v>
+        <v>260</v>
       </c>
       <c r="B392" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>140</v>
+        <v>261</v>
       </c>
       <c r="B393" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>254</v>
+        <v>188</v>
       </c>
       <c r="B394" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>331</v>
+        <v>190</v>
       </c>
       <c r="B395" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>210</v>
+        <v>936</v>
       </c>
       <c r="B396" t="s">
-        <v>549</v>
+        <v>937</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>234</v>
+        <v>1031</v>
       </c>
       <c r="B397" t="s">
-        <v>550</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>73</v>
+        <v>209</v>
       </c>
       <c r="B398" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>342</v>
+        <v>851</v>
       </c>
       <c r="B399" t="s">
-        <v>552</v>
+        <v>852</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>308</v>
+        <v>143</v>
       </c>
       <c r="B400" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>844</v>
+        <v>140</v>
       </c>
       <c r="B401" t="s">
-        <v>845</v>
+        <v>546</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>846</v>
+        <v>254</v>
       </c>
       <c r="B402" t="s">
-        <v>847</v>
+        <v>547</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>220</v>
+        <v>331</v>
       </c>
       <c r="B403" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>910</v>
+        <v>210</v>
       </c>
       <c r="B404" t="s">
-        <v>911</v>
+        <v>549</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>964</v>
+        <v>234</v>
       </c>
       <c r="B405" t="s">
-        <v>965</v>
+        <v>550</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>227</v>
+        <v>73</v>
       </c>
       <c r="B406" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="B407" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>972</v>
+        <v>308</v>
       </c>
       <c r="B408" t="s">
-        <v>973</v>
+        <v>553</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>779</v>
+        <v>843</v>
       </c>
       <c r="B409" t="s">
-        <v>780</v>
+        <v>844</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>294</v>
+        <v>845</v>
       </c>
       <c r="B410" t="s">
-        <v>557</v>
+        <v>846</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>953</v>
+        <v>220</v>
       </c>
       <c r="B411" t="s">
-        <v>954</v>
+        <v>554</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>339</v>
+        <v>909</v>
       </c>
       <c r="B412" t="s">
-        <v>558</v>
+        <v>910</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>781</v>
+        <v>963</v>
       </c>
       <c r="B413" t="s">
-        <v>780</v>
+        <v>964</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>340</v>
+        <v>227</v>
       </c>
       <c r="B414" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B415" t="s">
-        <v>560</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>646</v>
+        <v>971</v>
       </c>
       <c r="B416" t="s">
-        <v>741</v>
+        <v>972</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>39</v>
+        <v>778</v>
       </c>
       <c r="B417" t="s">
-        <v>561</v>
+        <v>779</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>38</v>
+        <v>294</v>
       </c>
       <c r="B418" t="s">
-        <v>1130</v>
+        <v>556</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>343</v>
+        <v>952</v>
       </c>
       <c r="B419" t="s">
-        <v>562</v>
+        <v>953</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>107</v>
+        <v>339</v>
       </c>
       <c r="B420" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>1030</v>
+        <v>780</v>
       </c>
       <c r="B421" t="s">
-        <v>1031</v>
+        <v>779</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>904</v>
+        <v>340</v>
       </c>
       <c r="B422" t="s">
-        <v>905</v>
+        <v>558</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>117</v>
+        <v>341</v>
       </c>
       <c r="B423" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>1026</v>
+        <v>645</v>
       </c>
       <c r="B424" t="s">
-        <v>1027</v>
+        <v>740</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="B425" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="B426" t="s">
-        <v>566</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>667</v>
+        <v>343</v>
       </c>
       <c r="B427" t="s">
-        <v>742</v>
+        <v>561</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>1108</v>
+        <v>107</v>
       </c>
       <c r="B428" t="s">
-        <v>1025</v>
+        <v>562</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>824</v>
+        <v>1029</v>
       </c>
       <c r="B429" t="s">
-        <v>825</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>113</v>
+        <v>903</v>
       </c>
       <c r="B430" t="s">
-        <v>567</v>
+        <v>904</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>890</v>
+        <v>117</v>
       </c>
       <c r="B431" t="s">
-        <v>891</v>
+        <v>563</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>45</v>
+        <v>1025</v>
       </c>
       <c r="B432" t="s">
-        <v>1129</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>290</v>
+        <v>98</v>
       </c>
       <c r="B433" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>299</v>
+        <v>99</v>
       </c>
       <c r="B434" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>47</v>
+        <v>666</v>
       </c>
       <c r="B435" t="s">
-        <v>570</v>
+        <v>741</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>848</v>
+        <v>1107</v>
       </c>
       <c r="B436" t="s">
-        <v>849</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>51</v>
+        <v>823</v>
       </c>
       <c r="B437" t="s">
-        <v>571</v>
+        <v>824</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>872</v>
+        <v>113</v>
       </c>
       <c r="B438" t="s">
-        <v>873</v>
+        <v>566</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>114</v>
+        <v>889</v>
       </c>
       <c r="B439" t="s">
-        <v>572</v>
+        <v>890</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>854</v>
+        <v>45</v>
       </c>
       <c r="B440" t="s">
-        <v>855</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>144</v>
+        <v>290</v>
       </c>
       <c r="B441" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>1081</v>
+        <v>299</v>
       </c>
       <c r="B442" t="s">
-        <v>1082</v>
+        <v>568</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>176</v>
+        <v>47</v>
       </c>
       <c r="B443" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>316</v>
+        <v>847</v>
       </c>
       <c r="B444" t="s">
-        <v>575</v>
+        <v>848</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="B445" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>1105</v>
+        <v>871</v>
       </c>
       <c r="B446" t="s">
-        <v>1106</v>
+        <v>872</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>1019</v>
+        <v>114</v>
       </c>
       <c r="B447" t="s">
-        <v>1020</v>
+        <v>571</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>293</v>
+        <v>853</v>
       </c>
       <c r="B448" t="s">
-        <v>577</v>
+        <v>854</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>982</v>
+        <v>144</v>
       </c>
       <c r="B449" t="s">
-        <v>983</v>
+        <v>572</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>301</v>
+        <v>1080</v>
       </c>
       <c r="B450" t="s">
-        <v>578</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>1004</v>
+        <v>176</v>
       </c>
       <c r="B451" t="s">
-        <v>1005</v>
+        <v>573</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>1008</v>
+        <v>316</v>
       </c>
       <c r="B452" t="s">
-        <v>1009</v>
+        <v>574</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="B453" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>76</v>
+        <v>1104</v>
       </c>
       <c r="B454" t="s">
-        <v>580</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>78</v>
+        <v>1018</v>
       </c>
       <c r="B455" t="s">
-        <v>581</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>329</v>
+        <v>293</v>
       </c>
       <c r="B456" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>753</v>
+        <v>981</v>
       </c>
       <c r="B457" t="s">
-        <v>754</v>
+        <v>982</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>806</v>
+        <v>301</v>
       </c>
       <c r="B458" t="s">
-        <v>807</v>
+        <v>577</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>135</v>
+        <v>1003</v>
       </c>
       <c r="B459" t="s">
-        <v>583</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>1039</v>
+        <v>1007</v>
       </c>
       <c r="B460" t="s">
-        <v>1040</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>215</v>
+        <v>75</v>
       </c>
       <c r="B461" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>936</v>
+        <v>76</v>
       </c>
       <c r="B462" t="s">
-        <v>1146</v>
+        <v>579</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>216</v>
+        <v>78</v>
       </c>
       <c r="B463" t="s">
-        <v>1127</v>
+        <v>580</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="B464" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>1083</v>
+        <v>752</v>
       </c>
       <c r="B465" t="s">
-        <v>1084</v>
+        <v>753</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>214</v>
+        <v>805</v>
       </c>
       <c r="B466" t="s">
-        <v>1128</v>
+        <v>806</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>1000</v>
+        <v>135</v>
       </c>
       <c r="B467" t="s">
-        <v>1001</v>
+        <v>582</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>1002</v>
+        <v>1038</v>
       </c>
       <c r="B468" t="s">
-        <v>1003</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="B469" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>949</v>
+        <v>935</v>
       </c>
       <c r="B470" t="s">
-        <v>950</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>1099</v>
+        <v>216</v>
       </c>
       <c r="B471" t="s">
-        <v>1100</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>1049</v>
+        <v>317</v>
       </c>
       <c r="B472" t="s">
-        <v>1050</v>
+        <v>584</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>93</v>
+        <v>1082</v>
       </c>
       <c r="B473" t="s">
-        <v>587</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>120</v>
+        <v>214</v>
       </c>
       <c r="B474" t="s">
-        <v>588</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>784</v>
+        <v>999</v>
       </c>
       <c r="B475" t="s">
-        <v>785</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>133</v>
+        <v>1001</v>
       </c>
       <c r="B476" t="s">
-        <v>589</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>62</v>
+        <v>225</v>
       </c>
       <c r="B477" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>66</v>
+        <v>948</v>
       </c>
       <c r="B478" t="s">
-        <v>591</v>
+        <v>949</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>826</v>
+        <v>1098</v>
       </c>
       <c r="B479" t="s">
-        <v>827</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>951</v>
+        <v>1048</v>
       </c>
       <c r="B480" t="s">
-        <v>952</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="B481" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="B482" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>122</v>
+        <v>783</v>
       </c>
       <c r="B483" t="s">
-        <v>594</v>
+        <v>784</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>181</v>
+        <v>133</v>
       </c>
       <c r="B484" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>802</v>
+        <v>62</v>
       </c>
       <c r="B485" t="s">
-        <v>803</v>
+        <v>589</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>692</v>
+        <v>66</v>
       </c>
       <c r="B486" t="s">
-        <v>743</v>
+        <v>590</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>284</v>
+        <v>825</v>
       </c>
       <c r="B487" t="s">
-        <v>596</v>
+        <v>826</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>974</v>
+        <v>950</v>
       </c>
       <c r="B488" t="s">
-        <v>975</v>
+        <v>951</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>842</v>
+        <v>79</v>
       </c>
       <c r="B489" t="s">
-        <v>843</v>
+        <v>591</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>283</v>
+        <v>64</v>
       </c>
       <c r="B490" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>884</v>
+        <v>122</v>
       </c>
       <c r="B491" t="s">
-        <v>885</v>
+        <v>593</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>757</v>
+        <v>181</v>
       </c>
       <c r="B492" t="s">
-        <v>758</v>
+        <v>594</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>1079</v>
+        <v>801</v>
       </c>
       <c r="B493" t="s">
-        <v>1080</v>
+        <v>802</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>67</v>
+        <v>691</v>
       </c>
       <c r="B494" t="s">
-        <v>598</v>
+        <v>742</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>68</v>
+        <v>1151</v>
       </c>
       <c r="B495" t="s">
-        <v>599</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>95</v>
+        <v>1149</v>
       </c>
       <c r="B496" t="s">
-        <v>600</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B497" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>297</v>
+        <v>973</v>
       </c>
       <c r="B498" t="s">
-        <v>602</v>
+        <v>974</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>264</v>
+        <v>841</v>
       </c>
       <c r="B499" t="s">
-        <v>603</v>
+        <v>842</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>193</v>
+        <v>283</v>
       </c>
       <c r="B500" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>902</v>
+        <v>883</v>
       </c>
       <c r="B501" t="s">
-        <v>903</v>
+        <v>884</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>44</v>
+        <v>756</v>
       </c>
       <c r="B502" t="s">
-        <v>1126</v>
+        <v>757</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>1071</v>
+        <v>1078</v>
       </c>
       <c r="B503" t="s">
-        <v>1072</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>324</v>
+        <v>67</v>
       </c>
       <c r="B504" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>325</v>
+        <v>68</v>
       </c>
       <c r="B505" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>850</v>
+        <v>95</v>
       </c>
       <c r="B506" t="s">
-        <v>851</v>
+        <v>599</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>888</v>
+        <v>289</v>
       </c>
       <c r="B507" t="s">
-        <v>889</v>
+        <v>600</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>870</v>
+        <v>297</v>
       </c>
       <c r="B508" t="s">
-        <v>871</v>
+        <v>601</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>33</v>
+        <v>264</v>
       </c>
       <c r="B509" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>36</v>
+        <v>193</v>
       </c>
       <c r="B510" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>1144</v>
+        <v>901</v>
       </c>
       <c r="B511" t="s">
-        <v>1145</v>
+        <v>902</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>309</v>
+        <v>44</v>
       </c>
       <c r="B512" t="s">
-        <v>609</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>257</v>
+        <v>1070</v>
       </c>
       <c r="B513" t="s">
-        <v>610</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="B514" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>228</v>
+        <v>325</v>
       </c>
       <c r="B515" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>17</v>
+        <v>849</v>
       </c>
       <c r="B516" t="s">
-        <v>18</v>
+        <v>850</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>656</v>
+        <v>887</v>
       </c>
       <c r="B517" t="s">
-        <v>744</v>
+        <v>888</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>786</v>
+        <v>869</v>
       </c>
       <c r="B518" t="s">
-        <v>787</v>
+        <v>870</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>142</v>
+        <v>33</v>
       </c>
       <c r="B519" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>957</v>
+        <v>36</v>
       </c>
       <c r="B520" t="s">
-        <v>958</v>
+        <v>607</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>54</v>
+        <v>1143</v>
       </c>
       <c r="B521" t="s">
-        <v>614</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>265</v>
+        <v>309</v>
       </c>
       <c r="B522" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>977</v>
+        <v>257</v>
       </c>
       <c r="B523" t="s">
-        <v>976</v>
+        <v>609</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>56</v>
+        <v>302</v>
       </c>
       <c r="B524" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>185</v>
+        <v>228</v>
       </c>
       <c r="B525" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>159</v>
+        <v>17</v>
       </c>
       <c r="B526" t="s">
-        <v>618</v>
+        <v>18</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>43</v>
+        <v>655</v>
       </c>
       <c r="B527" t="s">
-        <v>1147</v>
+        <v>743</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>40</v>
+        <v>785</v>
       </c>
       <c r="B528" t="s">
-        <v>1125</v>
+        <v>786</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="B529" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>12</v>
+        <v>956</v>
       </c>
       <c r="B530" t="s">
-        <v>11</v>
+        <v>957</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>250</v>
+        <v>54</v>
       </c>
       <c r="B531" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>27</v>
+        <v>265</v>
       </c>
       <c r="B532" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>1041</v>
+        <v>976</v>
       </c>
       <c r="B533" t="s">
-        <v>1042</v>
+        <v>975</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="B534" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>255</v>
+        <v>185</v>
       </c>
       <c r="B535" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>796</v>
+        <v>159</v>
       </c>
       <c r="B536" t="s">
-        <v>797</v>
+        <v>617</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>267</v>
+        <v>43</v>
       </c>
       <c r="B537" t="s">
-        <v>624</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>662</v>
+        <v>40</v>
       </c>
       <c r="B538" t="s">
-        <v>745</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>663</v>
+        <v>165</v>
       </c>
       <c r="B539" t="s">
-        <v>746</v>
+        <v>618</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>139</v>
+        <v>12</v>
       </c>
       <c r="B540" t="s">
-        <v>625</v>
+        <v>11</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>7</v>
+        <v>250</v>
       </c>
       <c r="B541" t="s">
-        <v>2</v>
+        <v>619</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="B542" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>1035</v>
+        <v>1040</v>
       </c>
       <c r="B543" t="s">
-        <v>1124</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>866</v>
+        <v>28</v>
       </c>
       <c r="B544" t="s">
-        <v>867</v>
+        <v>621</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>1036</v>
+        <v>255</v>
       </c>
       <c r="B545" t="s">
-        <v>1123</v>
+        <v>622</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>292</v>
+        <v>795</v>
       </c>
       <c r="B546" t="s">
-        <v>627</v>
+        <v>796</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>8</v>
+        <v>267</v>
       </c>
       <c r="B547" t="s">
-        <v>11</v>
+        <v>623</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>335</v>
+        <v>661</v>
       </c>
       <c r="B548" t="s">
-        <v>628</v>
+        <v>744</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>332</v>
+        <v>662</v>
       </c>
       <c r="B549" t="s">
-        <v>629</v>
+        <v>745</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>259</v>
+        <v>139</v>
       </c>
       <c r="B550" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>319</v>
+        <v>7</v>
       </c>
       <c r="B551" t="s">
-        <v>631</v>
+        <v>2</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>860</v>
+        <v>105</v>
       </c>
       <c r="B552" t="s">
-        <v>861</v>
+        <v>625</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>268</v>
+        <v>1034</v>
       </c>
       <c r="B553" t="s">
-        <v>632</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>271</v>
+        <v>865</v>
       </c>
       <c r="B554" t="s">
-        <v>1118</v>
+        <v>866</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>274</v>
+        <v>1035</v>
       </c>
       <c r="B555" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="B556" t="s">
-        <v>1120</v>
+        <v>626</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>273</v>
+        <v>8</v>
       </c>
       <c r="B557" t="s">
-        <v>1121</v>
+        <v>11</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>269</v>
+        <v>335</v>
       </c>
       <c r="B558" t="s">
-        <v>1122</v>
+        <v>627</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>272</v>
+        <v>332</v>
       </c>
       <c r="B559" t="s">
-        <v>1117</v>
+        <v>628</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>92</v>
+        <v>259</v>
       </c>
       <c r="B560" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>200</v>
+        <v>319</v>
       </c>
       <c r="B561" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>203</v>
+        <v>859</v>
       </c>
       <c r="B562" t="s">
-        <v>635</v>
+        <v>860</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>172</v>
+        <v>268</v>
       </c>
       <c r="B563" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>694</v>
+        <v>271</v>
       </c>
       <c r="B564" t="s">
-        <v>747</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="B565" t="s">
-        <v>637</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>695</v>
+        <v>270</v>
       </c>
       <c r="B566" t="s">
-        <v>748</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>189</v>
+        <v>273</v>
       </c>
       <c r="B567" t="s">
-        <v>638</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>990</v>
+        <v>269</v>
       </c>
       <c r="B568" t="s">
-        <v>991</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>311</v>
+        <v>272</v>
       </c>
       <c r="B569" t="s">
-        <v>639</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>312</v>
+        <v>92</v>
       </c>
       <c r="B570" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>1034</v>
+        <v>200</v>
       </c>
       <c r="B571" t="s">
-        <v>1116</v>
+        <v>633</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>1006</v>
+        <v>203</v>
       </c>
       <c r="B572" t="s">
-        <v>1007</v>
+        <v>634</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>81</v>
+        <v>172</v>
       </c>
       <c r="B573" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>652</v>
+        <v>693</v>
       </c>
       <c r="B574" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>923</v>
+        <v>252</v>
       </c>
       <c r="B575" t="s">
-        <v>924</v>
+        <v>636</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>643</v>
+        <v>694</v>
       </c>
       <c r="B576" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
+        <v>189</v>
+      </c>
+      <c r="B577" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A578" t="s">
+        <v>989</v>
+      </c>
+      <c r="B578" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A579" t="s">
+        <v>311</v>
+      </c>
+      <c r="B579" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A580" t="s">
+        <v>312</v>
+      </c>
+      <c r="B580" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A581" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B581" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A582" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B582" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A583" t="s">
+        <v>81</v>
+      </c>
+      <c r="B583" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A584" t="s">
+        <v>651</v>
+      </c>
+      <c r="B584" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A585" t="s">
+        <v>922</v>
+      </c>
+      <c r="B585" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A586" t="s">
+        <v>642</v>
+      </c>
+      <c r="B586" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A587" t="s">
+        <v>969</v>
+      </c>
+      <c r="B587" t="s">
         <v>970</v>
       </c>
-      <c r="B577" t="s">
-        <v>971</v>
+    </row>
+    <row r="588" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A588" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B588" t="s">
+        <v>1163</v>
       </c>
     </row>
   </sheetData>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15397DE8-B2F9-4228-8B59-E54937A47490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE61584-0E78-4394-842C-E20E24B646FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="1170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="1178">
   <si>
     <t>trigger</t>
   </si>
@@ -3535,6 +3535,30 @@
   </si>
   <si>
     <t>disc-osteophyte complex</t>
+  </si>
+  <si>
+    <t>sx</t>
+  </si>
+  <si>
+    <t>surgery</t>
+  </si>
+  <si>
+    <t>hx</t>
+  </si>
+  <si>
+    <t>history</t>
+  </si>
+  <si>
+    <t>tx</t>
+  </si>
+  <si>
+    <t>treatment</t>
+  </si>
+  <si>
+    <t>chemo</t>
+  </si>
+  <si>
+    <t>chemotherapy</t>
   </si>
 </sst>
 </file>
@@ -3590,10 +3614,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B588" totalsRowShown="0">
-  <autoFilter ref="A1:B588" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B588">
-    <sortCondition ref="A1:A588"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B592" totalsRowShown="0">
+  <autoFilter ref="A1:B592" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B592">
+    <sortCondition ref="A1:A592"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -3866,7 +3890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B588"/>
+  <dimension ref="A1:B592"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -4707,647 +4731,647 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>879</v>
+        <v>1176</v>
       </c>
       <c r="B105" t="s">
-        <v>880</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>807</v>
+        <v>879</v>
       </c>
       <c r="B106" t="s">
-        <v>808</v>
+        <v>880</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>152</v>
+        <v>807</v>
       </c>
       <c r="B107" t="s">
-        <v>394</v>
+        <v>808</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="B108" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B109" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="B110" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>967</v>
+        <v>155</v>
       </c>
       <c r="B111" t="s">
-        <v>968</v>
+        <v>397</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>84</v>
+        <v>967</v>
       </c>
       <c r="B112" t="s">
-        <v>398</v>
+        <v>968</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>965</v>
+        <v>84</v>
       </c>
       <c r="B113" t="s">
-        <v>966</v>
+        <v>398</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>103</v>
+        <v>965</v>
       </c>
       <c r="B114" t="s">
-        <v>399</v>
+        <v>966</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>198</v>
+        <v>103</v>
       </c>
       <c r="B115" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>314</v>
+        <v>198</v>
       </c>
       <c r="B116" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>104</v>
+        <v>314</v>
       </c>
       <c r="B117" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="B118" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="B119" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B120" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>1046</v>
+        <v>102</v>
       </c>
       <c r="B121" t="s">
-        <v>1047</v>
+        <v>405</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>930</v>
+        <v>1046</v>
       </c>
       <c r="B122" t="s">
-        <v>931</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B123" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>162</v>
+        <v>928</v>
       </c>
       <c r="B124" t="s">
-        <v>406</v>
+        <v>929</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>1153</v>
+        <v>162</v>
       </c>
       <c r="B125" t="s">
-        <v>1154</v>
+        <v>406</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>837</v>
+        <v>1153</v>
       </c>
       <c r="B126" t="s">
-        <v>838</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B127" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>1084</v>
+        <v>839</v>
       </c>
       <c r="B128" t="s">
-        <v>1085</v>
+        <v>840</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>665</v>
+        <v>1084</v>
       </c>
       <c r="B129" t="s">
-        <v>708</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>646</v>
+        <v>665</v>
       </c>
       <c r="B130" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>940</v>
+        <v>646</v>
       </c>
       <c r="B131" t="s">
-        <v>941</v>
+        <v>709</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>683</v>
+        <v>940</v>
       </c>
       <c r="B132" t="s">
-        <v>710</v>
+        <v>941</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B133" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B134" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="B135" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B136" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B137" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B138" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B139" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B140" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B141" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B142" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>175</v>
+        <v>682</v>
       </c>
       <c r="B143" t="s">
-        <v>407</v>
+        <v>720</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="B144" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B145" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>149</v>
+        <v>213</v>
       </c>
       <c r="B146" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>247</v>
+        <v>149</v>
       </c>
       <c r="B147" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B148" t="s">
-        <v>1138</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>336</v>
+        <v>245</v>
       </c>
       <c r="B149" t="s">
-        <v>412</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>650</v>
+        <v>336</v>
       </c>
       <c r="B150" t="s">
-        <v>721</v>
+        <v>412</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>91</v>
+        <v>650</v>
       </c>
       <c r="B151" t="s">
-        <v>413</v>
+        <v>721</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>266</v>
+        <v>91</v>
       </c>
       <c r="B152" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>1096</v>
+        <v>266</v>
       </c>
       <c r="B153" t="s">
-        <v>1097</v>
+        <v>414</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>799</v>
+        <v>1096</v>
       </c>
       <c r="B154" t="s">
-        <v>800</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>1168</v>
+        <v>799</v>
       </c>
       <c r="B155" t="s">
-        <v>1169</v>
+        <v>800</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>295</v>
+        <v>1168</v>
       </c>
       <c r="B156" t="s">
-        <v>415</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>1086</v>
+        <v>295</v>
       </c>
       <c r="B157" t="s">
-        <v>1087</v>
+        <v>415</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="B158" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>151</v>
+        <v>1092</v>
       </c>
       <c r="B159" t="s">
-        <v>416</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>961</v>
+        <v>151</v>
       </c>
       <c r="B160" t="s">
-        <v>962</v>
+        <v>416</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>813</v>
+        <v>961</v>
       </c>
       <c r="B161" t="s">
-        <v>814</v>
+        <v>962</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>932</v>
+        <v>813</v>
       </c>
       <c r="B162" t="s">
-        <v>933</v>
+        <v>814</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>833</v>
+        <v>932</v>
       </c>
       <c r="B163" t="s">
-        <v>834</v>
+        <v>933</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>793</v>
+        <v>833</v>
       </c>
       <c r="B164" t="s">
-        <v>794</v>
+        <v>834</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>754</v>
+        <v>793</v>
       </c>
       <c r="B165" t="s">
-        <v>755</v>
+        <v>794</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>100</v>
+        <v>754</v>
       </c>
       <c r="B166" t="s">
-        <v>417</v>
+        <v>755</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>1042</v>
+        <v>100</v>
       </c>
       <c r="B167" t="s">
-        <v>1043</v>
+        <v>417</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>154</v>
+        <v>1042</v>
       </c>
       <c r="B168" t="s">
-        <v>418</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B169" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="B170" t="s">
-        <v>1137</v>
+        <v>419</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>1164</v>
+        <v>24</v>
       </c>
       <c r="B171" t="s">
-        <v>1165</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>1076</v>
+        <v>1164</v>
       </c>
       <c r="B172" t="s">
-        <v>1077</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>819</v>
+        <v>1076</v>
       </c>
       <c r="B173" t="s">
-        <v>820</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>130</v>
+        <v>819</v>
       </c>
       <c r="B174" t="s">
-        <v>420</v>
+        <v>820</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>322</v>
+        <v>130</v>
       </c>
       <c r="B175" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>867</v>
+        <v>322</v>
       </c>
       <c r="B176" t="s">
-        <v>868</v>
+        <v>421</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>183</v>
+        <v>867</v>
       </c>
       <c r="B177" t="s">
-        <v>422</v>
+        <v>868</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>1155</v>
+        <v>183</v>
       </c>
       <c r="B178" t="s">
-        <v>1156</v>
+        <v>422</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="B179" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>891</v>
+        <v>1157</v>
       </c>
       <c r="B180" t="s">
-        <v>892</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>32</v>
+        <v>891</v>
       </c>
       <c r="B181" t="s">
-        <v>423</v>
+        <v>892</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B182" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>764</v>
+        <v>35</v>
       </c>
       <c r="B183" t="s">
-        <v>1010</v>
+        <v>424</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>169</v>
+        <v>764</v>
       </c>
       <c r="B184" t="s">
-        <v>425</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B185" t="s">
         <v>425</v>
@@ -5355,1463 +5379,1463 @@
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>1011</v>
+        <v>170</v>
       </c>
       <c r="B186" t="s">
-        <v>765</v>
+        <v>425</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>178</v>
+        <v>1011</v>
       </c>
       <c r="B187" t="s">
-        <v>426</v>
+        <v>765</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="B188" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>238</v>
+        <v>111</v>
       </c>
       <c r="B189" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="B190" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B191" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="B192" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>667</v>
+        <v>179</v>
       </c>
       <c r="B193" t="s">
-        <v>722</v>
+        <v>431</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>97</v>
+        <v>667</v>
       </c>
       <c r="B194" t="s">
-        <v>432</v>
+        <v>722</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B195" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>242</v>
+        <v>110</v>
       </c>
       <c r="B196" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B197" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="B198" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B199" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>1110</v>
+        <v>182</v>
       </c>
       <c r="B200" t="s">
-        <v>1111</v>
+        <v>437</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>977</v>
+        <v>1110</v>
       </c>
       <c r="B201" t="s">
-        <v>978</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="B202" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>253</v>
+        <v>979</v>
       </c>
       <c r="B203" t="s">
-        <v>438</v>
+        <v>980</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="B204" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>787</v>
+        <v>34</v>
       </c>
       <c r="B205" t="s">
-        <v>788</v>
+        <v>439</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>180</v>
+        <v>787</v>
       </c>
       <c r="B206" t="s">
-        <v>440</v>
+        <v>788</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>275</v>
+        <v>180</v>
       </c>
       <c r="B207" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>857</v>
+        <v>275</v>
       </c>
       <c r="B208" t="s">
-        <v>858</v>
+        <v>441</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>116</v>
+        <v>857</v>
       </c>
       <c r="B209" t="s">
-        <v>442</v>
+        <v>858</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>208</v>
+        <v>116</v>
       </c>
       <c r="B210" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>1056</v>
+        <v>208</v>
       </c>
       <c r="B211" t="s">
-        <v>1057</v>
+        <v>443</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>118</v>
+        <v>1056</v>
       </c>
       <c r="B212" t="s">
-        <v>444</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>641</v>
+        <v>118</v>
       </c>
       <c r="B213" t="s">
-        <v>723</v>
+        <v>444</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>815</v>
+        <v>641</v>
       </c>
       <c r="B214" t="s">
-        <v>816</v>
+        <v>723</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>298</v>
+        <v>815</v>
       </c>
       <c r="B215" t="s">
-        <v>445</v>
+        <v>816</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>643</v>
+        <v>298</v>
       </c>
       <c r="B216" t="s">
-        <v>724</v>
+        <v>445</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B217" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>1036</v>
+        <v>644</v>
       </c>
       <c r="B218" t="s">
-        <v>1037</v>
+        <v>725</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>90</v>
+        <v>1036</v>
       </c>
       <c r="B219" t="s">
-        <v>446</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B220" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B221" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>1072</v>
+        <v>89</v>
       </c>
       <c r="B222" t="s">
-        <v>1073</v>
+        <v>448</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>23</v>
+        <v>1072</v>
       </c>
       <c r="B223" t="s">
-        <v>1136</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B224" t="s">
-        <v>6</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>1141</v>
+        <v>5</v>
       </c>
       <c r="B225" t="s">
-        <v>1142</v>
+        <v>6</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>126</v>
+        <v>1141</v>
       </c>
       <c r="B226" t="s">
-        <v>449</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B227" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B228" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B229" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B230" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>277</v>
+        <v>119</v>
       </c>
       <c r="B231" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>1074</v>
+        <v>277</v>
       </c>
       <c r="B232" t="s">
-        <v>1075</v>
+        <v>454</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>9</v>
+        <v>1074</v>
       </c>
       <c r="B233" t="s">
-        <v>10</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="B234" t="s">
-        <v>455</v>
+        <v>10</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B235" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="B236" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="B237" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>77</v>
+        <v>262</v>
       </c>
       <c r="B238" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>938</v>
+        <v>77</v>
       </c>
       <c r="B239" t="s">
-        <v>939</v>
+        <v>459</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>168</v>
+        <v>938</v>
       </c>
       <c r="B240" t="s">
-        <v>460</v>
+        <v>939</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>167</v>
+        <v>1172</v>
       </c>
       <c r="B241" t="s">
-        <v>461</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>835</v>
+        <v>168</v>
       </c>
       <c r="B242" t="s">
-        <v>836</v>
+        <v>460</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>791</v>
+        <v>167</v>
       </c>
       <c r="B243" t="s">
-        <v>792</v>
+        <v>461</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>304</v>
+        <v>835</v>
       </c>
       <c r="B244" t="s">
-        <v>462</v>
+        <v>836</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>758</v>
+        <v>791</v>
       </c>
       <c r="B245" t="s">
-        <v>759</v>
+        <v>792</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>897</v>
+        <v>304</v>
       </c>
       <c r="B246" t="s">
-        <v>898</v>
+        <v>462</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>652</v>
+        <v>758</v>
       </c>
       <c r="B247" t="s">
-        <v>726</v>
+        <v>759</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>86</v>
+        <v>897</v>
       </c>
       <c r="B248" t="s">
-        <v>463</v>
+        <v>898</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>87</v>
+        <v>652</v>
       </c>
       <c r="B249" t="s">
-        <v>464</v>
+        <v>726</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>153</v>
+        <v>86</v>
       </c>
       <c r="B250" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>156</v>
+        <v>87</v>
       </c>
       <c r="B251" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B252" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>251</v>
+        <v>156</v>
       </c>
       <c r="B253" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>285</v>
+        <v>158</v>
       </c>
       <c r="B254" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>326</v>
+        <v>251</v>
       </c>
       <c r="B255" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>327</v>
+        <v>285</v>
       </c>
       <c r="B256" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>229</v>
+        <v>326</v>
       </c>
       <c r="B257" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>55</v>
+        <v>327</v>
       </c>
       <c r="B258" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>657</v>
+        <v>229</v>
       </c>
       <c r="B259" t="s">
-        <v>727</v>
+        <v>472</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>235</v>
+        <v>55</v>
       </c>
       <c r="B260" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>57</v>
+        <v>657</v>
       </c>
       <c r="B261" t="s">
-        <v>475</v>
+        <v>727</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B262" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>766</v>
+        <v>57</v>
       </c>
       <c r="B263" t="s">
-        <v>1009</v>
+        <v>475</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>1012</v>
+        <v>236</v>
       </c>
       <c r="B264" t="s">
-        <v>767</v>
+        <v>476</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>164</v>
+        <v>766</v>
       </c>
       <c r="B265" t="s">
-        <v>477</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>201</v>
+        <v>1012</v>
       </c>
       <c r="B266" t="s">
-        <v>478</v>
+        <v>767</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>204</v>
+        <v>164</v>
       </c>
       <c r="B267" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>313</v>
+        <v>201</v>
       </c>
       <c r="B268" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>873</v>
+        <v>204</v>
       </c>
       <c r="B269" t="s">
-        <v>874</v>
+        <v>479</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>997</v>
+        <v>313</v>
       </c>
       <c r="B270" t="s">
-        <v>998</v>
+        <v>480</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>258</v>
+        <v>873</v>
       </c>
       <c r="B271" t="s">
-        <v>481</v>
+        <v>874</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>983</v>
+        <v>997</v>
       </c>
       <c r="B272" t="s">
-        <v>984</v>
+        <v>998</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>160</v>
+        <v>258</v>
       </c>
       <c r="B273" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>692</v>
+        <v>983</v>
       </c>
       <c r="B274" t="s">
-        <v>728</v>
+        <v>984</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>1166</v>
+        <v>160</v>
       </c>
       <c r="B275" t="s">
-        <v>1167</v>
+        <v>482</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>760</v>
+        <v>692</v>
       </c>
       <c r="B276" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>895</v>
+        <v>1166</v>
       </c>
       <c r="B277" t="s">
-        <v>896</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>893</v>
+        <v>760</v>
       </c>
       <c r="B278" t="s">
-        <v>894</v>
+        <v>761</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>184</v>
+        <v>895</v>
       </c>
       <c r="B279" t="s">
-        <v>483</v>
+        <v>896</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>244</v>
+        <v>893</v>
       </c>
       <c r="B280" t="s">
-        <v>484</v>
+        <v>894</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>243</v>
+        <v>184</v>
       </c>
       <c r="B281" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>686</v>
+        <v>244</v>
       </c>
       <c r="B282" t="s">
-        <v>729</v>
+        <v>484</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>687</v>
+        <v>243</v>
       </c>
       <c r="B283" t="s">
-        <v>730</v>
+        <v>485</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B284" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B285" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B286" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>280</v>
+        <v>689</v>
       </c>
       <c r="B287" t="s">
-        <v>486</v>
+        <v>732</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>281</v>
+        <v>690</v>
       </c>
       <c r="B288" t="s">
-        <v>487</v>
+        <v>733</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>49</v>
+        <v>280</v>
       </c>
       <c r="B289" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>53</v>
+        <v>281</v>
       </c>
       <c r="B290" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="B291" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="B292" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>221</v>
+        <v>136</v>
       </c>
       <c r="B293" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="B294" t="s">
-        <v>16</v>
+        <v>490</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>1060</v>
+        <v>221</v>
       </c>
       <c r="B295" t="s">
-        <v>1061</v>
+        <v>492</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>920</v>
+        <v>15</v>
       </c>
       <c r="B296" t="s">
-        <v>921</v>
+        <v>16</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>108</v>
+        <v>1060</v>
       </c>
       <c r="B297" t="s">
-        <v>493</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>241</v>
+        <v>920</v>
       </c>
       <c r="B298" t="s">
-        <v>494</v>
+        <v>921</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>328</v>
+        <v>108</v>
       </c>
       <c r="B299" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>1100</v>
+        <v>241</v>
       </c>
       <c r="B300" t="s">
-        <v>1101</v>
+        <v>494</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>1052</v>
+        <v>328</v>
       </c>
       <c r="B301" t="s">
-        <v>1053</v>
+        <v>495</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>121</v>
+        <v>1100</v>
       </c>
       <c r="B302" t="s">
-        <v>496</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>750</v>
+        <v>1052</v>
       </c>
       <c r="B303" t="s">
-        <v>751</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>781</v>
+        <v>121</v>
       </c>
       <c r="B304" t="s">
-        <v>782</v>
+        <v>496</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>134</v>
+        <v>750</v>
       </c>
       <c r="B305" t="s">
-        <v>497</v>
+        <v>751</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>63</v>
+        <v>781</v>
       </c>
       <c r="B306" t="s">
-        <v>498</v>
+        <v>782</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>224</v>
+        <v>134</v>
       </c>
       <c r="B307" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="B308" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>26</v>
+        <v>224</v>
       </c>
       <c r="B309" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>207</v>
+        <v>25</v>
       </c>
       <c r="B310" t="s">
-        <v>1133</v>
+        <v>500</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>960</v>
+        <v>26</v>
       </c>
       <c r="B311" t="s">
-        <v>1134</v>
+        <v>501</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>1113</v>
+        <v>207</v>
       </c>
       <c r="B312" t="s">
-        <v>1114</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>206</v>
+        <v>960</v>
       </c>
       <c r="B313" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>202</v>
+        <v>1113</v>
       </c>
       <c r="B314" t="s">
-        <v>502</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B315" t="s">
-        <v>503</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>145</v>
+        <v>202</v>
       </c>
       <c r="B316" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>663</v>
+        <v>205</v>
       </c>
       <c r="B317" t="s">
-        <v>734</v>
+        <v>503</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="B318" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>1088</v>
+        <v>663</v>
       </c>
       <c r="B319" t="s">
-        <v>1089</v>
+        <v>734</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>263</v>
+        <v>171</v>
       </c>
       <c r="B320" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="B321" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="B322" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>65</v>
+        <v>1090</v>
       </c>
       <c r="B323" t="s">
-        <v>508</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>191</v>
+        <v>80</v>
       </c>
       <c r="B324" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>123</v>
+        <v>65</v>
       </c>
       <c r="B325" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B326" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>231</v>
+        <v>123</v>
       </c>
       <c r="B327" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>233</v>
+        <v>192</v>
       </c>
       <c r="B328" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>31</v>
+        <v>231</v>
       </c>
       <c r="B329" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>30</v>
+        <v>233</v>
       </c>
       <c r="B330" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B331" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="B332" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>306</v>
+        <v>37</v>
       </c>
       <c r="B333" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>222</v>
+        <v>71</v>
       </c>
       <c r="B334" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="B335" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>278</v>
+        <v>222</v>
       </c>
       <c r="B336" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>279</v>
+        <v>315</v>
       </c>
       <c r="B337" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>831</v>
+        <v>278</v>
       </c>
       <c r="B338" t="s">
-        <v>832</v>
+        <v>521</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>48</v>
+        <v>279</v>
       </c>
       <c r="B339" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>146</v>
+        <v>831</v>
       </c>
       <c r="B340" t="s">
-        <v>524</v>
+        <v>832</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B341" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>223</v>
+        <v>146</v>
       </c>
       <c r="B342" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>1094</v>
+        <v>52</v>
       </c>
       <c r="B343" t="s">
-        <v>1095</v>
+        <v>525</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>1109</v>
+        <v>223</v>
       </c>
       <c r="B344" t="s">
-        <v>1112</v>
+        <v>526</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>1050</v>
+        <v>1094</v>
       </c>
       <c r="B345" t="s">
-        <v>1051</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>96</v>
+        <v>1109</v>
       </c>
       <c r="B346" t="s">
-        <v>527</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>248</v>
+        <v>1050</v>
       </c>
       <c r="B347" t="s">
-        <v>528</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>249</v>
+        <v>96</v>
       </c>
       <c r="B348" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>94</v>
+        <v>248</v>
       </c>
       <c r="B349" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>1064</v>
+        <v>249</v>
       </c>
       <c r="B350" t="s">
-        <v>1065</v>
+        <v>529</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>212</v>
+        <v>94</v>
       </c>
       <c r="B351" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>916</v>
+        <v>1064</v>
       </c>
       <c r="B352" t="s">
-        <v>917</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>914</v>
+        <v>212</v>
       </c>
       <c r="B353" t="s">
-        <v>915</v>
+        <v>531</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B354" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>330</v>
+        <v>914</v>
       </c>
       <c r="B355" t="s">
-        <v>532</v>
+        <v>915</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>1066</v>
+        <v>918</v>
       </c>
       <c r="B356" t="s">
-        <v>1067</v>
+        <v>919</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>995</v>
+        <v>330</v>
       </c>
       <c r="B357" t="s">
-        <v>996</v>
+        <v>532</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>991</v>
+        <v>1066</v>
       </c>
       <c r="B358" t="s">
-        <v>992</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="B359" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>82</v>
+        <v>991</v>
       </c>
       <c r="B360" t="s">
-        <v>533</v>
+        <v>992</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>772</v>
+        <v>993</v>
       </c>
       <c r="B361" t="s">
-        <v>773</v>
+        <v>994</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="B362" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>654</v>
+        <v>772</v>
       </c>
       <c r="B363" t="s">
-        <v>735</v>
+        <v>773</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>821</v>
+        <v>197</v>
       </c>
       <c r="B364" t="s">
-        <v>822</v>
+        <v>534</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>1068</v>
+        <v>654</v>
       </c>
       <c r="B365" t="s">
-        <v>1069</v>
+        <v>735</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>3</v>
+        <v>821</v>
       </c>
       <c r="B366" t="s">
-        <v>4</v>
+        <v>822</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>958</v>
+        <v>1068</v>
       </c>
       <c r="B367" t="s">
-        <v>4</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>959</v>
+        <v>3</v>
       </c>
       <c r="B368" t="s">
         <v>4</v>
@@ -6819,1761 +6843,1793 @@
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>664</v>
+        <v>958</v>
       </c>
       <c r="B369" t="s">
-        <v>736</v>
+        <v>4</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>770</v>
+        <v>959</v>
       </c>
       <c r="B370" t="s">
-        <v>771</v>
+        <v>4</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>85</v>
+        <v>664</v>
       </c>
       <c r="B371" t="s">
-        <v>535</v>
+        <v>736</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>1062</v>
+        <v>770</v>
       </c>
       <c r="B372" t="s">
-        <v>1063</v>
+        <v>771</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>829</v>
+        <v>85</v>
       </c>
       <c r="B373" t="s">
-        <v>830</v>
+        <v>535</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>809</v>
+        <v>1062</v>
       </c>
       <c r="B374" t="s">
-        <v>810</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>187</v>
+        <v>829</v>
       </c>
       <c r="B375" t="s">
-        <v>536</v>
+        <v>830</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>827</v>
+        <v>809</v>
       </c>
       <c r="B376" t="s">
-        <v>828</v>
+        <v>810</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>934</v>
+        <v>187</v>
       </c>
       <c r="B377" t="s">
-        <v>1130</v>
+        <v>536</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>863</v>
+        <v>827</v>
       </c>
       <c r="B378" t="s">
-        <v>864</v>
+        <v>828</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>1044</v>
+        <v>934</v>
       </c>
       <c r="B379" t="s">
-        <v>1045</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>798</v>
+        <v>863</v>
       </c>
       <c r="B380" t="s">
-        <v>1131</v>
+        <v>864</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>797</v>
+        <v>1044</v>
       </c>
       <c r="B381" t="s">
-        <v>1132</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>13</v>
+        <v>798</v>
       </c>
       <c r="B382" t="s">
-        <v>14</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>817</v>
+        <v>797</v>
       </c>
       <c r="B383" t="s">
-        <v>818</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>186</v>
+        <v>13</v>
       </c>
       <c r="B384" t="s">
-        <v>537</v>
+        <v>14</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="B385" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>320</v>
+        <v>186</v>
       </c>
       <c r="B386" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>656</v>
+        <v>811</v>
       </c>
       <c r="B387" t="s">
-        <v>737</v>
+        <v>812</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>855</v>
+        <v>320</v>
       </c>
       <c r="B388" t="s">
-        <v>856</v>
+        <v>538</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B389" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>653</v>
+        <v>855</v>
       </c>
       <c r="B390" t="s">
-        <v>739</v>
+        <v>856</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>256</v>
+        <v>658</v>
       </c>
       <c r="B391" t="s">
-        <v>539</v>
+        <v>738</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>260</v>
+        <v>653</v>
       </c>
       <c r="B392" t="s">
-        <v>540</v>
+        <v>739</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B393" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>188</v>
+        <v>260</v>
       </c>
       <c r="B394" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>190</v>
+        <v>261</v>
       </c>
       <c r="B395" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>936</v>
+        <v>188</v>
       </c>
       <c r="B396" t="s">
-        <v>937</v>
+        <v>542</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>1031</v>
+        <v>190</v>
       </c>
       <c r="B397" t="s">
-        <v>1032</v>
+        <v>543</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>209</v>
+        <v>936</v>
       </c>
       <c r="B398" t="s">
-        <v>544</v>
+        <v>937</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>851</v>
+        <v>1031</v>
       </c>
       <c r="B399" t="s">
-        <v>852</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>143</v>
+        <v>209</v>
       </c>
       <c r="B400" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>140</v>
+        <v>851</v>
       </c>
       <c r="B401" t="s">
-        <v>546</v>
+        <v>852</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>254</v>
+        <v>143</v>
       </c>
       <c r="B402" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>331</v>
+        <v>140</v>
       </c>
       <c r="B403" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>210</v>
+        <v>254</v>
       </c>
       <c r="B404" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>234</v>
+        <v>331</v>
       </c>
       <c r="B405" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>73</v>
+        <v>210</v>
       </c>
       <c r="B406" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>342</v>
+        <v>234</v>
       </c>
       <c r="B407" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>308</v>
+        <v>73</v>
       </c>
       <c r="B408" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>843</v>
+        <v>342</v>
       </c>
       <c r="B409" t="s">
-        <v>844</v>
+        <v>552</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>845</v>
+        <v>308</v>
       </c>
       <c r="B410" t="s">
-        <v>846</v>
+        <v>553</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>220</v>
+        <v>843</v>
       </c>
       <c r="B411" t="s">
-        <v>554</v>
+        <v>844</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>909</v>
+        <v>845</v>
       </c>
       <c r="B412" t="s">
-        <v>910</v>
+        <v>846</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>963</v>
+        <v>220</v>
       </c>
       <c r="B413" t="s">
-        <v>964</v>
+        <v>554</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>227</v>
+        <v>909</v>
       </c>
       <c r="B414" t="s">
-        <v>555</v>
+        <v>910</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>334</v>
+        <v>963</v>
       </c>
       <c r="B415" t="s">
-        <v>1161</v>
+        <v>964</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>971</v>
+        <v>227</v>
       </c>
       <c r="B416" t="s">
-        <v>972</v>
+        <v>555</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>778</v>
+        <v>334</v>
       </c>
       <c r="B417" t="s">
-        <v>779</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>294</v>
+        <v>971</v>
       </c>
       <c r="B418" t="s">
-        <v>556</v>
+        <v>972</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>952</v>
+        <v>778</v>
       </c>
       <c r="B419" t="s">
-        <v>953</v>
+        <v>779</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>339</v>
+        <v>294</v>
       </c>
       <c r="B420" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>780</v>
+        <v>952</v>
       </c>
       <c r="B421" t="s">
-        <v>779</v>
+        <v>953</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B422" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>341</v>
+        <v>780</v>
       </c>
       <c r="B423" t="s">
-        <v>559</v>
+        <v>779</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>645</v>
+        <v>340</v>
       </c>
       <c r="B424" t="s">
-        <v>740</v>
+        <v>558</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>39</v>
+        <v>341</v>
       </c>
       <c r="B425" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>38</v>
+        <v>645</v>
       </c>
       <c r="B426" t="s">
-        <v>1129</v>
+        <v>740</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>343</v>
+        <v>39</v>
       </c>
       <c r="B427" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="B428" t="s">
-        <v>562</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>1029</v>
+        <v>343</v>
       </c>
       <c r="B429" t="s">
-        <v>1030</v>
+        <v>561</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>903</v>
+        <v>107</v>
       </c>
       <c r="B430" t="s">
-        <v>904</v>
+        <v>562</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>117</v>
+        <v>1029</v>
       </c>
       <c r="B431" t="s">
-        <v>563</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>1025</v>
+        <v>903</v>
       </c>
       <c r="B432" t="s">
-        <v>1026</v>
+        <v>904</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="B433" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>99</v>
+        <v>1025</v>
       </c>
       <c r="B434" t="s">
-        <v>565</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>666</v>
+        <v>98</v>
       </c>
       <c r="B435" t="s">
-        <v>741</v>
+        <v>564</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>1107</v>
+        <v>99</v>
       </c>
       <c r="B436" t="s">
-        <v>1024</v>
+        <v>565</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>823</v>
+        <v>666</v>
       </c>
       <c r="B437" t="s">
-        <v>824</v>
+        <v>741</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>113</v>
+        <v>1107</v>
       </c>
       <c r="B438" t="s">
-        <v>566</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>889</v>
+        <v>823</v>
       </c>
       <c r="B439" t="s">
-        <v>890</v>
+        <v>824</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="B440" t="s">
-        <v>1128</v>
+        <v>566</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>290</v>
+        <v>889</v>
       </c>
       <c r="B441" t="s">
-        <v>567</v>
+        <v>890</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>299</v>
+        <v>45</v>
       </c>
       <c r="B442" t="s">
-        <v>568</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>47</v>
+        <v>290</v>
       </c>
       <c r="B443" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>847</v>
+        <v>299</v>
       </c>
       <c r="B444" t="s">
-        <v>848</v>
+        <v>568</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B445" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>871</v>
+        <v>847</v>
       </c>
       <c r="B446" t="s">
-        <v>872</v>
+        <v>848</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="B447" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>853</v>
+        <v>871</v>
       </c>
       <c r="B448" t="s">
-        <v>854</v>
+        <v>872</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="B449" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>1080</v>
+        <v>853</v>
       </c>
       <c r="B450" t="s">
-        <v>1081</v>
+        <v>854</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="B451" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>316</v>
+        <v>1080</v>
       </c>
       <c r="B452" t="s">
-        <v>574</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>29</v>
+        <v>176</v>
       </c>
       <c r="B453" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>1104</v>
+        <v>316</v>
       </c>
       <c r="B454" t="s">
-        <v>1105</v>
+        <v>574</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>1018</v>
+        <v>29</v>
       </c>
       <c r="B455" t="s">
-        <v>1019</v>
+        <v>575</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>293</v>
+        <v>1104</v>
       </c>
       <c r="B456" t="s">
-        <v>576</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>981</v>
+        <v>1018</v>
       </c>
       <c r="B457" t="s">
-        <v>982</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B458" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>1003</v>
+        <v>981</v>
       </c>
       <c r="B459" t="s">
-        <v>1004</v>
+        <v>982</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>1007</v>
+        <v>301</v>
       </c>
       <c r="B460" t="s">
-        <v>1008</v>
+        <v>577</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>75</v>
+        <v>1003</v>
       </c>
       <c r="B461" t="s">
-        <v>578</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>76</v>
+        <v>1007</v>
       </c>
       <c r="B462" t="s">
-        <v>579</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B463" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>329</v>
+        <v>76</v>
       </c>
       <c r="B464" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>752</v>
+        <v>78</v>
       </c>
       <c r="B465" t="s">
-        <v>753</v>
+        <v>580</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>805</v>
+        <v>329</v>
       </c>
       <c r="B466" t="s">
-        <v>806</v>
+        <v>581</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>135</v>
+        <v>752</v>
       </c>
       <c r="B467" t="s">
-        <v>582</v>
+        <v>753</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>1038</v>
+        <v>805</v>
       </c>
       <c r="B468" t="s">
-        <v>1039</v>
+        <v>806</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>215</v>
+        <v>135</v>
       </c>
       <c r="B469" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>935</v>
+        <v>1038</v>
       </c>
       <c r="B470" t="s">
-        <v>1145</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B471" t="s">
-        <v>1126</v>
+        <v>583</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>317</v>
+        <v>935</v>
       </c>
       <c r="B472" t="s">
-        <v>584</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>1082</v>
+        <v>216</v>
       </c>
       <c r="B473" t="s">
-        <v>1083</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>214</v>
+        <v>317</v>
       </c>
       <c r="B474" t="s">
-        <v>1127</v>
+        <v>584</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>999</v>
+        <v>1082</v>
       </c>
       <c r="B475" t="s">
-        <v>1000</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>1001</v>
+        <v>214</v>
       </c>
       <c r="B476" t="s">
-        <v>1002</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>225</v>
+        <v>999</v>
       </c>
       <c r="B477" t="s">
-        <v>585</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>948</v>
+        <v>1001</v>
       </c>
       <c r="B478" t="s">
-        <v>949</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>1098</v>
+        <v>225</v>
       </c>
       <c r="B479" t="s">
-        <v>1099</v>
+        <v>585</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>1048</v>
+        <v>948</v>
       </c>
       <c r="B480" t="s">
-        <v>1049</v>
+        <v>949</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>93</v>
+        <v>1098</v>
       </c>
       <c r="B481" t="s">
-        <v>586</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>120</v>
+        <v>1048</v>
       </c>
       <c r="B482" t="s">
-        <v>587</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>783</v>
+        <v>93</v>
       </c>
       <c r="B483" t="s">
-        <v>784</v>
+        <v>586</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="B484" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>62</v>
+        <v>783</v>
       </c>
       <c r="B485" t="s">
-        <v>589</v>
+        <v>784</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="B486" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>825</v>
+        <v>62</v>
       </c>
       <c r="B487" t="s">
-        <v>826</v>
+        <v>589</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>950</v>
+        <v>66</v>
       </c>
       <c r="B488" t="s">
-        <v>951</v>
+        <v>590</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>79</v>
+        <v>825</v>
       </c>
       <c r="B489" t="s">
-        <v>591</v>
+        <v>826</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>64</v>
+        <v>950</v>
       </c>
       <c r="B490" t="s">
-        <v>592</v>
+        <v>951</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="B491" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>181</v>
+        <v>64</v>
       </c>
       <c r="B492" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>801</v>
+        <v>122</v>
       </c>
       <c r="B493" t="s">
-        <v>802</v>
+        <v>593</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>691</v>
+        <v>181</v>
       </c>
       <c r="B494" t="s">
-        <v>742</v>
+        <v>594</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>1151</v>
+        <v>801</v>
       </c>
       <c r="B495" t="s">
-        <v>1152</v>
+        <v>802</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>1149</v>
+        <v>691</v>
       </c>
       <c r="B496" t="s">
-        <v>1150</v>
+        <v>742</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>284</v>
+        <v>1151</v>
       </c>
       <c r="B497" t="s">
-        <v>595</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>973</v>
+        <v>1149</v>
       </c>
       <c r="B498" t="s">
-        <v>974</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>841</v>
+        <v>284</v>
       </c>
       <c r="B499" t="s">
-        <v>842</v>
+        <v>595</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>283</v>
+        <v>973</v>
       </c>
       <c r="B500" t="s">
-        <v>596</v>
+        <v>974</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>883</v>
+        <v>841</v>
       </c>
       <c r="B501" t="s">
-        <v>884</v>
+        <v>842</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>756</v>
+        <v>283</v>
       </c>
       <c r="B502" t="s">
-        <v>757</v>
+        <v>596</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>1078</v>
+        <v>883</v>
       </c>
       <c r="B503" t="s">
-        <v>1079</v>
+        <v>884</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>67</v>
+        <v>756</v>
       </c>
       <c r="B504" t="s">
-        <v>597</v>
+        <v>757</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>68</v>
+        <v>1078</v>
       </c>
       <c r="B505" t="s">
-        <v>598</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="B506" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>289</v>
+        <v>68</v>
       </c>
       <c r="B507" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>297</v>
+        <v>95</v>
       </c>
       <c r="B508" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="B509" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>193</v>
+        <v>297</v>
       </c>
       <c r="B510" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>901</v>
+        <v>264</v>
       </c>
       <c r="B511" t="s">
-        <v>902</v>
+        <v>602</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>44</v>
+        <v>193</v>
       </c>
       <c r="B512" t="s">
-        <v>1125</v>
+        <v>603</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>1070</v>
+        <v>901</v>
       </c>
       <c r="B513" t="s">
-        <v>1071</v>
+        <v>902</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>324</v>
+        <v>44</v>
       </c>
       <c r="B514" t="s">
-        <v>604</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>325</v>
+        <v>1070</v>
       </c>
       <c r="B515" t="s">
-        <v>605</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>849</v>
+        <v>324</v>
       </c>
       <c r="B516" t="s">
-        <v>850</v>
+        <v>604</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>887</v>
+        <v>325</v>
       </c>
       <c r="B517" t="s">
-        <v>888</v>
+        <v>605</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>869</v>
+        <v>849</v>
       </c>
       <c r="B518" t="s">
-        <v>870</v>
+        <v>850</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>33</v>
+        <v>887</v>
       </c>
       <c r="B519" t="s">
-        <v>606</v>
+        <v>888</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>36</v>
+        <v>869</v>
       </c>
       <c r="B520" t="s">
-        <v>607</v>
+        <v>870</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>1143</v>
+        <v>33</v>
       </c>
       <c r="B521" t="s">
-        <v>1144</v>
+        <v>606</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>309</v>
+        <v>36</v>
       </c>
       <c r="B522" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>257</v>
+        <v>1143</v>
       </c>
       <c r="B523" t="s">
-        <v>609</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B524" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>228</v>
+        <v>257</v>
       </c>
       <c r="B525" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>17</v>
+        <v>302</v>
       </c>
       <c r="B526" t="s">
-        <v>18</v>
+        <v>610</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>655</v>
+        <v>228</v>
       </c>
       <c r="B527" t="s">
-        <v>743</v>
+        <v>611</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>785</v>
+        <v>17</v>
       </c>
       <c r="B528" t="s">
-        <v>786</v>
+        <v>18</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>142</v>
+        <v>655</v>
       </c>
       <c r="B529" t="s">
-        <v>612</v>
+        <v>743</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>956</v>
+        <v>785</v>
       </c>
       <c r="B530" t="s">
-        <v>957</v>
+        <v>786</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
       <c r="B531" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>265</v>
+        <v>956</v>
       </c>
       <c r="B532" t="s">
-        <v>614</v>
+        <v>957</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>976</v>
+        <v>54</v>
       </c>
       <c r="B533" t="s">
-        <v>975</v>
+        <v>613</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>56</v>
+        <v>265</v>
       </c>
       <c r="B534" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>185</v>
+        <v>976</v>
       </c>
       <c r="B535" t="s">
-        <v>616</v>
+        <v>975</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="B536" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>43</v>
+        <v>185</v>
       </c>
       <c r="B537" t="s">
-        <v>1146</v>
+        <v>616</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>40</v>
+        <v>159</v>
       </c>
       <c r="B538" t="s">
-        <v>1124</v>
+        <v>617</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>165</v>
+        <v>43</v>
       </c>
       <c r="B539" t="s">
-        <v>618</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="B540" t="s">
-        <v>11</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>250</v>
+        <v>1170</v>
       </c>
       <c r="B541" t="s">
-        <v>619</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>27</v>
+        <v>165</v>
       </c>
       <c r="B542" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>1040</v>
+        <v>12</v>
       </c>
       <c r="B543" t="s">
-        <v>1041</v>
+        <v>11</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>28</v>
+        <v>250</v>
       </c>
       <c r="B544" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>255</v>
+        <v>27</v>
       </c>
       <c r="B545" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>795</v>
+        <v>1040</v>
       </c>
       <c r="B546" t="s">
-        <v>796</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>267</v>
+        <v>28</v>
       </c>
       <c r="B547" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>661</v>
+        <v>255</v>
       </c>
       <c r="B548" t="s">
-        <v>744</v>
+        <v>622</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>662</v>
+        <v>795</v>
       </c>
       <c r="B549" t="s">
-        <v>745</v>
+        <v>796</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>139</v>
+        <v>267</v>
       </c>
       <c r="B550" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>7</v>
+        <v>661</v>
       </c>
       <c r="B551" t="s">
-        <v>2</v>
+        <v>744</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>105</v>
+        <v>662</v>
       </c>
       <c r="B552" t="s">
-        <v>625</v>
+        <v>745</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>1034</v>
+        <v>139</v>
       </c>
       <c r="B553" t="s">
-        <v>1123</v>
+        <v>624</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>865</v>
+        <v>7</v>
       </c>
       <c r="B554" t="s">
-        <v>866</v>
+        <v>2</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>1035</v>
+        <v>105</v>
       </c>
       <c r="B555" t="s">
-        <v>1122</v>
+        <v>625</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>292</v>
+        <v>1034</v>
       </c>
       <c r="B556" t="s">
-        <v>626</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>8</v>
+        <v>865</v>
       </c>
       <c r="B557" t="s">
-        <v>11</v>
+        <v>866</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>335</v>
+        <v>1035</v>
       </c>
       <c r="B558" t="s">
-        <v>627</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>332</v>
+        <v>292</v>
       </c>
       <c r="B559" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>259</v>
+        <v>8</v>
       </c>
       <c r="B560" t="s">
-        <v>629</v>
+        <v>11</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="B561" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>859</v>
+        <v>332</v>
       </c>
       <c r="B562" t="s">
-        <v>860</v>
+        <v>628</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="B563" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>271</v>
+        <v>319</v>
       </c>
       <c r="B564" t="s">
-        <v>1117</v>
+        <v>630</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>274</v>
+        <v>859</v>
       </c>
       <c r="B565" t="s">
-        <v>1118</v>
+        <v>860</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>270</v>
+        <v>1174</v>
       </c>
       <c r="B566" t="s">
-        <v>1119</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B567" t="s">
-        <v>1120</v>
+        <v>631</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B568" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B569" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>92</v>
+        <v>270</v>
       </c>
       <c r="B570" t="s">
-        <v>632</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>200</v>
+        <v>273</v>
       </c>
       <c r="B571" t="s">
-        <v>633</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>203</v>
+        <v>269</v>
       </c>
       <c r="B572" t="s">
-        <v>634</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>172</v>
+        <v>272</v>
       </c>
       <c r="B573" t="s">
-        <v>635</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>693</v>
+        <v>92</v>
       </c>
       <c r="B574" t="s">
-        <v>746</v>
+        <v>632</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>252</v>
+        <v>200</v>
       </c>
       <c r="B575" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>694</v>
+        <v>203</v>
       </c>
       <c r="B576" t="s">
-        <v>747</v>
+        <v>634</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="B577" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>989</v>
+        <v>693</v>
       </c>
       <c r="B578" t="s">
-        <v>990</v>
+        <v>746</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>311</v>
+        <v>252</v>
       </c>
       <c r="B579" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>312</v>
+        <v>694</v>
       </c>
       <c r="B580" t="s">
-        <v>639</v>
+        <v>747</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>1033</v>
+        <v>189</v>
       </c>
       <c r="B581" t="s">
-        <v>1115</v>
+        <v>637</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>1005</v>
+        <v>989</v>
       </c>
       <c r="B582" t="s">
-        <v>1006</v>
+        <v>990</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>81</v>
+        <v>311</v>
       </c>
       <c r="B583" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>651</v>
+        <v>312</v>
       </c>
       <c r="B584" t="s">
-        <v>748</v>
+        <v>639</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>922</v>
+        <v>1033</v>
       </c>
       <c r="B585" t="s">
-        <v>923</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>642</v>
+        <v>1005</v>
       </c>
       <c r="B586" t="s">
-        <v>749</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>969</v>
+        <v>81</v>
       </c>
       <c r="B587" t="s">
-        <v>970</v>
+        <v>640</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
+        <v>651</v>
+      </c>
+      <c r="B588" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A589" t="s">
+        <v>922</v>
+      </c>
+      <c r="B589" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A590" t="s">
+        <v>642</v>
+      </c>
+      <c r="B590" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A591" t="s">
+        <v>969</v>
+      </c>
+      <c r="B591" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A592" t="s">
         <v>1162</v>
       </c>
-      <c r="B588" t="s">
+      <c r="B592" t="s">
         <v>1163</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE61584-0E78-4394-842C-E20E24B646FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B6C1AB-09BF-422C-99D4-4C031127E77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="1178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="1180">
   <si>
     <t>trigger</t>
   </si>
@@ -3559,6 +3559,12 @@
   </si>
   <si>
     <t>chemotherapy</t>
+  </si>
+  <si>
+    <t>subcm</t>
+  </si>
+  <si>
+    <t>subcentimetric</t>
   </si>
 </sst>
 </file>
@@ -3614,10 +3620,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B592" totalsRowShown="0">
-  <autoFilter ref="A1:B592" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B592">
-    <sortCondition ref="A1:A592"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B593" totalsRowShown="0">
+  <autoFilter ref="A1:B593" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B593">
+    <sortCondition ref="A1:A593"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -3890,7 +3896,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B592"/>
+  <dimension ref="A1:B593"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -8147,489 +8153,497 @@
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>956</v>
+        <v>1178</v>
       </c>
       <c r="B532" t="s">
-        <v>957</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>54</v>
+        <v>956</v>
       </c>
       <c r="B533" t="s">
-        <v>613</v>
+        <v>957</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>265</v>
+        <v>54</v>
       </c>
       <c r="B534" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>976</v>
+        <v>265</v>
       </c>
       <c r="B535" t="s">
-        <v>975</v>
+        <v>614</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>56</v>
+        <v>976</v>
       </c>
       <c r="B536" t="s">
-        <v>615</v>
+        <v>975</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>185</v>
+        <v>56</v>
       </c>
       <c r="B537" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="B538" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="B539" t="s">
-        <v>1146</v>
+        <v>617</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B540" t="s">
-        <v>1124</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>1170</v>
+        <v>40</v>
       </c>
       <c r="B541" t="s">
-        <v>1171</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>165</v>
+        <v>1170</v>
       </c>
       <c r="B542" t="s">
-        <v>618</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="B543" t="s">
-        <v>11</v>
+        <v>618</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>250</v>
+        <v>12</v>
       </c>
       <c r="B544" t="s">
-        <v>619</v>
+        <v>11</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>27</v>
+        <v>250</v>
       </c>
       <c r="B545" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>1040</v>
+        <v>27</v>
       </c>
       <c r="B546" t="s">
-        <v>1041</v>
+        <v>620</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>28</v>
+        <v>1040</v>
       </c>
       <c r="B547" t="s">
-        <v>621</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>255</v>
+        <v>28</v>
       </c>
       <c r="B548" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>795</v>
+        <v>255</v>
       </c>
       <c r="B549" t="s">
-        <v>796</v>
+        <v>622</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>267</v>
+        <v>795</v>
       </c>
       <c r="B550" t="s">
-        <v>623</v>
+        <v>796</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>661</v>
+        <v>267</v>
       </c>
       <c r="B551" t="s">
-        <v>744</v>
+        <v>623</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B552" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>139</v>
+        <v>662</v>
       </c>
       <c r="B553" t="s">
-        <v>624</v>
+        <v>745</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="B554" t="s">
-        <v>2</v>
+        <v>624</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="B555" t="s">
-        <v>625</v>
+        <v>2</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>1034</v>
+        <v>105</v>
       </c>
       <c r="B556" t="s">
-        <v>1123</v>
+        <v>625</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>865</v>
+        <v>1034</v>
       </c>
       <c r="B557" t="s">
-        <v>866</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>1035</v>
+        <v>865</v>
       </c>
       <c r="B558" t="s">
-        <v>1122</v>
+        <v>866</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>292</v>
+        <v>1035</v>
       </c>
       <c r="B559" t="s">
-        <v>626</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>8</v>
+        <v>292</v>
       </c>
       <c r="B560" t="s">
-        <v>11</v>
+        <v>626</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>335</v>
+        <v>8</v>
       </c>
       <c r="B561" t="s">
-        <v>627</v>
+        <v>11</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B562" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>259</v>
+        <v>332</v>
       </c>
       <c r="B563" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>319</v>
+        <v>259</v>
       </c>
       <c r="B564" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>859</v>
+        <v>319</v>
       </c>
       <c r="B565" t="s">
-        <v>860</v>
+        <v>630</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>1174</v>
+        <v>859</v>
       </c>
       <c r="B566" t="s">
-        <v>1175</v>
+        <v>860</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>268</v>
+        <v>1174</v>
       </c>
       <c r="B567" t="s">
-        <v>631</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B568" t="s">
-        <v>1117</v>
+        <v>631</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B569" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B570" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B571" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B572" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B573" t="s">
-        <v>1116</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>92</v>
+        <v>272</v>
       </c>
       <c r="B574" t="s">
-        <v>632</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>200</v>
+        <v>92</v>
       </c>
       <c r="B575" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B576" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="B577" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>693</v>
+        <v>172</v>
       </c>
       <c r="B578" t="s">
-        <v>746</v>
+        <v>635</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>252</v>
+        <v>693</v>
       </c>
       <c r="B579" t="s">
-        <v>636</v>
+        <v>746</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>694</v>
+        <v>252</v>
       </c>
       <c r="B580" t="s">
-        <v>747</v>
+        <v>636</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>189</v>
+        <v>694</v>
       </c>
       <c r="B581" t="s">
-        <v>637</v>
+        <v>747</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>989</v>
+        <v>189</v>
       </c>
       <c r="B582" t="s">
-        <v>990</v>
+        <v>637</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>311</v>
+        <v>989</v>
       </c>
       <c r="B583" t="s">
-        <v>638</v>
+        <v>990</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B584" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>1033</v>
+        <v>312</v>
       </c>
       <c r="B585" t="s">
-        <v>1115</v>
+        <v>639</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>1005</v>
+        <v>1033</v>
       </c>
       <c r="B586" t="s">
-        <v>1006</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>81</v>
+        <v>1005</v>
       </c>
       <c r="B587" t="s">
-        <v>640</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>651</v>
+        <v>81</v>
       </c>
       <c r="B588" t="s">
-        <v>748</v>
+        <v>640</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>922</v>
+        <v>651</v>
       </c>
       <c r="B589" t="s">
-        <v>923</v>
+        <v>748</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>642</v>
+        <v>922</v>
       </c>
       <c r="B590" t="s">
-        <v>749</v>
+        <v>923</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>969</v>
+        <v>642</v>
       </c>
       <c r="B591" t="s">
-        <v>970</v>
+        <v>749</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
+        <v>969</v>
+      </c>
+      <c r="B592" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A593" t="s">
         <v>1162</v>
       </c>
-      <c r="B592" t="s">
+      <c r="B593" t="s">
         <v>1163</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B6C1AB-09BF-422C-99D4-4C031127E77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0199381C-F526-4EB8-BABD-324F0ED2DB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="1180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="1182">
   <si>
     <t>trigger</t>
   </si>
@@ -3565,6 +3565,12 @@
   </si>
   <si>
     <t>subcentimetric</t>
+  </si>
+  <si>
+    <t>scp</t>
+  </si>
+  <si>
+    <t>subcutaneous plane</t>
   </si>
 </sst>
 </file>
@@ -3620,10 +3626,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B593" totalsRowShown="0">
-  <autoFilter ref="A1:B593" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B593">
-    <sortCondition ref="A1:A593"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B594" totalsRowShown="0">
+  <autoFilter ref="A1:B594" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B594">
+    <sortCondition ref="A1:A594"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -3896,7 +3902,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B593"/>
+  <dimension ref="A1:B594"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -7929,721 +7935,729 @@
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>756</v>
+        <v>1180</v>
       </c>
       <c r="B504" t="s">
-        <v>757</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>1078</v>
+        <v>756</v>
       </c>
       <c r="B505" t="s">
-        <v>1079</v>
+        <v>757</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>67</v>
+        <v>1078</v>
       </c>
       <c r="B506" t="s">
-        <v>597</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B507" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="B508" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>289</v>
+        <v>95</v>
       </c>
       <c r="B509" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B510" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="B511" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>193</v>
+        <v>264</v>
       </c>
       <c r="B512" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>901</v>
+        <v>193</v>
       </c>
       <c r="B513" t="s">
-        <v>902</v>
+        <v>603</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>44</v>
+        <v>901</v>
       </c>
       <c r="B514" t="s">
-        <v>1125</v>
+        <v>902</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>1070</v>
+        <v>44</v>
       </c>
       <c r="B515" t="s">
-        <v>1071</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>324</v>
+        <v>1070</v>
       </c>
       <c r="B516" t="s">
-        <v>604</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B517" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>849</v>
+        <v>325</v>
       </c>
       <c r="B518" t="s">
-        <v>850</v>
+        <v>605</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>887</v>
+        <v>849</v>
       </c>
       <c r="B519" t="s">
-        <v>888</v>
+        <v>850</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>869</v>
+        <v>887</v>
       </c>
       <c r="B520" t="s">
-        <v>870</v>
+        <v>888</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>33</v>
+        <v>869</v>
       </c>
       <c r="B521" t="s">
-        <v>606</v>
+        <v>870</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B522" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>1143</v>
+        <v>36</v>
       </c>
       <c r="B523" t="s">
-        <v>1144</v>
+        <v>607</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>309</v>
+        <v>1143</v>
       </c>
       <c r="B524" t="s">
-        <v>608</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>257</v>
+        <v>309</v>
       </c>
       <c r="B525" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>302</v>
+        <v>257</v>
       </c>
       <c r="B526" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>228</v>
+        <v>302</v>
       </c>
       <c r="B527" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c r="B528" t="s">
-        <v>18</v>
+        <v>611</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>655</v>
+        <v>17</v>
       </c>
       <c r="B529" t="s">
-        <v>743</v>
+        <v>18</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>785</v>
+        <v>655</v>
       </c>
       <c r="B530" t="s">
-        <v>786</v>
+        <v>743</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>142</v>
+        <v>785</v>
       </c>
       <c r="B531" t="s">
-        <v>612</v>
+        <v>786</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>1178</v>
+        <v>142</v>
       </c>
       <c r="B532" t="s">
-        <v>1179</v>
+        <v>612</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>956</v>
+        <v>1178</v>
       </c>
       <c r="B533" t="s">
-        <v>957</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>54</v>
+        <v>956</v>
       </c>
       <c r="B534" t="s">
-        <v>613</v>
+        <v>957</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>265</v>
+        <v>54</v>
       </c>
       <c r="B535" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>976</v>
+        <v>265</v>
       </c>
       <c r="B536" t="s">
-        <v>975</v>
+        <v>614</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>56</v>
+        <v>976</v>
       </c>
       <c r="B537" t="s">
-        <v>615</v>
+        <v>975</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>185</v>
+        <v>56</v>
       </c>
       <c r="B538" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="B539" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="B540" t="s">
-        <v>1146</v>
+        <v>617</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B541" t="s">
-        <v>1124</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>1170</v>
+        <v>40</v>
       </c>
       <c r="B542" t="s">
-        <v>1171</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>165</v>
+        <v>1170</v>
       </c>
       <c r="B543" t="s">
-        <v>618</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="B544" t="s">
-        <v>11</v>
+        <v>618</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>250</v>
+        <v>12</v>
       </c>
       <c r="B545" t="s">
-        <v>619</v>
+        <v>11</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>27</v>
+        <v>250</v>
       </c>
       <c r="B546" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>1040</v>
+        <v>27</v>
       </c>
       <c r="B547" t="s">
-        <v>1041</v>
+        <v>620</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>28</v>
+        <v>1040</v>
       </c>
       <c r="B548" t="s">
-        <v>621</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>255</v>
+        <v>28</v>
       </c>
       <c r="B549" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>795</v>
+        <v>255</v>
       </c>
       <c r="B550" t="s">
-        <v>796</v>
+        <v>622</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>267</v>
+        <v>795</v>
       </c>
       <c r="B551" t="s">
-        <v>623</v>
+        <v>796</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>661</v>
+        <v>267</v>
       </c>
       <c r="B552" t="s">
-        <v>744</v>
+        <v>623</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B553" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>139</v>
+        <v>662</v>
       </c>
       <c r="B554" t="s">
-        <v>624</v>
+        <v>745</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="B555" t="s">
-        <v>2</v>
+        <v>624</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="B556" t="s">
-        <v>625</v>
+        <v>2</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>1034</v>
+        <v>105</v>
       </c>
       <c r="B557" t="s">
-        <v>1123</v>
+        <v>625</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>865</v>
+        <v>1034</v>
       </c>
       <c r="B558" t="s">
-        <v>866</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>1035</v>
+        <v>865</v>
       </c>
       <c r="B559" t="s">
-        <v>1122</v>
+        <v>866</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>292</v>
+        <v>1035</v>
       </c>
       <c r="B560" t="s">
-        <v>626</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>8</v>
+        <v>292</v>
       </c>
       <c r="B561" t="s">
-        <v>11</v>
+        <v>626</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>335</v>
+        <v>8</v>
       </c>
       <c r="B562" t="s">
-        <v>627</v>
+        <v>11</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B563" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>259</v>
+        <v>332</v>
       </c>
       <c r="B564" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>319</v>
+        <v>259</v>
       </c>
       <c r="B565" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>859</v>
+        <v>319</v>
       </c>
       <c r="B566" t="s">
-        <v>860</v>
+        <v>630</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>1174</v>
+        <v>859</v>
       </c>
       <c r="B567" t="s">
-        <v>1175</v>
+        <v>860</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>268</v>
+        <v>1174</v>
       </c>
       <c r="B568" t="s">
-        <v>631</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B569" t="s">
-        <v>1117</v>
+        <v>631</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B570" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B571" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B572" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B573" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B574" t="s">
-        <v>1116</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>92</v>
+        <v>272</v>
       </c>
       <c r="B575" t="s">
-        <v>632</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>200</v>
+        <v>92</v>
       </c>
       <c r="B576" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B577" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="B578" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>693</v>
+        <v>172</v>
       </c>
       <c r="B579" t="s">
-        <v>746</v>
+        <v>635</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>252</v>
+        <v>693</v>
       </c>
       <c r="B580" t="s">
-        <v>636</v>
+        <v>746</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>694</v>
+        <v>252</v>
       </c>
       <c r="B581" t="s">
-        <v>747</v>
+        <v>636</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>189</v>
+        <v>694</v>
       </c>
       <c r="B582" t="s">
-        <v>637</v>
+        <v>747</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>989</v>
+        <v>189</v>
       </c>
       <c r="B583" t="s">
-        <v>990</v>
+        <v>637</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>311</v>
+        <v>989</v>
       </c>
       <c r="B584" t="s">
-        <v>638</v>
+        <v>990</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B585" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>1033</v>
+        <v>312</v>
       </c>
       <c r="B586" t="s">
-        <v>1115</v>
+        <v>639</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>1005</v>
+        <v>1033</v>
       </c>
       <c r="B587" t="s">
-        <v>1006</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>81</v>
+        <v>1005</v>
       </c>
       <c r="B588" t="s">
-        <v>640</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>651</v>
+        <v>81</v>
       </c>
       <c r="B589" t="s">
-        <v>748</v>
+        <v>640</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>922</v>
+        <v>651</v>
       </c>
       <c r="B590" t="s">
-        <v>923</v>
+        <v>748</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>642</v>
+        <v>922</v>
       </c>
       <c r="B591" t="s">
-        <v>749</v>
+        <v>923</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>969</v>
+        <v>642</v>
       </c>
       <c r="B592" t="s">
-        <v>970</v>
+        <v>749</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
+        <v>969</v>
+      </c>
+      <c r="B593" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A594" t="s">
         <v>1162</v>
       </c>
-      <c r="B593" t="s">
+      <c r="B594" t="s">
         <v>1163</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0199381C-F526-4EB8-BABD-324F0ED2DB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE8513B0-56BF-4367-A2DD-D16AB3CE1B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="1182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="1186">
   <si>
     <t>trigger</t>
   </si>
@@ -3571,6 +3571,18 @@
   </si>
   <si>
     <t>subcutaneous plane</t>
+  </si>
+  <si>
+    <t>amt</t>
+  </si>
+  <si>
+    <t>amount</t>
+  </si>
+  <si>
+    <t>rxn</t>
+  </si>
+  <si>
+    <t>reaction</t>
   </si>
 </sst>
 </file>
@@ -3626,10 +3638,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B594" totalsRowShown="0">
-  <autoFilter ref="A1:B594" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B594">
-    <sortCondition ref="A1:A594"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B596" totalsRowShown="0">
+  <autoFilter ref="A1:B596" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B596">
+    <sortCondition ref="A1:A596"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -3902,7 +3914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B594"/>
+  <dimension ref="A1:B596"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -4151,1247 +4163,1247 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>46</v>
+        <v>1182</v>
       </c>
       <c r="B31" t="s">
-        <v>353</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B32" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="B33" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>1022</v>
+        <v>150</v>
       </c>
       <c r="B34" t="s">
-        <v>1023</v>
+        <v>355</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>69</v>
+        <v>1022</v>
       </c>
       <c r="B35" t="s">
-        <v>356</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>282</v>
+        <v>69</v>
       </c>
       <c r="B36" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>141</v>
+        <v>282</v>
       </c>
       <c r="B37" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>911</v>
+        <v>141</v>
       </c>
       <c r="B38" t="s">
-        <v>912</v>
+        <v>358</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>148</v>
+        <v>911</v>
       </c>
       <c r="B39" t="s">
-        <v>359</v>
+        <v>912</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>1102</v>
+        <v>148</v>
       </c>
       <c r="B40" t="s">
-        <v>1103</v>
+        <v>359</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>660</v>
+        <v>1102</v>
       </c>
       <c r="B41" t="s">
-        <v>696</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>1016</v>
+        <v>660</v>
       </c>
       <c r="B42" t="s">
-        <v>1017</v>
+        <v>696</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>166</v>
+        <v>1016</v>
       </c>
       <c r="B43" t="s">
-        <v>360</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>291</v>
+        <v>166</v>
       </c>
       <c r="B44" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="B45" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>239</v>
+        <v>310</v>
       </c>
       <c r="B46" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>195</v>
+        <v>239</v>
       </c>
       <c r="B47" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>246</v>
+        <v>195</v>
       </c>
       <c r="B48" t="s">
-        <v>1140</v>
+        <v>364</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>647</v>
+        <v>246</v>
       </c>
       <c r="B49" t="s">
-        <v>697</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>240</v>
+        <v>647</v>
       </c>
       <c r="B50" t="s">
-        <v>363</v>
+        <v>697</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>861</v>
+        <v>240</v>
       </c>
       <c r="B51" t="s">
-        <v>862</v>
+        <v>363</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>987</v>
+        <v>861</v>
       </c>
       <c r="B52" t="s">
-        <v>988</v>
+        <v>862</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>774</v>
+        <v>987</v>
       </c>
       <c r="B53" t="s">
-        <v>775</v>
+        <v>988</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B54" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>300</v>
+        <v>776</v>
       </c>
       <c r="B55" t="s">
-        <v>365</v>
+        <v>777</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>1147</v>
+        <v>300</v>
       </c>
       <c r="B56" t="s">
-        <v>1148</v>
+        <v>365</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>303</v>
+        <v>1147</v>
       </c>
       <c r="B57" t="s">
-        <v>366</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>230</v>
+        <v>303</v>
       </c>
       <c r="B58" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B59" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>789</v>
+        <v>232</v>
       </c>
       <c r="B60" t="s">
-        <v>790</v>
+        <v>368</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>318</v>
+        <v>789</v>
       </c>
       <c r="B61" t="s">
-        <v>369</v>
+        <v>790</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>762</v>
+        <v>318</v>
       </c>
       <c r="B62" t="s">
-        <v>763</v>
+        <v>369</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>61</v>
+        <v>762</v>
       </c>
       <c r="B63" t="s">
-        <v>370</v>
+        <v>763</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B64" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B65" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>885</v>
+        <v>58</v>
       </c>
       <c r="B66" t="s">
-        <v>886</v>
+        <v>372</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>659</v>
+        <v>885</v>
       </c>
       <c r="B67" t="s">
-        <v>698</v>
+        <v>886</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>237</v>
+        <v>659</v>
       </c>
       <c r="B68" t="s">
-        <v>373</v>
+        <v>698</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>60</v>
+        <v>237</v>
       </c>
       <c r="B69" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>1014</v>
+        <v>60</v>
       </c>
       <c r="B70" t="s">
-        <v>1015</v>
+        <v>374</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>668</v>
+        <v>1014</v>
       </c>
       <c r="B71" t="s">
-        <v>699</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B72" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B73" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B74" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B75" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B76" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B77" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>875</v>
+        <v>674</v>
       </c>
       <c r="B78" t="s">
-        <v>876</v>
+        <v>705</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>321</v>
+        <v>875</v>
       </c>
       <c r="B79" t="s">
-        <v>375</v>
+        <v>876</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>194</v>
+        <v>321</v>
       </c>
       <c r="B80" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="B81" t="s">
-        <v>22</v>
+        <v>376</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B82" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>196</v>
+        <v>19</v>
       </c>
       <c r="B83" t="s">
-        <v>377</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>287</v>
+        <v>196</v>
       </c>
       <c r="B84" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B85" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>337</v>
+        <v>286</v>
       </c>
       <c r="B86" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>899</v>
+        <v>337</v>
       </c>
       <c r="B87" t="s">
-        <v>900</v>
+        <v>380</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>305</v>
+        <v>899</v>
       </c>
       <c r="B88" t="s">
-        <v>381</v>
+        <v>900</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="B89" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>1159</v>
+        <v>323</v>
       </c>
       <c r="B90" t="s">
-        <v>1160</v>
+        <v>382</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>276</v>
+        <v>1159</v>
       </c>
       <c r="B91" t="s">
-        <v>383</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>333</v>
+        <v>276</v>
       </c>
       <c r="B92" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>42</v>
+        <v>333</v>
       </c>
       <c r="B93" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B94" t="s">
-        <v>1139</v>
+        <v>385</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>649</v>
+        <v>41</v>
       </c>
       <c r="B95" t="s">
-        <v>706</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>217</v>
+        <v>649</v>
       </c>
       <c r="B96" t="s">
-        <v>386</v>
+        <v>706</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>288</v>
+        <v>217</v>
       </c>
       <c r="B97" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>218</v>
+        <v>288</v>
       </c>
       <c r="B98" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>296</v>
+        <v>218</v>
       </c>
       <c r="B99" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>199</v>
+        <v>296</v>
       </c>
       <c r="B100" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>648</v>
+        <v>199</v>
       </c>
       <c r="B101" t="s">
-        <v>707</v>
+        <v>390</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>112</v>
+        <v>648</v>
       </c>
       <c r="B102" t="s">
-        <v>391</v>
+        <v>707</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="B103" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="B104" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>1176</v>
+        <v>115</v>
       </c>
       <c r="B105" t="s">
-        <v>1177</v>
+        <v>393</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>879</v>
+        <v>1176</v>
       </c>
       <c r="B106" t="s">
-        <v>880</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>807</v>
+        <v>879</v>
       </c>
       <c r="B107" t="s">
-        <v>808</v>
+        <v>880</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>152</v>
+        <v>807</v>
       </c>
       <c r="B108" t="s">
-        <v>394</v>
+        <v>808</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="B109" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B110" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="B111" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>967</v>
+        <v>155</v>
       </c>
       <c r="B112" t="s">
-        <v>968</v>
+        <v>397</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>84</v>
+        <v>967</v>
       </c>
       <c r="B113" t="s">
-        <v>398</v>
+        <v>968</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>965</v>
+        <v>84</v>
       </c>
       <c r="B114" t="s">
-        <v>966</v>
+        <v>398</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>103</v>
+        <v>965</v>
       </c>
       <c r="B115" t="s">
-        <v>399</v>
+        <v>966</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>198</v>
+        <v>103</v>
       </c>
       <c r="B116" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>314</v>
+        <v>198</v>
       </c>
       <c r="B117" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>104</v>
+        <v>314</v>
       </c>
       <c r="B118" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="B119" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="B120" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B121" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>1046</v>
+        <v>102</v>
       </c>
       <c r="B122" t="s">
-        <v>1047</v>
+        <v>405</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>930</v>
+        <v>1046</v>
       </c>
       <c r="B123" t="s">
-        <v>931</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B124" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>162</v>
+        <v>928</v>
       </c>
       <c r="B125" t="s">
-        <v>406</v>
+        <v>929</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>1153</v>
+        <v>162</v>
       </c>
       <c r="B126" t="s">
-        <v>1154</v>
+        <v>406</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>837</v>
+        <v>1153</v>
       </c>
       <c r="B127" t="s">
-        <v>838</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B128" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>1084</v>
+        <v>839</v>
       </c>
       <c r="B129" t="s">
-        <v>1085</v>
+        <v>840</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>665</v>
+        <v>1084</v>
       </c>
       <c r="B130" t="s">
-        <v>708</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>646</v>
+        <v>665</v>
       </c>
       <c r="B131" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>940</v>
+        <v>646</v>
       </c>
       <c r="B132" t="s">
-        <v>941</v>
+        <v>709</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>683</v>
+        <v>940</v>
       </c>
       <c r="B133" t="s">
-        <v>710</v>
+        <v>941</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B134" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B135" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="B136" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B137" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B138" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B139" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B140" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B141" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B142" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B143" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>175</v>
+        <v>682</v>
       </c>
       <c r="B144" t="s">
-        <v>407</v>
+        <v>720</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="B145" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B146" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>149</v>
+        <v>213</v>
       </c>
       <c r="B147" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>247</v>
+        <v>149</v>
       </c>
       <c r="B148" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B149" t="s">
-        <v>1138</v>
+        <v>411</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>336</v>
+        <v>245</v>
       </c>
       <c r="B150" t="s">
-        <v>412</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>650</v>
+        <v>336</v>
       </c>
       <c r="B151" t="s">
-        <v>721</v>
+        <v>412</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>91</v>
+        <v>650</v>
       </c>
       <c r="B152" t="s">
-        <v>413</v>
+        <v>721</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>266</v>
+        <v>91</v>
       </c>
       <c r="B153" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>1096</v>
+        <v>266</v>
       </c>
       <c r="B154" t="s">
-        <v>1097</v>
+        <v>414</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>799</v>
+        <v>1096</v>
       </c>
       <c r="B155" t="s">
-        <v>800</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>1168</v>
+        <v>799</v>
       </c>
       <c r="B156" t="s">
-        <v>1169</v>
+        <v>800</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>295</v>
+        <v>1168</v>
       </c>
       <c r="B157" t="s">
-        <v>415</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>1086</v>
+        <v>295</v>
       </c>
       <c r="B158" t="s">
-        <v>1087</v>
+        <v>415</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="B159" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>151</v>
+        <v>1092</v>
       </c>
       <c r="B160" t="s">
-        <v>416</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>961</v>
+        <v>151</v>
       </c>
       <c r="B161" t="s">
-        <v>962</v>
+        <v>416</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>813</v>
+        <v>961</v>
       </c>
       <c r="B162" t="s">
-        <v>814</v>
+        <v>962</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>932</v>
+        <v>813</v>
       </c>
       <c r="B163" t="s">
-        <v>933</v>
+        <v>814</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>833</v>
+        <v>932</v>
       </c>
       <c r="B164" t="s">
-        <v>834</v>
+        <v>933</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>793</v>
+        <v>833</v>
       </c>
       <c r="B165" t="s">
-        <v>794</v>
+        <v>834</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>754</v>
+        <v>793</v>
       </c>
       <c r="B166" t="s">
-        <v>755</v>
+        <v>794</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>100</v>
+        <v>754</v>
       </c>
       <c r="B167" t="s">
-        <v>417</v>
+        <v>755</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>1042</v>
+        <v>100</v>
       </c>
       <c r="B168" t="s">
-        <v>1043</v>
+        <v>417</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>154</v>
+        <v>1042</v>
       </c>
       <c r="B169" t="s">
-        <v>418</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B170" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="B171" t="s">
-        <v>1137</v>
+        <v>419</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>1164</v>
+        <v>24</v>
       </c>
       <c r="B172" t="s">
-        <v>1165</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>1076</v>
+        <v>1164</v>
       </c>
       <c r="B173" t="s">
-        <v>1077</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>819</v>
+        <v>1076</v>
       </c>
       <c r="B174" t="s">
-        <v>820</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>130</v>
+        <v>819</v>
       </c>
       <c r="B175" t="s">
-        <v>420</v>
+        <v>820</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>322</v>
+        <v>130</v>
       </c>
       <c r="B176" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>867</v>
+        <v>322</v>
       </c>
       <c r="B177" t="s">
-        <v>868</v>
+        <v>421</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>183</v>
+        <v>867</v>
       </c>
       <c r="B178" t="s">
-        <v>422</v>
+        <v>868</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>1155</v>
+        <v>183</v>
       </c>
       <c r="B179" t="s">
-        <v>1156</v>
+        <v>422</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="B180" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>891</v>
+        <v>1157</v>
       </c>
       <c r="B181" t="s">
-        <v>892</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>32</v>
+        <v>891</v>
       </c>
       <c r="B182" t="s">
-        <v>423</v>
+        <v>892</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B183" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>764</v>
+        <v>35</v>
       </c>
       <c r="B184" t="s">
-        <v>1010</v>
+        <v>424</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>169</v>
+        <v>764</v>
       </c>
       <c r="B185" t="s">
-        <v>425</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B186" t="s">
         <v>425</v>
@@ -5399,1463 +5411,1463 @@
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>1011</v>
+        <v>170</v>
       </c>
       <c r="B187" t="s">
-        <v>765</v>
+        <v>425</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>178</v>
+        <v>1011</v>
       </c>
       <c r="B188" t="s">
-        <v>426</v>
+        <v>765</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="B189" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>238</v>
+        <v>111</v>
       </c>
       <c r="B190" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="B191" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B192" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="B193" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>667</v>
+        <v>179</v>
       </c>
       <c r="B194" t="s">
-        <v>722</v>
+        <v>431</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>97</v>
+        <v>667</v>
       </c>
       <c r="B195" t="s">
-        <v>432</v>
+        <v>722</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B196" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>242</v>
+        <v>110</v>
       </c>
       <c r="B197" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B198" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="B199" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B200" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>1110</v>
+        <v>182</v>
       </c>
       <c r="B201" t="s">
-        <v>1111</v>
+        <v>437</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>977</v>
+        <v>1110</v>
       </c>
       <c r="B202" t="s">
-        <v>978</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="B203" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>253</v>
+        <v>979</v>
       </c>
       <c r="B204" t="s">
-        <v>438</v>
+        <v>980</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="B205" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>787</v>
+        <v>34</v>
       </c>
       <c r="B206" t="s">
-        <v>788</v>
+        <v>439</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>180</v>
+        <v>787</v>
       </c>
       <c r="B207" t="s">
-        <v>440</v>
+        <v>788</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>275</v>
+        <v>180</v>
       </c>
       <c r="B208" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>857</v>
+        <v>275</v>
       </c>
       <c r="B209" t="s">
-        <v>858</v>
+        <v>441</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>116</v>
+        <v>857</v>
       </c>
       <c r="B210" t="s">
-        <v>442</v>
+        <v>858</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>208</v>
+        <v>116</v>
       </c>
       <c r="B211" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>1056</v>
+        <v>208</v>
       </c>
       <c r="B212" t="s">
-        <v>1057</v>
+        <v>443</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>118</v>
+        <v>1056</v>
       </c>
       <c r="B213" t="s">
-        <v>444</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>641</v>
+        <v>118</v>
       </c>
       <c r="B214" t="s">
-        <v>723</v>
+        <v>444</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>815</v>
+        <v>641</v>
       </c>
       <c r="B215" t="s">
-        <v>816</v>
+        <v>723</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>298</v>
+        <v>815</v>
       </c>
       <c r="B216" t="s">
-        <v>445</v>
+        <v>816</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>643</v>
+        <v>298</v>
       </c>
       <c r="B217" t="s">
-        <v>724</v>
+        <v>445</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B218" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>1036</v>
+        <v>644</v>
       </c>
       <c r="B219" t="s">
-        <v>1037</v>
+        <v>725</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>90</v>
+        <v>1036</v>
       </c>
       <c r="B220" t="s">
-        <v>446</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B221" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B222" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>1072</v>
+        <v>89</v>
       </c>
       <c r="B223" t="s">
-        <v>1073</v>
+        <v>448</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>23</v>
+        <v>1072</v>
       </c>
       <c r="B224" t="s">
-        <v>1136</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B225" t="s">
-        <v>6</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>1141</v>
+        <v>5</v>
       </c>
       <c r="B226" t="s">
-        <v>1142</v>
+        <v>6</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>126</v>
+        <v>1141</v>
       </c>
       <c r="B227" t="s">
-        <v>449</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B228" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B229" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B230" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B231" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>277</v>
+        <v>119</v>
       </c>
       <c r="B232" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>1074</v>
+        <v>277</v>
       </c>
       <c r="B233" t="s">
-        <v>1075</v>
+        <v>454</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>9</v>
+        <v>1074</v>
       </c>
       <c r="B234" t="s">
-        <v>10</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="B235" t="s">
-        <v>455</v>
+        <v>10</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B236" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="B237" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="B238" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>77</v>
+        <v>262</v>
       </c>
       <c r="B239" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>938</v>
+        <v>77</v>
       </c>
       <c r="B240" t="s">
-        <v>939</v>
+        <v>459</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>1172</v>
+        <v>938</v>
       </c>
       <c r="B241" t="s">
-        <v>1173</v>
+        <v>939</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>168</v>
+        <v>1172</v>
       </c>
       <c r="B242" t="s">
-        <v>460</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B243" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>835</v>
+        <v>167</v>
       </c>
       <c r="B244" t="s">
-        <v>836</v>
+        <v>461</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>791</v>
+        <v>835</v>
       </c>
       <c r="B245" t="s">
-        <v>792</v>
+        <v>836</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>304</v>
+        <v>791</v>
       </c>
       <c r="B246" t="s">
-        <v>462</v>
+        <v>792</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>758</v>
+        <v>304</v>
       </c>
       <c r="B247" t="s">
-        <v>759</v>
+        <v>462</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>897</v>
+        <v>758</v>
       </c>
       <c r="B248" t="s">
-        <v>898</v>
+        <v>759</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>652</v>
+        <v>897</v>
       </c>
       <c r="B249" t="s">
-        <v>726</v>
+        <v>898</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>86</v>
+        <v>652</v>
       </c>
       <c r="B250" t="s">
-        <v>463</v>
+        <v>726</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B251" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="B252" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B253" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B254" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>251</v>
+        <v>158</v>
       </c>
       <c r="B255" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="B256" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>326</v>
+        <v>285</v>
       </c>
       <c r="B257" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B258" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>229</v>
+        <v>327</v>
       </c>
       <c r="B259" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>55</v>
+        <v>229</v>
       </c>
       <c r="B260" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>657</v>
+        <v>55</v>
       </c>
       <c r="B261" t="s">
-        <v>727</v>
+        <v>473</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>235</v>
+        <v>657</v>
       </c>
       <c r="B262" t="s">
-        <v>474</v>
+        <v>727</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="B263" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="B264" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>766</v>
+        <v>236</v>
       </c>
       <c r="B265" t="s">
-        <v>1009</v>
+        <v>476</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>1012</v>
+        <v>766</v>
       </c>
       <c r="B266" t="s">
-        <v>767</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>164</v>
+        <v>1012</v>
       </c>
       <c r="B267" t="s">
-        <v>477</v>
+        <v>767</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="B268" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B269" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>313</v>
+        <v>204</v>
       </c>
       <c r="B270" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>873</v>
+        <v>313</v>
       </c>
       <c r="B271" t="s">
-        <v>874</v>
+        <v>480</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>997</v>
+        <v>873</v>
       </c>
       <c r="B272" t="s">
-        <v>998</v>
+        <v>874</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>258</v>
+        <v>997</v>
       </c>
       <c r="B273" t="s">
-        <v>481</v>
+        <v>998</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>983</v>
+        <v>258</v>
       </c>
       <c r="B274" t="s">
-        <v>984</v>
+        <v>481</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>160</v>
+        <v>983</v>
       </c>
       <c r="B275" t="s">
-        <v>482</v>
+        <v>984</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>692</v>
+        <v>160</v>
       </c>
       <c r="B276" t="s">
-        <v>728</v>
+        <v>482</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>1166</v>
+        <v>692</v>
       </c>
       <c r="B277" t="s">
-        <v>1167</v>
+        <v>728</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>760</v>
+        <v>1166</v>
       </c>
       <c r="B278" t="s">
-        <v>761</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>895</v>
+        <v>760</v>
       </c>
       <c r="B279" t="s">
-        <v>896</v>
+        <v>761</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B280" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>184</v>
+        <v>893</v>
       </c>
       <c r="B281" t="s">
-        <v>483</v>
+        <v>894</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>244</v>
+        <v>184</v>
       </c>
       <c r="B282" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B283" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>686</v>
+        <v>243</v>
       </c>
       <c r="B284" t="s">
-        <v>729</v>
+        <v>485</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B285" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B286" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B287" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B288" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>280</v>
+        <v>690</v>
       </c>
       <c r="B289" t="s">
-        <v>486</v>
+        <v>733</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B290" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>49</v>
+        <v>281</v>
       </c>
       <c r="B291" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B292" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="B293" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="B294" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>221</v>
+        <v>72</v>
       </c>
       <c r="B295" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>15</v>
+        <v>221</v>
       </c>
       <c r="B296" t="s">
-        <v>16</v>
+        <v>492</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>1060</v>
+        <v>15</v>
       </c>
       <c r="B297" t="s">
-        <v>1061</v>
+        <v>16</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>920</v>
+        <v>1060</v>
       </c>
       <c r="B298" t="s">
-        <v>921</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>108</v>
+        <v>920</v>
       </c>
       <c r="B299" t="s">
-        <v>493</v>
+        <v>921</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>241</v>
+        <v>108</v>
       </c>
       <c r="B300" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>328</v>
+        <v>241</v>
       </c>
       <c r="B301" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>1100</v>
+        <v>328</v>
       </c>
       <c r="B302" t="s">
-        <v>1101</v>
+        <v>495</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>1052</v>
+        <v>1100</v>
       </c>
       <c r="B303" t="s">
-        <v>1053</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>121</v>
+        <v>1052</v>
       </c>
       <c r="B304" t="s">
-        <v>496</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>750</v>
+        <v>121</v>
       </c>
       <c r="B305" t="s">
-        <v>751</v>
+        <v>496</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>781</v>
+        <v>750</v>
       </c>
       <c r="B306" t="s">
-        <v>782</v>
+        <v>751</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>134</v>
+        <v>781</v>
       </c>
       <c r="B307" t="s">
-        <v>497</v>
+        <v>782</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="B308" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>224</v>
+        <v>63</v>
       </c>
       <c r="B309" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>25</v>
+        <v>224</v>
       </c>
       <c r="B310" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B311" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>207</v>
+        <v>26</v>
       </c>
       <c r="B312" t="s">
-        <v>1133</v>
+        <v>501</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>960</v>
+        <v>207</v>
       </c>
       <c r="B313" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>1113</v>
+        <v>960</v>
       </c>
       <c r="B314" t="s">
-        <v>1114</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>206</v>
+        <v>1113</v>
       </c>
       <c r="B315" t="s">
-        <v>1135</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B316" t="s">
-        <v>502</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B317" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="B318" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>663</v>
+        <v>145</v>
       </c>
       <c r="B319" t="s">
-        <v>734</v>
+        <v>504</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>171</v>
+        <v>663</v>
       </c>
       <c r="B320" t="s">
-        <v>505</v>
+        <v>734</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>1088</v>
+        <v>171</v>
       </c>
       <c r="B321" t="s">
-        <v>1089</v>
+        <v>505</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>263</v>
+        <v>1088</v>
       </c>
       <c r="B322" t="s">
-        <v>506</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>1090</v>
+        <v>263</v>
       </c>
       <c r="B323" t="s">
-        <v>1091</v>
+        <v>506</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>80</v>
+        <v>1090</v>
       </c>
       <c r="B324" t="s">
-        <v>507</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B325" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>191</v>
+        <v>65</v>
       </c>
       <c r="B326" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="B327" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>192</v>
+        <v>123</v>
       </c>
       <c r="B328" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="B329" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B330" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>31</v>
+        <v>233</v>
       </c>
       <c r="B331" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B332" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B333" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B334" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>306</v>
+        <v>71</v>
       </c>
       <c r="B335" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>222</v>
+        <v>306</v>
       </c>
       <c r="B336" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>315</v>
+        <v>222</v>
       </c>
       <c r="B337" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>278</v>
+        <v>315</v>
       </c>
       <c r="B338" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B339" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>831</v>
+        <v>279</v>
       </c>
       <c r="B340" t="s">
-        <v>832</v>
+        <v>522</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>48</v>
+        <v>831</v>
       </c>
       <c r="B341" t="s">
-        <v>523</v>
+        <v>832</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="B342" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="B343" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>223</v>
+        <v>52</v>
       </c>
       <c r="B344" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>1094</v>
+        <v>223</v>
       </c>
       <c r="B345" t="s">
-        <v>1095</v>
+        <v>526</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>1109</v>
+        <v>1094</v>
       </c>
       <c r="B346" t="s">
-        <v>1112</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>1050</v>
+        <v>1109</v>
       </c>
       <c r="B347" t="s">
-        <v>1051</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>96</v>
+        <v>1050</v>
       </c>
       <c r="B348" t="s">
-        <v>527</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>248</v>
+        <v>96</v>
       </c>
       <c r="B349" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B350" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>94</v>
+        <v>249</v>
       </c>
       <c r="B351" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>1064</v>
+        <v>94</v>
       </c>
       <c r="B352" t="s">
-        <v>1065</v>
+        <v>530</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>212</v>
+        <v>1064</v>
       </c>
       <c r="B353" t="s">
-        <v>531</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>916</v>
+        <v>212</v>
       </c>
       <c r="B354" t="s">
-        <v>917</v>
+        <v>531</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B355" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="B356" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>330</v>
+        <v>918</v>
       </c>
       <c r="B357" t="s">
-        <v>532</v>
+        <v>919</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>1066</v>
+        <v>330</v>
       </c>
       <c r="B358" t="s">
-        <v>1067</v>
+        <v>532</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>995</v>
+        <v>1066</v>
       </c>
       <c r="B359" t="s">
-        <v>996</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="B360" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B361" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>82</v>
+        <v>993</v>
       </c>
       <c r="B362" t="s">
-        <v>533</v>
+        <v>994</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>772</v>
+        <v>82</v>
       </c>
       <c r="B363" t="s">
-        <v>773</v>
+        <v>533</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>197</v>
+        <v>772</v>
       </c>
       <c r="B364" t="s">
-        <v>534</v>
+        <v>773</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>654</v>
+        <v>197</v>
       </c>
       <c r="B365" t="s">
-        <v>735</v>
+        <v>534</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>821</v>
+        <v>654</v>
       </c>
       <c r="B366" t="s">
-        <v>822</v>
+        <v>735</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>1068</v>
+        <v>821</v>
       </c>
       <c r="B367" t="s">
-        <v>1069</v>
+        <v>822</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>3</v>
+        <v>1068</v>
       </c>
       <c r="B368" t="s">
-        <v>4</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>958</v>
+        <v>3</v>
       </c>
       <c r="B369" t="s">
         <v>4</v>
@@ -6863,7 +6875,7 @@
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B370" t="s">
         <v>4</v>
@@ -6871,1793 +6883,1809 @@
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>664</v>
+        <v>959</v>
       </c>
       <c r="B371" t="s">
-        <v>736</v>
+        <v>4</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>770</v>
+        <v>664</v>
       </c>
       <c r="B372" t="s">
-        <v>771</v>
+        <v>736</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>85</v>
+        <v>770</v>
       </c>
       <c r="B373" t="s">
-        <v>535</v>
+        <v>771</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>1062</v>
+        <v>85</v>
       </c>
       <c r="B374" t="s">
-        <v>1063</v>
+        <v>535</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>829</v>
+        <v>1062</v>
       </c>
       <c r="B375" t="s">
-        <v>830</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>809</v>
+        <v>829</v>
       </c>
       <c r="B376" t="s">
-        <v>810</v>
+        <v>830</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>187</v>
+        <v>809</v>
       </c>
       <c r="B377" t="s">
-        <v>536</v>
+        <v>810</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>827</v>
+        <v>187</v>
       </c>
       <c r="B378" t="s">
-        <v>828</v>
+        <v>536</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>934</v>
+        <v>827</v>
       </c>
       <c r="B379" t="s">
-        <v>1130</v>
+        <v>828</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>863</v>
+        <v>934</v>
       </c>
       <c r="B380" t="s">
-        <v>864</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>1044</v>
+        <v>863</v>
       </c>
       <c r="B381" t="s">
-        <v>1045</v>
+        <v>864</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>798</v>
+        <v>1044</v>
       </c>
       <c r="B382" t="s">
-        <v>1131</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B383" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>13</v>
+        <v>797</v>
       </c>
       <c r="B384" t="s">
-        <v>14</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>817</v>
+        <v>13</v>
       </c>
       <c r="B385" t="s">
-        <v>818</v>
+        <v>14</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>186</v>
+        <v>817</v>
       </c>
       <c r="B386" t="s">
-        <v>537</v>
+        <v>818</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>811</v>
+        <v>186</v>
       </c>
       <c r="B387" t="s">
-        <v>812</v>
+        <v>537</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>320</v>
+        <v>811</v>
       </c>
       <c r="B388" t="s">
-        <v>538</v>
+        <v>812</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>656</v>
+        <v>320</v>
       </c>
       <c r="B389" t="s">
-        <v>737</v>
+        <v>538</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>855</v>
+        <v>656</v>
       </c>
       <c r="B390" t="s">
-        <v>856</v>
+        <v>737</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>658</v>
+        <v>855</v>
       </c>
       <c r="B391" t="s">
-        <v>738</v>
+        <v>856</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="B392" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>256</v>
+        <v>653</v>
       </c>
       <c r="B393" t="s">
-        <v>539</v>
+        <v>739</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B394" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B395" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>188</v>
+        <v>261</v>
       </c>
       <c r="B396" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B397" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>936</v>
+        <v>190</v>
       </c>
       <c r="B398" t="s">
-        <v>937</v>
+        <v>543</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>1031</v>
+        <v>936</v>
       </c>
       <c r="B399" t="s">
-        <v>1032</v>
+        <v>937</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>209</v>
+        <v>1031</v>
       </c>
       <c r="B400" t="s">
-        <v>544</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>851</v>
+        <v>209</v>
       </c>
       <c r="B401" t="s">
-        <v>852</v>
+        <v>544</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>143</v>
+        <v>851</v>
       </c>
       <c r="B402" t="s">
-        <v>545</v>
+        <v>852</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B403" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>254</v>
+        <v>140</v>
       </c>
       <c r="B404" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>331</v>
+        <v>254</v>
       </c>
       <c r="B405" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>210</v>
+        <v>331</v>
       </c>
       <c r="B406" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="B407" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>73</v>
+        <v>234</v>
       </c>
       <c r="B408" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>342</v>
+        <v>73</v>
       </c>
       <c r="B409" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="B410" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>843</v>
+        <v>308</v>
       </c>
       <c r="B411" t="s">
-        <v>844</v>
+        <v>553</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B412" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>220</v>
+        <v>845</v>
       </c>
       <c r="B413" t="s">
-        <v>554</v>
+        <v>846</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>909</v>
+        <v>220</v>
       </c>
       <c r="B414" t="s">
-        <v>910</v>
+        <v>554</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>963</v>
+        <v>909</v>
       </c>
       <c r="B415" t="s">
-        <v>964</v>
+        <v>910</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>227</v>
+        <v>963</v>
       </c>
       <c r="B416" t="s">
-        <v>555</v>
+        <v>964</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>334</v>
+        <v>227</v>
       </c>
       <c r="B417" t="s">
-        <v>1161</v>
+        <v>555</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>971</v>
+        <v>334</v>
       </c>
       <c r="B418" t="s">
-        <v>972</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>778</v>
+        <v>971</v>
       </c>
       <c r="B419" t="s">
-        <v>779</v>
+        <v>972</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>294</v>
+        <v>778</v>
       </c>
       <c r="B420" t="s">
-        <v>556</v>
+        <v>779</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>952</v>
+        <v>294</v>
       </c>
       <c r="B421" t="s">
-        <v>953</v>
+        <v>556</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>339</v>
+        <v>952</v>
       </c>
       <c r="B422" t="s">
-        <v>557</v>
+        <v>953</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>780</v>
+        <v>339</v>
       </c>
       <c r="B423" t="s">
-        <v>779</v>
+        <v>557</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>340</v>
+        <v>780</v>
       </c>
       <c r="B424" t="s">
-        <v>558</v>
+        <v>779</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B425" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>645</v>
+        <v>341</v>
       </c>
       <c r="B426" t="s">
-        <v>740</v>
+        <v>559</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>39</v>
+        <v>645</v>
       </c>
       <c r="B427" t="s">
-        <v>560</v>
+        <v>740</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B428" t="s">
-        <v>1129</v>
+        <v>560</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>343</v>
+        <v>38</v>
       </c>
       <c r="B429" t="s">
-        <v>561</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>107</v>
+        <v>343</v>
       </c>
       <c r="B430" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>1029</v>
+        <v>107</v>
       </c>
       <c r="B431" t="s">
-        <v>1030</v>
+        <v>562</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>903</v>
+        <v>1029</v>
       </c>
       <c r="B432" t="s">
-        <v>904</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>117</v>
+        <v>903</v>
       </c>
       <c r="B433" t="s">
-        <v>563</v>
+        <v>904</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>1025</v>
+        <v>117</v>
       </c>
       <c r="B434" t="s">
-        <v>1026</v>
+        <v>563</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>98</v>
+        <v>1025</v>
       </c>
       <c r="B435" t="s">
-        <v>564</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B436" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>666</v>
+        <v>99</v>
       </c>
       <c r="B437" t="s">
-        <v>741</v>
+        <v>565</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>1107</v>
+        <v>666</v>
       </c>
       <c r="B438" t="s">
-        <v>1024</v>
+        <v>741</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>823</v>
+        <v>1107</v>
       </c>
       <c r="B439" t="s">
-        <v>824</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>113</v>
+        <v>823</v>
       </c>
       <c r="B440" t="s">
-        <v>566</v>
+        <v>824</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>889</v>
+        <v>113</v>
       </c>
       <c r="B441" t="s">
-        <v>890</v>
+        <v>566</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>45</v>
+        <v>889</v>
       </c>
       <c r="B442" t="s">
-        <v>1128</v>
+        <v>890</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>290</v>
+        <v>45</v>
       </c>
       <c r="B443" t="s">
-        <v>567</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B444" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>47</v>
+        <v>299</v>
       </c>
       <c r="B445" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>847</v>
+        <v>47</v>
       </c>
       <c r="B446" t="s">
-        <v>848</v>
+        <v>569</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>51</v>
+        <v>847</v>
       </c>
       <c r="B447" t="s">
-        <v>570</v>
+        <v>848</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>871</v>
+        <v>51</v>
       </c>
       <c r="B448" t="s">
-        <v>872</v>
+        <v>570</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>114</v>
+        <v>871</v>
       </c>
       <c r="B449" t="s">
-        <v>571</v>
+        <v>872</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>853</v>
+        <v>114</v>
       </c>
       <c r="B450" t="s">
-        <v>854</v>
+        <v>571</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>144</v>
+        <v>853</v>
       </c>
       <c r="B451" t="s">
-        <v>572</v>
+        <v>854</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>1080</v>
+        <v>144</v>
       </c>
       <c r="B452" t="s">
-        <v>1081</v>
+        <v>572</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>176</v>
+        <v>1080</v>
       </c>
       <c r="B453" t="s">
-        <v>573</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>316</v>
+        <v>176</v>
       </c>
       <c r="B454" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>29</v>
+        <v>316</v>
       </c>
       <c r="B455" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>1104</v>
+        <v>29</v>
       </c>
       <c r="B456" t="s">
-        <v>1105</v>
+        <v>575</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>1018</v>
+        <v>1104</v>
       </c>
       <c r="B457" t="s">
-        <v>1019</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>293</v>
+        <v>1018</v>
       </c>
       <c r="B458" t="s">
-        <v>576</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>981</v>
+        <v>293</v>
       </c>
       <c r="B459" t="s">
-        <v>982</v>
+        <v>576</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>301</v>
+        <v>981</v>
       </c>
       <c r="B460" t="s">
-        <v>577</v>
+        <v>982</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>1003</v>
+        <v>301</v>
       </c>
       <c r="B461" t="s">
-        <v>1004</v>
+        <v>577</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="B462" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>75</v>
+        <v>1007</v>
       </c>
       <c r="B463" t="s">
-        <v>578</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B464" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B465" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>329</v>
+        <v>78</v>
       </c>
       <c r="B466" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>752</v>
+        <v>329</v>
       </c>
       <c r="B467" t="s">
-        <v>753</v>
+        <v>581</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>805</v>
+        <v>752</v>
       </c>
       <c r="B468" t="s">
-        <v>806</v>
+        <v>753</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>135</v>
+        <v>805</v>
       </c>
       <c r="B469" t="s">
-        <v>582</v>
+        <v>806</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>1038</v>
+        <v>135</v>
       </c>
       <c r="B470" t="s">
-        <v>1039</v>
+        <v>582</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>215</v>
+        <v>1038</v>
       </c>
       <c r="B471" t="s">
-        <v>583</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>935</v>
+        <v>215</v>
       </c>
       <c r="B472" t="s">
-        <v>1145</v>
+        <v>583</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>216</v>
+        <v>935</v>
       </c>
       <c r="B473" t="s">
-        <v>1126</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>317</v>
+        <v>216</v>
       </c>
       <c r="B474" t="s">
-        <v>584</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>1082</v>
+        <v>317</v>
       </c>
       <c r="B475" t="s">
-        <v>1083</v>
+        <v>584</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>214</v>
+        <v>1082</v>
       </c>
       <c r="B476" t="s">
-        <v>1127</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>999</v>
+        <v>214</v>
       </c>
       <c r="B477" t="s">
-        <v>1000</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B478" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>225</v>
+        <v>1001</v>
       </c>
       <c r="B479" t="s">
-        <v>585</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>948</v>
+        <v>225</v>
       </c>
       <c r="B480" t="s">
-        <v>949</v>
+        <v>585</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>1098</v>
+        <v>948</v>
       </c>
       <c r="B481" t="s">
-        <v>1099</v>
+        <v>949</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>1048</v>
+        <v>1098</v>
       </c>
       <c r="B482" t="s">
-        <v>1049</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>93</v>
+        <v>1048</v>
       </c>
       <c r="B483" t="s">
-        <v>586</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="B484" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>783</v>
+        <v>120</v>
       </c>
       <c r="B485" t="s">
-        <v>784</v>
+        <v>587</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>133</v>
+        <v>783</v>
       </c>
       <c r="B486" t="s">
-        <v>588</v>
+        <v>784</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="B487" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B488" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>825</v>
+        <v>66</v>
       </c>
       <c r="B489" t="s">
-        <v>826</v>
+        <v>590</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>950</v>
+        <v>825</v>
       </c>
       <c r="B490" t="s">
-        <v>951</v>
+        <v>826</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>79</v>
+        <v>950</v>
       </c>
       <c r="B491" t="s">
-        <v>591</v>
+        <v>951</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="B492" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="B493" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>181</v>
+        <v>122</v>
       </c>
       <c r="B494" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>801</v>
+        <v>1184</v>
       </c>
       <c r="B495" t="s">
-        <v>802</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>691</v>
+        <v>181</v>
       </c>
       <c r="B496" t="s">
-        <v>742</v>
+        <v>594</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>1151</v>
+        <v>801</v>
       </c>
       <c r="B497" t="s">
-        <v>1152</v>
+        <v>802</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>1149</v>
+        <v>691</v>
       </c>
       <c r="B498" t="s">
-        <v>1150</v>
+        <v>742</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>284</v>
+        <v>1151</v>
       </c>
       <c r="B499" t="s">
-        <v>595</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>973</v>
+        <v>1149</v>
       </c>
       <c r="B500" t="s">
-        <v>974</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>841</v>
+        <v>284</v>
       </c>
       <c r="B501" t="s">
-        <v>842</v>
+        <v>595</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>283</v>
+        <v>973</v>
       </c>
       <c r="B502" t="s">
-        <v>596</v>
+        <v>974</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>883</v>
+        <v>841</v>
       </c>
       <c r="B503" t="s">
-        <v>884</v>
+        <v>842</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>1180</v>
+        <v>283</v>
       </c>
       <c r="B504" t="s">
-        <v>1181</v>
+        <v>596</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>756</v>
+        <v>883</v>
       </c>
       <c r="B505" t="s">
-        <v>757</v>
+        <v>884</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>1078</v>
+        <v>1180</v>
       </c>
       <c r="B506" t="s">
-        <v>1079</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>67</v>
+        <v>756</v>
       </c>
       <c r="B507" t="s">
-        <v>597</v>
+        <v>757</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>68</v>
+        <v>1078</v>
       </c>
       <c r="B508" t="s">
-        <v>598</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="B509" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>289</v>
+        <v>68</v>
       </c>
       <c r="B510" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>297</v>
+        <v>95</v>
       </c>
       <c r="B511" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="B512" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>193</v>
+        <v>297</v>
       </c>
       <c r="B513" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>901</v>
+        <v>264</v>
       </c>
       <c r="B514" t="s">
-        <v>902</v>
+        <v>602</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>44</v>
+        <v>193</v>
       </c>
       <c r="B515" t="s">
-        <v>1125</v>
+        <v>603</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>1070</v>
+        <v>901</v>
       </c>
       <c r="B516" t="s">
-        <v>1071</v>
+        <v>902</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>324</v>
+        <v>44</v>
       </c>
       <c r="B517" t="s">
-        <v>604</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>325</v>
+        <v>1070</v>
       </c>
       <c r="B518" t="s">
-        <v>605</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>849</v>
+        <v>324</v>
       </c>
       <c r="B519" t="s">
-        <v>850</v>
+        <v>604</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>887</v>
+        <v>325</v>
       </c>
       <c r="B520" t="s">
-        <v>888</v>
+        <v>605</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>869</v>
+        <v>849</v>
       </c>
       <c r="B521" t="s">
-        <v>870</v>
+        <v>850</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>33</v>
+        <v>887</v>
       </c>
       <c r="B522" t="s">
-        <v>606</v>
+        <v>888</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>36</v>
+        <v>869</v>
       </c>
       <c r="B523" t="s">
-        <v>607</v>
+        <v>870</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>1143</v>
+        <v>33</v>
       </c>
       <c r="B524" t="s">
-        <v>1144</v>
+        <v>606</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>309</v>
+        <v>36</v>
       </c>
       <c r="B525" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>257</v>
+        <v>1143</v>
       </c>
       <c r="B526" t="s">
-        <v>609</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B527" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>228</v>
+        <v>257</v>
       </c>
       <c r="B528" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>17</v>
+        <v>302</v>
       </c>
       <c r="B529" t="s">
-        <v>18</v>
+        <v>610</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>655</v>
+        <v>228</v>
       </c>
       <c r="B530" t="s">
-        <v>743</v>
+        <v>611</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>785</v>
+        <v>17</v>
       </c>
       <c r="B531" t="s">
-        <v>786</v>
+        <v>18</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>142</v>
+        <v>655</v>
       </c>
       <c r="B532" t="s">
-        <v>612</v>
+        <v>743</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>1178</v>
+        <v>785</v>
       </c>
       <c r="B533" t="s">
-        <v>1179</v>
+        <v>786</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>956</v>
+        <v>142</v>
       </c>
       <c r="B534" t="s">
-        <v>957</v>
+        <v>612</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>54</v>
+        <v>1178</v>
       </c>
       <c r="B535" t="s">
-        <v>613</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>265</v>
+        <v>956</v>
       </c>
       <c r="B536" t="s">
-        <v>614</v>
+        <v>957</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>976</v>
+        <v>54</v>
       </c>
       <c r="B537" t="s">
-        <v>975</v>
+        <v>613</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>56</v>
+        <v>265</v>
       </c>
       <c r="B538" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>185</v>
+        <v>976</v>
       </c>
       <c r="B539" t="s">
-        <v>616</v>
+        <v>975</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="B540" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>43</v>
+        <v>185</v>
       </c>
       <c r="B541" t="s">
-        <v>1146</v>
+        <v>616</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>40</v>
+        <v>159</v>
       </c>
       <c r="B542" t="s">
-        <v>1124</v>
+        <v>617</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>1170</v>
+        <v>43</v>
       </c>
       <c r="B543" t="s">
-        <v>1171</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>165</v>
+        <v>40</v>
       </c>
       <c r="B544" t="s">
-        <v>618</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>12</v>
+        <v>1170</v>
       </c>
       <c r="B545" t="s">
-        <v>11</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>250</v>
+        <v>165</v>
       </c>
       <c r="B546" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B547" t="s">
-        <v>620</v>
+        <v>11</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>1040</v>
+        <v>250</v>
       </c>
       <c r="B548" t="s">
-        <v>1041</v>
+        <v>619</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B549" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>255</v>
+        <v>1040</v>
       </c>
       <c r="B550" t="s">
-        <v>622</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>795</v>
+        <v>28</v>
       </c>
       <c r="B551" t="s">
-        <v>796</v>
+        <v>621</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="B552" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>661</v>
+        <v>795</v>
       </c>
       <c r="B553" t="s">
-        <v>744</v>
+        <v>796</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>662</v>
+        <v>267</v>
       </c>
       <c r="B554" t="s">
-        <v>745</v>
+        <v>623</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>139</v>
+        <v>661</v>
       </c>
       <c r="B555" t="s">
-        <v>624</v>
+        <v>744</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>7</v>
+        <v>662</v>
       </c>
       <c r="B556" t="s">
-        <v>2</v>
+        <v>745</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="B557" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>1034</v>
+        <v>7</v>
       </c>
       <c r="B558" t="s">
-        <v>1123</v>
+        <v>2</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>865</v>
+        <v>105</v>
       </c>
       <c r="B559" t="s">
-        <v>866</v>
+        <v>625</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B560" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>292</v>
+        <v>865</v>
       </c>
       <c r="B561" t="s">
-        <v>626</v>
+        <v>866</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>8</v>
+        <v>1035</v>
       </c>
       <c r="B562" t="s">
-        <v>11</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>335</v>
+        <v>292</v>
       </c>
       <c r="B563" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>332</v>
+        <v>8</v>
       </c>
       <c r="B564" t="s">
-        <v>628</v>
+        <v>11</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>259</v>
+        <v>335</v>
       </c>
       <c r="B565" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="B566" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>859</v>
+        <v>259</v>
       </c>
       <c r="B567" t="s">
-        <v>860</v>
+        <v>629</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>1174</v>
+        <v>319</v>
       </c>
       <c r="B568" t="s">
-        <v>1175</v>
+        <v>630</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>268</v>
+        <v>859</v>
       </c>
       <c r="B569" t="s">
-        <v>631</v>
+        <v>860</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>271</v>
+        <v>1174</v>
       </c>
       <c r="B570" t="s">
-        <v>1117</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B571" t="s">
-        <v>1118</v>
+        <v>631</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B572" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B573" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B574" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B575" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>92</v>
+        <v>269</v>
       </c>
       <c r="B576" t="s">
-        <v>632</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>200</v>
+        <v>272</v>
       </c>
       <c r="B577" t="s">
-        <v>633</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>203</v>
+        <v>92</v>
       </c>
       <c r="B578" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="B579" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>693</v>
+        <v>203</v>
       </c>
       <c r="B580" t="s">
-        <v>746</v>
+        <v>634</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>252</v>
+        <v>172</v>
       </c>
       <c r="B581" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B582" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>189</v>
+        <v>252</v>
       </c>
       <c r="B583" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>989</v>
+        <v>694</v>
       </c>
       <c r="B584" t="s">
-        <v>990</v>
+        <v>747</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>311</v>
+        <v>189</v>
       </c>
       <c r="B585" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>312</v>
+        <v>989</v>
       </c>
       <c r="B586" t="s">
-        <v>639</v>
+        <v>990</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>1033</v>
+        <v>311</v>
       </c>
       <c r="B587" t="s">
-        <v>1115</v>
+        <v>638</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>1005</v>
+        <v>312</v>
       </c>
       <c r="B588" t="s">
-        <v>1006</v>
+        <v>639</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>81</v>
+        <v>1033</v>
       </c>
       <c r="B589" t="s">
-        <v>640</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>651</v>
+        <v>1005</v>
       </c>
       <c r="B590" t="s">
-        <v>748</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>922</v>
+        <v>81</v>
       </c>
       <c r="B591" t="s">
-        <v>923</v>
+        <v>640</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>642</v>
+        <v>651</v>
       </c>
       <c r="B592" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>969</v>
+        <v>922</v>
       </c>
       <c r="B593" t="s">
-        <v>970</v>
+        <v>923</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
+        <v>642</v>
+      </c>
+      <c r="B594" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A595" t="s">
+        <v>969</v>
+      </c>
+      <c r="B595" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A596" t="s">
         <v>1162</v>
       </c>
-      <c r="B594" t="s">
+      <c r="B596" t="s">
         <v>1163</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE8513B0-56BF-4367-A2DD-D16AB3CE1B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F101A8A-6051-48BB-A766-8466C343B4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="1186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="1196">
   <si>
     <t>trigger</t>
   </si>
@@ -3583,6 +3583,36 @@
   </si>
   <si>
     <t>reaction</t>
+  </si>
+  <si>
+    <t>rca</t>
+  </si>
+  <si>
+    <t>right coronary artery</t>
+  </si>
+  <si>
+    <t>pda</t>
+  </si>
+  <si>
+    <t>posterior descending artery</t>
+  </si>
+  <si>
+    <t>lca</t>
+  </si>
+  <si>
+    <t>left coronary artery</t>
+  </si>
+  <si>
+    <t>lad</t>
+  </si>
+  <si>
+    <t>left anterior descending artery</t>
+  </si>
+  <si>
+    <t>lcx</t>
+  </si>
+  <si>
+    <t>left circumflex artery</t>
   </si>
 </sst>
 </file>
@@ -3638,10 +3668,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B596" totalsRowShown="0">
-  <autoFilter ref="A1:B596" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B596">
-    <sortCondition ref="A1:A596"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B601" totalsRowShown="0">
+  <autoFilter ref="A1:B601" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B601">
+    <sortCondition ref="A1:A601"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -3914,7 +3944,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B596"/>
+  <dimension ref="A1:B601"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -6235,1079 +6265,1079 @@
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>280</v>
+        <v>1192</v>
       </c>
       <c r="B290" t="s">
-        <v>486</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B291" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>49</v>
+        <v>281</v>
       </c>
       <c r="B292" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B293" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="B294" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="B295" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>221</v>
+        <v>72</v>
       </c>
       <c r="B296" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>15</v>
+        <v>1190</v>
       </c>
       <c r="B297" t="s">
-        <v>16</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>1060</v>
+        <v>221</v>
       </c>
       <c r="B298" t="s">
-        <v>1061</v>
+        <v>492</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>920</v>
+        <v>1194</v>
       </c>
       <c r="B299" t="s">
-        <v>921</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="B300" t="s">
-        <v>493</v>
+        <v>16</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>241</v>
+        <v>1060</v>
       </c>
       <c r="B301" t="s">
-        <v>494</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>328</v>
+        <v>920</v>
       </c>
       <c r="B302" t="s">
-        <v>495</v>
+        <v>921</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>1100</v>
+        <v>108</v>
       </c>
       <c r="B303" t="s">
-        <v>1101</v>
+        <v>493</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>1052</v>
+        <v>241</v>
       </c>
       <c r="B304" t="s">
-        <v>1053</v>
+        <v>494</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>121</v>
+        <v>328</v>
       </c>
       <c r="B305" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>750</v>
+        <v>1100</v>
       </c>
       <c r="B306" t="s">
-        <v>751</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>781</v>
+        <v>1052</v>
       </c>
       <c r="B307" t="s">
-        <v>782</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="B308" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>63</v>
+        <v>750</v>
       </c>
       <c r="B309" t="s">
-        <v>498</v>
+        <v>751</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>224</v>
+        <v>781</v>
       </c>
       <c r="B310" t="s">
-        <v>499</v>
+        <v>782</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>25</v>
+        <v>134</v>
       </c>
       <c r="B311" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="B312" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="B313" t="s">
-        <v>1133</v>
+        <v>499</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>960</v>
+        <v>25</v>
       </c>
       <c r="B314" t="s">
-        <v>1134</v>
+        <v>500</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>1113</v>
+        <v>26</v>
       </c>
       <c r="B315" t="s">
-        <v>1114</v>
+        <v>501</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B316" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>202</v>
+        <v>960</v>
       </c>
       <c r="B317" t="s">
-        <v>502</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>205</v>
+        <v>1113</v>
       </c>
       <c r="B318" t="s">
-        <v>503</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="B319" t="s">
-        <v>504</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>663</v>
+        <v>202</v>
       </c>
       <c r="B320" t="s">
-        <v>734</v>
+        <v>502</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="B321" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>1088</v>
+        <v>145</v>
       </c>
       <c r="B322" t="s">
-        <v>1089</v>
+        <v>504</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>263</v>
+        <v>663</v>
       </c>
       <c r="B323" t="s">
-        <v>506</v>
+        <v>734</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>1090</v>
+        <v>171</v>
       </c>
       <c r="B324" t="s">
-        <v>1091</v>
+        <v>505</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>80</v>
+        <v>1088</v>
       </c>
       <c r="B325" t="s">
-        <v>507</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>65</v>
+        <v>263</v>
       </c>
       <c r="B326" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>191</v>
+        <v>1090</v>
       </c>
       <c r="B327" t="s">
-        <v>509</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="B328" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>192</v>
+        <v>65</v>
       </c>
       <c r="B329" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="B330" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>233</v>
+        <v>123</v>
       </c>
       <c r="B331" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>31</v>
+        <v>192</v>
       </c>
       <c r="B332" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>30</v>
+        <v>231</v>
       </c>
       <c r="B333" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>37</v>
+        <v>233</v>
       </c>
       <c r="B334" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="B335" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>306</v>
+        <v>30</v>
       </c>
       <c r="B336" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>222</v>
+        <v>37</v>
       </c>
       <c r="B337" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>315</v>
+        <v>71</v>
       </c>
       <c r="B338" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="B339" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>279</v>
+        <v>222</v>
       </c>
       <c r="B340" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>831</v>
+        <v>315</v>
       </c>
       <c r="B341" t="s">
-        <v>832</v>
+        <v>520</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>48</v>
+        <v>278</v>
       </c>
       <c r="B342" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>146</v>
+        <v>279</v>
       </c>
       <c r="B343" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>52</v>
+        <v>831</v>
       </c>
       <c r="B344" t="s">
-        <v>525</v>
+        <v>832</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>223</v>
+        <v>48</v>
       </c>
       <c r="B345" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>1094</v>
+        <v>146</v>
       </c>
       <c r="B346" t="s">
-        <v>1095</v>
+        <v>524</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>1109</v>
+        <v>52</v>
       </c>
       <c r="B347" t="s">
-        <v>1112</v>
+        <v>525</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>1050</v>
+        <v>223</v>
       </c>
       <c r="B348" t="s">
-        <v>1051</v>
+        <v>526</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>96</v>
+        <v>1094</v>
       </c>
       <c r="B349" t="s">
-        <v>527</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>248</v>
+        <v>1109</v>
       </c>
       <c r="B350" t="s">
-        <v>528</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>249</v>
+        <v>1050</v>
       </c>
       <c r="B351" t="s">
-        <v>529</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B352" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>1064</v>
+        <v>248</v>
       </c>
       <c r="B353" t="s">
-        <v>1065</v>
+        <v>528</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
       <c r="B354" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>916</v>
+        <v>94</v>
       </c>
       <c r="B355" t="s">
-        <v>917</v>
+        <v>530</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>914</v>
+        <v>1064</v>
       </c>
       <c r="B356" t="s">
-        <v>915</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>918</v>
+        <v>212</v>
       </c>
       <c r="B357" t="s">
-        <v>919</v>
+        <v>531</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>330</v>
+        <v>916</v>
       </c>
       <c r="B358" t="s">
-        <v>532</v>
+        <v>917</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>1066</v>
+        <v>914</v>
       </c>
       <c r="B359" t="s">
-        <v>1067</v>
+        <v>915</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>995</v>
+        <v>918</v>
       </c>
       <c r="B360" t="s">
-        <v>996</v>
+        <v>919</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>991</v>
+        <v>330</v>
       </c>
       <c r="B361" t="s">
-        <v>992</v>
+        <v>532</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>993</v>
+        <v>1066</v>
       </c>
       <c r="B362" t="s">
-        <v>994</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>82</v>
+        <v>995</v>
       </c>
       <c r="B363" t="s">
-        <v>533</v>
+        <v>996</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>772</v>
+        <v>991</v>
       </c>
       <c r="B364" t="s">
-        <v>773</v>
+        <v>992</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>197</v>
+        <v>993</v>
       </c>
       <c r="B365" t="s">
-        <v>534</v>
+        <v>994</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>654</v>
+        <v>82</v>
       </c>
       <c r="B366" t="s">
-        <v>735</v>
+        <v>533</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>821</v>
+        <v>772</v>
       </c>
       <c r="B367" t="s">
-        <v>822</v>
+        <v>773</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>1068</v>
+        <v>197</v>
       </c>
       <c r="B368" t="s">
-        <v>1069</v>
+        <v>534</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>3</v>
+        <v>654</v>
       </c>
       <c r="B369" t="s">
-        <v>4</v>
+        <v>735</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>958</v>
+        <v>821</v>
       </c>
       <c r="B370" t="s">
-        <v>4</v>
+        <v>822</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>959</v>
+        <v>1068</v>
       </c>
       <c r="B371" t="s">
-        <v>4</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>664</v>
+        <v>3</v>
       </c>
       <c r="B372" t="s">
-        <v>736</v>
+        <v>4</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>770</v>
+        <v>958</v>
       </c>
       <c r="B373" t="s">
-        <v>771</v>
+        <v>4</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>85</v>
+        <v>959</v>
       </c>
       <c r="B374" t="s">
-        <v>535</v>
+        <v>4</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>1062</v>
+        <v>664</v>
       </c>
       <c r="B375" t="s">
-        <v>1063</v>
+        <v>736</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>829</v>
+        <v>770</v>
       </c>
       <c r="B376" t="s">
-        <v>830</v>
+        <v>771</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>809</v>
+        <v>85</v>
       </c>
       <c r="B377" t="s">
-        <v>810</v>
+        <v>535</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>187</v>
+        <v>1062</v>
       </c>
       <c r="B378" t="s">
-        <v>536</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="B379" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>934</v>
+        <v>809</v>
       </c>
       <c r="B380" t="s">
-        <v>1130</v>
+        <v>810</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>863</v>
+        <v>187</v>
       </c>
       <c r="B381" t="s">
-        <v>864</v>
+        <v>536</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>1044</v>
+        <v>827</v>
       </c>
       <c r="B382" t="s">
-        <v>1045</v>
+        <v>828</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>798</v>
+        <v>934</v>
       </c>
       <c r="B383" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>797</v>
+        <v>863</v>
       </c>
       <c r="B384" t="s">
-        <v>1132</v>
+        <v>864</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>13</v>
+        <v>1044</v>
       </c>
       <c r="B385" t="s">
-        <v>14</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>817</v>
+        <v>798</v>
       </c>
       <c r="B386" t="s">
-        <v>818</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>186</v>
+        <v>797</v>
       </c>
       <c r="B387" t="s">
-        <v>537</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>811</v>
+        <v>13</v>
       </c>
       <c r="B388" t="s">
-        <v>812</v>
+        <v>14</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>320</v>
+        <v>817</v>
       </c>
       <c r="B389" t="s">
-        <v>538</v>
+        <v>818</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>656</v>
+        <v>186</v>
       </c>
       <c r="B390" t="s">
-        <v>737</v>
+        <v>537</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>855</v>
+        <v>811</v>
       </c>
       <c r="B391" t="s">
-        <v>856</v>
+        <v>812</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>658</v>
+        <v>320</v>
       </c>
       <c r="B392" t="s">
-        <v>738</v>
+        <v>538</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B393" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>256</v>
+        <v>855</v>
       </c>
       <c r="B394" t="s">
-        <v>539</v>
+        <v>856</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>260</v>
+        <v>658</v>
       </c>
       <c r="B395" t="s">
-        <v>540</v>
+        <v>738</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>261</v>
+        <v>653</v>
       </c>
       <c r="B396" t="s">
-        <v>541</v>
+        <v>739</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>188</v>
+        <v>256</v>
       </c>
       <c r="B397" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="B398" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>936</v>
+        <v>261</v>
       </c>
       <c r="B399" t="s">
-        <v>937</v>
+        <v>541</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>1031</v>
+        <v>188</v>
       </c>
       <c r="B400" t="s">
-        <v>1032</v>
+        <v>542</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="B401" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>851</v>
+        <v>936</v>
       </c>
       <c r="B402" t="s">
-        <v>852</v>
+        <v>937</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>143</v>
+        <v>1031</v>
       </c>
       <c r="B403" t="s">
-        <v>545</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>140</v>
+        <v>209</v>
       </c>
       <c r="B404" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>254</v>
+        <v>851</v>
       </c>
       <c r="B405" t="s">
-        <v>547</v>
+        <v>852</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>331</v>
+        <v>143</v>
       </c>
       <c r="B406" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="B407" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="B408" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>73</v>
+        <v>331</v>
       </c>
       <c r="B409" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>342</v>
+        <v>210</v>
       </c>
       <c r="B410" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>308</v>
+        <v>234</v>
       </c>
       <c r="B411" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>843</v>
+        <v>73</v>
       </c>
       <c r="B412" t="s">
-        <v>844</v>
+        <v>551</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>845</v>
+        <v>342</v>
       </c>
       <c r="B413" t="s">
-        <v>846</v>
+        <v>552</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>220</v>
+        <v>308</v>
       </c>
       <c r="B414" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>909</v>
+        <v>843</v>
       </c>
       <c r="B415" t="s">
-        <v>910</v>
+        <v>844</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>963</v>
+        <v>845</v>
       </c>
       <c r="B416" t="s">
-        <v>964</v>
+        <v>846</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B417" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>334</v>
+        <v>909</v>
       </c>
       <c r="B418" t="s">
-        <v>1161</v>
+        <v>910</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>971</v>
+        <v>963</v>
       </c>
       <c r="B419" t="s">
-        <v>972</v>
+        <v>964</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>778</v>
+        <v>1188</v>
       </c>
       <c r="B420" t="s">
-        <v>779</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>294</v>
+        <v>227</v>
       </c>
       <c r="B421" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>952</v>
+        <v>334</v>
       </c>
       <c r="B422" t="s">
-        <v>953</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>339</v>
+        <v>971</v>
       </c>
       <c r="B423" t="s">
-        <v>557</v>
+        <v>972</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B424" t="s">
         <v>779</v>
@@ -7315,1377 +7345,1417 @@
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>340</v>
+        <v>294</v>
       </c>
       <c r="B425" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>341</v>
+        <v>952</v>
       </c>
       <c r="B426" t="s">
-        <v>559</v>
+        <v>953</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>645</v>
+        <v>339</v>
       </c>
       <c r="B427" t="s">
-        <v>740</v>
+        <v>557</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>39</v>
+        <v>780</v>
       </c>
       <c r="B428" t="s">
-        <v>560</v>
+        <v>779</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>38</v>
+        <v>340</v>
       </c>
       <c r="B429" t="s">
-        <v>1129</v>
+        <v>558</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B430" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>107</v>
+        <v>645</v>
       </c>
       <c r="B431" t="s">
-        <v>562</v>
+        <v>740</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>1029</v>
+        <v>39</v>
       </c>
       <c r="B432" t="s">
-        <v>1030</v>
+        <v>560</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>903</v>
+        <v>38</v>
       </c>
       <c r="B433" t="s">
-        <v>904</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>117</v>
+        <v>343</v>
       </c>
       <c r="B434" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>1025</v>
+        <v>107</v>
       </c>
       <c r="B435" t="s">
-        <v>1026</v>
+        <v>562</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>98</v>
+        <v>1029</v>
       </c>
       <c r="B436" t="s">
-        <v>564</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>99</v>
+        <v>903</v>
       </c>
       <c r="B437" t="s">
-        <v>565</v>
+        <v>904</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>666</v>
+        <v>117</v>
       </c>
       <c r="B438" t="s">
-        <v>741</v>
+        <v>563</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>1107</v>
+        <v>1025</v>
       </c>
       <c r="B439" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>823</v>
+        <v>98</v>
       </c>
       <c r="B440" t="s">
-        <v>824</v>
+        <v>564</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="B441" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>889</v>
+        <v>666</v>
       </c>
       <c r="B442" t="s">
-        <v>890</v>
+        <v>741</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>45</v>
+        <v>1107</v>
       </c>
       <c r="B443" t="s">
-        <v>1128</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>290</v>
+        <v>823</v>
       </c>
       <c r="B444" t="s">
-        <v>567</v>
+        <v>824</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>299</v>
+        <v>113</v>
       </c>
       <c r="B445" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>47</v>
+        <v>889</v>
       </c>
       <c r="B446" t="s">
-        <v>569</v>
+        <v>890</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>847</v>
+        <v>45</v>
       </c>
       <c r="B447" t="s">
-        <v>848</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>51</v>
+        <v>290</v>
       </c>
       <c r="B448" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>871</v>
+        <v>299</v>
       </c>
       <c r="B449" t="s">
-        <v>872</v>
+        <v>568</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>114</v>
+        <v>47</v>
       </c>
       <c r="B450" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="B451" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>144</v>
+        <v>51</v>
       </c>
       <c r="B452" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>1080</v>
+        <v>871</v>
       </c>
       <c r="B453" t="s">
-        <v>1081</v>
+        <v>872</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>176</v>
+        <v>114</v>
       </c>
       <c r="B454" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>316</v>
+        <v>853</v>
       </c>
       <c r="B455" t="s">
-        <v>574</v>
+        <v>854</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>29</v>
+        <v>144</v>
       </c>
       <c r="B456" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>1104</v>
+        <v>1080</v>
       </c>
       <c r="B457" t="s">
-        <v>1105</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>1018</v>
+        <v>176</v>
       </c>
       <c r="B458" t="s">
-        <v>1019</v>
+        <v>573</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="B459" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>981</v>
+        <v>29</v>
       </c>
       <c r="B460" t="s">
-        <v>982</v>
+        <v>575</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>301</v>
+        <v>1104</v>
       </c>
       <c r="B461" t="s">
-        <v>577</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>1003</v>
+        <v>1018</v>
       </c>
       <c r="B462" t="s">
-        <v>1004</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>1007</v>
+        <v>293</v>
       </c>
       <c r="B463" t="s">
-        <v>1008</v>
+        <v>576</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>75</v>
+        <v>981</v>
       </c>
       <c r="B464" t="s">
-        <v>578</v>
+        <v>982</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>76</v>
+        <v>301</v>
       </c>
       <c r="B465" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>78</v>
+        <v>1003</v>
       </c>
       <c r="B466" t="s">
-        <v>580</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>329</v>
+        <v>1007</v>
       </c>
       <c r="B467" t="s">
-        <v>581</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>752</v>
+        <v>75</v>
       </c>
       <c r="B468" t="s">
-        <v>753</v>
+        <v>578</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>805</v>
+        <v>76</v>
       </c>
       <c r="B469" t="s">
-        <v>806</v>
+        <v>579</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="B470" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>1038</v>
+        <v>329</v>
       </c>
       <c r="B471" t="s">
-        <v>1039</v>
+        <v>581</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>215</v>
+        <v>752</v>
       </c>
       <c r="B472" t="s">
-        <v>583</v>
+        <v>753</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>935</v>
+        <v>805</v>
       </c>
       <c r="B473" t="s">
-        <v>1145</v>
+        <v>806</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>216</v>
+        <v>135</v>
       </c>
       <c r="B474" t="s">
-        <v>1126</v>
+        <v>582</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>317</v>
+        <v>1186</v>
       </c>
       <c r="B475" t="s">
-        <v>584</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>1082</v>
+        <v>1038</v>
       </c>
       <c r="B476" t="s">
-        <v>1083</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B477" t="s">
-        <v>1127</v>
+        <v>583</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>999</v>
+        <v>935</v>
       </c>
       <c r="B478" t="s">
-        <v>1000</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>1001</v>
+        <v>216</v>
       </c>
       <c r="B479" t="s">
-        <v>1002</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>225</v>
+        <v>317</v>
       </c>
       <c r="B480" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>948</v>
+        <v>1082</v>
       </c>
       <c r="B481" t="s">
-        <v>949</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>1098</v>
+        <v>214</v>
       </c>
       <c r="B482" t="s">
-        <v>1099</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>1048</v>
+        <v>999</v>
       </c>
       <c r="B483" t="s">
-        <v>1049</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>93</v>
+        <v>1001</v>
       </c>
       <c r="B484" t="s">
-        <v>586</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>120</v>
+        <v>225</v>
       </c>
       <c r="B485" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>783</v>
+        <v>948</v>
       </c>
       <c r="B486" t="s">
-        <v>784</v>
+        <v>949</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>133</v>
+        <v>1098</v>
       </c>
       <c r="B487" t="s">
-        <v>588</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>62</v>
+        <v>1048</v>
       </c>
       <c r="B488" t="s">
-        <v>589</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="B489" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>825</v>
+        <v>120</v>
       </c>
       <c r="B490" t="s">
-        <v>826</v>
+        <v>587</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>950</v>
+        <v>783</v>
       </c>
       <c r="B491" t="s">
-        <v>951</v>
+        <v>784</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="B492" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B493" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="B494" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>1184</v>
+        <v>825</v>
       </c>
       <c r="B495" t="s">
-        <v>1185</v>
+        <v>826</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>181</v>
+        <v>950</v>
       </c>
       <c r="B496" t="s">
-        <v>594</v>
+        <v>951</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>801</v>
+        <v>79</v>
       </c>
       <c r="B497" t="s">
-        <v>802</v>
+        <v>591</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>691</v>
+        <v>64</v>
       </c>
       <c r="B498" t="s">
-        <v>742</v>
+        <v>592</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>1151</v>
+        <v>122</v>
       </c>
       <c r="B499" t="s">
-        <v>1152</v>
+        <v>593</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>1149</v>
+        <v>1184</v>
       </c>
       <c r="B500" t="s">
-        <v>1150</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>284</v>
+        <v>181</v>
       </c>
       <c r="B501" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>973</v>
+        <v>801</v>
       </c>
       <c r="B502" t="s">
-        <v>974</v>
+        <v>802</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>841</v>
+        <v>691</v>
       </c>
       <c r="B503" t="s">
-        <v>842</v>
+        <v>742</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>283</v>
+        <v>1151</v>
       </c>
       <c r="B504" t="s">
-        <v>596</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>883</v>
+        <v>1149</v>
       </c>
       <c r="B505" t="s">
-        <v>884</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>1180</v>
+        <v>284</v>
       </c>
       <c r="B506" t="s">
-        <v>1181</v>
+        <v>595</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>756</v>
+        <v>973</v>
       </c>
       <c r="B507" t="s">
-        <v>757</v>
+        <v>974</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>1078</v>
+        <v>841</v>
       </c>
       <c r="B508" t="s">
-        <v>1079</v>
+        <v>842</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>67</v>
+        <v>283</v>
       </c>
       <c r="B509" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>68</v>
+        <v>883</v>
       </c>
       <c r="B510" t="s">
-        <v>598</v>
+        <v>884</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>95</v>
+        <v>1180</v>
       </c>
       <c r="B511" t="s">
-        <v>599</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>289</v>
+        <v>756</v>
       </c>
       <c r="B512" t="s">
-        <v>600</v>
+        <v>757</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>297</v>
+        <v>1078</v>
       </c>
       <c r="B513" t="s">
-        <v>601</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>264</v>
+        <v>67</v>
       </c>
       <c r="B514" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>193</v>
+        <v>68</v>
       </c>
       <c r="B515" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>901</v>
+        <v>95</v>
       </c>
       <c r="B516" t="s">
-        <v>902</v>
+        <v>599</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>44</v>
+        <v>289</v>
       </c>
       <c r="B517" t="s">
-        <v>1125</v>
+        <v>600</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>1070</v>
+        <v>297</v>
       </c>
       <c r="B518" t="s">
-        <v>1071</v>
+        <v>601</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>324</v>
+        <v>264</v>
       </c>
       <c r="B519" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>325</v>
+        <v>193</v>
       </c>
       <c r="B520" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>849</v>
+        <v>901</v>
       </c>
       <c r="B521" t="s">
-        <v>850</v>
+        <v>902</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>887</v>
+        <v>44</v>
       </c>
       <c r="B522" t="s">
-        <v>888</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>869</v>
+        <v>1070</v>
       </c>
       <c r="B523" t="s">
-        <v>870</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>33</v>
+        <v>324</v>
       </c>
       <c r="B524" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>36</v>
+        <v>325</v>
       </c>
       <c r="B525" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>1143</v>
+        <v>849</v>
       </c>
       <c r="B526" t="s">
-        <v>1144</v>
+        <v>850</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>309</v>
+        <v>887</v>
       </c>
       <c r="B527" t="s">
-        <v>608</v>
+        <v>888</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>257</v>
+        <v>869</v>
       </c>
       <c r="B528" t="s">
-        <v>609</v>
+        <v>870</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>302</v>
+        <v>33</v>
       </c>
       <c r="B529" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>228</v>
+        <v>36</v>
       </c>
       <c r="B530" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>17</v>
+        <v>1143</v>
       </c>
       <c r="B531" t="s">
-        <v>18</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>655</v>
+        <v>309</v>
       </c>
       <c r="B532" t="s">
-        <v>743</v>
+        <v>608</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>785</v>
+        <v>257</v>
       </c>
       <c r="B533" t="s">
-        <v>786</v>
+        <v>609</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>142</v>
+        <v>302</v>
       </c>
       <c r="B534" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>1178</v>
+        <v>228</v>
       </c>
       <c r="B535" t="s">
-        <v>1179</v>
+        <v>611</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>956</v>
+        <v>17</v>
       </c>
       <c r="B536" t="s">
-        <v>957</v>
+        <v>18</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>54</v>
+        <v>655</v>
       </c>
       <c r="B537" t="s">
-        <v>613</v>
+        <v>743</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>265</v>
+        <v>785</v>
       </c>
       <c r="B538" t="s">
-        <v>614</v>
+        <v>786</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>976</v>
+        <v>142</v>
       </c>
       <c r="B539" t="s">
-        <v>975</v>
+        <v>612</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>56</v>
+        <v>1178</v>
       </c>
       <c r="B540" t="s">
-        <v>615</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>185</v>
+        <v>956</v>
       </c>
       <c r="B541" t="s">
-        <v>616</v>
+        <v>957</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>159</v>
+        <v>54</v>
       </c>
       <c r="B542" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>43</v>
+        <v>265</v>
       </c>
       <c r="B543" t="s">
-        <v>1146</v>
+        <v>614</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>40</v>
+        <v>976</v>
       </c>
       <c r="B544" t="s">
-        <v>1124</v>
+        <v>975</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>1170</v>
+        <v>56</v>
       </c>
       <c r="B545" t="s">
-        <v>1171</v>
+        <v>615</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="B546" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>12</v>
+        <v>159</v>
       </c>
       <c r="B547" t="s">
-        <v>11</v>
+        <v>617</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>250</v>
+        <v>43</v>
       </c>
       <c r="B548" t="s">
-        <v>619</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B549" t="s">
-        <v>620</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>1040</v>
+        <v>1170</v>
       </c>
       <c r="B550" t="s">
-        <v>1041</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>28</v>
+        <v>165</v>
       </c>
       <c r="B551" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>255</v>
+        <v>12</v>
       </c>
       <c r="B552" t="s">
-        <v>622</v>
+        <v>11</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>795</v>
+        <v>250</v>
       </c>
       <c r="B553" t="s">
-        <v>796</v>
+        <v>619</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>267</v>
+        <v>27</v>
       </c>
       <c r="B554" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>661</v>
+        <v>1040</v>
       </c>
       <c r="B555" t="s">
-        <v>744</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>662</v>
+        <v>28</v>
       </c>
       <c r="B556" t="s">
-        <v>745</v>
+        <v>621</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>139</v>
+        <v>255</v>
       </c>
       <c r="B557" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>7</v>
+        <v>795</v>
       </c>
       <c r="B558" t="s">
-        <v>2</v>
+        <v>796</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>105</v>
+        <v>267</v>
       </c>
       <c r="B559" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>1034</v>
+        <v>661</v>
       </c>
       <c r="B560" t="s">
-        <v>1123</v>
+        <v>744</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>865</v>
+        <v>662</v>
       </c>
       <c r="B561" t="s">
-        <v>866</v>
+        <v>745</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>1035</v>
+        <v>139</v>
       </c>
       <c r="B562" t="s">
-        <v>1122</v>
+        <v>624</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>292</v>
+        <v>7</v>
       </c>
       <c r="B563" t="s">
-        <v>626</v>
+        <v>2</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B564" t="s">
-        <v>11</v>
+        <v>625</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>335</v>
+        <v>1034</v>
       </c>
       <c r="B565" t="s">
-        <v>627</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>332</v>
+        <v>865</v>
       </c>
       <c r="B566" t="s">
-        <v>628</v>
+        <v>866</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>259</v>
+        <v>1035</v>
       </c>
       <c r="B567" t="s">
-        <v>629</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>319</v>
+        <v>292</v>
       </c>
       <c r="B568" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>859</v>
+        <v>8</v>
       </c>
       <c r="B569" t="s">
-        <v>860</v>
+        <v>11</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>1174</v>
+        <v>335</v>
       </c>
       <c r="B570" t="s">
-        <v>1175</v>
+        <v>627</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="B571" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="B572" t="s">
-        <v>1117</v>
+        <v>629</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="B573" t="s">
-        <v>1118</v>
+        <v>630</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>270</v>
+        <v>859</v>
       </c>
       <c r="B574" t="s">
-        <v>1119</v>
+        <v>860</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>273</v>
+        <v>1174</v>
       </c>
       <c r="B575" t="s">
-        <v>1120</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B576" t="s">
-        <v>1121</v>
+        <v>631</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B577" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>92</v>
+        <v>274</v>
       </c>
       <c r="B578" t="s">
-        <v>632</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="B579" t="s">
-        <v>633</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>203</v>
+        <v>273</v>
       </c>
       <c r="B580" t="s">
-        <v>634</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>172</v>
+        <v>269</v>
       </c>
       <c r="B581" t="s">
-        <v>635</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>693</v>
+        <v>272</v>
       </c>
       <c r="B582" t="s">
-        <v>746</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>252</v>
+        <v>92</v>
       </c>
       <c r="B583" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>694</v>
+        <v>200</v>
       </c>
       <c r="B584" t="s">
-        <v>747</v>
+        <v>633</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="B585" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>989</v>
+        <v>172</v>
       </c>
       <c r="B586" t="s">
-        <v>990</v>
+        <v>635</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>311</v>
+        <v>693</v>
       </c>
       <c r="B587" t="s">
-        <v>638</v>
+        <v>746</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>312</v>
+        <v>252</v>
       </c>
       <c r="B588" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>1033</v>
+        <v>694</v>
       </c>
       <c r="B589" t="s">
-        <v>1115</v>
+        <v>747</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>1005</v>
+        <v>189</v>
       </c>
       <c r="B590" t="s">
-        <v>1006</v>
+        <v>637</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>81</v>
+        <v>989</v>
       </c>
       <c r="B591" t="s">
-        <v>640</v>
+        <v>990</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>651</v>
+        <v>311</v>
       </c>
       <c r="B592" t="s">
-        <v>748</v>
+        <v>638</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>922</v>
+        <v>312</v>
       </c>
       <c r="B593" t="s">
-        <v>923</v>
+        <v>639</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>642</v>
+        <v>1033</v>
       </c>
       <c r="B594" t="s">
-        <v>749</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>969</v>
+        <v>1005</v>
       </c>
       <c r="B595" t="s">
-        <v>970</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
+        <v>81</v>
+      </c>
+      <c r="B596" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A597" t="s">
+        <v>651</v>
+      </c>
+      <c r="B597" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A598" t="s">
+        <v>922</v>
+      </c>
+      <c r="B598" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A599" t="s">
+        <v>642</v>
+      </c>
+      <c r="B599" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A600" t="s">
+        <v>969</v>
+      </c>
+      <c r="B600" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A601" t="s">
         <v>1162</v>
       </c>
-      <c r="B596" t="s">
+      <c r="B601" t="s">
         <v>1163</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F101A8A-6051-48BB-A766-8466C343B4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E5168C-1D5E-4C61-8079-AB3CA10ED0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="1196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="1198">
   <si>
     <t>trigger</t>
   </si>
@@ -3613,6 +3613,12 @@
   </si>
   <si>
     <t>left circumflex artery</t>
+  </si>
+  <si>
+    <t>aaa</t>
+  </si>
+  <si>
+    <t>abdominal aortic aneurysm</t>
   </si>
 </sst>
 </file>
@@ -3668,10 +3674,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B601" totalsRowShown="0">
-  <autoFilter ref="A1:B601" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B601">
-    <sortCondition ref="A1:A601"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B602" totalsRowShown="0">
+  <autoFilter ref="A1:B602" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B602">
+    <sortCondition ref="A1:A602"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -3944,7 +3950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B601"/>
+  <dimension ref="A1:B602"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -3969,1479 +3975,1479 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>944</v>
+        <v>1196</v>
       </c>
       <c r="B3" t="s">
-        <v>945</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="B4" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="B5" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>954</v>
+        <v>946</v>
       </c>
       <c r="B6" t="s">
-        <v>955</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>905</v>
+        <v>954</v>
       </c>
       <c r="B7" t="s">
-        <v>906</v>
+        <v>955</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>905</v>
       </c>
       <c r="B8" t="s">
-        <v>345</v>
+        <v>906</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>924</v>
+        <v>70</v>
       </c>
       <c r="B9" t="s">
-        <v>925</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="B10" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>338</v>
+        <v>926</v>
       </c>
       <c r="B11" t="s">
-        <v>346</v>
+        <v>927</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="B12" t="s">
-        <v>913</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>881</v>
+        <v>307</v>
       </c>
       <c r="B13" t="s">
-        <v>882</v>
+        <v>913</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>219</v>
+        <v>881</v>
       </c>
       <c r="B14" t="s">
-        <v>347</v>
+        <v>882</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>907</v>
+        <v>219</v>
       </c>
       <c r="B15" t="s">
-        <v>908</v>
+        <v>347</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>803</v>
+        <v>907</v>
       </c>
       <c r="B16" t="s">
-        <v>804</v>
+        <v>908</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>985</v>
+        <v>803</v>
       </c>
       <c r="B17" t="s">
-        <v>986</v>
+        <v>804</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>1058</v>
+        <v>985</v>
       </c>
       <c r="B18" t="s">
-        <v>1059</v>
+        <v>986</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>877</v>
+        <v>1058</v>
       </c>
       <c r="B19" t="s">
-        <v>878</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>768</v>
+        <v>877</v>
       </c>
       <c r="B20" t="s">
-        <v>769</v>
+        <v>878</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>1054</v>
+        <v>768</v>
       </c>
       <c r="B21" t="s">
-        <v>1055</v>
+        <v>769</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>174</v>
+        <v>1054</v>
       </c>
       <c r="B22" t="s">
-        <v>348</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="B23" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B24" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="B25" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>1027</v>
+        <v>161</v>
       </c>
       <c r="B26" t="s">
-        <v>1028</v>
+        <v>351</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>1020</v>
+        <v>1027</v>
       </c>
       <c r="B27" t="s">
-        <v>1021</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>1106</v>
+        <v>1020</v>
       </c>
       <c r="B28" t="s">
-        <v>695</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>74</v>
+        <v>1106</v>
       </c>
       <c r="B29" t="s">
-        <v>352</v>
+        <v>695</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>1108</v>
+        <v>74</v>
       </c>
       <c r="B30" t="s">
-        <v>1013</v>
+        <v>352</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>1182</v>
+        <v>1108</v>
       </c>
       <c r="B31" t="s">
-        <v>1183</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>1182</v>
       </c>
       <c r="B32" t="s">
-        <v>353</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B33" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="B34" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>1022</v>
+        <v>150</v>
       </c>
       <c r="B35" t="s">
-        <v>1023</v>
+        <v>355</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>69</v>
+        <v>1022</v>
       </c>
       <c r="B36" t="s">
-        <v>356</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>282</v>
+        <v>69</v>
       </c>
       <c r="B37" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>141</v>
+        <v>282</v>
       </c>
       <c r="B38" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>911</v>
+        <v>141</v>
       </c>
       <c r="B39" t="s">
-        <v>912</v>
+        <v>358</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>148</v>
+        <v>911</v>
       </c>
       <c r="B40" t="s">
-        <v>359</v>
+        <v>912</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>1102</v>
+        <v>148</v>
       </c>
       <c r="B41" t="s">
-        <v>1103</v>
+        <v>359</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>660</v>
+        <v>1102</v>
       </c>
       <c r="B42" t="s">
-        <v>696</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>1016</v>
+        <v>660</v>
       </c>
       <c r="B43" t="s">
-        <v>1017</v>
+        <v>696</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>166</v>
+        <v>1016</v>
       </c>
       <c r="B44" t="s">
-        <v>360</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>291</v>
+        <v>166</v>
       </c>
       <c r="B45" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="B46" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>239</v>
+        <v>310</v>
       </c>
       <c r="B47" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>195</v>
+        <v>239</v>
       </c>
       <c r="B48" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>246</v>
+        <v>195</v>
       </c>
       <c r="B49" t="s">
-        <v>1140</v>
+        <v>364</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>647</v>
+        <v>246</v>
       </c>
       <c r="B50" t="s">
-        <v>697</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>240</v>
+        <v>647</v>
       </c>
       <c r="B51" t="s">
-        <v>363</v>
+        <v>697</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>861</v>
+        <v>240</v>
       </c>
       <c r="B52" t="s">
-        <v>862</v>
+        <v>363</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>987</v>
+        <v>861</v>
       </c>
       <c r="B53" t="s">
-        <v>988</v>
+        <v>862</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>774</v>
+        <v>987</v>
       </c>
       <c r="B54" t="s">
-        <v>775</v>
+        <v>988</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B55" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>300</v>
+        <v>776</v>
       </c>
       <c r="B56" t="s">
-        <v>365</v>
+        <v>777</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>1147</v>
+        <v>300</v>
       </c>
       <c r="B57" t="s">
-        <v>1148</v>
+        <v>365</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>303</v>
+        <v>1147</v>
       </c>
       <c r="B58" t="s">
-        <v>366</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>230</v>
+        <v>303</v>
       </c>
       <c r="B59" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B60" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>789</v>
+        <v>232</v>
       </c>
       <c r="B61" t="s">
-        <v>790</v>
+        <v>368</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>318</v>
+        <v>789</v>
       </c>
       <c r="B62" t="s">
-        <v>369</v>
+        <v>790</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>762</v>
+        <v>318</v>
       </c>
       <c r="B63" t="s">
-        <v>763</v>
+        <v>369</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>61</v>
+        <v>762</v>
       </c>
       <c r="B64" t="s">
-        <v>370</v>
+        <v>763</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B65" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B66" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>885</v>
+        <v>58</v>
       </c>
       <c r="B67" t="s">
-        <v>886</v>
+        <v>372</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>659</v>
+        <v>885</v>
       </c>
       <c r="B68" t="s">
-        <v>698</v>
+        <v>886</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>237</v>
+        <v>659</v>
       </c>
       <c r="B69" t="s">
-        <v>373</v>
+        <v>698</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>60</v>
+        <v>237</v>
       </c>
       <c r="B70" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>1014</v>
+        <v>60</v>
       </c>
       <c r="B71" t="s">
-        <v>1015</v>
+        <v>374</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>668</v>
+        <v>1014</v>
       </c>
       <c r="B72" t="s">
-        <v>699</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B73" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B74" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B75" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B76" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B77" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B78" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>875</v>
+        <v>674</v>
       </c>
       <c r="B79" t="s">
-        <v>876</v>
+        <v>705</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>321</v>
+        <v>875</v>
       </c>
       <c r="B80" t="s">
-        <v>375</v>
+        <v>876</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>194</v>
+        <v>321</v>
       </c>
       <c r="B81" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="B82" t="s">
-        <v>22</v>
+        <v>376</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B83" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>196</v>
+        <v>19</v>
       </c>
       <c r="B84" t="s">
-        <v>377</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>287</v>
+        <v>196</v>
       </c>
       <c r="B85" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B86" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>337</v>
+        <v>286</v>
       </c>
       <c r="B87" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>899</v>
+        <v>337</v>
       </c>
       <c r="B88" t="s">
-        <v>900</v>
+        <v>380</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>305</v>
+        <v>899</v>
       </c>
       <c r="B89" t="s">
-        <v>381</v>
+        <v>900</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="B90" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>1159</v>
+        <v>323</v>
       </c>
       <c r="B91" t="s">
-        <v>1160</v>
+        <v>382</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>276</v>
+        <v>1159</v>
       </c>
       <c r="B92" t="s">
-        <v>383</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>333</v>
+        <v>276</v>
       </c>
       <c r="B93" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>42</v>
+        <v>333</v>
       </c>
       <c r="B94" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B95" t="s">
-        <v>1139</v>
+        <v>385</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>649</v>
+        <v>41</v>
       </c>
       <c r="B96" t="s">
-        <v>706</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>217</v>
+        <v>649</v>
       </c>
       <c r="B97" t="s">
-        <v>386</v>
+        <v>706</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>288</v>
+        <v>217</v>
       </c>
       <c r="B98" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>218</v>
+        <v>288</v>
       </c>
       <c r="B99" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>296</v>
+        <v>218</v>
       </c>
       <c r="B100" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>199</v>
+        <v>296</v>
       </c>
       <c r="B101" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>648</v>
+        <v>199</v>
       </c>
       <c r="B102" t="s">
-        <v>707</v>
+        <v>390</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>112</v>
+        <v>648</v>
       </c>
       <c r="B103" t="s">
-        <v>391</v>
+        <v>707</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="B104" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="B105" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>1176</v>
+        <v>115</v>
       </c>
       <c r="B106" t="s">
-        <v>1177</v>
+        <v>393</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>879</v>
+        <v>1176</v>
       </c>
       <c r="B107" t="s">
-        <v>880</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>807</v>
+        <v>879</v>
       </c>
       <c r="B108" t="s">
-        <v>808</v>
+        <v>880</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>152</v>
+        <v>807</v>
       </c>
       <c r="B109" t="s">
-        <v>394</v>
+        <v>808</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="B110" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B111" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="B112" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>967</v>
+        <v>155</v>
       </c>
       <c r="B113" t="s">
-        <v>968</v>
+        <v>397</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>84</v>
+        <v>967</v>
       </c>
       <c r="B114" t="s">
-        <v>398</v>
+        <v>968</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>965</v>
+        <v>84</v>
       </c>
       <c r="B115" t="s">
-        <v>966</v>
+        <v>398</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>103</v>
+        <v>965</v>
       </c>
       <c r="B116" t="s">
-        <v>399</v>
+        <v>966</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>198</v>
+        <v>103</v>
       </c>
       <c r="B117" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>314</v>
+        <v>198</v>
       </c>
       <c r="B118" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>104</v>
+        <v>314</v>
       </c>
       <c r="B119" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="B120" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="B121" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B122" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>1046</v>
+        <v>102</v>
       </c>
       <c r="B123" t="s">
-        <v>1047</v>
+        <v>405</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>930</v>
+        <v>1046</v>
       </c>
       <c r="B124" t="s">
-        <v>931</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B125" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>162</v>
+        <v>928</v>
       </c>
       <c r="B126" t="s">
-        <v>406</v>
+        <v>929</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>1153</v>
+        <v>162</v>
       </c>
       <c r="B127" t="s">
-        <v>1154</v>
+        <v>406</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>837</v>
+        <v>1153</v>
       </c>
       <c r="B128" t="s">
-        <v>838</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B129" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>1084</v>
+        <v>839</v>
       </c>
       <c r="B130" t="s">
-        <v>1085</v>
+        <v>840</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>665</v>
+        <v>1084</v>
       </c>
       <c r="B131" t="s">
-        <v>708</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>646</v>
+        <v>665</v>
       </c>
       <c r="B132" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>940</v>
+        <v>646</v>
       </c>
       <c r="B133" t="s">
-        <v>941</v>
+        <v>709</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>683</v>
+        <v>940</v>
       </c>
       <c r="B134" t="s">
-        <v>710</v>
+        <v>941</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B135" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B136" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="B137" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B138" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B139" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B140" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B141" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B142" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B143" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B144" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>175</v>
+        <v>682</v>
       </c>
       <c r="B145" t="s">
-        <v>407</v>
+        <v>720</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="B146" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B147" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>149</v>
+        <v>213</v>
       </c>
       <c r="B148" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>247</v>
+        <v>149</v>
       </c>
       <c r="B149" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B150" t="s">
-        <v>1138</v>
+        <v>411</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>336</v>
+        <v>245</v>
       </c>
       <c r="B151" t="s">
-        <v>412</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>650</v>
+        <v>336</v>
       </c>
       <c r="B152" t="s">
-        <v>721</v>
+        <v>412</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>91</v>
+        <v>650</v>
       </c>
       <c r="B153" t="s">
-        <v>413</v>
+        <v>721</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>266</v>
+        <v>91</v>
       </c>
       <c r="B154" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>1096</v>
+        <v>266</v>
       </c>
       <c r="B155" t="s">
-        <v>1097</v>
+        <v>414</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>799</v>
+        <v>1096</v>
       </c>
       <c r="B156" t="s">
-        <v>800</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>1168</v>
+        <v>799</v>
       </c>
       <c r="B157" t="s">
-        <v>1169</v>
+        <v>800</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>295</v>
+        <v>1168</v>
       </c>
       <c r="B158" t="s">
-        <v>415</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>1086</v>
+        <v>295</v>
       </c>
       <c r="B159" t="s">
-        <v>1087</v>
+        <v>415</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="B160" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>151</v>
+        <v>1092</v>
       </c>
       <c r="B161" t="s">
-        <v>416</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>961</v>
+        <v>151</v>
       </c>
       <c r="B162" t="s">
-        <v>962</v>
+        <v>416</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>813</v>
+        <v>961</v>
       </c>
       <c r="B163" t="s">
-        <v>814</v>
+        <v>962</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>932</v>
+        <v>813</v>
       </c>
       <c r="B164" t="s">
-        <v>933</v>
+        <v>814</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>833</v>
+        <v>932</v>
       </c>
       <c r="B165" t="s">
-        <v>834</v>
+        <v>933</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>793</v>
+        <v>833</v>
       </c>
       <c r="B166" t="s">
-        <v>794</v>
+        <v>834</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>754</v>
+        <v>793</v>
       </c>
       <c r="B167" t="s">
-        <v>755</v>
+        <v>794</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>100</v>
+        <v>754</v>
       </c>
       <c r="B168" t="s">
-        <v>417</v>
+        <v>755</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>1042</v>
+        <v>100</v>
       </c>
       <c r="B169" t="s">
-        <v>1043</v>
+        <v>417</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>154</v>
+        <v>1042</v>
       </c>
       <c r="B170" t="s">
-        <v>418</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B171" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="B172" t="s">
-        <v>1137</v>
+        <v>419</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>1164</v>
+        <v>24</v>
       </c>
       <c r="B173" t="s">
-        <v>1165</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>1076</v>
+        <v>1164</v>
       </c>
       <c r="B174" t="s">
-        <v>1077</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>819</v>
+        <v>1076</v>
       </c>
       <c r="B175" t="s">
-        <v>820</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>130</v>
+        <v>819</v>
       </c>
       <c r="B176" t="s">
-        <v>420</v>
+        <v>820</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>322</v>
+        <v>130</v>
       </c>
       <c r="B177" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>867</v>
+        <v>322</v>
       </c>
       <c r="B178" t="s">
-        <v>868</v>
+        <v>421</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>183</v>
+        <v>867</v>
       </c>
       <c r="B179" t="s">
-        <v>422</v>
+        <v>868</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>1155</v>
+        <v>183</v>
       </c>
       <c r="B180" t="s">
-        <v>1156</v>
+        <v>422</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="B181" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>891</v>
+        <v>1157</v>
       </c>
       <c r="B182" t="s">
-        <v>892</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>32</v>
+        <v>891</v>
       </c>
       <c r="B183" t="s">
-        <v>423</v>
+        <v>892</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B184" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>764</v>
+        <v>35</v>
       </c>
       <c r="B185" t="s">
-        <v>1010</v>
+        <v>424</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>169</v>
+        <v>764</v>
       </c>
       <c r="B186" t="s">
-        <v>425</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B187" t="s">
         <v>425</v>
@@ -5449,1487 +5455,1487 @@
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>1011</v>
+        <v>170</v>
       </c>
       <c r="B188" t="s">
-        <v>765</v>
+        <v>425</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>178</v>
+        <v>1011</v>
       </c>
       <c r="B189" t="s">
-        <v>426</v>
+        <v>765</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="B190" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>238</v>
+        <v>111</v>
       </c>
       <c r="B191" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="B192" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B193" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="B194" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>667</v>
+        <v>179</v>
       </c>
       <c r="B195" t="s">
-        <v>722</v>
+        <v>431</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>97</v>
+        <v>667</v>
       </c>
       <c r="B196" t="s">
-        <v>432</v>
+        <v>722</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B197" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>242</v>
+        <v>110</v>
       </c>
       <c r="B198" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B199" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="B200" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B201" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>1110</v>
+        <v>182</v>
       </c>
       <c r="B202" t="s">
-        <v>1111</v>
+        <v>437</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>977</v>
+        <v>1110</v>
       </c>
       <c r="B203" t="s">
-        <v>978</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="B204" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>253</v>
+        <v>979</v>
       </c>
       <c r="B205" t="s">
-        <v>438</v>
+        <v>980</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="B206" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>787</v>
+        <v>34</v>
       </c>
       <c r="B207" t="s">
-        <v>788</v>
+        <v>439</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>180</v>
+        <v>787</v>
       </c>
       <c r="B208" t="s">
-        <v>440</v>
+        <v>788</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>275</v>
+        <v>180</v>
       </c>
       <c r="B209" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>857</v>
+        <v>275</v>
       </c>
       <c r="B210" t="s">
-        <v>858</v>
+        <v>441</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>116</v>
+        <v>857</v>
       </c>
       <c r="B211" t="s">
-        <v>442</v>
+        <v>858</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>208</v>
+        <v>116</v>
       </c>
       <c r="B212" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>1056</v>
+        <v>208</v>
       </c>
       <c r="B213" t="s">
-        <v>1057</v>
+        <v>443</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>118</v>
+        <v>1056</v>
       </c>
       <c r="B214" t="s">
-        <v>444</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>641</v>
+        <v>118</v>
       </c>
       <c r="B215" t="s">
-        <v>723</v>
+        <v>444</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>815</v>
+        <v>641</v>
       </c>
       <c r="B216" t="s">
-        <v>816</v>
+        <v>723</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>298</v>
+        <v>815</v>
       </c>
       <c r="B217" t="s">
-        <v>445</v>
+        <v>816</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>643</v>
+        <v>298</v>
       </c>
       <c r="B218" t="s">
-        <v>724</v>
+        <v>445</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B219" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>1036</v>
+        <v>644</v>
       </c>
       <c r="B220" t="s">
-        <v>1037</v>
+        <v>725</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>90</v>
+        <v>1036</v>
       </c>
       <c r="B221" t="s">
-        <v>446</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B222" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B223" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>1072</v>
+        <v>89</v>
       </c>
       <c r="B224" t="s">
-        <v>1073</v>
+        <v>448</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>23</v>
+        <v>1072</v>
       </c>
       <c r="B225" t="s">
-        <v>1136</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B226" t="s">
-        <v>6</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>1141</v>
+        <v>5</v>
       </c>
       <c r="B227" t="s">
-        <v>1142</v>
+        <v>6</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>126</v>
+        <v>1141</v>
       </c>
       <c r="B228" t="s">
-        <v>449</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B229" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B230" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B231" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B232" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>277</v>
+        <v>119</v>
       </c>
       <c r="B233" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>1074</v>
+        <v>277</v>
       </c>
       <c r="B234" t="s">
-        <v>1075</v>
+        <v>454</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>9</v>
+        <v>1074</v>
       </c>
       <c r="B235" t="s">
-        <v>10</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="B236" t="s">
-        <v>455</v>
+        <v>10</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B237" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="B238" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="B239" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>77</v>
+        <v>262</v>
       </c>
       <c r="B240" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>938</v>
+        <v>77</v>
       </c>
       <c r="B241" t="s">
-        <v>939</v>
+        <v>459</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>1172</v>
+        <v>938</v>
       </c>
       <c r="B242" t="s">
-        <v>1173</v>
+        <v>939</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>168</v>
+        <v>1172</v>
       </c>
       <c r="B243" t="s">
-        <v>460</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B244" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>835</v>
+        <v>167</v>
       </c>
       <c r="B245" t="s">
-        <v>836</v>
+        <v>461</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>791</v>
+        <v>835</v>
       </c>
       <c r="B246" t="s">
-        <v>792</v>
+        <v>836</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>304</v>
+        <v>791</v>
       </c>
       <c r="B247" t="s">
-        <v>462</v>
+        <v>792</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>758</v>
+        <v>304</v>
       </c>
       <c r="B248" t="s">
-        <v>759</v>
+        <v>462</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>897</v>
+        <v>758</v>
       </c>
       <c r="B249" t="s">
-        <v>898</v>
+        <v>759</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>652</v>
+        <v>897</v>
       </c>
       <c r="B250" t="s">
-        <v>726</v>
+        <v>898</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>86</v>
+        <v>652</v>
       </c>
       <c r="B251" t="s">
-        <v>463</v>
+        <v>726</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B252" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="B253" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B254" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B255" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>251</v>
+        <v>158</v>
       </c>
       <c r="B256" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="B257" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>326</v>
+        <v>285</v>
       </c>
       <c r="B258" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B259" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>229</v>
+        <v>327</v>
       </c>
       <c r="B260" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>55</v>
+        <v>229</v>
       </c>
       <c r="B261" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>657</v>
+        <v>55</v>
       </c>
       <c r="B262" t="s">
-        <v>727</v>
+        <v>473</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>235</v>
+        <v>657</v>
       </c>
       <c r="B263" t="s">
-        <v>474</v>
+        <v>727</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="B264" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="B265" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>766</v>
+        <v>236</v>
       </c>
       <c r="B266" t="s">
-        <v>1009</v>
+        <v>476</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>1012</v>
+        <v>766</v>
       </c>
       <c r="B267" t="s">
-        <v>767</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>164</v>
+        <v>1012</v>
       </c>
       <c r="B268" t="s">
-        <v>477</v>
+        <v>767</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="B269" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B270" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>313</v>
+        <v>204</v>
       </c>
       <c r="B271" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>873</v>
+        <v>313</v>
       </c>
       <c r="B272" t="s">
-        <v>874</v>
+        <v>480</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>997</v>
+        <v>873</v>
       </c>
       <c r="B273" t="s">
-        <v>998</v>
+        <v>874</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>258</v>
+        <v>997</v>
       </c>
       <c r="B274" t="s">
-        <v>481</v>
+        <v>998</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>983</v>
+        <v>258</v>
       </c>
       <c r="B275" t="s">
-        <v>984</v>
+        <v>481</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>160</v>
+        <v>983</v>
       </c>
       <c r="B276" t="s">
-        <v>482</v>
+        <v>984</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>692</v>
+        <v>160</v>
       </c>
       <c r="B277" t="s">
-        <v>728</v>
+        <v>482</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>1166</v>
+        <v>692</v>
       </c>
       <c r="B278" t="s">
-        <v>1167</v>
+        <v>728</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>760</v>
+        <v>1166</v>
       </c>
       <c r="B279" t="s">
-        <v>761</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>895</v>
+        <v>760</v>
       </c>
       <c r="B280" t="s">
-        <v>896</v>
+        <v>761</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B281" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>184</v>
+        <v>893</v>
       </c>
       <c r="B282" t="s">
-        <v>483</v>
+        <v>894</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>244</v>
+        <v>184</v>
       </c>
       <c r="B283" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B284" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>686</v>
+        <v>243</v>
       </c>
       <c r="B285" t="s">
-        <v>729</v>
+        <v>485</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B286" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B287" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B288" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B289" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>1192</v>
+        <v>690</v>
       </c>
       <c r="B290" t="s">
-        <v>1193</v>
+        <v>733</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>280</v>
+        <v>1192</v>
       </c>
       <c r="B291" t="s">
-        <v>486</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B292" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>49</v>
+        <v>281</v>
       </c>
       <c r="B293" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B294" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="B295" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="B296" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>1190</v>
+        <v>72</v>
       </c>
       <c r="B297" t="s">
-        <v>1191</v>
+        <v>490</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>221</v>
+        <v>1190</v>
       </c>
       <c r="B298" t="s">
-        <v>492</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>1194</v>
+        <v>221</v>
       </c>
       <c r="B299" t="s">
-        <v>1195</v>
+        <v>492</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>15</v>
+        <v>1194</v>
       </c>
       <c r="B300" t="s">
-        <v>16</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>1060</v>
+        <v>15</v>
       </c>
       <c r="B301" t="s">
-        <v>1061</v>
+        <v>16</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>920</v>
+        <v>1060</v>
       </c>
       <c r="B302" t="s">
-        <v>921</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>108</v>
+        <v>920</v>
       </c>
       <c r="B303" t="s">
-        <v>493</v>
+        <v>921</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>241</v>
+        <v>108</v>
       </c>
       <c r="B304" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>328</v>
+        <v>241</v>
       </c>
       <c r="B305" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>1100</v>
+        <v>328</v>
       </c>
       <c r="B306" t="s">
-        <v>1101</v>
+        <v>495</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>1052</v>
+        <v>1100</v>
       </c>
       <c r="B307" t="s">
-        <v>1053</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>121</v>
+        <v>1052</v>
       </c>
       <c r="B308" t="s">
-        <v>496</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>750</v>
+        <v>121</v>
       </c>
       <c r="B309" t="s">
-        <v>751</v>
+        <v>496</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>781</v>
+        <v>750</v>
       </c>
       <c r="B310" t="s">
-        <v>782</v>
+        <v>751</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>134</v>
+        <v>781</v>
       </c>
       <c r="B311" t="s">
-        <v>497</v>
+        <v>782</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="B312" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>224</v>
+        <v>63</v>
       </c>
       <c r="B313" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>25</v>
+        <v>224</v>
       </c>
       <c r="B314" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B315" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>207</v>
+        <v>26</v>
       </c>
       <c r="B316" t="s">
-        <v>1133</v>
+        <v>501</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>960</v>
+        <v>207</v>
       </c>
       <c r="B317" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>1113</v>
+        <v>960</v>
       </c>
       <c r="B318" t="s">
-        <v>1114</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>206</v>
+        <v>1113</v>
       </c>
       <c r="B319" t="s">
-        <v>1135</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B320" t="s">
-        <v>502</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B321" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="B322" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>663</v>
+        <v>145</v>
       </c>
       <c r="B323" t="s">
-        <v>734</v>
+        <v>504</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>171</v>
+        <v>663</v>
       </c>
       <c r="B324" t="s">
-        <v>505</v>
+        <v>734</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>1088</v>
+        <v>171</v>
       </c>
       <c r="B325" t="s">
-        <v>1089</v>
+        <v>505</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>263</v>
+        <v>1088</v>
       </c>
       <c r="B326" t="s">
-        <v>506</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>1090</v>
+        <v>263</v>
       </c>
       <c r="B327" t="s">
-        <v>1091</v>
+        <v>506</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>80</v>
+        <v>1090</v>
       </c>
       <c r="B328" t="s">
-        <v>507</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B329" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>191</v>
+        <v>65</v>
       </c>
       <c r="B330" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="B331" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>192</v>
+        <v>123</v>
       </c>
       <c r="B332" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="B333" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B334" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>31</v>
+        <v>233</v>
       </c>
       <c r="B335" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B336" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B337" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B338" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>306</v>
+        <v>71</v>
       </c>
       <c r="B339" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>222</v>
+        <v>306</v>
       </c>
       <c r="B340" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>315</v>
+        <v>222</v>
       </c>
       <c r="B341" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>278</v>
+        <v>315</v>
       </c>
       <c r="B342" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B343" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>831</v>
+        <v>279</v>
       </c>
       <c r="B344" t="s">
-        <v>832</v>
+        <v>522</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>48</v>
+        <v>831</v>
       </c>
       <c r="B345" t="s">
-        <v>523</v>
+        <v>832</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="B346" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="B347" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>223</v>
+        <v>52</v>
       </c>
       <c r="B348" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>1094</v>
+        <v>223</v>
       </c>
       <c r="B349" t="s">
-        <v>1095</v>
+        <v>526</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>1109</v>
+        <v>1094</v>
       </c>
       <c r="B350" t="s">
-        <v>1112</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>1050</v>
+        <v>1109</v>
       </c>
       <c r="B351" t="s">
-        <v>1051</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>96</v>
+        <v>1050</v>
       </c>
       <c r="B352" t="s">
-        <v>527</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>248</v>
+        <v>96</v>
       </c>
       <c r="B353" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B354" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>94</v>
+        <v>249</v>
       </c>
       <c r="B355" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>1064</v>
+        <v>94</v>
       </c>
       <c r="B356" t="s">
-        <v>1065</v>
+        <v>530</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>212</v>
+        <v>1064</v>
       </c>
       <c r="B357" t="s">
-        <v>531</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>916</v>
+        <v>212</v>
       </c>
       <c r="B358" t="s">
-        <v>917</v>
+        <v>531</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B359" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="B360" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>330</v>
+        <v>918</v>
       </c>
       <c r="B361" t="s">
-        <v>532</v>
+        <v>919</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>1066</v>
+        <v>330</v>
       </c>
       <c r="B362" t="s">
-        <v>1067</v>
+        <v>532</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>995</v>
+        <v>1066</v>
       </c>
       <c r="B363" t="s">
-        <v>996</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="B364" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B365" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>82</v>
+        <v>993</v>
       </c>
       <c r="B366" t="s">
-        <v>533</v>
+        <v>994</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>772</v>
+        <v>82</v>
       </c>
       <c r="B367" t="s">
-        <v>773</v>
+        <v>533</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>197</v>
+        <v>772</v>
       </c>
       <c r="B368" t="s">
-        <v>534</v>
+        <v>773</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>654</v>
+        <v>197</v>
       </c>
       <c r="B369" t="s">
-        <v>735</v>
+        <v>534</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>821</v>
+        <v>654</v>
       </c>
       <c r="B370" t="s">
-        <v>822</v>
+        <v>735</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>1068</v>
+        <v>821</v>
       </c>
       <c r="B371" t="s">
-        <v>1069</v>
+        <v>822</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>3</v>
+        <v>1068</v>
       </c>
       <c r="B372" t="s">
-        <v>4</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>958</v>
+        <v>3</v>
       </c>
       <c r="B373" t="s">
         <v>4</v>
@@ -6937,7 +6943,7 @@
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B374" t="s">
         <v>4</v>
@@ -6945,1817 +6951,1825 @@
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>664</v>
+        <v>959</v>
       </c>
       <c r="B375" t="s">
-        <v>736</v>
+        <v>4</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>770</v>
+        <v>664</v>
       </c>
       <c r="B376" t="s">
-        <v>771</v>
+        <v>736</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>85</v>
+        <v>770</v>
       </c>
       <c r="B377" t="s">
-        <v>535</v>
+        <v>771</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>1062</v>
+        <v>85</v>
       </c>
       <c r="B378" t="s">
-        <v>1063</v>
+        <v>535</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>829</v>
+        <v>1062</v>
       </c>
       <c r="B379" t="s">
-        <v>830</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>809</v>
+        <v>829</v>
       </c>
       <c r="B380" t="s">
-        <v>810</v>
+        <v>830</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>187</v>
+        <v>809</v>
       </c>
       <c r="B381" t="s">
-        <v>536</v>
+        <v>810</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>827</v>
+        <v>187</v>
       </c>
       <c r="B382" t="s">
-        <v>828</v>
+        <v>536</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>934</v>
+        <v>827</v>
       </c>
       <c r="B383" t="s">
-        <v>1130</v>
+        <v>828</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>863</v>
+        <v>934</v>
       </c>
       <c r="B384" t="s">
-        <v>864</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>1044</v>
+        <v>863</v>
       </c>
       <c r="B385" t="s">
-        <v>1045</v>
+        <v>864</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>798</v>
+        <v>1044</v>
       </c>
       <c r="B386" t="s">
-        <v>1131</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B387" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>13</v>
+        <v>797</v>
       </c>
       <c r="B388" t="s">
-        <v>14</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>817</v>
+        <v>13</v>
       </c>
       <c r="B389" t="s">
-        <v>818</v>
+        <v>14</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>186</v>
+        <v>817</v>
       </c>
       <c r="B390" t="s">
-        <v>537</v>
+        <v>818</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>811</v>
+        <v>186</v>
       </c>
       <c r="B391" t="s">
-        <v>812</v>
+        <v>537</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>320</v>
+        <v>811</v>
       </c>
       <c r="B392" t="s">
-        <v>538</v>
+        <v>812</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>656</v>
+        <v>320</v>
       </c>
       <c r="B393" t="s">
-        <v>737</v>
+        <v>538</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>855</v>
+        <v>656</v>
       </c>
       <c r="B394" t="s">
-        <v>856</v>
+        <v>737</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>658</v>
+        <v>855</v>
       </c>
       <c r="B395" t="s">
-        <v>738</v>
+        <v>856</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="B396" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>256</v>
+        <v>653</v>
       </c>
       <c r="B397" t="s">
-        <v>539</v>
+        <v>739</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B398" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B399" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>188</v>
+        <v>261</v>
       </c>
       <c r="B400" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B401" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>936</v>
+        <v>190</v>
       </c>
       <c r="B402" t="s">
-        <v>937</v>
+        <v>543</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>1031</v>
+        <v>936</v>
       </c>
       <c r="B403" t="s">
-        <v>1032</v>
+        <v>937</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>209</v>
+        <v>1031</v>
       </c>
       <c r="B404" t="s">
-        <v>544</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>851</v>
+        <v>209</v>
       </c>
       <c r="B405" t="s">
-        <v>852</v>
+        <v>544</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>143</v>
+        <v>851</v>
       </c>
       <c r="B406" t="s">
-        <v>545</v>
+        <v>852</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B407" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>254</v>
+        <v>140</v>
       </c>
       <c r="B408" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>331</v>
+        <v>254</v>
       </c>
       <c r="B409" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>210</v>
+        <v>331</v>
       </c>
       <c r="B410" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="B411" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>73</v>
+        <v>234</v>
       </c>
       <c r="B412" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>342</v>
+        <v>73</v>
       </c>
       <c r="B413" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="B414" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>843</v>
+        <v>308</v>
       </c>
       <c r="B415" t="s">
-        <v>844</v>
+        <v>553</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B416" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>220</v>
+        <v>845</v>
       </c>
       <c r="B417" t="s">
-        <v>554</v>
+        <v>846</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>909</v>
+        <v>220</v>
       </c>
       <c r="B418" t="s">
-        <v>910</v>
+        <v>554</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>963</v>
+        <v>909</v>
       </c>
       <c r="B419" t="s">
-        <v>964</v>
+        <v>910</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>1188</v>
+        <v>963</v>
       </c>
       <c r="B420" t="s">
-        <v>1189</v>
+        <v>964</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>227</v>
+        <v>1188</v>
       </c>
       <c r="B421" t="s">
-        <v>555</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>334</v>
+        <v>227</v>
       </c>
       <c r="B422" t="s">
-        <v>1161</v>
+        <v>555</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>971</v>
+        <v>334</v>
       </c>
       <c r="B423" t="s">
-        <v>972</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>778</v>
+        <v>971</v>
       </c>
       <c r="B424" t="s">
-        <v>779</v>
+        <v>972</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>294</v>
+        <v>778</v>
       </c>
       <c r="B425" t="s">
-        <v>556</v>
+        <v>779</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>952</v>
+        <v>294</v>
       </c>
       <c r="B426" t="s">
-        <v>953</v>
+        <v>556</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>339</v>
+        <v>952</v>
       </c>
       <c r="B427" t="s">
-        <v>557</v>
+        <v>953</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>780</v>
+        <v>339</v>
       </c>
       <c r="B428" t="s">
-        <v>779</v>
+        <v>557</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>340</v>
+        <v>780</v>
       </c>
       <c r="B429" t="s">
-        <v>558</v>
+        <v>779</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B430" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>645</v>
+        <v>341</v>
       </c>
       <c r="B431" t="s">
-        <v>740</v>
+        <v>559</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>39</v>
+        <v>645</v>
       </c>
       <c r="B432" t="s">
-        <v>560</v>
+        <v>740</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B433" t="s">
-        <v>1129</v>
+        <v>560</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>343</v>
+        <v>38</v>
       </c>
       <c r="B434" t="s">
-        <v>561</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>107</v>
+        <v>343</v>
       </c>
       <c r="B435" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>1029</v>
+        <v>107</v>
       </c>
       <c r="B436" t="s">
-        <v>1030</v>
+        <v>562</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>903</v>
+        <v>1029</v>
       </c>
       <c r="B437" t="s">
-        <v>904</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>117</v>
+        <v>903</v>
       </c>
       <c r="B438" t="s">
-        <v>563</v>
+        <v>904</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>1025</v>
+        <v>117</v>
       </c>
       <c r="B439" t="s">
-        <v>1026</v>
+        <v>563</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>98</v>
+        <v>1025</v>
       </c>
       <c r="B440" t="s">
-        <v>564</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B441" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>666</v>
+        <v>99</v>
       </c>
       <c r="B442" t="s">
-        <v>741</v>
+        <v>565</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>1107</v>
+        <v>666</v>
       </c>
       <c r="B443" t="s">
-        <v>1024</v>
+        <v>741</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>823</v>
+        <v>1107</v>
       </c>
       <c r="B444" t="s">
-        <v>824</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>113</v>
+        <v>823</v>
       </c>
       <c r="B445" t="s">
-        <v>566</v>
+        <v>824</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>889</v>
+        <v>113</v>
       </c>
       <c r="B446" t="s">
-        <v>890</v>
+        <v>566</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>45</v>
+        <v>889</v>
       </c>
       <c r="B447" t="s">
-        <v>1128</v>
+        <v>890</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>290</v>
+        <v>45</v>
       </c>
       <c r="B448" t="s">
-        <v>567</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B449" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>47</v>
+        <v>299</v>
       </c>
       <c r="B450" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>847</v>
+        <v>47</v>
       </c>
       <c r="B451" t="s">
-        <v>848</v>
+        <v>569</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>51</v>
+        <v>847</v>
       </c>
       <c r="B452" t="s">
-        <v>570</v>
+        <v>848</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>871</v>
+        <v>51</v>
       </c>
       <c r="B453" t="s">
-        <v>872</v>
+        <v>570</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>114</v>
+        <v>871</v>
       </c>
       <c r="B454" t="s">
-        <v>571</v>
+        <v>872</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>853</v>
+        <v>114</v>
       </c>
       <c r="B455" t="s">
-        <v>854</v>
+        <v>571</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>144</v>
+        <v>853</v>
       </c>
       <c r="B456" t="s">
-        <v>572</v>
+        <v>854</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>1080</v>
+        <v>144</v>
       </c>
       <c r="B457" t="s">
-        <v>1081</v>
+        <v>572</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>176</v>
+        <v>1080</v>
       </c>
       <c r="B458" t="s">
-        <v>573</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>316</v>
+        <v>176</v>
       </c>
       <c r="B459" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>29</v>
+        <v>316</v>
       </c>
       <c r="B460" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>1104</v>
+        <v>29</v>
       </c>
       <c r="B461" t="s">
-        <v>1105</v>
+        <v>575</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>1018</v>
+        <v>1104</v>
       </c>
       <c r="B462" t="s">
-        <v>1019</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>293</v>
+        <v>1018</v>
       </c>
       <c r="B463" t="s">
-        <v>576</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>981</v>
+        <v>293</v>
       </c>
       <c r="B464" t="s">
-        <v>982</v>
+        <v>576</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>301</v>
+        <v>981</v>
       </c>
       <c r="B465" t="s">
-        <v>577</v>
+        <v>982</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>1003</v>
+        <v>301</v>
       </c>
       <c r="B466" t="s">
-        <v>1004</v>
+        <v>577</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="B467" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>75</v>
+        <v>1007</v>
       </c>
       <c r="B468" t="s">
-        <v>578</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B469" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B470" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>329</v>
+        <v>78</v>
       </c>
       <c r="B471" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>752</v>
+        <v>329</v>
       </c>
       <c r="B472" t="s">
-        <v>753</v>
+        <v>581</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>805</v>
+        <v>752</v>
       </c>
       <c r="B473" t="s">
-        <v>806</v>
+        <v>753</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>135</v>
+        <v>805</v>
       </c>
       <c r="B474" t="s">
-        <v>582</v>
+        <v>806</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>1186</v>
+        <v>135</v>
       </c>
       <c r="B475" t="s">
-        <v>1187</v>
+        <v>582</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>1038</v>
+        <v>1186</v>
       </c>
       <c r="B476" t="s">
-        <v>1039</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>215</v>
+        <v>1038</v>
       </c>
       <c r="B477" t="s">
-        <v>583</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>935</v>
+        <v>215</v>
       </c>
       <c r="B478" t="s">
-        <v>1145</v>
+        <v>583</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>216</v>
+        <v>935</v>
       </c>
       <c r="B479" t="s">
-        <v>1126</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>317</v>
+        <v>216</v>
       </c>
       <c r="B480" t="s">
-        <v>584</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>1082</v>
+        <v>317</v>
       </c>
       <c r="B481" t="s">
-        <v>1083</v>
+        <v>584</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>214</v>
+        <v>1082</v>
       </c>
       <c r="B482" t="s">
-        <v>1127</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>999</v>
+        <v>214</v>
       </c>
       <c r="B483" t="s">
-        <v>1000</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B484" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>225</v>
+        <v>1001</v>
       </c>
       <c r="B485" t="s">
-        <v>585</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>948</v>
+        <v>225</v>
       </c>
       <c r="B486" t="s">
-        <v>949</v>
+        <v>585</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>1098</v>
+        <v>948</v>
       </c>
       <c r="B487" t="s">
-        <v>1099</v>
+        <v>949</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>1048</v>
+        <v>1098</v>
       </c>
       <c r="B488" t="s">
-        <v>1049</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>93</v>
+        <v>1048</v>
       </c>
       <c r="B489" t="s">
-        <v>586</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="B490" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>783</v>
+        <v>120</v>
       </c>
       <c r="B491" t="s">
-        <v>784</v>
+        <v>587</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>133</v>
+        <v>783</v>
       </c>
       <c r="B492" t="s">
-        <v>588</v>
+        <v>784</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="B493" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B494" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>825</v>
+        <v>66</v>
       </c>
       <c r="B495" t="s">
-        <v>826</v>
+        <v>590</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>950</v>
+        <v>825</v>
       </c>
       <c r="B496" t="s">
-        <v>951</v>
+        <v>826</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>79</v>
+        <v>950</v>
       </c>
       <c r="B497" t="s">
-        <v>591</v>
+        <v>951</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="B498" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="B499" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>1184</v>
+        <v>122</v>
       </c>
       <c r="B500" t="s">
-        <v>1185</v>
+        <v>593</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>181</v>
+        <v>1184</v>
       </c>
       <c r="B501" t="s">
-        <v>594</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>801</v>
+        <v>181</v>
       </c>
       <c r="B502" t="s">
-        <v>802</v>
+        <v>594</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>691</v>
+        <v>801</v>
       </c>
       <c r="B503" t="s">
-        <v>742</v>
+        <v>802</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>1151</v>
+        <v>691</v>
       </c>
       <c r="B504" t="s">
-        <v>1152</v>
+        <v>742</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="B505" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>284</v>
+        <v>1149</v>
       </c>
       <c r="B506" t="s">
-        <v>595</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>973</v>
+        <v>284</v>
       </c>
       <c r="B507" t="s">
-        <v>974</v>
+        <v>595</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>841</v>
+        <v>973</v>
       </c>
       <c r="B508" t="s">
-        <v>842</v>
+        <v>974</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>283</v>
+        <v>841</v>
       </c>
       <c r="B509" t="s">
-        <v>596</v>
+        <v>842</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>883</v>
+        <v>283</v>
       </c>
       <c r="B510" t="s">
-        <v>884</v>
+        <v>596</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>1180</v>
+        <v>883</v>
       </c>
       <c r="B511" t="s">
-        <v>1181</v>
+        <v>884</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>756</v>
+        <v>1180</v>
       </c>
       <c r="B512" t="s">
-        <v>757</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>1078</v>
+        <v>756</v>
       </c>
       <c r="B513" t="s">
-        <v>1079</v>
+        <v>757</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>67</v>
+        <v>1078</v>
       </c>
       <c r="B514" t="s">
-        <v>597</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B515" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="B516" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>289</v>
+        <v>95</v>
       </c>
       <c r="B517" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B518" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="B519" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>193</v>
+        <v>264</v>
       </c>
       <c r="B520" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>901</v>
+        <v>193</v>
       </c>
       <c r="B521" t="s">
-        <v>902</v>
+        <v>603</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>44</v>
+        <v>901</v>
       </c>
       <c r="B522" t="s">
-        <v>1125</v>
+        <v>902</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>1070</v>
+        <v>44</v>
       </c>
       <c r="B523" t="s">
-        <v>1071</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>324</v>
+        <v>1070</v>
       </c>
       <c r="B524" t="s">
-        <v>604</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B525" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>849</v>
+        <v>325</v>
       </c>
       <c r="B526" t="s">
-        <v>850</v>
+        <v>605</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>887</v>
+        <v>849</v>
       </c>
       <c r="B527" t="s">
-        <v>888</v>
+        <v>850</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>869</v>
+        <v>887</v>
       </c>
       <c r="B528" t="s">
-        <v>870</v>
+        <v>888</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>33</v>
+        <v>869</v>
       </c>
       <c r="B529" t="s">
-        <v>606</v>
+        <v>870</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B530" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>1143</v>
+        <v>36</v>
       </c>
       <c r="B531" t="s">
-        <v>1144</v>
+        <v>607</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>309</v>
+        <v>1143</v>
       </c>
       <c r="B532" t="s">
-        <v>608</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>257</v>
+        <v>309</v>
       </c>
       <c r="B533" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>302</v>
+        <v>257</v>
       </c>
       <c r="B534" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>228</v>
+        <v>302</v>
       </c>
       <c r="B535" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c r="B536" t="s">
-        <v>18</v>
+        <v>611</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>655</v>
+        <v>17</v>
       </c>
       <c r="B537" t="s">
-        <v>743</v>
+        <v>18</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>785</v>
+        <v>655</v>
       </c>
       <c r="B538" t="s">
-        <v>786</v>
+        <v>743</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>142</v>
+        <v>785</v>
       </c>
       <c r="B539" t="s">
-        <v>612</v>
+        <v>786</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>1178</v>
+        <v>142</v>
       </c>
       <c r="B540" t="s">
-        <v>1179</v>
+        <v>612</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>956</v>
+        <v>1178</v>
       </c>
       <c r="B541" t="s">
-        <v>957</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>54</v>
+        <v>956</v>
       </c>
       <c r="B542" t="s">
-        <v>613</v>
+        <v>957</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>265</v>
+        <v>54</v>
       </c>
       <c r="B543" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>976</v>
+        <v>265</v>
       </c>
       <c r="B544" t="s">
-        <v>975</v>
+        <v>614</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>56</v>
+        <v>976</v>
       </c>
       <c r="B545" t="s">
-        <v>615</v>
+        <v>975</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>185</v>
+        <v>56</v>
       </c>
       <c r="B546" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="B547" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="B548" t="s">
-        <v>1146</v>
+        <v>617</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B549" t="s">
-        <v>1124</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>1170</v>
+        <v>40</v>
       </c>
       <c r="B550" t="s">
-        <v>1171</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>165</v>
+        <v>1170</v>
       </c>
       <c r="B551" t="s">
-        <v>618</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="B552" t="s">
-        <v>11</v>
+        <v>618</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>250</v>
+        <v>12</v>
       </c>
       <c r="B553" t="s">
-        <v>619</v>
+        <v>11</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>27</v>
+        <v>250</v>
       </c>
       <c r="B554" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>1040</v>
+        <v>27</v>
       </c>
       <c r="B555" t="s">
-        <v>1041</v>
+        <v>620</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>28</v>
+        <v>1040</v>
       </c>
       <c r="B556" t="s">
-        <v>621</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>255</v>
+        <v>28</v>
       </c>
       <c r="B557" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>795</v>
+        <v>255</v>
       </c>
       <c r="B558" t="s">
-        <v>796</v>
+        <v>622</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>267</v>
+        <v>795</v>
       </c>
       <c r="B559" t="s">
-        <v>623</v>
+        <v>796</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>661</v>
+        <v>267</v>
       </c>
       <c r="B560" t="s">
-        <v>744</v>
+        <v>623</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B561" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>139</v>
+        <v>662</v>
       </c>
       <c r="B562" t="s">
-        <v>624</v>
+        <v>745</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="B563" t="s">
-        <v>2</v>
+        <v>624</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="B564" t="s">
-        <v>625</v>
+        <v>2</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>1034</v>
+        <v>105</v>
       </c>
       <c r="B565" t="s">
-        <v>1123</v>
+        <v>625</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>865</v>
+        <v>1034</v>
       </c>
       <c r="B566" t="s">
-        <v>866</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>1035</v>
+        <v>865</v>
       </c>
       <c r="B567" t="s">
-        <v>1122</v>
+        <v>866</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>292</v>
+        <v>1035</v>
       </c>
       <c r="B568" t="s">
-        <v>626</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>8</v>
+        <v>292</v>
       </c>
       <c r="B569" t="s">
-        <v>11</v>
+        <v>626</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>335</v>
+        <v>8</v>
       </c>
       <c r="B570" t="s">
-        <v>627</v>
+        <v>11</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B571" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>259</v>
+        <v>332</v>
       </c>
       <c r="B572" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>319</v>
+        <v>259</v>
       </c>
       <c r="B573" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>859</v>
+        <v>319</v>
       </c>
       <c r="B574" t="s">
-        <v>860</v>
+        <v>630</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>1174</v>
+        <v>859</v>
       </c>
       <c r="B575" t="s">
-        <v>1175</v>
+        <v>860</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>268</v>
+        <v>1174</v>
       </c>
       <c r="B576" t="s">
-        <v>631</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B577" t="s">
-        <v>1117</v>
+        <v>631</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B578" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B579" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B580" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B581" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B582" t="s">
-        <v>1116</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>92</v>
+        <v>272</v>
       </c>
       <c r="B583" t="s">
-        <v>632</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>200</v>
+        <v>92</v>
       </c>
       <c r="B584" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B585" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="B586" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>693</v>
+        <v>172</v>
       </c>
       <c r="B587" t="s">
-        <v>746</v>
+        <v>635</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>252</v>
+        <v>693</v>
       </c>
       <c r="B588" t="s">
-        <v>636</v>
+        <v>746</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>694</v>
+        <v>252</v>
       </c>
       <c r="B589" t="s">
-        <v>747</v>
+        <v>636</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>189</v>
+        <v>694</v>
       </c>
       <c r="B590" t="s">
-        <v>637</v>
+        <v>747</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>989</v>
+        <v>189</v>
       </c>
       <c r="B591" t="s">
-        <v>990</v>
+        <v>637</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>311</v>
+        <v>989</v>
       </c>
       <c r="B592" t="s">
-        <v>638</v>
+        <v>990</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B593" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>1033</v>
+        <v>312</v>
       </c>
       <c r="B594" t="s">
-        <v>1115</v>
+        <v>639</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>1005</v>
+        <v>1033</v>
       </c>
       <c r="B595" t="s">
-        <v>1006</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>81</v>
+        <v>1005</v>
       </c>
       <c r="B596" t="s">
-        <v>640</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>651</v>
+        <v>81</v>
       </c>
       <c r="B597" t="s">
-        <v>748</v>
+        <v>640</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>922</v>
+        <v>651</v>
       </c>
       <c r="B598" t="s">
-        <v>923</v>
+        <v>748</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>642</v>
+        <v>922</v>
       </c>
       <c r="B599" t="s">
-        <v>749</v>
+        <v>923</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>969</v>
+        <v>642</v>
       </c>
       <c r="B600" t="s">
-        <v>970</v>
+        <v>749</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
+        <v>969</v>
+      </c>
+      <c r="B601" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A602" t="s">
         <v>1162</v>
       </c>
-      <c r="B601" t="s">
+      <c r="B602" t="s">
         <v>1163</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E5168C-1D5E-4C61-8079-AB3CA10ED0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CDF1007-A889-4609-B13C-B65FD312DE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="1198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="1215">
   <si>
     <t>trigger</t>
   </si>
@@ -3619,6 +3619,57 @@
   </si>
   <si>
     <t>abdominal aortic aneurysm</t>
+  </si>
+  <si>
+    <t>fr</t>
+  </si>
+  <si>
+    <t>fracture</t>
+  </si>
+  <si>
+    <t>mas</t>
+  </si>
+  <si>
+    <t>frob</t>
+  </si>
+  <si>
+    <t>frontal bone</t>
+  </si>
+  <si>
+    <t>parb</t>
+  </si>
+  <si>
+    <t>parietal bone</t>
+  </si>
+  <si>
+    <t>temb</t>
+  </si>
+  <si>
+    <t>temporal bone</t>
+  </si>
+  <si>
+    <t>occb</t>
+  </si>
+  <si>
+    <t>occipital bone</t>
+  </si>
+  <si>
+    <t>des</t>
+  </si>
+  <si>
+    <t>ascc</t>
+  </si>
+  <si>
+    <t>ascending colon</t>
+  </si>
+  <si>
+    <t>descending colon</t>
+  </si>
+  <si>
+    <t>asca</t>
+  </si>
+  <si>
+    <t>ascending aorta</t>
   </si>
 </sst>
 </file>
@@ -3674,10 +3725,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B602" totalsRowShown="0">
-  <autoFilter ref="A1:B602" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B602">
-    <sortCondition ref="A1:A602"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B611" totalsRowShown="0">
+  <autoFilter ref="A1:B611" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B611">
+    <sortCondition ref="A1:A611"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -3950,7 +4001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B602"/>
+  <dimension ref="A1:B611"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -4287,4489 +4338,4561 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>1102</v>
+        <v>1213</v>
       </c>
       <c r="B42" t="s">
-        <v>1103</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>660</v>
+        <v>1210</v>
       </c>
       <c r="B43" t="s">
-        <v>696</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>1016</v>
+        <v>1102</v>
       </c>
       <c r="B44" t="s">
-        <v>1017</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>166</v>
+        <v>660</v>
       </c>
       <c r="B45" t="s">
-        <v>360</v>
+        <v>696</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>291</v>
+        <v>1016</v>
       </c>
       <c r="B46" t="s">
-        <v>361</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>310</v>
+        <v>166</v>
       </c>
       <c r="B47" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>239</v>
+        <v>291</v>
       </c>
       <c r="B48" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>195</v>
+        <v>310</v>
       </c>
       <c r="B49" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B50" t="s">
-        <v>1140</v>
+        <v>363</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>647</v>
+        <v>195</v>
       </c>
       <c r="B51" t="s">
-        <v>697</v>
+        <v>364</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B52" t="s">
-        <v>363</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>861</v>
+        <v>647</v>
       </c>
       <c r="B53" t="s">
-        <v>862</v>
+        <v>697</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>987</v>
+        <v>240</v>
       </c>
       <c r="B54" t="s">
-        <v>988</v>
+        <v>363</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>774</v>
+        <v>861</v>
       </c>
       <c r="B55" t="s">
-        <v>775</v>
+        <v>862</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>776</v>
+        <v>987</v>
       </c>
       <c r="B56" t="s">
-        <v>777</v>
+        <v>988</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>300</v>
+        <v>774</v>
       </c>
       <c r="B57" t="s">
-        <v>365</v>
+        <v>775</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>1147</v>
+        <v>776</v>
       </c>
       <c r="B58" t="s">
-        <v>1148</v>
+        <v>777</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B59" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>230</v>
+        <v>1147</v>
       </c>
       <c r="B60" t="s">
-        <v>367</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>232</v>
+        <v>303</v>
       </c>
       <c r="B61" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>789</v>
+        <v>230</v>
       </c>
       <c r="B62" t="s">
-        <v>790</v>
+        <v>367</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>318</v>
+        <v>232</v>
       </c>
       <c r="B63" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>762</v>
+        <v>789</v>
       </c>
       <c r="B64" t="s">
-        <v>763</v>
+        <v>790</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>61</v>
+        <v>318</v>
       </c>
       <c r="B65" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>59</v>
+        <v>762</v>
       </c>
       <c r="B66" t="s">
-        <v>371</v>
+        <v>763</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B67" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>885</v>
+        <v>59</v>
       </c>
       <c r="B68" t="s">
-        <v>886</v>
+        <v>371</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>659</v>
+        <v>58</v>
       </c>
       <c r="B69" t="s">
-        <v>698</v>
+        <v>372</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>237</v>
+        <v>885</v>
       </c>
       <c r="B70" t="s">
-        <v>373</v>
+        <v>886</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>60</v>
+        <v>659</v>
       </c>
       <c r="B71" t="s">
-        <v>374</v>
+        <v>698</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>1014</v>
+        <v>237</v>
       </c>
       <c r="B72" t="s">
-        <v>1015</v>
+        <v>373</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>668</v>
+        <v>60</v>
       </c>
       <c r="B73" t="s">
-        <v>699</v>
+        <v>374</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>669</v>
+        <v>1014</v>
       </c>
       <c r="B74" t="s">
-        <v>700</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B75" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B76" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B77" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B78" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B79" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>875</v>
+        <v>673</v>
       </c>
       <c r="B80" t="s">
-        <v>876</v>
+        <v>704</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>321</v>
+        <v>674</v>
       </c>
       <c r="B81" t="s">
-        <v>375</v>
+        <v>705</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>194</v>
+        <v>875</v>
       </c>
       <c r="B82" t="s">
-        <v>376</v>
+        <v>876</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>21</v>
+        <v>321</v>
       </c>
       <c r="B83" t="s">
-        <v>22</v>
+        <v>375</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>19</v>
+        <v>194</v>
       </c>
       <c r="B84" t="s">
-        <v>20</v>
+        <v>376</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>196</v>
+        <v>21</v>
       </c>
       <c r="B85" t="s">
-        <v>377</v>
+        <v>22</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>287</v>
+        <v>19</v>
       </c>
       <c r="B86" t="s">
-        <v>378</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>286</v>
+        <v>196</v>
       </c>
       <c r="B87" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>337</v>
+        <v>287</v>
       </c>
       <c r="B88" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>899</v>
+        <v>286</v>
       </c>
       <c r="B89" t="s">
-        <v>900</v>
+        <v>379</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>305</v>
+        <v>337</v>
       </c>
       <c r="B90" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>323</v>
+        <v>899</v>
       </c>
       <c r="B91" t="s">
-        <v>382</v>
+        <v>900</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>1159</v>
+        <v>305</v>
       </c>
       <c r="B92" t="s">
-        <v>1160</v>
+        <v>381</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="B93" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>333</v>
+        <v>1159</v>
       </c>
       <c r="B94" t="s">
-        <v>384</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>42</v>
+        <v>276</v>
       </c>
       <c r="B95" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>41</v>
+        <v>333</v>
       </c>
       <c r="B96" t="s">
-        <v>1139</v>
+        <v>384</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>649</v>
+        <v>42</v>
       </c>
       <c r="B97" t="s">
-        <v>706</v>
+        <v>385</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>217</v>
+        <v>41</v>
       </c>
       <c r="B98" t="s">
-        <v>386</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>288</v>
+        <v>649</v>
       </c>
       <c r="B99" t="s">
-        <v>387</v>
+        <v>706</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B100" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="B101" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="B102" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>648</v>
+        <v>296</v>
       </c>
       <c r="B103" t="s">
-        <v>707</v>
+        <v>389</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>112</v>
+        <v>199</v>
       </c>
       <c r="B104" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>83</v>
+        <v>648</v>
       </c>
       <c r="B105" t="s">
-        <v>392</v>
+        <v>707</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B106" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>1176</v>
+        <v>83</v>
       </c>
       <c r="B107" t="s">
-        <v>1177</v>
+        <v>392</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>879</v>
+        <v>115</v>
       </c>
       <c r="B108" t="s">
-        <v>880</v>
+        <v>393</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>807</v>
+        <v>1176</v>
       </c>
       <c r="B109" t="s">
-        <v>808</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>152</v>
+        <v>879</v>
       </c>
       <c r="B110" t="s">
-        <v>394</v>
+        <v>880</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>124</v>
+        <v>807</v>
       </c>
       <c r="B111" t="s">
-        <v>396</v>
+        <v>808</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="B112" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="B113" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>967</v>
+        <v>125</v>
       </c>
       <c r="B114" t="s">
-        <v>968</v>
+        <v>395</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="B115" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B116" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="B117" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>198</v>
+        <v>965</v>
       </c>
       <c r="B118" t="s">
-        <v>400</v>
+        <v>966</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>314</v>
+        <v>103</v>
       </c>
       <c r="B119" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>104</v>
+        <v>198</v>
       </c>
       <c r="B120" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>163</v>
+        <v>314</v>
       </c>
       <c r="B121" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B122" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="B123" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>1046</v>
+        <v>101</v>
       </c>
       <c r="B124" t="s">
-        <v>1047</v>
+        <v>404</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>930</v>
+        <v>102</v>
       </c>
       <c r="B125" t="s">
-        <v>931</v>
+        <v>405</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>928</v>
+        <v>1046</v>
       </c>
       <c r="B126" t="s">
-        <v>929</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>162</v>
+        <v>930</v>
       </c>
       <c r="B127" t="s">
-        <v>406</v>
+        <v>931</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>1153</v>
+        <v>928</v>
       </c>
       <c r="B128" t="s">
-        <v>1154</v>
+        <v>929</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>837</v>
+        <v>162</v>
       </c>
       <c r="B129" t="s">
-        <v>838</v>
+        <v>406</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>839</v>
+        <v>1153</v>
       </c>
       <c r="B130" t="s">
-        <v>840</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>1084</v>
+        <v>837</v>
       </c>
       <c r="B131" t="s">
-        <v>1085</v>
+        <v>838</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>665</v>
+        <v>839</v>
       </c>
       <c r="B132" t="s">
-        <v>708</v>
+        <v>840</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>646</v>
+        <v>1084</v>
       </c>
       <c r="B133" t="s">
-        <v>709</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>940</v>
+        <v>665</v>
       </c>
       <c r="B134" t="s">
-        <v>941</v>
+        <v>708</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>683</v>
+        <v>646</v>
       </c>
       <c r="B135" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>684</v>
+        <v>940</v>
       </c>
       <c r="B136" t="s">
-        <v>711</v>
+        <v>941</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B137" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>675</v>
+        <v>684</v>
       </c>
       <c r="B138" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>676</v>
+        <v>685</v>
       </c>
       <c r="B139" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B140" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B141" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B142" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B143" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B144" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B145" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>175</v>
+        <v>681</v>
       </c>
       <c r="B146" t="s">
-        <v>407</v>
+        <v>719</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>211</v>
+        <v>682</v>
       </c>
       <c r="B147" t="s">
-        <v>408</v>
+        <v>720</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>213</v>
+        <v>175</v>
       </c>
       <c r="B148" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>149</v>
+        <v>211</v>
       </c>
       <c r="B149" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>247</v>
+        <v>213</v>
       </c>
       <c r="B150" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>245</v>
+        <v>1209</v>
       </c>
       <c r="B151" t="s">
-        <v>1138</v>
+        <v>410</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>336</v>
+        <v>149</v>
       </c>
       <c r="B152" t="s">
-        <v>412</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>650</v>
+        <v>247</v>
       </c>
       <c r="B153" t="s">
-        <v>721</v>
+        <v>411</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="B154" t="s">
-        <v>413</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>266</v>
+        <v>336</v>
       </c>
       <c r="B155" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>1096</v>
+        <v>650</v>
       </c>
       <c r="B156" t="s">
-        <v>1097</v>
+        <v>721</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>799</v>
+        <v>91</v>
       </c>
       <c r="B157" t="s">
-        <v>800</v>
+        <v>413</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>1168</v>
+        <v>266</v>
       </c>
       <c r="B158" t="s">
-        <v>1169</v>
+        <v>414</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>295</v>
+        <v>1096</v>
       </c>
       <c r="B159" t="s">
-        <v>415</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>1086</v>
+        <v>799</v>
       </c>
       <c r="B160" t="s">
-        <v>1087</v>
+        <v>800</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>1092</v>
+        <v>1168</v>
       </c>
       <c r="B161" t="s">
-        <v>1093</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>151</v>
+        <v>295</v>
       </c>
       <c r="B162" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>961</v>
+        <v>1086</v>
       </c>
       <c r="B163" t="s">
-        <v>962</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>813</v>
+        <v>1092</v>
       </c>
       <c r="B164" t="s">
-        <v>814</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>932</v>
+        <v>151</v>
       </c>
       <c r="B165" t="s">
-        <v>933</v>
+        <v>416</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>833</v>
+        <v>961</v>
       </c>
       <c r="B166" t="s">
-        <v>834</v>
+        <v>962</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>793</v>
+        <v>813</v>
       </c>
       <c r="B167" t="s">
-        <v>794</v>
+        <v>814</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>754</v>
+        <v>932</v>
       </c>
       <c r="B168" t="s">
-        <v>755</v>
+        <v>933</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>100</v>
+        <v>833</v>
       </c>
       <c r="B169" t="s">
-        <v>417</v>
+        <v>834</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>1042</v>
+        <v>793</v>
       </c>
       <c r="B170" t="s">
-        <v>1043</v>
+        <v>794</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>154</v>
+        <v>754</v>
       </c>
       <c r="B171" t="s">
-        <v>418</v>
+        <v>755</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>157</v>
+        <v>100</v>
       </c>
       <c r="B172" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>24</v>
+        <v>1042</v>
       </c>
       <c r="B173" t="s">
-        <v>1137</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>1164</v>
+        <v>154</v>
       </c>
       <c r="B174" t="s">
-        <v>1165</v>
+        <v>418</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>1076</v>
+        <v>157</v>
       </c>
       <c r="B175" t="s">
-        <v>1077</v>
+        <v>419</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>819</v>
+        <v>24</v>
       </c>
       <c r="B176" t="s">
-        <v>820</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>130</v>
+        <v>1164</v>
       </c>
       <c r="B177" t="s">
-        <v>420</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>322</v>
+        <v>1076</v>
       </c>
       <c r="B178" t="s">
-        <v>421</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>867</v>
+        <v>819</v>
       </c>
       <c r="B179" t="s">
-        <v>868</v>
+        <v>820</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>183</v>
+        <v>130</v>
       </c>
       <c r="B180" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>1155</v>
+        <v>322</v>
       </c>
       <c r="B181" t="s">
-        <v>1156</v>
+        <v>421</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>1157</v>
+        <v>867</v>
       </c>
       <c r="B182" t="s">
-        <v>1158</v>
+        <v>868</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>891</v>
+        <v>183</v>
       </c>
       <c r="B183" t="s">
-        <v>892</v>
+        <v>422</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>32</v>
+        <v>1155</v>
       </c>
       <c r="B184" t="s">
-        <v>423</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>35</v>
+        <v>1157</v>
       </c>
       <c r="B185" t="s">
-        <v>424</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>764</v>
+        <v>891</v>
       </c>
       <c r="B186" t="s">
-        <v>1010</v>
+        <v>892</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>169</v>
+        <v>32</v>
       </c>
       <c r="B187" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>170</v>
+        <v>35</v>
       </c>
       <c r="B188" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>1011</v>
+        <v>764</v>
       </c>
       <c r="B189" t="s">
-        <v>765</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="B190" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="B191" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>238</v>
+        <v>1011</v>
       </c>
       <c r="B192" t="s">
-        <v>428</v>
+        <v>765</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="B193" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B194" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>179</v>
+        <v>238</v>
       </c>
       <c r="B195" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>667</v>
+        <v>106</v>
       </c>
       <c r="B196" t="s">
-        <v>722</v>
+        <v>429</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B197" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>110</v>
+        <v>179</v>
       </c>
       <c r="B198" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>242</v>
+        <v>667</v>
       </c>
       <c r="B199" t="s">
-        <v>434</v>
+        <v>722</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>226</v>
+        <v>97</v>
       </c>
       <c r="B200" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>177</v>
+        <v>110</v>
       </c>
       <c r="B201" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>182</v>
+        <v>242</v>
       </c>
       <c r="B202" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>1110</v>
+        <v>226</v>
       </c>
       <c r="B203" t="s">
-        <v>1111</v>
+        <v>435</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>977</v>
+        <v>177</v>
       </c>
       <c r="B204" t="s">
-        <v>978</v>
+        <v>436</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>979</v>
+        <v>182</v>
       </c>
       <c r="B205" t="s">
-        <v>980</v>
+        <v>437</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>253</v>
+        <v>1110</v>
       </c>
       <c r="B206" t="s">
-        <v>438</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>34</v>
+        <v>977</v>
       </c>
       <c r="B207" t="s">
-        <v>439</v>
+        <v>978</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>787</v>
+        <v>979</v>
       </c>
       <c r="B208" t="s">
-        <v>788</v>
+        <v>980</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>180</v>
+        <v>1198</v>
       </c>
       <c r="B209" t="s">
-        <v>440</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>275</v>
+        <v>1201</v>
       </c>
       <c r="B210" t="s">
-        <v>441</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>857</v>
+        <v>253</v>
       </c>
       <c r="B211" t="s">
-        <v>858</v>
+        <v>438</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>116</v>
+        <v>34</v>
       </c>
       <c r="B212" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>208</v>
+        <v>787</v>
       </c>
       <c r="B213" t="s">
-        <v>443</v>
+        <v>788</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>1056</v>
+        <v>180</v>
       </c>
       <c r="B214" t="s">
-        <v>1057</v>
+        <v>440</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>118</v>
+        <v>275</v>
       </c>
       <c r="B215" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>641</v>
+        <v>857</v>
       </c>
       <c r="B216" t="s">
-        <v>723</v>
+        <v>858</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>815</v>
+        <v>116</v>
       </c>
       <c r="B217" t="s">
-        <v>816</v>
+        <v>442</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>298</v>
+        <v>208</v>
       </c>
       <c r="B218" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>643</v>
+        <v>1056</v>
       </c>
       <c r="B219" t="s">
-        <v>724</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>644</v>
+        <v>118</v>
       </c>
       <c r="B220" t="s">
-        <v>725</v>
+        <v>444</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>1036</v>
+        <v>641</v>
       </c>
       <c r="B221" t="s">
-        <v>1037</v>
+        <v>723</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>90</v>
+        <v>815</v>
       </c>
       <c r="B222" t="s">
-        <v>446</v>
+        <v>816</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>88</v>
+        <v>298</v>
       </c>
       <c r="B223" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>89</v>
+        <v>643</v>
       </c>
       <c r="B224" t="s">
-        <v>448</v>
+        <v>724</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>1072</v>
+        <v>644</v>
       </c>
       <c r="B225" t="s">
-        <v>1073</v>
+        <v>725</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>23</v>
+        <v>1036</v>
       </c>
       <c r="B226" t="s">
-        <v>1136</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="B227" t="s">
-        <v>6</v>
+        <v>446</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>1141</v>
+        <v>88</v>
       </c>
       <c r="B228" t="s">
-        <v>1142</v>
+        <v>447</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>126</v>
+        <v>89</v>
       </c>
       <c r="B229" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>128</v>
+        <v>1072</v>
       </c>
       <c r="B230" t="s">
-        <v>450</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="B231" t="s">
-        <v>451</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>132</v>
+        <v>5</v>
       </c>
       <c r="B232" t="s">
-        <v>452</v>
+        <v>6</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>119</v>
+        <v>1141</v>
       </c>
       <c r="B233" t="s">
-        <v>453</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>277</v>
+        <v>126</v>
       </c>
       <c r="B234" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>1074</v>
+        <v>128</v>
       </c>
       <c r="B235" t="s">
-        <v>1075</v>
+        <v>450</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="B236" t="s">
-        <v>10</v>
+        <v>451</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B237" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B238" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>173</v>
+        <v>277</v>
       </c>
       <c r="B239" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>262</v>
+        <v>1074</v>
       </c>
       <c r="B240" t="s">
-        <v>458</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="B241" t="s">
-        <v>459</v>
+        <v>10</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>938</v>
+        <v>129</v>
       </c>
       <c r="B242" t="s">
-        <v>939</v>
+        <v>455</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>1172</v>
+        <v>127</v>
       </c>
       <c r="B243" t="s">
-        <v>1173</v>
+        <v>456</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B244" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>167</v>
+        <v>262</v>
       </c>
       <c r="B245" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>835</v>
+        <v>77</v>
       </c>
       <c r="B246" t="s">
-        <v>836</v>
+        <v>459</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>791</v>
+        <v>938</v>
       </c>
       <c r="B247" t="s">
-        <v>792</v>
+        <v>939</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>304</v>
+        <v>1172</v>
       </c>
       <c r="B248" t="s">
-        <v>462</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>758</v>
+        <v>168</v>
       </c>
       <c r="B249" t="s">
-        <v>759</v>
+        <v>460</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>897</v>
+        <v>167</v>
       </c>
       <c r="B250" t="s">
-        <v>898</v>
+        <v>461</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>652</v>
+        <v>835</v>
       </c>
       <c r="B251" t="s">
-        <v>726</v>
+        <v>836</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>86</v>
+        <v>791</v>
       </c>
       <c r="B252" t="s">
-        <v>463</v>
+        <v>792</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>87</v>
+        <v>304</v>
       </c>
       <c r="B253" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>153</v>
+        <v>758</v>
       </c>
       <c r="B254" t="s">
-        <v>465</v>
+        <v>759</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>156</v>
+        <v>897</v>
       </c>
       <c r="B255" t="s">
-        <v>466</v>
+        <v>898</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>158</v>
+        <v>652</v>
       </c>
       <c r="B256" t="s">
-        <v>467</v>
+        <v>726</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>251</v>
+        <v>86</v>
       </c>
       <c r="B257" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>285</v>
+        <v>87</v>
       </c>
       <c r="B258" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>326</v>
+        <v>153</v>
       </c>
       <c r="B259" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>327</v>
+        <v>156</v>
       </c>
       <c r="B260" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>229</v>
+        <v>158</v>
       </c>
       <c r="B261" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>55</v>
+        <v>251</v>
       </c>
       <c r="B262" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>657</v>
+        <v>285</v>
       </c>
       <c r="B263" t="s">
-        <v>727</v>
+        <v>469</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>235</v>
+        <v>326</v>
       </c>
       <c r="B264" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>57</v>
+        <v>327</v>
       </c>
       <c r="B265" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B266" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>766</v>
+        <v>55</v>
       </c>
       <c r="B267" t="s">
-        <v>1009</v>
+        <v>473</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>1012</v>
+        <v>657</v>
       </c>
       <c r="B268" t="s">
-        <v>767</v>
+        <v>727</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>164</v>
+        <v>235</v>
       </c>
       <c r="B269" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>201</v>
+        <v>57</v>
       </c>
       <c r="B270" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="B271" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>313</v>
+        <v>766</v>
       </c>
       <c r="B272" t="s">
-        <v>480</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>873</v>
+        <v>1012</v>
       </c>
       <c r="B273" t="s">
-        <v>874</v>
+        <v>767</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>997</v>
+        <v>164</v>
       </c>
       <c r="B274" t="s">
-        <v>998</v>
+        <v>477</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>258</v>
+        <v>201</v>
       </c>
       <c r="B275" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>983</v>
+        <v>204</v>
       </c>
       <c r="B276" t="s">
-        <v>984</v>
+        <v>479</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>160</v>
+        <v>313</v>
       </c>
       <c r="B277" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>692</v>
+        <v>873</v>
       </c>
       <c r="B278" t="s">
-        <v>728</v>
+        <v>874</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>1166</v>
+        <v>997</v>
       </c>
       <c r="B279" t="s">
-        <v>1167</v>
+        <v>998</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>760</v>
+        <v>258</v>
       </c>
       <c r="B280" t="s">
-        <v>761</v>
+        <v>481</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>895</v>
+        <v>983</v>
       </c>
       <c r="B281" t="s">
-        <v>896</v>
+        <v>984</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>893</v>
+        <v>160</v>
       </c>
       <c r="B282" t="s">
-        <v>894</v>
+        <v>482</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>184</v>
+        <v>692</v>
       </c>
       <c r="B283" t="s">
-        <v>483</v>
+        <v>728</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>244</v>
+        <v>1166</v>
       </c>
       <c r="B284" t="s">
-        <v>484</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>243</v>
+        <v>760</v>
       </c>
       <c r="B285" t="s">
-        <v>485</v>
+        <v>761</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>686</v>
+        <v>895</v>
       </c>
       <c r="B286" t="s">
-        <v>729</v>
+        <v>896</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>687</v>
+        <v>893</v>
       </c>
       <c r="B287" t="s">
-        <v>730</v>
+        <v>894</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>688</v>
+        <v>184</v>
       </c>
       <c r="B288" t="s">
-        <v>731</v>
+        <v>483</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>689</v>
+        <v>244</v>
       </c>
       <c r="B289" t="s">
-        <v>732</v>
+        <v>484</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>690</v>
+        <v>243</v>
       </c>
       <c r="B290" t="s">
-        <v>733</v>
+        <v>485</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>1192</v>
+        <v>686</v>
       </c>
       <c r="B291" t="s">
-        <v>1193</v>
+        <v>729</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>280</v>
+        <v>687</v>
       </c>
       <c r="B292" t="s">
-        <v>486</v>
+        <v>730</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>281</v>
+        <v>688</v>
       </c>
       <c r="B293" t="s">
-        <v>487</v>
+        <v>731</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>49</v>
+        <v>689</v>
       </c>
       <c r="B294" t="s">
-        <v>488</v>
+        <v>732</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>53</v>
+        <v>690</v>
       </c>
       <c r="B295" t="s">
-        <v>489</v>
+        <v>733</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>136</v>
+        <v>1192</v>
       </c>
       <c r="B296" t="s">
-        <v>491</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>72</v>
+        <v>280</v>
       </c>
       <c r="B297" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>1190</v>
+        <v>281</v>
       </c>
       <c r="B298" t="s">
-        <v>1191</v>
+        <v>487</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>221</v>
+        <v>49</v>
       </c>
       <c r="B299" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>1194</v>
+        <v>53</v>
       </c>
       <c r="B300" t="s">
-        <v>1195</v>
+        <v>489</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>15</v>
+        <v>136</v>
       </c>
       <c r="B301" t="s">
-        <v>16</v>
+        <v>491</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>1060</v>
+        <v>72</v>
       </c>
       <c r="B302" t="s">
-        <v>1061</v>
+        <v>490</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>920</v>
+        <v>1190</v>
       </c>
       <c r="B303" t="s">
-        <v>921</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>108</v>
+        <v>221</v>
       </c>
       <c r="B304" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>241</v>
+        <v>1194</v>
       </c>
       <c r="B305" t="s">
-        <v>494</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>328</v>
+        <v>15</v>
       </c>
       <c r="B306" t="s">
-        <v>495</v>
+        <v>16</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>1100</v>
+        <v>1060</v>
       </c>
       <c r="B307" t="s">
-        <v>1101</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>1052</v>
+        <v>920</v>
       </c>
       <c r="B308" t="s">
-        <v>1053</v>
+        <v>921</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="B309" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>750</v>
+        <v>241</v>
       </c>
       <c r="B310" t="s">
-        <v>751</v>
+        <v>494</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>781</v>
+        <v>328</v>
       </c>
       <c r="B311" t="s">
-        <v>782</v>
+        <v>495</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>134</v>
+        <v>1100</v>
       </c>
       <c r="B312" t="s">
-        <v>497</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>63</v>
+        <v>1052</v>
       </c>
       <c r="B313" t="s">
-        <v>498</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>224</v>
+        <v>121</v>
       </c>
       <c r="B314" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>25</v>
+        <v>750</v>
       </c>
       <c r="B315" t="s">
-        <v>500</v>
+        <v>751</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>26</v>
+        <v>781</v>
       </c>
       <c r="B316" t="s">
-        <v>501</v>
+        <v>782</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>207</v>
+        <v>134</v>
       </c>
       <c r="B317" t="s">
-        <v>1133</v>
+        <v>497</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>960</v>
+        <v>63</v>
       </c>
       <c r="B318" t="s">
-        <v>1134</v>
+        <v>498</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>1113</v>
+        <v>224</v>
       </c>
       <c r="B319" t="s">
-        <v>1114</v>
+        <v>499</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>206</v>
+        <v>25</v>
       </c>
       <c r="B320" t="s">
-        <v>1135</v>
+        <v>500</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>202</v>
+        <v>26</v>
       </c>
       <c r="B321" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B322" t="s">
-        <v>503</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>145</v>
+        <v>960</v>
       </c>
       <c r="B323" t="s">
-        <v>504</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>663</v>
+        <v>1113</v>
       </c>
       <c r="B324" t="s">
-        <v>734</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>171</v>
+        <v>206</v>
       </c>
       <c r="B325" t="s">
-        <v>505</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>1088</v>
+        <v>202</v>
       </c>
       <c r="B326" t="s">
-        <v>1089</v>
+        <v>502</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>263</v>
+        <v>205</v>
       </c>
       <c r="B327" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>1090</v>
+        <v>145</v>
       </c>
       <c r="B328" t="s">
-        <v>1091</v>
+        <v>504</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>80</v>
+        <v>663</v>
       </c>
       <c r="B329" t="s">
-        <v>507</v>
+        <v>734</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>65</v>
+        <v>171</v>
       </c>
       <c r="B330" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>191</v>
+        <v>1088</v>
       </c>
       <c r="B331" t="s">
-        <v>509</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>123</v>
+        <v>263</v>
       </c>
       <c r="B332" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>192</v>
+        <v>1090</v>
       </c>
       <c r="B333" t="s">
-        <v>511</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>231</v>
+        <v>80</v>
       </c>
       <c r="B334" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>233</v>
+        <v>65</v>
       </c>
       <c r="B335" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="B336" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>30</v>
+        <v>123</v>
       </c>
       <c r="B337" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>37</v>
+        <v>192</v>
       </c>
       <c r="B338" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>71</v>
+        <v>231</v>
       </c>
       <c r="B339" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>306</v>
+        <v>233</v>
       </c>
       <c r="B340" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>222</v>
+        <v>1200</v>
       </c>
       <c r="B341" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>315</v>
+        <v>31</v>
       </c>
       <c r="B342" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>278</v>
+        <v>30</v>
       </c>
       <c r="B343" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>279</v>
+        <v>37</v>
       </c>
       <c r="B344" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>831</v>
+        <v>71</v>
       </c>
       <c r="B345" t="s">
-        <v>832</v>
+        <v>517</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>48</v>
+        <v>306</v>
       </c>
       <c r="B346" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>146</v>
+        <v>222</v>
       </c>
       <c r="B347" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>52</v>
+        <v>315</v>
       </c>
       <c r="B348" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>223</v>
+        <v>278</v>
       </c>
       <c r="B349" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>1094</v>
+        <v>279</v>
       </c>
       <c r="B350" t="s">
-        <v>1095</v>
+        <v>522</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>1109</v>
+        <v>831</v>
       </c>
       <c r="B351" t="s">
-        <v>1112</v>
+        <v>832</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>1050</v>
+        <v>48</v>
       </c>
       <c r="B352" t="s">
-        <v>1051</v>
+        <v>523</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="B353" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>248</v>
+        <v>52</v>
       </c>
       <c r="B354" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="B355" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>94</v>
+        <v>1094</v>
       </c>
       <c r="B356" t="s">
-        <v>530</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>1064</v>
+        <v>1109</v>
       </c>
       <c r="B357" t="s">
-        <v>1065</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>212</v>
+        <v>1050</v>
       </c>
       <c r="B358" t="s">
-        <v>531</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>916</v>
+        <v>96</v>
       </c>
       <c r="B359" t="s">
-        <v>917</v>
+        <v>527</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>914</v>
+        <v>248</v>
       </c>
       <c r="B360" t="s">
-        <v>915</v>
+        <v>528</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>918</v>
+        <v>249</v>
       </c>
       <c r="B361" t="s">
-        <v>919</v>
+        <v>529</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>330</v>
+        <v>94</v>
       </c>
       <c r="B362" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="B363" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>995</v>
+        <v>212</v>
       </c>
       <c r="B364" t="s">
-        <v>996</v>
+        <v>531</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>991</v>
+        <v>916</v>
       </c>
       <c r="B365" t="s">
-        <v>992</v>
+        <v>917</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>993</v>
+        <v>914</v>
       </c>
       <c r="B366" t="s">
-        <v>994</v>
+        <v>915</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>82</v>
+        <v>918</v>
       </c>
       <c r="B367" t="s">
-        <v>533</v>
+        <v>919</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>772</v>
+        <v>330</v>
       </c>
       <c r="B368" t="s">
-        <v>773</v>
+        <v>532</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>197</v>
+        <v>1066</v>
       </c>
       <c r="B369" t="s">
-        <v>534</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>654</v>
+        <v>995</v>
       </c>
       <c r="B370" t="s">
-        <v>735</v>
+        <v>996</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>821</v>
+        <v>991</v>
       </c>
       <c r="B371" t="s">
-        <v>822</v>
+        <v>992</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>1068</v>
+        <v>993</v>
       </c>
       <c r="B372" t="s">
-        <v>1069</v>
+        <v>994</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="B373" t="s">
-        <v>4</v>
+        <v>533</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>958</v>
+        <v>772</v>
       </c>
       <c r="B374" t="s">
-        <v>4</v>
+        <v>773</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>959</v>
+        <v>197</v>
       </c>
       <c r="B375" t="s">
-        <v>4</v>
+        <v>534</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="B376" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>770</v>
+        <v>821</v>
       </c>
       <c r="B377" t="s">
-        <v>771</v>
+        <v>822</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>85</v>
+        <v>1068</v>
       </c>
       <c r="B378" t="s">
-        <v>535</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>1062</v>
+        <v>3</v>
       </c>
       <c r="B379" t="s">
-        <v>1063</v>
+        <v>4</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>829</v>
+        <v>958</v>
       </c>
       <c r="B380" t="s">
-        <v>830</v>
+        <v>4</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>809</v>
+        <v>959</v>
       </c>
       <c r="B381" t="s">
-        <v>810</v>
+        <v>4</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>187</v>
+        <v>664</v>
       </c>
       <c r="B382" t="s">
-        <v>536</v>
+        <v>736</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>827</v>
+        <v>770</v>
       </c>
       <c r="B383" t="s">
-        <v>828</v>
+        <v>771</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>934</v>
+        <v>85</v>
       </c>
       <c r="B384" t="s">
-        <v>1130</v>
+        <v>535</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>863</v>
+        <v>1062</v>
       </c>
       <c r="B385" t="s">
-        <v>864</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>1044</v>
+        <v>829</v>
       </c>
       <c r="B386" t="s">
-        <v>1045</v>
+        <v>830</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>798</v>
+        <v>809</v>
       </c>
       <c r="B387" t="s">
-        <v>1131</v>
+        <v>810</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>797</v>
+        <v>187</v>
       </c>
       <c r="B388" t="s">
-        <v>1132</v>
+        <v>536</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>13</v>
+        <v>827</v>
       </c>
       <c r="B389" t="s">
-        <v>14</v>
+        <v>828</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>817</v>
+        <v>934</v>
       </c>
       <c r="B390" t="s">
-        <v>818</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>186</v>
+        <v>863</v>
       </c>
       <c r="B391" t="s">
-        <v>537</v>
+        <v>864</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>811</v>
+        <v>1044</v>
       </c>
       <c r="B392" t="s">
-        <v>812</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>320</v>
+        <v>798</v>
       </c>
       <c r="B393" t="s">
-        <v>538</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>656</v>
+        <v>797</v>
       </c>
       <c r="B394" t="s">
-        <v>737</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>855</v>
+        <v>13</v>
       </c>
       <c r="B395" t="s">
-        <v>856</v>
+        <v>14</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>658</v>
+        <v>817</v>
       </c>
       <c r="B396" t="s">
-        <v>738</v>
+        <v>818</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>653</v>
+        <v>186</v>
       </c>
       <c r="B397" t="s">
-        <v>739</v>
+        <v>537</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>256</v>
+        <v>811</v>
       </c>
       <c r="B398" t="s">
-        <v>539</v>
+        <v>812</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="B399" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>261</v>
+        <v>656</v>
       </c>
       <c r="B400" t="s">
-        <v>541</v>
+        <v>737</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>188</v>
+        <v>855</v>
       </c>
       <c r="B401" t="s">
-        <v>542</v>
+        <v>856</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>190</v>
+        <v>658</v>
       </c>
       <c r="B402" t="s">
-        <v>543</v>
+        <v>738</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>936</v>
+        <v>653</v>
       </c>
       <c r="B403" t="s">
-        <v>937</v>
+        <v>739</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>1031</v>
+        <v>1207</v>
       </c>
       <c r="B404" t="s">
-        <v>1032</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>209</v>
+        <v>256</v>
       </c>
       <c r="B405" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>851</v>
+        <v>260</v>
       </c>
       <c r="B406" t="s">
-        <v>852</v>
+        <v>540</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>143</v>
+        <v>261</v>
       </c>
       <c r="B407" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="B408" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>254</v>
+        <v>190</v>
       </c>
       <c r="B409" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>331</v>
+        <v>936</v>
       </c>
       <c r="B410" t="s">
-        <v>548</v>
+        <v>937</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>210</v>
+        <v>1031</v>
       </c>
       <c r="B411" t="s">
-        <v>549</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="B412" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>73</v>
+        <v>851</v>
       </c>
       <c r="B413" t="s">
-        <v>551</v>
+        <v>852</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>342</v>
+        <v>143</v>
       </c>
       <c r="B414" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>308</v>
+        <v>140</v>
       </c>
       <c r="B415" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>843</v>
+        <v>1203</v>
       </c>
       <c r="B416" t="s">
-        <v>844</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>845</v>
+        <v>254</v>
       </c>
       <c r="B417" t="s">
-        <v>846</v>
+        <v>547</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>220</v>
+        <v>331</v>
       </c>
       <c r="B418" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>909</v>
+        <v>210</v>
       </c>
       <c r="B419" t="s">
-        <v>910</v>
+        <v>549</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>963</v>
+        <v>234</v>
       </c>
       <c r="B420" t="s">
-        <v>964</v>
+        <v>550</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>1188</v>
+        <v>73</v>
       </c>
       <c r="B421" t="s">
-        <v>1189</v>
+        <v>551</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>227</v>
+        <v>342</v>
       </c>
       <c r="B422" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>334</v>
+        <v>308</v>
       </c>
       <c r="B423" t="s">
-        <v>1161</v>
+        <v>553</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>971</v>
+        <v>843</v>
       </c>
       <c r="B424" t="s">
-        <v>972</v>
+        <v>844</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>778</v>
+        <v>845</v>
       </c>
       <c r="B425" t="s">
-        <v>779</v>
+        <v>846</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>294</v>
+        <v>220</v>
       </c>
       <c r="B426" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>952</v>
+        <v>909</v>
       </c>
       <c r="B427" t="s">
-        <v>953</v>
+        <v>910</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>339</v>
+        <v>963</v>
       </c>
       <c r="B428" t="s">
-        <v>557</v>
+        <v>964</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>780</v>
+        <v>1188</v>
       </c>
       <c r="B429" t="s">
-        <v>779</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>340</v>
+        <v>227</v>
       </c>
       <c r="B430" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B431" t="s">
-        <v>559</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>645</v>
+        <v>971</v>
       </c>
       <c r="B432" t="s">
-        <v>740</v>
+        <v>972</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>39</v>
+        <v>778</v>
       </c>
       <c r="B433" t="s">
-        <v>560</v>
+        <v>779</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>38</v>
+        <v>294</v>
       </c>
       <c r="B434" t="s">
-        <v>1129</v>
+        <v>556</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>343</v>
+        <v>952</v>
       </c>
       <c r="B435" t="s">
-        <v>561</v>
+        <v>953</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>107</v>
+        <v>339</v>
       </c>
       <c r="B436" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>1029</v>
+        <v>780</v>
       </c>
       <c r="B437" t="s">
-        <v>1030</v>
+        <v>779</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>903</v>
+        <v>340</v>
       </c>
       <c r="B438" t="s">
-        <v>904</v>
+        <v>558</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>117</v>
+        <v>341</v>
       </c>
       <c r="B439" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>1025</v>
+        <v>645</v>
       </c>
       <c r="B440" t="s">
-        <v>1026</v>
+        <v>740</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="B441" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="B442" t="s">
-        <v>565</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>666</v>
+        <v>343</v>
       </c>
       <c r="B443" t="s">
-        <v>741</v>
+        <v>561</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>1107</v>
+        <v>107</v>
       </c>
       <c r="B444" t="s">
-        <v>1024</v>
+        <v>562</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>823</v>
+        <v>1029</v>
       </c>
       <c r="B445" t="s">
-        <v>824</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>113</v>
+        <v>903</v>
       </c>
       <c r="B446" t="s">
-        <v>566</v>
+        <v>904</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>889</v>
+        <v>117</v>
       </c>
       <c r="B447" t="s">
-        <v>890</v>
+        <v>563</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>45</v>
+        <v>1025</v>
       </c>
       <c r="B448" t="s">
-        <v>1128</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>290</v>
+        <v>98</v>
       </c>
       <c r="B449" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>299</v>
+        <v>99</v>
       </c>
       <c r="B450" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>47</v>
+        <v>666</v>
       </c>
       <c r="B451" t="s">
-        <v>569</v>
+        <v>741</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>847</v>
+        <v>1107</v>
       </c>
       <c r="B452" t="s">
-        <v>848</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>51</v>
+        <v>823</v>
       </c>
       <c r="B453" t="s">
-        <v>570</v>
+        <v>824</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>871</v>
+        <v>113</v>
       </c>
       <c r="B454" t="s">
-        <v>872</v>
+        <v>566</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>114</v>
+        <v>889</v>
       </c>
       <c r="B455" t="s">
-        <v>571</v>
+        <v>890</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>853</v>
+        <v>45</v>
       </c>
       <c r="B456" t="s">
-        <v>854</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>144</v>
+        <v>290</v>
       </c>
       <c r="B457" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>1080</v>
+        <v>299</v>
       </c>
       <c r="B458" t="s">
-        <v>1081</v>
+        <v>568</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>176</v>
+        <v>47</v>
       </c>
       <c r="B459" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>316</v>
+        <v>847</v>
       </c>
       <c r="B460" t="s">
-        <v>574</v>
+        <v>848</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="B461" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>1104</v>
+        <v>871</v>
       </c>
       <c r="B462" t="s">
-        <v>1105</v>
+        <v>872</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>1018</v>
+        <v>114</v>
       </c>
       <c r="B463" t="s">
-        <v>1019</v>
+        <v>571</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>293</v>
+        <v>853</v>
       </c>
       <c r="B464" t="s">
-        <v>576</v>
+        <v>854</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>981</v>
+        <v>144</v>
       </c>
       <c r="B465" t="s">
-        <v>982</v>
+        <v>572</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>301</v>
+        <v>1080</v>
       </c>
       <c r="B466" t="s">
-        <v>577</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>1003</v>
+        <v>176</v>
       </c>
       <c r="B467" t="s">
-        <v>1004</v>
+        <v>573</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>1007</v>
+        <v>316</v>
       </c>
       <c r="B468" t="s">
-        <v>1008</v>
+        <v>574</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="B469" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>76</v>
+        <v>1104</v>
       </c>
       <c r="B470" t="s">
-        <v>579</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>78</v>
+        <v>1018</v>
       </c>
       <c r="B471" t="s">
-        <v>580</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>329</v>
+        <v>293</v>
       </c>
       <c r="B472" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>752</v>
+        <v>981</v>
       </c>
       <c r="B473" t="s">
-        <v>753</v>
+        <v>982</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>805</v>
+        <v>301</v>
       </c>
       <c r="B474" t="s">
-        <v>806</v>
+        <v>577</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>135</v>
+        <v>1003</v>
       </c>
       <c r="B475" t="s">
-        <v>582</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>1186</v>
+        <v>1007</v>
       </c>
       <c r="B476" t="s">
-        <v>1187</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>1038</v>
+        <v>75</v>
       </c>
       <c r="B477" t="s">
-        <v>1039</v>
+        <v>578</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>215</v>
+        <v>76</v>
       </c>
       <c r="B478" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>935</v>
+        <v>78</v>
       </c>
       <c r="B479" t="s">
-        <v>1145</v>
+        <v>580</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>216</v>
+        <v>329</v>
       </c>
       <c r="B480" t="s">
-        <v>1126</v>
+        <v>581</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>317</v>
+        <v>752</v>
       </c>
       <c r="B481" t="s">
-        <v>584</v>
+        <v>753</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>1082</v>
+        <v>805</v>
       </c>
       <c r="B482" t="s">
-        <v>1083</v>
+        <v>806</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>214</v>
+        <v>135</v>
       </c>
       <c r="B483" t="s">
-        <v>1127</v>
+        <v>582</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>999</v>
+        <v>1186</v>
       </c>
       <c r="B484" t="s">
-        <v>1000</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>1001</v>
+        <v>1038</v>
       </c>
       <c r="B485" t="s">
-        <v>1002</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="B486" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>948</v>
+        <v>935</v>
       </c>
       <c r="B487" t="s">
-        <v>949</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>1098</v>
+        <v>216</v>
       </c>
       <c r="B488" t="s">
-        <v>1099</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>1048</v>
+        <v>317</v>
       </c>
       <c r="B489" t="s">
-        <v>1049</v>
+        <v>584</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>93</v>
+        <v>1082</v>
       </c>
       <c r="B490" t="s">
-        <v>586</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>120</v>
+        <v>214</v>
       </c>
       <c r="B491" t="s">
-        <v>587</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>783</v>
+        <v>999</v>
       </c>
       <c r="B492" t="s">
-        <v>784</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>133</v>
+        <v>1001</v>
       </c>
       <c r="B493" t="s">
-        <v>588</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>62</v>
+        <v>225</v>
       </c>
       <c r="B494" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>66</v>
+        <v>948</v>
       </c>
       <c r="B495" t="s">
-        <v>590</v>
+        <v>949</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>825</v>
+        <v>1098</v>
       </c>
       <c r="B496" t="s">
-        <v>826</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>950</v>
+        <v>1048</v>
       </c>
       <c r="B497" t="s">
-        <v>951</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="B498" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="B499" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>122</v>
+        <v>783</v>
       </c>
       <c r="B500" t="s">
-        <v>593</v>
+        <v>784</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>1184</v>
+        <v>133</v>
       </c>
       <c r="B501" t="s">
-        <v>1185</v>
+        <v>588</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>181</v>
+        <v>62</v>
       </c>
       <c r="B502" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>801</v>
+        <v>66</v>
       </c>
       <c r="B503" t="s">
-        <v>802</v>
+        <v>590</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>691</v>
+        <v>825</v>
       </c>
       <c r="B504" t="s">
-        <v>742</v>
+        <v>826</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>1151</v>
+        <v>950</v>
       </c>
       <c r="B505" t="s">
-        <v>1152</v>
+        <v>951</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>1149</v>
+        <v>79</v>
       </c>
       <c r="B506" t="s">
-        <v>1150</v>
+        <v>591</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>284</v>
+        <v>64</v>
       </c>
       <c r="B507" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>973</v>
+        <v>122</v>
       </c>
       <c r="B508" t="s">
-        <v>974</v>
+        <v>593</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>841</v>
+        <v>1184</v>
       </c>
       <c r="B509" t="s">
-        <v>842</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>283</v>
+        <v>181</v>
       </c>
       <c r="B510" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>883</v>
+        <v>801</v>
       </c>
       <c r="B511" t="s">
-        <v>884</v>
+        <v>802</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>1180</v>
+        <v>691</v>
       </c>
       <c r="B512" t="s">
-        <v>1181</v>
+        <v>742</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>756</v>
+        <v>1151</v>
       </c>
       <c r="B513" t="s">
-        <v>757</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>1078</v>
+        <v>1149</v>
       </c>
       <c r="B514" t="s">
-        <v>1079</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>67</v>
+        <v>284</v>
       </c>
       <c r="B515" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>68</v>
+        <v>973</v>
       </c>
       <c r="B516" t="s">
-        <v>598</v>
+        <v>974</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>95</v>
+        <v>841</v>
       </c>
       <c r="B517" t="s">
-        <v>599</v>
+        <v>842</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="B518" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>297</v>
+        <v>883</v>
       </c>
       <c r="B519" t="s">
-        <v>601</v>
+        <v>884</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>264</v>
+        <v>1180</v>
       </c>
       <c r="B520" t="s">
-        <v>602</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>193</v>
+        <v>756</v>
       </c>
       <c r="B521" t="s">
-        <v>603</v>
+        <v>757</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>901</v>
+        <v>1078</v>
       </c>
       <c r="B522" t="s">
-        <v>902</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="B523" t="s">
-        <v>1125</v>
+        <v>597</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>1070</v>
+        <v>68</v>
       </c>
       <c r="B524" t="s">
-        <v>1071</v>
+        <v>598</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>324</v>
+        <v>95</v>
       </c>
       <c r="B525" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>325</v>
+        <v>289</v>
       </c>
       <c r="B526" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>849</v>
+        <v>297</v>
       </c>
       <c r="B527" t="s">
-        <v>850</v>
+        <v>601</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>887</v>
+        <v>264</v>
       </c>
       <c r="B528" t="s">
-        <v>888</v>
+        <v>602</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>869</v>
+        <v>193</v>
       </c>
       <c r="B529" t="s">
-        <v>870</v>
+        <v>603</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>33</v>
+        <v>901</v>
       </c>
       <c r="B530" t="s">
-        <v>606</v>
+        <v>902</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B531" t="s">
-        <v>607</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>1143</v>
+        <v>1070</v>
       </c>
       <c r="B532" t="s">
-        <v>1144</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="B533" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>257</v>
+        <v>325</v>
       </c>
       <c r="B534" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>302</v>
+        <v>849</v>
       </c>
       <c r="B535" t="s">
-        <v>610</v>
+        <v>850</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>228</v>
+        <v>887</v>
       </c>
       <c r="B536" t="s">
-        <v>611</v>
+        <v>888</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>17</v>
+        <v>869</v>
       </c>
       <c r="B537" t="s">
-        <v>18</v>
+        <v>870</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>655</v>
+        <v>33</v>
       </c>
       <c r="B538" t="s">
-        <v>743</v>
+        <v>606</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>785</v>
+        <v>36</v>
       </c>
       <c r="B539" t="s">
-        <v>786</v>
+        <v>607</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>142</v>
+        <v>1143</v>
       </c>
       <c r="B540" t="s">
-        <v>612</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>1178</v>
+        <v>309</v>
       </c>
       <c r="B541" t="s">
-        <v>1179</v>
+        <v>608</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>956</v>
+        <v>257</v>
       </c>
       <c r="B542" t="s">
-        <v>957</v>
+        <v>609</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>54</v>
+        <v>302</v>
       </c>
       <c r="B543" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>265</v>
+        <v>228</v>
       </c>
       <c r="B544" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>976</v>
+        <v>17</v>
       </c>
       <c r="B545" t="s">
-        <v>975</v>
+        <v>18</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>56</v>
+        <v>655</v>
       </c>
       <c r="B546" t="s">
-        <v>615</v>
+        <v>743</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>185</v>
+        <v>785</v>
       </c>
       <c r="B547" t="s">
-        <v>616</v>
+        <v>786</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="B548" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>43</v>
+        <v>1178</v>
       </c>
       <c r="B549" t="s">
-        <v>1146</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>40</v>
+        <v>956</v>
       </c>
       <c r="B550" t="s">
-        <v>1124</v>
+        <v>957</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>1170</v>
+        <v>54</v>
       </c>
       <c r="B551" t="s">
-        <v>1171</v>
+        <v>613</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>165</v>
+        <v>265</v>
       </c>
       <c r="B552" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>12</v>
+        <v>976</v>
       </c>
       <c r="B553" t="s">
-        <v>11</v>
+        <v>975</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>250</v>
+        <v>56</v>
       </c>
       <c r="B554" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="B555" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>1040</v>
+        <v>159</v>
       </c>
       <c r="B556" t="s">
-        <v>1041</v>
+        <v>617</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B557" t="s">
-        <v>621</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>255</v>
+        <v>40</v>
       </c>
       <c r="B558" t="s">
-        <v>622</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>795</v>
+        <v>1170</v>
       </c>
       <c r="B559" t="s">
-        <v>796</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>267</v>
+        <v>165</v>
       </c>
       <c r="B560" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>661</v>
+        <v>12</v>
       </c>
       <c r="B561" t="s">
-        <v>744</v>
+        <v>11</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>662</v>
+        <v>250</v>
       </c>
       <c r="B562" t="s">
-        <v>745</v>
+        <v>619</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>139</v>
+        <v>27</v>
       </c>
       <c r="B563" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>7</v>
+        <v>1040</v>
       </c>
       <c r="B564" t="s">
-        <v>2</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="B565" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>1034</v>
+        <v>1205</v>
       </c>
       <c r="B566" t="s">
-        <v>1123</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>865</v>
+        <v>255</v>
       </c>
       <c r="B567" t="s">
-        <v>866</v>
+        <v>622</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>1035</v>
+        <v>795</v>
       </c>
       <c r="B568" t="s">
-        <v>1122</v>
+        <v>796</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="B569" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>8</v>
+        <v>661</v>
       </c>
       <c r="B570" t="s">
-        <v>11</v>
+        <v>744</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>335</v>
+        <v>662</v>
       </c>
       <c r="B571" t="s">
-        <v>627</v>
+        <v>745</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>332</v>
+        <v>139</v>
       </c>
       <c r="B572" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>259</v>
+        <v>7</v>
       </c>
       <c r="B573" t="s">
-        <v>629</v>
+        <v>2</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>319</v>
+        <v>105</v>
       </c>
       <c r="B574" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>859</v>
+        <v>1034</v>
       </c>
       <c r="B575" t="s">
-        <v>860</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>1174</v>
+        <v>865</v>
       </c>
       <c r="B576" t="s">
-        <v>1175</v>
+        <v>866</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>268</v>
+        <v>1035</v>
       </c>
       <c r="B577" t="s">
-        <v>631</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="B578" t="s">
-        <v>1117</v>
+        <v>626</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>274</v>
+        <v>8</v>
       </c>
       <c r="B579" t="s">
-        <v>1118</v>
+        <v>11</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>270</v>
+        <v>335</v>
       </c>
       <c r="B580" t="s">
-        <v>1119</v>
+        <v>627</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>273</v>
+        <v>332</v>
       </c>
       <c r="B581" t="s">
-        <v>1120</v>
+        <v>628</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="B582" t="s">
-        <v>1121</v>
+        <v>629</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>272</v>
+        <v>319</v>
       </c>
       <c r="B583" t="s">
-        <v>1116</v>
+        <v>630</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>92</v>
+        <v>859</v>
       </c>
       <c r="B584" t="s">
-        <v>632</v>
+        <v>860</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>200</v>
+        <v>1174</v>
       </c>
       <c r="B585" t="s">
-        <v>633</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>203</v>
+        <v>268</v>
       </c>
       <c r="B586" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>172</v>
+        <v>271</v>
       </c>
       <c r="B587" t="s">
-        <v>635</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>693</v>
+        <v>274</v>
       </c>
       <c r="B588" t="s">
-        <v>746</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="B589" t="s">
-        <v>636</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>694</v>
+        <v>273</v>
       </c>
       <c r="B590" t="s">
-        <v>747</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>189</v>
+        <v>269</v>
       </c>
       <c r="B591" t="s">
-        <v>637</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>989</v>
+        <v>272</v>
       </c>
       <c r="B592" t="s">
-        <v>990</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>311</v>
+        <v>92</v>
       </c>
       <c r="B593" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>312</v>
+        <v>200</v>
       </c>
       <c r="B594" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>1033</v>
+        <v>203</v>
       </c>
       <c r="B595" t="s">
-        <v>1115</v>
+        <v>634</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>1005</v>
+        <v>172</v>
       </c>
       <c r="B596" t="s">
-        <v>1006</v>
+        <v>635</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>81</v>
+        <v>693</v>
       </c>
       <c r="B597" t="s">
-        <v>640</v>
+        <v>746</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>651</v>
+        <v>252</v>
       </c>
       <c r="B598" t="s">
-        <v>748</v>
+        <v>636</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>922</v>
+        <v>694</v>
       </c>
       <c r="B599" t="s">
-        <v>923</v>
+        <v>747</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>642</v>
+        <v>189</v>
       </c>
       <c r="B600" t="s">
-        <v>749</v>
+        <v>637</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>969</v>
+        <v>989</v>
       </c>
       <c r="B601" t="s">
-        <v>970</v>
+        <v>990</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
+        <v>311</v>
+      </c>
+      <c r="B602" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A603" t="s">
+        <v>312</v>
+      </c>
+      <c r="B603" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A604" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B604" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A605" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B605" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A606" t="s">
+        <v>81</v>
+      </c>
+      <c r="B606" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A607" t="s">
+        <v>651</v>
+      </c>
+      <c r="B607" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A608" t="s">
+        <v>922</v>
+      </c>
+      <c r="B608" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A609" t="s">
+        <v>642</v>
+      </c>
+      <c r="B609" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A610" t="s">
+        <v>969</v>
+      </c>
+      <c r="B610" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A611" t="s">
         <v>1162</v>
       </c>
-      <c r="B602" t="s">
+      <c r="B611" t="s">
         <v>1163</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CDF1007-A889-4609-B13C-B65FD312DE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA7C5438-6779-40C6-8BC1-CFDDA8870D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="1215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="1217">
   <si>
     <t>trigger</t>
   </si>
@@ -3670,6 +3670,12 @@
   </si>
   <si>
     <t>ascending aorta</t>
+  </si>
+  <si>
+    <t>rpl</t>
+  </si>
+  <si>
+    <t>retroperitoneal</t>
   </si>
 </sst>
 </file>
@@ -3725,10 +3731,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B611" totalsRowShown="0">
-  <autoFilter ref="A1:B611" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B611">
-    <sortCondition ref="A1:A611"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B612" totalsRowShown="0">
+  <autoFilter ref="A1:B612" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B612">
+    <sortCondition ref="A1:A612"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4001,7 +4007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B611"/>
+  <dimension ref="A1:B612"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -8050,849 +8056,857 @@
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>79</v>
+        <v>1215</v>
       </c>
       <c r="B506" t="s">
-        <v>591</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="B507" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="B508" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>1184</v>
+        <v>122</v>
       </c>
       <c r="B509" t="s">
-        <v>1185</v>
+        <v>593</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>181</v>
+        <v>1184</v>
       </c>
       <c r="B510" t="s">
-        <v>594</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>801</v>
+        <v>181</v>
       </c>
       <c r="B511" t="s">
-        <v>802</v>
+        <v>594</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>691</v>
+        <v>801</v>
       </c>
       <c r="B512" t="s">
-        <v>742</v>
+        <v>802</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>1151</v>
+        <v>691</v>
       </c>
       <c r="B513" t="s">
-        <v>1152</v>
+        <v>742</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="B514" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>284</v>
+        <v>1149</v>
       </c>
       <c r="B515" t="s">
-        <v>595</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>973</v>
+        <v>284</v>
       </c>
       <c r="B516" t="s">
-        <v>974</v>
+        <v>595</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>841</v>
+        <v>973</v>
       </c>
       <c r="B517" t="s">
-        <v>842</v>
+        <v>974</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>283</v>
+        <v>841</v>
       </c>
       <c r="B518" t="s">
-        <v>596</v>
+        <v>842</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>883</v>
+        <v>283</v>
       </c>
       <c r="B519" t="s">
-        <v>884</v>
+        <v>596</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>1180</v>
+        <v>883</v>
       </c>
       <c r="B520" t="s">
-        <v>1181</v>
+        <v>884</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>756</v>
+        <v>1180</v>
       </c>
       <c r="B521" t="s">
-        <v>757</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>1078</v>
+        <v>756</v>
       </c>
       <c r="B522" t="s">
-        <v>1079</v>
+        <v>757</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>67</v>
+        <v>1078</v>
       </c>
       <c r="B523" t="s">
-        <v>597</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B524" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="B525" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>289</v>
+        <v>95</v>
       </c>
       <c r="B526" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B527" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="B528" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>193</v>
+        <v>264</v>
       </c>
       <c r="B529" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>901</v>
+        <v>193</v>
       </c>
       <c r="B530" t="s">
-        <v>902</v>
+        <v>603</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>44</v>
+        <v>901</v>
       </c>
       <c r="B531" t="s">
-        <v>1125</v>
+        <v>902</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>1070</v>
+        <v>44</v>
       </c>
       <c r="B532" t="s">
-        <v>1071</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>324</v>
+        <v>1070</v>
       </c>
       <c r="B533" t="s">
-        <v>604</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B534" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>849</v>
+        <v>325</v>
       </c>
       <c r="B535" t="s">
-        <v>850</v>
+        <v>605</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>887</v>
+        <v>849</v>
       </c>
       <c r="B536" t="s">
-        <v>888</v>
+        <v>850</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>869</v>
+        <v>887</v>
       </c>
       <c r="B537" t="s">
-        <v>870</v>
+        <v>888</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>33</v>
+        <v>869</v>
       </c>
       <c r="B538" t="s">
-        <v>606</v>
+        <v>870</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B539" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>1143</v>
+        <v>36</v>
       </c>
       <c r="B540" t="s">
-        <v>1144</v>
+        <v>607</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>309</v>
+        <v>1143</v>
       </c>
       <c r="B541" t="s">
-        <v>608</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>257</v>
+        <v>309</v>
       </c>
       <c r="B542" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>302</v>
+        <v>257</v>
       </c>
       <c r="B543" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>228</v>
+        <v>302</v>
       </c>
       <c r="B544" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c r="B545" t="s">
-        <v>18</v>
+        <v>611</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>655</v>
+        <v>17</v>
       </c>
       <c r="B546" t="s">
-        <v>743</v>
+        <v>18</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>785</v>
+        <v>655</v>
       </c>
       <c r="B547" t="s">
-        <v>786</v>
+        <v>743</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>142</v>
+        <v>785</v>
       </c>
       <c r="B548" t="s">
-        <v>612</v>
+        <v>786</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>1178</v>
+        <v>142</v>
       </c>
       <c r="B549" t="s">
-        <v>1179</v>
+        <v>612</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>956</v>
+        <v>1178</v>
       </c>
       <c r="B550" t="s">
-        <v>957</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>54</v>
+        <v>956</v>
       </c>
       <c r="B551" t="s">
-        <v>613</v>
+        <v>957</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>265</v>
+        <v>54</v>
       </c>
       <c r="B552" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>976</v>
+        <v>265</v>
       </c>
       <c r="B553" t="s">
-        <v>975</v>
+        <v>614</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>56</v>
+        <v>976</v>
       </c>
       <c r="B554" t="s">
-        <v>615</v>
+        <v>975</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>185</v>
+        <v>56</v>
       </c>
       <c r="B555" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="B556" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="B557" t="s">
-        <v>1146</v>
+        <v>617</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B558" t="s">
-        <v>1124</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>1170</v>
+        <v>40</v>
       </c>
       <c r="B559" t="s">
-        <v>1171</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>165</v>
+        <v>1170</v>
       </c>
       <c r="B560" t="s">
-        <v>618</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="B561" t="s">
-        <v>11</v>
+        <v>618</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>250</v>
+        <v>12</v>
       </c>
       <c r="B562" t="s">
-        <v>619</v>
+        <v>11</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>27</v>
+        <v>250</v>
       </c>
       <c r="B563" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>1040</v>
+        <v>27</v>
       </c>
       <c r="B564" t="s">
-        <v>1041</v>
+        <v>620</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>28</v>
+        <v>1040</v>
       </c>
       <c r="B565" t="s">
-        <v>621</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>1205</v>
+        <v>28</v>
       </c>
       <c r="B566" t="s">
-        <v>1206</v>
+        <v>621</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>255</v>
+        <v>1205</v>
       </c>
       <c r="B567" t="s">
-        <v>622</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>795</v>
+        <v>255</v>
       </c>
       <c r="B568" t="s">
-        <v>796</v>
+        <v>622</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>267</v>
+        <v>795</v>
       </c>
       <c r="B569" t="s">
-        <v>623</v>
+        <v>796</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>661</v>
+        <v>267</v>
       </c>
       <c r="B570" t="s">
-        <v>744</v>
+        <v>623</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B571" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>139</v>
+        <v>662</v>
       </c>
       <c r="B572" t="s">
-        <v>624</v>
+        <v>745</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="B573" t="s">
-        <v>2</v>
+        <v>624</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="B574" t="s">
-        <v>625</v>
+        <v>2</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>1034</v>
+        <v>105</v>
       </c>
       <c r="B575" t="s">
-        <v>1123</v>
+        <v>625</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>865</v>
+        <v>1034</v>
       </c>
       <c r="B576" t="s">
-        <v>866</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>1035</v>
+        <v>865</v>
       </c>
       <c r="B577" t="s">
-        <v>1122</v>
+        <v>866</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>292</v>
+        <v>1035</v>
       </c>
       <c r="B578" t="s">
-        <v>626</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>8</v>
+        <v>292</v>
       </c>
       <c r="B579" t="s">
-        <v>11</v>
+        <v>626</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>335</v>
+        <v>8</v>
       </c>
       <c r="B580" t="s">
-        <v>627</v>
+        <v>11</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B581" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>259</v>
+        <v>332</v>
       </c>
       <c r="B582" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>319</v>
+        <v>259</v>
       </c>
       <c r="B583" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>859</v>
+        <v>319</v>
       </c>
       <c r="B584" t="s">
-        <v>860</v>
+        <v>630</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>1174</v>
+        <v>859</v>
       </c>
       <c r="B585" t="s">
-        <v>1175</v>
+        <v>860</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>268</v>
+        <v>1174</v>
       </c>
       <c r="B586" t="s">
-        <v>631</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B587" t="s">
-        <v>1117</v>
+        <v>631</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B588" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B589" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B590" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B591" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B592" t="s">
-        <v>1116</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>92</v>
+        <v>272</v>
       </c>
       <c r="B593" t="s">
-        <v>632</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>200</v>
+        <v>92</v>
       </c>
       <c r="B594" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B595" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="B596" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>693</v>
+        <v>172</v>
       </c>
       <c r="B597" t="s">
-        <v>746</v>
+        <v>635</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>252</v>
+        <v>693</v>
       </c>
       <c r="B598" t="s">
-        <v>636</v>
+        <v>746</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>694</v>
+        <v>252</v>
       </c>
       <c r="B599" t="s">
-        <v>747</v>
+        <v>636</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>189</v>
+        <v>694</v>
       </c>
       <c r="B600" t="s">
-        <v>637</v>
+        <v>747</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>989</v>
+        <v>189</v>
       </c>
       <c r="B601" t="s">
-        <v>990</v>
+        <v>637</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>311</v>
+        <v>989</v>
       </c>
       <c r="B602" t="s">
-        <v>638</v>
+        <v>990</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B603" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>1033</v>
+        <v>312</v>
       </c>
       <c r="B604" t="s">
-        <v>1115</v>
+        <v>639</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>1005</v>
+        <v>1033</v>
       </c>
       <c r="B605" t="s">
-        <v>1006</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>81</v>
+        <v>1005</v>
       </c>
       <c r="B606" t="s">
-        <v>640</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>651</v>
+        <v>81</v>
       </c>
       <c r="B607" t="s">
-        <v>748</v>
+        <v>640</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>922</v>
+        <v>651</v>
       </c>
       <c r="B608" t="s">
-        <v>923</v>
+        <v>748</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>642</v>
+        <v>922</v>
       </c>
       <c r="B609" t="s">
-        <v>749</v>
+        <v>923</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>969</v>
+        <v>642</v>
       </c>
       <c r="B610" t="s">
-        <v>970</v>
+        <v>749</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
+        <v>969</v>
+      </c>
+      <c r="B611" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A612" t="s">
         <v>1162</v>
       </c>
-      <c r="B611" t="s">
+      <c r="B612" t="s">
         <v>1163</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA7C5438-6779-40C6-8BC1-CFDDA8870D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4A2126-F41E-4680-86AE-909D22521FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1224" uniqueCount="1217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1234" uniqueCount="1227">
   <si>
     <t>trigger</t>
   </si>
@@ -3676,6 +3676,36 @@
   </si>
   <si>
     <t>retroperitoneal</t>
+  </si>
+  <si>
+    <t>sur</t>
+  </si>
+  <si>
+    <t>surrounding</t>
+  </si>
+  <si>
+    <t>scat</t>
+  </si>
+  <si>
+    <t>scattered</t>
+  </si>
+  <si>
+    <t>ggo</t>
+  </si>
+  <si>
+    <t>ground glass opacities</t>
+  </si>
+  <si>
+    <t>paco</t>
+  </si>
+  <si>
+    <t>patchy consolidation</t>
+  </si>
+  <si>
+    <t>movt</t>
+  </si>
+  <si>
+    <t>movement</t>
   </si>
 </sst>
 </file>
@@ -3731,10 +3761,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B612" totalsRowShown="0">
-  <autoFilter ref="A1:B612" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B612">
-    <sortCondition ref="A1:A612"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B617" totalsRowShown="0">
+  <autoFilter ref="A1:B617" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B617">
+    <sortCondition ref="A1:A617"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4007,7 +4037,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B612"/>
+  <dimension ref="A1:B617"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -5760,991 +5790,991 @@
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>1056</v>
+        <v>1221</v>
       </c>
       <c r="B219" t="s">
-        <v>1057</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>118</v>
+        <v>1056</v>
       </c>
       <c r="B220" t="s">
-        <v>444</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>641</v>
+        <v>118</v>
       </c>
       <c r="B221" t="s">
-        <v>723</v>
+        <v>444</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>815</v>
+        <v>641</v>
       </c>
       <c r="B222" t="s">
-        <v>816</v>
+        <v>723</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>298</v>
+        <v>815</v>
       </c>
       <c r="B223" t="s">
-        <v>445</v>
+        <v>816</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>643</v>
+        <v>298</v>
       </c>
       <c r="B224" t="s">
-        <v>724</v>
+        <v>445</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B225" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>1036</v>
+        <v>644</v>
       </c>
       <c r="B226" t="s">
-        <v>1037</v>
+        <v>725</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>90</v>
+        <v>1036</v>
       </c>
       <c r="B227" t="s">
-        <v>446</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B228" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B229" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>1072</v>
+        <v>89</v>
       </c>
       <c r="B230" t="s">
-        <v>1073</v>
+        <v>448</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>23</v>
+        <v>1072</v>
       </c>
       <c r="B231" t="s">
-        <v>1136</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B232" t="s">
-        <v>6</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>1141</v>
+        <v>5</v>
       </c>
       <c r="B233" t="s">
-        <v>1142</v>
+        <v>6</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>126</v>
+        <v>1141</v>
       </c>
       <c r="B234" t="s">
-        <v>449</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B235" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B236" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B237" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B238" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>277</v>
+        <v>119</v>
       </c>
       <c r="B239" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>1074</v>
+        <v>277</v>
       </c>
       <c r="B240" t="s">
-        <v>1075</v>
+        <v>454</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>9</v>
+        <v>1074</v>
       </c>
       <c r="B241" t="s">
-        <v>10</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="B242" t="s">
-        <v>455</v>
+        <v>10</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B243" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="B244" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="B245" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>77</v>
+        <v>262</v>
       </c>
       <c r="B246" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>938</v>
+        <v>77</v>
       </c>
       <c r="B247" t="s">
-        <v>939</v>
+        <v>459</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>1172</v>
+        <v>938</v>
       </c>
       <c r="B248" t="s">
-        <v>1173</v>
+        <v>939</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>168</v>
+        <v>1172</v>
       </c>
       <c r="B249" t="s">
-        <v>460</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B250" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>835</v>
+        <v>167</v>
       </c>
       <c r="B251" t="s">
-        <v>836</v>
+        <v>461</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>791</v>
+        <v>835</v>
       </c>
       <c r="B252" t="s">
-        <v>792</v>
+        <v>836</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>304</v>
+        <v>791</v>
       </c>
       <c r="B253" t="s">
-        <v>462</v>
+        <v>792</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>758</v>
+        <v>304</v>
       </c>
       <c r="B254" t="s">
-        <v>759</v>
+        <v>462</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>897</v>
+        <v>758</v>
       </c>
       <c r="B255" t="s">
-        <v>898</v>
+        <v>759</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>652</v>
+        <v>897</v>
       </c>
       <c r="B256" t="s">
-        <v>726</v>
+        <v>898</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>86</v>
+        <v>652</v>
       </c>
       <c r="B257" t="s">
-        <v>463</v>
+        <v>726</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B258" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="B259" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B260" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B261" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>251</v>
+        <v>158</v>
       </c>
       <c r="B262" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="B263" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>326</v>
+        <v>285</v>
       </c>
       <c r="B264" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B265" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>229</v>
+        <v>327</v>
       </c>
       <c r="B266" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>55</v>
+        <v>229</v>
       </c>
       <c r="B267" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>657</v>
+        <v>55</v>
       </c>
       <c r="B268" t="s">
-        <v>727</v>
+        <v>473</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>235</v>
+        <v>657</v>
       </c>
       <c r="B269" t="s">
-        <v>474</v>
+        <v>727</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="B270" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="B271" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>766</v>
+        <v>236</v>
       </c>
       <c r="B272" t="s">
-        <v>1009</v>
+        <v>476</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>1012</v>
+        <v>766</v>
       </c>
       <c r="B273" t="s">
-        <v>767</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>164</v>
+        <v>1012</v>
       </c>
       <c r="B274" t="s">
-        <v>477</v>
+        <v>767</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="B275" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B276" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>313</v>
+        <v>204</v>
       </c>
       <c r="B277" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>873</v>
+        <v>313</v>
       </c>
       <c r="B278" t="s">
-        <v>874</v>
+        <v>480</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>997</v>
+        <v>873</v>
       </c>
       <c r="B279" t="s">
-        <v>998</v>
+        <v>874</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>258</v>
+        <v>997</v>
       </c>
       <c r="B280" t="s">
-        <v>481</v>
+        <v>998</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>983</v>
+        <v>258</v>
       </c>
       <c r="B281" t="s">
-        <v>984</v>
+        <v>481</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>160</v>
+        <v>983</v>
       </c>
       <c r="B282" t="s">
-        <v>482</v>
+        <v>984</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>692</v>
+        <v>160</v>
       </c>
       <c r="B283" t="s">
-        <v>728</v>
+        <v>482</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>1166</v>
+        <v>692</v>
       </c>
       <c r="B284" t="s">
-        <v>1167</v>
+        <v>728</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>760</v>
+        <v>1166</v>
       </c>
       <c r="B285" t="s">
-        <v>761</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>895</v>
+        <v>760</v>
       </c>
       <c r="B286" t="s">
-        <v>896</v>
+        <v>761</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B287" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>184</v>
+        <v>893</v>
       </c>
       <c r="B288" t="s">
-        <v>483</v>
+        <v>894</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>244</v>
+        <v>184</v>
       </c>
       <c r="B289" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B290" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>686</v>
+        <v>243</v>
       </c>
       <c r="B291" t="s">
-        <v>729</v>
+        <v>485</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B292" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B293" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B294" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B295" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>1192</v>
+        <v>690</v>
       </c>
       <c r="B296" t="s">
-        <v>1193</v>
+        <v>733</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>280</v>
+        <v>1192</v>
       </c>
       <c r="B297" t="s">
-        <v>486</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B298" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>49</v>
+        <v>281</v>
       </c>
       <c r="B299" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B300" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="B301" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="B302" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>1190</v>
+        <v>72</v>
       </c>
       <c r="B303" t="s">
-        <v>1191</v>
+        <v>490</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>221</v>
+        <v>1190</v>
       </c>
       <c r="B304" t="s">
-        <v>492</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>1194</v>
+        <v>221</v>
       </c>
       <c r="B305" t="s">
-        <v>1195</v>
+        <v>492</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>15</v>
+        <v>1194</v>
       </c>
       <c r="B306" t="s">
-        <v>16</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>1060</v>
+        <v>15</v>
       </c>
       <c r="B307" t="s">
-        <v>1061</v>
+        <v>16</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>920</v>
+        <v>1060</v>
       </c>
       <c r="B308" t="s">
-        <v>921</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>108</v>
+        <v>920</v>
       </c>
       <c r="B309" t="s">
-        <v>493</v>
+        <v>921</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>241</v>
+        <v>108</v>
       </c>
       <c r="B310" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>328</v>
+        <v>241</v>
       </c>
       <c r="B311" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>1100</v>
+        <v>328</v>
       </c>
       <c r="B312" t="s">
-        <v>1101</v>
+        <v>495</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>1052</v>
+        <v>1100</v>
       </c>
       <c r="B313" t="s">
-        <v>1053</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>121</v>
+        <v>1052</v>
       </c>
       <c r="B314" t="s">
-        <v>496</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>750</v>
+        <v>121</v>
       </c>
       <c r="B315" t="s">
-        <v>751</v>
+        <v>496</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>781</v>
+        <v>750</v>
       </c>
       <c r="B316" t="s">
-        <v>782</v>
+        <v>751</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>134</v>
+        <v>781</v>
       </c>
       <c r="B317" t="s">
-        <v>497</v>
+        <v>782</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="B318" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>224</v>
+        <v>63</v>
       </c>
       <c r="B319" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>25</v>
+        <v>224</v>
       </c>
       <c r="B320" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B321" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>207</v>
+        <v>26</v>
       </c>
       <c r="B322" t="s">
-        <v>1133</v>
+        <v>501</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>960</v>
+        <v>207</v>
       </c>
       <c r="B323" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>1113</v>
+        <v>960</v>
       </c>
       <c r="B324" t="s">
-        <v>1114</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>206</v>
+        <v>1113</v>
       </c>
       <c r="B325" t="s">
-        <v>1135</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B326" t="s">
-        <v>502</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B327" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="B328" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>663</v>
+        <v>145</v>
       </c>
       <c r="B329" t="s">
-        <v>734</v>
+        <v>504</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>171</v>
+        <v>663</v>
       </c>
       <c r="B330" t="s">
-        <v>505</v>
+        <v>734</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>1088</v>
+        <v>171</v>
       </c>
       <c r="B331" t="s">
-        <v>1089</v>
+        <v>505</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>263</v>
+        <v>1088</v>
       </c>
       <c r="B332" t="s">
-        <v>506</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>1090</v>
+        <v>263</v>
       </c>
       <c r="B333" t="s">
-        <v>1091</v>
+        <v>506</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>80</v>
+        <v>1090</v>
       </c>
       <c r="B334" t="s">
-        <v>507</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B335" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>191</v>
+        <v>65</v>
       </c>
       <c r="B336" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="B337" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>192</v>
+        <v>123</v>
       </c>
       <c r="B338" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="B339" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B340" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>1200</v>
+        <v>233</v>
       </c>
       <c r="B341" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>31</v>
+        <v>1200</v>
       </c>
       <c r="B342" t="s">
         <v>514</v>
@@ -6752,311 +6782,311 @@
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B343" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B344" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B345" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>306</v>
+        <v>71</v>
       </c>
       <c r="B346" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>222</v>
+        <v>306</v>
       </c>
       <c r="B347" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>315</v>
+        <v>222</v>
       </c>
       <c r="B348" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>278</v>
+        <v>315</v>
       </c>
       <c r="B349" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B350" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>831</v>
+        <v>279</v>
       </c>
       <c r="B351" t="s">
-        <v>832</v>
+        <v>522</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>48</v>
+        <v>831</v>
       </c>
       <c r="B352" t="s">
-        <v>523</v>
+        <v>832</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="B353" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="B354" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>223</v>
+        <v>52</v>
       </c>
       <c r="B355" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>1094</v>
+        <v>223</v>
       </c>
       <c r="B356" t="s">
-        <v>1095</v>
+        <v>526</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>1109</v>
+        <v>1094</v>
       </c>
       <c r="B357" t="s">
-        <v>1112</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>1050</v>
+        <v>1109</v>
       </c>
       <c r="B358" t="s">
-        <v>1051</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>96</v>
+        <v>1050</v>
       </c>
       <c r="B359" t="s">
-        <v>527</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>248</v>
+        <v>96</v>
       </c>
       <c r="B360" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B361" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>94</v>
+        <v>249</v>
       </c>
       <c r="B362" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>1064</v>
+        <v>94</v>
       </c>
       <c r="B363" t="s">
-        <v>1065</v>
+        <v>530</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>212</v>
+        <v>1064</v>
       </c>
       <c r="B364" t="s">
-        <v>531</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>916</v>
+        <v>212</v>
       </c>
       <c r="B365" t="s">
-        <v>917</v>
+        <v>531</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>914</v>
+        <v>1225</v>
       </c>
       <c r="B366" t="s">
-        <v>915</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B367" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>330</v>
+        <v>914</v>
       </c>
       <c r="B368" t="s">
-        <v>532</v>
+        <v>915</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>1066</v>
+        <v>918</v>
       </c>
       <c r="B369" t="s">
-        <v>1067</v>
+        <v>919</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>995</v>
+        <v>330</v>
       </c>
       <c r="B370" t="s">
-        <v>996</v>
+        <v>532</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>991</v>
+        <v>1066</v>
       </c>
       <c r="B371" t="s">
-        <v>992</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="B372" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>82</v>
+        <v>991</v>
       </c>
       <c r="B373" t="s">
-        <v>533</v>
+        <v>992</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>772</v>
+        <v>993</v>
       </c>
       <c r="B374" t="s">
-        <v>773</v>
+        <v>994</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="B375" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>654</v>
+        <v>772</v>
       </c>
       <c r="B376" t="s">
-        <v>735</v>
+        <v>773</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>821</v>
+        <v>197</v>
       </c>
       <c r="B377" t="s">
-        <v>822</v>
+        <v>534</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>1068</v>
+        <v>654</v>
       </c>
       <c r="B378" t="s">
-        <v>1069</v>
+        <v>735</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>3</v>
+        <v>821</v>
       </c>
       <c r="B379" t="s">
-        <v>4</v>
+        <v>822</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>958</v>
+        <v>1068</v>
       </c>
       <c r="B380" t="s">
-        <v>4</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>959</v>
+        <v>3</v>
       </c>
       <c r="B381" t="s">
         <v>4</v>
@@ -7064,1849 +7094,1889 @@
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>664</v>
+        <v>958</v>
       </c>
       <c r="B382" t="s">
-        <v>736</v>
+        <v>4</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>770</v>
+        <v>959</v>
       </c>
       <c r="B383" t="s">
-        <v>771</v>
+        <v>4</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>85</v>
+        <v>664</v>
       </c>
       <c r="B384" t="s">
-        <v>535</v>
+        <v>736</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>1062</v>
+        <v>770</v>
       </c>
       <c r="B385" t="s">
-        <v>1063</v>
+        <v>771</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>829</v>
+        <v>85</v>
       </c>
       <c r="B386" t="s">
-        <v>830</v>
+        <v>535</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>809</v>
+        <v>1062</v>
       </c>
       <c r="B387" t="s">
-        <v>810</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>187</v>
+        <v>829</v>
       </c>
       <c r="B388" t="s">
-        <v>536</v>
+        <v>830</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>827</v>
+        <v>809</v>
       </c>
       <c r="B389" t="s">
-        <v>828</v>
+        <v>810</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>934</v>
+        <v>187</v>
       </c>
       <c r="B390" t="s">
-        <v>1130</v>
+        <v>536</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>863</v>
+        <v>827</v>
       </c>
       <c r="B391" t="s">
-        <v>864</v>
+        <v>828</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>1044</v>
+        <v>934</v>
       </c>
       <c r="B392" t="s">
-        <v>1045</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>798</v>
+        <v>863</v>
       </c>
       <c r="B393" t="s">
-        <v>1131</v>
+        <v>864</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>797</v>
+        <v>1044</v>
       </c>
       <c r="B394" t="s">
-        <v>1132</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>13</v>
+        <v>798</v>
       </c>
       <c r="B395" t="s">
-        <v>14</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>817</v>
+        <v>797</v>
       </c>
       <c r="B396" t="s">
-        <v>818</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>186</v>
+        <v>13</v>
       </c>
       <c r="B397" t="s">
-        <v>537</v>
+        <v>14</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>811</v>
+        <v>817</v>
       </c>
       <c r="B398" t="s">
-        <v>812</v>
+        <v>818</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>320</v>
+        <v>186</v>
       </c>
       <c r="B399" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>656</v>
+        <v>811</v>
       </c>
       <c r="B400" t="s">
-        <v>737</v>
+        <v>812</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>855</v>
+        <v>320</v>
       </c>
       <c r="B401" t="s">
-        <v>856</v>
+        <v>538</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B402" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>653</v>
+        <v>855</v>
       </c>
       <c r="B403" t="s">
-        <v>739</v>
+        <v>856</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>1207</v>
+        <v>658</v>
       </c>
       <c r="B404" t="s">
-        <v>1208</v>
+        <v>738</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>256</v>
+        <v>653</v>
       </c>
       <c r="B405" t="s">
-        <v>539</v>
+        <v>739</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>260</v>
+        <v>1207</v>
       </c>
       <c r="B406" t="s">
-        <v>540</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B407" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>188</v>
+        <v>260</v>
       </c>
       <c r="B408" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>190</v>
+        <v>261</v>
       </c>
       <c r="B409" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>936</v>
+        <v>188</v>
       </c>
       <c r="B410" t="s">
-        <v>937</v>
+        <v>542</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>1031</v>
+        <v>190</v>
       </c>
       <c r="B411" t="s">
-        <v>1032</v>
+        <v>543</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>209</v>
+        <v>936</v>
       </c>
       <c r="B412" t="s">
-        <v>544</v>
+        <v>937</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>851</v>
+        <v>1031</v>
       </c>
       <c r="B413" t="s">
-        <v>852</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>143</v>
+        <v>1223</v>
       </c>
       <c r="B414" t="s">
-        <v>545</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>140</v>
+        <v>209</v>
       </c>
       <c r="B415" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>1203</v>
+        <v>851</v>
       </c>
       <c r="B416" t="s">
-        <v>1204</v>
+        <v>852</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>254</v>
+        <v>143</v>
       </c>
       <c r="B417" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>331</v>
+        <v>140</v>
       </c>
       <c r="B418" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>210</v>
+        <v>1203</v>
       </c>
       <c r="B419" t="s">
-        <v>549</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="B420" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>73</v>
+        <v>331</v>
       </c>
       <c r="B421" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>342</v>
+        <v>210</v>
       </c>
       <c r="B422" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>308</v>
+        <v>234</v>
       </c>
       <c r="B423" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>843</v>
+        <v>73</v>
       </c>
       <c r="B424" t="s">
-        <v>844</v>
+        <v>551</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>845</v>
+        <v>342</v>
       </c>
       <c r="B425" t="s">
-        <v>846</v>
+        <v>552</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>220</v>
+        <v>308</v>
       </c>
       <c r="B426" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>909</v>
+        <v>843</v>
       </c>
       <c r="B427" t="s">
-        <v>910</v>
+        <v>844</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>963</v>
+        <v>845</v>
       </c>
       <c r="B428" t="s">
-        <v>964</v>
+        <v>846</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>1188</v>
+        <v>220</v>
       </c>
       <c r="B429" t="s">
-        <v>1189</v>
+        <v>554</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>227</v>
+        <v>909</v>
       </c>
       <c r="B430" t="s">
-        <v>555</v>
+        <v>910</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>334</v>
+        <v>963</v>
       </c>
       <c r="B431" t="s">
-        <v>1161</v>
+        <v>964</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>971</v>
+        <v>1188</v>
       </c>
       <c r="B432" t="s">
-        <v>972</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>778</v>
+        <v>227</v>
       </c>
       <c r="B433" t="s">
-        <v>779</v>
+        <v>555</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>294</v>
+        <v>334</v>
       </c>
       <c r="B434" t="s">
-        <v>556</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>952</v>
+        <v>971</v>
       </c>
       <c r="B435" t="s">
-        <v>953</v>
+        <v>972</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>339</v>
+        <v>778</v>
       </c>
       <c r="B436" t="s">
-        <v>557</v>
+        <v>779</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>780</v>
+        <v>294</v>
       </c>
       <c r="B437" t="s">
-        <v>779</v>
+        <v>556</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>340</v>
+        <v>952</v>
       </c>
       <c r="B438" t="s">
-        <v>558</v>
+        <v>953</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B439" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>645</v>
+        <v>780</v>
       </c>
       <c r="B440" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>39</v>
+        <v>340</v>
       </c>
       <c r="B441" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>38</v>
+        <v>341</v>
       </c>
       <c r="B442" t="s">
-        <v>1129</v>
+        <v>559</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>343</v>
+        <v>645</v>
       </c>
       <c r="B443" t="s">
-        <v>561</v>
+        <v>740</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="B444" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>1029</v>
+        <v>38</v>
       </c>
       <c r="B445" t="s">
-        <v>1030</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>903</v>
+        <v>343</v>
       </c>
       <c r="B446" t="s">
-        <v>904</v>
+        <v>561</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B447" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="B448" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>98</v>
+        <v>903</v>
       </c>
       <c r="B449" t="s">
-        <v>564</v>
+        <v>904</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="B450" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>666</v>
+        <v>1025</v>
       </c>
       <c r="B451" t="s">
-        <v>741</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>1107</v>
+        <v>98</v>
       </c>
       <c r="B452" t="s">
-        <v>1024</v>
+        <v>564</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>823</v>
+        <v>99</v>
       </c>
       <c r="B453" t="s">
-        <v>824</v>
+        <v>565</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>113</v>
+        <v>666</v>
       </c>
       <c r="B454" t="s">
-        <v>566</v>
+        <v>741</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>889</v>
+        <v>1107</v>
       </c>
       <c r="B455" t="s">
-        <v>890</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>45</v>
+        <v>823</v>
       </c>
       <c r="B456" t="s">
-        <v>1128</v>
+        <v>824</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>290</v>
+        <v>113</v>
       </c>
       <c r="B457" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>299</v>
+        <v>889</v>
       </c>
       <c r="B458" t="s">
-        <v>568</v>
+        <v>890</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B459" t="s">
-        <v>569</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>847</v>
+        <v>290</v>
       </c>
       <c r="B460" t="s">
-        <v>848</v>
+        <v>567</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>51</v>
+        <v>299</v>
       </c>
       <c r="B461" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>871</v>
+        <v>47</v>
       </c>
       <c r="B462" t="s">
-        <v>872</v>
+        <v>569</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>114</v>
+        <v>847</v>
       </c>
       <c r="B463" t="s">
-        <v>571</v>
+        <v>848</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>853</v>
+        <v>51</v>
       </c>
       <c r="B464" t="s">
-        <v>854</v>
+        <v>570</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>144</v>
+        <v>871</v>
       </c>
       <c r="B465" t="s">
-        <v>572</v>
+        <v>872</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>1080</v>
+        <v>114</v>
       </c>
       <c r="B466" t="s">
-        <v>1081</v>
+        <v>571</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>176</v>
+        <v>853</v>
       </c>
       <c r="B467" t="s">
-        <v>573</v>
+        <v>854</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>316</v>
+        <v>144</v>
       </c>
       <c r="B468" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>29</v>
+        <v>1080</v>
       </c>
       <c r="B469" t="s">
-        <v>575</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>1104</v>
+        <v>176</v>
       </c>
       <c r="B470" t="s">
-        <v>1105</v>
+        <v>573</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>1018</v>
+        <v>316</v>
       </c>
       <c r="B471" t="s">
-        <v>1019</v>
+        <v>574</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>293</v>
+        <v>29</v>
       </c>
       <c r="B472" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>981</v>
+        <v>1104</v>
       </c>
       <c r="B473" t="s">
-        <v>982</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>301</v>
+        <v>1018</v>
       </c>
       <c r="B474" t="s">
-        <v>577</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>1003</v>
+        <v>293</v>
       </c>
       <c r="B475" t="s">
-        <v>1004</v>
+        <v>576</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>1007</v>
+        <v>981</v>
       </c>
       <c r="B476" t="s">
-        <v>1008</v>
+        <v>982</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>75</v>
+        <v>301</v>
       </c>
       <c r="B477" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>76</v>
+        <v>1003</v>
       </c>
       <c r="B478" t="s">
-        <v>579</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>78</v>
+        <v>1007</v>
       </c>
       <c r="B479" t="s">
-        <v>580</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>329</v>
+        <v>75</v>
       </c>
       <c r="B480" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>752</v>
+        <v>76</v>
       </c>
       <c r="B481" t="s">
-        <v>753</v>
+        <v>579</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>805</v>
+        <v>78</v>
       </c>
       <c r="B482" t="s">
-        <v>806</v>
+        <v>580</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>135</v>
+        <v>329</v>
       </c>
       <c r="B483" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>1186</v>
+        <v>752</v>
       </c>
       <c r="B484" t="s">
-        <v>1187</v>
+        <v>753</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>1038</v>
+        <v>805</v>
       </c>
       <c r="B485" t="s">
-        <v>1039</v>
+        <v>806</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>215</v>
+        <v>135</v>
       </c>
       <c r="B486" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>935</v>
+        <v>1186</v>
       </c>
       <c r="B487" t="s">
-        <v>1145</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>216</v>
+        <v>1038</v>
       </c>
       <c r="B488" t="s">
-        <v>1126</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>317</v>
+        <v>215</v>
       </c>
       <c r="B489" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>1082</v>
+        <v>935</v>
       </c>
       <c r="B490" t="s">
-        <v>1083</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B491" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>999</v>
+        <v>317</v>
       </c>
       <c r="B492" t="s">
-        <v>1000</v>
+        <v>584</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>1001</v>
+        <v>1082</v>
       </c>
       <c r="B493" t="s">
-        <v>1002</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="B494" t="s">
-        <v>585</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>948</v>
+        <v>999</v>
       </c>
       <c r="B495" t="s">
-        <v>949</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>1098</v>
+        <v>1001</v>
       </c>
       <c r="B496" t="s">
-        <v>1099</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>1048</v>
+        <v>225</v>
       </c>
       <c r="B497" t="s">
-        <v>1049</v>
+        <v>585</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>93</v>
+        <v>948</v>
       </c>
       <c r="B498" t="s">
-        <v>586</v>
+        <v>949</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>120</v>
+        <v>1098</v>
       </c>
       <c r="B499" t="s">
-        <v>587</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>783</v>
+        <v>1048</v>
       </c>
       <c r="B500" t="s">
-        <v>784</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="B501" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="B502" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>66</v>
+        <v>783</v>
       </c>
       <c r="B503" t="s">
-        <v>590</v>
+        <v>784</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>825</v>
+        <v>133</v>
       </c>
       <c r="B504" t="s">
-        <v>826</v>
+        <v>588</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>950</v>
+        <v>62</v>
       </c>
       <c r="B505" t="s">
-        <v>951</v>
+        <v>589</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>1215</v>
+        <v>66</v>
       </c>
       <c r="B506" t="s">
-        <v>1216</v>
+        <v>590</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>79</v>
+        <v>825</v>
       </c>
       <c r="B507" t="s">
-        <v>591</v>
+        <v>826</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>64</v>
+        <v>950</v>
       </c>
       <c r="B508" t="s">
-        <v>592</v>
+        <v>951</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>122</v>
+        <v>1215</v>
       </c>
       <c r="B509" t="s">
-        <v>593</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>1184</v>
+        <v>79</v>
       </c>
       <c r="B510" t="s">
-        <v>1185</v>
+        <v>591</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>181</v>
+        <v>64</v>
       </c>
       <c r="B511" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>801</v>
+        <v>122</v>
       </c>
       <c r="B512" t="s">
-        <v>802</v>
+        <v>593</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>691</v>
+        <v>1184</v>
       </c>
       <c r="B513" t="s">
-        <v>742</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>1151</v>
+        <v>181</v>
       </c>
       <c r="B514" t="s">
-        <v>1152</v>
+        <v>594</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>1149</v>
+        <v>801</v>
       </c>
       <c r="B515" t="s">
-        <v>1150</v>
+        <v>802</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>284</v>
+        <v>691</v>
       </c>
       <c r="B516" t="s">
-        <v>595</v>
+        <v>742</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>973</v>
+        <v>1151</v>
       </c>
       <c r="B517" t="s">
-        <v>974</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>841</v>
+        <v>1149</v>
       </c>
       <c r="B518" t="s">
-        <v>842</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B519" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>883</v>
+        <v>973</v>
       </c>
       <c r="B520" t="s">
-        <v>884</v>
+        <v>974</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>1180</v>
+        <v>1219</v>
       </c>
       <c r="B521" t="s">
-        <v>1181</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>756</v>
+        <v>841</v>
       </c>
       <c r="B522" t="s">
-        <v>757</v>
+        <v>842</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>1078</v>
+        <v>283</v>
       </c>
       <c r="B523" t="s">
-        <v>1079</v>
+        <v>596</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>67</v>
+        <v>883</v>
       </c>
       <c r="B524" t="s">
-        <v>597</v>
+        <v>884</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>68</v>
+        <v>1180</v>
       </c>
       <c r="B525" t="s">
-        <v>598</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>95</v>
+        <v>756</v>
       </c>
       <c r="B526" t="s">
-        <v>599</v>
+        <v>757</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>289</v>
+        <v>1078</v>
       </c>
       <c r="B527" t="s">
-        <v>600</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>297</v>
+        <v>67</v>
       </c>
       <c r="B528" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>264</v>
+        <v>68</v>
       </c>
       <c r="B529" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>193</v>
+        <v>95</v>
       </c>
       <c r="B530" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>901</v>
+        <v>289</v>
       </c>
       <c r="B531" t="s">
-        <v>902</v>
+        <v>600</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>44</v>
+        <v>297</v>
       </c>
       <c r="B532" t="s">
-        <v>1125</v>
+        <v>601</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>1070</v>
+        <v>264</v>
       </c>
       <c r="B533" t="s">
-        <v>1071</v>
+        <v>602</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>324</v>
+        <v>193</v>
       </c>
       <c r="B534" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>325</v>
+        <v>901</v>
       </c>
       <c r="B535" t="s">
-        <v>605</v>
+        <v>902</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>849</v>
+        <v>44</v>
       </c>
       <c r="B536" t="s">
-        <v>850</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>887</v>
+        <v>1070</v>
       </c>
       <c r="B537" t="s">
-        <v>888</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>869</v>
+        <v>324</v>
       </c>
       <c r="B538" t="s">
-        <v>870</v>
+        <v>604</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>33</v>
+        <v>325</v>
       </c>
       <c r="B539" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>36</v>
+        <v>849</v>
       </c>
       <c r="B540" t="s">
-        <v>607</v>
+        <v>850</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>1143</v>
+        <v>887</v>
       </c>
       <c r="B541" t="s">
-        <v>1144</v>
+        <v>888</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>309</v>
+        <v>869</v>
       </c>
       <c r="B542" t="s">
-        <v>608</v>
+        <v>870</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>257</v>
+        <v>33</v>
       </c>
       <c r="B543" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>302</v>
+        <v>36</v>
       </c>
       <c r="B544" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>228</v>
+        <v>1143</v>
       </c>
       <c r="B545" t="s">
-        <v>611</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>17</v>
+        <v>309</v>
       </c>
       <c r="B546" t="s">
-        <v>18</v>
+        <v>608</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>655</v>
+        <v>257</v>
       </c>
       <c r="B547" t="s">
-        <v>743</v>
+        <v>609</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>785</v>
+        <v>302</v>
       </c>
       <c r="B548" t="s">
-        <v>786</v>
+        <v>610</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>142</v>
+        <v>228</v>
       </c>
       <c r="B549" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>1178</v>
+        <v>17</v>
       </c>
       <c r="B550" t="s">
-        <v>1179</v>
+        <v>18</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>956</v>
+        <v>655</v>
       </c>
       <c r="B551" t="s">
-        <v>957</v>
+        <v>743</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>54</v>
+        <v>785</v>
       </c>
       <c r="B552" t="s">
-        <v>613</v>
+        <v>786</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>265</v>
+        <v>142</v>
       </c>
       <c r="B553" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>976</v>
+        <v>1178</v>
       </c>
       <c r="B554" t="s">
-        <v>975</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>56</v>
+        <v>956</v>
       </c>
       <c r="B555" t="s">
-        <v>615</v>
+        <v>957</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>185</v>
+        <v>54</v>
       </c>
       <c r="B556" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="B557" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>43</v>
+        <v>976</v>
       </c>
       <c r="B558" t="s">
-        <v>1146</v>
+        <v>975</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="B559" t="s">
-        <v>1124</v>
+        <v>615</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>1170</v>
+        <v>1217</v>
       </c>
       <c r="B560" t="s">
-        <v>1171</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="B561" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>12</v>
+        <v>159</v>
       </c>
       <c r="B562" t="s">
-        <v>11</v>
+        <v>617</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>250</v>
+        <v>43</v>
       </c>
       <c r="B563" t="s">
-        <v>619</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B564" t="s">
-        <v>620</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>1040</v>
+        <v>1170</v>
       </c>
       <c r="B565" t="s">
-        <v>1041</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>28</v>
+        <v>165</v>
       </c>
       <c r="B566" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>1205</v>
+        <v>12</v>
       </c>
       <c r="B567" t="s">
-        <v>1206</v>
+        <v>11</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B568" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>795</v>
+        <v>27</v>
       </c>
       <c r="B569" t="s">
-        <v>796</v>
+        <v>620</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>267</v>
+        <v>1040</v>
       </c>
       <c r="B570" t="s">
-        <v>623</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>661</v>
+        <v>28</v>
       </c>
       <c r="B571" t="s">
-        <v>744</v>
+        <v>621</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>662</v>
+        <v>1205</v>
       </c>
       <c r="B572" t="s">
-        <v>745</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>139</v>
+        <v>255</v>
       </c>
       <c r="B573" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>7</v>
+        <v>795</v>
       </c>
       <c r="B574" t="s">
-        <v>2</v>
+        <v>796</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>105</v>
+        <v>267</v>
       </c>
       <c r="B575" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>1034</v>
+        <v>661</v>
       </c>
       <c r="B576" t="s">
-        <v>1123</v>
+        <v>744</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>865</v>
+        <v>662</v>
       </c>
       <c r="B577" t="s">
-        <v>866</v>
+        <v>745</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>1035</v>
+        <v>139</v>
       </c>
       <c r="B578" t="s">
-        <v>1122</v>
+        <v>624</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>292</v>
+        <v>7</v>
       </c>
       <c r="B579" t="s">
-        <v>626</v>
+        <v>2</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="B580" t="s">
-        <v>11</v>
+        <v>625</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>335</v>
+        <v>1034</v>
       </c>
       <c r="B581" t="s">
-        <v>627</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>332</v>
+        <v>865</v>
       </c>
       <c r="B582" t="s">
-        <v>628</v>
+        <v>866</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>259</v>
+        <v>1035</v>
       </c>
       <c r="B583" t="s">
-        <v>629</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>319</v>
+        <v>292</v>
       </c>
       <c r="B584" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>859</v>
+        <v>8</v>
       </c>
       <c r="B585" t="s">
-        <v>860</v>
+        <v>11</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>1174</v>
+        <v>335</v>
       </c>
       <c r="B586" t="s">
-        <v>1175</v>
+        <v>627</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="B587" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="B588" t="s">
-        <v>1117</v>
+        <v>629</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>274</v>
+        <v>319</v>
       </c>
       <c r="B589" t="s">
-        <v>1118</v>
+        <v>630</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>270</v>
+        <v>859</v>
       </c>
       <c r="B590" t="s">
-        <v>1119</v>
+        <v>860</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>273</v>
+        <v>1174</v>
       </c>
       <c r="B591" t="s">
-        <v>1120</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B592" t="s">
-        <v>1121</v>
+        <v>631</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B593" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>92</v>
+        <v>274</v>
       </c>
       <c r="B594" t="s">
-        <v>632</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="B595" t="s">
-        <v>633</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>203</v>
+        <v>273</v>
       </c>
       <c r="B596" t="s">
-        <v>634</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>172</v>
+        <v>269</v>
       </c>
       <c r="B597" t="s">
-        <v>635</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>693</v>
+        <v>272</v>
       </c>
       <c r="B598" t="s">
-        <v>746</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>252</v>
+        <v>92</v>
       </c>
       <c r="B599" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>694</v>
+        <v>200</v>
       </c>
       <c r="B600" t="s">
-        <v>747</v>
+        <v>633</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="B601" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>989</v>
+        <v>172</v>
       </c>
       <c r="B602" t="s">
-        <v>990</v>
+        <v>635</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>311</v>
+        <v>693</v>
       </c>
       <c r="B603" t="s">
-        <v>638</v>
+        <v>746</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>312</v>
+        <v>252</v>
       </c>
       <c r="B604" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>1033</v>
+        <v>694</v>
       </c>
       <c r="B605" t="s">
-        <v>1115</v>
+        <v>747</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>1005</v>
+        <v>189</v>
       </c>
       <c r="B606" t="s">
-        <v>1006</v>
+        <v>637</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>81</v>
+        <v>989</v>
       </c>
       <c r="B607" t="s">
-        <v>640</v>
+        <v>990</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>651</v>
+        <v>311</v>
       </c>
       <c r="B608" t="s">
-        <v>748</v>
+        <v>638</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>922</v>
+        <v>312</v>
       </c>
       <c r="B609" t="s">
-        <v>923</v>
+        <v>639</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>642</v>
+        <v>1033</v>
       </c>
       <c r="B610" t="s">
-        <v>749</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>969</v>
+        <v>1005</v>
       </c>
       <c r="B611" t="s">
-        <v>970</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
+        <v>81</v>
+      </c>
+      <c r="B612" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A613" t="s">
+        <v>651</v>
+      </c>
+      <c r="B613" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A614" t="s">
+        <v>922</v>
+      </c>
+      <c r="B614" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A615" t="s">
+        <v>642</v>
+      </c>
+      <c r="B615" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A616" t="s">
+        <v>969</v>
+      </c>
+      <c r="B616" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A617" t="s">
         <v>1162</v>
       </c>
-      <c r="B612" t="s">
+      <c r="B617" t="s">
         <v>1163</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D4A2126-F41E-4680-86AE-909D22521FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09CFFA8-486A-4F88-905E-153893DD928A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1234" uniqueCount="1227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="1229">
   <si>
     <t>trigger</t>
   </si>
@@ -3706,6 +3706,12 @@
   </si>
   <si>
     <t>movement</t>
+  </si>
+  <si>
+    <t>usg</t>
+  </si>
+  <si>
+    <t>ultrasound</t>
   </si>
 </sst>
 </file>
@@ -3761,10 +3767,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B617" totalsRowShown="0">
-  <autoFilter ref="A1:B617" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B617">
-    <sortCondition ref="A1:A617"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B618" totalsRowShown="0">
+  <autoFilter ref="A1:B618" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B618">
+    <sortCondition ref="A1:A618"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4037,7 +4043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B617"/>
+  <dimension ref="A1:B618"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -8854,129 +8860,137 @@
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>172</v>
+        <v>1227</v>
       </c>
       <c r="B602" t="s">
-        <v>635</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>693</v>
+        <v>172</v>
       </c>
       <c r="B603" t="s">
-        <v>746</v>
+        <v>635</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>252</v>
+        <v>693</v>
       </c>
       <c r="B604" t="s">
-        <v>636</v>
+        <v>746</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>694</v>
+        <v>252</v>
       </c>
       <c r="B605" t="s">
-        <v>747</v>
+        <v>636</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>189</v>
+        <v>694</v>
       </c>
       <c r="B606" t="s">
-        <v>637</v>
+        <v>747</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>989</v>
+        <v>189</v>
       </c>
       <c r="B607" t="s">
-        <v>990</v>
+        <v>637</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>311</v>
+        <v>989</v>
       </c>
       <c r="B608" t="s">
-        <v>638</v>
+        <v>990</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B609" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>1033</v>
+        <v>312</v>
       </c>
       <c r="B610" t="s">
-        <v>1115</v>
+        <v>639</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>1005</v>
+        <v>1033</v>
       </c>
       <c r="B611" t="s">
-        <v>1006</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>81</v>
+        <v>1005</v>
       </c>
       <c r="B612" t="s">
-        <v>640</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>651</v>
+        <v>81</v>
       </c>
       <c r="B613" t="s">
-        <v>748</v>
+        <v>640</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>922</v>
+        <v>651</v>
       </c>
       <c r="B614" t="s">
-        <v>923</v>
+        <v>748</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>642</v>
+        <v>922</v>
       </c>
       <c r="B615" t="s">
-        <v>749</v>
+        <v>923</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>969</v>
+        <v>642</v>
       </c>
       <c r="B616" t="s">
-        <v>970</v>
+        <v>749</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
+        <v>969</v>
+      </c>
+      <c r="B617" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A618" t="s">
         <v>1162</v>
       </c>
-      <c r="B617" t="s">
+      <c r="B618" t="s">
         <v>1163</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09CFFA8-486A-4F88-905E-153893DD928A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FBC6E8-59B4-4341-8A69-44E04D49BE38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="1229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="1231">
   <si>
     <t>trigger</t>
   </si>
@@ -3712,6 +3712,12 @@
   </si>
   <si>
     <t>ultrasound</t>
+  </si>
+  <si>
+    <t>bs</t>
+  </si>
+  <si>
+    <t>basal segments</t>
   </si>
 </sst>
 </file>
@@ -3767,10 +3773,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B618" totalsRowShown="0">
-  <autoFilter ref="A1:B618" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B618">
-    <sortCondition ref="A1:A618"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B619" totalsRowShown="0">
+  <autoFilter ref="A1:B619" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B619">
+    <sortCondition ref="A1:A619"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4043,7 +4049,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B618"/>
+  <dimension ref="A1:B619"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -4628,951 +4634,951 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>60</v>
+        <v>1229</v>
       </c>
       <c r="B73" t="s">
-        <v>374</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>1014</v>
+        <v>60</v>
       </c>
       <c r="B74" t="s">
-        <v>1015</v>
+        <v>374</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>668</v>
+        <v>1014</v>
       </c>
       <c r="B75" t="s">
-        <v>699</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B76" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B77" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B78" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B79" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B80" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B81" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>875</v>
+        <v>674</v>
       </c>
       <c r="B82" t="s">
-        <v>876</v>
+        <v>705</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>321</v>
+        <v>875</v>
       </c>
       <c r="B83" t="s">
-        <v>375</v>
+        <v>876</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>194</v>
+        <v>321</v>
       </c>
       <c r="B84" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="B85" t="s">
-        <v>22</v>
+        <v>376</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B86" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>196</v>
+        <v>19</v>
       </c>
       <c r="B87" t="s">
-        <v>377</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>287</v>
+        <v>196</v>
       </c>
       <c r="B88" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B89" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>337</v>
+        <v>286</v>
       </c>
       <c r="B90" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>899</v>
+        <v>337</v>
       </c>
       <c r="B91" t="s">
-        <v>900</v>
+        <v>380</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>305</v>
+        <v>899</v>
       </c>
       <c r="B92" t="s">
-        <v>381</v>
+        <v>900</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="B93" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>1159</v>
+        <v>323</v>
       </c>
       <c r="B94" t="s">
-        <v>1160</v>
+        <v>382</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>276</v>
+        <v>1159</v>
       </c>
       <c r="B95" t="s">
-        <v>383</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>333</v>
+        <v>276</v>
       </c>
       <c r="B96" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>42</v>
+        <v>333</v>
       </c>
       <c r="B97" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B98" t="s">
-        <v>1139</v>
+        <v>385</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>649</v>
+        <v>41</v>
       </c>
       <c r="B99" t="s">
-        <v>706</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>217</v>
+        <v>649</v>
       </c>
       <c r="B100" t="s">
-        <v>386</v>
+        <v>706</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>288</v>
+        <v>217</v>
       </c>
       <c r="B101" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>218</v>
+        <v>288</v>
       </c>
       <c r="B102" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>296</v>
+        <v>218</v>
       </c>
       <c r="B103" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>199</v>
+        <v>296</v>
       </c>
       <c r="B104" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>648</v>
+        <v>199</v>
       </c>
       <c r="B105" t="s">
-        <v>707</v>
+        <v>390</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>112</v>
+        <v>648</v>
       </c>
       <c r="B106" t="s">
-        <v>391</v>
+        <v>707</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="B107" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="B108" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>1176</v>
+        <v>115</v>
       </c>
       <c r="B109" t="s">
-        <v>1177</v>
+        <v>393</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>879</v>
+        <v>1176</v>
       </c>
       <c r="B110" t="s">
-        <v>880</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>807</v>
+        <v>879</v>
       </c>
       <c r="B111" t="s">
-        <v>808</v>
+        <v>880</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>152</v>
+        <v>807</v>
       </c>
       <c r="B112" t="s">
-        <v>394</v>
+        <v>808</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="B113" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B114" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="B115" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>967</v>
+        <v>155</v>
       </c>
       <c r="B116" t="s">
-        <v>968</v>
+        <v>397</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>84</v>
+        <v>967</v>
       </c>
       <c r="B117" t="s">
-        <v>398</v>
+        <v>968</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>965</v>
+        <v>84</v>
       </c>
       <c r="B118" t="s">
-        <v>966</v>
+        <v>398</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>103</v>
+        <v>965</v>
       </c>
       <c r="B119" t="s">
-        <v>399</v>
+        <v>966</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>198</v>
+        <v>103</v>
       </c>
       <c r="B120" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>314</v>
+        <v>198</v>
       </c>
       <c r="B121" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>104</v>
+        <v>314</v>
       </c>
       <c r="B122" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="B123" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="B124" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B125" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>1046</v>
+        <v>102</v>
       </c>
       <c r="B126" t="s">
-        <v>1047</v>
+        <v>405</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>930</v>
+        <v>1046</v>
       </c>
       <c r="B127" t="s">
-        <v>931</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B128" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>162</v>
+        <v>928</v>
       </c>
       <c r="B129" t="s">
-        <v>406</v>
+        <v>929</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>1153</v>
+        <v>162</v>
       </c>
       <c r="B130" t="s">
-        <v>1154</v>
+        <v>406</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>837</v>
+        <v>1153</v>
       </c>
       <c r="B131" t="s">
-        <v>838</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B132" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>1084</v>
+        <v>839</v>
       </c>
       <c r="B133" t="s">
-        <v>1085</v>
+        <v>840</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>665</v>
+        <v>1084</v>
       </c>
       <c r="B134" t="s">
-        <v>708</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>646</v>
+        <v>665</v>
       </c>
       <c r="B135" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>940</v>
+        <v>646</v>
       </c>
       <c r="B136" t="s">
-        <v>941</v>
+        <v>709</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>683</v>
+        <v>940</v>
       </c>
       <c r="B137" t="s">
-        <v>710</v>
+        <v>941</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B138" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B139" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="B140" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B141" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B142" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B143" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B144" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B145" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B146" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B147" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>175</v>
+        <v>682</v>
       </c>
       <c r="B148" t="s">
-        <v>407</v>
+        <v>720</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="B149" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B150" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>1209</v>
+        <v>213</v>
       </c>
       <c r="B151" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>149</v>
+        <v>1209</v>
       </c>
       <c r="B152" t="s">
-        <v>1212</v>
+        <v>410</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>247</v>
+        <v>149</v>
       </c>
       <c r="B153" t="s">
-        <v>411</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B154" t="s">
-        <v>1138</v>
+        <v>411</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>336</v>
+        <v>245</v>
       </c>
       <c r="B155" t="s">
-        <v>412</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>650</v>
+        <v>336</v>
       </c>
       <c r="B156" t="s">
-        <v>721</v>
+        <v>412</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>91</v>
+        <v>650</v>
       </c>
       <c r="B157" t="s">
-        <v>413</v>
+        <v>721</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>266</v>
+        <v>91</v>
       </c>
       <c r="B158" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>1096</v>
+        <v>266</v>
       </c>
       <c r="B159" t="s">
-        <v>1097</v>
+        <v>414</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>799</v>
+        <v>1096</v>
       </c>
       <c r="B160" t="s">
-        <v>800</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>1168</v>
+        <v>799</v>
       </c>
       <c r="B161" t="s">
-        <v>1169</v>
+        <v>800</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>295</v>
+        <v>1168</v>
       </c>
       <c r="B162" t="s">
-        <v>415</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>1086</v>
+        <v>295</v>
       </c>
       <c r="B163" t="s">
-        <v>1087</v>
+        <v>415</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="B164" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>151</v>
+        <v>1092</v>
       </c>
       <c r="B165" t="s">
-        <v>416</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>961</v>
+        <v>151</v>
       </c>
       <c r="B166" t="s">
-        <v>962</v>
+        <v>416</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>813</v>
+        <v>961</v>
       </c>
       <c r="B167" t="s">
-        <v>814</v>
+        <v>962</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>932</v>
+        <v>813</v>
       </c>
       <c r="B168" t="s">
-        <v>933</v>
+        <v>814</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>833</v>
+        <v>932</v>
       </c>
       <c r="B169" t="s">
-        <v>834</v>
+        <v>933</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>793</v>
+        <v>833</v>
       </c>
       <c r="B170" t="s">
-        <v>794</v>
+        <v>834</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>754</v>
+        <v>793</v>
       </c>
       <c r="B171" t="s">
-        <v>755</v>
+        <v>794</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>100</v>
+        <v>754</v>
       </c>
       <c r="B172" t="s">
-        <v>417</v>
+        <v>755</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>1042</v>
+        <v>100</v>
       </c>
       <c r="B173" t="s">
-        <v>1043</v>
+        <v>417</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>154</v>
+        <v>1042</v>
       </c>
       <c r="B174" t="s">
-        <v>418</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B175" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="B176" t="s">
-        <v>1137</v>
+        <v>419</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>1164</v>
+        <v>24</v>
       </c>
       <c r="B177" t="s">
-        <v>1165</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>1076</v>
+        <v>1164</v>
       </c>
       <c r="B178" t="s">
-        <v>1077</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>819</v>
+        <v>1076</v>
       </c>
       <c r="B179" t="s">
-        <v>820</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>130</v>
+        <v>819</v>
       </c>
       <c r="B180" t="s">
-        <v>420</v>
+        <v>820</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>322</v>
+        <v>130</v>
       </c>
       <c r="B181" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>867</v>
+        <v>322</v>
       </c>
       <c r="B182" t="s">
-        <v>868</v>
+        <v>421</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>183</v>
+        <v>867</v>
       </c>
       <c r="B183" t="s">
-        <v>422</v>
+        <v>868</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>1155</v>
+        <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>1156</v>
+        <v>422</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="B185" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>891</v>
+        <v>1157</v>
       </c>
       <c r="B186" t="s">
-        <v>892</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>32</v>
+        <v>891</v>
       </c>
       <c r="B187" t="s">
-        <v>423</v>
+        <v>892</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B188" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>764</v>
+        <v>35</v>
       </c>
       <c r="B189" t="s">
-        <v>1010</v>
+        <v>424</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>169</v>
+        <v>764</v>
       </c>
       <c r="B190" t="s">
-        <v>425</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B191" t="s">
         <v>425</v>
@@ -5580,1215 +5586,1215 @@
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>1011</v>
+        <v>170</v>
       </c>
       <c r="B192" t="s">
-        <v>765</v>
+        <v>425</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>178</v>
+        <v>1011</v>
       </c>
       <c r="B193" t="s">
-        <v>426</v>
+        <v>765</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="B194" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>238</v>
+        <v>111</v>
       </c>
       <c r="B195" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="B196" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B197" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="B198" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>667</v>
+        <v>179</v>
       </c>
       <c r="B199" t="s">
-        <v>722</v>
+        <v>431</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>97</v>
+        <v>667</v>
       </c>
       <c r="B200" t="s">
-        <v>432</v>
+        <v>722</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B201" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>242</v>
+        <v>110</v>
       </c>
       <c r="B202" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B203" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="B204" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B205" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>1110</v>
+        <v>182</v>
       </c>
       <c r="B206" t="s">
-        <v>1111</v>
+        <v>437</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>977</v>
+        <v>1110</v>
       </c>
       <c r="B207" t="s">
-        <v>978</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="B208" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>1198</v>
+        <v>979</v>
       </c>
       <c r="B209" t="s">
-        <v>1199</v>
+        <v>980</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="B210" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>253</v>
+        <v>1201</v>
       </c>
       <c r="B211" t="s">
-        <v>438</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="B212" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>787</v>
+        <v>34</v>
       </c>
       <c r="B213" t="s">
-        <v>788</v>
+        <v>439</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>180</v>
+        <v>787</v>
       </c>
       <c r="B214" t="s">
-        <v>440</v>
+        <v>788</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>275</v>
+        <v>180</v>
       </c>
       <c r="B215" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>857</v>
+        <v>275</v>
       </c>
       <c r="B216" t="s">
-        <v>858</v>
+        <v>441</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>116</v>
+        <v>857</v>
       </c>
       <c r="B217" t="s">
-        <v>442</v>
+        <v>858</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>208</v>
+        <v>116</v>
       </c>
       <c r="B218" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>1221</v>
+        <v>208</v>
       </c>
       <c r="B219" t="s">
-        <v>1222</v>
+        <v>443</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>1056</v>
+        <v>1221</v>
       </c>
       <c r="B220" t="s">
-        <v>1057</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>118</v>
+        <v>1056</v>
       </c>
       <c r="B221" t="s">
-        <v>444</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>641</v>
+        <v>118</v>
       </c>
       <c r="B222" t="s">
-        <v>723</v>
+        <v>444</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>815</v>
+        <v>641</v>
       </c>
       <c r="B223" t="s">
-        <v>816</v>
+        <v>723</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>298</v>
+        <v>815</v>
       </c>
       <c r="B224" t="s">
-        <v>445</v>
+        <v>816</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>643</v>
+        <v>298</v>
       </c>
       <c r="B225" t="s">
-        <v>724</v>
+        <v>445</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B226" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>1036</v>
+        <v>644</v>
       </c>
       <c r="B227" t="s">
-        <v>1037</v>
+        <v>725</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>90</v>
+        <v>1036</v>
       </c>
       <c r="B228" t="s">
-        <v>446</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B229" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B230" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>1072</v>
+        <v>89</v>
       </c>
       <c r="B231" t="s">
-        <v>1073</v>
+        <v>448</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>23</v>
+        <v>1072</v>
       </c>
       <c r="B232" t="s">
-        <v>1136</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B233" t="s">
-        <v>6</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>1141</v>
+        <v>5</v>
       </c>
       <c r="B234" t="s">
-        <v>1142</v>
+        <v>6</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>126</v>
+        <v>1141</v>
       </c>
       <c r="B235" t="s">
-        <v>449</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B236" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B237" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B238" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B239" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>277</v>
+        <v>119</v>
       </c>
       <c r="B240" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>1074</v>
+        <v>277</v>
       </c>
       <c r="B241" t="s">
-        <v>1075</v>
+        <v>454</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>9</v>
+        <v>1074</v>
       </c>
       <c r="B242" t="s">
-        <v>10</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="B243" t="s">
-        <v>455</v>
+        <v>10</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B244" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="B245" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="B246" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>77</v>
+        <v>262</v>
       </c>
       <c r="B247" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>938</v>
+        <v>77</v>
       </c>
       <c r="B248" t="s">
-        <v>939</v>
+        <v>459</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>1172</v>
+        <v>938</v>
       </c>
       <c r="B249" t="s">
-        <v>1173</v>
+        <v>939</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>168</v>
+        <v>1172</v>
       </c>
       <c r="B250" t="s">
-        <v>460</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B251" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>835</v>
+        <v>167</v>
       </c>
       <c r="B252" t="s">
-        <v>836</v>
+        <v>461</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>791</v>
+        <v>835</v>
       </c>
       <c r="B253" t="s">
-        <v>792</v>
+        <v>836</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>304</v>
+        <v>791</v>
       </c>
       <c r="B254" t="s">
-        <v>462</v>
+        <v>792</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>758</v>
+        <v>304</v>
       </c>
       <c r="B255" t="s">
-        <v>759</v>
+        <v>462</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>897</v>
+        <v>758</v>
       </c>
       <c r="B256" t="s">
-        <v>898</v>
+        <v>759</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>652</v>
+        <v>897</v>
       </c>
       <c r="B257" t="s">
-        <v>726</v>
+        <v>898</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>86</v>
+        <v>652</v>
       </c>
       <c r="B258" t="s">
-        <v>463</v>
+        <v>726</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B259" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="B260" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B261" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B262" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>251</v>
+        <v>158</v>
       </c>
       <c r="B263" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="B264" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>326</v>
+        <v>285</v>
       </c>
       <c r="B265" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B266" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>229</v>
+        <v>327</v>
       </c>
       <c r="B267" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>55</v>
+        <v>229</v>
       </c>
       <c r="B268" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>657</v>
+        <v>55</v>
       </c>
       <c r="B269" t="s">
-        <v>727</v>
+        <v>473</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>235</v>
+        <v>657</v>
       </c>
       <c r="B270" t="s">
-        <v>474</v>
+        <v>727</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="B271" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="B272" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>766</v>
+        <v>236</v>
       </c>
       <c r="B273" t="s">
-        <v>1009</v>
+        <v>476</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>1012</v>
+        <v>766</v>
       </c>
       <c r="B274" t="s">
-        <v>767</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>164</v>
+        <v>1012</v>
       </c>
       <c r="B275" t="s">
-        <v>477</v>
+        <v>767</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="B276" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B277" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>313</v>
+        <v>204</v>
       </c>
       <c r="B278" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>873</v>
+        <v>313</v>
       </c>
       <c r="B279" t="s">
-        <v>874</v>
+        <v>480</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>997</v>
+        <v>873</v>
       </c>
       <c r="B280" t="s">
-        <v>998</v>
+        <v>874</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>258</v>
+        <v>997</v>
       </c>
       <c r="B281" t="s">
-        <v>481</v>
+        <v>998</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>983</v>
+        <v>258</v>
       </c>
       <c r="B282" t="s">
-        <v>984</v>
+        <v>481</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>160</v>
+        <v>983</v>
       </c>
       <c r="B283" t="s">
-        <v>482</v>
+        <v>984</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>692</v>
+        <v>160</v>
       </c>
       <c r="B284" t="s">
-        <v>728</v>
+        <v>482</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>1166</v>
+        <v>692</v>
       </c>
       <c r="B285" t="s">
-        <v>1167</v>
+        <v>728</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>760</v>
+        <v>1166</v>
       </c>
       <c r="B286" t="s">
-        <v>761</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>895</v>
+        <v>760</v>
       </c>
       <c r="B287" t="s">
-        <v>896</v>
+        <v>761</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B288" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>184</v>
+        <v>893</v>
       </c>
       <c r="B289" t="s">
-        <v>483</v>
+        <v>894</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>244</v>
+        <v>184</v>
       </c>
       <c r="B290" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B291" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>686</v>
+        <v>243</v>
       </c>
       <c r="B292" t="s">
-        <v>729</v>
+        <v>485</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B293" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B294" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B295" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B296" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>1192</v>
+        <v>690</v>
       </c>
       <c r="B297" t="s">
-        <v>1193</v>
+        <v>733</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>280</v>
+        <v>1192</v>
       </c>
       <c r="B298" t="s">
-        <v>486</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B299" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>49</v>
+        <v>281</v>
       </c>
       <c r="B300" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B301" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="B302" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="B303" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>1190</v>
+        <v>72</v>
       </c>
       <c r="B304" t="s">
-        <v>1191</v>
+        <v>490</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>221</v>
+        <v>1190</v>
       </c>
       <c r="B305" t="s">
-        <v>492</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>1194</v>
+        <v>221</v>
       </c>
       <c r="B306" t="s">
-        <v>1195</v>
+        <v>492</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>15</v>
+        <v>1194</v>
       </c>
       <c r="B307" t="s">
-        <v>16</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>1060</v>
+        <v>15</v>
       </c>
       <c r="B308" t="s">
-        <v>1061</v>
+        <v>16</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>920</v>
+        <v>1060</v>
       </c>
       <c r="B309" t="s">
-        <v>921</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>108</v>
+        <v>920</v>
       </c>
       <c r="B310" t="s">
-        <v>493</v>
+        <v>921</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>241</v>
+        <v>108</v>
       </c>
       <c r="B311" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>328</v>
+        <v>241</v>
       </c>
       <c r="B312" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>1100</v>
+        <v>328</v>
       </c>
       <c r="B313" t="s">
-        <v>1101</v>
+        <v>495</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>1052</v>
+        <v>1100</v>
       </c>
       <c r="B314" t="s">
-        <v>1053</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>121</v>
+        <v>1052</v>
       </c>
       <c r="B315" t="s">
-        <v>496</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>750</v>
+        <v>121</v>
       </c>
       <c r="B316" t="s">
-        <v>751</v>
+        <v>496</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>781</v>
+        <v>750</v>
       </c>
       <c r="B317" t="s">
-        <v>782</v>
+        <v>751</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>134</v>
+        <v>781</v>
       </c>
       <c r="B318" t="s">
-        <v>497</v>
+        <v>782</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="B319" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>224</v>
+        <v>63</v>
       </c>
       <c r="B320" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>25</v>
+        <v>224</v>
       </c>
       <c r="B321" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B322" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>207</v>
+        <v>26</v>
       </c>
       <c r="B323" t="s">
-        <v>1133</v>
+        <v>501</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>960</v>
+        <v>207</v>
       </c>
       <c r="B324" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>1113</v>
+        <v>960</v>
       </c>
       <c r="B325" t="s">
-        <v>1114</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>206</v>
+        <v>1113</v>
       </c>
       <c r="B326" t="s">
-        <v>1135</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B327" t="s">
-        <v>502</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B328" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="B329" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>663</v>
+        <v>145</v>
       </c>
       <c r="B330" t="s">
-        <v>734</v>
+        <v>504</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>171</v>
+        <v>663</v>
       </c>
       <c r="B331" t="s">
-        <v>505</v>
+        <v>734</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>1088</v>
+        <v>171</v>
       </c>
       <c r="B332" t="s">
-        <v>1089</v>
+        <v>505</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>263</v>
+        <v>1088</v>
       </c>
       <c r="B333" t="s">
-        <v>506</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>1090</v>
+        <v>263</v>
       </c>
       <c r="B334" t="s">
-        <v>1091</v>
+        <v>506</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>80</v>
+        <v>1090</v>
       </c>
       <c r="B335" t="s">
-        <v>507</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B336" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>191</v>
+        <v>65</v>
       </c>
       <c r="B337" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="B338" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>192</v>
+        <v>123</v>
       </c>
       <c r="B339" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="B340" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B341" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>1200</v>
+        <v>233</v>
       </c>
       <c r="B342" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>31</v>
+        <v>1200</v>
       </c>
       <c r="B343" t="s">
         <v>514</v>
@@ -6796,311 +6802,311 @@
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B344" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B345" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B346" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>306</v>
+        <v>71</v>
       </c>
       <c r="B347" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>222</v>
+        <v>306</v>
       </c>
       <c r="B348" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>315</v>
+        <v>222</v>
       </c>
       <c r="B349" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>278</v>
+        <v>315</v>
       </c>
       <c r="B350" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B351" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>831</v>
+        <v>279</v>
       </c>
       <c r="B352" t="s">
-        <v>832</v>
+        <v>522</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>48</v>
+        <v>831</v>
       </c>
       <c r="B353" t="s">
-        <v>523</v>
+        <v>832</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="B354" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="B355" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>223</v>
+        <v>52</v>
       </c>
       <c r="B356" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>1094</v>
+        <v>223</v>
       </c>
       <c r="B357" t="s">
-        <v>1095</v>
+        <v>526</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>1109</v>
+        <v>1094</v>
       </c>
       <c r="B358" t="s">
-        <v>1112</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>1050</v>
+        <v>1109</v>
       </c>
       <c r="B359" t="s">
-        <v>1051</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>96</v>
+        <v>1050</v>
       </c>
       <c r="B360" t="s">
-        <v>527</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>248</v>
+        <v>96</v>
       </c>
       <c r="B361" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B362" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>94</v>
+        <v>249</v>
       </c>
       <c r="B363" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>1064</v>
+        <v>94</v>
       </c>
       <c r="B364" t="s">
-        <v>1065</v>
+        <v>530</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>212</v>
+        <v>1064</v>
       </c>
       <c r="B365" t="s">
-        <v>531</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>1225</v>
+        <v>212</v>
       </c>
       <c r="B366" t="s">
-        <v>1226</v>
+        <v>531</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>916</v>
+        <v>1225</v>
       </c>
       <c r="B367" t="s">
-        <v>917</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B368" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="B369" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>330</v>
+        <v>918</v>
       </c>
       <c r="B370" t="s">
-        <v>532</v>
+        <v>919</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>1066</v>
+        <v>330</v>
       </c>
       <c r="B371" t="s">
-        <v>1067</v>
+        <v>532</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>995</v>
+        <v>1066</v>
       </c>
       <c r="B372" t="s">
-        <v>996</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="B373" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B374" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>82</v>
+        <v>993</v>
       </c>
       <c r="B375" t="s">
-        <v>533</v>
+        <v>994</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>772</v>
+        <v>82</v>
       </c>
       <c r="B376" t="s">
-        <v>773</v>
+        <v>533</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>197</v>
+        <v>772</v>
       </c>
       <c r="B377" t="s">
-        <v>534</v>
+        <v>773</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>654</v>
+        <v>197</v>
       </c>
       <c r="B378" t="s">
-        <v>735</v>
+        <v>534</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>821</v>
+        <v>654</v>
       </c>
       <c r="B379" t="s">
-        <v>822</v>
+        <v>735</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>1068</v>
+        <v>821</v>
       </c>
       <c r="B380" t="s">
-        <v>1069</v>
+        <v>822</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>3</v>
+        <v>1068</v>
       </c>
       <c r="B381" t="s">
-        <v>4</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>958</v>
+        <v>3</v>
       </c>
       <c r="B382" t="s">
         <v>4</v>
@@ -7108,7 +7114,7 @@
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B383" t="s">
         <v>4</v>
@@ -7116,1881 +7122,1889 @@
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>664</v>
+        <v>959</v>
       </c>
       <c r="B384" t="s">
-        <v>736</v>
+        <v>4</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>770</v>
+        <v>664</v>
       </c>
       <c r="B385" t="s">
-        <v>771</v>
+        <v>736</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>85</v>
+        <v>770</v>
       </c>
       <c r="B386" t="s">
-        <v>535</v>
+        <v>771</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>1062</v>
+        <v>85</v>
       </c>
       <c r="B387" t="s">
-        <v>1063</v>
+        <v>535</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>829</v>
+        <v>1062</v>
       </c>
       <c r="B388" t="s">
-        <v>830</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>809</v>
+        <v>829</v>
       </c>
       <c r="B389" t="s">
-        <v>810</v>
+        <v>830</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>187</v>
+        <v>809</v>
       </c>
       <c r="B390" t="s">
-        <v>536</v>
+        <v>810</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>827</v>
+        <v>187</v>
       </c>
       <c r="B391" t="s">
-        <v>828</v>
+        <v>536</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>934</v>
+        <v>827</v>
       </c>
       <c r="B392" t="s">
-        <v>1130</v>
+        <v>828</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>863</v>
+        <v>934</v>
       </c>
       <c r="B393" t="s">
-        <v>864</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>1044</v>
+        <v>863</v>
       </c>
       <c r="B394" t="s">
-        <v>1045</v>
+        <v>864</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>798</v>
+        <v>1044</v>
       </c>
       <c r="B395" t="s">
-        <v>1131</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B396" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>13</v>
+        <v>797</v>
       </c>
       <c r="B397" t="s">
-        <v>14</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>817</v>
+        <v>13</v>
       </c>
       <c r="B398" t="s">
-        <v>818</v>
+        <v>14</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>186</v>
+        <v>817</v>
       </c>
       <c r="B399" t="s">
-        <v>537</v>
+        <v>818</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>811</v>
+        <v>186</v>
       </c>
       <c r="B400" t="s">
-        <v>812</v>
+        <v>537</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>320</v>
+        <v>811</v>
       </c>
       <c r="B401" t="s">
-        <v>538</v>
+        <v>812</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>656</v>
+        <v>320</v>
       </c>
       <c r="B402" t="s">
-        <v>737</v>
+        <v>538</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>855</v>
+        <v>656</v>
       </c>
       <c r="B403" t="s">
-        <v>856</v>
+        <v>737</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>658</v>
+        <v>855</v>
       </c>
       <c r="B404" t="s">
-        <v>738</v>
+        <v>856</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="B405" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>1207</v>
+        <v>653</v>
       </c>
       <c r="B406" t="s">
-        <v>1208</v>
+        <v>739</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>256</v>
+        <v>1207</v>
       </c>
       <c r="B407" t="s">
-        <v>539</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B408" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B409" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>188</v>
+        <v>261</v>
       </c>
       <c r="B410" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B411" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>936</v>
+        <v>190</v>
       </c>
       <c r="B412" t="s">
-        <v>937</v>
+        <v>543</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>1031</v>
+        <v>936</v>
       </c>
       <c r="B413" t="s">
-        <v>1032</v>
+        <v>937</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>1223</v>
+        <v>1031</v>
       </c>
       <c r="B414" t="s">
-        <v>1224</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>209</v>
+        <v>1223</v>
       </c>
       <c r="B415" t="s">
-        <v>544</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>851</v>
+        <v>209</v>
       </c>
       <c r="B416" t="s">
-        <v>852</v>
+        <v>544</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>143</v>
+        <v>851</v>
       </c>
       <c r="B417" t="s">
-        <v>545</v>
+        <v>852</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B418" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>1203</v>
+        <v>140</v>
       </c>
       <c r="B419" t="s">
-        <v>1204</v>
+        <v>546</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>254</v>
+        <v>1203</v>
       </c>
       <c r="B420" t="s">
-        <v>547</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>331</v>
+        <v>254</v>
       </c>
       <c r="B421" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>210</v>
+        <v>331</v>
       </c>
       <c r="B422" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="B423" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>73</v>
+        <v>234</v>
       </c>
       <c r="B424" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>342</v>
+        <v>73</v>
       </c>
       <c r="B425" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="B426" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>843</v>
+        <v>308</v>
       </c>
       <c r="B427" t="s">
-        <v>844</v>
+        <v>553</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B428" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>220</v>
+        <v>845</v>
       </c>
       <c r="B429" t="s">
-        <v>554</v>
+        <v>846</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>909</v>
+        <v>220</v>
       </c>
       <c r="B430" t="s">
-        <v>910</v>
+        <v>554</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>963</v>
+        <v>909</v>
       </c>
       <c r="B431" t="s">
-        <v>964</v>
+        <v>910</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>1188</v>
+        <v>963</v>
       </c>
       <c r="B432" t="s">
-        <v>1189</v>
+        <v>964</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>227</v>
+        <v>1188</v>
       </c>
       <c r="B433" t="s">
-        <v>555</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>334</v>
+        <v>227</v>
       </c>
       <c r="B434" t="s">
-        <v>1161</v>
+        <v>555</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>971</v>
+        <v>334</v>
       </c>
       <c r="B435" t="s">
-        <v>972</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>778</v>
+        <v>971</v>
       </c>
       <c r="B436" t="s">
-        <v>779</v>
+        <v>972</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>294</v>
+        <v>778</v>
       </c>
       <c r="B437" t="s">
-        <v>556</v>
+        <v>779</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>952</v>
+        <v>294</v>
       </c>
       <c r="B438" t="s">
-        <v>953</v>
+        <v>556</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>339</v>
+        <v>952</v>
       </c>
       <c r="B439" t="s">
-        <v>557</v>
+        <v>953</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>780</v>
+        <v>339</v>
       </c>
       <c r="B440" t="s">
-        <v>779</v>
+        <v>557</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>340</v>
+        <v>780</v>
       </c>
       <c r="B441" t="s">
-        <v>558</v>
+        <v>779</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B442" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>645</v>
+        <v>341</v>
       </c>
       <c r="B443" t="s">
-        <v>740</v>
+        <v>559</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>39</v>
+        <v>645</v>
       </c>
       <c r="B444" t="s">
-        <v>560</v>
+        <v>740</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B445" t="s">
-        <v>1129</v>
+        <v>560</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>343</v>
+        <v>38</v>
       </c>
       <c r="B446" t="s">
-        <v>561</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>107</v>
+        <v>343</v>
       </c>
       <c r="B447" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>1029</v>
+        <v>107</v>
       </c>
       <c r="B448" t="s">
-        <v>1030</v>
+        <v>562</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>903</v>
+        <v>1029</v>
       </c>
       <c r="B449" t="s">
-        <v>904</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>117</v>
+        <v>903</v>
       </c>
       <c r="B450" t="s">
-        <v>563</v>
+        <v>904</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>1025</v>
+        <v>117</v>
       </c>
       <c r="B451" t="s">
-        <v>1026</v>
+        <v>563</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>98</v>
+        <v>1025</v>
       </c>
       <c r="B452" t="s">
-        <v>564</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B453" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>666</v>
+        <v>99</v>
       </c>
       <c r="B454" t="s">
-        <v>741</v>
+        <v>565</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>1107</v>
+        <v>666</v>
       </c>
       <c r="B455" t="s">
-        <v>1024</v>
+        <v>741</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>823</v>
+        <v>1107</v>
       </c>
       <c r="B456" t="s">
-        <v>824</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>113</v>
+        <v>823</v>
       </c>
       <c r="B457" t="s">
-        <v>566</v>
+        <v>824</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>889</v>
+        <v>113</v>
       </c>
       <c r="B458" t="s">
-        <v>890</v>
+        <v>566</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>45</v>
+        <v>889</v>
       </c>
       <c r="B459" t="s">
-        <v>1128</v>
+        <v>890</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>290</v>
+        <v>45</v>
       </c>
       <c r="B460" t="s">
-        <v>567</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B461" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>47</v>
+        <v>299</v>
       </c>
       <c r="B462" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>847</v>
+        <v>47</v>
       </c>
       <c r="B463" t="s">
-        <v>848</v>
+        <v>569</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>51</v>
+        <v>847</v>
       </c>
       <c r="B464" t="s">
-        <v>570</v>
+        <v>848</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>871</v>
+        <v>51</v>
       </c>
       <c r="B465" t="s">
-        <v>872</v>
+        <v>570</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>114</v>
+        <v>871</v>
       </c>
       <c r="B466" t="s">
-        <v>571</v>
+        <v>872</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>853</v>
+        <v>114</v>
       </c>
       <c r="B467" t="s">
-        <v>854</v>
+        <v>571</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>144</v>
+        <v>853</v>
       </c>
       <c r="B468" t="s">
-        <v>572</v>
+        <v>854</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>1080</v>
+        <v>144</v>
       </c>
       <c r="B469" t="s">
-        <v>1081</v>
+        <v>572</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>176</v>
+        <v>1080</v>
       </c>
       <c r="B470" t="s">
-        <v>573</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>316</v>
+        <v>176</v>
       </c>
       <c r="B471" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>29</v>
+        <v>316</v>
       </c>
       <c r="B472" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>1104</v>
+        <v>29</v>
       </c>
       <c r="B473" t="s">
-        <v>1105</v>
+        <v>575</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>1018</v>
+        <v>1104</v>
       </c>
       <c r="B474" t="s">
-        <v>1019</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>293</v>
+        <v>1018</v>
       </c>
       <c r="B475" t="s">
-        <v>576</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>981</v>
+        <v>293</v>
       </c>
       <c r="B476" t="s">
-        <v>982</v>
+        <v>576</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>301</v>
+        <v>981</v>
       </c>
       <c r="B477" t="s">
-        <v>577</v>
+        <v>982</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>1003</v>
+        <v>301</v>
       </c>
       <c r="B478" t="s">
-        <v>1004</v>
+        <v>577</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="B479" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>75</v>
+        <v>1007</v>
       </c>
       <c r="B480" t="s">
-        <v>578</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B481" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B482" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>329</v>
+        <v>78</v>
       </c>
       <c r="B483" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>752</v>
+        <v>329</v>
       </c>
       <c r="B484" t="s">
-        <v>753</v>
+        <v>581</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>805</v>
+        <v>752</v>
       </c>
       <c r="B485" t="s">
-        <v>806</v>
+        <v>753</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>135</v>
+        <v>805</v>
       </c>
       <c r="B486" t="s">
-        <v>582</v>
+        <v>806</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>1186</v>
+        <v>135</v>
       </c>
       <c r="B487" t="s">
-        <v>1187</v>
+        <v>582</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>1038</v>
+        <v>1186</v>
       </c>
       <c r="B488" t="s">
-        <v>1039</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>215</v>
+        <v>1038</v>
       </c>
       <c r="B489" t="s">
-        <v>583</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>935</v>
+        <v>215</v>
       </c>
       <c r="B490" t="s">
-        <v>1145</v>
+        <v>583</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>216</v>
+        <v>935</v>
       </c>
       <c r="B491" t="s">
-        <v>1126</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>317</v>
+        <v>216</v>
       </c>
       <c r="B492" t="s">
-        <v>584</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>1082</v>
+        <v>317</v>
       </c>
       <c r="B493" t="s">
-        <v>1083</v>
+        <v>584</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>214</v>
+        <v>1082</v>
       </c>
       <c r="B494" t="s">
-        <v>1127</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>999</v>
+        <v>214</v>
       </c>
       <c r="B495" t="s">
-        <v>1000</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B496" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>225</v>
+        <v>1001</v>
       </c>
       <c r="B497" t="s">
-        <v>585</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>948</v>
+        <v>225</v>
       </c>
       <c r="B498" t="s">
-        <v>949</v>
+        <v>585</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>1098</v>
+        <v>948</v>
       </c>
       <c r="B499" t="s">
-        <v>1099</v>
+        <v>949</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>1048</v>
+        <v>1098</v>
       </c>
       <c r="B500" t="s">
-        <v>1049</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>93</v>
+        <v>1048</v>
       </c>
       <c r="B501" t="s">
-        <v>586</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="B502" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>783</v>
+        <v>120</v>
       </c>
       <c r="B503" t="s">
-        <v>784</v>
+        <v>587</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>133</v>
+        <v>783</v>
       </c>
       <c r="B504" t="s">
-        <v>588</v>
+        <v>784</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="B505" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B506" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>825</v>
+        <v>66</v>
       </c>
       <c r="B507" t="s">
-        <v>826</v>
+        <v>590</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>950</v>
+        <v>825</v>
       </c>
       <c r="B508" t="s">
-        <v>951</v>
+        <v>826</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>1215</v>
+        <v>950</v>
       </c>
       <c r="B509" t="s">
-        <v>1216</v>
+        <v>951</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>79</v>
+        <v>1215</v>
       </c>
       <c r="B510" t="s">
-        <v>591</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="B511" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="B512" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>1184</v>
+        <v>122</v>
       </c>
       <c r="B513" t="s">
-        <v>1185</v>
+        <v>593</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>181</v>
+        <v>1184</v>
       </c>
       <c r="B514" t="s">
-        <v>594</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>801</v>
+        <v>181</v>
       </c>
       <c r="B515" t="s">
-        <v>802</v>
+        <v>594</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>691</v>
+        <v>801</v>
       </c>
       <c r="B516" t="s">
-        <v>742</v>
+        <v>802</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>1151</v>
+        <v>691</v>
       </c>
       <c r="B517" t="s">
-        <v>1152</v>
+        <v>742</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="B518" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>284</v>
+        <v>1149</v>
       </c>
       <c r="B519" t="s">
-        <v>595</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>973</v>
+        <v>284</v>
       </c>
       <c r="B520" t="s">
-        <v>974</v>
+        <v>595</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>1219</v>
+        <v>973</v>
       </c>
       <c r="B521" t="s">
-        <v>1220</v>
+        <v>974</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>841</v>
+        <v>1219</v>
       </c>
       <c r="B522" t="s">
-        <v>842</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>283</v>
+        <v>841</v>
       </c>
       <c r="B523" t="s">
-        <v>596</v>
+        <v>842</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>883</v>
+        <v>283</v>
       </c>
       <c r="B524" t="s">
-        <v>884</v>
+        <v>596</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>1180</v>
+        <v>883</v>
       </c>
       <c r="B525" t="s">
-        <v>1181</v>
+        <v>884</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>756</v>
+        <v>1180</v>
       </c>
       <c r="B526" t="s">
-        <v>757</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>1078</v>
+        <v>756</v>
       </c>
       <c r="B527" t="s">
-        <v>1079</v>
+        <v>757</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>67</v>
+        <v>1078</v>
       </c>
       <c r="B528" t="s">
-        <v>597</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B529" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="B530" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>289</v>
+        <v>95</v>
       </c>
       <c r="B531" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B532" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="B533" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>193</v>
+        <v>264</v>
       </c>
       <c r="B534" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>901</v>
+        <v>193</v>
       </c>
       <c r="B535" t="s">
-        <v>902</v>
+        <v>603</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>44</v>
+        <v>901</v>
       </c>
       <c r="B536" t="s">
-        <v>1125</v>
+        <v>902</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>1070</v>
+        <v>44</v>
       </c>
       <c r="B537" t="s">
-        <v>1071</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>324</v>
+        <v>1070</v>
       </c>
       <c r="B538" t="s">
-        <v>604</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B539" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>849</v>
+        <v>325</v>
       </c>
       <c r="B540" t="s">
-        <v>850</v>
+        <v>605</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>887</v>
+        <v>849</v>
       </c>
       <c r="B541" t="s">
-        <v>888</v>
+        <v>850</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>869</v>
+        <v>887</v>
       </c>
       <c r="B542" t="s">
-        <v>870</v>
+        <v>888</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>33</v>
+        <v>869</v>
       </c>
       <c r="B543" t="s">
-        <v>606</v>
+        <v>870</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B544" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>1143</v>
+        <v>36</v>
       </c>
       <c r="B545" t="s">
-        <v>1144</v>
+        <v>607</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>309</v>
+        <v>1143</v>
       </c>
       <c r="B546" t="s">
-        <v>608</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>257</v>
+        <v>309</v>
       </c>
       <c r="B547" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>302</v>
+        <v>257</v>
       </c>
       <c r="B548" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>228</v>
+        <v>302</v>
       </c>
       <c r="B549" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c r="B550" t="s">
-        <v>18</v>
+        <v>611</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>655</v>
+        <v>17</v>
       </c>
       <c r="B551" t="s">
-        <v>743</v>
+        <v>18</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>785</v>
+        <v>655</v>
       </c>
       <c r="B552" t="s">
-        <v>786</v>
+        <v>743</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>142</v>
+        <v>785</v>
       </c>
       <c r="B553" t="s">
-        <v>612</v>
+        <v>786</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>1178</v>
+        <v>142</v>
       </c>
       <c r="B554" t="s">
-        <v>1179</v>
+        <v>612</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>956</v>
+        <v>1178</v>
       </c>
       <c r="B555" t="s">
-        <v>957</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>54</v>
+        <v>956</v>
       </c>
       <c r="B556" t="s">
-        <v>613</v>
+        <v>957</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>265</v>
+        <v>54</v>
       </c>
       <c r="B557" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>976</v>
+        <v>265</v>
       </c>
       <c r="B558" t="s">
-        <v>975</v>
+        <v>614</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>56</v>
+        <v>976</v>
       </c>
       <c r="B559" t="s">
-        <v>615</v>
+        <v>975</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>1217</v>
+        <v>56</v>
       </c>
       <c r="B560" t="s">
-        <v>1218</v>
+        <v>615</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>185</v>
+        <v>1217</v>
       </c>
       <c r="B561" t="s">
-        <v>616</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="B562" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="B563" t="s">
-        <v>1146</v>
+        <v>617</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B564" t="s">
-        <v>1124</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>1170</v>
+        <v>40</v>
       </c>
       <c r="B565" t="s">
-        <v>1171</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>165</v>
+        <v>1170</v>
       </c>
       <c r="B566" t="s">
-        <v>618</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="B567" t="s">
-        <v>11</v>
+        <v>618</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>250</v>
+        <v>12</v>
       </c>
       <c r="B568" t="s">
-        <v>619</v>
+        <v>11</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>27</v>
+        <v>250</v>
       </c>
       <c r="B569" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>1040</v>
+        <v>27</v>
       </c>
       <c r="B570" t="s">
-        <v>1041</v>
+        <v>620</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>28</v>
+        <v>1040</v>
       </c>
       <c r="B571" t="s">
-        <v>621</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>1205</v>
+        <v>28</v>
       </c>
       <c r="B572" t="s">
-        <v>1206</v>
+        <v>621</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>255</v>
+        <v>1205</v>
       </c>
       <c r="B573" t="s">
-        <v>622</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>795</v>
+        <v>255</v>
       </c>
       <c r="B574" t="s">
-        <v>796</v>
+        <v>622</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>267</v>
+        <v>795</v>
       </c>
       <c r="B575" t="s">
-        <v>623</v>
+        <v>796</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>661</v>
+        <v>267</v>
       </c>
       <c r="B576" t="s">
-        <v>744</v>
+        <v>623</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B577" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>139</v>
+        <v>662</v>
       </c>
       <c r="B578" t="s">
-        <v>624</v>
+        <v>745</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="B579" t="s">
-        <v>2</v>
+        <v>624</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="B580" t="s">
-        <v>625</v>
+        <v>2</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>1034</v>
+        <v>105</v>
       </c>
       <c r="B581" t="s">
-        <v>1123</v>
+        <v>625</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>865</v>
+        <v>1034</v>
       </c>
       <c r="B582" t="s">
-        <v>866</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>1035</v>
+        <v>865</v>
       </c>
       <c r="B583" t="s">
-        <v>1122</v>
+        <v>866</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>292</v>
+        <v>1035</v>
       </c>
       <c r="B584" t="s">
-        <v>626</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>8</v>
+        <v>292</v>
       </c>
       <c r="B585" t="s">
-        <v>11</v>
+        <v>626</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>335</v>
+        <v>8</v>
       </c>
       <c r="B586" t="s">
-        <v>627</v>
+        <v>11</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B587" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>259</v>
+        <v>332</v>
       </c>
       <c r="B588" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>319</v>
+        <v>259</v>
       </c>
       <c r="B589" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>859</v>
+        <v>319</v>
       </c>
       <c r="B590" t="s">
-        <v>860</v>
+        <v>630</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>1174</v>
+        <v>859</v>
       </c>
       <c r="B591" t="s">
-        <v>1175</v>
+        <v>860</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>268</v>
+        <v>1174</v>
       </c>
       <c r="B592" t="s">
-        <v>631</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B593" t="s">
-        <v>1117</v>
+        <v>631</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B594" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B595" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B596" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B597" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B598" t="s">
-        <v>1116</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>92</v>
+        <v>272</v>
       </c>
       <c r="B599" t="s">
-        <v>632</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>200</v>
+        <v>92</v>
       </c>
       <c r="B600" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B601" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>1227</v>
+        <v>203</v>
       </c>
       <c r="B602" t="s">
-        <v>1228</v>
+        <v>634</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>172</v>
+        <v>1227</v>
       </c>
       <c r="B603" t="s">
-        <v>635</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>693</v>
+        <v>172</v>
       </c>
       <c r="B604" t="s">
-        <v>746</v>
+        <v>635</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>252</v>
+        <v>693</v>
       </c>
       <c r="B605" t="s">
-        <v>636</v>
+        <v>746</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>694</v>
+        <v>252</v>
       </c>
       <c r="B606" t="s">
-        <v>747</v>
+        <v>636</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>189</v>
+        <v>694</v>
       </c>
       <c r="B607" t="s">
-        <v>637</v>
+        <v>747</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>989</v>
+        <v>189</v>
       </c>
       <c r="B608" t="s">
-        <v>990</v>
+        <v>637</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>311</v>
+        <v>989</v>
       </c>
       <c r="B609" t="s">
-        <v>638</v>
+        <v>990</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B610" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>1033</v>
+        <v>312</v>
       </c>
       <c r="B611" t="s">
-        <v>1115</v>
+        <v>639</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>1005</v>
+        <v>1033</v>
       </c>
       <c r="B612" t="s">
-        <v>1006</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>81</v>
+        <v>1005</v>
       </c>
       <c r="B613" t="s">
-        <v>640</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>651</v>
+        <v>81</v>
       </c>
       <c r="B614" t="s">
-        <v>748</v>
+        <v>640</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>922</v>
+        <v>651</v>
       </c>
       <c r="B615" t="s">
-        <v>923</v>
+        <v>748</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>642</v>
+        <v>922</v>
       </c>
       <c r="B616" t="s">
-        <v>749</v>
+        <v>923</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>969</v>
+        <v>642</v>
       </c>
       <c r="B617" t="s">
-        <v>970</v>
+        <v>749</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
+        <v>969</v>
+      </c>
+      <c r="B618" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A619" t="s">
         <v>1162</v>
       </c>
-      <c r="B618" t="s">
+      <c r="B619" t="s">
         <v>1163</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FBC6E8-59B4-4341-8A69-44E04D49BE38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6375AF06-C340-4F6D-AE3E-EDA2D368ECB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="1231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="1233">
   <si>
     <t>trigger</t>
   </si>
@@ -3718,6 +3718,12 @@
   </si>
   <si>
     <t>basal segments</t>
+  </si>
+  <si>
+    <t>pt</t>
+  </si>
+  <si>
+    <t>patient</t>
   </si>
 </sst>
 </file>
@@ -3773,10 +3779,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B619" totalsRowShown="0">
-  <autoFilter ref="A1:B619" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B619">
-    <sortCondition ref="A1:A619"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B620" totalsRowShown="0">
+  <autoFilter ref="A1:B620" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B620">
+    <sortCondition ref="A1:A620"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4049,7 +4055,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B619"/>
+  <dimension ref="A1:B620"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -7858,1153 +7864,1161 @@
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>293</v>
+        <v>1231</v>
       </c>
       <c r="B476" t="s">
-        <v>576</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>981</v>
+        <v>293</v>
       </c>
       <c r="B477" t="s">
-        <v>982</v>
+        <v>576</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>301</v>
+        <v>981</v>
       </c>
       <c r="B478" t="s">
-        <v>577</v>
+        <v>982</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>1003</v>
+        <v>301</v>
       </c>
       <c r="B479" t="s">
-        <v>1004</v>
+        <v>577</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="B480" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>75</v>
+        <v>1007</v>
       </c>
       <c r="B481" t="s">
-        <v>578</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B482" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B483" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>329</v>
+        <v>78</v>
       </c>
       <c r="B484" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>752</v>
+        <v>329</v>
       </c>
       <c r="B485" t="s">
-        <v>753</v>
+        <v>581</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>805</v>
+        <v>752</v>
       </c>
       <c r="B486" t="s">
-        <v>806</v>
+        <v>753</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>135</v>
+        <v>805</v>
       </c>
       <c r="B487" t="s">
-        <v>582</v>
+        <v>806</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>1186</v>
+        <v>135</v>
       </c>
       <c r="B488" t="s">
-        <v>1187</v>
+        <v>582</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>1038</v>
+        <v>1186</v>
       </c>
       <c r="B489" t="s">
-        <v>1039</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>215</v>
+        <v>1038</v>
       </c>
       <c r="B490" t="s">
-        <v>583</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>935</v>
+        <v>215</v>
       </c>
       <c r="B491" t="s">
-        <v>1145</v>
+        <v>583</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>216</v>
+        <v>935</v>
       </c>
       <c r="B492" t="s">
-        <v>1126</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>317</v>
+        <v>216</v>
       </c>
       <c r="B493" t="s">
-        <v>584</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>1082</v>
+        <v>317</v>
       </c>
       <c r="B494" t="s">
-        <v>1083</v>
+        <v>584</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>214</v>
+        <v>1082</v>
       </c>
       <c r="B495" t="s">
-        <v>1127</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>999</v>
+        <v>214</v>
       </c>
       <c r="B496" t="s">
-        <v>1000</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B497" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>225</v>
+        <v>1001</v>
       </c>
       <c r="B498" t="s">
-        <v>585</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>948</v>
+        <v>225</v>
       </c>
       <c r="B499" t="s">
-        <v>949</v>
+        <v>585</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>1098</v>
+        <v>948</v>
       </c>
       <c r="B500" t="s">
-        <v>1099</v>
+        <v>949</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>1048</v>
+        <v>1098</v>
       </c>
       <c r="B501" t="s">
-        <v>1049</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>93</v>
+        <v>1048</v>
       </c>
       <c r="B502" t="s">
-        <v>586</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="B503" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>783</v>
+        <v>120</v>
       </c>
       <c r="B504" t="s">
-        <v>784</v>
+        <v>587</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>133</v>
+        <v>783</v>
       </c>
       <c r="B505" t="s">
-        <v>588</v>
+        <v>784</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="B506" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B507" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>825</v>
+        <v>66</v>
       </c>
       <c r="B508" t="s">
-        <v>826</v>
+        <v>590</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>950</v>
+        <v>825</v>
       </c>
       <c r="B509" t="s">
-        <v>951</v>
+        <v>826</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>1215</v>
+        <v>950</v>
       </c>
       <c r="B510" t="s">
-        <v>1216</v>
+        <v>951</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>79</v>
+        <v>1215</v>
       </c>
       <c r="B511" t="s">
-        <v>591</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="B512" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="B513" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>1184</v>
+        <v>122</v>
       </c>
       <c r="B514" t="s">
-        <v>1185</v>
+        <v>593</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>181</v>
+        <v>1184</v>
       </c>
       <c r="B515" t="s">
-        <v>594</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>801</v>
+        <v>181</v>
       </c>
       <c r="B516" t="s">
-        <v>802</v>
+        <v>594</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>691</v>
+        <v>801</v>
       </c>
       <c r="B517" t="s">
-        <v>742</v>
+        <v>802</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>1151</v>
+        <v>691</v>
       </c>
       <c r="B518" t="s">
-        <v>1152</v>
+        <v>742</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="B519" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>284</v>
+        <v>1149</v>
       </c>
       <c r="B520" t="s">
-        <v>595</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>973</v>
+        <v>284</v>
       </c>
       <c r="B521" t="s">
-        <v>974</v>
+        <v>595</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>1219</v>
+        <v>973</v>
       </c>
       <c r="B522" t="s">
-        <v>1220</v>
+        <v>974</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>841</v>
+        <v>1219</v>
       </c>
       <c r="B523" t="s">
-        <v>842</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>283</v>
+        <v>841</v>
       </c>
       <c r="B524" t="s">
-        <v>596</v>
+        <v>842</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>883</v>
+        <v>283</v>
       </c>
       <c r="B525" t="s">
-        <v>884</v>
+        <v>596</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>1180</v>
+        <v>883</v>
       </c>
       <c r="B526" t="s">
-        <v>1181</v>
+        <v>884</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>756</v>
+        <v>1180</v>
       </c>
       <c r="B527" t="s">
-        <v>757</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>1078</v>
+        <v>756</v>
       </c>
       <c r="B528" t="s">
-        <v>1079</v>
+        <v>757</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>67</v>
+        <v>1078</v>
       </c>
       <c r="B529" t="s">
-        <v>597</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B530" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="B531" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>289</v>
+        <v>95</v>
       </c>
       <c r="B532" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B533" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="B534" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>193</v>
+        <v>264</v>
       </c>
       <c r="B535" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>901</v>
+        <v>193</v>
       </c>
       <c r="B536" t="s">
-        <v>902</v>
+        <v>603</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>44</v>
+        <v>901</v>
       </c>
       <c r="B537" t="s">
-        <v>1125</v>
+        <v>902</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>1070</v>
+        <v>44</v>
       </c>
       <c r="B538" t="s">
-        <v>1071</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>324</v>
+        <v>1070</v>
       </c>
       <c r="B539" t="s">
-        <v>604</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B540" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>849</v>
+        <v>325</v>
       </c>
       <c r="B541" t="s">
-        <v>850</v>
+        <v>605</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>887</v>
+        <v>849</v>
       </c>
       <c r="B542" t="s">
-        <v>888</v>
+        <v>850</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>869</v>
+        <v>887</v>
       </c>
       <c r="B543" t="s">
-        <v>870</v>
+        <v>888</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>33</v>
+        <v>869</v>
       </c>
       <c r="B544" t="s">
-        <v>606</v>
+        <v>870</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B545" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>1143</v>
+        <v>36</v>
       </c>
       <c r="B546" t="s">
-        <v>1144</v>
+        <v>607</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>309</v>
+        <v>1143</v>
       </c>
       <c r="B547" t="s">
-        <v>608</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>257</v>
+        <v>309</v>
       </c>
       <c r="B548" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>302</v>
+        <v>257</v>
       </c>
       <c r="B549" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>228</v>
+        <v>302</v>
       </c>
       <c r="B550" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c r="B551" t="s">
-        <v>18</v>
+        <v>611</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>655</v>
+        <v>17</v>
       </c>
       <c r="B552" t="s">
-        <v>743</v>
+        <v>18</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>785</v>
+        <v>655</v>
       </c>
       <c r="B553" t="s">
-        <v>786</v>
+        <v>743</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>142</v>
+        <v>785</v>
       </c>
       <c r="B554" t="s">
-        <v>612</v>
+        <v>786</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>1178</v>
+        <v>142</v>
       </c>
       <c r="B555" t="s">
-        <v>1179</v>
+        <v>612</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>956</v>
+        <v>1178</v>
       </c>
       <c r="B556" t="s">
-        <v>957</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>54</v>
+        <v>956</v>
       </c>
       <c r="B557" t="s">
-        <v>613</v>
+        <v>957</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>265</v>
+        <v>54</v>
       </c>
       <c r="B558" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>976</v>
+        <v>265</v>
       </c>
       <c r="B559" t="s">
-        <v>975</v>
+        <v>614</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>56</v>
+        <v>976</v>
       </c>
       <c r="B560" t="s">
-        <v>615</v>
+        <v>975</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>1217</v>
+        <v>56</v>
       </c>
       <c r="B561" t="s">
-        <v>1218</v>
+        <v>615</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>185</v>
+        <v>1217</v>
       </c>
       <c r="B562" t="s">
-        <v>616</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="B563" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="B564" t="s">
-        <v>1146</v>
+        <v>617</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B565" t="s">
-        <v>1124</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>1170</v>
+        <v>40</v>
       </c>
       <c r="B566" t="s">
-        <v>1171</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>165</v>
+        <v>1170</v>
       </c>
       <c r="B567" t="s">
-        <v>618</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="B568" t="s">
-        <v>11</v>
+        <v>618</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>250</v>
+        <v>12</v>
       </c>
       <c r="B569" t="s">
-        <v>619</v>
+        <v>11</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>27</v>
+        <v>250</v>
       </c>
       <c r="B570" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>1040</v>
+        <v>27</v>
       </c>
       <c r="B571" t="s">
-        <v>1041</v>
+        <v>620</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>28</v>
+        <v>1040</v>
       </c>
       <c r="B572" t="s">
-        <v>621</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>1205</v>
+        <v>28</v>
       </c>
       <c r="B573" t="s">
-        <v>1206</v>
+        <v>621</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>255</v>
+        <v>1205</v>
       </c>
       <c r="B574" t="s">
-        <v>622</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>795</v>
+        <v>255</v>
       </c>
       <c r="B575" t="s">
-        <v>796</v>
+        <v>622</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>267</v>
+        <v>795</v>
       </c>
       <c r="B576" t="s">
-        <v>623</v>
+        <v>796</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>661</v>
+        <v>267</v>
       </c>
       <c r="B577" t="s">
-        <v>744</v>
+        <v>623</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B578" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>139</v>
+        <v>662</v>
       </c>
       <c r="B579" t="s">
-        <v>624</v>
+        <v>745</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="B580" t="s">
-        <v>2</v>
+        <v>624</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="B581" t="s">
-        <v>625</v>
+        <v>2</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>1034</v>
+        <v>105</v>
       </c>
       <c r="B582" t="s">
-        <v>1123</v>
+        <v>625</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>865</v>
+        <v>1034</v>
       </c>
       <c r="B583" t="s">
-        <v>866</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>1035</v>
+        <v>865</v>
       </c>
       <c r="B584" t="s">
-        <v>1122</v>
+        <v>866</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>292</v>
+        <v>1035</v>
       </c>
       <c r="B585" t="s">
-        <v>626</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>8</v>
+        <v>292</v>
       </c>
       <c r="B586" t="s">
-        <v>11</v>
+        <v>626</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>335</v>
+        <v>8</v>
       </c>
       <c r="B587" t="s">
-        <v>627</v>
+        <v>11</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B588" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>259</v>
+        <v>332</v>
       </c>
       <c r="B589" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>319</v>
+        <v>259</v>
       </c>
       <c r="B590" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>859</v>
+        <v>319</v>
       </c>
       <c r="B591" t="s">
-        <v>860</v>
+        <v>630</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>1174</v>
+        <v>859</v>
       </c>
       <c r="B592" t="s">
-        <v>1175</v>
+        <v>860</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>268</v>
+        <v>1174</v>
       </c>
       <c r="B593" t="s">
-        <v>631</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B594" t="s">
-        <v>1117</v>
+        <v>631</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B595" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B596" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B597" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B598" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B599" t="s">
-        <v>1116</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>92</v>
+        <v>272</v>
       </c>
       <c r="B600" t="s">
-        <v>632</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>200</v>
+        <v>92</v>
       </c>
       <c r="B601" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B602" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>1227</v>
+        <v>203</v>
       </c>
       <c r="B603" t="s">
-        <v>1228</v>
+        <v>634</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>172</v>
+        <v>1227</v>
       </c>
       <c r="B604" t="s">
-        <v>635</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>693</v>
+        <v>172</v>
       </c>
       <c r="B605" t="s">
-        <v>746</v>
+        <v>635</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>252</v>
+        <v>693</v>
       </c>
       <c r="B606" t="s">
-        <v>636</v>
+        <v>746</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>694</v>
+        <v>252</v>
       </c>
       <c r="B607" t="s">
-        <v>747</v>
+        <v>636</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>189</v>
+        <v>694</v>
       </c>
       <c r="B608" t="s">
-        <v>637</v>
+        <v>747</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>989</v>
+        <v>189</v>
       </c>
       <c r="B609" t="s">
-        <v>990</v>
+        <v>637</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>311</v>
+        <v>989</v>
       </c>
       <c r="B610" t="s">
-        <v>638</v>
+        <v>990</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B611" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>1033</v>
+        <v>312</v>
       </c>
       <c r="B612" t="s">
-        <v>1115</v>
+        <v>639</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>1005</v>
+        <v>1033</v>
       </c>
       <c r="B613" t="s">
-        <v>1006</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>81</v>
+        <v>1005</v>
       </c>
       <c r="B614" t="s">
-        <v>640</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>651</v>
+        <v>81</v>
       </c>
       <c r="B615" t="s">
-        <v>748</v>
+        <v>640</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>922</v>
+        <v>651</v>
       </c>
       <c r="B616" t="s">
-        <v>923</v>
+        <v>748</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>642</v>
+        <v>922</v>
       </c>
       <c r="B617" t="s">
-        <v>749</v>
+        <v>923</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>969</v>
+        <v>642</v>
       </c>
       <c r="B618" t="s">
-        <v>970</v>
+        <v>749</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
+        <v>969</v>
+      </c>
+      <c r="B619" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A620" t="s">
         <v>1162</v>
       </c>
-      <c r="B619" t="s">
+      <c r="B620" t="s">
         <v>1163</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6375AF06-C340-4F6D-AE3E-EDA2D368ECB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{219392D0-E27F-4CAF-84DF-3ACC189C787A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="1233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="1235">
   <si>
     <t>trigger</t>
   </si>
@@ -3724,6 +3724,12 @@
   </si>
   <si>
     <t>patient</t>
+  </si>
+  <si>
+    <t>eval</t>
+  </si>
+  <si>
+    <t>evaluation</t>
   </si>
 </sst>
 </file>
@@ -3779,10 +3785,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B620" totalsRowShown="0">
-  <autoFilter ref="A1:B620" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B620">
-    <sortCondition ref="A1:A620"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B621" totalsRowShown="0">
+  <autoFilter ref="A1:B621" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B621">
+    <sortCondition ref="A1:A621"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4055,7 +4061,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B620"/>
+  <dimension ref="A1:B621"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -5576,23 +5582,23 @@
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>764</v>
+        <v>1233</v>
       </c>
       <c r="B190" t="s">
-        <v>1010</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>169</v>
+        <v>764</v>
       </c>
       <c r="B191" t="s">
-        <v>425</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B192" t="s">
         <v>425</v>
@@ -5600,1215 +5606,1215 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>1011</v>
+        <v>170</v>
       </c>
       <c r="B193" t="s">
-        <v>765</v>
+        <v>425</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>178</v>
+        <v>1011</v>
       </c>
       <c r="B194" t="s">
-        <v>426</v>
+        <v>765</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="B195" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>238</v>
+        <v>111</v>
       </c>
       <c r="B196" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>106</v>
+        <v>238</v>
       </c>
       <c r="B197" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B198" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="B199" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>667</v>
+        <v>179</v>
       </c>
       <c r="B200" t="s">
-        <v>722</v>
+        <v>431</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>97</v>
+        <v>667</v>
       </c>
       <c r="B201" t="s">
-        <v>432</v>
+        <v>722</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B202" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>242</v>
+        <v>110</v>
       </c>
       <c r="B203" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="B204" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="B205" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B206" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>1110</v>
+        <v>182</v>
       </c>
       <c r="B207" t="s">
-        <v>1111</v>
+        <v>437</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>977</v>
+        <v>1110</v>
       </c>
       <c r="B208" t="s">
-        <v>978</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="B209" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>1198</v>
+        <v>979</v>
       </c>
       <c r="B210" t="s">
-        <v>1199</v>
+        <v>980</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="B211" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>253</v>
+        <v>1201</v>
       </c>
       <c r="B212" t="s">
-        <v>438</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>34</v>
+        <v>253</v>
       </c>
       <c r="B213" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>787</v>
+        <v>34</v>
       </c>
       <c r="B214" t="s">
-        <v>788</v>
+        <v>439</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>180</v>
+        <v>787</v>
       </c>
       <c r="B215" t="s">
-        <v>440</v>
+        <v>788</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>275</v>
+        <v>180</v>
       </c>
       <c r="B216" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>857</v>
+        <v>275</v>
       </c>
       <c r="B217" t="s">
-        <v>858</v>
+        <v>441</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>116</v>
+        <v>857</v>
       </c>
       <c r="B218" t="s">
-        <v>442</v>
+        <v>858</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>208</v>
+        <v>116</v>
       </c>
       <c r="B219" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>1221</v>
+        <v>208</v>
       </c>
       <c r="B220" t="s">
-        <v>1222</v>
+        <v>443</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>1056</v>
+        <v>1221</v>
       </c>
       <c r="B221" t="s">
-        <v>1057</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>118</v>
+        <v>1056</v>
       </c>
       <c r="B222" t="s">
-        <v>444</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>641</v>
+        <v>118</v>
       </c>
       <c r="B223" t="s">
-        <v>723</v>
+        <v>444</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>815</v>
+        <v>641</v>
       </c>
       <c r="B224" t="s">
-        <v>816</v>
+        <v>723</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>298</v>
+        <v>815</v>
       </c>
       <c r="B225" t="s">
-        <v>445</v>
+        <v>816</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>643</v>
+        <v>298</v>
       </c>
       <c r="B226" t="s">
-        <v>724</v>
+        <v>445</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B227" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>1036</v>
+        <v>644</v>
       </c>
       <c r="B228" t="s">
-        <v>1037</v>
+        <v>725</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>90</v>
+        <v>1036</v>
       </c>
       <c r="B229" t="s">
-        <v>446</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B230" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B231" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>1072</v>
+        <v>89</v>
       </c>
       <c r="B232" t="s">
-        <v>1073</v>
+        <v>448</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>23</v>
+        <v>1072</v>
       </c>
       <c r="B233" t="s">
-        <v>1136</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B234" t="s">
-        <v>6</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>1141</v>
+        <v>5</v>
       </c>
       <c r="B235" t="s">
-        <v>1142</v>
+        <v>6</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>126</v>
+        <v>1141</v>
       </c>
       <c r="B236" t="s">
-        <v>449</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B237" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B238" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B239" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B240" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>277</v>
+        <v>119</v>
       </c>
       <c r="B241" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>1074</v>
+        <v>277</v>
       </c>
       <c r="B242" t="s">
-        <v>1075</v>
+        <v>454</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>9</v>
+        <v>1074</v>
       </c>
       <c r="B243" t="s">
-        <v>10</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>129</v>
+        <v>9</v>
       </c>
       <c r="B244" t="s">
-        <v>455</v>
+        <v>10</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B245" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="B246" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="B247" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>77</v>
+        <v>262</v>
       </c>
       <c r="B248" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>938</v>
+        <v>77</v>
       </c>
       <c r="B249" t="s">
-        <v>939</v>
+        <v>459</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>1172</v>
+        <v>938</v>
       </c>
       <c r="B250" t="s">
-        <v>1173</v>
+        <v>939</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>168</v>
+        <v>1172</v>
       </c>
       <c r="B251" t="s">
-        <v>460</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B252" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>835</v>
+        <v>167</v>
       </c>
       <c r="B253" t="s">
-        <v>836</v>
+        <v>461</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>791</v>
+        <v>835</v>
       </c>
       <c r="B254" t="s">
-        <v>792</v>
+        <v>836</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>304</v>
+        <v>791</v>
       </c>
       <c r="B255" t="s">
-        <v>462</v>
+        <v>792</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>758</v>
+        <v>304</v>
       </c>
       <c r="B256" t="s">
-        <v>759</v>
+        <v>462</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>897</v>
+        <v>758</v>
       </c>
       <c r="B257" t="s">
-        <v>898</v>
+        <v>759</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>652</v>
+        <v>897</v>
       </c>
       <c r="B258" t="s">
-        <v>726</v>
+        <v>898</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>86</v>
+        <v>652</v>
       </c>
       <c r="B259" t="s">
-        <v>463</v>
+        <v>726</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B260" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="B261" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B262" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B263" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>251</v>
+        <v>158</v>
       </c>
       <c r="B264" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>285</v>
+        <v>251</v>
       </c>
       <c r="B265" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>326</v>
+        <v>285</v>
       </c>
       <c r="B266" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B267" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>229</v>
+        <v>327</v>
       </c>
       <c r="B268" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>55</v>
+        <v>229</v>
       </c>
       <c r="B269" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>657</v>
+        <v>55</v>
       </c>
       <c r="B270" t="s">
-        <v>727</v>
+        <v>473</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>235</v>
+        <v>657</v>
       </c>
       <c r="B271" t="s">
-        <v>474</v>
+        <v>727</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>57</v>
+        <v>235</v>
       </c>
       <c r="B272" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>236</v>
+        <v>57</v>
       </c>
       <c r="B273" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>766</v>
+        <v>236</v>
       </c>
       <c r="B274" t="s">
-        <v>1009</v>
+        <v>476</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>1012</v>
+        <v>766</v>
       </c>
       <c r="B275" t="s">
-        <v>767</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>164</v>
+        <v>1012</v>
       </c>
       <c r="B276" t="s">
-        <v>477</v>
+        <v>767</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>201</v>
+        <v>164</v>
       </c>
       <c r="B277" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B278" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>313</v>
+        <v>204</v>
       </c>
       <c r="B279" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>873</v>
+        <v>313</v>
       </c>
       <c r="B280" t="s">
-        <v>874</v>
+        <v>480</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>997</v>
+        <v>873</v>
       </c>
       <c r="B281" t="s">
-        <v>998</v>
+        <v>874</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>258</v>
+        <v>997</v>
       </c>
       <c r="B282" t="s">
-        <v>481</v>
+        <v>998</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>983</v>
+        <v>258</v>
       </c>
       <c r="B283" t="s">
-        <v>984</v>
+        <v>481</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>160</v>
+        <v>983</v>
       </c>
       <c r="B284" t="s">
-        <v>482</v>
+        <v>984</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>692</v>
+        <v>160</v>
       </c>
       <c r="B285" t="s">
-        <v>728</v>
+        <v>482</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>1166</v>
+        <v>692</v>
       </c>
       <c r="B286" t="s">
-        <v>1167</v>
+        <v>728</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>760</v>
+        <v>1166</v>
       </c>
       <c r="B287" t="s">
-        <v>761</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>895</v>
+        <v>760</v>
       </c>
       <c r="B288" t="s">
-        <v>896</v>
+        <v>761</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B289" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>184</v>
+        <v>893</v>
       </c>
       <c r="B290" t="s">
-        <v>483</v>
+        <v>894</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>244</v>
+        <v>184</v>
       </c>
       <c r="B291" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B292" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>686</v>
+        <v>243</v>
       </c>
       <c r="B293" t="s">
-        <v>729</v>
+        <v>485</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B294" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B295" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B296" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B297" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>1192</v>
+        <v>690</v>
       </c>
       <c r="B298" t="s">
-        <v>1193</v>
+        <v>733</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>280</v>
+        <v>1192</v>
       </c>
       <c r="B299" t="s">
-        <v>486</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B300" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>49</v>
+        <v>281</v>
       </c>
       <c r="B301" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B302" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>136</v>
+        <v>53</v>
       </c>
       <c r="B303" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="B304" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>1190</v>
+        <v>72</v>
       </c>
       <c r="B305" t="s">
-        <v>1191</v>
+        <v>490</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>221</v>
+        <v>1190</v>
       </c>
       <c r="B306" t="s">
-        <v>492</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>1194</v>
+        <v>221</v>
       </c>
       <c r="B307" t="s">
-        <v>1195</v>
+        <v>492</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>15</v>
+        <v>1194</v>
       </c>
       <c r="B308" t="s">
-        <v>16</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>1060</v>
+        <v>15</v>
       </c>
       <c r="B309" t="s">
-        <v>1061</v>
+        <v>16</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>920</v>
+        <v>1060</v>
       </c>
       <c r="B310" t="s">
-        <v>921</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>108</v>
+        <v>920</v>
       </c>
       <c r="B311" t="s">
-        <v>493</v>
+        <v>921</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>241</v>
+        <v>108</v>
       </c>
       <c r="B312" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>328</v>
+        <v>241</v>
       </c>
       <c r="B313" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>1100</v>
+        <v>328</v>
       </c>
       <c r="B314" t="s">
-        <v>1101</v>
+        <v>495</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>1052</v>
+        <v>1100</v>
       </c>
       <c r="B315" t="s">
-        <v>1053</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>121</v>
+        <v>1052</v>
       </c>
       <c r="B316" t="s">
-        <v>496</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>750</v>
+        <v>121</v>
       </c>
       <c r="B317" t="s">
-        <v>751</v>
+        <v>496</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>781</v>
+        <v>750</v>
       </c>
       <c r="B318" t="s">
-        <v>782</v>
+        <v>751</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>134</v>
+        <v>781</v>
       </c>
       <c r="B319" t="s">
-        <v>497</v>
+        <v>782</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>63</v>
+        <v>134</v>
       </c>
       <c r="B320" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>224</v>
+        <v>63</v>
       </c>
       <c r="B321" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>25</v>
+        <v>224</v>
       </c>
       <c r="B322" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B323" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>207</v>
+        <v>26</v>
       </c>
       <c r="B324" t="s">
-        <v>1133</v>
+        <v>501</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>960</v>
+        <v>207</v>
       </c>
       <c r="B325" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>1113</v>
+        <v>960</v>
       </c>
       <c r="B326" t="s">
-        <v>1114</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>206</v>
+        <v>1113</v>
       </c>
       <c r="B327" t="s">
-        <v>1135</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B328" t="s">
-        <v>502</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B329" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>145</v>
+        <v>205</v>
       </c>
       <c r="B330" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>663</v>
+        <v>145</v>
       </c>
       <c r="B331" t="s">
-        <v>734</v>
+        <v>504</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>171</v>
+        <v>663</v>
       </c>
       <c r="B332" t="s">
-        <v>505</v>
+        <v>734</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>1088</v>
+        <v>171</v>
       </c>
       <c r="B333" t="s">
-        <v>1089</v>
+        <v>505</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>263</v>
+        <v>1088</v>
       </c>
       <c r="B334" t="s">
-        <v>506</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>1090</v>
+        <v>263</v>
       </c>
       <c r="B335" t="s">
-        <v>1091</v>
+        <v>506</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>80</v>
+        <v>1090</v>
       </c>
       <c r="B336" t="s">
-        <v>507</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B337" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>191</v>
+        <v>65</v>
       </c>
       <c r="B338" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="B339" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>192</v>
+        <v>123</v>
       </c>
       <c r="B340" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="B341" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B342" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>1200</v>
+        <v>233</v>
       </c>
       <c r="B343" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>31</v>
+        <v>1200</v>
       </c>
       <c r="B344" t="s">
         <v>514</v>
@@ -6816,311 +6822,311 @@
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B345" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B346" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="B347" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>306</v>
+        <v>71</v>
       </c>
       <c r="B348" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>222</v>
+        <v>306</v>
       </c>
       <c r="B349" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>315</v>
+        <v>222</v>
       </c>
       <c r="B350" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>278</v>
+        <v>315</v>
       </c>
       <c r="B351" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B352" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>831</v>
+        <v>279</v>
       </c>
       <c r="B353" t="s">
-        <v>832</v>
+        <v>522</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>48</v>
+        <v>831</v>
       </c>
       <c r="B354" t="s">
-        <v>523</v>
+        <v>832</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="B355" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="B356" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>223</v>
+        <v>52</v>
       </c>
       <c r="B357" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>1094</v>
+        <v>223</v>
       </c>
       <c r="B358" t="s">
-        <v>1095</v>
+        <v>526</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>1109</v>
+        <v>1094</v>
       </c>
       <c r="B359" t="s">
-        <v>1112</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>1050</v>
+        <v>1109</v>
       </c>
       <c r="B360" t="s">
-        <v>1051</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>96</v>
+        <v>1050</v>
       </c>
       <c r="B361" t="s">
-        <v>527</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>248</v>
+        <v>96</v>
       </c>
       <c r="B362" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B363" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>94</v>
+        <v>249</v>
       </c>
       <c r="B364" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>1064</v>
+        <v>94</v>
       </c>
       <c r="B365" t="s">
-        <v>1065</v>
+        <v>530</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>212</v>
+        <v>1064</v>
       </c>
       <c r="B366" t="s">
-        <v>531</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>1225</v>
+        <v>212</v>
       </c>
       <c r="B367" t="s">
-        <v>1226</v>
+        <v>531</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>916</v>
+        <v>1225</v>
       </c>
       <c r="B368" t="s">
-        <v>917</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B369" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="B370" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>330</v>
+        <v>918</v>
       </c>
       <c r="B371" t="s">
-        <v>532</v>
+        <v>919</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>1066</v>
+        <v>330</v>
       </c>
       <c r="B372" t="s">
-        <v>1067</v>
+        <v>532</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>995</v>
+        <v>1066</v>
       </c>
       <c r="B373" t="s">
-        <v>996</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="B374" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="B375" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>82</v>
+        <v>993</v>
       </c>
       <c r="B376" t="s">
-        <v>533</v>
+        <v>994</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>772</v>
+        <v>82</v>
       </c>
       <c r="B377" t="s">
-        <v>773</v>
+        <v>533</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>197</v>
+        <v>772</v>
       </c>
       <c r="B378" t="s">
-        <v>534</v>
+        <v>773</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>654</v>
+        <v>197</v>
       </c>
       <c r="B379" t="s">
-        <v>735</v>
+        <v>534</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>821</v>
+        <v>654</v>
       </c>
       <c r="B380" t="s">
-        <v>822</v>
+        <v>735</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>1068</v>
+        <v>821</v>
       </c>
       <c r="B381" t="s">
-        <v>1069</v>
+        <v>822</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>3</v>
+        <v>1068</v>
       </c>
       <c r="B382" t="s">
-        <v>4</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>958</v>
+        <v>3</v>
       </c>
       <c r="B383" t="s">
         <v>4</v>
@@ -7128,7 +7134,7 @@
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B384" t="s">
         <v>4</v>
@@ -7136,1889 +7142,1897 @@
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>664</v>
+        <v>959</v>
       </c>
       <c r="B385" t="s">
-        <v>736</v>
+        <v>4</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>770</v>
+        <v>664</v>
       </c>
       <c r="B386" t="s">
-        <v>771</v>
+        <v>736</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>85</v>
+        <v>770</v>
       </c>
       <c r="B387" t="s">
-        <v>535</v>
+        <v>771</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>1062</v>
+        <v>85</v>
       </c>
       <c r="B388" t="s">
-        <v>1063</v>
+        <v>535</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>829</v>
+        <v>1062</v>
       </c>
       <c r="B389" t="s">
-        <v>830</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>809</v>
+        <v>829</v>
       </c>
       <c r="B390" t="s">
-        <v>810</v>
+        <v>830</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>187</v>
+        <v>809</v>
       </c>
       <c r="B391" t="s">
-        <v>536</v>
+        <v>810</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>827</v>
+        <v>187</v>
       </c>
       <c r="B392" t="s">
-        <v>828</v>
+        <v>536</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>934</v>
+        <v>827</v>
       </c>
       <c r="B393" t="s">
-        <v>1130</v>
+        <v>828</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>863</v>
+        <v>934</v>
       </c>
       <c r="B394" t="s">
-        <v>864</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>1044</v>
+        <v>863</v>
       </c>
       <c r="B395" t="s">
-        <v>1045</v>
+        <v>864</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>798</v>
+        <v>1044</v>
       </c>
       <c r="B396" t="s">
-        <v>1131</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B397" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>13</v>
+        <v>797</v>
       </c>
       <c r="B398" t="s">
-        <v>14</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>817</v>
+        <v>13</v>
       </c>
       <c r="B399" t="s">
-        <v>818</v>
+        <v>14</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>186</v>
+        <v>817</v>
       </c>
       <c r="B400" t="s">
-        <v>537</v>
+        <v>818</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>811</v>
+        <v>186</v>
       </c>
       <c r="B401" t="s">
-        <v>812</v>
+        <v>537</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>320</v>
+        <v>811</v>
       </c>
       <c r="B402" t="s">
-        <v>538</v>
+        <v>812</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>656</v>
+        <v>320</v>
       </c>
       <c r="B403" t="s">
-        <v>737</v>
+        <v>538</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>855</v>
+        <v>656</v>
       </c>
       <c r="B404" t="s">
-        <v>856</v>
+        <v>737</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>658</v>
+        <v>855</v>
       </c>
       <c r="B405" t="s">
-        <v>738</v>
+        <v>856</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="B406" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>1207</v>
+        <v>653</v>
       </c>
       <c r="B407" t="s">
-        <v>1208</v>
+        <v>739</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>256</v>
+        <v>1207</v>
       </c>
       <c r="B408" t="s">
-        <v>539</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B409" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B410" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>188</v>
+        <v>261</v>
       </c>
       <c r="B411" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B412" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>936</v>
+        <v>190</v>
       </c>
       <c r="B413" t="s">
-        <v>937</v>
+        <v>543</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>1031</v>
+        <v>936</v>
       </c>
       <c r="B414" t="s">
-        <v>1032</v>
+        <v>937</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>1223</v>
+        <v>1031</v>
       </c>
       <c r="B415" t="s">
-        <v>1224</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>209</v>
+        <v>1223</v>
       </c>
       <c r="B416" t="s">
-        <v>544</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>851</v>
+        <v>209</v>
       </c>
       <c r="B417" t="s">
-        <v>852</v>
+        <v>544</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>143</v>
+        <v>851</v>
       </c>
       <c r="B418" t="s">
-        <v>545</v>
+        <v>852</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B419" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>1203</v>
+        <v>140</v>
       </c>
       <c r="B420" t="s">
-        <v>1204</v>
+        <v>546</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>254</v>
+        <v>1203</v>
       </c>
       <c r="B421" t="s">
-        <v>547</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>331</v>
+        <v>254</v>
       </c>
       <c r="B422" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>210</v>
+        <v>331</v>
       </c>
       <c r="B423" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="B424" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>73</v>
+        <v>234</v>
       </c>
       <c r="B425" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>342</v>
+        <v>73</v>
       </c>
       <c r="B426" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="B427" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>843</v>
+        <v>308</v>
       </c>
       <c r="B428" t="s">
-        <v>844</v>
+        <v>553</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B429" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>220</v>
+        <v>845</v>
       </c>
       <c r="B430" t="s">
-        <v>554</v>
+        <v>846</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>909</v>
+        <v>220</v>
       </c>
       <c r="B431" t="s">
-        <v>910</v>
+        <v>554</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>963</v>
+        <v>909</v>
       </c>
       <c r="B432" t="s">
-        <v>964</v>
+        <v>910</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>1188</v>
+        <v>963</v>
       </c>
       <c r="B433" t="s">
-        <v>1189</v>
+        <v>964</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>227</v>
+        <v>1188</v>
       </c>
       <c r="B434" t="s">
-        <v>555</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>334</v>
+        <v>227</v>
       </c>
       <c r="B435" t="s">
-        <v>1161</v>
+        <v>555</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>971</v>
+        <v>334</v>
       </c>
       <c r="B436" t="s">
-        <v>972</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>778</v>
+        <v>971</v>
       </c>
       <c r="B437" t="s">
-        <v>779</v>
+        <v>972</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>294</v>
+        <v>778</v>
       </c>
       <c r="B438" t="s">
-        <v>556</v>
+        <v>779</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>952</v>
+        <v>294</v>
       </c>
       <c r="B439" t="s">
-        <v>953</v>
+        <v>556</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>339</v>
+        <v>952</v>
       </c>
       <c r="B440" t="s">
-        <v>557</v>
+        <v>953</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>780</v>
+        <v>339</v>
       </c>
       <c r="B441" t="s">
-        <v>779</v>
+        <v>557</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>340</v>
+        <v>780</v>
       </c>
       <c r="B442" t="s">
-        <v>558</v>
+        <v>779</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B443" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>645</v>
+        <v>341</v>
       </c>
       <c r="B444" t="s">
-        <v>740</v>
+        <v>559</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>39</v>
+        <v>645</v>
       </c>
       <c r="B445" t="s">
-        <v>560</v>
+        <v>740</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B446" t="s">
-        <v>1129</v>
+        <v>560</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>343</v>
+        <v>38</v>
       </c>
       <c r="B447" t="s">
-        <v>561</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>107</v>
+        <v>343</v>
       </c>
       <c r="B448" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>1029</v>
+        <v>107</v>
       </c>
       <c r="B449" t="s">
-        <v>1030</v>
+        <v>562</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>903</v>
+        <v>1029</v>
       </c>
       <c r="B450" t="s">
-        <v>904</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>117</v>
+        <v>903</v>
       </c>
       <c r="B451" t="s">
-        <v>563</v>
+        <v>904</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>1025</v>
+        <v>117</v>
       </c>
       <c r="B452" t="s">
-        <v>1026</v>
+        <v>563</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>98</v>
+        <v>1025</v>
       </c>
       <c r="B453" t="s">
-        <v>564</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B454" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>666</v>
+        <v>99</v>
       </c>
       <c r="B455" t="s">
-        <v>741</v>
+        <v>565</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>1107</v>
+        <v>666</v>
       </c>
       <c r="B456" t="s">
-        <v>1024</v>
+        <v>741</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>823</v>
+        <v>1107</v>
       </c>
       <c r="B457" t="s">
-        <v>824</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>113</v>
+        <v>823</v>
       </c>
       <c r="B458" t="s">
-        <v>566</v>
+        <v>824</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>889</v>
+        <v>113</v>
       </c>
       <c r="B459" t="s">
-        <v>890</v>
+        <v>566</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>45</v>
+        <v>889</v>
       </c>
       <c r="B460" t="s">
-        <v>1128</v>
+        <v>890</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>290</v>
+        <v>45</v>
       </c>
       <c r="B461" t="s">
-        <v>567</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B462" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>47</v>
+        <v>299</v>
       </c>
       <c r="B463" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>847</v>
+        <v>47</v>
       </c>
       <c r="B464" t="s">
-        <v>848</v>
+        <v>569</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>51</v>
+        <v>847</v>
       </c>
       <c r="B465" t="s">
-        <v>570</v>
+        <v>848</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>871</v>
+        <v>51</v>
       </c>
       <c r="B466" t="s">
-        <v>872</v>
+        <v>570</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>114</v>
+        <v>871</v>
       </c>
       <c r="B467" t="s">
-        <v>571</v>
+        <v>872</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>853</v>
+        <v>114</v>
       </c>
       <c r="B468" t="s">
-        <v>854</v>
+        <v>571</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>144</v>
+        <v>853</v>
       </c>
       <c r="B469" t="s">
-        <v>572</v>
+        <v>854</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>1080</v>
+        <v>144</v>
       </c>
       <c r="B470" t="s">
-        <v>1081</v>
+        <v>572</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>176</v>
+        <v>1080</v>
       </c>
       <c r="B471" t="s">
-        <v>573</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>316</v>
+        <v>176</v>
       </c>
       <c r="B472" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>29</v>
+        <v>316</v>
       </c>
       <c r="B473" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>1104</v>
+        <v>29</v>
       </c>
       <c r="B474" t="s">
-        <v>1105</v>
+        <v>575</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>1018</v>
+        <v>1104</v>
       </c>
       <c r="B475" t="s">
-        <v>1019</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>1231</v>
+        <v>1018</v>
       </c>
       <c r="B476" t="s">
-        <v>1232</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>293</v>
+        <v>1231</v>
       </c>
       <c r="B477" t="s">
-        <v>576</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>981</v>
+        <v>293</v>
       </c>
       <c r="B478" t="s">
-        <v>982</v>
+        <v>576</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>301</v>
+        <v>981</v>
       </c>
       <c r="B479" t="s">
-        <v>577</v>
+        <v>982</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>1003</v>
+        <v>301</v>
       </c>
       <c r="B480" t="s">
-        <v>1004</v>
+        <v>577</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="B481" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>75</v>
+        <v>1007</v>
       </c>
       <c r="B482" t="s">
-        <v>578</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B483" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B484" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>329</v>
+        <v>78</v>
       </c>
       <c r="B485" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>752</v>
+        <v>329</v>
       </c>
       <c r="B486" t="s">
-        <v>753</v>
+        <v>581</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>805</v>
+        <v>752</v>
       </c>
       <c r="B487" t="s">
-        <v>806</v>
+        <v>753</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>135</v>
+        <v>805</v>
       </c>
       <c r="B488" t="s">
-        <v>582</v>
+        <v>806</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>1186</v>
+        <v>135</v>
       </c>
       <c r="B489" t="s">
-        <v>1187</v>
+        <v>582</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>1038</v>
+        <v>1186</v>
       </c>
       <c r="B490" t="s">
-        <v>1039</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>215</v>
+        <v>1038</v>
       </c>
       <c r="B491" t="s">
-        <v>583</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>935</v>
+        <v>215</v>
       </c>
       <c r="B492" t="s">
-        <v>1145</v>
+        <v>583</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>216</v>
+        <v>935</v>
       </c>
       <c r="B493" t="s">
-        <v>1126</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>317</v>
+        <v>216</v>
       </c>
       <c r="B494" t="s">
-        <v>584</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>1082</v>
+        <v>317</v>
       </c>
       <c r="B495" t="s">
-        <v>1083</v>
+        <v>584</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>214</v>
+        <v>1082</v>
       </c>
       <c r="B496" t="s">
-        <v>1127</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>999</v>
+        <v>214</v>
       </c>
       <c r="B497" t="s">
-        <v>1000</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B498" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>225</v>
+        <v>1001</v>
       </c>
       <c r="B499" t="s">
-        <v>585</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>948</v>
+        <v>225</v>
       </c>
       <c r="B500" t="s">
-        <v>949</v>
+        <v>585</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>1098</v>
+        <v>948</v>
       </c>
       <c r="B501" t="s">
-        <v>1099</v>
+        <v>949</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>1048</v>
+        <v>1098</v>
       </c>
       <c r="B502" t="s">
-        <v>1049</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>93</v>
+        <v>1048</v>
       </c>
       <c r="B503" t="s">
-        <v>586</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="B504" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>783</v>
+        <v>120</v>
       </c>
       <c r="B505" t="s">
-        <v>784</v>
+        <v>587</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>133</v>
+        <v>783</v>
       </c>
       <c r="B506" t="s">
-        <v>588</v>
+        <v>784</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="B507" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B508" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>825</v>
+        <v>66</v>
       </c>
       <c r="B509" t="s">
-        <v>826</v>
+        <v>590</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>950</v>
+        <v>825</v>
       </c>
       <c r="B510" t="s">
-        <v>951</v>
+        <v>826</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>1215</v>
+        <v>950</v>
       </c>
       <c r="B511" t="s">
-        <v>1216</v>
+        <v>951</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>79</v>
+        <v>1215</v>
       </c>
       <c r="B512" t="s">
-        <v>591</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="B513" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="B514" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>1184</v>
+        <v>122</v>
       </c>
       <c r="B515" t="s">
-        <v>1185</v>
+        <v>593</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>181</v>
+        <v>1184</v>
       </c>
       <c r="B516" t="s">
-        <v>594</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>801</v>
+        <v>181</v>
       </c>
       <c r="B517" t="s">
-        <v>802</v>
+        <v>594</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>691</v>
+        <v>801</v>
       </c>
       <c r="B518" t="s">
-        <v>742</v>
+        <v>802</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>1151</v>
+        <v>691</v>
       </c>
       <c r="B519" t="s">
-        <v>1152</v>
+        <v>742</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="B520" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>284</v>
+        <v>1149</v>
       </c>
       <c r="B521" t="s">
-        <v>595</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>973</v>
+        <v>284</v>
       </c>
       <c r="B522" t="s">
-        <v>974</v>
+        <v>595</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>1219</v>
+        <v>973</v>
       </c>
       <c r="B523" t="s">
-        <v>1220</v>
+        <v>974</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>841</v>
+        <v>1219</v>
       </c>
       <c r="B524" t="s">
-        <v>842</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>283</v>
+        <v>841</v>
       </c>
       <c r="B525" t="s">
-        <v>596</v>
+        <v>842</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>883</v>
+        <v>283</v>
       </c>
       <c r="B526" t="s">
-        <v>884</v>
+        <v>596</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>1180</v>
+        <v>883</v>
       </c>
       <c r="B527" t="s">
-        <v>1181</v>
+        <v>884</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>756</v>
+        <v>1180</v>
       </c>
       <c r="B528" t="s">
-        <v>757</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>1078</v>
+        <v>756</v>
       </c>
       <c r="B529" t="s">
-        <v>1079</v>
+        <v>757</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>67</v>
+        <v>1078</v>
       </c>
       <c r="B530" t="s">
-        <v>597</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B531" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="B532" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>289</v>
+        <v>95</v>
       </c>
       <c r="B533" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B534" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="B535" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>193</v>
+        <v>264</v>
       </c>
       <c r="B536" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>901</v>
+        <v>193</v>
       </c>
       <c r="B537" t="s">
-        <v>902</v>
+        <v>603</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>44</v>
+        <v>901</v>
       </c>
       <c r="B538" t="s">
-        <v>1125</v>
+        <v>902</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>1070</v>
+        <v>44</v>
       </c>
       <c r="B539" t="s">
-        <v>1071</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>324</v>
+        <v>1070</v>
       </c>
       <c r="B540" t="s">
-        <v>604</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B541" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>849</v>
+        <v>325</v>
       </c>
       <c r="B542" t="s">
-        <v>850</v>
+        <v>605</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>887</v>
+        <v>849</v>
       </c>
       <c r="B543" t="s">
-        <v>888</v>
+        <v>850</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>869</v>
+        <v>887</v>
       </c>
       <c r="B544" t="s">
-        <v>870</v>
+        <v>888</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>33</v>
+        <v>869</v>
       </c>
       <c r="B545" t="s">
-        <v>606</v>
+        <v>870</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B546" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>1143</v>
+        <v>36</v>
       </c>
       <c r="B547" t="s">
-        <v>1144</v>
+        <v>607</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>309</v>
+        <v>1143</v>
       </c>
       <c r="B548" t="s">
-        <v>608</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>257</v>
+        <v>309</v>
       </c>
       <c r="B549" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>302</v>
+        <v>257</v>
       </c>
       <c r="B550" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>228</v>
+        <v>302</v>
       </c>
       <c r="B551" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>17</v>
+        <v>228</v>
       </c>
       <c r="B552" t="s">
-        <v>18</v>
+        <v>611</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>655</v>
+        <v>17</v>
       </c>
       <c r="B553" t="s">
-        <v>743</v>
+        <v>18</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>785</v>
+        <v>655</v>
       </c>
       <c r="B554" t="s">
-        <v>786</v>
+        <v>743</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>142</v>
+        <v>785</v>
       </c>
       <c r="B555" t="s">
-        <v>612</v>
+        <v>786</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>1178</v>
+        <v>142</v>
       </c>
       <c r="B556" t="s">
-        <v>1179</v>
+        <v>612</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>956</v>
+        <v>1178</v>
       </c>
       <c r="B557" t="s">
-        <v>957</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>54</v>
+        <v>956</v>
       </c>
       <c r="B558" t="s">
-        <v>613</v>
+        <v>957</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>265</v>
+        <v>54</v>
       </c>
       <c r="B559" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>976</v>
+        <v>265</v>
       </c>
       <c r="B560" t="s">
-        <v>975</v>
+        <v>614</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>56</v>
+        <v>976</v>
       </c>
       <c r="B561" t="s">
-        <v>615</v>
+        <v>975</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>1217</v>
+        <v>56</v>
       </c>
       <c r="B562" t="s">
-        <v>1218</v>
+        <v>615</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>185</v>
+        <v>1217</v>
       </c>
       <c r="B563" t="s">
-        <v>616</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="B564" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="B565" t="s">
-        <v>1146</v>
+        <v>617</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B566" t="s">
-        <v>1124</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>1170</v>
+        <v>40</v>
       </c>
       <c r="B567" t="s">
-        <v>1171</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>165</v>
+        <v>1170</v>
       </c>
       <c r="B568" t="s">
-        <v>618</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>12</v>
+        <v>165</v>
       </c>
       <c r="B569" t="s">
-        <v>11</v>
+        <v>618</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>250</v>
+        <v>12</v>
       </c>
       <c r="B570" t="s">
-        <v>619</v>
+        <v>11</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>27</v>
+        <v>250</v>
       </c>
       <c r="B571" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>1040</v>
+        <v>27</v>
       </c>
       <c r="B572" t="s">
-        <v>1041</v>
+        <v>620</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>28</v>
+        <v>1040</v>
       </c>
       <c r="B573" t="s">
-        <v>621</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>1205</v>
+        <v>28</v>
       </c>
       <c r="B574" t="s">
-        <v>1206</v>
+        <v>621</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>255</v>
+        <v>1205</v>
       </c>
       <c r="B575" t="s">
-        <v>622</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>795</v>
+        <v>255</v>
       </c>
       <c r="B576" t="s">
-        <v>796</v>
+        <v>622</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>267</v>
+        <v>795</v>
       </c>
       <c r="B577" t="s">
-        <v>623</v>
+        <v>796</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>661</v>
+        <v>267</v>
       </c>
       <c r="B578" t="s">
-        <v>744</v>
+        <v>623</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B579" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>139</v>
+        <v>662</v>
       </c>
       <c r="B580" t="s">
-        <v>624</v>
+        <v>745</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>7</v>
+        <v>139</v>
       </c>
       <c r="B581" t="s">
-        <v>2</v>
+        <v>624</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>105</v>
+        <v>7</v>
       </c>
       <c r="B582" t="s">
-        <v>625</v>
+        <v>2</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>1034</v>
+        <v>105</v>
       </c>
       <c r="B583" t="s">
-        <v>1123</v>
+        <v>625</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>865</v>
+        <v>1034</v>
       </c>
       <c r="B584" t="s">
-        <v>866</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>1035</v>
+        <v>865</v>
       </c>
       <c r="B585" t="s">
-        <v>1122</v>
+        <v>866</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>292</v>
+        <v>1035</v>
       </c>
       <c r="B586" t="s">
-        <v>626</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>8</v>
+        <v>292</v>
       </c>
       <c r="B587" t="s">
-        <v>11</v>
+        <v>626</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>335</v>
+        <v>8</v>
       </c>
       <c r="B588" t="s">
-        <v>627</v>
+        <v>11</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B589" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>259</v>
+        <v>332</v>
       </c>
       <c r="B590" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>319</v>
+        <v>259</v>
       </c>
       <c r="B591" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>859</v>
+        <v>319</v>
       </c>
       <c r="B592" t="s">
-        <v>860</v>
+        <v>630</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>1174</v>
+        <v>859</v>
       </c>
       <c r="B593" t="s">
-        <v>1175</v>
+        <v>860</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>268</v>
+        <v>1174</v>
       </c>
       <c r="B594" t="s">
-        <v>631</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B595" t="s">
-        <v>1117</v>
+        <v>631</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B596" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B597" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B598" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B599" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B600" t="s">
-        <v>1116</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>92</v>
+        <v>272</v>
       </c>
       <c r="B601" t="s">
-        <v>632</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>200</v>
+        <v>92</v>
       </c>
       <c r="B602" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B603" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>1227</v>
+        <v>203</v>
       </c>
       <c r="B604" t="s">
-        <v>1228</v>
+        <v>634</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>172</v>
+        <v>1227</v>
       </c>
       <c r="B605" t="s">
-        <v>635</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>693</v>
+        <v>172</v>
       </c>
       <c r="B606" t="s">
-        <v>746</v>
+        <v>635</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>252</v>
+        <v>693</v>
       </c>
       <c r="B607" t="s">
-        <v>636</v>
+        <v>746</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>694</v>
+        <v>252</v>
       </c>
       <c r="B608" t="s">
-        <v>747</v>
+        <v>636</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>189</v>
+        <v>694</v>
       </c>
       <c r="B609" t="s">
-        <v>637</v>
+        <v>747</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>989</v>
+        <v>189</v>
       </c>
       <c r="B610" t="s">
-        <v>990</v>
+        <v>637</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>311</v>
+        <v>989</v>
       </c>
       <c r="B611" t="s">
-        <v>638</v>
+        <v>990</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B612" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>1033</v>
+        <v>312</v>
       </c>
       <c r="B613" t="s">
-        <v>1115</v>
+        <v>639</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>1005</v>
+        <v>1033</v>
       </c>
       <c r="B614" t="s">
-        <v>1006</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>81</v>
+        <v>1005</v>
       </c>
       <c r="B615" t="s">
-        <v>640</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>651</v>
+        <v>81</v>
       </c>
       <c r="B616" t="s">
-        <v>748</v>
+        <v>640</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>922</v>
+        <v>651</v>
       </c>
       <c r="B617" t="s">
-        <v>923</v>
+        <v>748</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>642</v>
+        <v>922</v>
       </c>
       <c r="B618" t="s">
-        <v>749</v>
+        <v>923</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>969</v>
+        <v>642</v>
       </c>
       <c r="B619" t="s">
-        <v>970</v>
+        <v>749</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
+        <v>969</v>
+      </c>
+      <c r="B620" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A621" t="s">
         <v>1162</v>
       </c>
-      <c r="B620" t="s">
+      <c r="B621" t="s">
         <v>1163</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{219392D0-E27F-4CAF-84DF-3ACC189C787A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A82E17C-936E-497C-BB3F-8EA81F8E4B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1242" uniqueCount="1235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="1239">
   <si>
     <t>trigger</t>
   </si>
@@ -3730,6 +3730,18 @@
   </si>
   <si>
     <t>evaluation</t>
+  </si>
+  <si>
+    <t>num</t>
+  </si>
+  <si>
+    <t>number</t>
+  </si>
+  <si>
+    <t>sot</t>
+  </si>
+  <si>
+    <t>some of the</t>
   </si>
 </sst>
 </file>
@@ -3785,10 +3797,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B621" totalsRowShown="0">
-  <autoFilter ref="A1:B621" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B621">
-    <sortCondition ref="A1:A621"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B623" totalsRowShown="0">
+  <autoFilter ref="A1:B623" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B623">
+    <sortCondition ref="A1:A623"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4061,7 +4073,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B621"/>
+  <dimension ref="A1:B623"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -7270,1769 +7282,1785 @@
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>186</v>
+        <v>1235</v>
       </c>
       <c r="B401" t="s">
-        <v>537</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>811</v>
+        <v>186</v>
       </c>
       <c r="B402" t="s">
-        <v>812</v>
+        <v>537</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>320</v>
+        <v>811</v>
       </c>
       <c r="B403" t="s">
-        <v>538</v>
+        <v>812</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>656</v>
+        <v>320</v>
       </c>
       <c r="B404" t="s">
-        <v>737</v>
+        <v>538</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>855</v>
+        <v>656</v>
       </c>
       <c r="B405" t="s">
-        <v>856</v>
+        <v>737</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>658</v>
+        <v>855</v>
       </c>
       <c r="B406" t="s">
-        <v>738</v>
+        <v>856</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="B407" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>1207</v>
+        <v>653</v>
       </c>
       <c r="B408" t="s">
-        <v>1208</v>
+        <v>739</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>256</v>
+        <v>1207</v>
       </c>
       <c r="B409" t="s">
-        <v>539</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B410" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B411" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>188</v>
+        <v>261</v>
       </c>
       <c r="B412" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B413" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>936</v>
+        <v>190</v>
       </c>
       <c r="B414" t="s">
-        <v>937</v>
+        <v>543</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>1031</v>
+        <v>936</v>
       </c>
       <c r="B415" t="s">
-        <v>1032</v>
+        <v>937</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>1223</v>
+        <v>1031</v>
       </c>
       <c r="B416" t="s">
-        <v>1224</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>209</v>
+        <v>1223</v>
       </c>
       <c r="B417" t="s">
-        <v>544</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>851</v>
+        <v>209</v>
       </c>
       <c r="B418" t="s">
-        <v>852</v>
+        <v>544</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>143</v>
+        <v>851</v>
       </c>
       <c r="B419" t="s">
-        <v>545</v>
+        <v>852</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B420" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>1203</v>
+        <v>140</v>
       </c>
       <c r="B421" t="s">
-        <v>1204</v>
+        <v>546</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>254</v>
+        <v>1203</v>
       </c>
       <c r="B422" t="s">
-        <v>547</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>331</v>
+        <v>254</v>
       </c>
       <c r="B423" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>210</v>
+        <v>331</v>
       </c>
       <c r="B424" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="B425" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>73</v>
+        <v>234</v>
       </c>
       <c r="B426" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>342</v>
+        <v>73</v>
       </c>
       <c r="B427" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>308</v>
+        <v>342</v>
       </c>
       <c r="B428" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>843</v>
+        <v>308</v>
       </c>
       <c r="B429" t="s">
-        <v>844</v>
+        <v>553</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B430" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>220</v>
+        <v>845</v>
       </c>
       <c r="B431" t="s">
-        <v>554</v>
+        <v>846</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>909</v>
+        <v>220</v>
       </c>
       <c r="B432" t="s">
-        <v>910</v>
+        <v>554</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>963</v>
+        <v>909</v>
       </c>
       <c r="B433" t="s">
-        <v>964</v>
+        <v>910</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>1188</v>
+        <v>963</v>
       </c>
       <c r="B434" t="s">
-        <v>1189</v>
+        <v>964</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>227</v>
+        <v>1188</v>
       </c>
       <c r="B435" t="s">
-        <v>555</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>334</v>
+        <v>227</v>
       </c>
       <c r="B436" t="s">
-        <v>1161</v>
+        <v>555</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>971</v>
+        <v>334</v>
       </c>
       <c r="B437" t="s">
-        <v>972</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>778</v>
+        <v>971</v>
       </c>
       <c r="B438" t="s">
-        <v>779</v>
+        <v>972</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>294</v>
+        <v>778</v>
       </c>
       <c r="B439" t="s">
-        <v>556</v>
+        <v>779</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>952</v>
+        <v>294</v>
       </c>
       <c r="B440" t="s">
-        <v>953</v>
+        <v>556</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>339</v>
+        <v>952</v>
       </c>
       <c r="B441" t="s">
-        <v>557</v>
+        <v>953</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>780</v>
+        <v>339</v>
       </c>
       <c r="B442" t="s">
-        <v>779</v>
+        <v>557</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>340</v>
+        <v>780</v>
       </c>
       <c r="B443" t="s">
-        <v>558</v>
+        <v>779</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B444" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>645</v>
+        <v>341</v>
       </c>
       <c r="B445" t="s">
-        <v>740</v>
+        <v>559</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>39</v>
+        <v>645</v>
       </c>
       <c r="B446" t="s">
-        <v>560</v>
+        <v>740</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B447" t="s">
-        <v>1129</v>
+        <v>560</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>343</v>
+        <v>38</v>
       </c>
       <c r="B448" t="s">
-        <v>561</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>107</v>
+        <v>343</v>
       </c>
       <c r="B449" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>1029</v>
+        <v>107</v>
       </c>
       <c r="B450" t="s">
-        <v>1030</v>
+        <v>562</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>903</v>
+        <v>1029</v>
       </c>
       <c r="B451" t="s">
-        <v>904</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>117</v>
+        <v>903</v>
       </c>
       <c r="B452" t="s">
-        <v>563</v>
+        <v>904</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>1025</v>
+        <v>117</v>
       </c>
       <c r="B453" t="s">
-        <v>1026</v>
+        <v>563</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>98</v>
+        <v>1025</v>
       </c>
       <c r="B454" t="s">
-        <v>564</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B455" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>666</v>
+        <v>99</v>
       </c>
       <c r="B456" t="s">
-        <v>741</v>
+        <v>565</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>1107</v>
+        <v>666</v>
       </c>
       <c r="B457" t="s">
-        <v>1024</v>
+        <v>741</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>823</v>
+        <v>1107</v>
       </c>
       <c r="B458" t="s">
-        <v>824</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>113</v>
+        <v>823</v>
       </c>
       <c r="B459" t="s">
-        <v>566</v>
+        <v>824</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>889</v>
+        <v>113</v>
       </c>
       <c r="B460" t="s">
-        <v>890</v>
+        <v>566</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>45</v>
+        <v>889</v>
       </c>
       <c r="B461" t="s">
-        <v>1128</v>
+        <v>890</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>290</v>
+        <v>45</v>
       </c>
       <c r="B462" t="s">
-        <v>567</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B463" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>47</v>
+        <v>299</v>
       </c>
       <c r="B464" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>847</v>
+        <v>47</v>
       </c>
       <c r="B465" t="s">
-        <v>848</v>
+        <v>569</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>51</v>
+        <v>847</v>
       </c>
       <c r="B466" t="s">
-        <v>570</v>
+        <v>848</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>871</v>
+        <v>51</v>
       </c>
       <c r="B467" t="s">
-        <v>872</v>
+        <v>570</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>114</v>
+        <v>871</v>
       </c>
       <c r="B468" t="s">
-        <v>571</v>
+        <v>872</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>853</v>
+        <v>114</v>
       </c>
       <c r="B469" t="s">
-        <v>854</v>
+        <v>571</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>144</v>
+        <v>853</v>
       </c>
       <c r="B470" t="s">
-        <v>572</v>
+        <v>854</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>1080</v>
+        <v>144</v>
       </c>
       <c r="B471" t="s">
-        <v>1081</v>
+        <v>572</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>176</v>
+        <v>1080</v>
       </c>
       <c r="B472" t="s">
-        <v>573</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>316</v>
+        <v>176</v>
       </c>
       <c r="B473" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>29</v>
+        <v>316</v>
       </c>
       <c r="B474" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>1104</v>
+        <v>29</v>
       </c>
       <c r="B475" t="s">
-        <v>1105</v>
+        <v>575</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>1018</v>
+        <v>1104</v>
       </c>
       <c r="B476" t="s">
-        <v>1019</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>1231</v>
+        <v>1018</v>
       </c>
       <c r="B477" t="s">
-        <v>1232</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>293</v>
+        <v>1231</v>
       </c>
       <c r="B478" t="s">
-        <v>576</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>981</v>
+        <v>293</v>
       </c>
       <c r="B479" t="s">
-        <v>982</v>
+        <v>576</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>301</v>
+        <v>981</v>
       </c>
       <c r="B480" t="s">
-        <v>577</v>
+        <v>982</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>1003</v>
+        <v>301</v>
       </c>
       <c r="B481" t="s">
-        <v>1004</v>
+        <v>577</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="B482" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>75</v>
+        <v>1007</v>
       </c>
       <c r="B483" t="s">
-        <v>578</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B484" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B485" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>329</v>
+        <v>78</v>
       </c>
       <c r="B486" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>752</v>
+        <v>329</v>
       </c>
       <c r="B487" t="s">
-        <v>753</v>
+        <v>581</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>805</v>
+        <v>752</v>
       </c>
       <c r="B488" t="s">
-        <v>806</v>
+        <v>753</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>135</v>
+        <v>805</v>
       </c>
       <c r="B489" t="s">
-        <v>582</v>
+        <v>806</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>1186</v>
+        <v>135</v>
       </c>
       <c r="B490" t="s">
-        <v>1187</v>
+        <v>582</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>1038</v>
+        <v>1186</v>
       </c>
       <c r="B491" t="s">
-        <v>1039</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>215</v>
+        <v>1038</v>
       </c>
       <c r="B492" t="s">
-        <v>583</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>935</v>
+        <v>215</v>
       </c>
       <c r="B493" t="s">
-        <v>1145</v>
+        <v>583</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>216</v>
+        <v>935</v>
       </c>
       <c r="B494" t="s">
-        <v>1126</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>317</v>
+        <v>216</v>
       </c>
       <c r="B495" t="s">
-        <v>584</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>1082</v>
+        <v>317</v>
       </c>
       <c r="B496" t="s">
-        <v>1083</v>
+        <v>584</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>214</v>
+        <v>1082</v>
       </c>
       <c r="B497" t="s">
-        <v>1127</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>999</v>
+        <v>214</v>
       </c>
       <c r="B498" t="s">
-        <v>1000</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B499" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>225</v>
+        <v>1001</v>
       </c>
       <c r="B500" t="s">
-        <v>585</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>948</v>
+        <v>225</v>
       </c>
       <c r="B501" t="s">
-        <v>949</v>
+        <v>585</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>1098</v>
+        <v>948</v>
       </c>
       <c r="B502" t="s">
-        <v>1099</v>
+        <v>949</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>1048</v>
+        <v>1098</v>
       </c>
       <c r="B503" t="s">
-        <v>1049</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>93</v>
+        <v>1048</v>
       </c>
       <c r="B504" t="s">
-        <v>586</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="B505" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>783</v>
+        <v>120</v>
       </c>
       <c r="B506" t="s">
-        <v>784</v>
+        <v>587</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>133</v>
+        <v>783</v>
       </c>
       <c r="B507" t="s">
-        <v>588</v>
+        <v>784</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>62</v>
+        <v>133</v>
       </c>
       <c r="B508" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B509" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>825</v>
+        <v>66</v>
       </c>
       <c r="B510" t="s">
-        <v>826</v>
+        <v>590</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>950</v>
+        <v>825</v>
       </c>
       <c r="B511" t="s">
-        <v>951</v>
+        <v>826</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>1215</v>
+        <v>950</v>
       </c>
       <c r="B512" t="s">
-        <v>1216</v>
+        <v>951</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>79</v>
+        <v>1215</v>
       </c>
       <c r="B513" t="s">
-        <v>591</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="B514" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>122</v>
+        <v>64</v>
       </c>
       <c r="B515" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>1184</v>
+        <v>122</v>
       </c>
       <c r="B516" t="s">
-        <v>1185</v>
+        <v>593</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>181</v>
+        <v>1184</v>
       </c>
       <c r="B517" t="s">
-        <v>594</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>801</v>
+        <v>181</v>
       </c>
       <c r="B518" t="s">
-        <v>802</v>
+        <v>594</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>691</v>
+        <v>801</v>
       </c>
       <c r="B519" t="s">
-        <v>742</v>
+        <v>802</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>1151</v>
+        <v>691</v>
       </c>
       <c r="B520" t="s">
-        <v>1152</v>
+        <v>742</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="B521" t="s">
-        <v>1150</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>284</v>
+        <v>1149</v>
       </c>
       <c r="B522" t="s">
-        <v>595</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>973</v>
+        <v>284</v>
       </c>
       <c r="B523" t="s">
-        <v>974</v>
+        <v>595</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>1219</v>
+        <v>973</v>
       </c>
       <c r="B524" t="s">
-        <v>1220</v>
+        <v>974</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>841</v>
+        <v>1219</v>
       </c>
       <c r="B525" t="s">
-        <v>842</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>283</v>
+        <v>841</v>
       </c>
       <c r="B526" t="s">
-        <v>596</v>
+        <v>842</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>883</v>
+        <v>283</v>
       </c>
       <c r="B527" t="s">
-        <v>884</v>
+        <v>596</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>1180</v>
+        <v>883</v>
       </c>
       <c r="B528" t="s">
-        <v>1181</v>
+        <v>884</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>756</v>
+        <v>1180</v>
       </c>
       <c r="B529" t="s">
-        <v>757</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>1078</v>
+        <v>756</v>
       </c>
       <c r="B530" t="s">
-        <v>1079</v>
+        <v>757</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>67</v>
+        <v>1078</v>
       </c>
       <c r="B531" t="s">
-        <v>597</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B532" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="B533" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>289</v>
+        <v>95</v>
       </c>
       <c r="B534" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B535" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>264</v>
+        <v>297</v>
       </c>
       <c r="B536" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>193</v>
+        <v>264</v>
       </c>
       <c r="B537" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>901</v>
+        <v>193</v>
       </c>
       <c r="B538" t="s">
-        <v>902</v>
+        <v>603</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>44</v>
+        <v>901</v>
       </c>
       <c r="B539" t="s">
-        <v>1125</v>
+        <v>902</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>1070</v>
+        <v>44</v>
       </c>
       <c r="B540" t="s">
-        <v>1071</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>324</v>
+        <v>1070</v>
       </c>
       <c r="B541" t="s">
-        <v>604</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B542" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>849</v>
+        <v>325</v>
       </c>
       <c r="B543" t="s">
-        <v>850</v>
+        <v>605</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>887</v>
+        <v>849</v>
       </c>
       <c r="B544" t="s">
-        <v>888</v>
+        <v>850</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>869</v>
+        <v>887</v>
       </c>
       <c r="B545" t="s">
-        <v>870</v>
+        <v>888</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>33</v>
+        <v>1237</v>
       </c>
       <c r="B546" t="s">
-        <v>606</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>36</v>
+        <v>869</v>
       </c>
       <c r="B547" t="s">
-        <v>607</v>
+        <v>870</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>1143</v>
+        <v>33</v>
       </c>
       <c r="B548" t="s">
-        <v>1144</v>
+        <v>606</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>309</v>
+        <v>36</v>
       </c>
       <c r="B549" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>257</v>
+        <v>1143</v>
       </c>
       <c r="B550" t="s">
-        <v>609</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B551" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>228</v>
+        <v>257</v>
       </c>
       <c r="B552" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>17</v>
+        <v>302</v>
       </c>
       <c r="B553" t="s">
-        <v>18</v>
+        <v>610</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>655</v>
+        <v>228</v>
       </c>
       <c r="B554" t="s">
-        <v>743</v>
+        <v>611</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>785</v>
+        <v>17</v>
       </c>
       <c r="B555" t="s">
-        <v>786</v>
+        <v>18</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>142</v>
+        <v>655</v>
       </c>
       <c r="B556" t="s">
-        <v>612</v>
+        <v>743</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>1178</v>
+        <v>785</v>
       </c>
       <c r="B557" t="s">
-        <v>1179</v>
+        <v>786</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>956</v>
+        <v>142</v>
       </c>
       <c r="B558" t="s">
-        <v>957</v>
+        <v>612</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>54</v>
+        <v>1178</v>
       </c>
       <c r="B559" t="s">
-        <v>613</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>265</v>
+        <v>956</v>
       </c>
       <c r="B560" t="s">
-        <v>614</v>
+        <v>957</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>976</v>
+        <v>54</v>
       </c>
       <c r="B561" t="s">
-        <v>975</v>
+        <v>613</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>56</v>
+        <v>265</v>
       </c>
       <c r="B562" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>1217</v>
+        <v>976</v>
       </c>
       <c r="B563" t="s">
-        <v>1218</v>
+        <v>975</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>185</v>
+        <v>56</v>
       </c>
       <c r="B564" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>159</v>
+        <v>1217</v>
       </c>
       <c r="B565" t="s">
-        <v>617</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>43</v>
+        <v>185</v>
       </c>
       <c r="B566" t="s">
-        <v>1146</v>
+        <v>616</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>40</v>
+        <v>159</v>
       </c>
       <c r="B567" t="s">
-        <v>1124</v>
+        <v>617</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>1170</v>
+        <v>43</v>
       </c>
       <c r="B568" t="s">
-        <v>1171</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>165</v>
+        <v>40</v>
       </c>
       <c r="B569" t="s">
-        <v>618</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>12</v>
+        <v>1170</v>
       </c>
       <c r="B570" t="s">
-        <v>11</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>250</v>
+        <v>165</v>
       </c>
       <c r="B571" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B572" t="s">
-        <v>620</v>
+        <v>11</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>1040</v>
+        <v>250</v>
       </c>
       <c r="B573" t="s">
-        <v>1041</v>
+        <v>619</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B574" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>1205</v>
+        <v>1040</v>
       </c>
       <c r="B575" t="s">
-        <v>1206</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>255</v>
+        <v>28</v>
       </c>
       <c r="B576" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>795</v>
+        <v>1205</v>
       </c>
       <c r="B577" t="s">
-        <v>796</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="B578" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>661</v>
+        <v>795</v>
       </c>
       <c r="B579" t="s">
-        <v>744</v>
+        <v>796</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>662</v>
+        <v>267</v>
       </c>
       <c r="B580" t="s">
-        <v>745</v>
+        <v>623</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>139</v>
+        <v>661</v>
       </c>
       <c r="B581" t="s">
-        <v>624</v>
+        <v>744</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>7</v>
+        <v>662</v>
       </c>
       <c r="B582" t="s">
-        <v>2</v>
+        <v>745</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="B583" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>1034</v>
+        <v>7</v>
       </c>
       <c r="B584" t="s">
-        <v>1123</v>
+        <v>2</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>865</v>
+        <v>105</v>
       </c>
       <c r="B585" t="s">
-        <v>866</v>
+        <v>625</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B586" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>292</v>
+        <v>865</v>
       </c>
       <c r="B587" t="s">
-        <v>626</v>
+        <v>866</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>8</v>
+        <v>1035</v>
       </c>
       <c r="B588" t="s">
-        <v>11</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>335</v>
+        <v>292</v>
       </c>
       <c r="B589" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>332</v>
+        <v>8</v>
       </c>
       <c r="B590" t="s">
-        <v>628</v>
+        <v>11</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>259</v>
+        <v>335</v>
       </c>
       <c r="B591" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="B592" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>859</v>
+        <v>259</v>
       </c>
       <c r="B593" t="s">
-        <v>860</v>
+        <v>629</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>1174</v>
+        <v>319</v>
       </c>
       <c r="B594" t="s">
-        <v>1175</v>
+        <v>630</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>268</v>
+        <v>859</v>
       </c>
       <c r="B595" t="s">
-        <v>631</v>
+        <v>860</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>271</v>
+        <v>1174</v>
       </c>
       <c r="B596" t="s">
-        <v>1117</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B597" t="s">
-        <v>1118</v>
+        <v>631</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B598" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B599" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B600" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B601" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>92</v>
+        <v>269</v>
       </c>
       <c r="B602" t="s">
-        <v>632</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>200</v>
+        <v>272</v>
       </c>
       <c r="B603" t="s">
-        <v>633</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>203</v>
+        <v>92</v>
       </c>
       <c r="B604" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>1227</v>
+        <v>200</v>
       </c>
       <c r="B605" t="s">
-        <v>1228</v>
+        <v>633</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="B606" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>693</v>
+        <v>1227</v>
       </c>
       <c r="B607" t="s">
-        <v>746</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>252</v>
+        <v>172</v>
       </c>
       <c r="B608" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B609" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>189</v>
+        <v>252</v>
       </c>
       <c r="B610" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>989</v>
+        <v>694</v>
       </c>
       <c r="B611" t="s">
-        <v>990</v>
+        <v>747</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>311</v>
+        <v>189</v>
       </c>
       <c r="B612" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>312</v>
+        <v>989</v>
       </c>
       <c r="B613" t="s">
-        <v>639</v>
+        <v>990</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>1033</v>
+        <v>311</v>
       </c>
       <c r="B614" t="s">
-        <v>1115</v>
+        <v>638</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>1005</v>
+        <v>312</v>
       </c>
       <c r="B615" t="s">
-        <v>1006</v>
+        <v>639</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>81</v>
+        <v>1033</v>
       </c>
       <c r="B616" t="s">
-        <v>640</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>651</v>
+        <v>1005</v>
       </c>
       <c r="B617" t="s">
-        <v>748</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>922</v>
+        <v>81</v>
       </c>
       <c r="B618" t="s">
-        <v>923</v>
+        <v>640</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>642</v>
+        <v>651</v>
       </c>
       <c r="B619" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>969</v>
+        <v>922</v>
       </c>
       <c r="B620" t="s">
-        <v>970</v>
+        <v>923</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
+        <v>642</v>
+      </c>
+      <c r="B621" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A622" t="s">
+        <v>969</v>
+      </c>
+      <c r="B622" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A623" t="s">
         <v>1162</v>
       </c>
-      <c r="B621" t="s">
+      <c r="B623" t="s">
         <v>1163</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A82E17C-936E-497C-BB3F-8EA81F8E4B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F869831E-8A32-4AB9-9B21-822EEAD42575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1246" uniqueCount="1239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="1299">
   <si>
     <t>trigger</t>
   </si>
@@ -3742,16 +3742,202 @@
   </si>
   <si>
     <t>some of the</t>
+  </si>
+  <si>
+    <t>c1</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>c2</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>c3</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>c4</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>c5</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>c6</t>
+  </si>
+  <si>
+    <t>c7</t>
+  </si>
+  <si>
+    <t>c8</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>d1</t>
+  </si>
+  <si>
+    <t>d2</t>
+  </si>
+  <si>
+    <t>d3</t>
+  </si>
+  <si>
+    <t>d4</t>
+  </si>
+  <si>
+    <t>d5</t>
+  </si>
+  <si>
+    <t>d6</t>
+  </si>
+  <si>
+    <t>d7</t>
+  </si>
+  <si>
+    <t>d8</t>
+  </si>
+  <si>
+    <t>d9</t>
+  </si>
+  <si>
+    <t>d10</t>
+  </si>
+  <si>
+    <t>d11</t>
+  </si>
+  <si>
+    <t>d12</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>D7</t>
+  </si>
+  <si>
+    <t>D8</t>
+  </si>
+  <si>
+    <t>D9</t>
+  </si>
+  <si>
+    <t>D10</t>
+  </si>
+  <si>
+    <t>D11</t>
+  </si>
+  <si>
+    <t>D12</t>
+  </si>
+  <si>
+    <t>l1</t>
+  </si>
+  <si>
+    <t>l2</t>
+  </si>
+  <si>
+    <t>l3</t>
+  </si>
+  <si>
+    <t>l4</t>
+  </si>
+  <si>
+    <t>l5</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>L3</t>
+  </si>
+  <si>
+    <t>L4</t>
+  </si>
+  <si>
+    <t>L5</t>
+  </si>
+  <si>
+    <t>s1</t>
+  </si>
+  <si>
+    <t>s2</t>
+  </si>
+  <si>
+    <t>s3</t>
+  </si>
+  <si>
+    <t>s4</t>
+  </si>
+  <si>
+    <t>s5</t>
+  </si>
+  <si>
+    <t>S1</t>
+  </si>
+  <si>
+    <t>S2</t>
+  </si>
+  <si>
+    <t>S3</t>
+  </si>
+  <si>
+    <t>S4</t>
+  </si>
+  <si>
+    <t>S5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3797,10 +3983,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B623" totalsRowShown="0">
-  <autoFilter ref="A1:B623" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B623">
-    <sortCondition ref="A1:A623"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B653" totalsRowShown="0">
+  <autoFilter ref="A1:B653" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B653">
+    <sortCondition ref="A1:A653"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4073,7 +4259,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B623"/>
+  <dimension ref="A1:B653"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -4682,4389 +4868,4630 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>668</v>
+        <v>1239</v>
       </c>
       <c r="B76" t="s">
-        <v>699</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B77" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>670</v>
+        <v>1241</v>
       </c>
       <c r="B78" t="s">
-        <v>701</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B79" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>672</v>
+        <v>1243</v>
       </c>
       <c r="B80" t="s">
-        <v>703</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="B81" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>674</v>
+        <v>1245</v>
       </c>
       <c r="B82" t="s">
-        <v>705</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>875</v>
+        <v>671</v>
       </c>
       <c r="B83" t="s">
-        <v>876</v>
+        <v>702</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>321</v>
+        <v>1247</v>
       </c>
       <c r="B84" t="s">
-        <v>375</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>194</v>
+        <v>672</v>
       </c>
       <c r="B85" t="s">
-        <v>376</v>
+        <v>703</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>21</v>
+        <v>1249</v>
       </c>
       <c r="B86" t="s">
-        <v>22</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>19</v>
+        <v>673</v>
       </c>
       <c r="B87" t="s">
-        <v>20</v>
+        <v>704</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>196</v>
+        <v>1250</v>
       </c>
       <c r="B88" t="s">
-        <v>377</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>287</v>
+        <v>674</v>
       </c>
       <c r="B89" t="s">
-        <v>378</v>
+        <v>705</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>286</v>
+        <v>1251</v>
       </c>
       <c r="B90" t="s">
-        <v>379</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>337</v>
+        <v>875</v>
       </c>
       <c r="B91" t="s">
-        <v>380</v>
+        <v>876</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>899</v>
+        <v>321</v>
       </c>
       <c r="B92" t="s">
-        <v>900</v>
+        <v>375</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>305</v>
+        <v>194</v>
       </c>
       <c r="B93" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>323</v>
+        <v>21</v>
       </c>
       <c r="B94" t="s">
-        <v>382</v>
+        <v>22</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>1159</v>
+        <v>19</v>
       </c>
       <c r="B95" t="s">
-        <v>1160</v>
+        <v>20</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>276</v>
+        <v>196</v>
       </c>
       <c r="B96" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>333</v>
+        <v>287</v>
       </c>
       <c r="B97" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>42</v>
+        <v>286</v>
       </c>
       <c r="B98" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>41</v>
+        <v>337</v>
       </c>
       <c r="B99" t="s">
-        <v>1139</v>
+        <v>380</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>649</v>
+        <v>899</v>
       </c>
       <c r="B100" t="s">
-        <v>706</v>
+        <v>900</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>217</v>
+        <v>305</v>
       </c>
       <c r="B101" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>288</v>
+        <v>323</v>
       </c>
       <c r="B102" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>218</v>
+        <v>1159</v>
       </c>
       <c r="B103" t="s">
-        <v>388</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="B104" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>199</v>
+        <v>333</v>
       </c>
       <c r="B105" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>648</v>
+        <v>42</v>
       </c>
       <c r="B106" t="s">
-        <v>707</v>
+        <v>385</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>112</v>
+        <v>41</v>
       </c>
       <c r="B107" t="s">
-        <v>391</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>83</v>
+        <v>649</v>
       </c>
       <c r="B108" t="s">
-        <v>392</v>
+        <v>706</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>115</v>
+        <v>217</v>
       </c>
       <c r="B109" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>1176</v>
+        <v>288</v>
       </c>
       <c r="B110" t="s">
-        <v>1177</v>
+        <v>387</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>879</v>
+        <v>218</v>
       </c>
       <c r="B111" t="s">
-        <v>880</v>
+        <v>388</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>807</v>
+        <v>296</v>
       </c>
       <c r="B112" t="s">
-        <v>808</v>
+        <v>389</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>152</v>
+        <v>199</v>
       </c>
       <c r="B113" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>124</v>
+        <v>648</v>
       </c>
       <c r="B114" t="s">
-        <v>396</v>
+        <v>707</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="B115" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>155</v>
+        <v>83</v>
       </c>
       <c r="B116" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>967</v>
+        <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>968</v>
+        <v>393</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>84</v>
+        <v>1176</v>
       </c>
       <c r="B118" t="s">
-        <v>398</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>965</v>
+        <v>879</v>
       </c>
       <c r="B119" t="s">
-        <v>966</v>
+        <v>880</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>103</v>
+        <v>807</v>
       </c>
       <c r="B120" t="s">
-        <v>399</v>
+        <v>808</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>198</v>
+        <v>152</v>
       </c>
       <c r="B121" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>314</v>
+        <v>124</v>
       </c>
       <c r="B122" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="B123" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B124" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>101</v>
+        <v>967</v>
       </c>
       <c r="B125" t="s">
-        <v>404</v>
+        <v>968</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="B126" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>1046</v>
+        <v>965</v>
       </c>
       <c r="B127" t="s">
-        <v>1047</v>
+        <v>966</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>930</v>
+        <v>103</v>
       </c>
       <c r="B128" t="s">
-        <v>931</v>
+        <v>399</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>928</v>
+        <v>198</v>
       </c>
       <c r="B129" t="s">
-        <v>929</v>
+        <v>400</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>162</v>
+        <v>314</v>
       </c>
       <c r="B130" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>1153</v>
+        <v>104</v>
       </c>
       <c r="B131" t="s">
-        <v>1154</v>
+        <v>402</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>837</v>
+        <v>163</v>
       </c>
       <c r="B132" t="s">
-        <v>838</v>
+        <v>403</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>839</v>
+        <v>101</v>
       </c>
       <c r="B133" t="s">
-        <v>840</v>
+        <v>404</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>1084</v>
+        <v>102</v>
       </c>
       <c r="B134" t="s">
-        <v>1085</v>
+        <v>405</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>665</v>
+        <v>1046</v>
       </c>
       <c r="B135" t="s">
-        <v>708</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>646</v>
+        <v>930</v>
       </c>
       <c r="B136" t="s">
-        <v>709</v>
+        <v>931</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>940</v>
+        <v>928</v>
       </c>
       <c r="B137" t="s">
-        <v>941</v>
+        <v>929</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>683</v>
+        <v>162</v>
       </c>
       <c r="B138" t="s">
-        <v>710</v>
+        <v>406</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>684</v>
+        <v>1153</v>
       </c>
       <c r="B139" t="s">
-        <v>711</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>685</v>
+        <v>837</v>
       </c>
       <c r="B140" t="s">
-        <v>712</v>
+        <v>838</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>675</v>
+        <v>839</v>
       </c>
       <c r="B141" t="s">
-        <v>713</v>
+        <v>840</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>676</v>
+        <v>1084</v>
       </c>
       <c r="B142" t="s">
-        <v>714</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="B143" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>678</v>
+        <v>646</v>
       </c>
       <c r="B144" t="s">
-        <v>716</v>
+        <v>709</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>679</v>
+        <v>940</v>
       </c>
       <c r="B145" t="s">
-        <v>717</v>
+        <v>941</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>680</v>
+        <v>1255</v>
       </c>
       <c r="B146" t="s">
-        <v>718</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>681</v>
+        <v>1264</v>
       </c>
       <c r="B147" t="s">
-        <v>719</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B148" t="s">
-        <v>720</v>
+        <v>710</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>175</v>
+        <v>1265</v>
       </c>
       <c r="B149" t="s">
-        <v>407</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>211</v>
+        <v>684</v>
       </c>
       <c r="B150" t="s">
-        <v>408</v>
+        <v>711</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>213</v>
+        <v>1266</v>
       </c>
       <c r="B151" t="s">
-        <v>409</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>1209</v>
+        <v>685</v>
       </c>
       <c r="B152" t="s">
-        <v>410</v>
+        <v>712</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>149</v>
+        <v>1256</v>
       </c>
       <c r="B153" t="s">
-        <v>1212</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>247</v>
+        <v>675</v>
       </c>
       <c r="B154" t="s">
-        <v>411</v>
+        <v>713</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>245</v>
+        <v>1257</v>
       </c>
       <c r="B155" t="s">
-        <v>1138</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>336</v>
+        <v>676</v>
       </c>
       <c r="B156" t="s">
-        <v>412</v>
+        <v>714</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>650</v>
+        <v>1258</v>
       </c>
       <c r="B157" t="s">
-        <v>721</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>91</v>
+        <v>677</v>
       </c>
       <c r="B158" t="s">
-        <v>413</v>
+        <v>715</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>266</v>
+        <v>1259</v>
       </c>
       <c r="B159" t="s">
-        <v>414</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>1096</v>
+        <v>678</v>
       </c>
       <c r="B160" t="s">
-        <v>1097</v>
+        <v>716</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>799</v>
+        <v>1260</v>
       </c>
       <c r="B161" t="s">
-        <v>800</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>1168</v>
+        <v>679</v>
       </c>
       <c r="B162" t="s">
-        <v>1169</v>
+        <v>717</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>295</v>
+        <v>1261</v>
       </c>
       <c r="B163" t="s">
-        <v>415</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>1086</v>
+        <v>680</v>
       </c>
       <c r="B164" t="s">
-        <v>1087</v>
+        <v>718</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>1092</v>
+        <v>1262</v>
       </c>
       <c r="B165" t="s">
-        <v>1093</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>151</v>
+        <v>681</v>
       </c>
       <c r="B166" t="s">
-        <v>416</v>
+        <v>719</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>961</v>
+        <v>1263</v>
       </c>
       <c r="B167" t="s">
-        <v>962</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>813</v>
+        <v>682</v>
       </c>
       <c r="B168" t="s">
-        <v>814</v>
+        <v>720</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>932</v>
+        <v>175</v>
       </c>
       <c r="B169" t="s">
-        <v>933</v>
+        <v>407</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>833</v>
+        <v>211</v>
       </c>
       <c r="B170" t="s">
-        <v>834</v>
+        <v>408</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>793</v>
+        <v>213</v>
       </c>
       <c r="B171" t="s">
-        <v>794</v>
+        <v>409</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>754</v>
+        <v>1209</v>
       </c>
       <c r="B172" t="s">
-        <v>755</v>
+        <v>410</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>100</v>
+        <v>149</v>
       </c>
       <c r="B173" t="s">
-        <v>417</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>1042</v>
+        <v>247</v>
       </c>
       <c r="B174" t="s">
-        <v>1043</v>
+        <v>411</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>154</v>
+        <v>245</v>
       </c>
       <c r="B175" t="s">
-        <v>418</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>157</v>
+        <v>336</v>
       </c>
       <c r="B176" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>24</v>
+        <v>650</v>
       </c>
       <c r="B177" t="s">
-        <v>1137</v>
+        <v>721</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>1164</v>
+        <v>91</v>
       </c>
       <c r="B178" t="s">
-        <v>1165</v>
+        <v>413</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>1076</v>
+        <v>266</v>
       </c>
       <c r="B179" t="s">
-        <v>1077</v>
+        <v>414</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>819</v>
+        <v>1096</v>
       </c>
       <c r="B180" t="s">
-        <v>820</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>130</v>
+        <v>799</v>
       </c>
       <c r="B181" t="s">
-        <v>420</v>
+        <v>800</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>322</v>
+        <v>1168</v>
       </c>
       <c r="B182" t="s">
-        <v>421</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>867</v>
+        <v>295</v>
       </c>
       <c r="B183" t="s">
-        <v>868</v>
+        <v>415</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>183</v>
+        <v>1086</v>
       </c>
       <c r="B184" t="s">
-        <v>422</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>1155</v>
+        <v>1092</v>
       </c>
       <c r="B185" t="s">
-        <v>1156</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>1157</v>
+        <v>151</v>
       </c>
       <c r="B186" t="s">
-        <v>1158</v>
+        <v>416</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>891</v>
+        <v>961</v>
       </c>
       <c r="B187" t="s">
-        <v>892</v>
+        <v>962</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>32</v>
+        <v>813</v>
       </c>
       <c r="B188" t="s">
-        <v>423</v>
+        <v>814</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>35</v>
+        <v>932</v>
       </c>
       <c r="B189" t="s">
-        <v>424</v>
+        <v>933</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>1233</v>
+        <v>833</v>
       </c>
       <c r="B190" t="s">
-        <v>1234</v>
+        <v>834</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>764</v>
+        <v>793</v>
       </c>
       <c r="B191" t="s">
-        <v>1010</v>
+        <v>794</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>169</v>
+        <v>754</v>
       </c>
       <c r="B192" t="s">
-        <v>425</v>
+        <v>755</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="B193" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>1011</v>
+        <v>1042</v>
       </c>
       <c r="B194" t="s">
-        <v>765</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="B195" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>111</v>
+        <v>157</v>
       </c>
       <c r="B196" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>238</v>
+        <v>24</v>
       </c>
       <c r="B197" t="s">
-        <v>428</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>106</v>
+        <v>1164</v>
       </c>
       <c r="B198" t="s">
-        <v>429</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>109</v>
+        <v>1076</v>
       </c>
       <c r="B199" t="s">
-        <v>430</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>179</v>
+        <v>819</v>
       </c>
       <c r="B200" t="s">
-        <v>431</v>
+        <v>820</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>667</v>
+        <v>130</v>
       </c>
       <c r="B201" t="s">
-        <v>722</v>
+        <v>420</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>97</v>
+        <v>322</v>
       </c>
       <c r="B202" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>110</v>
+        <v>867</v>
       </c>
       <c r="B203" t="s">
-        <v>433</v>
+        <v>868</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>242</v>
+        <v>183</v>
       </c>
       <c r="B204" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>226</v>
+        <v>1155</v>
       </c>
       <c r="B205" t="s">
-        <v>435</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>177</v>
+        <v>1157</v>
       </c>
       <c r="B206" t="s">
-        <v>436</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>182</v>
+        <v>891</v>
       </c>
       <c r="B207" t="s">
-        <v>437</v>
+        <v>892</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>1110</v>
+        <v>32</v>
       </c>
       <c r="B208" t="s">
-        <v>1111</v>
+        <v>423</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>977</v>
+        <v>35</v>
       </c>
       <c r="B209" t="s">
-        <v>978</v>
+        <v>424</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>979</v>
+        <v>1233</v>
       </c>
       <c r="B210" t="s">
-        <v>980</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>1198</v>
+        <v>764</v>
       </c>
       <c r="B211" t="s">
-        <v>1199</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>1201</v>
+        <v>169</v>
       </c>
       <c r="B212" t="s">
-        <v>1202</v>
+        <v>425</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>253</v>
+        <v>170</v>
       </c>
       <c r="B213" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>34</v>
+        <v>1011</v>
       </c>
       <c r="B214" t="s">
-        <v>439</v>
+        <v>765</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>787</v>
+        <v>178</v>
       </c>
       <c r="B215" t="s">
-        <v>788</v>
+        <v>426</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>180</v>
+        <v>111</v>
       </c>
       <c r="B216" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>275</v>
+        <v>238</v>
       </c>
       <c r="B217" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>857</v>
+        <v>106</v>
       </c>
       <c r="B218" t="s">
-        <v>858</v>
+        <v>429</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B219" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="B220" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>1221</v>
+        <v>667</v>
       </c>
       <c r="B221" t="s">
-        <v>1222</v>
+        <v>722</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>1056</v>
+        <v>97</v>
       </c>
       <c r="B222" t="s">
-        <v>1057</v>
+        <v>432</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B223" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>641</v>
+        <v>242</v>
       </c>
       <c r="B224" t="s">
-        <v>723</v>
+        <v>434</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>815</v>
+        <v>226</v>
       </c>
       <c r="B225" t="s">
-        <v>816</v>
+        <v>435</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>298</v>
+        <v>177</v>
       </c>
       <c r="B226" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>643</v>
+        <v>182</v>
       </c>
       <c r="B227" t="s">
-        <v>724</v>
+        <v>437</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>644</v>
+        <v>1110</v>
       </c>
       <c r="B228" t="s">
-        <v>725</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>1036</v>
+        <v>977</v>
       </c>
       <c r="B229" t="s">
-        <v>1037</v>
+        <v>978</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>90</v>
+        <v>979</v>
       </c>
       <c r="B230" t="s">
-        <v>446</v>
+        <v>980</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>88</v>
+        <v>1198</v>
       </c>
       <c r="B231" t="s">
-        <v>447</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>89</v>
+        <v>1201</v>
       </c>
       <c r="B232" t="s">
-        <v>448</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>1072</v>
+        <v>253</v>
       </c>
       <c r="B233" t="s">
-        <v>1073</v>
+        <v>438</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B234" t="s">
-        <v>1136</v>
+        <v>439</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>5</v>
+        <v>787</v>
       </c>
       <c r="B235" t="s">
-        <v>6</v>
+        <v>788</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>1141</v>
+        <v>180</v>
       </c>
       <c r="B236" t="s">
-        <v>1142</v>
+        <v>440</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>126</v>
+        <v>275</v>
       </c>
       <c r="B237" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>128</v>
+        <v>857</v>
       </c>
       <c r="B238" t="s">
-        <v>450</v>
+        <v>858</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="B239" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>132</v>
+        <v>208</v>
       </c>
       <c r="B240" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>119</v>
+        <v>1221</v>
       </c>
       <c r="B241" t="s">
-        <v>453</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>277</v>
+        <v>1056</v>
       </c>
       <c r="B242" t="s">
-        <v>454</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>1074</v>
+        <v>118</v>
       </c>
       <c r="B243" t="s">
-        <v>1075</v>
+        <v>444</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>9</v>
+        <v>641</v>
       </c>
       <c r="B244" t="s">
-        <v>10</v>
+        <v>723</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>129</v>
+        <v>815</v>
       </c>
       <c r="B245" t="s">
-        <v>455</v>
+        <v>816</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>127</v>
+        <v>298</v>
       </c>
       <c r="B246" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>173</v>
+        <v>643</v>
       </c>
       <c r="B247" t="s">
-        <v>457</v>
+        <v>724</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>262</v>
+        <v>644</v>
       </c>
       <c r="B248" t="s">
-        <v>458</v>
+        <v>725</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>77</v>
+        <v>1036</v>
       </c>
       <c r="B249" t="s">
-        <v>459</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>938</v>
+        <v>90</v>
       </c>
       <c r="B250" t="s">
-        <v>939</v>
+        <v>446</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>1172</v>
+        <v>88</v>
       </c>
       <c r="B251" t="s">
-        <v>1173</v>
+        <v>447</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>168</v>
+        <v>89</v>
       </c>
       <c r="B252" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>167</v>
+        <v>1072</v>
       </c>
       <c r="B253" t="s">
-        <v>461</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>835</v>
+        <v>23</v>
       </c>
       <c r="B254" t="s">
-        <v>836</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>791</v>
+        <v>5</v>
       </c>
       <c r="B255" t="s">
-        <v>792</v>
+        <v>6</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>304</v>
+        <v>1141</v>
       </c>
       <c r="B256" t="s">
-        <v>462</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>758</v>
+        <v>126</v>
       </c>
       <c r="B257" t="s">
-        <v>759</v>
+        <v>449</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>897</v>
+        <v>128</v>
       </c>
       <c r="B258" t="s">
-        <v>898</v>
+        <v>450</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>652</v>
+        <v>131</v>
       </c>
       <c r="B259" t="s">
-        <v>726</v>
+        <v>451</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="B260" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="B261" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>153</v>
+        <v>277</v>
       </c>
       <c r="B262" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>156</v>
+        <v>1074</v>
       </c>
       <c r="B263" t="s">
-        <v>466</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>158</v>
+        <v>9</v>
       </c>
       <c r="B264" t="s">
-        <v>467</v>
+        <v>10</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>251</v>
+        <v>129</v>
       </c>
       <c r="B265" t="s">
-        <v>468</v>
+        <v>455</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>285</v>
+        <v>127</v>
       </c>
       <c r="B266" t="s">
-        <v>469</v>
+        <v>456</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>326</v>
+        <v>173</v>
       </c>
       <c r="B267" t="s">
-        <v>470</v>
+        <v>457</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>327</v>
+        <v>262</v>
       </c>
       <c r="B268" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>229</v>
+        <v>77</v>
       </c>
       <c r="B269" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>55</v>
+        <v>938</v>
       </c>
       <c r="B270" t="s">
-        <v>473</v>
+        <v>939</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>657</v>
+        <v>1172</v>
       </c>
       <c r="B271" t="s">
-        <v>727</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>235</v>
+        <v>168</v>
       </c>
       <c r="B272" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="B273" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>236</v>
+        <v>835</v>
       </c>
       <c r="B274" t="s">
-        <v>476</v>
+        <v>836</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>766</v>
+        <v>791</v>
       </c>
       <c r="B275" t="s">
-        <v>1009</v>
+        <v>792</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>1012</v>
+        <v>304</v>
       </c>
       <c r="B276" t="s">
-        <v>767</v>
+        <v>462</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>164</v>
+        <v>758</v>
       </c>
       <c r="B277" t="s">
-        <v>477</v>
+        <v>759</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>201</v>
+        <v>897</v>
       </c>
       <c r="B278" t="s">
-        <v>478</v>
+        <v>898</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>204</v>
+        <v>652</v>
       </c>
       <c r="B279" t="s">
-        <v>479</v>
+        <v>726</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>313</v>
+        <v>86</v>
       </c>
       <c r="B280" t="s">
-        <v>480</v>
+        <v>463</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>873</v>
+        <v>87</v>
       </c>
       <c r="B281" t="s">
-        <v>874</v>
+        <v>464</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>997</v>
+        <v>153</v>
       </c>
       <c r="B282" t="s">
-        <v>998</v>
+        <v>465</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>258</v>
+        <v>156</v>
       </c>
       <c r="B283" t="s">
-        <v>481</v>
+        <v>466</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>983</v>
+        <v>158</v>
       </c>
       <c r="B284" t="s">
-        <v>984</v>
+        <v>467</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>160</v>
+        <v>251</v>
       </c>
       <c r="B285" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>692</v>
+        <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>728</v>
+        <v>469</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>1166</v>
+        <v>326</v>
       </c>
       <c r="B287" t="s">
-        <v>1167</v>
+        <v>470</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>760</v>
+        <v>327</v>
       </c>
       <c r="B288" t="s">
-        <v>761</v>
+        <v>471</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>895</v>
+        <v>229</v>
       </c>
       <c r="B289" t="s">
-        <v>896</v>
+        <v>472</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>893</v>
+        <v>55</v>
       </c>
       <c r="B290" t="s">
-        <v>894</v>
+        <v>473</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>184</v>
+        <v>657</v>
       </c>
       <c r="B291" t="s">
-        <v>483</v>
+        <v>727</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="B292" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>243</v>
+        <v>57</v>
       </c>
       <c r="B293" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>686</v>
+        <v>236</v>
       </c>
       <c r="B294" t="s">
-        <v>729</v>
+        <v>476</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>687</v>
+        <v>766</v>
       </c>
       <c r="B295" t="s">
-        <v>730</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>688</v>
+        <v>1012</v>
       </c>
       <c r="B296" t="s">
-        <v>731</v>
+        <v>767</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>689</v>
+        <v>164</v>
       </c>
       <c r="B297" t="s">
-        <v>732</v>
+        <v>477</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>690</v>
+        <v>201</v>
       </c>
       <c r="B298" t="s">
-        <v>733</v>
+        <v>478</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>1192</v>
+        <v>204</v>
       </c>
       <c r="B299" t="s">
-        <v>1193</v>
+        <v>479</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>280</v>
+        <v>313</v>
       </c>
       <c r="B300" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>281</v>
+        <v>873</v>
       </c>
       <c r="B301" t="s">
-        <v>487</v>
+        <v>874</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>49</v>
+        <v>997</v>
       </c>
       <c r="B302" t="s">
-        <v>488</v>
+        <v>998</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>53</v>
+        <v>258</v>
       </c>
       <c r="B303" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>136</v>
+        <v>983</v>
       </c>
       <c r="B304" t="s">
-        <v>491</v>
+        <v>984</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
       <c r="B305" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>1190</v>
+        <v>692</v>
       </c>
       <c r="B306" t="s">
-        <v>1191</v>
+        <v>728</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>221</v>
+        <v>1166</v>
       </c>
       <c r="B307" t="s">
-        <v>492</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>1194</v>
+        <v>760</v>
       </c>
       <c r="B308" t="s">
-        <v>1195</v>
+        <v>761</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>15</v>
+        <v>895</v>
       </c>
       <c r="B309" t="s">
-        <v>16</v>
+        <v>896</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>1060</v>
+        <v>893</v>
       </c>
       <c r="B310" t="s">
-        <v>1061</v>
+        <v>894</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>920</v>
+        <v>184</v>
       </c>
       <c r="B311" t="s">
-        <v>921</v>
+        <v>483</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>108</v>
+        <v>244</v>
       </c>
       <c r="B312" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B313" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>328</v>
+        <v>1279</v>
       </c>
       <c r="B314" t="s">
-        <v>495</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>1100</v>
+        <v>686</v>
       </c>
       <c r="B315" t="s">
-        <v>1101</v>
+        <v>729</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>1052</v>
+        <v>1280</v>
       </c>
       <c r="B316" t="s">
-        <v>1053</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>121</v>
+        <v>687</v>
       </c>
       <c r="B317" t="s">
-        <v>496</v>
+        <v>730</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>750</v>
+        <v>1281</v>
       </c>
       <c r="B318" t="s">
-        <v>751</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>781</v>
+        <v>688</v>
       </c>
       <c r="B319" t="s">
-        <v>782</v>
+        <v>731</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>134</v>
+        <v>1282</v>
       </c>
       <c r="B320" t="s">
-        <v>497</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>63</v>
+        <v>689</v>
       </c>
       <c r="B321" t="s">
-        <v>498</v>
+        <v>732</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>224</v>
+        <v>1283</v>
       </c>
       <c r="B322" t="s">
-        <v>499</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>25</v>
+        <v>690</v>
       </c>
       <c r="B323" t="s">
-        <v>500</v>
+        <v>733</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>26</v>
+        <v>1192</v>
       </c>
       <c r="B324" t="s">
-        <v>501</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>207</v>
+        <v>280</v>
       </c>
       <c r="B325" t="s">
-        <v>1133</v>
+        <v>486</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>960</v>
+        <v>281</v>
       </c>
       <c r="B326" t="s">
-        <v>1134</v>
+        <v>487</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>1113</v>
+        <v>49</v>
       </c>
       <c r="B327" t="s">
-        <v>1114</v>
+        <v>488</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>206</v>
+        <v>53</v>
       </c>
       <c r="B328" t="s">
-        <v>1135</v>
+        <v>489</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>202</v>
+        <v>136</v>
       </c>
       <c r="B329" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>205</v>
+        <v>72</v>
       </c>
       <c r="B330" t="s">
-        <v>503</v>
+        <v>490</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>145</v>
+        <v>1190</v>
       </c>
       <c r="B331" t="s">
-        <v>504</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>663</v>
+        <v>221</v>
       </c>
       <c r="B332" t="s">
-        <v>734</v>
+        <v>492</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>171</v>
+        <v>1194</v>
       </c>
       <c r="B333" t="s">
-        <v>505</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>1088</v>
+        <v>15</v>
       </c>
       <c r="B334" t="s">
-        <v>1089</v>
+        <v>16</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>263</v>
+        <v>1060</v>
       </c>
       <c r="B335" t="s">
-        <v>506</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>1090</v>
+        <v>920</v>
       </c>
       <c r="B336" t="s">
-        <v>1091</v>
+        <v>921</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="B337" t="s">
-        <v>507</v>
+        <v>493</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>65</v>
+        <v>241</v>
       </c>
       <c r="B338" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>191</v>
+        <v>328</v>
       </c>
       <c r="B339" t="s">
-        <v>509</v>
+        <v>495</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>123</v>
+        <v>1100</v>
       </c>
       <c r="B340" t="s">
-        <v>510</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>192</v>
+        <v>1052</v>
       </c>
       <c r="B341" t="s">
-        <v>511</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>231</v>
+        <v>121</v>
       </c>
       <c r="B342" t="s">
-        <v>512</v>
+        <v>496</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>233</v>
+        <v>750</v>
       </c>
       <c r="B343" t="s">
-        <v>513</v>
+        <v>751</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>1200</v>
+        <v>781</v>
       </c>
       <c r="B344" t="s">
-        <v>514</v>
+        <v>782</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="B345" t="s">
-        <v>514</v>
+        <v>497</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="B346" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>37</v>
+        <v>224</v>
       </c>
       <c r="B347" t="s">
-        <v>516</v>
+        <v>499</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="B348" t="s">
-        <v>517</v>
+        <v>500</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>306</v>
+        <v>26</v>
       </c>
       <c r="B349" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="B350" t="s">
-        <v>519</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>315</v>
+        <v>960</v>
       </c>
       <c r="B351" t="s">
-        <v>520</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>278</v>
+        <v>1113</v>
       </c>
       <c r="B352" t="s">
-        <v>521</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>279</v>
+        <v>206</v>
       </c>
       <c r="B353" t="s">
-        <v>522</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>831</v>
+        <v>202</v>
       </c>
       <c r="B354" t="s">
-        <v>832</v>
+        <v>502</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>48</v>
+        <v>205</v>
       </c>
       <c r="B355" t="s">
-        <v>523</v>
+        <v>503</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B356" t="s">
-        <v>524</v>
+        <v>504</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>52</v>
+        <v>663</v>
       </c>
       <c r="B357" t="s">
-        <v>525</v>
+        <v>734</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>223</v>
+        <v>171</v>
       </c>
       <c r="B358" t="s">
-        <v>526</v>
+        <v>505</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
       <c r="B359" t="s">
-        <v>1095</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>1109</v>
+        <v>263</v>
       </c>
       <c r="B360" t="s">
-        <v>1112</v>
+        <v>506</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>1050</v>
+        <v>1090</v>
       </c>
       <c r="B361" t="s">
-        <v>1051</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="B362" t="s">
-        <v>527</v>
+        <v>507</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>248</v>
+        <v>65</v>
       </c>
       <c r="B363" t="s">
-        <v>528</v>
+        <v>508</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>249</v>
+        <v>191</v>
       </c>
       <c r="B364" t="s">
-        <v>529</v>
+        <v>509</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="B365" t="s">
-        <v>530</v>
+        <v>510</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>1064</v>
+        <v>192</v>
       </c>
       <c r="B366" t="s">
-        <v>1065</v>
+        <v>511</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="B367" t="s">
-        <v>531</v>
+        <v>512</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>1225</v>
+        <v>233</v>
       </c>
       <c r="B368" t="s">
-        <v>1226</v>
+        <v>513</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>916</v>
+        <v>1200</v>
       </c>
       <c r="B369" t="s">
-        <v>917</v>
+        <v>514</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>914</v>
+        <v>31</v>
       </c>
       <c r="B370" t="s">
-        <v>915</v>
+        <v>514</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>918</v>
+        <v>30</v>
       </c>
       <c r="B371" t="s">
-        <v>919</v>
+        <v>515</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>330</v>
+        <v>37</v>
       </c>
       <c r="B372" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>1066</v>
+        <v>71</v>
       </c>
       <c r="B373" t="s">
-        <v>1067</v>
+        <v>517</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>995</v>
+        <v>306</v>
       </c>
       <c r="B374" t="s">
-        <v>996</v>
+        <v>518</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>991</v>
+        <v>222</v>
       </c>
       <c r="B375" t="s">
-        <v>992</v>
+        <v>519</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>993</v>
+        <v>315</v>
       </c>
       <c r="B376" t="s">
-        <v>994</v>
+        <v>520</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>82</v>
+        <v>278</v>
       </c>
       <c r="B377" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>772</v>
+        <v>279</v>
       </c>
       <c r="B378" t="s">
-        <v>773</v>
+        <v>522</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>197</v>
+        <v>831</v>
       </c>
       <c r="B379" t="s">
-        <v>534</v>
+        <v>832</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>654</v>
+        <v>48</v>
       </c>
       <c r="B380" t="s">
-        <v>735</v>
+        <v>523</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>821</v>
+        <v>146</v>
       </c>
       <c r="B381" t="s">
-        <v>822</v>
+        <v>524</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>1068</v>
+        <v>52</v>
       </c>
       <c r="B382" t="s">
-        <v>1069</v>
+        <v>525</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>3</v>
+        <v>223</v>
       </c>
       <c r="B383" t="s">
-        <v>4</v>
+        <v>526</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>958</v>
+        <v>1094</v>
       </c>
       <c r="B384" t="s">
-        <v>4</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>959</v>
+        <v>1109</v>
       </c>
       <c r="B385" t="s">
-        <v>4</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>664</v>
+        <v>1050</v>
       </c>
       <c r="B386" t="s">
-        <v>736</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>770</v>
+        <v>96</v>
       </c>
       <c r="B387" t="s">
-        <v>771</v>
+        <v>527</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>85</v>
+        <v>248</v>
       </c>
       <c r="B388" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>1062</v>
+        <v>249</v>
       </c>
       <c r="B389" t="s">
-        <v>1063</v>
+        <v>529</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>829</v>
+        <v>94</v>
       </c>
       <c r="B390" t="s">
-        <v>830</v>
+        <v>530</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>809</v>
+        <v>1064</v>
       </c>
       <c r="B391" t="s">
-        <v>810</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="B392" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>827</v>
+        <v>1225</v>
       </c>
       <c r="B393" t="s">
-        <v>828</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>934</v>
+        <v>916</v>
       </c>
       <c r="B394" t="s">
-        <v>1130</v>
+        <v>917</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>863</v>
+        <v>914</v>
       </c>
       <c r="B395" t="s">
-        <v>864</v>
+        <v>915</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>1044</v>
+        <v>918</v>
       </c>
       <c r="B396" t="s">
-        <v>1045</v>
+        <v>919</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>798</v>
+        <v>330</v>
       </c>
       <c r="B397" t="s">
-        <v>1131</v>
+        <v>532</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>797</v>
+        <v>1066</v>
       </c>
       <c r="B398" t="s">
-        <v>1132</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>13</v>
+        <v>995</v>
       </c>
       <c r="B399" t="s">
-        <v>14</v>
+        <v>996</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>817</v>
+        <v>991</v>
       </c>
       <c r="B400" t="s">
-        <v>818</v>
+        <v>992</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>1235</v>
+        <v>993</v>
       </c>
       <c r="B401" t="s">
-        <v>1236</v>
+        <v>994</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="B402" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>811</v>
+        <v>772</v>
       </c>
       <c r="B403" t="s">
-        <v>812</v>
+        <v>773</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>320</v>
+        <v>197</v>
       </c>
       <c r="B404" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B405" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>855</v>
+        <v>821</v>
       </c>
       <c r="B406" t="s">
-        <v>856</v>
+        <v>822</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>658</v>
+        <v>1068</v>
       </c>
       <c r="B407" t="s">
-        <v>738</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>653</v>
+        <v>3</v>
       </c>
       <c r="B408" t="s">
-        <v>739</v>
+        <v>4</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>1207</v>
+        <v>958</v>
       </c>
       <c r="B409" t="s">
-        <v>1208</v>
+        <v>4</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>256</v>
+        <v>959</v>
       </c>
       <c r="B410" t="s">
-        <v>539</v>
+        <v>4</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>260</v>
+        <v>664</v>
       </c>
       <c r="B411" t="s">
-        <v>540</v>
+        <v>736</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>261</v>
+        <v>770</v>
       </c>
       <c r="B412" t="s">
-        <v>541</v>
+        <v>771</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>188</v>
+        <v>85</v>
       </c>
       <c r="B413" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>190</v>
+        <v>1062</v>
       </c>
       <c r="B414" t="s">
-        <v>543</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>936</v>
+        <v>829</v>
       </c>
       <c r="B415" t="s">
-        <v>937</v>
+        <v>830</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>1031</v>
+        <v>809</v>
       </c>
       <c r="B416" t="s">
-        <v>1032</v>
+        <v>810</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>1223</v>
+        <v>187</v>
       </c>
       <c r="B417" t="s">
-        <v>1224</v>
+        <v>536</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>209</v>
+        <v>827</v>
       </c>
       <c r="B418" t="s">
-        <v>544</v>
+        <v>828</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>851</v>
+        <v>934</v>
       </c>
       <c r="B419" t="s">
-        <v>852</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>143</v>
+        <v>863</v>
       </c>
       <c r="B420" t="s">
-        <v>545</v>
+        <v>864</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>140</v>
+        <v>1044</v>
       </c>
       <c r="B421" t="s">
-        <v>546</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>1203</v>
+        <v>798</v>
       </c>
       <c r="B422" t="s">
-        <v>1204</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>254</v>
+        <v>797</v>
       </c>
       <c r="B423" t="s">
-        <v>547</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>331</v>
+        <v>13</v>
       </c>
       <c r="B424" t="s">
-        <v>548</v>
+        <v>14</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>210</v>
+        <v>817</v>
       </c>
       <c r="B425" t="s">
-        <v>549</v>
+        <v>818</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>234</v>
+        <v>1235</v>
       </c>
       <c r="B426" t="s">
-        <v>550</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>73</v>
+        <v>186</v>
       </c>
       <c r="B427" t="s">
-        <v>551</v>
+        <v>537</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>342</v>
+        <v>811</v>
       </c>
       <c r="B428" t="s">
-        <v>552</v>
+        <v>812</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B429" t="s">
-        <v>553</v>
+        <v>538</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>843</v>
+        <v>656</v>
       </c>
       <c r="B430" t="s">
-        <v>844</v>
+        <v>737</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>845</v>
+        <v>855</v>
       </c>
       <c r="B431" t="s">
-        <v>846</v>
+        <v>856</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>220</v>
+        <v>658</v>
       </c>
       <c r="B432" t="s">
-        <v>554</v>
+        <v>738</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>909</v>
+        <v>653</v>
       </c>
       <c r="B433" t="s">
-        <v>910</v>
+        <v>739</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>963</v>
+        <v>1207</v>
       </c>
       <c r="B434" t="s">
-        <v>964</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>1188</v>
+        <v>256</v>
       </c>
       <c r="B435" t="s">
-        <v>1189</v>
+        <v>539</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>227</v>
+        <v>260</v>
       </c>
       <c r="B436" t="s">
-        <v>555</v>
+        <v>540</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>334</v>
+        <v>261</v>
       </c>
       <c r="B437" t="s">
-        <v>1161</v>
+        <v>541</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>971</v>
+        <v>188</v>
       </c>
       <c r="B438" t="s">
-        <v>972</v>
+        <v>542</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>778</v>
+        <v>190</v>
       </c>
       <c r="B439" t="s">
-        <v>779</v>
+        <v>543</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>294</v>
+        <v>936</v>
       </c>
       <c r="B440" t="s">
-        <v>556</v>
+        <v>937</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>952</v>
+        <v>1031</v>
       </c>
       <c r="B441" t="s">
-        <v>953</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>339</v>
+        <v>1223</v>
       </c>
       <c r="B442" t="s">
-        <v>557</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>780</v>
+        <v>209</v>
       </c>
       <c r="B443" t="s">
-        <v>779</v>
+        <v>544</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>340</v>
+        <v>851</v>
       </c>
       <c r="B444" t="s">
-        <v>558</v>
+        <v>852</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>341</v>
+        <v>143</v>
       </c>
       <c r="B445" t="s">
-        <v>559</v>
+        <v>545</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>645</v>
+        <v>140</v>
       </c>
       <c r="B446" t="s">
-        <v>740</v>
+        <v>546</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>39</v>
+        <v>1203</v>
       </c>
       <c r="B447" t="s">
-        <v>560</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>38</v>
+        <v>254</v>
       </c>
       <c r="B448" t="s">
-        <v>1129</v>
+        <v>547</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="B449" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>107</v>
+        <v>210</v>
       </c>
       <c r="B450" t="s">
-        <v>562</v>
+        <v>549</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>1029</v>
+        <v>234</v>
       </c>
       <c r="B451" t="s">
-        <v>1030</v>
+        <v>550</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>903</v>
+        <v>73</v>
       </c>
       <c r="B452" t="s">
-        <v>904</v>
+        <v>551</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>117</v>
+        <v>342</v>
       </c>
       <c r="B453" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>1025</v>
+        <v>308</v>
       </c>
       <c r="B454" t="s">
-        <v>1026</v>
+        <v>553</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>98</v>
+        <v>843</v>
       </c>
       <c r="B455" t="s">
-        <v>564</v>
+        <v>844</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>99</v>
+        <v>845</v>
       </c>
       <c r="B456" t="s">
-        <v>565</v>
+        <v>846</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>666</v>
+        <v>220</v>
       </c>
       <c r="B457" t="s">
-        <v>741</v>
+        <v>554</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>1107</v>
+        <v>909</v>
       </c>
       <c r="B458" t="s">
-        <v>1024</v>
+        <v>910</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>823</v>
+        <v>963</v>
       </c>
       <c r="B459" t="s">
-        <v>824</v>
+        <v>964</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>113</v>
+        <v>1188</v>
       </c>
       <c r="B460" t="s">
-        <v>566</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>889</v>
+        <v>227</v>
       </c>
       <c r="B461" t="s">
-        <v>890</v>
+        <v>555</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>45</v>
+        <v>334</v>
       </c>
       <c r="B462" t="s">
-        <v>1128</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>290</v>
+        <v>971</v>
       </c>
       <c r="B463" t="s">
-        <v>567</v>
+        <v>972</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>299</v>
+        <v>778</v>
       </c>
       <c r="B464" t="s">
-        <v>568</v>
+        <v>779</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>47</v>
+        <v>294</v>
       </c>
       <c r="B465" t="s">
-        <v>569</v>
+        <v>556</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>847</v>
+        <v>952</v>
       </c>
       <c r="B466" t="s">
-        <v>848</v>
+        <v>953</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>51</v>
+        <v>339</v>
       </c>
       <c r="B467" t="s">
-        <v>570</v>
+        <v>557</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>871</v>
+        <v>780</v>
       </c>
       <c r="B468" t="s">
-        <v>872</v>
+        <v>779</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>114</v>
+        <v>340</v>
       </c>
       <c r="B469" t="s">
-        <v>571</v>
+        <v>558</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>853</v>
+        <v>341</v>
       </c>
       <c r="B470" t="s">
-        <v>854</v>
+        <v>559</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>144</v>
+        <v>645</v>
       </c>
       <c r="B471" t="s">
-        <v>572</v>
+        <v>740</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>1080</v>
+        <v>39</v>
       </c>
       <c r="B472" t="s">
-        <v>1081</v>
+        <v>560</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>176</v>
+        <v>38</v>
       </c>
       <c r="B473" t="s">
-        <v>573</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>316</v>
+        <v>343</v>
       </c>
       <c r="B474" t="s">
-        <v>574</v>
+        <v>561</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="B475" t="s">
-        <v>575</v>
+        <v>562</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>1104</v>
+        <v>1029</v>
       </c>
       <c r="B476" t="s">
-        <v>1105</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>1018</v>
+        <v>903</v>
       </c>
       <c r="B477" t="s">
-        <v>1019</v>
+        <v>904</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>1231</v>
+        <v>117</v>
       </c>
       <c r="B478" t="s">
-        <v>1232</v>
+        <v>563</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>293</v>
+        <v>1025</v>
       </c>
       <c r="B479" t="s">
-        <v>576</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>981</v>
+        <v>98</v>
       </c>
       <c r="B480" t="s">
-        <v>982</v>
+        <v>564</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>301</v>
+        <v>99</v>
       </c>
       <c r="B481" t="s">
-        <v>577</v>
+        <v>565</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>1003</v>
+        <v>666</v>
       </c>
       <c r="B482" t="s">
-        <v>1004</v>
+        <v>741</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>1007</v>
+        <v>1107</v>
       </c>
       <c r="B483" t="s">
-        <v>1008</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>75</v>
+        <v>823</v>
       </c>
       <c r="B484" t="s">
-        <v>578</v>
+        <v>824</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="B485" t="s">
-        <v>579</v>
+        <v>566</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>78</v>
+        <v>889</v>
       </c>
       <c r="B486" t="s">
-        <v>580</v>
+        <v>890</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>329</v>
+        <v>45</v>
       </c>
       <c r="B487" t="s">
-        <v>581</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>752</v>
+        <v>290</v>
       </c>
       <c r="B488" t="s">
-        <v>753</v>
+        <v>567</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>805</v>
+        <v>299</v>
       </c>
       <c r="B489" t="s">
-        <v>806</v>
+        <v>568</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>135</v>
+        <v>47</v>
       </c>
       <c r="B490" t="s">
-        <v>582</v>
+        <v>569</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>1186</v>
+        <v>847</v>
       </c>
       <c r="B491" t="s">
-        <v>1187</v>
+        <v>848</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>1038</v>
+        <v>51</v>
       </c>
       <c r="B492" t="s">
-        <v>1039</v>
+        <v>570</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>215</v>
+        <v>871</v>
       </c>
       <c r="B493" t="s">
-        <v>583</v>
+        <v>872</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>935</v>
+        <v>114</v>
       </c>
       <c r="B494" t="s">
-        <v>1145</v>
+        <v>571</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>216</v>
+        <v>853</v>
       </c>
       <c r="B495" t="s">
-        <v>1126</v>
+        <v>854</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>317</v>
+        <v>144</v>
       </c>
       <c r="B496" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="B497" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="B498" t="s">
-        <v>1127</v>
+        <v>573</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>999</v>
+        <v>316</v>
       </c>
       <c r="B499" t="s">
-        <v>1000</v>
+        <v>574</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>1001</v>
+        <v>29</v>
       </c>
       <c r="B500" t="s">
-        <v>1002</v>
+        <v>575</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>225</v>
+        <v>1104</v>
       </c>
       <c r="B501" t="s">
-        <v>585</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>948</v>
+        <v>1018</v>
       </c>
       <c r="B502" t="s">
-        <v>949</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>1098</v>
+        <v>1231</v>
       </c>
       <c r="B503" t="s">
-        <v>1099</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>1048</v>
+        <v>293</v>
       </c>
       <c r="B504" t="s">
-        <v>1049</v>
+        <v>576</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>93</v>
+        <v>981</v>
       </c>
       <c r="B505" t="s">
-        <v>586</v>
+        <v>982</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>120</v>
+        <v>301</v>
       </c>
       <c r="B506" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>783</v>
+        <v>1003</v>
       </c>
       <c r="B507" t="s">
-        <v>784</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>133</v>
+        <v>1007</v>
       </c>
       <c r="B508" t="s">
-        <v>588</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B509" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B510" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>825</v>
+        <v>78</v>
       </c>
       <c r="B511" t="s">
-        <v>826</v>
+        <v>580</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>950</v>
+        <v>329</v>
       </c>
       <c r="B512" t="s">
-        <v>951</v>
+        <v>581</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>1215</v>
+        <v>752</v>
       </c>
       <c r="B513" t="s">
-        <v>1216</v>
+        <v>753</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>79</v>
+        <v>805</v>
       </c>
       <c r="B514" t="s">
-        <v>591</v>
+        <v>806</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>64</v>
+        <v>135</v>
       </c>
       <c r="B515" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>122</v>
+        <v>1186</v>
       </c>
       <c r="B516" t="s">
-        <v>593</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>1184</v>
+        <v>1038</v>
       </c>
       <c r="B517" t="s">
-        <v>1185</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="B518" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>801</v>
+        <v>935</v>
       </c>
       <c r="B519" t="s">
-        <v>802</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>691</v>
+        <v>216</v>
       </c>
       <c r="B520" t="s">
-        <v>742</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>1151</v>
+        <v>317</v>
       </c>
       <c r="B521" t="s">
-        <v>1152</v>
+        <v>584</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>1149</v>
+        <v>1082</v>
       </c>
       <c r="B522" t="s">
-        <v>1150</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>284</v>
+        <v>214</v>
       </c>
       <c r="B523" t="s">
-        <v>595</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>973</v>
+        <v>999</v>
       </c>
       <c r="B524" t="s">
-        <v>974</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>1219</v>
+        <v>1001</v>
       </c>
       <c r="B525" t="s">
-        <v>1220</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>841</v>
+        <v>225</v>
       </c>
       <c r="B526" t="s">
-        <v>842</v>
+        <v>585</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>283</v>
+        <v>948</v>
       </c>
       <c r="B527" t="s">
-        <v>596</v>
+        <v>949</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>883</v>
+        <v>1098</v>
       </c>
       <c r="B528" t="s">
-        <v>884</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>1180</v>
+        <v>1048</v>
       </c>
       <c r="B529" t="s">
-        <v>1181</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>756</v>
+        <v>93</v>
       </c>
       <c r="B530" t="s">
-        <v>757</v>
+        <v>586</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>1078</v>
+        <v>120</v>
       </c>
       <c r="B531" t="s">
-        <v>1079</v>
+        <v>587</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>67</v>
+        <v>783</v>
       </c>
       <c r="B532" t="s">
-        <v>597</v>
+        <v>784</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>68</v>
+        <v>133</v>
       </c>
       <c r="B533" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="B534" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>289</v>
+        <v>66</v>
       </c>
       <c r="B535" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>297</v>
+        <v>825</v>
       </c>
       <c r="B536" t="s">
-        <v>601</v>
+        <v>826</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>264</v>
+        <v>950</v>
       </c>
       <c r="B537" t="s">
-        <v>602</v>
+        <v>951</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>193</v>
+        <v>1215</v>
       </c>
       <c r="B538" t="s">
-        <v>603</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>901</v>
+        <v>79</v>
       </c>
       <c r="B539" t="s">
-        <v>902</v>
+        <v>591</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="B540" t="s">
-        <v>1125</v>
+        <v>592</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>1070</v>
+        <v>122</v>
       </c>
       <c r="B541" t="s">
-        <v>1071</v>
+        <v>593</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>324</v>
+        <v>1184</v>
       </c>
       <c r="B542" t="s">
-        <v>604</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>325</v>
+        <v>181</v>
       </c>
       <c r="B543" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>849</v>
+        <v>801</v>
       </c>
       <c r="B544" t="s">
-        <v>850</v>
+        <v>802</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>887</v>
+        <v>1289</v>
       </c>
       <c r="B545" t="s">
-        <v>888</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>1237</v>
+        <v>691</v>
       </c>
       <c r="B546" t="s">
-        <v>1238</v>
+        <v>742</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>869</v>
+        <v>1290</v>
       </c>
       <c r="B547" t="s">
-        <v>870</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>33</v>
+        <v>1291</v>
       </c>
       <c r="B548" t="s">
-        <v>606</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>36</v>
+        <v>1292</v>
       </c>
       <c r="B549" t="s">
-        <v>607</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>1143</v>
+        <v>1293</v>
       </c>
       <c r="B550" t="s">
-        <v>1144</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>309</v>
+        <v>1151</v>
       </c>
       <c r="B551" t="s">
-        <v>608</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>257</v>
+        <v>1149</v>
       </c>
       <c r="B552" t="s">
-        <v>609</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="B553" t="s">
-        <v>610</v>
+        <v>595</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>228</v>
+        <v>973</v>
       </c>
       <c r="B554" t="s">
-        <v>611</v>
+        <v>974</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>17</v>
+        <v>1219</v>
       </c>
       <c r="B555" t="s">
-        <v>18</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>655</v>
+        <v>841</v>
       </c>
       <c r="B556" t="s">
-        <v>743</v>
+        <v>842</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>785</v>
+        <v>283</v>
       </c>
       <c r="B557" t="s">
-        <v>786</v>
+        <v>596</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>142</v>
+        <v>883</v>
       </c>
       <c r="B558" t="s">
-        <v>612</v>
+        <v>884</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="B559" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>956</v>
+        <v>756</v>
       </c>
       <c r="B560" t="s">
-        <v>957</v>
+        <v>757</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>54</v>
+        <v>1078</v>
       </c>
       <c r="B561" t="s">
-        <v>613</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>265</v>
+        <v>67</v>
       </c>
       <c r="B562" t="s">
-        <v>614</v>
+        <v>597</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>976</v>
+        <v>68</v>
       </c>
       <c r="B563" t="s">
-        <v>975</v>
+        <v>598</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="B564" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>1217</v>
+        <v>289</v>
       </c>
       <c r="B565" t="s">
-        <v>1218</v>
+        <v>600</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>185</v>
+        <v>297</v>
       </c>
       <c r="B566" t="s">
-        <v>616</v>
+        <v>601</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>159</v>
+        <v>264</v>
       </c>
       <c r="B567" t="s">
-        <v>617</v>
+        <v>602</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>43</v>
+        <v>193</v>
       </c>
       <c r="B568" t="s">
-        <v>1146</v>
+        <v>603</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>40</v>
+        <v>901</v>
       </c>
       <c r="B569" t="s">
-        <v>1124</v>
+        <v>902</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>1170</v>
+        <v>44</v>
       </c>
       <c r="B570" t="s">
-        <v>1171</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>165</v>
+        <v>1070</v>
       </c>
       <c r="B571" t="s">
-        <v>618</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>12</v>
+        <v>324</v>
       </c>
       <c r="B572" t="s">
-        <v>11</v>
+        <v>604</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="B573" t="s">
-        <v>619</v>
+        <v>605</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>27</v>
+        <v>849</v>
       </c>
       <c r="B574" t="s">
-        <v>620</v>
+        <v>850</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>1040</v>
+        <v>887</v>
       </c>
       <c r="B575" t="s">
-        <v>1041</v>
+        <v>888</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>28</v>
+        <v>1237</v>
       </c>
       <c r="B576" t="s">
-        <v>621</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>1205</v>
+        <v>869</v>
       </c>
       <c r="B577" t="s">
-        <v>1206</v>
+        <v>870</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>255</v>
+        <v>33</v>
       </c>
       <c r="B578" t="s">
-        <v>622</v>
+        <v>606</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>795</v>
+        <v>36</v>
       </c>
       <c r="B579" t="s">
-        <v>796</v>
+        <v>607</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>267</v>
+        <v>1143</v>
       </c>
       <c r="B580" t="s">
-        <v>623</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>661</v>
+        <v>309</v>
       </c>
       <c r="B581" t="s">
-        <v>744</v>
+        <v>608</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>662</v>
+        <v>257</v>
       </c>
       <c r="B582" t="s">
-        <v>745</v>
+        <v>609</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>139</v>
+        <v>302</v>
       </c>
       <c r="B583" t="s">
-        <v>624</v>
+        <v>610</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>7</v>
+        <v>228</v>
       </c>
       <c r="B584" t="s">
-        <v>2</v>
+        <v>611</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="B585" t="s">
-        <v>625</v>
+        <v>18</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>1034</v>
+        <v>655</v>
       </c>
       <c r="B586" t="s">
-        <v>1123</v>
+        <v>743</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>865</v>
+        <v>785</v>
       </c>
       <c r="B587" t="s">
-        <v>866</v>
+        <v>786</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>1035</v>
+        <v>142</v>
       </c>
       <c r="B588" t="s">
-        <v>1122</v>
+        <v>612</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>292</v>
+        <v>1178</v>
       </c>
       <c r="B589" t="s">
-        <v>626</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>8</v>
+        <v>956</v>
       </c>
       <c r="B590" t="s">
-        <v>11</v>
+        <v>957</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>335</v>
+        <v>54</v>
       </c>
       <c r="B591" t="s">
-        <v>627</v>
+        <v>613</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>332</v>
+        <v>265</v>
       </c>
       <c r="B592" t="s">
-        <v>628</v>
+        <v>614</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>259</v>
+        <v>976</v>
       </c>
       <c r="B593" t="s">
-        <v>629</v>
+        <v>975</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>319</v>
+        <v>56</v>
       </c>
       <c r="B594" t="s">
-        <v>630</v>
+        <v>615</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>859</v>
+        <v>1217</v>
       </c>
       <c r="B595" t="s">
-        <v>860</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>1174</v>
+        <v>185</v>
       </c>
       <c r="B596" t="s">
-        <v>1175</v>
+        <v>616</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>268</v>
+        <v>159</v>
       </c>
       <c r="B597" t="s">
-        <v>631</v>
+        <v>617</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>271</v>
+        <v>43</v>
       </c>
       <c r="B598" t="s">
-        <v>1117</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>274</v>
+        <v>40</v>
       </c>
       <c r="B599" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>270</v>
+        <v>1170</v>
       </c>
       <c r="B600" t="s">
-        <v>1119</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>273</v>
+        <v>165</v>
       </c>
       <c r="B601" t="s">
-        <v>1120</v>
+        <v>618</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>269</v>
+        <v>12</v>
       </c>
       <c r="B602" t="s">
-        <v>1121</v>
+        <v>11</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="B603" t="s">
-        <v>1116</v>
+        <v>619</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="B604" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>200</v>
+        <v>1040</v>
       </c>
       <c r="B605" t="s">
-        <v>633</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>203</v>
+        <v>28</v>
       </c>
       <c r="B606" t="s">
-        <v>634</v>
+        <v>621</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>1227</v>
+        <v>1205</v>
       </c>
       <c r="B607" t="s">
-        <v>1228</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>172</v>
+        <v>255</v>
       </c>
       <c r="B608" t="s">
-        <v>635</v>
+        <v>622</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>693</v>
+        <v>795</v>
       </c>
       <c r="B609" t="s">
-        <v>746</v>
+        <v>796</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="B610" t="s">
-        <v>636</v>
+        <v>623</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>694</v>
+        <v>661</v>
       </c>
       <c r="B611" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>189</v>
+        <v>662</v>
       </c>
       <c r="B612" t="s">
-        <v>637</v>
+        <v>745</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>989</v>
+        <v>139</v>
       </c>
       <c r="B613" t="s">
-        <v>990</v>
+        <v>624</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>311</v>
+        <v>7</v>
       </c>
       <c r="B614" t="s">
-        <v>638</v>
+        <v>2</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>312</v>
+        <v>105</v>
       </c>
       <c r="B615" t="s">
-        <v>639</v>
+        <v>625</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B616" t="s">
-        <v>1115</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>1005</v>
+        <v>865</v>
       </c>
       <c r="B617" t="s">
-        <v>1006</v>
+        <v>866</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>81</v>
+        <v>1035</v>
       </c>
       <c r="B618" t="s">
-        <v>640</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>651</v>
+        <v>292</v>
       </c>
       <c r="B619" t="s">
-        <v>748</v>
+        <v>626</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>922</v>
+        <v>8</v>
       </c>
       <c r="B620" t="s">
-        <v>923</v>
+        <v>11</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>642</v>
+        <v>335</v>
       </c>
       <c r="B621" t="s">
-        <v>749</v>
+        <v>627</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
-        <v>969</v>
+        <v>332</v>
       </c>
       <c r="B622" t="s">
-        <v>970</v>
+        <v>628</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
+        <v>259</v>
+      </c>
+      <c r="B623" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A624" t="s">
+        <v>319</v>
+      </c>
+      <c r="B624" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A625" t="s">
+        <v>859</v>
+      </c>
+      <c r="B625" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A626" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B626" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A627" t="s">
+        <v>268</v>
+      </c>
+      <c r="B627" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A628" t="s">
+        <v>271</v>
+      </c>
+      <c r="B628" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A629" t="s">
+        <v>274</v>
+      </c>
+      <c r="B629" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A630" t="s">
+        <v>270</v>
+      </c>
+      <c r="B630" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A631" t="s">
+        <v>273</v>
+      </c>
+      <c r="B631" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A632" t="s">
+        <v>269</v>
+      </c>
+      <c r="B632" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A633" t="s">
+        <v>272</v>
+      </c>
+      <c r="B633" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A634" t="s">
+        <v>92</v>
+      </c>
+      <c r="B634" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A635" t="s">
+        <v>200</v>
+      </c>
+      <c r="B635" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A636" t="s">
+        <v>203</v>
+      </c>
+      <c r="B636" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A637" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B637" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A638" t="s">
+        <v>172</v>
+      </c>
+      <c r="B638" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A639" t="s">
+        <v>693</v>
+      </c>
+      <c r="B639" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A640" t="s">
+        <v>252</v>
+      </c>
+      <c r="B640" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A641" t="s">
+        <v>694</v>
+      </c>
+      <c r="B641" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A642" t="s">
+        <v>189</v>
+      </c>
+      <c r="B642" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A643" t="s">
+        <v>989</v>
+      </c>
+      <c r="B643" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A644" t="s">
+        <v>311</v>
+      </c>
+      <c r="B644" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A645" t="s">
+        <v>312</v>
+      </c>
+      <c r="B645" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A646" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B646" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A647" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B647" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A648" t="s">
+        <v>81</v>
+      </c>
+      <c r="B648" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A649" t="s">
+        <v>651</v>
+      </c>
+      <c r="B649" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A650" t="s">
+        <v>922</v>
+      </c>
+      <c r="B650" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A651" t="s">
+        <v>642</v>
+      </c>
+      <c r="B651" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A652" t="s">
+        <v>969</v>
+      </c>
+      <c r="B652" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A653" t="s">
         <v>1162</v>
       </c>
-      <c r="B623" t="s">
+      <c r="B653" t="s">
         <v>1163</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F869831E-8A32-4AB9-9B21-822EEAD42575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91C02F4-70EF-4281-956B-8DC39704C450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="1299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="1303">
   <si>
     <t>trigger</t>
   </si>
@@ -3922,6 +3922,18 @@
   </si>
   <si>
     <t>S5</t>
+  </si>
+  <si>
+    <t>t1</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>t2</t>
+  </si>
+  <si>
+    <t>T2</t>
   </si>
 </sst>
 </file>
@@ -3983,10 +3995,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B653" totalsRowShown="0">
-  <autoFilter ref="A1:B653" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B653">
-    <sortCondition ref="A1:A653"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B655" totalsRowShown="0">
+  <autoFilter ref="A1:B655" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B655">
+    <sortCondition ref="A1:A655"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4259,7 +4271,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B653"/>
+  <dimension ref="A1:B655"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -9076,417 +9088,433 @@
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>12</v>
+        <v>1299</v>
       </c>
       <c r="B602" t="s">
-        <v>11</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>250</v>
+        <v>1301</v>
       </c>
       <c r="B603" t="s">
-        <v>619</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B604" t="s">
-        <v>620</v>
+        <v>11</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>1040</v>
+        <v>250</v>
       </c>
       <c r="B605" t="s">
-        <v>1041</v>
+        <v>619</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B606" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>1205</v>
+        <v>1040</v>
       </c>
       <c r="B607" t="s">
-        <v>1206</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>255</v>
+        <v>28</v>
       </c>
       <c r="B608" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>795</v>
+        <v>1205</v>
       </c>
       <c r="B609" t="s">
-        <v>796</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="B610" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>661</v>
+        <v>795</v>
       </c>
       <c r="B611" t="s">
-        <v>744</v>
+        <v>796</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>662</v>
+        <v>267</v>
       </c>
       <c r="B612" t="s">
-        <v>745</v>
+        <v>623</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>139</v>
+        <v>661</v>
       </c>
       <c r="B613" t="s">
-        <v>624</v>
+        <v>744</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>7</v>
+        <v>662</v>
       </c>
       <c r="B614" t="s">
-        <v>2</v>
+        <v>745</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="B615" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>1034</v>
+        <v>7</v>
       </c>
       <c r="B616" t="s">
-        <v>1123</v>
+        <v>2</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>865</v>
+        <v>105</v>
       </c>
       <c r="B617" t="s">
-        <v>866</v>
+        <v>625</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B618" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>292</v>
+        <v>865</v>
       </c>
       <c r="B619" t="s">
-        <v>626</v>
+        <v>866</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>8</v>
+        <v>1035</v>
       </c>
       <c r="B620" t="s">
-        <v>11</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>335</v>
+        <v>292</v>
       </c>
       <c r="B621" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
-        <v>332</v>
+        <v>8</v>
       </c>
       <c r="B622" t="s">
-        <v>628</v>
+        <v>11</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
-        <v>259</v>
+        <v>335</v>
       </c>
       <c r="B623" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="B624" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
-        <v>859</v>
+        <v>259</v>
       </c>
       <c r="B625" t="s">
-        <v>860</v>
+        <v>629</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
-        <v>1174</v>
+        <v>319</v>
       </c>
       <c r="B626" t="s">
-        <v>1175</v>
+        <v>630</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
-        <v>268</v>
+        <v>859</v>
       </c>
       <c r="B627" t="s">
-        <v>631</v>
+        <v>860</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
-        <v>271</v>
+        <v>1174</v>
       </c>
       <c r="B628" t="s">
-        <v>1117</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B629" t="s">
-        <v>1118</v>
+        <v>631</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B630" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B631" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B632" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B633" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
-        <v>92</v>
+        <v>269</v>
       </c>
       <c r="B634" t="s">
-        <v>632</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
-        <v>200</v>
+        <v>272</v>
       </c>
       <c r="B635" t="s">
-        <v>633</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
-        <v>203</v>
+        <v>92</v>
       </c>
       <c r="B636" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
-        <v>1227</v>
+        <v>200</v>
       </c>
       <c r="B637" t="s">
-        <v>1228</v>
+        <v>633</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="B638" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
-        <v>693</v>
+        <v>1227</v>
       </c>
       <c r="B639" t="s">
-        <v>746</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
-        <v>252</v>
+        <v>172</v>
       </c>
       <c r="B640" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B641" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
-        <v>189</v>
+        <v>252</v>
       </c>
       <c r="B642" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
-        <v>989</v>
+        <v>694</v>
       </c>
       <c r="B643" t="s">
-        <v>990</v>
+        <v>747</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
-        <v>311</v>
+        <v>189</v>
       </c>
       <c r="B644" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
-        <v>312</v>
+        <v>989</v>
       </c>
       <c r="B645" t="s">
-        <v>639</v>
+        <v>990</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
-        <v>1033</v>
+        <v>311</v>
       </c>
       <c r="B646" t="s">
-        <v>1115</v>
+        <v>638</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
-        <v>1005</v>
+        <v>312</v>
       </c>
       <c r="B647" t="s">
-        <v>1006</v>
+        <v>639</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
-        <v>81</v>
+        <v>1033</v>
       </c>
       <c r="B648" t="s">
-        <v>640</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
-        <v>651</v>
+        <v>1005</v>
       </c>
       <c r="B649" t="s">
-        <v>748</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
-        <v>922</v>
+        <v>81</v>
       </c>
       <c r="B650" t="s">
-        <v>923</v>
+        <v>640</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
-        <v>642</v>
+        <v>651</v>
       </c>
       <c r="B651" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
-        <v>969</v>
+        <v>922</v>
       </c>
       <c r="B652" t="s">
-        <v>970</v>
+        <v>923</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
+        <v>642</v>
+      </c>
+      <c r="B653" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A654" t="s">
+        <v>969</v>
+      </c>
+      <c r="B654" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A655" t="s">
         <v>1162</v>
       </c>
-      <c r="B653" t="s">
+      <c r="B655" t="s">
         <v>1163</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91C02F4-70EF-4281-956B-8DC39704C450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CA7E01-AD57-46DD-AEF2-6451C1E4443C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1310" uniqueCount="1303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="1321">
   <si>
     <t>trigger</t>
   </si>
@@ -3934,6 +3934,60 @@
   </si>
   <si>
     <t>T2</t>
+  </si>
+  <si>
+    <t>paren</t>
+  </si>
+  <si>
+    <t>parenchyma</t>
+  </si>
+  <si>
+    <t>ngt</t>
+  </si>
+  <si>
+    <t>nasogastric tube</t>
+  </si>
+  <si>
+    <t>ett</t>
+  </si>
+  <si>
+    <t>endotracheal tube</t>
+  </si>
+  <si>
+    <t>quad</t>
+  </si>
+  <si>
+    <t>quadrant</t>
+  </si>
+  <si>
+    <t>rlq</t>
+  </si>
+  <si>
+    <t>right lower quadrant</t>
+  </si>
+  <si>
+    <t>llq</t>
+  </si>
+  <si>
+    <t>left lower quadrant</t>
+  </si>
+  <si>
+    <t>panc</t>
+  </si>
+  <si>
+    <t>pancreas</t>
+  </si>
+  <si>
+    <t>envt</t>
+  </si>
+  <si>
+    <t>environment</t>
+  </si>
+  <si>
+    <t>perin</t>
+  </si>
+  <si>
+    <t>perinephric</t>
   </si>
 </sst>
 </file>
@@ -3995,10 +4049,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B655" totalsRowShown="0">
-  <autoFilter ref="A1:B655" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B655">
-    <sortCondition ref="A1:A655"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B664" totalsRowShown="0">
+  <autoFilter ref="A1:B664" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B664">
+    <sortCondition ref="A1:A664"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4271,7 +4325,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B655"/>
+  <dimension ref="A1:B664"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -5904,3617 +5958,3689 @@
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>183</v>
+        <v>1317</v>
       </c>
       <c r="B204" t="s">
-        <v>422</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>1155</v>
+        <v>183</v>
       </c>
       <c r="B205" t="s">
-        <v>1156</v>
+        <v>422</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="B206" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>891</v>
+        <v>1157</v>
       </c>
       <c r="B207" t="s">
-        <v>892</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>32</v>
+        <v>891</v>
       </c>
       <c r="B208" t="s">
-        <v>423</v>
+        <v>892</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B209" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>1233</v>
+        <v>35</v>
       </c>
       <c r="B210" t="s">
-        <v>1234</v>
+        <v>424</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>764</v>
+        <v>1307</v>
       </c>
       <c r="B211" t="s">
-        <v>1010</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>169</v>
+        <v>1233</v>
       </c>
       <c r="B212" t="s">
-        <v>425</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>170</v>
+        <v>764</v>
       </c>
       <c r="B213" t="s">
-        <v>425</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>1011</v>
+        <v>169</v>
       </c>
       <c r="B214" t="s">
-        <v>765</v>
+        <v>425</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B215" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>111</v>
+        <v>1011</v>
       </c>
       <c r="B216" t="s">
-        <v>427</v>
+        <v>765</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>238</v>
+        <v>178</v>
       </c>
       <c r="B217" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B218" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>109</v>
+        <v>238</v>
       </c>
       <c r="B219" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>179</v>
+        <v>106</v>
       </c>
       <c r="B220" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>667</v>
+        <v>109</v>
       </c>
       <c r="B221" t="s">
-        <v>722</v>
+        <v>430</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>97</v>
+        <v>179</v>
       </c>
       <c r="B222" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>110</v>
+        <v>667</v>
       </c>
       <c r="B223" t="s">
-        <v>433</v>
+        <v>722</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>242</v>
+        <v>97</v>
       </c>
       <c r="B224" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>226</v>
+        <v>110</v>
       </c>
       <c r="B225" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>177</v>
+        <v>242</v>
       </c>
       <c r="B226" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>182</v>
+        <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>1110</v>
+        <v>177</v>
       </c>
       <c r="B228" t="s">
-        <v>1111</v>
+        <v>436</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>977</v>
+        <v>182</v>
       </c>
       <c r="B229" t="s">
-        <v>978</v>
+        <v>437</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>979</v>
+        <v>1110</v>
       </c>
       <c r="B230" t="s">
-        <v>980</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>1198</v>
+        <v>977</v>
       </c>
       <c r="B231" t="s">
-        <v>1199</v>
+        <v>978</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>1201</v>
+        <v>979</v>
       </c>
       <c r="B232" t="s">
-        <v>1202</v>
+        <v>980</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>253</v>
+        <v>1198</v>
       </c>
       <c r="B233" t="s">
-        <v>438</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>34</v>
+        <v>1201</v>
       </c>
       <c r="B234" t="s">
-        <v>439</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>787</v>
+        <v>253</v>
       </c>
       <c r="B235" t="s">
-        <v>788</v>
+        <v>438</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>180</v>
+        <v>34</v>
       </c>
       <c r="B236" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>275</v>
+        <v>787</v>
       </c>
       <c r="B237" t="s">
-        <v>441</v>
+        <v>788</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>857</v>
+        <v>180</v>
       </c>
       <c r="B238" t="s">
-        <v>858</v>
+        <v>440</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>116</v>
+        <v>275</v>
       </c>
       <c r="B239" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>208</v>
+        <v>857</v>
       </c>
       <c r="B240" t="s">
-        <v>443</v>
+        <v>858</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>1221</v>
+        <v>116</v>
       </c>
       <c r="B241" t="s">
-        <v>1222</v>
+        <v>442</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>1056</v>
+        <v>208</v>
       </c>
       <c r="B242" t="s">
-        <v>1057</v>
+        <v>443</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>118</v>
+        <v>1221</v>
       </c>
       <c r="B243" t="s">
-        <v>444</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>641</v>
+        <v>1056</v>
       </c>
       <c r="B244" t="s">
-        <v>723</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>815</v>
+        <v>118</v>
       </c>
       <c r="B245" t="s">
-        <v>816</v>
+        <v>444</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>298</v>
+        <v>641</v>
       </c>
       <c r="B246" t="s">
-        <v>445</v>
+        <v>723</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>643</v>
+        <v>815</v>
       </c>
       <c r="B247" t="s">
-        <v>724</v>
+        <v>816</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>644</v>
+        <v>298</v>
       </c>
       <c r="B248" t="s">
-        <v>725</v>
+        <v>445</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>1036</v>
+        <v>643</v>
       </c>
       <c r="B249" t="s">
-        <v>1037</v>
+        <v>724</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>90</v>
+        <v>644</v>
       </c>
       <c r="B250" t="s">
-        <v>446</v>
+        <v>725</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>88</v>
+        <v>1036</v>
       </c>
       <c r="B251" t="s">
-        <v>447</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B252" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>1072</v>
+        <v>88</v>
       </c>
       <c r="B253" t="s">
-        <v>1073</v>
+        <v>447</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="B254" t="s">
-        <v>1136</v>
+        <v>448</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>5</v>
+        <v>1072</v>
       </c>
       <c r="B255" t="s">
-        <v>6</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>1141</v>
+        <v>23</v>
       </c>
       <c r="B256" t="s">
-        <v>1142</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>126</v>
+        <v>5</v>
       </c>
       <c r="B257" t="s">
-        <v>449</v>
+        <v>6</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>128</v>
+        <v>1141</v>
       </c>
       <c r="B258" t="s">
-        <v>450</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B259" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B260" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="B261" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>277</v>
+        <v>132</v>
       </c>
       <c r="B262" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>1074</v>
+        <v>119</v>
       </c>
       <c r="B263" t="s">
-        <v>1075</v>
+        <v>453</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>9</v>
+        <v>277</v>
       </c>
       <c r="B264" t="s">
-        <v>10</v>
+        <v>454</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>129</v>
+        <v>1074</v>
       </c>
       <c r="B265" t="s">
-        <v>455</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>127</v>
+        <v>9</v>
       </c>
       <c r="B266" t="s">
-        <v>456</v>
+        <v>10</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>173</v>
+        <v>129</v>
       </c>
       <c r="B267" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>262</v>
+        <v>127</v>
       </c>
       <c r="B268" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>77</v>
+        <v>173</v>
       </c>
       <c r="B269" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>938</v>
+        <v>262</v>
       </c>
       <c r="B270" t="s">
-        <v>939</v>
+        <v>458</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>1172</v>
+        <v>77</v>
       </c>
       <c r="B271" t="s">
-        <v>1173</v>
+        <v>459</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>168</v>
+        <v>938</v>
       </c>
       <c r="B272" t="s">
-        <v>460</v>
+        <v>939</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>167</v>
+        <v>1172</v>
       </c>
       <c r="B273" t="s">
-        <v>461</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>835</v>
+        <v>168</v>
       </c>
       <c r="B274" t="s">
-        <v>836</v>
+        <v>460</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>791</v>
+        <v>167</v>
       </c>
       <c r="B275" t="s">
-        <v>792</v>
+        <v>461</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>304</v>
+        <v>835</v>
       </c>
       <c r="B276" t="s">
-        <v>462</v>
+        <v>836</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>758</v>
+        <v>791</v>
       </c>
       <c r="B277" t="s">
-        <v>759</v>
+        <v>792</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>897</v>
+        <v>304</v>
       </c>
       <c r="B278" t="s">
-        <v>898</v>
+        <v>462</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>652</v>
+        <v>758</v>
       </c>
       <c r="B279" t="s">
-        <v>726</v>
+        <v>759</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>86</v>
+        <v>897</v>
       </c>
       <c r="B280" t="s">
-        <v>463</v>
+        <v>898</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>87</v>
+        <v>652</v>
       </c>
       <c r="B281" t="s">
-        <v>464</v>
+        <v>726</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>153</v>
+        <v>86</v>
       </c>
       <c r="B282" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>156</v>
+        <v>87</v>
       </c>
       <c r="B283" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B284" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>251</v>
+        <v>156</v>
       </c>
       <c r="B285" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>285</v>
+        <v>158</v>
       </c>
       <c r="B286" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>326</v>
+        <v>251</v>
       </c>
       <c r="B287" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>327</v>
+        <v>285</v>
       </c>
       <c r="B288" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>229</v>
+        <v>326</v>
       </c>
       <c r="B289" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>55</v>
+        <v>327</v>
       </c>
       <c r="B290" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>657</v>
+        <v>229</v>
       </c>
       <c r="B291" t="s">
-        <v>727</v>
+        <v>472</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>235</v>
+        <v>55</v>
       </c>
       <c r="B292" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>57</v>
+        <v>657</v>
       </c>
       <c r="B293" t="s">
-        <v>475</v>
+        <v>727</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B294" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>766</v>
+        <v>57</v>
       </c>
       <c r="B295" t="s">
-        <v>1009</v>
+        <v>475</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>1012</v>
+        <v>236</v>
       </c>
       <c r="B296" t="s">
-        <v>767</v>
+        <v>476</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>164</v>
+        <v>766</v>
       </c>
       <c r="B297" t="s">
-        <v>477</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>201</v>
+        <v>1012</v>
       </c>
       <c r="B298" t="s">
-        <v>478</v>
+        <v>767</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>204</v>
+        <v>164</v>
       </c>
       <c r="B299" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>313</v>
+        <v>201</v>
       </c>
       <c r="B300" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>873</v>
+        <v>204</v>
       </c>
       <c r="B301" t="s">
-        <v>874</v>
+        <v>479</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>997</v>
+        <v>313</v>
       </c>
       <c r="B302" t="s">
-        <v>998</v>
+        <v>480</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>258</v>
+        <v>873</v>
       </c>
       <c r="B303" t="s">
-        <v>481</v>
+        <v>874</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>983</v>
+        <v>997</v>
       </c>
       <c r="B304" t="s">
-        <v>984</v>
+        <v>998</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>160</v>
+        <v>258</v>
       </c>
       <c r="B305" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>692</v>
+        <v>983</v>
       </c>
       <c r="B306" t="s">
-        <v>728</v>
+        <v>984</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>1166</v>
+        <v>160</v>
       </c>
       <c r="B307" t="s">
-        <v>1167</v>
+        <v>482</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>760</v>
+        <v>692</v>
       </c>
       <c r="B308" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>895</v>
+        <v>1166</v>
       </c>
       <c r="B309" t="s">
-        <v>896</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>893</v>
+        <v>760</v>
       </c>
       <c r="B310" t="s">
-        <v>894</v>
+        <v>761</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>184</v>
+        <v>895</v>
       </c>
       <c r="B311" t="s">
-        <v>483</v>
+        <v>896</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>244</v>
+        <v>893</v>
       </c>
       <c r="B312" t="s">
-        <v>484</v>
+        <v>894</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>243</v>
+        <v>184</v>
       </c>
       <c r="B313" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>1279</v>
+        <v>244</v>
       </c>
       <c r="B314" t="s">
-        <v>1284</v>
+        <v>484</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>686</v>
+        <v>243</v>
       </c>
       <c r="B315" t="s">
-        <v>729</v>
+        <v>485</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="B316" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B317" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="B318" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B319" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="B320" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B321" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="B322" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B323" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>1192</v>
+        <v>1283</v>
       </c>
       <c r="B324" t="s">
-        <v>1193</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>280</v>
+        <v>690</v>
       </c>
       <c r="B325" t="s">
-        <v>486</v>
+        <v>733</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>281</v>
+        <v>1192</v>
       </c>
       <c r="B326" t="s">
-        <v>487</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>49</v>
+        <v>280</v>
       </c>
       <c r="B327" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>53</v>
+        <v>281</v>
       </c>
       <c r="B328" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="B329" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="B330" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>1190</v>
+        <v>136</v>
       </c>
       <c r="B331" t="s">
-        <v>1191</v>
+        <v>491</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>221</v>
+        <v>72</v>
       </c>
       <c r="B332" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="B333" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>15</v>
+        <v>221</v>
       </c>
       <c r="B334" t="s">
-        <v>16</v>
+        <v>492</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>1060</v>
+        <v>1194</v>
       </c>
       <c r="B335" t="s">
-        <v>1061</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>920</v>
+        <v>15</v>
       </c>
       <c r="B336" t="s">
-        <v>921</v>
+        <v>16</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>108</v>
+        <v>1060</v>
       </c>
       <c r="B337" t="s">
-        <v>493</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>241</v>
+        <v>920</v>
       </c>
       <c r="B338" t="s">
-        <v>494</v>
+        <v>921</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>328</v>
+        <v>108</v>
       </c>
       <c r="B339" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>1100</v>
+        <v>241</v>
       </c>
       <c r="B340" t="s">
-        <v>1101</v>
+        <v>494</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>1052</v>
+        <v>328</v>
       </c>
       <c r="B341" t="s">
-        <v>1053</v>
+        <v>495</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>121</v>
+        <v>1100</v>
       </c>
       <c r="B342" t="s">
-        <v>496</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>750</v>
+        <v>1052</v>
       </c>
       <c r="B343" t="s">
-        <v>751</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>781</v>
+        <v>121</v>
       </c>
       <c r="B344" t="s">
-        <v>782</v>
+        <v>496</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>134</v>
+        <v>750</v>
       </c>
       <c r="B345" t="s">
-        <v>497</v>
+        <v>751</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>63</v>
+        <v>781</v>
       </c>
       <c r="B346" t="s">
-        <v>498</v>
+        <v>782</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>224</v>
+        <v>134</v>
       </c>
       <c r="B347" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="B348" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>26</v>
+        <v>1313</v>
       </c>
       <c r="B349" t="s">
-        <v>501</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="B350" t="s">
-        <v>1133</v>
+        <v>499</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>960</v>
+        <v>25</v>
       </c>
       <c r="B351" t="s">
-        <v>1134</v>
+        <v>500</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>1113</v>
+        <v>26</v>
       </c>
       <c r="B352" t="s">
-        <v>1114</v>
+        <v>501</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B353" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>202</v>
+        <v>960</v>
       </c>
       <c r="B354" t="s">
-        <v>502</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>205</v>
+        <v>1113</v>
       </c>
       <c r="B355" t="s">
-        <v>503</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="B356" t="s">
-        <v>504</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>663</v>
+        <v>202</v>
       </c>
       <c r="B357" t="s">
-        <v>734</v>
+        <v>502</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="B358" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>1088</v>
+        <v>145</v>
       </c>
       <c r="B359" t="s">
-        <v>1089</v>
+        <v>504</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>263</v>
+        <v>663</v>
       </c>
       <c r="B360" t="s">
-        <v>506</v>
+        <v>734</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>1090</v>
+        <v>171</v>
       </c>
       <c r="B361" t="s">
-        <v>1091</v>
+        <v>505</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>80</v>
+        <v>1088</v>
       </c>
       <c r="B362" t="s">
-        <v>507</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>65</v>
+        <v>263</v>
       </c>
       <c r="B363" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>191</v>
+        <v>1090</v>
       </c>
       <c r="B364" t="s">
-        <v>509</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="B365" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>192</v>
+        <v>65</v>
       </c>
       <c r="B366" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="B367" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>233</v>
+        <v>123</v>
       </c>
       <c r="B368" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>1200</v>
+        <v>192</v>
       </c>
       <c r="B369" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>31</v>
+        <v>231</v>
       </c>
       <c r="B370" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>30</v>
+        <v>233</v>
       </c>
       <c r="B371" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>37</v>
+        <v>1200</v>
       </c>
       <c r="B372" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="B373" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>306</v>
+        <v>30</v>
       </c>
       <c r="B374" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>222</v>
+        <v>37</v>
       </c>
       <c r="B375" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>315</v>
+        <v>71</v>
       </c>
       <c r="B376" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>278</v>
+        <v>306</v>
       </c>
       <c r="B377" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>279</v>
+        <v>222</v>
       </c>
       <c r="B378" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>831</v>
+        <v>315</v>
       </c>
       <c r="B379" t="s">
-        <v>832</v>
+        <v>520</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>48</v>
+        <v>278</v>
       </c>
       <c r="B380" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>146</v>
+        <v>279</v>
       </c>
       <c r="B381" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>52</v>
+        <v>831</v>
       </c>
       <c r="B382" t="s">
-        <v>525</v>
+        <v>832</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>223</v>
+        <v>48</v>
       </c>
       <c r="B383" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>1094</v>
+        <v>146</v>
       </c>
       <c r="B384" t="s">
-        <v>1095</v>
+        <v>524</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>1109</v>
+        <v>52</v>
       </c>
       <c r="B385" t="s">
-        <v>1112</v>
+        <v>525</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>1050</v>
+        <v>223</v>
       </c>
       <c r="B386" t="s">
-        <v>1051</v>
+        <v>526</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>96</v>
+        <v>1094</v>
       </c>
       <c r="B387" t="s">
-        <v>527</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>248</v>
+        <v>1109</v>
       </c>
       <c r="B388" t="s">
-        <v>528</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>249</v>
+        <v>1050</v>
       </c>
       <c r="B389" t="s">
-        <v>529</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B390" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>1064</v>
+        <v>248</v>
       </c>
       <c r="B391" t="s">
-        <v>1065</v>
+        <v>528</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
       <c r="B392" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>1225</v>
+        <v>94</v>
       </c>
       <c r="B393" t="s">
-        <v>1226</v>
+        <v>530</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>916</v>
+        <v>1064</v>
       </c>
       <c r="B394" t="s">
-        <v>917</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>914</v>
+        <v>212</v>
       </c>
       <c r="B395" t="s">
-        <v>915</v>
+        <v>531</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>918</v>
+        <v>1225</v>
       </c>
       <c r="B396" t="s">
-        <v>919</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>330</v>
+        <v>916</v>
       </c>
       <c r="B397" t="s">
-        <v>532</v>
+        <v>917</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>1066</v>
+        <v>914</v>
       </c>
       <c r="B398" t="s">
-        <v>1067</v>
+        <v>915</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>995</v>
+        <v>918</v>
       </c>
       <c r="B399" t="s">
-        <v>996</v>
+        <v>919</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>991</v>
+        <v>330</v>
       </c>
       <c r="B400" t="s">
-        <v>992</v>
+        <v>532</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>993</v>
+        <v>1066</v>
       </c>
       <c r="B401" t="s">
-        <v>994</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>82</v>
+        <v>995</v>
       </c>
       <c r="B402" t="s">
-        <v>533</v>
+        <v>996</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>772</v>
+        <v>991</v>
       </c>
       <c r="B403" t="s">
-        <v>773</v>
+        <v>992</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>197</v>
+        <v>993</v>
       </c>
       <c r="B404" t="s">
-        <v>534</v>
+        <v>994</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>654</v>
+        <v>82</v>
       </c>
       <c r="B405" t="s">
-        <v>735</v>
+        <v>533</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>821</v>
+        <v>772</v>
       </c>
       <c r="B406" t="s">
-        <v>822</v>
+        <v>773</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>1068</v>
+        <v>197</v>
       </c>
       <c r="B407" t="s">
-        <v>1069</v>
+        <v>534</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>3</v>
+        <v>654</v>
       </c>
       <c r="B408" t="s">
-        <v>4</v>
+        <v>735</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>958</v>
+        <v>821</v>
       </c>
       <c r="B409" t="s">
-        <v>4</v>
+        <v>822</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>959</v>
+        <v>1068</v>
       </c>
       <c r="B410" t="s">
-        <v>4</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>664</v>
+        <v>3</v>
       </c>
       <c r="B411" t="s">
-        <v>736</v>
+        <v>4</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>770</v>
+        <v>958</v>
       </c>
       <c r="B412" t="s">
-        <v>771</v>
+        <v>4</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>85</v>
+        <v>959</v>
       </c>
       <c r="B413" t="s">
-        <v>535</v>
+        <v>4</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>1062</v>
+        <v>664</v>
       </c>
       <c r="B414" t="s">
-        <v>1063</v>
+        <v>736</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>829</v>
+        <v>1305</v>
       </c>
       <c r="B415" t="s">
-        <v>830</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>809</v>
+        <v>770</v>
       </c>
       <c r="B416" t="s">
-        <v>810</v>
+        <v>771</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>187</v>
+        <v>85</v>
       </c>
       <c r="B417" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>827</v>
+        <v>1062</v>
       </c>
       <c r="B418" t="s">
-        <v>828</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>934</v>
+        <v>829</v>
       </c>
       <c r="B419" t="s">
-        <v>1130</v>
+        <v>830</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>863</v>
+        <v>809</v>
       </c>
       <c r="B420" t="s">
-        <v>864</v>
+        <v>810</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>1044</v>
+        <v>187</v>
       </c>
       <c r="B421" t="s">
-        <v>1045</v>
+        <v>536</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>798</v>
+        <v>827</v>
       </c>
       <c r="B422" t="s">
-        <v>1131</v>
+        <v>828</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>797</v>
+        <v>934</v>
       </c>
       <c r="B423" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>13</v>
+        <v>863</v>
       </c>
       <c r="B424" t="s">
-        <v>14</v>
+        <v>864</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>817</v>
+        <v>1044</v>
       </c>
       <c r="B425" t="s">
-        <v>818</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>1235</v>
+        <v>798</v>
       </c>
       <c r="B426" t="s">
-        <v>1236</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>186</v>
+        <v>797</v>
       </c>
       <c r="B427" t="s">
-        <v>537</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>811</v>
+        <v>13</v>
       </c>
       <c r="B428" t="s">
-        <v>812</v>
+        <v>14</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>320</v>
+        <v>817</v>
       </c>
       <c r="B429" t="s">
-        <v>538</v>
+        <v>818</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>656</v>
+        <v>1235</v>
       </c>
       <c r="B430" t="s">
-        <v>737</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>855</v>
+        <v>186</v>
       </c>
       <c r="B431" t="s">
-        <v>856</v>
+        <v>537</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>658</v>
+        <v>811</v>
       </c>
       <c r="B432" t="s">
-        <v>738</v>
+        <v>812</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>653</v>
+        <v>320</v>
       </c>
       <c r="B433" t="s">
-        <v>739</v>
+        <v>538</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>1207</v>
+        <v>656</v>
       </c>
       <c r="B434" t="s">
-        <v>1208</v>
+        <v>737</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>256</v>
+        <v>855</v>
       </c>
       <c r="B435" t="s">
-        <v>539</v>
+        <v>856</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>260</v>
+        <v>658</v>
       </c>
       <c r="B436" t="s">
-        <v>540</v>
+        <v>738</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>261</v>
+        <v>653</v>
       </c>
       <c r="B437" t="s">
-        <v>541</v>
+        <v>739</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>188</v>
+        <v>1207</v>
       </c>
       <c r="B438" t="s">
-        <v>542</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>190</v>
+        <v>256</v>
       </c>
       <c r="B439" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>936</v>
+        <v>260</v>
       </c>
       <c r="B440" t="s">
-        <v>937</v>
+        <v>540</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>1031</v>
+        <v>261</v>
       </c>
       <c r="B441" t="s">
-        <v>1032</v>
+        <v>541</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>1223</v>
+        <v>188</v>
       </c>
       <c r="B442" t="s">
-        <v>1224</v>
+        <v>542</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="B443" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>851</v>
+        <v>936</v>
       </c>
       <c r="B444" t="s">
-        <v>852</v>
+        <v>937</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>143</v>
+        <v>1031</v>
       </c>
       <c r="B445" t="s">
-        <v>545</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>140</v>
+        <v>1223</v>
       </c>
       <c r="B446" t="s">
-        <v>546</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>1203</v>
+        <v>209</v>
       </c>
       <c r="B447" t="s">
-        <v>1204</v>
+        <v>544</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>254</v>
+        <v>1315</v>
       </c>
       <c r="B448" t="s">
-        <v>547</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>331</v>
+        <v>851</v>
       </c>
       <c r="B449" t="s">
-        <v>548</v>
+        <v>852</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="B450" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>234</v>
+        <v>140</v>
       </c>
       <c r="B451" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>73</v>
+        <v>1203</v>
       </c>
       <c r="B452" t="s">
-        <v>551</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>342</v>
+        <v>1303</v>
       </c>
       <c r="B453" t="s">
-        <v>552</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>308</v>
+        <v>254</v>
       </c>
       <c r="B454" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>843</v>
+        <v>331</v>
       </c>
       <c r="B455" t="s">
-        <v>844</v>
+        <v>548</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>845</v>
+        <v>210</v>
       </c>
       <c r="B456" t="s">
-        <v>846</v>
+        <v>549</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="B457" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>909</v>
+        <v>73</v>
       </c>
       <c r="B458" t="s">
-        <v>910</v>
+        <v>551</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>963</v>
+        <v>342</v>
       </c>
       <c r="B459" t="s">
-        <v>964</v>
+        <v>552</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>1188</v>
+        <v>308</v>
       </c>
       <c r="B460" t="s">
-        <v>1189</v>
+        <v>553</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>227</v>
+        <v>843</v>
       </c>
       <c r="B461" t="s">
-        <v>555</v>
+        <v>844</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>334</v>
+        <v>845</v>
       </c>
       <c r="B462" t="s">
-        <v>1161</v>
+        <v>846</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>971</v>
+        <v>220</v>
       </c>
       <c r="B463" t="s">
-        <v>972</v>
+        <v>554</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>778</v>
+        <v>909</v>
       </c>
       <c r="B464" t="s">
-        <v>779</v>
+        <v>910</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>294</v>
+        <v>963</v>
       </c>
       <c r="B465" t="s">
-        <v>556</v>
+        <v>964</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>952</v>
+        <v>1188</v>
       </c>
       <c r="B466" t="s">
-        <v>953</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>339</v>
+        <v>227</v>
       </c>
       <c r="B467" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>780</v>
+        <v>334</v>
       </c>
       <c r="B468" t="s">
-        <v>779</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>340</v>
+        <v>971</v>
       </c>
       <c r="B469" t="s">
-        <v>558</v>
+        <v>972</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>341</v>
+        <v>778</v>
       </c>
       <c r="B470" t="s">
-        <v>559</v>
+        <v>779</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>645</v>
+        <v>294</v>
       </c>
       <c r="B471" t="s">
-        <v>740</v>
+        <v>556</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>39</v>
+        <v>952</v>
       </c>
       <c r="B472" t="s">
-        <v>560</v>
+        <v>953</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>38</v>
+        <v>339</v>
       </c>
       <c r="B473" t="s">
-        <v>1129</v>
+        <v>557</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>343</v>
+        <v>780</v>
       </c>
       <c r="B474" t="s">
-        <v>561</v>
+        <v>779</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>107</v>
+        <v>1319</v>
       </c>
       <c r="B475" t="s">
-        <v>562</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>1029</v>
+        <v>340</v>
       </c>
       <c r="B476" t="s">
-        <v>1030</v>
+        <v>558</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>903</v>
+        <v>341</v>
       </c>
       <c r="B477" t="s">
-        <v>904</v>
+        <v>559</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>117</v>
+        <v>645</v>
       </c>
       <c r="B478" t="s">
-        <v>563</v>
+        <v>740</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>1025</v>
+        <v>39</v>
       </c>
       <c r="B479" t="s">
-        <v>1026</v>
+        <v>560</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="B480" t="s">
-        <v>564</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>99</v>
+        <v>343</v>
       </c>
       <c r="B481" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>666</v>
+        <v>107</v>
       </c>
       <c r="B482" t="s">
-        <v>741</v>
+        <v>562</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>1107</v>
+        <v>1029</v>
       </c>
       <c r="B483" t="s">
-        <v>1024</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>823</v>
+        <v>903</v>
       </c>
       <c r="B484" t="s">
-        <v>824</v>
+        <v>904</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B485" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>889</v>
+        <v>1025</v>
       </c>
       <c r="B486" t="s">
-        <v>890</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="B487" t="s">
-        <v>1128</v>
+        <v>564</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>290</v>
+        <v>99</v>
       </c>
       <c r="B488" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>299</v>
+        <v>666</v>
       </c>
       <c r="B489" t="s">
-        <v>568</v>
+        <v>741</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>47</v>
+        <v>1107</v>
       </c>
       <c r="B490" t="s">
-        <v>569</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>847</v>
+        <v>823</v>
       </c>
       <c r="B491" t="s">
-        <v>848</v>
+        <v>824</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="B492" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>871</v>
+        <v>889</v>
       </c>
       <c r="B493" t="s">
-        <v>872</v>
+        <v>890</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>114</v>
+        <v>45</v>
       </c>
       <c r="B494" t="s">
-        <v>571</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>853</v>
+        <v>290</v>
       </c>
       <c r="B495" t="s">
-        <v>854</v>
+        <v>567</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>144</v>
+        <v>299</v>
       </c>
       <c r="B496" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>1080</v>
+        <v>47</v>
       </c>
       <c r="B497" t="s">
-        <v>1081</v>
+        <v>569</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>176</v>
+        <v>847</v>
       </c>
       <c r="B498" t="s">
-        <v>573</v>
+        <v>848</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>316</v>
+        <v>51</v>
       </c>
       <c r="B499" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>29</v>
+        <v>871</v>
       </c>
       <c r="B500" t="s">
-        <v>575</v>
+        <v>872</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>1104</v>
+        <v>114</v>
       </c>
       <c r="B501" t="s">
-        <v>1105</v>
+        <v>571</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>1018</v>
+        <v>853</v>
       </c>
       <c r="B502" t="s">
-        <v>1019</v>
+        <v>854</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>1231</v>
+        <v>144</v>
       </c>
       <c r="B503" t="s">
-        <v>1232</v>
+        <v>572</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>293</v>
+        <v>1080</v>
       </c>
       <c r="B504" t="s">
-        <v>576</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>981</v>
+        <v>176</v>
       </c>
       <c r="B505" t="s">
-        <v>982</v>
+        <v>573</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="B506" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>1003</v>
+        <v>29</v>
       </c>
       <c r="B507" t="s">
-        <v>1004</v>
+        <v>575</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>1007</v>
+        <v>1104</v>
       </c>
       <c r="B508" t="s">
-        <v>1008</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>75</v>
+        <v>1018</v>
       </c>
       <c r="B509" t="s">
-        <v>578</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>76</v>
+        <v>1231</v>
       </c>
       <c r="B510" t="s">
-        <v>579</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>78</v>
+        <v>293</v>
       </c>
       <c r="B511" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>329</v>
+        <v>981</v>
       </c>
       <c r="B512" t="s">
-        <v>581</v>
+        <v>982</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>752</v>
+        <v>301</v>
       </c>
       <c r="B513" t="s">
-        <v>753</v>
+        <v>577</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>805</v>
+        <v>1003</v>
       </c>
       <c r="B514" t="s">
-        <v>806</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>135</v>
+        <v>1007</v>
       </c>
       <c r="B515" t="s">
-        <v>582</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>1186</v>
+        <v>75</v>
       </c>
       <c r="B516" t="s">
-        <v>1187</v>
+        <v>578</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>1038</v>
+        <v>76</v>
       </c>
       <c r="B517" t="s">
-        <v>1039</v>
+        <v>579</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="B518" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>935</v>
+        <v>329</v>
       </c>
       <c r="B519" t="s">
-        <v>1145</v>
+        <v>581</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>216</v>
+        <v>1309</v>
       </c>
       <c r="B520" t="s">
-        <v>1126</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>317</v>
+        <v>752</v>
       </c>
       <c r="B521" t="s">
-        <v>584</v>
+        <v>753</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>1082</v>
+        <v>805</v>
       </c>
       <c r="B522" t="s">
-        <v>1083</v>
+        <v>806</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>214</v>
+        <v>135</v>
       </c>
       <c r="B523" t="s">
-        <v>1127</v>
+        <v>582</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>999</v>
+        <v>1186</v>
       </c>
       <c r="B524" t="s">
-        <v>1000</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>1001</v>
+        <v>1038</v>
       </c>
       <c r="B525" t="s">
-        <v>1002</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="B526" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>948</v>
+        <v>935</v>
       </c>
       <c r="B527" t="s">
-        <v>949</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>1098</v>
+        <v>216</v>
       </c>
       <c r="B528" t="s">
-        <v>1099</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>1048</v>
+        <v>317</v>
       </c>
       <c r="B529" t="s">
-        <v>1049</v>
+        <v>584</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>93</v>
+        <v>1082</v>
       </c>
       <c r="B530" t="s">
-        <v>586</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>120</v>
+        <v>214</v>
       </c>
       <c r="B531" t="s">
-        <v>587</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>783</v>
+        <v>999</v>
       </c>
       <c r="B532" t="s">
-        <v>784</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>133</v>
+        <v>1001</v>
       </c>
       <c r="B533" t="s">
-        <v>588</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>62</v>
+        <v>225</v>
       </c>
       <c r="B534" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>66</v>
+        <v>948</v>
       </c>
       <c r="B535" t="s">
-        <v>590</v>
+        <v>949</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>825</v>
+        <v>1098</v>
       </c>
       <c r="B536" t="s">
-        <v>826</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>950</v>
+        <v>1048</v>
       </c>
       <c r="B537" t="s">
-        <v>951</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>1215</v>
+        <v>93</v>
       </c>
       <c r="B538" t="s">
-        <v>1216</v>
+        <v>586</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="B539" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>64</v>
+        <v>783</v>
       </c>
       <c r="B540" t="s">
-        <v>592</v>
+        <v>784</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B541" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>1184</v>
+        <v>62</v>
       </c>
       <c r="B542" t="s">
-        <v>1185</v>
+        <v>589</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>181</v>
+        <v>1311</v>
       </c>
       <c r="B543" t="s">
-        <v>594</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>801</v>
+        <v>66</v>
       </c>
       <c r="B544" t="s">
-        <v>802</v>
+        <v>590</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>1289</v>
+        <v>825</v>
       </c>
       <c r="B545" t="s">
-        <v>1294</v>
+        <v>826</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>691</v>
+        <v>950</v>
       </c>
       <c r="B546" t="s">
-        <v>742</v>
+        <v>951</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>1290</v>
+        <v>1215</v>
       </c>
       <c r="B547" t="s">
-        <v>1295</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>1291</v>
+        <v>79</v>
       </c>
       <c r="B548" t="s">
-        <v>1296</v>
+        <v>591</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>1292</v>
+        <v>64</v>
       </c>
       <c r="B549" t="s">
-        <v>1297</v>
+        <v>592</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>1293</v>
+        <v>122</v>
       </c>
       <c r="B550" t="s">
-        <v>1298</v>
+        <v>593</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>1151</v>
+        <v>1184</v>
       </c>
       <c r="B551" t="s">
-        <v>1152</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>1149</v>
+        <v>181</v>
       </c>
       <c r="B552" t="s">
-        <v>1150</v>
+        <v>594</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>284</v>
+        <v>801</v>
       </c>
       <c r="B553" t="s">
-        <v>595</v>
+        <v>802</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>973</v>
+        <v>1289</v>
       </c>
       <c r="B554" t="s">
-        <v>974</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>1219</v>
+        <v>691</v>
       </c>
       <c r="B555" t="s">
-        <v>1220</v>
+        <v>742</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>841</v>
+        <v>1290</v>
       </c>
       <c r="B556" t="s">
-        <v>842</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>283</v>
+        <v>1291</v>
       </c>
       <c r="B557" t="s">
-        <v>596</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>883</v>
+        <v>1292</v>
       </c>
       <c r="B558" t="s">
-        <v>884</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>1180</v>
+        <v>1293</v>
       </c>
       <c r="B559" t="s">
-        <v>1181</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>756</v>
+        <v>1151</v>
       </c>
       <c r="B560" t="s">
-        <v>757</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>1078</v>
+        <v>1149</v>
       </c>
       <c r="B561" t="s">
-        <v>1079</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>67</v>
+        <v>284</v>
       </c>
       <c r="B562" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>68</v>
+        <v>973</v>
       </c>
       <c r="B563" t="s">
-        <v>598</v>
+        <v>974</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>95</v>
+        <v>1219</v>
       </c>
       <c r="B564" t="s">
-        <v>599</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>289</v>
+        <v>841</v>
       </c>
       <c r="B565" t="s">
-        <v>600</v>
+        <v>842</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="B566" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>264</v>
+        <v>883</v>
       </c>
       <c r="B567" t="s">
-        <v>602</v>
+        <v>884</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>193</v>
+        <v>1180</v>
       </c>
       <c r="B568" t="s">
-        <v>603</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>901</v>
+        <v>756</v>
       </c>
       <c r="B569" t="s">
-        <v>902</v>
+        <v>757</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>44</v>
+        <v>1078</v>
       </c>
       <c r="B570" t="s">
-        <v>1125</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>1070</v>
+        <v>67</v>
       </c>
       <c r="B571" t="s">
-        <v>1071</v>
+        <v>597</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>324</v>
+        <v>68</v>
       </c>
       <c r="B572" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>325</v>
+        <v>95</v>
       </c>
       <c r="B573" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>849</v>
+        <v>289</v>
       </c>
       <c r="B574" t="s">
-        <v>850</v>
+        <v>600</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>887</v>
+        <v>297</v>
       </c>
       <c r="B575" t="s">
-        <v>888</v>
+        <v>601</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>1237</v>
+        <v>264</v>
       </c>
       <c r="B576" t="s">
-        <v>1238</v>
+        <v>602</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>869</v>
+        <v>193</v>
       </c>
       <c r="B577" t="s">
-        <v>870</v>
+        <v>603</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>33</v>
+        <v>901</v>
       </c>
       <c r="B578" t="s">
-        <v>606</v>
+        <v>902</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B579" t="s">
-        <v>607</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>1143</v>
+        <v>1070</v>
       </c>
       <c r="B580" t="s">
-        <v>1144</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="B581" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>257</v>
+        <v>325</v>
       </c>
       <c r="B582" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>302</v>
+        <v>849</v>
       </c>
       <c r="B583" t="s">
-        <v>610</v>
+        <v>850</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>228</v>
+        <v>887</v>
       </c>
       <c r="B584" t="s">
-        <v>611</v>
+        <v>888</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>17</v>
+        <v>1237</v>
       </c>
       <c r="B585" t="s">
-        <v>18</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>655</v>
+        <v>869</v>
       </c>
       <c r="B586" t="s">
-        <v>743</v>
+        <v>870</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>785</v>
+        <v>33</v>
       </c>
       <c r="B587" t="s">
-        <v>786</v>
+        <v>606</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>142</v>
+        <v>36</v>
       </c>
       <c r="B588" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>1178</v>
+        <v>1143</v>
       </c>
       <c r="B589" t="s">
-        <v>1179</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>956</v>
+        <v>309</v>
       </c>
       <c r="B590" t="s">
-        <v>957</v>
+        <v>608</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>54</v>
+        <v>257</v>
       </c>
       <c r="B591" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>265</v>
+        <v>302</v>
       </c>
       <c r="B592" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>976</v>
+        <v>228</v>
       </c>
       <c r="B593" t="s">
-        <v>975</v>
+        <v>611</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="B594" t="s">
-        <v>615</v>
+        <v>18</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>1217</v>
+        <v>655</v>
       </c>
       <c r="B595" t="s">
-        <v>1218</v>
+        <v>743</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>185</v>
+        <v>785</v>
       </c>
       <c r="B596" t="s">
-        <v>616</v>
+        <v>786</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="B597" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>43</v>
+        <v>1178</v>
       </c>
       <c r="B598" t="s">
-        <v>1146</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>40</v>
+        <v>956</v>
       </c>
       <c r="B599" t="s">
-        <v>1124</v>
+        <v>957</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>1170</v>
+        <v>54</v>
       </c>
       <c r="B600" t="s">
-        <v>1171</v>
+        <v>613</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>165</v>
+        <v>265</v>
       </c>
       <c r="B601" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>1299</v>
+        <v>976</v>
       </c>
       <c r="B602" t="s">
-        <v>1300</v>
+        <v>975</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>1301</v>
+        <v>56</v>
       </c>
       <c r="B603" t="s">
-        <v>1302</v>
+        <v>615</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>12</v>
+        <v>1217</v>
       </c>
       <c r="B604" t="s">
-        <v>11</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>250</v>
+        <v>185</v>
       </c>
       <c r="B605" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>27</v>
+        <v>159</v>
       </c>
       <c r="B606" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>1040</v>
+        <v>43</v>
       </c>
       <c r="B607" t="s">
-        <v>1041</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B608" t="s">
-        <v>621</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>1205</v>
+        <v>1170</v>
       </c>
       <c r="B609" t="s">
-        <v>1206</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>255</v>
+        <v>165</v>
       </c>
       <c r="B610" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>795</v>
+        <v>1299</v>
       </c>
       <c r="B611" t="s">
-        <v>796</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>267</v>
+        <v>1301</v>
       </c>
       <c r="B612" t="s">
-        <v>623</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>661</v>
+        <v>12</v>
       </c>
       <c r="B613" t="s">
-        <v>744</v>
+        <v>11</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>662</v>
+        <v>250</v>
       </c>
       <c r="B614" t="s">
-        <v>745</v>
+        <v>619</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>139</v>
+        <v>27</v>
       </c>
       <c r="B615" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>7</v>
+        <v>1040</v>
       </c>
       <c r="B616" t="s">
-        <v>2</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>105</v>
+        <v>28</v>
       </c>
       <c r="B617" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>1034</v>
+        <v>1205</v>
       </c>
       <c r="B618" t="s">
-        <v>1123</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>865</v>
+        <v>255</v>
       </c>
       <c r="B619" t="s">
-        <v>866</v>
+        <v>622</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>1035</v>
+        <v>795</v>
       </c>
       <c r="B620" t="s">
-        <v>1122</v>
+        <v>796</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="B621" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
-        <v>8</v>
+        <v>661</v>
       </c>
       <c r="B622" t="s">
-        <v>11</v>
+        <v>744</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
-        <v>335</v>
+        <v>662</v>
       </c>
       <c r="B623" t="s">
-        <v>627</v>
+        <v>745</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
-        <v>332</v>
+        <v>139</v>
       </c>
       <c r="B624" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
-        <v>259</v>
+        <v>7</v>
       </c>
       <c r="B625" t="s">
-        <v>629</v>
+        <v>2</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
-        <v>319</v>
+        <v>105</v>
       </c>
       <c r="B626" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
-        <v>859</v>
+        <v>1034</v>
       </c>
       <c r="B627" t="s">
-        <v>860</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
-        <v>1174</v>
+        <v>865</v>
       </c>
       <c r="B628" t="s">
-        <v>1175</v>
+        <v>866</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
-        <v>268</v>
+        <v>1035</v>
       </c>
       <c r="B629" t="s">
-        <v>631</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="B630" t="s">
-        <v>1117</v>
+        <v>626</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>274</v>
+        <v>8</v>
       </c>
       <c r="B631" t="s">
-        <v>1118</v>
+        <v>11</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>270</v>
+        <v>335</v>
       </c>
       <c r="B632" t="s">
-        <v>1119</v>
+        <v>627</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
-        <v>273</v>
+        <v>332</v>
       </c>
       <c r="B633" t="s">
-        <v>1120</v>
+        <v>628</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="B634" t="s">
-        <v>1121</v>
+        <v>629</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
-        <v>272</v>
+        <v>319</v>
       </c>
       <c r="B635" t="s">
-        <v>1116</v>
+        <v>630</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
-        <v>92</v>
+        <v>859</v>
       </c>
       <c r="B636" t="s">
-        <v>632</v>
+        <v>860</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
-        <v>200</v>
+        <v>1174</v>
       </c>
       <c r="B637" t="s">
-        <v>633</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
-        <v>203</v>
+        <v>268</v>
       </c>
       <c r="B638" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
-        <v>1227</v>
+        <v>271</v>
       </c>
       <c r="B639" t="s">
-        <v>1228</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
-        <v>172</v>
+        <v>274</v>
       </c>
       <c r="B640" t="s">
-        <v>635</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
-        <v>693</v>
+        <v>270</v>
       </c>
       <c r="B641" t="s">
-        <v>746</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="B642" t="s">
-        <v>636</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
-        <v>694</v>
+        <v>269</v>
       </c>
       <c r="B643" t="s">
-        <v>747</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
-        <v>189</v>
+        <v>272</v>
       </c>
       <c r="B644" t="s">
-        <v>637</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
-        <v>989</v>
+        <v>92</v>
       </c>
       <c r="B645" t="s">
-        <v>990</v>
+        <v>632</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
-        <v>311</v>
+        <v>200</v>
       </c>
       <c r="B646" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
-        <v>312</v>
+        <v>203</v>
       </c>
       <c r="B647" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
-        <v>1033</v>
+        <v>1227</v>
       </c>
       <c r="B648" t="s">
-        <v>1115</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
-        <v>1005</v>
+        <v>172</v>
       </c>
       <c r="B649" t="s">
-        <v>1006</v>
+        <v>635</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
-        <v>81</v>
+        <v>693</v>
       </c>
       <c r="B650" t="s">
-        <v>640</v>
+        <v>746</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
-        <v>651</v>
+        <v>252</v>
       </c>
       <c r="B651" t="s">
-        <v>748</v>
+        <v>636</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
-        <v>922</v>
+        <v>694</v>
       </c>
       <c r="B652" t="s">
-        <v>923</v>
+        <v>747</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
-        <v>642</v>
+        <v>189</v>
       </c>
       <c r="B653" t="s">
-        <v>749</v>
+        <v>637</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
-        <v>969</v>
+        <v>989</v>
       </c>
       <c r="B654" t="s">
-        <v>970</v>
+        <v>990</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
+        <v>311</v>
+      </c>
+      <c r="B655" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A656" t="s">
+        <v>312</v>
+      </c>
+      <c r="B656" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A657" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B657" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A658" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B658" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A659" t="s">
+        <v>81</v>
+      </c>
+      <c r="B659" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A660" t="s">
+        <v>651</v>
+      </c>
+      <c r="B660" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A661" t="s">
+        <v>922</v>
+      </c>
+      <c r="B661" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A662" t="s">
+        <v>642</v>
+      </c>
+      <c r="B662" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A663" t="s">
+        <v>969</v>
+      </c>
+      <c r="B663" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A664" t="s">
         <v>1162</v>
       </c>
-      <c r="B655" t="s">
+      <c r="B664" t="s">
         <v>1163</v>
       </c>
     </row>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81CA7E01-AD57-46DD-AEF2-6451C1E4443C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C2FEDE-6C86-4950-9DBE-503BD9AB6D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="1321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="1337">
   <si>
     <t>trigger</t>
   </si>
@@ -3165,12 +3165,6 @@
     <t>non-specific</t>
   </si>
   <si>
-    <t>com</t>
-  </si>
-  <si>
-    <t>complete</t>
-  </si>
-  <si>
     <t>rhv</t>
   </si>
   <si>
@@ -3333,18 +3327,6 @@
     <t>left hepatic duct</t>
   </si>
   <si>
-    <t>asd</t>
-  </si>
-  <si>
-    <t>anterior sectoral duct</t>
-  </si>
-  <si>
-    <t>psd</t>
-  </si>
-  <si>
-    <t>posterior sectoral duct</t>
-  </si>
-  <si>
     <t>allg</t>
   </si>
   <si>
@@ -3988,6 +3970,72 @@
   </si>
   <si>
     <t>perinephric</t>
+  </si>
+  <si>
+    <t>cic</t>
+  </si>
+  <si>
+    <t>rasd</t>
+  </si>
+  <si>
+    <t>right anterior sectoral duct</t>
+  </si>
+  <si>
+    <t>rpsd</t>
+  </si>
+  <si>
+    <t>right posterior sectoral duct</t>
+  </si>
+  <si>
+    <t>cicatrization collapse</t>
+  </si>
+  <si>
+    <t>cpe</t>
+  </si>
+  <si>
+    <t>Centriacinar and paraseptal emphysematous changes</t>
+  </si>
+  <si>
+    <t>empc</t>
+  </si>
+  <si>
+    <t>emphysematous changes</t>
+  </si>
+  <si>
+    <t>boo</t>
+  </si>
+  <si>
+    <t>bladder outlet obstruction</t>
+  </si>
+  <si>
+    <t>goo</t>
+  </si>
+  <si>
+    <t>gastric outlet obstruction</t>
+  </si>
+  <si>
+    <t>thad</t>
+  </si>
+  <si>
+    <t>isod</t>
+  </si>
+  <si>
+    <t>isodense</t>
+  </si>
+  <si>
+    <t>deg</t>
+  </si>
+  <si>
+    <t>degenerative</t>
+  </si>
+  <si>
+    <t>Geographic arterial phase hyperenhancement is seen in segment ... of the liver without associated mass effect or contour abnormality, becoming isodense on portal venous phase - suggestive of transient hepatic attenuation difference (THAD)</t>
+  </si>
+  <si>
+    <t>colla</t>
+  </si>
+  <si>
+    <t>collateral</t>
   </si>
 </sst>
 </file>
@@ -4049,10 +4097,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B664" totalsRowShown="0">
-  <autoFilter ref="A1:B664" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B664">
-    <sortCondition ref="A1:A664"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B672" totalsRowShown="0">
+  <autoFilter ref="A1:B672" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B672">
+    <sortCondition ref="A1:A672"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4325,7 +4373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B664"/>
+  <dimension ref="A1:B672"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -4350,10 +4398,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
       <c r="B3" t="s">
-        <v>1197</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -4478,10 +4526,10 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="B19" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
@@ -4502,10 +4550,10 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B22" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
@@ -4558,7 +4606,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="B29" t="s">
         <v>695</v>
@@ -4574,7 +4622,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="B31" t="s">
         <v>1013</v>
@@ -4582,10 +4630,10 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>1182</v>
+        <v>1176</v>
       </c>
       <c r="B32" t="s">
-        <v>1183</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
@@ -4662,234 +4710,234 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>1213</v>
+        <v>1207</v>
       </c>
       <c r="B42" t="s">
-        <v>1214</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B43" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>1102</v>
+        <v>660</v>
       </c>
       <c r="B44" t="s">
-        <v>1103</v>
+        <v>696</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>660</v>
+        <v>1016</v>
       </c>
       <c r="B45" t="s">
-        <v>696</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>1016</v>
+        <v>166</v>
       </c>
       <c r="B46" t="s">
-        <v>1017</v>
+        <v>360</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>166</v>
+        <v>291</v>
       </c>
       <c r="B47" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="B48" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>310</v>
+        <v>239</v>
       </c>
       <c r="B49" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>239</v>
+        <v>195</v>
       </c>
       <c r="B50" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>195</v>
+        <v>246</v>
       </c>
       <c r="B51" t="s">
-        <v>364</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>246</v>
+        <v>647</v>
       </c>
       <c r="B52" t="s">
-        <v>1140</v>
+        <v>697</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>647</v>
+        <v>240</v>
       </c>
       <c r="B53" t="s">
-        <v>697</v>
+        <v>363</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>240</v>
+        <v>861</v>
       </c>
       <c r="B54" t="s">
-        <v>363</v>
+        <v>862</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>861</v>
+        <v>987</v>
       </c>
       <c r="B55" t="s">
-        <v>862</v>
+        <v>988</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>987</v>
+        <v>774</v>
       </c>
       <c r="B56" t="s">
-        <v>988</v>
+        <v>775</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="B57" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>776</v>
+        <v>300</v>
       </c>
       <c r="B58" t="s">
-        <v>777</v>
+        <v>365</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>300</v>
+        <v>1141</v>
       </c>
       <c r="B59" t="s">
-        <v>365</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>1147</v>
+        <v>303</v>
       </c>
       <c r="B60" t="s">
-        <v>1148</v>
+        <v>366</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>303</v>
+        <v>230</v>
       </c>
       <c r="B61" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B62" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>232</v>
+        <v>789</v>
       </c>
       <c r="B63" t="s">
-        <v>368</v>
+        <v>790</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>789</v>
+        <v>318</v>
       </c>
       <c r="B64" t="s">
-        <v>790</v>
+        <v>369</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>318</v>
+        <v>762</v>
       </c>
       <c r="B65" t="s">
-        <v>369</v>
+        <v>763</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>762</v>
+        <v>61</v>
       </c>
       <c r="B66" t="s">
-        <v>763</v>
+        <v>370</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B67" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B68" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>58</v>
+        <v>885</v>
       </c>
       <c r="B69" t="s">
-        <v>372</v>
+        <v>886</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>885</v>
+        <v>1325</v>
       </c>
       <c r="B70" t="s">
-        <v>886</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
@@ -4910,10 +4958,10 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="B73" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
@@ -4934,10 +4982,10 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>1239</v>
+        <v>1233</v>
       </c>
       <c r="B76" t="s">
-        <v>1240</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
@@ -4950,10 +4998,10 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>1241</v>
+        <v>1235</v>
       </c>
       <c r="B78" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
@@ -4966,10 +5014,10 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="B80" t="s">
-        <v>1244</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
@@ -4982,10 +5030,10 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>1245</v>
+        <v>1239</v>
       </c>
       <c r="B82" t="s">
-        <v>1246</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
@@ -4998,10 +5046,10 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>1247</v>
+        <v>1241</v>
       </c>
       <c r="B84" t="s">
-        <v>1248</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
@@ -5014,10 +5062,10 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>1249</v>
+        <v>1243</v>
       </c>
       <c r="B86" t="s">
-        <v>1252</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
@@ -5030,10 +5078,10 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>1250</v>
+        <v>1244</v>
       </c>
       <c r="B88" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
@@ -5046,10 +5094,10 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="B90" t="s">
-        <v>1254</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
@@ -5150,10 +5198,10 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>1159</v>
+        <v>1153</v>
       </c>
       <c r="B103" t="s">
-        <v>1160</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
@@ -5185,7 +5233,7 @@
         <v>41</v>
       </c>
       <c r="B107" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
@@ -5270,10 +5318,10 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
       <c r="B118" t="s">
-        <v>1177</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
@@ -5302,4346 +5350,4410 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>124</v>
+        <v>1315</v>
       </c>
       <c r="B122" t="s">
-        <v>396</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B123" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="B124" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>967</v>
+        <v>155</v>
       </c>
       <c r="B125" t="s">
-        <v>968</v>
+        <v>397</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>84</v>
+        <v>967</v>
       </c>
       <c r="B126" t="s">
-        <v>398</v>
+        <v>968</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>965</v>
+        <v>84</v>
       </c>
       <c r="B127" t="s">
-        <v>966</v>
+        <v>398</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>103</v>
+        <v>965</v>
       </c>
       <c r="B128" t="s">
-        <v>399</v>
+        <v>966</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>198</v>
+        <v>103</v>
       </c>
       <c r="B129" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>314</v>
+        <v>198</v>
       </c>
       <c r="B130" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>104</v>
+        <v>314</v>
       </c>
       <c r="B131" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="B132" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="B133" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B134" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>1046</v>
+        <v>102</v>
       </c>
       <c r="B135" t="s">
-        <v>1047</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>930</v>
+        <v>1335</v>
       </c>
       <c r="B136" t="s">
-        <v>931</v>
+        <v>405</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B137" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>162</v>
+        <v>928</v>
       </c>
       <c r="B138" t="s">
-        <v>406</v>
+        <v>929</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>1153</v>
+        <v>162</v>
       </c>
       <c r="B139" t="s">
-        <v>1154</v>
+        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>837</v>
+        <v>1147</v>
       </c>
       <c r="B140" t="s">
-        <v>838</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="B141" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>1084</v>
+        <v>839</v>
       </c>
       <c r="B142" t="s">
-        <v>1085</v>
+        <v>840</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>665</v>
+        <v>1321</v>
       </c>
       <c r="B143" t="s">
-        <v>708</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>646</v>
+        <v>1082</v>
       </c>
       <c r="B144" t="s">
-        <v>709</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>940</v>
+        <v>665</v>
       </c>
       <c r="B145" t="s">
-        <v>941</v>
+        <v>708</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>1255</v>
+        <v>646</v>
       </c>
       <c r="B146" t="s">
-        <v>1267</v>
+        <v>709</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>1264</v>
+        <v>940</v>
       </c>
       <c r="B147" t="s">
-        <v>1276</v>
+        <v>941</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>683</v>
+        <v>1249</v>
       </c>
       <c r="B148" t="s">
-        <v>710</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>1265</v>
+        <v>1258</v>
       </c>
       <c r="B149" t="s">
-        <v>1277</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B150" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>1266</v>
+        <v>1259</v>
       </c>
       <c r="B151" t="s">
-        <v>1278</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B152" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>1256</v>
+        <v>1260</v>
       </c>
       <c r="B153" t="s">
-        <v>1268</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="B154" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>1257</v>
+        <v>1250</v>
       </c>
       <c r="B155" t="s">
-        <v>1269</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B156" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>1258</v>
+        <v>1251</v>
       </c>
       <c r="B157" t="s">
-        <v>1270</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B158" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>1259</v>
+        <v>1252</v>
       </c>
       <c r="B159" t="s">
-        <v>1271</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B160" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>1260</v>
+        <v>1253</v>
       </c>
       <c r="B161" t="s">
-        <v>1272</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B162" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>1261</v>
+        <v>1254</v>
       </c>
       <c r="B163" t="s">
-        <v>1273</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B164" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>1262</v>
+        <v>1255</v>
       </c>
       <c r="B165" t="s">
-        <v>1274</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B166" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>1263</v>
+        <v>1256</v>
       </c>
       <c r="B167" t="s">
-        <v>1275</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B168" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>175</v>
+        <v>1257</v>
       </c>
       <c r="B169" t="s">
-        <v>407</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>211</v>
+        <v>682</v>
       </c>
       <c r="B170" t="s">
-        <v>408</v>
+        <v>720</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>213</v>
+        <v>175</v>
       </c>
       <c r="B171" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>1209</v>
+        <v>211</v>
       </c>
       <c r="B172" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>149</v>
+        <v>213</v>
       </c>
       <c r="B173" t="s">
-        <v>1212</v>
+        <v>409</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>247</v>
+        <v>1332</v>
       </c>
       <c r="B174" t="s">
-        <v>411</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>245</v>
+        <v>1203</v>
       </c>
       <c r="B175" t="s">
-        <v>1138</v>
+        <v>410</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>336</v>
+        <v>149</v>
       </c>
       <c r="B176" t="s">
-        <v>412</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>650</v>
+        <v>247</v>
       </c>
       <c r="B177" t="s">
-        <v>721</v>
+        <v>411</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>91</v>
+        <v>245</v>
       </c>
       <c r="B178" t="s">
-        <v>413</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>266</v>
+        <v>336</v>
       </c>
       <c r="B179" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>1096</v>
+        <v>650</v>
       </c>
       <c r="B180" t="s">
-        <v>1097</v>
+        <v>721</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>799</v>
+        <v>91</v>
       </c>
       <c r="B181" t="s">
-        <v>800</v>
+        <v>413</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>1168</v>
+        <v>266</v>
       </c>
       <c r="B182" t="s">
-        <v>1169</v>
+        <v>414</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>295</v>
+        <v>1094</v>
       </c>
       <c r="B183" t="s">
-        <v>415</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>1086</v>
+        <v>799</v>
       </c>
       <c r="B184" t="s">
-        <v>1087</v>
+        <v>800</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
-        <v>1092</v>
+        <v>1162</v>
       </c>
       <c r="B185" t="s">
-        <v>1093</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>151</v>
+        <v>295</v>
       </c>
       <c r="B186" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
-        <v>961</v>
+        <v>1084</v>
       </c>
       <c r="B187" t="s">
-        <v>962</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>813</v>
+        <v>1090</v>
       </c>
       <c r="B188" t="s">
-        <v>814</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>932</v>
+        <v>151</v>
       </c>
       <c r="B189" t="s">
-        <v>933</v>
+        <v>416</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>833</v>
+        <v>961</v>
       </c>
       <c r="B190" t="s">
-        <v>834</v>
+        <v>962</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>793</v>
+        <v>813</v>
       </c>
       <c r="B191" t="s">
-        <v>794</v>
+        <v>814</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>754</v>
+        <v>932</v>
       </c>
       <c r="B192" t="s">
-        <v>755</v>
+        <v>933</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>100</v>
+        <v>833</v>
       </c>
       <c r="B193" t="s">
-        <v>417</v>
+        <v>834</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>1042</v>
+        <v>793</v>
       </c>
       <c r="B194" t="s">
-        <v>1043</v>
+        <v>794</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>154</v>
+        <v>754</v>
       </c>
       <c r="B195" t="s">
-        <v>418</v>
+        <v>755</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>157</v>
+        <v>100</v>
       </c>
       <c r="B196" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>24</v>
+        <v>1042</v>
       </c>
       <c r="B197" t="s">
-        <v>1137</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>1164</v>
+        <v>154</v>
       </c>
       <c r="B198" t="s">
-        <v>1165</v>
+        <v>418</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>1076</v>
+        <v>157</v>
       </c>
       <c r="B199" t="s">
-        <v>1077</v>
+        <v>419</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>819</v>
+        <v>24</v>
       </c>
       <c r="B200" t="s">
-        <v>820</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>130</v>
+        <v>1158</v>
       </c>
       <c r="B201" t="s">
-        <v>420</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>322</v>
+        <v>1323</v>
       </c>
       <c r="B202" t="s">
-        <v>421</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>867</v>
+        <v>1074</v>
       </c>
       <c r="B203" t="s">
-        <v>868</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>1317</v>
+        <v>819</v>
       </c>
       <c r="B204" t="s">
-        <v>1318</v>
+        <v>820</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>183</v>
+        <v>130</v>
       </c>
       <c r="B205" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>1155</v>
+        <v>322</v>
       </c>
       <c r="B206" t="s">
-        <v>1156</v>
+        <v>421</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>1157</v>
+        <v>867</v>
       </c>
       <c r="B207" t="s">
-        <v>1158</v>
+        <v>868</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>891</v>
+        <v>1311</v>
       </c>
       <c r="B208" t="s">
-        <v>892</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>32</v>
+        <v>183</v>
       </c>
       <c r="B209" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>35</v>
+        <v>1149</v>
       </c>
       <c r="B210" t="s">
-        <v>424</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>1307</v>
+        <v>1151</v>
       </c>
       <c r="B211" t="s">
-        <v>1308</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>1233</v>
+        <v>891</v>
       </c>
       <c r="B212" t="s">
-        <v>1234</v>
+        <v>892</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>764</v>
+        <v>32</v>
       </c>
       <c r="B213" t="s">
-        <v>1010</v>
+        <v>423</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>169</v>
+        <v>35</v>
       </c>
       <c r="B214" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>170</v>
+        <v>1301</v>
       </c>
       <c r="B215" t="s">
-        <v>425</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>1011</v>
+        <v>1227</v>
       </c>
       <c r="B216" t="s">
-        <v>765</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>178</v>
+        <v>764</v>
       </c>
       <c r="B217" t="s">
-        <v>426</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>111</v>
+        <v>169</v>
       </c>
       <c r="B218" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>238</v>
+        <v>170</v>
       </c>
       <c r="B219" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>106</v>
+        <v>1011</v>
       </c>
       <c r="B220" t="s">
-        <v>429</v>
+        <v>765</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>109</v>
+        <v>178</v>
       </c>
       <c r="B221" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>179</v>
+        <v>111</v>
       </c>
       <c r="B222" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>667</v>
+        <v>238</v>
       </c>
       <c r="B223" t="s">
-        <v>722</v>
+        <v>428</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B224" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B225" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>242</v>
+        <v>179</v>
       </c>
       <c r="B226" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>226</v>
+        <v>667</v>
       </c>
       <c r="B227" t="s">
-        <v>435</v>
+        <v>722</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>177</v>
+        <v>97</v>
       </c>
       <c r="B228" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>182</v>
+        <v>110</v>
       </c>
       <c r="B229" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>1110</v>
+        <v>242</v>
       </c>
       <c r="B230" t="s">
-        <v>1111</v>
+        <v>434</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>977</v>
+        <v>226</v>
       </c>
       <c r="B231" t="s">
-        <v>978</v>
+        <v>435</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>979</v>
+        <v>177</v>
       </c>
       <c r="B232" t="s">
-        <v>980</v>
+        <v>436</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>1198</v>
+        <v>182</v>
       </c>
       <c r="B233" t="s">
-        <v>1199</v>
+        <v>437</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>1201</v>
+        <v>1104</v>
       </c>
       <c r="B234" t="s">
-        <v>1202</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>253</v>
+        <v>977</v>
       </c>
       <c r="B235" t="s">
-        <v>438</v>
+        <v>978</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>34</v>
+        <v>979</v>
       </c>
       <c r="B236" t="s">
-        <v>439</v>
+        <v>980</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>787</v>
+        <v>1192</v>
       </c>
       <c r="B237" t="s">
-        <v>788</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>180</v>
+        <v>1195</v>
       </c>
       <c r="B238" t="s">
-        <v>440</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="B239" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>857</v>
+        <v>34</v>
       </c>
       <c r="B240" t="s">
-        <v>858</v>
+        <v>439</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>116</v>
+        <v>787</v>
       </c>
       <c r="B241" t="s">
-        <v>442</v>
+        <v>788</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>208</v>
+        <v>180</v>
       </c>
       <c r="B242" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>1221</v>
+        <v>275</v>
       </c>
       <c r="B243" t="s">
-        <v>1222</v>
+        <v>441</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>1056</v>
+        <v>857</v>
       </c>
       <c r="B244" t="s">
-        <v>1057</v>
+        <v>858</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B245" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>641</v>
+        <v>208</v>
       </c>
       <c r="B246" t="s">
-        <v>723</v>
+        <v>443</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>815</v>
+        <v>1215</v>
       </c>
       <c r="B247" t="s">
-        <v>816</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>298</v>
+        <v>1054</v>
       </c>
       <c r="B248" t="s">
-        <v>445</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>643</v>
+        <v>118</v>
       </c>
       <c r="B249" t="s">
-        <v>724</v>
+        <v>444</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="B250" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>1036</v>
+        <v>1327</v>
       </c>
       <c r="B251" t="s">
-        <v>1037</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>90</v>
+        <v>815</v>
       </c>
       <c r="B252" t="s">
-        <v>446</v>
+        <v>816</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>88</v>
+        <v>298</v>
       </c>
       <c r="B253" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>89</v>
+        <v>643</v>
       </c>
       <c r="B254" t="s">
-        <v>448</v>
+        <v>724</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>1072</v>
+        <v>644</v>
       </c>
       <c r="B255" t="s">
-        <v>1073</v>
+        <v>725</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>23</v>
+        <v>1036</v>
       </c>
       <c r="B256" t="s">
-        <v>1136</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="B257" t="s">
-        <v>6</v>
+        <v>446</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>1141</v>
+        <v>88</v>
       </c>
       <c r="B258" t="s">
-        <v>1142</v>
+        <v>447</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>126</v>
+        <v>89</v>
       </c>
       <c r="B259" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>128</v>
+        <v>1070</v>
       </c>
       <c r="B260" t="s">
-        <v>450</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="B261" t="s">
-        <v>451</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>132</v>
+        <v>5</v>
       </c>
       <c r="B262" t="s">
-        <v>452</v>
+        <v>6</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>119</v>
+        <v>1135</v>
       </c>
       <c r="B263" t="s">
-        <v>453</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>277</v>
+        <v>126</v>
       </c>
       <c r="B264" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>1074</v>
+        <v>128</v>
       </c>
       <c r="B265" t="s">
-        <v>1075</v>
+        <v>450</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="B266" t="s">
-        <v>10</v>
+        <v>451</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B267" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B268" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>173</v>
+        <v>277</v>
       </c>
       <c r="B269" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>262</v>
+        <v>1072</v>
       </c>
       <c r="B270" t="s">
-        <v>458</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="B271" t="s">
-        <v>459</v>
+        <v>10</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>938</v>
+        <v>129</v>
       </c>
       <c r="B272" t="s">
-        <v>939</v>
+        <v>455</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>1172</v>
+        <v>127</v>
       </c>
       <c r="B273" t="s">
-        <v>1173</v>
+        <v>456</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="B274" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>167</v>
+        <v>262</v>
       </c>
       <c r="B275" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>835</v>
+        <v>77</v>
       </c>
       <c r="B276" t="s">
-        <v>836</v>
+        <v>459</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>791</v>
+        <v>938</v>
       </c>
       <c r="B277" t="s">
-        <v>792</v>
+        <v>939</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>304</v>
+        <v>1166</v>
       </c>
       <c r="B278" t="s">
-        <v>462</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>758</v>
+        <v>168</v>
       </c>
       <c r="B279" t="s">
-        <v>759</v>
+        <v>460</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>897</v>
+        <v>167</v>
       </c>
       <c r="B280" t="s">
-        <v>898</v>
+        <v>461</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>652</v>
+        <v>835</v>
       </c>
       <c r="B281" t="s">
-        <v>726</v>
+        <v>836</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>86</v>
+        <v>791</v>
       </c>
       <c r="B282" t="s">
-        <v>463</v>
+        <v>792</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>87</v>
+        <v>304</v>
       </c>
       <c r="B283" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>153</v>
+        <v>758</v>
       </c>
       <c r="B284" t="s">
-        <v>465</v>
+        <v>759</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>156</v>
+        <v>897</v>
       </c>
       <c r="B285" t="s">
-        <v>466</v>
+        <v>898</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>158</v>
+        <v>652</v>
       </c>
       <c r="B286" t="s">
-        <v>467</v>
+        <v>726</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>251</v>
+        <v>86</v>
       </c>
       <c r="B287" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>285</v>
+        <v>87</v>
       </c>
       <c r="B288" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>326</v>
+        <v>153</v>
       </c>
       <c r="B289" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>327</v>
+        <v>156</v>
       </c>
       <c r="B290" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>229</v>
+        <v>158</v>
       </c>
       <c r="B291" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>55</v>
+        <v>251</v>
       </c>
       <c r="B292" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>657</v>
+        <v>285</v>
       </c>
       <c r="B293" t="s">
-        <v>727</v>
+        <v>469</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>235</v>
+        <v>326</v>
       </c>
       <c r="B294" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>57</v>
+        <v>327</v>
       </c>
       <c r="B295" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="B296" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>766</v>
+        <v>55</v>
       </c>
       <c r="B297" t="s">
-        <v>1009</v>
+        <v>473</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>1012</v>
+        <v>657</v>
       </c>
       <c r="B298" t="s">
-        <v>767</v>
+        <v>727</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>164</v>
+        <v>235</v>
       </c>
       <c r="B299" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>201</v>
+        <v>57</v>
       </c>
       <c r="B300" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>204</v>
+        <v>236</v>
       </c>
       <c r="B301" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>313</v>
+        <v>766</v>
       </c>
       <c r="B302" t="s">
-        <v>480</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>873</v>
+        <v>1012</v>
       </c>
       <c r="B303" t="s">
-        <v>874</v>
+        <v>767</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>997</v>
+        <v>164</v>
       </c>
       <c r="B304" t="s">
-        <v>998</v>
+        <v>477</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>258</v>
+        <v>201</v>
       </c>
       <c r="B305" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>983</v>
+        <v>204</v>
       </c>
       <c r="B306" t="s">
-        <v>984</v>
+        <v>479</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>160</v>
+        <v>313</v>
       </c>
       <c r="B307" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>692</v>
+        <v>873</v>
       </c>
       <c r="B308" t="s">
-        <v>728</v>
+        <v>874</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>1166</v>
+        <v>997</v>
       </c>
       <c r="B309" t="s">
-        <v>1167</v>
+        <v>998</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>760</v>
+        <v>1330</v>
       </c>
       <c r="B310" t="s">
-        <v>761</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>895</v>
+        <v>258</v>
       </c>
       <c r="B311" t="s">
-        <v>896</v>
+        <v>481</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>893</v>
+        <v>983</v>
       </c>
       <c r="B312" t="s">
-        <v>894</v>
+        <v>984</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="B313" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>244</v>
+        <v>692</v>
       </c>
       <c r="B314" t="s">
-        <v>484</v>
+        <v>728</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>243</v>
+        <v>1160</v>
       </c>
       <c r="B315" t="s">
-        <v>485</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>1279</v>
+        <v>760</v>
       </c>
       <c r="B316" t="s">
-        <v>1284</v>
+        <v>761</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>686</v>
+        <v>895</v>
       </c>
       <c r="B317" t="s">
-        <v>729</v>
+        <v>896</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>1280</v>
+        <v>893</v>
       </c>
       <c r="B318" t="s">
-        <v>1285</v>
+        <v>894</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>687</v>
+        <v>184</v>
       </c>
       <c r="B319" t="s">
-        <v>730</v>
+        <v>483</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>1281</v>
+        <v>244</v>
       </c>
       <c r="B320" t="s">
-        <v>1286</v>
+        <v>484</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>688</v>
+        <v>243</v>
       </c>
       <c r="B321" t="s">
-        <v>731</v>
+        <v>485</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>1282</v>
+        <v>1273</v>
       </c>
       <c r="B322" t="s">
-        <v>1287</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="B323" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>1283</v>
+        <v>1274</v>
       </c>
       <c r="B324" t="s">
-        <v>1288</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B325" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>1192</v>
+        <v>1275</v>
       </c>
       <c r="B326" t="s">
-        <v>1193</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>280</v>
+        <v>688</v>
       </c>
       <c r="B327" t="s">
-        <v>486</v>
+        <v>731</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>281</v>
+        <v>1276</v>
       </c>
       <c r="B328" t="s">
-        <v>487</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>49</v>
+        <v>689</v>
       </c>
       <c r="B329" t="s">
-        <v>488</v>
+        <v>732</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>53</v>
+        <v>1277</v>
       </c>
       <c r="B330" t="s">
-        <v>489</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>136</v>
+        <v>690</v>
       </c>
       <c r="B331" t="s">
-        <v>491</v>
+        <v>733</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>72</v>
+        <v>1186</v>
       </c>
       <c r="B332" t="s">
-        <v>490</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>1190</v>
+        <v>280</v>
       </c>
       <c r="B333" t="s">
-        <v>1191</v>
+        <v>486</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>221</v>
+        <v>281</v>
       </c>
       <c r="B334" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>1194</v>
+        <v>49</v>
       </c>
       <c r="B335" t="s">
-        <v>1195</v>
+        <v>488</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="B336" t="s">
-        <v>16</v>
+        <v>489</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>1060</v>
+        <v>136</v>
       </c>
       <c r="B337" t="s">
-        <v>1061</v>
+        <v>491</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>920</v>
+        <v>72</v>
       </c>
       <c r="B338" t="s">
-        <v>921</v>
+        <v>490</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>108</v>
+        <v>1184</v>
       </c>
       <c r="B339" t="s">
-        <v>493</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="B340" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>328</v>
+        <v>1188</v>
       </c>
       <c r="B341" t="s">
-        <v>495</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>1100</v>
+        <v>15</v>
       </c>
       <c r="B342" t="s">
-        <v>1101</v>
+        <v>16</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="B343" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>121</v>
+        <v>920</v>
       </c>
       <c r="B344" t="s">
-        <v>496</v>
+        <v>921</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>750</v>
+        <v>108</v>
       </c>
       <c r="B345" t="s">
-        <v>751</v>
+        <v>493</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>781</v>
+        <v>241</v>
       </c>
       <c r="B346" t="s">
-        <v>782</v>
+        <v>494</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>134</v>
+        <v>328</v>
       </c>
       <c r="B347" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>63</v>
+        <v>1098</v>
       </c>
       <c r="B348" t="s">
-        <v>498</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>1313</v>
+        <v>1050</v>
       </c>
       <c r="B349" t="s">
-        <v>1314</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>224</v>
+        <v>121</v>
       </c>
       <c r="B350" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>25</v>
+        <v>750</v>
       </c>
       <c r="B351" t="s">
-        <v>500</v>
+        <v>751</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>26</v>
+        <v>781</v>
       </c>
       <c r="B352" t="s">
-        <v>501</v>
+        <v>782</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>207</v>
+        <v>134</v>
       </c>
       <c r="B353" t="s">
-        <v>1133</v>
+        <v>497</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>960</v>
+        <v>63</v>
       </c>
       <c r="B354" t="s">
-        <v>1134</v>
+        <v>498</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>1113</v>
+        <v>1307</v>
       </c>
       <c r="B355" t="s">
-        <v>1114</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="B356" t="s">
-        <v>1135</v>
+        <v>499</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>202</v>
+        <v>25</v>
       </c>
       <c r="B357" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>205</v>
+        <v>26</v>
       </c>
       <c r="B358" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>145</v>
+        <v>207</v>
       </c>
       <c r="B359" t="s">
-        <v>504</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>663</v>
+        <v>960</v>
       </c>
       <c r="B360" t="s">
-        <v>734</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>171</v>
+        <v>1107</v>
       </c>
       <c r="B361" t="s">
-        <v>505</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>1088</v>
+        <v>206</v>
       </c>
       <c r="B362" t="s">
-        <v>1089</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>263</v>
+        <v>202</v>
       </c>
       <c r="B363" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>1090</v>
+        <v>205</v>
       </c>
       <c r="B364" t="s">
-        <v>1091</v>
+        <v>503</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>80</v>
+        <v>145</v>
       </c>
       <c r="B365" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>65</v>
+        <v>663</v>
       </c>
       <c r="B366" t="s">
-        <v>508</v>
+        <v>734</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="B367" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>123</v>
+        <v>1086</v>
       </c>
       <c r="B368" t="s">
-        <v>510</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>192</v>
+        <v>263</v>
       </c>
       <c r="B369" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>231</v>
+        <v>1088</v>
       </c>
       <c r="B370" t="s">
-        <v>512</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>233</v>
+        <v>80</v>
       </c>
       <c r="B371" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>1200</v>
+        <v>65</v>
       </c>
       <c r="B372" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="B373" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>30</v>
+        <v>123</v>
       </c>
       <c r="B374" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>37</v>
+        <v>192</v>
       </c>
       <c r="B375" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>71</v>
+        <v>231</v>
       </c>
       <c r="B376" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>306</v>
+        <v>233</v>
       </c>
       <c r="B377" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>222</v>
+        <v>1194</v>
       </c>
       <c r="B378" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>315</v>
+        <v>31</v>
       </c>
       <c r="B379" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>278</v>
+        <v>30</v>
       </c>
       <c r="B380" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>279</v>
+        <v>37</v>
       </c>
       <c r="B381" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>831</v>
+        <v>71</v>
       </c>
       <c r="B382" t="s">
-        <v>832</v>
+        <v>517</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>48</v>
+        <v>306</v>
       </c>
       <c r="B383" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>146</v>
+        <v>222</v>
       </c>
       <c r="B384" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>52</v>
+        <v>315</v>
       </c>
       <c r="B385" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>223</v>
+        <v>278</v>
       </c>
       <c r="B386" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>1094</v>
+        <v>279</v>
       </c>
       <c r="B387" t="s">
-        <v>1095</v>
+        <v>522</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>1109</v>
+        <v>831</v>
       </c>
       <c r="B388" t="s">
-        <v>1112</v>
+        <v>832</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>1050</v>
+        <v>48</v>
       </c>
       <c r="B389" t="s">
-        <v>1051</v>
+        <v>523</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="B390" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>248</v>
+        <v>52</v>
       </c>
       <c r="B391" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="B392" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>94</v>
+        <v>1092</v>
       </c>
       <c r="B393" t="s">
-        <v>530</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>1064</v>
+        <v>1103</v>
       </c>
       <c r="B394" t="s">
-        <v>1065</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>212</v>
+        <v>1048</v>
       </c>
       <c r="B395" t="s">
-        <v>531</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>1225</v>
+        <v>96</v>
       </c>
       <c r="B396" t="s">
-        <v>1226</v>
+        <v>527</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>916</v>
+        <v>248</v>
       </c>
       <c r="B397" t="s">
-        <v>917</v>
+        <v>528</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>914</v>
+        <v>249</v>
       </c>
       <c r="B398" t="s">
-        <v>915</v>
+        <v>529</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>918</v>
+        <v>94</v>
       </c>
       <c r="B399" t="s">
-        <v>919</v>
+        <v>530</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>330</v>
+        <v>1062</v>
       </c>
       <c r="B400" t="s">
-        <v>532</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>1066</v>
+        <v>212</v>
       </c>
       <c r="B401" t="s">
-        <v>1067</v>
+        <v>531</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>995</v>
+        <v>1219</v>
       </c>
       <c r="B402" t="s">
-        <v>996</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>991</v>
+        <v>916</v>
       </c>
       <c r="B403" t="s">
-        <v>992</v>
+        <v>917</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>993</v>
+        <v>914</v>
       </c>
       <c r="B404" t="s">
-        <v>994</v>
+        <v>915</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>82</v>
+        <v>918</v>
       </c>
       <c r="B405" t="s">
-        <v>533</v>
+        <v>919</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>772</v>
+        <v>330</v>
       </c>
       <c r="B406" t="s">
-        <v>773</v>
+        <v>532</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>197</v>
+        <v>1064</v>
       </c>
       <c r="B407" t="s">
-        <v>534</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>654</v>
+        <v>995</v>
       </c>
       <c r="B408" t="s">
-        <v>735</v>
+        <v>996</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>821</v>
+        <v>991</v>
       </c>
       <c r="B409" t="s">
-        <v>822</v>
+        <v>992</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>1068</v>
+        <v>993</v>
       </c>
       <c r="B410" t="s">
-        <v>1069</v>
+        <v>994</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="B411" t="s">
-        <v>4</v>
+        <v>533</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>958</v>
+        <v>772</v>
       </c>
       <c r="B412" t="s">
-        <v>4</v>
+        <v>773</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>959</v>
+        <v>197</v>
       </c>
       <c r="B413" t="s">
-        <v>4</v>
+        <v>534</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="B414" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>1305</v>
+        <v>821</v>
       </c>
       <c r="B415" t="s">
-        <v>1306</v>
+        <v>822</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>770</v>
+        <v>1066</v>
       </c>
       <c r="B416" t="s">
-        <v>771</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>85</v>
+        <v>3</v>
       </c>
       <c r="B417" t="s">
-        <v>535</v>
+        <v>4</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>1062</v>
+        <v>958</v>
       </c>
       <c r="B418" t="s">
-        <v>1063</v>
+        <v>4</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>829</v>
+        <v>959</v>
       </c>
       <c r="B419" t="s">
-        <v>830</v>
+        <v>4</v>
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>809</v>
+        <v>664</v>
       </c>
       <c r="B420" t="s">
-        <v>810</v>
+        <v>736</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>187</v>
+        <v>1299</v>
       </c>
       <c r="B421" t="s">
-        <v>536</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>827</v>
+        <v>770</v>
       </c>
       <c r="B422" t="s">
-        <v>828</v>
+        <v>771</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>934</v>
+        <v>85</v>
       </c>
       <c r="B423" t="s">
-        <v>1130</v>
+        <v>535</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>863</v>
+        <v>1060</v>
       </c>
       <c r="B424" t="s">
-        <v>864</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>1044</v>
+        <v>829</v>
       </c>
       <c r="B425" t="s">
-        <v>1045</v>
+        <v>830</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>798</v>
+        <v>809</v>
       </c>
       <c r="B426" t="s">
-        <v>1131</v>
+        <v>810</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>797</v>
+        <v>187</v>
       </c>
       <c r="B427" t="s">
-        <v>1132</v>
+        <v>536</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>13</v>
+        <v>827</v>
       </c>
       <c r="B428" t="s">
-        <v>14</v>
+        <v>828</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>817</v>
+        <v>934</v>
       </c>
       <c r="B429" t="s">
-        <v>818</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>1235</v>
+        <v>863</v>
       </c>
       <c r="B430" t="s">
-        <v>1236</v>
+        <v>864</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>186</v>
+        <v>1044</v>
       </c>
       <c r="B431" t="s">
-        <v>537</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>811</v>
+        <v>798</v>
       </c>
       <c r="B432" t="s">
-        <v>812</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>320</v>
+        <v>797</v>
       </c>
       <c r="B433" t="s">
-        <v>538</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>656</v>
+        <v>13</v>
       </c>
       <c r="B434" t="s">
-        <v>737</v>
+        <v>14</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>855</v>
+        <v>817</v>
       </c>
       <c r="B435" t="s">
-        <v>856</v>
+        <v>818</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>658</v>
+        <v>1229</v>
       </c>
       <c r="B436" t="s">
-        <v>738</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>653</v>
+        <v>186</v>
       </c>
       <c r="B437" t="s">
-        <v>739</v>
+        <v>537</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>1207</v>
+        <v>811</v>
       </c>
       <c r="B438" t="s">
-        <v>1208</v>
+        <v>812</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="B439" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>260</v>
+        <v>656</v>
       </c>
       <c r="B440" t="s">
-        <v>540</v>
+        <v>737</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>261</v>
+        <v>855</v>
       </c>
       <c r="B441" t="s">
-        <v>541</v>
+        <v>856</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>188</v>
+        <v>658</v>
       </c>
       <c r="B442" t="s">
-        <v>542</v>
+        <v>738</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>190</v>
+        <v>653</v>
       </c>
       <c r="B443" t="s">
-        <v>543</v>
+        <v>739</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>936</v>
+        <v>1201</v>
       </c>
       <c r="B444" t="s">
-        <v>937</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>1031</v>
+        <v>256</v>
       </c>
       <c r="B445" t="s">
-        <v>1032</v>
+        <v>539</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>1223</v>
+        <v>260</v>
       </c>
       <c r="B446" t="s">
-        <v>1224</v>
+        <v>540</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>209</v>
+        <v>261</v>
       </c>
       <c r="B447" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>1315</v>
+        <v>188</v>
       </c>
       <c r="B448" t="s">
-        <v>1316</v>
+        <v>542</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>851</v>
+        <v>190</v>
       </c>
       <c r="B449" t="s">
-        <v>852</v>
+        <v>543</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>143</v>
+        <v>936</v>
       </c>
       <c r="B450" t="s">
-        <v>545</v>
+        <v>937</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>140</v>
+        <v>1031</v>
       </c>
       <c r="B451" t="s">
-        <v>546</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>1203</v>
+        <v>1217</v>
       </c>
       <c r="B452" t="s">
-        <v>1204</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>1303</v>
+        <v>209</v>
       </c>
       <c r="B453" t="s">
-        <v>1304</v>
+        <v>544</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>254</v>
+        <v>1309</v>
       </c>
       <c r="B454" t="s">
-        <v>547</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>331</v>
+        <v>851</v>
       </c>
       <c r="B455" t="s">
-        <v>548</v>
+        <v>852</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="B456" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>234</v>
+        <v>140</v>
       </c>
       <c r="B457" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>73</v>
+        <v>1197</v>
       </c>
       <c r="B458" t="s">
-        <v>551</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>342</v>
+        <v>1297</v>
       </c>
       <c r="B459" t="s">
-        <v>552</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>308</v>
+        <v>254</v>
       </c>
       <c r="B460" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>843</v>
+        <v>331</v>
       </c>
       <c r="B461" t="s">
-        <v>844</v>
+        <v>548</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>845</v>
+        <v>210</v>
       </c>
       <c r="B462" t="s">
-        <v>846</v>
+        <v>549</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="B463" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>909</v>
+        <v>73</v>
       </c>
       <c r="B464" t="s">
-        <v>910</v>
+        <v>551</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>963</v>
+        <v>342</v>
       </c>
       <c r="B465" t="s">
-        <v>964</v>
+        <v>552</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>1188</v>
+        <v>308</v>
       </c>
       <c r="B466" t="s">
-        <v>1189</v>
+        <v>553</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>227</v>
+        <v>843</v>
       </c>
       <c r="B467" t="s">
-        <v>555</v>
+        <v>844</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>334</v>
+        <v>845</v>
       </c>
       <c r="B468" t="s">
-        <v>1161</v>
+        <v>846</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>971</v>
+        <v>220</v>
       </c>
       <c r="B469" t="s">
-        <v>972</v>
+        <v>554</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>778</v>
+        <v>909</v>
       </c>
       <c r="B470" t="s">
-        <v>779</v>
+        <v>910</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>294</v>
+        <v>963</v>
       </c>
       <c r="B471" t="s">
-        <v>556</v>
+        <v>964</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>952</v>
+        <v>1182</v>
       </c>
       <c r="B472" t="s">
-        <v>953</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>339</v>
+        <v>227</v>
       </c>
       <c r="B473" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>780</v>
+        <v>334</v>
       </c>
       <c r="B474" t="s">
-        <v>779</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>1319</v>
+        <v>971</v>
       </c>
       <c r="B475" t="s">
-        <v>1320</v>
+        <v>972</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>340</v>
+        <v>778</v>
       </c>
       <c r="B476" t="s">
-        <v>558</v>
+        <v>779</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>341</v>
+        <v>294</v>
       </c>
       <c r="B477" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>645</v>
+        <v>952</v>
       </c>
       <c r="B478" t="s">
-        <v>740</v>
+        <v>953</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>39</v>
+        <v>339</v>
       </c>
       <c r="B479" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>38</v>
+        <v>780</v>
       </c>
       <c r="B480" t="s">
-        <v>1129</v>
+        <v>779</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>343</v>
+        <v>1313</v>
       </c>
       <c r="B481" t="s">
-        <v>561</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>107</v>
+        <v>340</v>
       </c>
       <c r="B482" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>1029</v>
+        <v>341</v>
       </c>
       <c r="B483" t="s">
-        <v>1030</v>
+        <v>559</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>903</v>
+        <v>645</v>
       </c>
       <c r="B484" t="s">
-        <v>904</v>
+        <v>740</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>117</v>
+        <v>39</v>
       </c>
       <c r="B485" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>1025</v>
+        <v>38</v>
       </c>
       <c r="B486" t="s">
-        <v>1026</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>98</v>
+        <v>343</v>
       </c>
       <c r="B487" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B488" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>666</v>
+        <v>1029</v>
       </c>
       <c r="B489" t="s">
-        <v>741</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>1107</v>
+        <v>903</v>
       </c>
       <c r="B490" t="s">
-        <v>1024</v>
+        <v>904</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>823</v>
+        <v>117</v>
       </c>
       <c r="B491" t="s">
-        <v>824</v>
+        <v>563</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>113</v>
+        <v>1025</v>
       </c>
       <c r="B492" t="s">
-        <v>566</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>889</v>
+        <v>98</v>
       </c>
       <c r="B493" t="s">
-        <v>890</v>
+        <v>564</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="B494" t="s">
-        <v>1128</v>
+        <v>565</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>290</v>
+        <v>666</v>
       </c>
       <c r="B495" t="s">
-        <v>567</v>
+        <v>741</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>299</v>
+        <v>1101</v>
       </c>
       <c r="B496" t="s">
-        <v>568</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>47</v>
+        <v>823</v>
       </c>
       <c r="B497" t="s">
-        <v>569</v>
+        <v>824</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>847</v>
+        <v>113</v>
       </c>
       <c r="B498" t="s">
-        <v>848</v>
+        <v>566</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>51</v>
+        <v>889</v>
       </c>
       <c r="B499" t="s">
-        <v>570</v>
+        <v>890</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>871</v>
+        <v>45</v>
       </c>
       <c r="B500" t="s">
-        <v>872</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>114</v>
+        <v>290</v>
       </c>
       <c r="B501" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>853</v>
+        <v>299</v>
       </c>
       <c r="B502" t="s">
-        <v>854</v>
+        <v>568</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>144</v>
+        <v>47</v>
       </c>
       <c r="B503" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>1080</v>
+        <v>847</v>
       </c>
       <c r="B504" t="s">
-        <v>1081</v>
+        <v>848</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>176</v>
+        <v>51</v>
       </c>
       <c r="B505" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>316</v>
+        <v>871</v>
       </c>
       <c r="B506" t="s">
-        <v>574</v>
+        <v>872</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>29</v>
+        <v>114</v>
       </c>
       <c r="B507" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>1104</v>
+        <v>853</v>
       </c>
       <c r="B508" t="s">
-        <v>1105</v>
+        <v>854</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>1018</v>
+        <v>144</v>
       </c>
       <c r="B509" t="s">
-        <v>1019</v>
+        <v>572</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>1231</v>
+        <v>1078</v>
       </c>
       <c r="B510" t="s">
-        <v>1232</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>293</v>
+        <v>176</v>
       </c>
       <c r="B511" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>981</v>
+        <v>316</v>
       </c>
       <c r="B512" t="s">
-        <v>982</v>
+        <v>574</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>301</v>
+        <v>29</v>
       </c>
       <c r="B513" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>1003</v>
+        <v>1018</v>
       </c>
       <c r="B514" t="s">
-        <v>1004</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>1007</v>
+        <v>1225</v>
       </c>
       <c r="B515" t="s">
-        <v>1008</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>75</v>
+        <v>293</v>
       </c>
       <c r="B516" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>76</v>
+        <v>981</v>
       </c>
       <c r="B517" t="s">
-        <v>579</v>
+        <v>982</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>78</v>
+        <v>301</v>
       </c>
       <c r="B518" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>329</v>
+        <v>1003</v>
       </c>
       <c r="B519" t="s">
-        <v>581</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>1309</v>
+        <v>1007</v>
       </c>
       <c r="B520" t="s">
-        <v>1310</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>752</v>
+        <v>75</v>
       </c>
       <c r="B521" t="s">
-        <v>753</v>
+        <v>578</v>
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>805</v>
+        <v>76</v>
       </c>
       <c r="B522" t="s">
-        <v>806</v>
+        <v>579</v>
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>135</v>
+        <v>78</v>
       </c>
       <c r="B523" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>1186</v>
+        <v>329</v>
       </c>
       <c r="B524" t="s">
-        <v>1187</v>
+        <v>581</v>
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>1038</v>
+        <v>1303</v>
       </c>
       <c r="B525" t="s">
-        <v>1039</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>215</v>
+        <v>752</v>
       </c>
       <c r="B526" t="s">
-        <v>583</v>
+        <v>753</v>
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>935</v>
+        <v>805</v>
       </c>
       <c r="B527" t="s">
-        <v>1145</v>
+        <v>806</v>
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>216</v>
+        <v>1316</v>
       </c>
       <c r="B528" t="s">
-        <v>1126</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>317</v>
+        <v>135</v>
       </c>
       <c r="B529" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>1082</v>
+        <v>1180</v>
       </c>
       <c r="B530" t="s">
-        <v>1083</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>214</v>
+        <v>1038</v>
       </c>
       <c r="B531" t="s">
-        <v>1127</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>999</v>
+        <v>215</v>
       </c>
       <c r="B532" t="s">
-        <v>1000</v>
+        <v>583</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>1001</v>
+        <v>935</v>
       </c>
       <c r="B533" t="s">
-        <v>1002</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="B534" t="s">
-        <v>585</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>948</v>
+        <v>317</v>
       </c>
       <c r="B535" t="s">
-        <v>949</v>
+        <v>584</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>1098</v>
+        <v>1080</v>
       </c>
       <c r="B536" t="s">
-        <v>1099</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>1048</v>
+        <v>214</v>
       </c>
       <c r="B537" t="s">
-        <v>1049</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>93</v>
+        <v>999</v>
       </c>
       <c r="B538" t="s">
-        <v>586</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>120</v>
+        <v>1001</v>
       </c>
       <c r="B539" t="s">
-        <v>587</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>783</v>
+        <v>225</v>
       </c>
       <c r="B540" t="s">
-        <v>784</v>
+        <v>585</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>133</v>
+        <v>948</v>
       </c>
       <c r="B541" t="s">
-        <v>588</v>
+        <v>949</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>62</v>
+        <v>1096</v>
       </c>
       <c r="B542" t="s">
-        <v>589</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>1311</v>
+        <v>1046</v>
       </c>
       <c r="B543" t="s">
-        <v>1312</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="B544" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>825</v>
+        <v>120</v>
       </c>
       <c r="B545" t="s">
-        <v>826</v>
+        <v>587</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>950</v>
+        <v>783</v>
       </c>
       <c r="B546" t="s">
-        <v>951</v>
+        <v>784</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>1215</v>
+        <v>133</v>
       </c>
       <c r="B547" t="s">
-        <v>1216</v>
+        <v>588</v>
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B548" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>64</v>
+        <v>1305</v>
       </c>
       <c r="B549" t="s">
-        <v>592</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>122</v>
+        <v>66</v>
       </c>
       <c r="B550" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>1184</v>
+        <v>825</v>
       </c>
       <c r="B551" t="s">
-        <v>1185</v>
+        <v>826</v>
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>181</v>
+        <v>950</v>
       </c>
       <c r="B552" t="s">
-        <v>594</v>
+        <v>951</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>801</v>
+        <v>1209</v>
       </c>
       <c r="B553" t="s">
-        <v>802</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>1289</v>
+        <v>1318</v>
       </c>
       <c r="B554" t="s">
-        <v>1294</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>691</v>
+        <v>79</v>
       </c>
       <c r="B555" t="s">
-        <v>742</v>
+        <v>591</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>1290</v>
+        <v>64</v>
       </c>
       <c r="B556" t="s">
-        <v>1295</v>
+        <v>592</v>
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>1291</v>
+        <v>122</v>
       </c>
       <c r="B557" t="s">
-        <v>1296</v>
+        <v>593</v>
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>1292</v>
+        <v>1178</v>
       </c>
       <c r="B558" t="s">
-        <v>1297</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>1293</v>
+        <v>181</v>
       </c>
       <c r="B559" t="s">
-        <v>1298</v>
+        <v>594</v>
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>1151</v>
+        <v>801</v>
       </c>
       <c r="B560" t="s">
-        <v>1152</v>
+        <v>802</v>
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>1149</v>
+        <v>1283</v>
       </c>
       <c r="B561" t="s">
-        <v>1150</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>284</v>
+        <v>691</v>
       </c>
       <c r="B562" t="s">
-        <v>595</v>
+        <v>742</v>
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>973</v>
+        <v>1284</v>
       </c>
       <c r="B563" t="s">
-        <v>974</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>1219</v>
+        <v>1285</v>
       </c>
       <c r="B564" t="s">
-        <v>1220</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>841</v>
+        <v>1286</v>
       </c>
       <c r="B565" t="s">
-        <v>842</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>283</v>
+        <v>1287</v>
       </c>
       <c r="B566" t="s">
-        <v>596</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>883</v>
+        <v>1145</v>
       </c>
       <c r="B567" t="s">
-        <v>884</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>1180</v>
+        <v>1143</v>
       </c>
       <c r="B568" t="s">
-        <v>1181</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>756</v>
+        <v>284</v>
       </c>
       <c r="B569" t="s">
-        <v>757</v>
+        <v>595</v>
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>1078</v>
+        <v>973</v>
       </c>
       <c r="B570" t="s">
-        <v>1079</v>
+        <v>974</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
-        <v>67</v>
+        <v>1213</v>
       </c>
       <c r="B571" t="s">
-        <v>597</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
-        <v>68</v>
+        <v>841</v>
       </c>
       <c r="B572" t="s">
-        <v>598</v>
+        <v>842</v>
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
-        <v>95</v>
+        <v>283</v>
       </c>
       <c r="B573" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
-        <v>289</v>
+        <v>883</v>
       </c>
       <c r="B574" t="s">
-        <v>600</v>
+        <v>884</v>
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
-        <v>297</v>
+        <v>1174</v>
       </c>
       <c r="B575" t="s">
-        <v>601</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
-        <v>264</v>
+        <v>756</v>
       </c>
       <c r="B576" t="s">
-        <v>602</v>
+        <v>757</v>
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
-        <v>193</v>
+        <v>1076</v>
       </c>
       <c r="B577" t="s">
-        <v>603</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
-        <v>901</v>
+        <v>67</v>
       </c>
       <c r="B578" t="s">
-        <v>902</v>
+        <v>597</v>
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="B579" t="s">
-        <v>1125</v>
+        <v>598</v>
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
-        <v>1070</v>
+        <v>95</v>
       </c>
       <c r="B580" t="s">
-        <v>1071</v>
+        <v>599</v>
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
-        <v>324</v>
+        <v>289</v>
       </c>
       <c r="B581" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
-        <v>325</v>
+        <v>297</v>
       </c>
       <c r="B582" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
-        <v>849</v>
+        <v>264</v>
       </c>
       <c r="B583" t="s">
-        <v>850</v>
+        <v>602</v>
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
-        <v>887</v>
+        <v>193</v>
       </c>
       <c r="B584" t="s">
-        <v>888</v>
+        <v>603</v>
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
-        <v>1237</v>
+        <v>901</v>
       </c>
       <c r="B585" t="s">
-        <v>1238</v>
+        <v>902</v>
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
-        <v>869</v>
+        <v>44</v>
       </c>
       <c r="B586" t="s">
-        <v>870</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
-        <v>33</v>
+        <v>1068</v>
       </c>
       <c r="B587" t="s">
-        <v>606</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
-        <v>36</v>
+        <v>324</v>
       </c>
       <c r="B588" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
-        <v>1143</v>
+        <v>325</v>
       </c>
       <c r="B589" t="s">
-        <v>1144</v>
+        <v>605</v>
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
-        <v>309</v>
+        <v>849</v>
       </c>
       <c r="B590" t="s">
-        <v>608</v>
+        <v>850</v>
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
-        <v>257</v>
+        <v>887</v>
       </c>
       <c r="B591" t="s">
-        <v>609</v>
+        <v>888</v>
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
-        <v>302</v>
+        <v>1231</v>
       </c>
       <c r="B592" t="s">
-        <v>610</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
-        <v>228</v>
+        <v>869</v>
       </c>
       <c r="B593" t="s">
-        <v>611</v>
+        <v>870</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="B594" t="s">
-        <v>18</v>
+        <v>606</v>
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
-        <v>655</v>
+        <v>36</v>
       </c>
       <c r="B595" t="s">
-        <v>743</v>
+        <v>607</v>
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
-        <v>785</v>
+        <v>1137</v>
       </c>
       <c r="B596" t="s">
-        <v>786</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>142</v>
+        <v>309</v>
       </c>
       <c r="B597" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>1178</v>
+        <v>257</v>
       </c>
       <c r="B598" t="s">
-        <v>1179</v>
+        <v>609</v>
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>956</v>
+        <v>302</v>
       </c>
       <c r="B599" t="s">
-        <v>957</v>
+        <v>610</v>
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>54</v>
+        <v>228</v>
       </c>
       <c r="B600" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>265</v>
+        <v>17</v>
       </c>
       <c r="B601" t="s">
-        <v>614</v>
+        <v>18</v>
       </c>
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>976</v>
+        <v>655</v>
       </c>
       <c r="B602" t="s">
-        <v>975</v>
+        <v>743</v>
       </c>
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>56</v>
+        <v>785</v>
       </c>
       <c r="B603" t="s">
-        <v>615</v>
+        <v>786</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>1217</v>
+        <v>142</v>
       </c>
       <c r="B604" t="s">
-        <v>1218</v>
+        <v>612</v>
       </c>
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>185</v>
+        <v>1172</v>
       </c>
       <c r="B605" t="s">
-        <v>616</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>159</v>
+        <v>956</v>
       </c>
       <c r="B606" t="s">
-        <v>617</v>
+        <v>957</v>
       </c>
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B607" t="s">
-        <v>1146</v>
+        <v>613</v>
       </c>
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>40</v>
+        <v>265</v>
       </c>
       <c r="B608" t="s">
-        <v>1124</v>
+        <v>614</v>
       </c>
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>1170</v>
+        <v>976</v>
       </c>
       <c r="B609" t="s">
-        <v>1171</v>
+        <v>975</v>
       </c>
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>165</v>
+        <v>56</v>
       </c>
       <c r="B610" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>1299</v>
+        <v>1211</v>
       </c>
       <c r="B611" t="s">
-        <v>1300</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>1301</v>
+        <v>185</v>
       </c>
       <c r="B612" t="s">
-        <v>1302</v>
+        <v>616</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>12</v>
+        <v>159</v>
       </c>
       <c r="B613" t="s">
-        <v>11</v>
+        <v>617</v>
       </c>
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>250</v>
+        <v>43</v>
       </c>
       <c r="B614" t="s">
-        <v>619</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="B615" t="s">
-        <v>620</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>1040</v>
+        <v>1164</v>
       </c>
       <c r="B616" t="s">
-        <v>1041</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>28</v>
+        <v>165</v>
       </c>
       <c r="B617" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>1205</v>
+        <v>1293</v>
       </c>
       <c r="B618" t="s">
-        <v>1206</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>255</v>
+        <v>1295</v>
       </c>
       <c r="B619" t="s">
-        <v>622</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>795</v>
+        <v>12</v>
       </c>
       <c r="B620" t="s">
-        <v>796</v>
+        <v>11</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="B621" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
-        <v>661</v>
+        <v>27</v>
       </c>
       <c r="B622" t="s">
-        <v>744</v>
+        <v>620</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
-        <v>662</v>
+        <v>1040</v>
       </c>
       <c r="B623" t="s">
-        <v>745</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="B624" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
-        <v>7</v>
+        <v>1199</v>
       </c>
       <c r="B625" t="s">
-        <v>2</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
-        <v>105</v>
+        <v>255</v>
       </c>
       <c r="B626" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
-        <v>1034</v>
+        <v>1329</v>
       </c>
       <c r="B627" t="s">
-        <v>1123</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
-        <v>865</v>
+        <v>795</v>
       </c>
       <c r="B628" t="s">
-        <v>866</v>
+        <v>796</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
-        <v>1035</v>
+        <v>267</v>
       </c>
       <c r="B629" t="s">
-        <v>1122</v>
+        <v>623</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
-        <v>292</v>
+        <v>661</v>
       </c>
       <c r="B630" t="s">
-        <v>626</v>
+        <v>744</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>8</v>
+        <v>662</v>
       </c>
       <c r="B631" t="s">
-        <v>11</v>
+        <v>745</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>335</v>
+        <v>139</v>
       </c>
       <c r="B632" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
-        <v>332</v>
+        <v>7</v>
       </c>
       <c r="B633" t="s">
-        <v>628</v>
+        <v>2</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
-        <v>259</v>
+        <v>105</v>
       </c>
       <c r="B634" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
-        <v>319</v>
+        <v>1034</v>
       </c>
       <c r="B635" t="s">
-        <v>630</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="B636" t="s">
-        <v>860</v>
+        <v>866</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
-        <v>1174</v>
+        <v>1035</v>
       </c>
       <c r="B637" t="s">
-        <v>1175</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="B638" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
-        <v>271</v>
+        <v>8</v>
       </c>
       <c r="B639" t="s">
-        <v>1117</v>
+        <v>11</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
-        <v>274</v>
+        <v>335</v>
       </c>
       <c r="B640" t="s">
-        <v>1118</v>
+        <v>627</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
-        <v>270</v>
+        <v>332</v>
       </c>
       <c r="B641" t="s">
-        <v>1119</v>
+        <v>628</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="B642" t="s">
-        <v>1120</v>
+        <v>629</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
-        <v>269</v>
+        <v>319</v>
       </c>
       <c r="B643" t="s">
-        <v>1121</v>
+        <v>630</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
-        <v>272</v>
+        <v>859</v>
       </c>
       <c r="B644" t="s">
-        <v>1116</v>
+        <v>860</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
-        <v>92</v>
+        <v>1168</v>
       </c>
       <c r="B645" t="s">
-        <v>632</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
-        <v>200</v>
+        <v>268</v>
       </c>
       <c r="B646" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
-        <v>203</v>
+        <v>271</v>
       </c>
       <c r="B647" t="s">
-        <v>634</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
-        <v>1227</v>
+        <v>274</v>
       </c>
       <c r="B648" t="s">
-        <v>1228</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
-        <v>172</v>
+        <v>270</v>
       </c>
       <c r="B649" t="s">
-        <v>635</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
-        <v>693</v>
+        <v>273</v>
       </c>
       <c r="B650" t="s">
-        <v>746</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="B651" t="s">
-        <v>636</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
-        <v>694</v>
+        <v>272</v>
       </c>
       <c r="B652" t="s">
-        <v>747</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
-        <v>189</v>
+        <v>92</v>
       </c>
       <c r="B653" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
-        <v>989</v>
+        <v>200</v>
       </c>
       <c r="B654" t="s">
-        <v>990</v>
+        <v>633</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
-        <v>311</v>
+        <v>203</v>
       </c>
       <c r="B655" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
-        <v>312</v>
+        <v>1221</v>
       </c>
       <c r="B656" t="s">
-        <v>639</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
-        <v>1033</v>
+        <v>172</v>
       </c>
       <c r="B657" t="s">
-        <v>1115</v>
+        <v>635</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
-        <v>1005</v>
+        <v>693</v>
       </c>
       <c r="B658" t="s">
-        <v>1006</v>
+        <v>746</v>
       </c>
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
-        <v>81</v>
+        <v>252</v>
       </c>
       <c r="B659" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
-        <v>651</v>
+        <v>694</v>
       </c>
       <c r="B660" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
-        <v>922</v>
+        <v>189</v>
       </c>
       <c r="B661" t="s">
-        <v>923</v>
+        <v>637</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
-        <v>642</v>
+        <v>989</v>
       </c>
       <c r="B662" t="s">
-        <v>749</v>
+        <v>990</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
-        <v>969</v>
+        <v>311</v>
       </c>
       <c r="B663" t="s">
-        <v>970</v>
+        <v>638</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
-        <v>1162</v>
+        <v>312</v>
       </c>
       <c r="B664" t="s">
-        <v>1163</v>
+        <v>639</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A665" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B665" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A666" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B666" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A667" t="s">
+        <v>81</v>
+      </c>
+      <c r="B667" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A668" t="s">
+        <v>651</v>
+      </c>
+      <c r="B668" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A669" t="s">
+        <v>922</v>
+      </c>
+      <c r="B669" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A670" t="s">
+        <v>642</v>
+      </c>
+      <c r="B670" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A671" t="s">
+        <v>969</v>
+      </c>
+      <c r="B671" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A672" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B672" t="s">
+        <v>1157</v>
       </c>
     </row>
   </sheetData>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C2FEDE-6C86-4950-9DBE-503BD9AB6D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656F971D-9635-47CE-8037-3C03D7A15426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="1337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="1341">
   <si>
     <t>trigger</t>
   </si>
@@ -3447,9 +3447,6 @@
     <t>renal cortical cyst (Bosniak cat-I)</t>
   </si>
   <si>
-    <t>small vessel disease (Fazekas grade-I)</t>
-  </si>
-  <si>
     <t>awa</t>
   </si>
   <si>
@@ -4036,6 +4033,21 @@
   </si>
   <si>
     <t>collateral</t>
+  </si>
+  <si>
+    <t>svdsc</t>
+  </si>
+  <si>
+    <t>Multiple hypodensities are noted in bilateral periventricular white matter and centrum semi-ovale</t>
+  </si>
+  <si>
+    <t>svdf</t>
+  </si>
+  <si>
+    <t>Small vessel disease (Fazekas grade-I)</t>
+  </si>
+  <si>
+    <t>Small vessel disease</t>
   </si>
 </sst>
 </file>
@@ -4097,10 +4109,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B672" totalsRowShown="0">
-  <autoFilter ref="A1:B672" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B672">
-    <sortCondition ref="A1:A672"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B674" totalsRowShown="0">
+  <autoFilter ref="A1:B674" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B674">
+    <sortCondition ref="A1:A674"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4373,7 +4385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B672"/>
+  <dimension ref="A1:B674"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -4398,10 +4410,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B3" t="s">
         <v>1190</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1191</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -4630,10 +4642,10 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B32" t="s">
         <v>1176</v>
-      </c>
-      <c r="B32" t="s">
-        <v>1177</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
@@ -4710,18 +4722,18 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B42" t="s">
         <v>1207</v>
-      </c>
-      <c r="B42" t="s">
-        <v>1208</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B43" t="s">
         <v>1204</v>
-      </c>
-      <c r="B43" t="s">
-        <v>1205</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
@@ -4846,10 +4858,10 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B59" t="s">
         <v>1141</v>
-      </c>
-      <c r="B59" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
@@ -4934,10 +4946,10 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B70" t="s">
         <v>1325</v>
-      </c>
-      <c r="B70" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
@@ -4958,10 +4970,10 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B73" t="s">
         <v>1223</v>
-      </c>
-      <c r="B73" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
@@ -4982,10 +4994,10 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B76" t="s">
         <v>1233</v>
-      </c>
-      <c r="B76" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
@@ -4998,10 +5010,10 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B78" t="s">
         <v>1235</v>
-      </c>
-      <c r="B78" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
@@ -5014,10 +5026,10 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B80" t="s">
         <v>1237</v>
-      </c>
-      <c r="B80" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
@@ -5030,10 +5042,10 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B82" t="s">
         <v>1239</v>
-      </c>
-      <c r="B82" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
@@ -5046,10 +5058,10 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B84" t="s">
         <v>1241</v>
-      </c>
-      <c r="B84" t="s">
-        <v>1242</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
@@ -5062,10 +5074,10 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="B86" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
@@ -5078,10 +5090,10 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="B88" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
@@ -5094,10 +5106,10 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="B90" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
@@ -5198,10 +5210,10 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B103" t="s">
         <v>1153</v>
-      </c>
-      <c r="B103" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
@@ -5318,10 +5330,10 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B118" t="s">
         <v>1170</v>
-      </c>
-      <c r="B118" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
@@ -5350,10 +5362,10 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="B122" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
@@ -5457,12 +5469,12 @@
         <v>102</v>
       </c>
       <c r="B135" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="B136" t="s">
         <v>405</v>
@@ -5494,10 +5506,10 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B140" t="s">
         <v>1147</v>
-      </c>
-      <c r="B140" t="s">
-        <v>1148</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
@@ -5518,10 +5530,10 @@
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B143" t="s">
         <v>1321</v>
-      </c>
-      <c r="B143" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
@@ -5558,18 +5570,18 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B148" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B149" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
@@ -5582,10 +5594,10 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="B151" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
@@ -5598,10 +5610,10 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="B153" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.35">
@@ -5614,10 +5626,10 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="B155" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.35">
@@ -5630,10 +5642,10 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B157" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.35">
@@ -5646,10 +5658,10 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="B159" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.35">
@@ -5662,10 +5674,10 @@
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B161" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.35">
@@ -5678,10 +5690,10 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B163" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.35">
@@ -5694,10 +5706,10 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B165" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.35">
@@ -5710,10 +5722,10 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="B167" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.35">
@@ -5726,10 +5738,10 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B169" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.35">
@@ -5766,15 +5778,15 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B174" t="s">
         <v>1332</v>
-      </c>
-      <c r="B174" t="s">
-        <v>1333</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B175" t="s">
         <v>410</v>
@@ -5785,7 +5797,7 @@
         <v>149</v>
       </c>
       <c r="B176" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.35">
@@ -5854,10 +5866,10 @@
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B185" t="s">
         <v>1162</v>
-      </c>
-      <c r="B185" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.35">
@@ -5982,18 +5994,18 @@
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B201" t="s">
         <v>1158</v>
-      </c>
-      <c r="B201" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B202" t="s">
         <v>1323</v>
-      </c>
-      <c r="B202" t="s">
-        <v>1324</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.35">
@@ -6038,10 +6050,10 @@
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B208" t="s">
         <v>1311</v>
-      </c>
-      <c r="B208" t="s">
-        <v>1312</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.35">
@@ -6054,18 +6066,18 @@
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B210" t="s">
         <v>1149</v>
-      </c>
-      <c r="B210" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B211" t="s">
         <v>1151</v>
-      </c>
-      <c r="B211" t="s">
-        <v>1152</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.35">
@@ -6094,18 +6106,18 @@
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B215" t="s">
         <v>1301</v>
-      </c>
-      <c r="B215" t="s">
-        <v>1302</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B216" t="s">
         <v>1227</v>
-      </c>
-      <c r="B216" t="s">
-        <v>1228</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.35">
@@ -6270,18 +6282,18 @@
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B237" t="s">
         <v>1192</v>
-      </c>
-      <c r="B237" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B238" t="s">
         <v>1195</v>
-      </c>
-      <c r="B238" t="s">
-        <v>1196</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.35">
@@ -6350,10 +6362,10 @@
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B247" t="s">
         <v>1215</v>
-      </c>
-      <c r="B247" t="s">
-        <v>1216</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
@@ -6382,10 +6394,10 @@
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B251" t="s">
         <v>1327</v>
-      </c>
-      <c r="B251" t="s">
-        <v>1328</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
@@ -6598,10 +6610,10 @@
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B278" t="s">
         <v>1166</v>
-      </c>
-      <c r="B278" t="s">
-        <v>1167</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
@@ -6854,10 +6866,10 @@
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B310" t="s">
         <v>1330</v>
-      </c>
-      <c r="B310" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
@@ -6894,10 +6906,10 @@
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B315" t="s">
         <v>1160</v>
-      </c>
-      <c r="B315" t="s">
-        <v>1161</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
@@ -6950,10 +6962,10 @@
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="B322" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
@@ -6966,10 +6978,10 @@
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="B324" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
@@ -6982,10 +6994,10 @@
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="B326" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
@@ -6998,10 +7010,10 @@
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="B328" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
@@ -7014,10 +7026,10 @@
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B330" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
@@ -7030,10 +7042,10 @@
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B332" t="s">
         <v>1186</v>
-      </c>
-      <c r="B332" t="s">
-        <v>1187</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
@@ -7086,10 +7098,10 @@
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B339" t="s">
         <v>1184</v>
-      </c>
-      <c r="B339" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
@@ -7102,10 +7114,10 @@
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B341" t="s">
         <v>1188</v>
-      </c>
-      <c r="B341" t="s">
-        <v>1189</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
@@ -7214,10 +7226,10 @@
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B355" t="s">
         <v>1307</v>
-      </c>
-      <c r="B355" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
@@ -7398,7 +7410,7 @@
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="B378" t="s">
         <v>514</v>
@@ -7590,10 +7602,10 @@
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B402" t="s">
         <v>1219</v>
-      </c>
-      <c r="B402" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
@@ -7742,10 +7754,10 @@
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B421" t="s">
         <v>1299</v>
-      </c>
-      <c r="B421" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
@@ -7862,10 +7874,10 @@
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B436" t="s">
         <v>1229</v>
-      </c>
-      <c r="B436" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
@@ -7926,10 +7938,10 @@
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B444" t="s">
         <v>1201</v>
-      </c>
-      <c r="B444" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
@@ -7990,10 +8002,10 @@
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B452" t="s">
         <v>1217</v>
-      </c>
-      <c r="B452" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
@@ -8006,10 +8018,10 @@
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B454" t="s">
         <v>1309</v>
-      </c>
-      <c r="B454" t="s">
-        <v>1310</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
@@ -8038,18 +8050,18 @@
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B458" t="s">
         <v>1197</v>
-      </c>
-      <c r="B458" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B459" t="s">
         <v>1297</v>
-      </c>
-      <c r="B459" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
@@ -8150,10 +8162,10 @@
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B472" t="s">
         <v>1182</v>
-      </c>
-      <c r="B472" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
@@ -8169,7 +8181,7 @@
         <v>334</v>
       </c>
       <c r="B474" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
@@ -8222,10 +8234,10 @@
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B481" t="s">
         <v>1313</v>
-      </c>
-      <c r="B481" t="s">
-        <v>1314</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
@@ -8494,10 +8506,10 @@
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B515" t="s">
         <v>1225</v>
-      </c>
-      <c r="B515" t="s">
-        <v>1226</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
@@ -8574,10 +8586,10 @@
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B525" t="s">
         <v>1303</v>
-      </c>
-      <c r="B525" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.35">
@@ -8598,10 +8610,10 @@
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B528" t="s">
         <v>1316</v>
-      </c>
-      <c r="B528" t="s">
-        <v>1317</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.35">
@@ -8614,10 +8626,10 @@
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B530" t="s">
         <v>1180</v>
-      </c>
-      <c r="B530" t="s">
-        <v>1181</v>
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.35">
@@ -8766,10 +8778,10 @@
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B549" t="s">
         <v>1305</v>
-      </c>
-      <c r="B549" t="s">
-        <v>1306</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.35">
@@ -8798,18 +8810,18 @@
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B553" t="s">
         <v>1209</v>
-      </c>
-      <c r="B553" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B554" t="s">
         <v>1318</v>
-      </c>
-      <c r="B554" t="s">
-        <v>1319</v>
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.35">
@@ -8838,10 +8850,10 @@
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B558" t="s">
         <v>1178</v>
-      </c>
-      <c r="B558" t="s">
-        <v>1179</v>
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.35">
@@ -8862,10 +8874,10 @@
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="B561" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.35">
@@ -8878,50 +8890,50 @@
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="B563" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="B564" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="B565" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="B566" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B567" t="s">
         <v>1145</v>
-      </c>
-      <c r="B567" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B568" t="s">
         <v>1143</v>
-      </c>
-      <c r="B568" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.35">
@@ -8942,10 +8954,10 @@
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B571" t="s">
         <v>1213</v>
-      </c>
-      <c r="B571" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.35">
@@ -8974,10 +8986,10 @@
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B575" t="s">
         <v>1174</v>
-      </c>
-      <c r="B575" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.35">
@@ -9110,10 +9122,10 @@
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B592" t="s">
         <v>1231</v>
-      </c>
-      <c r="B592" t="s">
-        <v>1232</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.35">
@@ -9214,10 +9226,10 @@
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B605" t="s">
         <v>1172</v>
-      </c>
-      <c r="B605" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.35">
@@ -9262,10 +9274,10 @@
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B611" t="s">
         <v>1211</v>
-      </c>
-      <c r="B611" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.35">
@@ -9289,471 +9301,487 @@
         <v>43</v>
       </c>
       <c r="B614" t="s">
-        <v>1140</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>40</v>
+        <v>1338</v>
       </c>
       <c r="B615" t="s">
-        <v>1118</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>1164</v>
+        <v>40</v>
       </c>
       <c r="B616" t="s">
-        <v>1165</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>165</v>
+        <v>1336</v>
       </c>
       <c r="B617" t="s">
-        <v>618</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>1293</v>
+        <v>1163</v>
       </c>
       <c r="B618" t="s">
-        <v>1294</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>1295</v>
+        <v>165</v>
       </c>
       <c r="B619" t="s">
-        <v>1296</v>
+        <v>618</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>12</v>
+        <v>1292</v>
       </c>
       <c r="B620" t="s">
-        <v>11</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>250</v>
+        <v>1294</v>
       </c>
       <c r="B621" t="s">
-        <v>619</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B622" t="s">
-        <v>620</v>
+        <v>11</v>
       </c>
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
-        <v>1040</v>
+        <v>250</v>
       </c>
       <c r="B623" t="s">
-        <v>1041</v>
+        <v>619</v>
       </c>
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B624" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="625" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
-        <v>1199</v>
+        <v>1040</v>
       </c>
       <c r="B625" t="s">
-        <v>1200</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="626" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
-        <v>255</v>
+        <v>28</v>
       </c>
       <c r="B626" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="627" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
-        <v>1329</v>
+        <v>1198</v>
       </c>
       <c r="B627" t="s">
-        <v>1334</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="628" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
-        <v>795</v>
+        <v>255</v>
       </c>
       <c r="B628" t="s">
-        <v>796</v>
+        <v>622</v>
       </c>
     </row>
     <row r="629" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
-        <v>267</v>
+        <v>1328</v>
       </c>
       <c r="B629" t="s">
-        <v>623</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="630" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
-        <v>661</v>
+        <v>795</v>
       </c>
       <c r="B630" t="s">
-        <v>744</v>
+        <v>796</v>
       </c>
     </row>
     <row r="631" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>662</v>
+        <v>267</v>
       </c>
       <c r="B631" t="s">
-        <v>745</v>
+        <v>623</v>
       </c>
     </row>
     <row r="632" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>139</v>
+        <v>661</v>
       </c>
       <c r="B632" t="s">
-        <v>624</v>
+        <v>744</v>
       </c>
     </row>
     <row r="633" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
-        <v>7</v>
+        <v>662</v>
       </c>
       <c r="B633" t="s">
-        <v>2</v>
+        <v>745</v>
       </c>
     </row>
     <row r="634" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="B634" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
-        <v>1034</v>
+        <v>7</v>
       </c>
       <c r="B635" t="s">
-        <v>1117</v>
+        <v>2</v>
       </c>
     </row>
     <row r="636" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
-        <v>865</v>
+        <v>105</v>
       </c>
       <c r="B636" t="s">
-        <v>866</v>
+        <v>625</v>
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B637" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
-        <v>292</v>
+        <v>865</v>
       </c>
       <c r="B638" t="s">
-        <v>626</v>
+        <v>866</v>
       </c>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
-        <v>8</v>
+        <v>1035</v>
       </c>
       <c r="B639" t="s">
-        <v>11</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
-        <v>335</v>
+        <v>292</v>
       </c>
       <c r="B640" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
-        <v>332</v>
+        <v>8</v>
       </c>
       <c r="B641" t="s">
-        <v>628</v>
+        <v>11</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
-        <v>259</v>
+        <v>335</v>
       </c>
       <c r="B642" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="B643" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
-        <v>859</v>
+        <v>259</v>
       </c>
       <c r="B644" t="s">
-        <v>860</v>
+        <v>629</v>
       </c>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
-        <v>1168</v>
+        <v>319</v>
       </c>
       <c r="B645" t="s">
-        <v>1169</v>
+        <v>630</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
-        <v>268</v>
+        <v>859</v>
       </c>
       <c r="B646" t="s">
-        <v>631</v>
+        <v>860</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
-        <v>271</v>
+        <v>1167</v>
       </c>
       <c r="B647" t="s">
-        <v>1111</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B648" t="s">
-        <v>1112</v>
+        <v>631</v>
       </c>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B649" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B650" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B651" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B652" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
-        <v>92</v>
+        <v>269</v>
       </c>
       <c r="B653" t="s">
-        <v>632</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
-        <v>200</v>
+        <v>272</v>
       </c>
       <c r="B654" t="s">
-        <v>633</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
-        <v>203</v>
+        <v>92</v>
       </c>
       <c r="B655" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
-        <v>1221</v>
+        <v>200</v>
       </c>
       <c r="B656" t="s">
-        <v>1222</v>
+        <v>633</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="B657" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
-        <v>693</v>
+        <v>1220</v>
       </c>
       <c r="B658" t="s">
-        <v>746</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
-        <v>252</v>
+        <v>172</v>
       </c>
       <c r="B659" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B660" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
-        <v>189</v>
+        <v>252</v>
       </c>
       <c r="B661" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
-        <v>989</v>
+        <v>694</v>
       </c>
       <c r="B662" t="s">
-        <v>990</v>
+        <v>747</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
-        <v>311</v>
+        <v>189</v>
       </c>
       <c r="B663" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
-        <v>312</v>
+        <v>989</v>
       </c>
       <c r="B664" t="s">
-        <v>639</v>
+        <v>990</v>
       </c>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
-        <v>1033</v>
+        <v>311</v>
       </c>
       <c r="B665" t="s">
-        <v>1109</v>
+        <v>638</v>
       </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
-        <v>1005</v>
+        <v>312</v>
       </c>
       <c r="B666" t="s">
-        <v>1006</v>
+        <v>639</v>
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
-        <v>81</v>
+        <v>1033</v>
       </c>
       <c r="B667" t="s">
-        <v>640</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
-        <v>651</v>
+        <v>1005</v>
       </c>
       <c r="B668" t="s">
-        <v>748</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
-        <v>922</v>
+        <v>81</v>
       </c>
       <c r="B669" t="s">
-        <v>923</v>
+        <v>640</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
-        <v>642</v>
+        <v>651</v>
       </c>
       <c r="B670" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
-        <v>969</v>
+        <v>922</v>
       </c>
       <c r="B671" t="s">
-        <v>970</v>
+        <v>923</v>
       </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
+        <v>642</v>
+      </c>
+      <c r="B672" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A673" t="s">
+        <v>969</v>
+      </c>
+      <c r="B673" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A674" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B674" t="s">
         <v>1156</v>
-      </c>
-      <c r="B672" t="s">
-        <v>1157</v>
       </c>
     </row>
   </sheetData>

--- a/shortcuts.xlsx
+++ b/shortcuts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Kushal MD\ECA\Programming\espanso-radiology\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656F971D-9635-47CE-8037-3C03D7A15426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A3CE0B7-FCBA-4787-887A-376EC88F8F9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="1341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="1345">
   <si>
     <t>trigger</t>
   </si>
@@ -4048,6 +4048,18 @@
   </si>
   <si>
     <t>Small vessel disease</t>
+  </si>
+  <si>
+    <t>fvc</t>
+  </si>
+  <si>
+    <t>Findings in visualised chest</t>
+  </si>
+  <si>
+    <t>fva</t>
+  </si>
+  <si>
+    <t>Findings in visualised abdomen</t>
   </si>
 </sst>
 </file>
@@ -4109,10 +4121,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B674" totalsRowShown="0">
-  <autoFilter ref="A1:B674" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B674">
-    <sortCondition ref="A1:A674"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}" name="Table1" displayName="Table1" ref="A1:B676" totalsRowShown="0">
+  <autoFilter ref="A1:B676" xr:uid="{EFCBFF11-4FFF-44D7-852C-AE59B684A2E3}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B676">
+    <sortCondition ref="A1:A676"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{4FC4E6C5-087A-465C-90C8-A2830BEBBA4B}" name="trigger"/>
@@ -4385,7 +4397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B674"/>
+  <dimension ref="A1:B676"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -6330,1415 +6342,1415 @@
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>275</v>
+        <v>1343</v>
       </c>
       <c r="B243" t="s">
-        <v>441</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>857</v>
+        <v>1341</v>
       </c>
       <c r="B244" t="s">
-        <v>858</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>116</v>
+        <v>275</v>
       </c>
       <c r="B245" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>208</v>
+        <v>857</v>
       </c>
       <c r="B246" t="s">
-        <v>443</v>
+        <v>858</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>1214</v>
+        <v>116</v>
       </c>
       <c r="B247" t="s">
-        <v>1215</v>
+        <v>442</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>1054</v>
+        <v>208</v>
       </c>
       <c r="B248" t="s">
-        <v>1055</v>
+        <v>443</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>118</v>
+        <v>1214</v>
       </c>
       <c r="B249" t="s">
-        <v>444</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>641</v>
+        <v>1054</v>
       </c>
       <c r="B250" t="s">
-        <v>723</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>1326</v>
+        <v>118</v>
       </c>
       <c r="B251" t="s">
-        <v>1327</v>
+        <v>444</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
-        <v>815</v>
+        <v>641</v>
       </c>
       <c r="B252" t="s">
-        <v>816</v>
+        <v>723</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>298</v>
+        <v>1326</v>
       </c>
       <c r="B253" t="s">
-        <v>445</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
-        <v>643</v>
+        <v>815</v>
       </c>
       <c r="B254" t="s">
-        <v>724</v>
+        <v>816</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>644</v>
+        <v>298</v>
       </c>
       <c r="B255" t="s">
-        <v>725</v>
+        <v>445</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>1036</v>
+        <v>643</v>
       </c>
       <c r="B256" t="s">
-        <v>1037</v>
+        <v>724</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>90</v>
+        <v>644</v>
       </c>
       <c r="B257" t="s">
-        <v>446</v>
+        <v>725</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>88</v>
+        <v>1036</v>
       </c>
       <c r="B258" t="s">
-        <v>447</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B259" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>1070</v>
+        <v>88</v>
       </c>
       <c r="B260" t="s">
-        <v>1071</v>
+        <v>447</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="B261" t="s">
-        <v>1130</v>
+        <v>448</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>5</v>
+        <v>1070</v>
       </c>
       <c r="B262" t="s">
-        <v>6</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>1135</v>
+        <v>23</v>
       </c>
       <c r="B263" t="s">
-        <v>1136</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>126</v>
+        <v>5</v>
       </c>
       <c r="B264" t="s">
-        <v>449</v>
+        <v>6</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>128</v>
+        <v>1135</v>
       </c>
       <c r="B265" t="s">
-        <v>450</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B266" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B267" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="B268" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>277</v>
+        <v>132</v>
       </c>
       <c r="B269" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>1072</v>
+        <v>119</v>
       </c>
       <c r="B270" t="s">
-        <v>1073</v>
+        <v>453</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>9</v>
+        <v>277</v>
       </c>
       <c r="B271" t="s">
-        <v>10</v>
+        <v>454</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>129</v>
+        <v>1072</v>
       </c>
       <c r="B272" t="s">
-        <v>455</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>127</v>
+        <v>9</v>
       </c>
       <c r="B273" t="s">
-        <v>456</v>
+        <v>10</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>173</v>
+        <v>129</v>
       </c>
       <c r="B274" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>262</v>
+        <v>127</v>
       </c>
       <c r="B275" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>77</v>
+        <v>173</v>
       </c>
       <c r="B276" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>938</v>
+        <v>262</v>
       </c>
       <c r="B277" t="s">
-        <v>939</v>
+        <v>458</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>1165</v>
+        <v>77</v>
       </c>
       <c r="B278" t="s">
-        <v>1166</v>
+        <v>459</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>168</v>
+        <v>938</v>
       </c>
       <c r="B279" t="s">
-        <v>460</v>
+        <v>939</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>167</v>
+        <v>1165</v>
       </c>
       <c r="B280" t="s">
-        <v>461</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>835</v>
+        <v>168</v>
       </c>
       <c r="B281" t="s">
-        <v>836</v>
+        <v>460</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>791</v>
+        <v>167</v>
       </c>
       <c r="B282" t="s">
-        <v>792</v>
+        <v>461</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>304</v>
+        <v>835</v>
       </c>
       <c r="B283" t="s">
-        <v>462</v>
+        <v>836</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>758</v>
+        <v>791</v>
       </c>
       <c r="B284" t="s">
-        <v>759</v>
+        <v>792</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>897</v>
+        <v>304</v>
       </c>
       <c r="B285" t="s">
-        <v>898</v>
+        <v>462</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>652</v>
+        <v>758</v>
       </c>
       <c r="B286" t="s">
-        <v>726</v>
+        <v>759</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>86</v>
+        <v>897</v>
       </c>
       <c r="B287" t="s">
-        <v>463</v>
+        <v>898</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>87</v>
+        <v>652</v>
       </c>
       <c r="B288" t="s">
-        <v>464</v>
+        <v>726</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>153</v>
+        <v>86</v>
       </c>
       <c r="B289" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>156</v>
+        <v>87</v>
       </c>
       <c r="B290" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B291" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>251</v>
+        <v>156</v>
       </c>
       <c r="B292" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>285</v>
+        <v>158</v>
       </c>
       <c r="B293" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>326</v>
+        <v>251</v>
       </c>
       <c r="B294" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>327</v>
+        <v>285</v>
       </c>
       <c r="B295" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>229</v>
+        <v>326</v>
       </c>
       <c r="B296" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>55</v>
+        <v>327</v>
       </c>
       <c r="B297" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>657</v>
+        <v>229</v>
       </c>
       <c r="B298" t="s">
-        <v>727</v>
+        <v>472</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>235</v>
+        <v>55</v>
       </c>
       <c r="B299" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>57</v>
+        <v>657</v>
       </c>
       <c r="B300" t="s">
-        <v>475</v>
+        <v>727</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B301" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>766</v>
+        <v>57</v>
       </c>
       <c r="B302" t="s">
-        <v>1009</v>
+        <v>475</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>1012</v>
+        <v>236</v>
       </c>
       <c r="B303" t="s">
-        <v>767</v>
+        <v>476</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>164</v>
+        <v>766</v>
       </c>
       <c r="B304" t="s">
-        <v>477</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>201</v>
+        <v>1012</v>
       </c>
       <c r="B305" t="s">
-        <v>478</v>
+        <v>767</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>204</v>
+        <v>164</v>
       </c>
       <c r="B306" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>313</v>
+        <v>201</v>
       </c>
       <c r="B307" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>873</v>
+        <v>204</v>
       </c>
       <c r="B308" t="s">
-        <v>874</v>
+        <v>479</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>997</v>
+        <v>313</v>
       </c>
       <c r="B309" t="s">
-        <v>998</v>
+        <v>480</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>1329</v>
+        <v>873</v>
       </c>
       <c r="B310" t="s">
-        <v>1330</v>
+        <v>874</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>258</v>
+        <v>997</v>
       </c>
       <c r="B311" t="s">
-        <v>481</v>
+        <v>998</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>983</v>
+        <v>1329</v>
       </c>
       <c r="B312" t="s">
-        <v>984</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>160</v>
+        <v>258</v>
       </c>
       <c r="B313" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>692</v>
+        <v>983</v>
       </c>
       <c r="B314" t="s">
-        <v>728</v>
+        <v>984</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>1159</v>
+        <v>160</v>
       </c>
       <c r="B315" t="s">
-        <v>1160</v>
+        <v>482</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>760</v>
+        <v>692</v>
       </c>
       <c r="B316" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>895</v>
+        <v>1159</v>
       </c>
       <c r="B317" t="s">
-        <v>896</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>893</v>
+        <v>760</v>
       </c>
       <c r="B318" t="s">
-        <v>894</v>
+        <v>761</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>184</v>
+        <v>895</v>
       </c>
       <c r="B319" t="s">
-        <v>483</v>
+        <v>896</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>244</v>
+        <v>893</v>
       </c>
       <c r="B320" t="s">
-        <v>484</v>
+        <v>894</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>243</v>
+        <v>184</v>
       </c>
       <c r="B321" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>1272</v>
+        <v>244</v>
       </c>
       <c r="B322" t="s">
-        <v>1277</v>
+        <v>484</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>686</v>
+        <v>243</v>
       </c>
       <c r="B323" t="s">
-        <v>729</v>
+        <v>485</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="B324" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B325" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="B326" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B327" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="B328" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B329" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="B330" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B331" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>1185</v>
+        <v>1276</v>
       </c>
       <c r="B332" t="s">
-        <v>1186</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>280</v>
+        <v>690</v>
       </c>
       <c r="B333" t="s">
-        <v>486</v>
+        <v>733</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>281</v>
+        <v>1185</v>
       </c>
       <c r="B334" t="s">
-        <v>487</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>49</v>
+        <v>280</v>
       </c>
       <c r="B335" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>53</v>
+        <v>281</v>
       </c>
       <c r="B336" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="B337" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="B338" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>1183</v>
+        <v>136</v>
       </c>
       <c r="B339" t="s">
-        <v>1184</v>
+        <v>491</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>221</v>
+        <v>72</v>
       </c>
       <c r="B340" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="B341" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>15</v>
+        <v>221</v>
       </c>
       <c r="B342" t="s">
-        <v>16</v>
+        <v>492</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>1058</v>
+        <v>1187</v>
       </c>
       <c r="B343" t="s">
-        <v>1059</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>920</v>
+        <v>15</v>
       </c>
       <c r="B344" t="s">
-        <v>921</v>
+        <v>16</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>108</v>
+        <v>1058</v>
       </c>
       <c r="B345" t="s">
-        <v>493</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>241</v>
+        <v>920</v>
       </c>
       <c r="B346" t="s">
-        <v>494</v>
+        <v>921</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>328</v>
+        <v>108</v>
       </c>
       <c r="B347" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>1098</v>
+        <v>241</v>
       </c>
       <c r="B348" t="s">
-        <v>1099</v>
+        <v>494</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>1050</v>
+        <v>328</v>
       </c>
       <c r="B349" t="s">
-        <v>1051</v>
+        <v>495</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>121</v>
+        <v>1098</v>
       </c>
       <c r="B350" t="s">
-        <v>496</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>750</v>
+        <v>1050</v>
       </c>
       <c r="B351" t="s">
-        <v>751</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>781</v>
+        <v>121</v>
       </c>
       <c r="B352" t="s">
-        <v>782</v>
+        <v>496</v>
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>134</v>
+        <v>750</v>
       </c>
       <c r="B353" t="s">
-        <v>497</v>
+        <v>751</v>
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>63</v>
+        <v>781</v>
       </c>
       <c r="B354" t="s">
-        <v>498</v>
+        <v>782</v>
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>1306</v>
+        <v>134</v>
       </c>
       <c r="B355" t="s">
-        <v>1307</v>
+        <v>497</v>
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>224</v>
+        <v>63</v>
       </c>
       <c r="B356" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>25</v>
+        <v>1306</v>
       </c>
       <c r="B357" t="s">
-        <v>500</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>26</v>
+        <v>224</v>
       </c>
       <c r="B358" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>207</v>
+        <v>25</v>
       </c>
       <c r="B359" t="s">
-        <v>1127</v>
+        <v>500</v>
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>960</v>
+        <v>26</v>
       </c>
       <c r="B360" t="s">
-        <v>1128</v>
+        <v>501</v>
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>1107</v>
+        <v>207</v>
       </c>
       <c r="B361" t="s">
-        <v>1108</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>206</v>
+        <v>960</v>
       </c>
       <c r="B362" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>202</v>
+        <v>1107</v>
       </c>
       <c r="B363" t="s">
-        <v>502</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B364" t="s">
-        <v>503</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>145</v>
+        <v>202</v>
       </c>
       <c r="B365" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>663</v>
+        <v>205</v>
       </c>
       <c r="B366" t="s">
-        <v>734</v>
+        <v>503</v>
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="B367" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>1086</v>
+        <v>663</v>
       </c>
       <c r="B368" t="s">
-        <v>1087</v>
+        <v>734</v>
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>263</v>
+        <v>171</v>
       </c>
       <c r="B369" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="B370" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>80</v>
+        <v>263</v>
       </c>
       <c r="B371" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>65</v>
+        <v>1088</v>
       </c>
       <c r="B372" t="s">
-        <v>508</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>191</v>
+        <v>80</v>
       </c>
       <c r="B373" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>123</v>
+        <v>65</v>
       </c>
       <c r="B374" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B375" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>231</v>
+        <v>123</v>
       </c>
       <c r="B376" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>233</v>
+        <v>192</v>
       </c>
       <c r="B377" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>1193</v>
+        <v>231</v>
       </c>
       <c r="B378" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>31</v>
+        <v>233</v>
       </c>
       <c r="B379" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>30</v>
+        <v>1193</v>
       </c>
       <c r="B380" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B381" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="B382" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>306</v>
+        <v>37</v>
       </c>
       <c r="B383" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>222</v>
+        <v>71</v>
       </c>
       <c r="B384" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="B385" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>278</v>
+        <v>222</v>
       </c>
       <c r="B386" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>279</v>
+        <v>315</v>
       </c>
       <c r="B387" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>831</v>
+        <v>278</v>
       </c>
       <c r="B388" t="s">
-        <v>832</v>
+        <v>521</v>
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>48</v>
+        <v>279</v>
       </c>
       <c r="B389" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>146</v>
+        <v>831</v>
       </c>
       <c r="B390" t="s">
-        <v>524</v>
+        <v>832</v>
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B391" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>223</v>
+        <v>146</v>
       </c>
       <c r="B392" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>1092</v>
+        <v>52</v>
       </c>
       <c r="B393" t="s">
-        <v>1093</v>
+        <v>525</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>1103</v>
+        <v>223</v>
       </c>
       <c r="B394" t="s">
-        <v>1106</v>
+        <v>526</v>
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>1048</v>
+        <v>1092</v>
       </c>
       <c r="B395" t="s">
-        <v>1049</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>96</v>
+        <v>1103</v>
       </c>
       <c r="B396" t="s">
-        <v>527</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>248</v>
+        <v>1048</v>
       </c>
       <c r="B397" t="s">
-        <v>528</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>249</v>
+        <v>96</v>
       </c>
       <c r="B398" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>94</v>
+        <v>248</v>
       </c>
       <c r="B399" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>1062</v>
+        <v>249</v>
       </c>
       <c r="B400" t="s">
-        <v>1063</v>
+        <v>529</v>
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>212</v>
+        <v>94</v>
       </c>
       <c r="B401" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>1218</v>
+        <v>1062</v>
       </c>
       <c r="B402" t="s">
-        <v>1219</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>916</v>
+        <v>212</v>
       </c>
       <c r="B403" t="s">
-        <v>917</v>
+        <v>531</v>
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>914</v>
+        <v>1218</v>
       </c>
       <c r="B404" t="s">
-        <v>915</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="B405" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>330</v>
+        <v>914</v>
       </c>
       <c r="B406" t="s">
-        <v>532</v>
+        <v>915</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>1064</v>
+        <v>918</v>
       </c>
       <c r="B407" t="s">
-        <v>1065</v>
+        <v>919</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>995</v>
+        <v>330</v>
       </c>
       <c r="B408" t="s">
-        <v>996</v>
+        <v>532</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>991</v>
+        <v>1064</v>
       </c>
       <c r="B409" t="s">
-        <v>992</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="B410" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>82</v>
+        <v>991</v>
       </c>
       <c r="B411" t="s">
-        <v>533</v>
+        <v>992</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>772</v>
+        <v>993</v>
       </c>
       <c r="B412" t="s">
-        <v>773</v>
+        <v>994</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="B413" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>654</v>
+        <v>772</v>
       </c>
       <c r="B414" t="s">
-        <v>735</v>
+        <v>773</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>821</v>
+        <v>197</v>
       </c>
       <c r="B415" t="s">
-        <v>822</v>
+        <v>534</v>
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>1066</v>
+        <v>654</v>
       </c>
       <c r="B416" t="s">
-        <v>1067</v>
+        <v>735</v>
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>3</v>
+        <v>821</v>
       </c>
       <c r="B417" t="s">
-        <v>4</v>
+        <v>822</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>958</v>
+        <v>1066</v>
       </c>
       <c r="B418" t="s">
-        <v>4</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>959</v>
+        <v>3</v>
       </c>
       <c r="B419" t="s">
         <v>4</v>
@@ -7746,2041 +7758,2057 @@
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>664</v>
+        <v>958</v>
       </c>
       <c r="B420" t="s">
-        <v>736</v>
+        <v>4</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>1298</v>
+        <v>959</v>
       </c>
       <c r="B421" t="s">
-        <v>1299</v>
+        <v>4</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>770</v>
+        <v>664</v>
       </c>
       <c r="B422" t="s">
-        <v>771</v>
+        <v>736</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>85</v>
+        <v>1298</v>
       </c>
       <c r="B423" t="s">
-        <v>535</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>1060</v>
+        <v>770</v>
       </c>
       <c r="B424" t="s">
-        <v>1061</v>
+        <v>771</v>
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>829</v>
+        <v>85</v>
       </c>
       <c r="B425" t="s">
-        <v>830</v>
+        <v>535</v>
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>809</v>
+        <v>1060</v>
       </c>
       <c r="B426" t="s">
-        <v>810</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>187</v>
+        <v>829</v>
       </c>
       <c r="B427" t="s">
-        <v>536</v>
+        <v>830</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>827</v>
+        <v>809</v>
       </c>
       <c r="B428" t="s">
-        <v>828</v>
+        <v>810</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>934</v>
+        <v>187</v>
       </c>
       <c r="B429" t="s">
-        <v>1124</v>
+        <v>536</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>863</v>
+        <v>827</v>
       </c>
       <c r="B430" t="s">
-        <v>864</v>
+        <v>828</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>1044</v>
+        <v>934</v>
       </c>
       <c r="B431" t="s">
-        <v>1045</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>798</v>
+        <v>863</v>
       </c>
       <c r="B432" t="s">
-        <v>1125</v>
+        <v>864</v>
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>797</v>
+        <v>1044</v>
       </c>
       <c r="B433" t="s">
-        <v>1126</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>13</v>
+        <v>798</v>
       </c>
       <c r="B434" t="s">
-        <v>14</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>817</v>
+        <v>797</v>
       </c>
       <c r="B435" t="s">
-        <v>818</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>1228</v>
+        <v>13</v>
       </c>
       <c r="B436" t="s">
-        <v>1229</v>
+        <v>14</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>186</v>
+        <v>817</v>
       </c>
       <c r="B437" t="s">
-        <v>537</v>
+        <v>818</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>811</v>
+        <v>1228</v>
       </c>
       <c r="B438" t="s">
-        <v>812</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>320</v>
+        <v>186</v>
       </c>
       <c r="B439" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>656</v>
+        <v>811</v>
       </c>
       <c r="B440" t="s">
-        <v>737</v>
+        <v>812</v>
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>855</v>
+        <v>320</v>
       </c>
       <c r="B441" t="s">
-        <v>856</v>
+        <v>538</v>
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B442" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>653</v>
+        <v>855</v>
       </c>
       <c r="B443" t="s">
-        <v>739</v>
+        <v>856</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>1200</v>
+        <v>658</v>
       </c>
       <c r="B444" t="s">
-        <v>1201</v>
+        <v>738</v>
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>256</v>
+        <v>653</v>
       </c>
       <c r="B445" t="s">
-        <v>539</v>
+        <v>739</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>260</v>
+        <v>1200</v>
       </c>
       <c r="B446" t="s">
-        <v>540</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B447" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>188</v>
+        <v>260</v>
       </c>
       <c r="B448" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>190</v>
+        <v>261</v>
       </c>
       <c r="B449" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>936</v>
+        <v>188</v>
       </c>
       <c r="B450" t="s">
-        <v>937</v>
+        <v>542</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>1031</v>
+        <v>190</v>
       </c>
       <c r="B451" t="s">
-        <v>1032</v>
+        <v>543</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>1216</v>
+        <v>936</v>
       </c>
       <c r="B452" t="s">
-        <v>1217</v>
+        <v>937</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>209</v>
+        <v>1031</v>
       </c>
       <c r="B453" t="s">
-        <v>544</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>1308</v>
+        <v>1216</v>
       </c>
       <c r="B454" t="s">
-        <v>1309</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>851</v>
+        <v>209</v>
       </c>
       <c r="B455" t="s">
-        <v>852</v>
+        <v>544</v>
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>143</v>
+        <v>1308</v>
       </c>
       <c r="B456" t="s">
-        <v>545</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>140</v>
+        <v>851</v>
       </c>
       <c r="B457" t="s">
-        <v>546</v>
+        <v>852</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>1196</v>
+        <v>143</v>
       </c>
       <c r="B458" t="s">
-        <v>1197</v>
+        <v>545</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>1296</v>
+        <v>140</v>
       </c>
       <c r="B459" t="s">
-        <v>1297</v>
+        <v>546</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>254</v>
+        <v>1196</v>
       </c>
       <c r="B460" t="s">
-        <v>547</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>331</v>
+        <v>1296</v>
       </c>
       <c r="B461" t="s">
-        <v>548</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>210</v>
+        <v>254</v>
       </c>
       <c r="B462" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>234</v>
+        <v>331</v>
       </c>
       <c r="B463" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>73</v>
+        <v>210</v>
       </c>
       <c r="B464" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>342</v>
+        <v>234</v>
       </c>
       <c r="B465" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>308</v>
+        <v>73</v>
       </c>
       <c r="B466" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>843</v>
+        <v>342</v>
       </c>
       <c r="B467" t="s">
-        <v>844</v>
+        <v>552</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>845</v>
+        <v>308</v>
       </c>
       <c r="B468" t="s">
-        <v>846</v>
+        <v>553</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>220</v>
+        <v>843</v>
       </c>
       <c r="B469" t="s">
-        <v>554</v>
+        <v>844</v>
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>909</v>
+        <v>845</v>
       </c>
       <c r="B470" t="s">
-        <v>910</v>
+        <v>846</v>
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>963</v>
+        <v>220</v>
       </c>
       <c r="B471" t="s">
-        <v>964</v>
+        <v>554</v>
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>1181</v>
+        <v>909</v>
       </c>
       <c r="B472" t="s">
-        <v>1182</v>
+        <v>910</v>
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>227</v>
+        <v>963</v>
       </c>
       <c r="B473" t="s">
-        <v>555</v>
+        <v>964</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>334</v>
+        <v>1181</v>
       </c>
       <c r="B474" t="s">
-        <v>1154</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>971</v>
+        <v>227</v>
       </c>
       <c r="B475" t="s">
-        <v>972</v>
+        <v>555</v>
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>778</v>
+        <v>334</v>
       </c>
       <c r="B476" t="s">
-        <v>779</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>294</v>
+        <v>971</v>
       </c>
       <c r="B477" t="s">
-        <v>556</v>
+        <v>972</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>952</v>
+        <v>778</v>
       </c>
       <c r="B478" t="s">
-        <v>953</v>
+        <v>779</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>339</v>
+        <v>294</v>
       </c>
       <c r="B479" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>780</v>
+        <v>952</v>
       </c>
       <c r="B480" t="s">
-        <v>779</v>
+        <v>953</v>
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>1312</v>
+        <v>339</v>
       </c>
       <c r="B481" t="s">
-        <v>1313</v>
+        <v>557</v>
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>340</v>
+        <v>780</v>
       </c>
       <c r="B482" t="s">
-        <v>558</v>
+        <v>779</v>
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>341</v>
+        <v>1312</v>
       </c>
       <c r="B483" t="s">
-        <v>559</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>645</v>
+        <v>340</v>
       </c>
       <c r="B484" t="s">
-        <v>740</v>
+        <v>558</v>
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>39</v>
+        <v>341</v>
       </c>
       <c r="B485" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>38</v>
+        <v>645</v>
       </c>
       <c r="B486" t="s">
-        <v>1123</v>
+        <v>740</v>
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>343</v>
+        <v>39</v>
       </c>
       <c r="B487" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="B488" t="s">
-        <v>562</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>1029</v>
+        <v>343</v>
       </c>
       <c r="B489" t="s">
-        <v>1030</v>
+        <v>561</v>
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>903</v>
+        <v>107</v>
       </c>
       <c r="B490" t="s">
-        <v>904</v>
+        <v>562</v>
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>117</v>
+        <v>1029</v>
       </c>
       <c r="B491" t="s">
-        <v>563</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>1025</v>
+        <v>903</v>
       </c>
       <c r="B492" t="s">
-        <v>1026</v>
+        <v>904</v>
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="B493" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>99</v>
+        <v>1025</v>
       </c>
       <c r="B494" t="s">
-        <v>565</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>666</v>
+        <v>98</v>
       </c>
       <c r="B495" t="s">
-        <v>741</v>
+        <v>564</v>
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>1101</v>
+        <v>99</v>
       </c>
       <c r="B496" t="s">
-        <v>1024</v>
+        <v>565</v>
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>823</v>
+        <v>666</v>
       </c>
       <c r="B497" t="s">
-        <v>824</v>
+        <v>741</v>
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>113</v>
+        <v>1101</v>
       </c>
       <c r="B498" t="s">
-        <v>566</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>889</v>
+        <v>823</v>
       </c>
       <c r="B499" t="s">
-        <v>890</v>
+        <v>824</v>
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="B500" t="s">
-        <v>1122</v>
+        <v>566</v>
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>290</v>
+        <v>889</v>
       </c>
       <c r="B501" t="s">
-        <v>567</v>
+        <v>890</v>
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>299</v>
+        <v>45</v>
       </c>
       <c r="B502" t="s">
-        <v>568</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>47</v>
+        <v>290</v>
       </c>
       <c r="B503" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>847</v>
+        <v>299</v>
       </c>
       <c r="B504" t="s">
-        <v>848</v>
+        <v>568</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B505" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>871</v>
+        <v>847</v>
       </c>
       <c r="B506" t="s">
-        <v>872</v>
+        <v>848</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="B507" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>853</v>
+        <v>871</v>
       </c>
       <c r="B508" t="s">
-        <v>854</v>
+        <v>872</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="B509" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>1078</v>
+        <v>853</v>
       </c>
       <c r="B510" t="s">
-        <v>1079</v>
+        <v>854</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="B511" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>316</v>
+        <v>1078</v>
       </c>
       <c r="B512" t="s">
-        <v>574</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>29</v>
+        <v>176</v>
       </c>
       <c r="B513" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>1018</v>
+        <v>316</v>
       </c>
       <c r="B514" t="s">
-        <v>1019</v>
+        <v>574</v>
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>1224</v>
+        <v>29</v>
       </c>
       <c r="B515" t="s">
-        <v>1225</v>
+        <v>575</v>
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>293</v>
+        <v>1018</v>
       </c>
       <c r="B516" t="s">
-        <v>576</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>981</v>
+        <v>1224</v>
       </c>
       <c r="B517" t="s">
-        <v>982</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="B518" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>1003</v>
+        <v>981</v>
       </c>
       <c r="B519" t="s">
-        <v>1004</v>
+        <v>982</v>
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>1007</v>
+        <v>301</v>
       </c>
       <c r="B520" t="s">
-        <v>1008</v>
+        <v>577</v>
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>75</v>
+        <v>1003</v>
       </c>
       <c r="B521" t="s">
-        <v>578</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="522" spans="1:2" 